--- a/attendance_sheet.xlsx
+++ b/attendance_sheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\repositary\3rd_Year_5th_Semester\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B5C3BD9-963D-46A6-B30D-D6C9A0801CC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F1011ED-CB81-47A3-BDD7-EA4E173CE3BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{EB654061-A886-47D1-BF86-9B1A84FCE7FB}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="810" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="818" uniqueCount="71">
   <si>
     <t>Date</t>
   </si>
@@ -247,6 +247,9 @@
   </si>
   <si>
     <t xml:space="preserve"> 1class p</t>
+  </si>
+  <si>
+    <t>1 class  p</t>
   </si>
 </sst>
 </file>
@@ -521,23 +524,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -557,11 +548,23 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -964,14 +967,14 @@
       <c r="C8" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D8" s="37" t="s">
+      <c r="D8" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="E8" s="37"/>
-      <c r="F8" s="37"/>
-      <c r="G8" s="37"/>
-      <c r="H8" s="37"/>
-      <c r="I8" s="37"/>
+      <c r="E8" s="25"/>
+      <c r="F8" s="25"/>
+      <c r="G8" s="25"/>
+      <c r="H8" s="25"/>
+      <c r="I8" s="25"/>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B9" s="4">
@@ -980,14 +983,14 @@
       <c r="C9" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D9" s="37" t="s">
+      <c r="D9" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="E9" s="37"/>
-      <c r="F9" s="37"/>
-      <c r="G9" s="37"/>
-      <c r="H9" s="37"/>
-      <c r="I9" s="37"/>
+      <c r="E9" s="25"/>
+      <c r="F9" s="25"/>
+      <c r="G9" s="25"/>
+      <c r="H9" s="25"/>
+      <c r="I9" s="25"/>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B10" s="4">
@@ -996,14 +999,14 @@
       <c r="C10" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D10" s="37" t="s">
+      <c r="D10" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="E10" s="37"/>
-      <c r="F10" s="37"/>
-      <c r="G10" s="37"/>
-      <c r="H10" s="37"/>
-      <c r="I10" s="37"/>
+      <c r="E10" s="25"/>
+      <c r="F10" s="25"/>
+      <c r="G10" s="25"/>
+      <c r="H10" s="25"/>
+      <c r="I10" s="25"/>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B11" s="4">
@@ -1012,14 +1015,14 @@
       <c r="C11" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D11" s="37" t="s">
+      <c r="D11" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="E11" s="37"/>
-      <c r="F11" s="37"/>
-      <c r="G11" s="37"/>
-      <c r="H11" s="37"/>
-      <c r="I11" s="37"/>
+      <c r="E11" s="25"/>
+      <c r="F11" s="25"/>
+      <c r="G11" s="25"/>
+      <c r="H11" s="25"/>
+      <c r="I11" s="25"/>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B12" s="4">
@@ -1063,10 +1066,10 @@
       <c r="F13" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="G13" s="37" t="s">
+      <c r="G13" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="H13" s="37"/>
+      <c r="H13" s="25"/>
       <c r="I13" s="1" t="s">
         <v>14</v>
       </c>
@@ -1078,14 +1081,14 @@
       <c r="C14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D14" s="37" t="s">
+      <c r="D14" s="25" t="s">
         <v>19</v>
       </c>
-      <c r="E14" s="37"/>
-      <c r="F14" s="37"/>
-      <c r="G14" s="37"/>
-      <c r="H14" s="37"/>
-      <c r="I14" s="37"/>
+      <c r="E14" s="25"/>
+      <c r="F14" s="25"/>
+      <c r="G14" s="25"/>
+      <c r="H14" s="25"/>
+      <c r="I14" s="25"/>
     </row>
     <row r="15" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B15" s="4">
@@ -1172,14 +1175,14 @@
       <c r="C18" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D18" s="37" t="s">
+      <c r="D18" s="25" t="s">
         <v>23</v>
       </c>
-      <c r="E18" s="37"/>
-      <c r="F18" s="37"/>
-      <c r="G18" s="37"/>
-      <c r="H18" s="37"/>
-      <c r="I18" s="37"/>
+      <c r="E18" s="25"/>
+      <c r="F18" s="25"/>
+      <c r="G18" s="25"/>
+      <c r="H18" s="25"/>
+      <c r="I18" s="25"/>
     </row>
     <row r="19" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B19" s="4">
@@ -1188,14 +1191,14 @@
       <c r="C19" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D19" s="37" t="s">
+      <c r="D19" s="25" t="s">
         <v>23</v>
       </c>
-      <c r="E19" s="37"/>
-      <c r="F19" s="37"/>
-      <c r="G19" s="37"/>
-      <c r="H19" s="37"/>
-      <c r="I19" s="37"/>
+      <c r="E19" s="25"/>
+      <c r="F19" s="25"/>
+      <c r="G19" s="25"/>
+      <c r="H19" s="25"/>
+      <c r="I19" s="25"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B20" s="4">
@@ -1213,10 +1216,10 @@
       <c r="F20" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G20" s="37" t="s">
+      <c r="G20" s="25" t="s">
         <v>15</v>
       </c>
-      <c r="H20" s="37"/>
+      <c r="H20" s="25"/>
       <c r="I20" s="1" t="s">
         <v>14</v>
       </c>
@@ -1332,14 +1335,14 @@
       <c r="C25" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D25" s="37" t="s">
+      <c r="D25" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="E25" s="37"/>
-      <c r="F25" s="37"/>
-      <c r="G25" s="37"/>
-      <c r="H25" s="37"/>
-      <c r="I25" s="37"/>
+      <c r="E25" s="25"/>
+      <c r="F25" s="25"/>
+      <c r="G25" s="25"/>
+      <c r="H25" s="25"/>
+      <c r="I25" s="25"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B26" s="4">
@@ -1383,10 +1386,10 @@
       <c r="F27" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G27" s="37" t="s">
+      <c r="G27" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="H27" s="37"/>
+      <c r="H27" s="25"/>
       <c r="I27" s="1" t="s">
         <v>14</v>
       </c>
@@ -1450,14 +1453,14 @@
       <c r="C30" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D30" s="36" t="s">
+      <c r="D30" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="E30" s="36"/>
-      <c r="F30" s="36"/>
-      <c r="G30" s="36"/>
-      <c r="H30" s="36"/>
-      <c r="I30" s="36"/>
+      <c r="E30" s="24"/>
+      <c r="F30" s="24"/>
+      <c r="G30" s="24"/>
+      <c r="H30" s="24"/>
+      <c r="I30" s="24"/>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B31" s="4">
@@ -1466,14 +1469,14 @@
       <c r="C31" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D31" s="36" t="s">
+      <c r="D31" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="E31" s="36"/>
-      <c r="F31" s="36"/>
-      <c r="G31" s="36"/>
-      <c r="H31" s="36"/>
-      <c r="I31" s="36"/>
+      <c r="E31" s="24"/>
+      <c r="F31" s="24"/>
+      <c r="G31" s="24"/>
+      <c r="H31" s="24"/>
+      <c r="I31" s="24"/>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B32" s="4">
@@ -1508,14 +1511,14 @@
       <c r="C33" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D33" s="36" t="s">
+      <c r="D33" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="E33" s="36"/>
-      <c r="F33" s="36"/>
-      <c r="G33" s="36"/>
-      <c r="H33" s="36"/>
-      <c r="I33" s="36"/>
+      <c r="E33" s="24"/>
+      <c r="F33" s="24"/>
+      <c r="G33" s="24"/>
+      <c r="H33" s="24"/>
+      <c r="I33" s="24"/>
     </row>
     <row r="34" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B34" s="4">
@@ -1559,10 +1562,10 @@
       <c r="F35" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G35" s="36" t="s">
+      <c r="G35" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="H35" s="36"/>
+      <c r="H35" s="24"/>
       <c r="I35" s="1" t="s">
         <v>14</v>
       </c>
@@ -1678,14 +1681,14 @@
       <c r="C40" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D40" s="36" t="s">
+      <c r="D40" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="E40" s="36"/>
-      <c r="F40" s="36"/>
-      <c r="G40" s="36"/>
-      <c r="H40" s="36"/>
-      <c r="I40" s="36"/>
+      <c r="E40" s="24"/>
+      <c r="F40" s="24"/>
+      <c r="G40" s="24"/>
+      <c r="H40" s="24"/>
+      <c r="I40" s="24"/>
     </row>
     <row r="41" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B41" s="4">
@@ -1729,10 +1732,10 @@
       <c r="F42" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G42" s="36" t="s">
+      <c r="G42" s="24" t="s">
         <v>28</v>
       </c>
-      <c r="H42" s="36"/>
+      <c r="H42" s="24"/>
       <c r="I42" s="1" t="s">
         <v>15</v>
       </c>
@@ -1744,14 +1747,14 @@
       <c r="C43" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D43" s="36" t="s">
+      <c r="D43" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="E43" s="36"/>
-      <c r="F43" s="36"/>
-      <c r="G43" s="36"/>
-      <c r="H43" s="36"/>
-      <c r="I43" s="36"/>
+      <c r="E43" s="24"/>
+      <c r="F43" s="24"/>
+      <c r="G43" s="24"/>
+      <c r="H43" s="24"/>
+      <c r="I43" s="24"/>
     </row>
     <row r="44" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B44" s="4">
@@ -1815,14 +1818,14 @@
       <c r="C46" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D46" s="36" t="s">
+      <c r="D46" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="E46" s="36"/>
-      <c r="F46" s="36"/>
-      <c r="G46" s="36"/>
-      <c r="H46" s="36"/>
-      <c r="I46" s="36"/>
+      <c r="E46" s="24"/>
+      <c r="F46" s="24"/>
+      <c r="G46" s="24"/>
+      <c r="H46" s="24"/>
+      <c r="I46" s="24"/>
     </row>
     <row r="47" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B47" s="4">
@@ -3108,28 +3111,28 @@
       <c r="I111" s="20"/>
     </row>
     <row r="112" spans="2:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B112" s="30" t="s">
+      <c r="B112" s="26" t="s">
         <v>57</v>
       </c>
-      <c r="C112" s="31"/>
-      <c r="D112" s="31"/>
-      <c r="E112" s="31"/>
-      <c r="F112" s="31"/>
-      <c r="G112" s="31"/>
-      <c r="H112" s="31"/>
-      <c r="I112" s="31"/>
-      <c r="J112" s="32"/>
+      <c r="C112" s="27"/>
+      <c r="D112" s="27"/>
+      <c r="E112" s="27"/>
+      <c r="F112" s="27"/>
+      <c r="G112" s="27"/>
+      <c r="H112" s="27"/>
+      <c r="I112" s="27"/>
+      <c r="J112" s="28"/>
     </row>
     <row r="113" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B113" s="33"/>
-      <c r="C113" s="34"/>
-      <c r="D113" s="34"/>
-      <c r="E113" s="34"/>
-      <c r="F113" s="34"/>
-      <c r="G113" s="34"/>
-      <c r="H113" s="34"/>
-      <c r="I113" s="34"/>
-      <c r="J113" s="35"/>
+      <c r="B113" s="29"/>
+      <c r="C113" s="30"/>
+      <c r="D113" s="30"/>
+      <c r="E113" s="30"/>
+      <c r="F113" s="30"/>
+      <c r="G113" s="30"/>
+      <c r="H113" s="30"/>
+      <c r="I113" s="30"/>
+      <c r="J113" s="31"/>
     </row>
     <row r="114" spans="2:10" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B114" s="8" t="s">
@@ -4051,15 +4054,15 @@
       <c r="C149" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D149" s="24" t="s">
+      <c r="D149" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="E149" s="25"/>
-      <c r="F149" s="25"/>
-      <c r="G149" s="25"/>
-      <c r="H149" s="25"/>
-      <c r="I149" s="25"/>
-      <c r="J149" s="26"/>
+      <c r="E149" s="33"/>
+      <c r="F149" s="33"/>
+      <c r="G149" s="33"/>
+      <c r="H149" s="33"/>
+      <c r="I149" s="33"/>
+      <c r="J149" s="34"/>
     </row>
     <row r="150" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B150" s="4">
@@ -4068,13 +4071,13 @@
       <c r="C150" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D150" s="27"/>
-      <c r="E150" s="28"/>
-      <c r="F150" s="28"/>
-      <c r="G150" s="28"/>
-      <c r="H150" s="28"/>
-      <c r="I150" s="28"/>
-      <c r="J150" s="29"/>
+      <c r="D150" s="35"/>
+      <c r="E150" s="36"/>
+      <c r="F150" s="36"/>
+      <c r="G150" s="36"/>
+      <c r="H150" s="36"/>
+      <c r="I150" s="36"/>
+      <c r="J150" s="37"/>
     </row>
     <row r="151" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B151" s="4">
@@ -4482,15 +4485,33 @@
       </c>
     </row>
     <row r="166" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B166" s="3"/>
-      <c r="C166" s="3"/>
-      <c r="D166" s="3"/>
-      <c r="E166" s="3"/>
-      <c r="F166" s="3"/>
-      <c r="G166" s="3"/>
-      <c r="H166" s="3"/>
-      <c r="I166" s="1"/>
-      <c r="J166" s="1"/>
+      <c r="B166" s="4">
+        <v>45864</v>
+      </c>
+      <c r="C166" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D166" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E166" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F166" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="G166" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H166" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I166" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="J166" s="1" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="167" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B167" s="3"/>
@@ -7244,6 +7265,74 @@
     </row>
   </sheetData>
   <mergeCells count="84">
+    <mergeCell ref="D164:J164"/>
+    <mergeCell ref="D157:J157"/>
+    <mergeCell ref="D143:J143"/>
+    <mergeCell ref="D135:J135"/>
+    <mergeCell ref="F127:J127"/>
+    <mergeCell ref="D107:E107"/>
+    <mergeCell ref="F118:J118"/>
+    <mergeCell ref="G152:I152"/>
+    <mergeCell ref="D149:J150"/>
+    <mergeCell ref="G146:J146"/>
+    <mergeCell ref="D106:E106"/>
+    <mergeCell ref="D99:G99"/>
+    <mergeCell ref="G126:I126"/>
+    <mergeCell ref="F125:J125"/>
+    <mergeCell ref="D128:J128"/>
+    <mergeCell ref="D103:E103"/>
+    <mergeCell ref="D104:E104"/>
+    <mergeCell ref="D105:E105"/>
+    <mergeCell ref="G100:I100"/>
+    <mergeCell ref="B101:I101"/>
+    <mergeCell ref="D108:E108"/>
+    <mergeCell ref="B112:J113"/>
+    <mergeCell ref="G124:J124"/>
+    <mergeCell ref="D120:H120"/>
+    <mergeCell ref="G123:J123"/>
+    <mergeCell ref="D121:J121"/>
+    <mergeCell ref="D30:I30"/>
+    <mergeCell ref="G80:H80"/>
+    <mergeCell ref="D78:I78"/>
+    <mergeCell ref="G71:H71"/>
+    <mergeCell ref="D76:I76"/>
+    <mergeCell ref="D66:H66"/>
+    <mergeCell ref="D77:I77"/>
+    <mergeCell ref="D73:I73"/>
+    <mergeCell ref="D70:E70"/>
+    <mergeCell ref="D31:I31"/>
+    <mergeCell ref="G35:H35"/>
+    <mergeCell ref="D40:I40"/>
+    <mergeCell ref="D33:I33"/>
+    <mergeCell ref="D46:I46"/>
+    <mergeCell ref="D43:I43"/>
+    <mergeCell ref="G57:H57"/>
+    <mergeCell ref="D14:I14"/>
+    <mergeCell ref="G27:H27"/>
+    <mergeCell ref="D25:I25"/>
+    <mergeCell ref="G20:H20"/>
+    <mergeCell ref="D19:I19"/>
+    <mergeCell ref="D18:I18"/>
+    <mergeCell ref="D8:I8"/>
+    <mergeCell ref="D9:I9"/>
+    <mergeCell ref="D10:I10"/>
+    <mergeCell ref="D11:I11"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="G81:H81"/>
+    <mergeCell ref="D67:F67"/>
+    <mergeCell ref="F68:I68"/>
+    <mergeCell ref="D87:E87"/>
+    <mergeCell ref="G87:I87"/>
+    <mergeCell ref="D74:F74"/>
+    <mergeCell ref="D84:I84"/>
+    <mergeCell ref="D69:I69"/>
+    <mergeCell ref="G42:H42"/>
+    <mergeCell ref="D60:I60"/>
+    <mergeCell ref="D62:I62"/>
+    <mergeCell ref="D61:I61"/>
+    <mergeCell ref="G49:H49"/>
+    <mergeCell ref="D47:I47"/>
+    <mergeCell ref="D55:I55"/>
     <mergeCell ref="D98:I98"/>
     <mergeCell ref="D94:I94"/>
     <mergeCell ref="H89:I89"/>
@@ -7260,74 +7349,6 @@
     <mergeCell ref="E86:G86"/>
     <mergeCell ref="D88:I88"/>
     <mergeCell ref="H67:I67"/>
-    <mergeCell ref="G42:H42"/>
-    <mergeCell ref="D60:I60"/>
-    <mergeCell ref="D62:I62"/>
-    <mergeCell ref="D61:I61"/>
-    <mergeCell ref="G49:H49"/>
-    <mergeCell ref="D47:I47"/>
-    <mergeCell ref="D55:I55"/>
-    <mergeCell ref="G81:H81"/>
-    <mergeCell ref="D67:F67"/>
-    <mergeCell ref="F68:I68"/>
-    <mergeCell ref="D87:E87"/>
-    <mergeCell ref="G87:I87"/>
-    <mergeCell ref="D74:F74"/>
-    <mergeCell ref="D84:I84"/>
-    <mergeCell ref="D69:I69"/>
-    <mergeCell ref="D8:I8"/>
-    <mergeCell ref="D9:I9"/>
-    <mergeCell ref="D10:I10"/>
-    <mergeCell ref="D11:I11"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="D14:I14"/>
-    <mergeCell ref="G27:H27"/>
-    <mergeCell ref="D25:I25"/>
-    <mergeCell ref="G20:H20"/>
-    <mergeCell ref="D19:I19"/>
-    <mergeCell ref="D18:I18"/>
-    <mergeCell ref="D30:I30"/>
-    <mergeCell ref="G80:H80"/>
-    <mergeCell ref="D78:I78"/>
-    <mergeCell ref="G71:H71"/>
-    <mergeCell ref="D76:I76"/>
-    <mergeCell ref="D66:H66"/>
-    <mergeCell ref="D77:I77"/>
-    <mergeCell ref="D73:I73"/>
-    <mergeCell ref="D70:E70"/>
-    <mergeCell ref="D31:I31"/>
-    <mergeCell ref="G35:H35"/>
-    <mergeCell ref="D40:I40"/>
-    <mergeCell ref="D33:I33"/>
-    <mergeCell ref="D46:I46"/>
-    <mergeCell ref="D43:I43"/>
-    <mergeCell ref="G57:H57"/>
-    <mergeCell ref="D106:E106"/>
-    <mergeCell ref="D99:G99"/>
-    <mergeCell ref="G126:I126"/>
-    <mergeCell ref="F125:J125"/>
-    <mergeCell ref="D128:J128"/>
-    <mergeCell ref="D103:E103"/>
-    <mergeCell ref="D104:E104"/>
-    <mergeCell ref="D105:E105"/>
-    <mergeCell ref="G100:I100"/>
-    <mergeCell ref="B101:I101"/>
-    <mergeCell ref="D108:E108"/>
-    <mergeCell ref="B112:J113"/>
-    <mergeCell ref="G124:J124"/>
-    <mergeCell ref="D120:H120"/>
-    <mergeCell ref="G123:J123"/>
-    <mergeCell ref="D121:J121"/>
-    <mergeCell ref="D107:E107"/>
-    <mergeCell ref="F118:J118"/>
-    <mergeCell ref="G152:I152"/>
-    <mergeCell ref="D149:J150"/>
-    <mergeCell ref="G146:J146"/>
-    <mergeCell ref="D164:J164"/>
-    <mergeCell ref="D157:J157"/>
-    <mergeCell ref="D143:J143"/>
-    <mergeCell ref="D135:J135"/>
-    <mergeCell ref="F127:J127"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/attendance_sheet.xlsx
+++ b/attendance_sheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\repositary\3rd_Year_5th_Semester\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F1011ED-CB81-47A3-BDD7-EA4E173CE3BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57CDE1BB-9B9F-43C2-8A85-189B090A98E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{EB654061-A886-47D1-BF86-9B1A84FCE7FB}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="818" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="820" uniqueCount="72">
   <si>
     <t>Date</t>
   </si>
@@ -250,6 +250,9 @@
   </si>
   <si>
     <t>1 class  p</t>
+  </si>
+  <si>
+    <t>DAY</t>
   </si>
 </sst>
 </file>
@@ -524,11 +527,23 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -548,23 +563,11 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -967,14 +970,14 @@
       <c r="C8" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D8" s="25" t="s">
+      <c r="D8" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="E8" s="25"/>
-      <c r="F8" s="25"/>
-      <c r="G8" s="25"/>
-      <c r="H8" s="25"/>
-      <c r="I8" s="25"/>
+      <c r="E8" s="37"/>
+      <c r="F8" s="37"/>
+      <c r="G8" s="37"/>
+      <c r="H8" s="37"/>
+      <c r="I8" s="37"/>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B9" s="4">
@@ -983,14 +986,14 @@
       <c r="C9" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D9" s="25" t="s">
+      <c r="D9" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="E9" s="25"/>
-      <c r="F9" s="25"/>
-      <c r="G9" s="25"/>
-      <c r="H9" s="25"/>
-      <c r="I9" s="25"/>
+      <c r="E9" s="37"/>
+      <c r="F9" s="37"/>
+      <c r="G9" s="37"/>
+      <c r="H9" s="37"/>
+      <c r="I9" s="37"/>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B10" s="4">
@@ -999,14 +1002,14 @@
       <c r="C10" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D10" s="25" t="s">
+      <c r="D10" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="E10" s="25"/>
-      <c r="F10" s="25"/>
-      <c r="G10" s="25"/>
-      <c r="H10" s="25"/>
-      <c r="I10" s="25"/>
+      <c r="E10" s="37"/>
+      <c r="F10" s="37"/>
+      <c r="G10" s="37"/>
+      <c r="H10" s="37"/>
+      <c r="I10" s="37"/>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B11" s="4">
@@ -1015,14 +1018,14 @@
       <c r="C11" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D11" s="25" t="s">
+      <c r="D11" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="E11" s="25"/>
-      <c r="F11" s="25"/>
-      <c r="G11" s="25"/>
-      <c r="H11" s="25"/>
-      <c r="I11" s="25"/>
+      <c r="E11" s="37"/>
+      <c r="F11" s="37"/>
+      <c r="G11" s="37"/>
+      <c r="H11" s="37"/>
+      <c r="I11" s="37"/>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B12" s="4">
@@ -1066,10 +1069,10 @@
       <c r="F13" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="G13" s="25" t="s">
+      <c r="G13" s="37" t="s">
         <v>18</v>
       </c>
-      <c r="H13" s="25"/>
+      <c r="H13" s="37"/>
       <c r="I13" s="1" t="s">
         <v>14</v>
       </c>
@@ -1081,14 +1084,14 @@
       <c r="C14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D14" s="25" t="s">
+      <c r="D14" s="37" t="s">
         <v>19</v>
       </c>
-      <c r="E14" s="25"/>
-      <c r="F14" s="25"/>
-      <c r="G14" s="25"/>
-      <c r="H14" s="25"/>
-      <c r="I14" s="25"/>
+      <c r="E14" s="37"/>
+      <c r="F14" s="37"/>
+      <c r="G14" s="37"/>
+      <c r="H14" s="37"/>
+      <c r="I14" s="37"/>
     </row>
     <row r="15" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B15" s="4">
@@ -1175,14 +1178,14 @@
       <c r="C18" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D18" s="25" t="s">
+      <c r="D18" s="37" t="s">
         <v>23</v>
       </c>
-      <c r="E18" s="25"/>
-      <c r="F18" s="25"/>
-      <c r="G18" s="25"/>
-      <c r="H18" s="25"/>
-      <c r="I18" s="25"/>
+      <c r="E18" s="37"/>
+      <c r="F18" s="37"/>
+      <c r="G18" s="37"/>
+      <c r="H18" s="37"/>
+      <c r="I18" s="37"/>
     </row>
     <row r="19" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B19" s="4">
@@ -1191,14 +1194,14 @@
       <c r="C19" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D19" s="25" t="s">
+      <c r="D19" s="37" t="s">
         <v>23</v>
       </c>
-      <c r="E19" s="25"/>
-      <c r="F19" s="25"/>
-      <c r="G19" s="25"/>
-      <c r="H19" s="25"/>
-      <c r="I19" s="25"/>
+      <c r="E19" s="37"/>
+      <c r="F19" s="37"/>
+      <c r="G19" s="37"/>
+      <c r="H19" s="37"/>
+      <c r="I19" s="37"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B20" s="4">
@@ -1216,10 +1219,10 @@
       <c r="F20" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G20" s="25" t="s">
+      <c r="G20" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="H20" s="25"/>
+      <c r="H20" s="37"/>
       <c r="I20" s="1" t="s">
         <v>14</v>
       </c>
@@ -1335,14 +1338,14 @@
       <c r="C25" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D25" s="25" t="s">
+      <c r="D25" s="37" t="s">
         <v>26</v>
       </c>
-      <c r="E25" s="25"/>
-      <c r="F25" s="25"/>
-      <c r="G25" s="25"/>
-      <c r="H25" s="25"/>
-      <c r="I25" s="25"/>
+      <c r="E25" s="37"/>
+      <c r="F25" s="37"/>
+      <c r="G25" s="37"/>
+      <c r="H25" s="37"/>
+      <c r="I25" s="37"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B26" s="4">
@@ -1386,10 +1389,10 @@
       <c r="F27" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G27" s="25" t="s">
+      <c r="G27" s="37" t="s">
         <v>18</v>
       </c>
-      <c r="H27" s="25"/>
+      <c r="H27" s="37"/>
       <c r="I27" s="1" t="s">
         <v>14</v>
       </c>
@@ -1453,14 +1456,14 @@
       <c r="C30" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D30" s="24" t="s">
+      <c r="D30" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="E30" s="24"/>
-      <c r="F30" s="24"/>
-      <c r="G30" s="24"/>
-      <c r="H30" s="24"/>
-      <c r="I30" s="24"/>
+      <c r="E30" s="36"/>
+      <c r="F30" s="36"/>
+      <c r="G30" s="36"/>
+      <c r="H30" s="36"/>
+      <c r="I30" s="36"/>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B31" s="4">
@@ -1469,14 +1472,14 @@
       <c r="C31" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D31" s="24" t="s">
+      <c r="D31" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="E31" s="24"/>
-      <c r="F31" s="24"/>
-      <c r="G31" s="24"/>
-      <c r="H31" s="24"/>
-      <c r="I31" s="24"/>
+      <c r="E31" s="36"/>
+      <c r="F31" s="36"/>
+      <c r="G31" s="36"/>
+      <c r="H31" s="36"/>
+      <c r="I31" s="36"/>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B32" s="4">
@@ -1511,14 +1514,14 @@
       <c r="C33" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D33" s="24" t="s">
+      <c r="D33" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="E33" s="24"/>
-      <c r="F33" s="24"/>
-      <c r="G33" s="24"/>
-      <c r="H33" s="24"/>
-      <c r="I33" s="24"/>
+      <c r="E33" s="36"/>
+      <c r="F33" s="36"/>
+      <c r="G33" s="36"/>
+      <c r="H33" s="36"/>
+      <c r="I33" s="36"/>
     </row>
     <row r="34" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B34" s="4">
@@ -1562,10 +1565,10 @@
       <c r="F35" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G35" s="24" t="s">
+      <c r="G35" s="36" t="s">
         <v>18</v>
       </c>
-      <c r="H35" s="24"/>
+      <c r="H35" s="36"/>
       <c r="I35" s="1" t="s">
         <v>14</v>
       </c>
@@ -1681,14 +1684,14 @@
       <c r="C40" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D40" s="24" t="s">
+      <c r="D40" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="E40" s="24"/>
-      <c r="F40" s="24"/>
-      <c r="G40" s="24"/>
-      <c r="H40" s="24"/>
-      <c r="I40" s="24"/>
+      <c r="E40" s="36"/>
+      <c r="F40" s="36"/>
+      <c r="G40" s="36"/>
+      <c r="H40" s="36"/>
+      <c r="I40" s="36"/>
     </row>
     <row r="41" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B41" s="4">
@@ -1732,10 +1735,10 @@
       <c r="F42" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G42" s="24" t="s">
+      <c r="G42" s="36" t="s">
         <v>28</v>
       </c>
-      <c r="H42" s="24"/>
+      <c r="H42" s="36"/>
       <c r="I42" s="1" t="s">
         <v>15</v>
       </c>
@@ -1747,14 +1750,14 @@
       <c r="C43" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D43" s="24" t="s">
+      <c r="D43" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="E43" s="24"/>
-      <c r="F43" s="24"/>
-      <c r="G43" s="24"/>
-      <c r="H43" s="24"/>
-      <c r="I43" s="24"/>
+      <c r="E43" s="36"/>
+      <c r="F43" s="36"/>
+      <c r="G43" s="36"/>
+      <c r="H43" s="36"/>
+      <c r="I43" s="36"/>
     </row>
     <row r="44" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B44" s="4">
@@ -1818,14 +1821,14 @@
       <c r="C46" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D46" s="24" t="s">
+      <c r="D46" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="E46" s="24"/>
-      <c r="F46" s="24"/>
-      <c r="G46" s="24"/>
-      <c r="H46" s="24"/>
-      <c r="I46" s="24"/>
+      <c r="E46" s="36"/>
+      <c r="F46" s="36"/>
+      <c r="G46" s="36"/>
+      <c r="H46" s="36"/>
+      <c r="I46" s="36"/>
     </row>
     <row r="47" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B47" s="4">
@@ -3111,28 +3114,28 @@
       <c r="I111" s="20"/>
     </row>
     <row r="112" spans="2:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B112" s="26" t="s">
+      <c r="B112" s="30" t="s">
         <v>57</v>
       </c>
-      <c r="C112" s="27"/>
-      <c r="D112" s="27"/>
-      <c r="E112" s="27"/>
-      <c r="F112" s="27"/>
-      <c r="G112" s="27"/>
-      <c r="H112" s="27"/>
-      <c r="I112" s="27"/>
-      <c r="J112" s="28"/>
+      <c r="C112" s="31"/>
+      <c r="D112" s="31"/>
+      <c r="E112" s="31"/>
+      <c r="F112" s="31"/>
+      <c r="G112" s="31"/>
+      <c r="H112" s="31"/>
+      <c r="I112" s="31"/>
+      <c r="J112" s="32"/>
     </row>
     <row r="113" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B113" s="29"/>
-      <c r="C113" s="30"/>
-      <c r="D113" s="30"/>
-      <c r="E113" s="30"/>
-      <c r="F113" s="30"/>
-      <c r="G113" s="30"/>
-      <c r="H113" s="30"/>
-      <c r="I113" s="30"/>
-      <c r="J113" s="31"/>
+      <c r="B113" s="33"/>
+      <c r="C113" s="34"/>
+      <c r="D113" s="34"/>
+      <c r="E113" s="34"/>
+      <c r="F113" s="34"/>
+      <c r="G113" s="34"/>
+      <c r="H113" s="34"/>
+      <c r="I113" s="34"/>
+      <c r="J113" s="35"/>
     </row>
     <row r="114" spans="2:10" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B114" s="8" t="s">
@@ -4054,15 +4057,15 @@
       <c r="C149" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D149" s="32" t="s">
+      <c r="D149" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="E149" s="33"/>
-      <c r="F149" s="33"/>
-      <c r="G149" s="33"/>
-      <c r="H149" s="33"/>
-      <c r="I149" s="33"/>
-      <c r="J149" s="34"/>
+      <c r="E149" s="25"/>
+      <c r="F149" s="25"/>
+      <c r="G149" s="25"/>
+      <c r="H149" s="25"/>
+      <c r="I149" s="25"/>
+      <c r="J149" s="26"/>
     </row>
     <row r="150" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B150" s="4">
@@ -4071,13 +4074,13 @@
       <c r="C150" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D150" s="35"/>
-      <c r="E150" s="36"/>
-      <c r="F150" s="36"/>
-      <c r="G150" s="36"/>
-      <c r="H150" s="36"/>
-      <c r="I150" s="36"/>
-      <c r="J150" s="37"/>
+      <c r="D150" s="27"/>
+      <c r="E150" s="28"/>
+      <c r="F150" s="28"/>
+      <c r="G150" s="28"/>
+      <c r="H150" s="28"/>
+      <c r="I150" s="28"/>
+      <c r="J150" s="29"/>
     </row>
     <row r="151" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B151" s="4">
@@ -4514,8 +4517,12 @@
       </c>
     </row>
     <row r="167" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B167" s="3"/>
-      <c r="C167" s="3"/>
+      <c r="B167" s="4">
+        <v>45896</v>
+      </c>
+      <c r="C167" s="3" t="s">
+        <v>8</v>
+      </c>
       <c r="D167" s="3"/>
       <c r="E167" s="3"/>
       <c r="F167" s="3"/>
@@ -4536,7 +4543,9 @@
       <c r="J168" s="1"/>
     </row>
     <row r="169" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B169" s="3"/>
+      <c r="B169" s="3" t="s">
+        <v>71</v>
+      </c>
       <c r="C169" s="3"/>
       <c r="D169" s="3"/>
       <c r="E169" s="3"/>
@@ -7265,16 +7274,64 @@
     </row>
   </sheetData>
   <mergeCells count="84">
-    <mergeCell ref="D164:J164"/>
-    <mergeCell ref="D157:J157"/>
-    <mergeCell ref="D143:J143"/>
-    <mergeCell ref="D135:J135"/>
-    <mergeCell ref="F127:J127"/>
-    <mergeCell ref="D107:E107"/>
-    <mergeCell ref="F118:J118"/>
-    <mergeCell ref="G152:I152"/>
-    <mergeCell ref="D149:J150"/>
-    <mergeCell ref="G146:J146"/>
+    <mergeCell ref="D98:I98"/>
+    <mergeCell ref="D94:I94"/>
+    <mergeCell ref="H89:I89"/>
+    <mergeCell ref="D89:F89"/>
+    <mergeCell ref="G64:H64"/>
+    <mergeCell ref="D96:I96"/>
+    <mergeCell ref="D95:F95"/>
+    <mergeCell ref="G95:H95"/>
+    <mergeCell ref="D92:I92"/>
+    <mergeCell ref="D97:I97"/>
+    <mergeCell ref="D93:I93"/>
+    <mergeCell ref="D90:E90"/>
+    <mergeCell ref="D91:H91"/>
+    <mergeCell ref="E86:G86"/>
+    <mergeCell ref="D88:I88"/>
+    <mergeCell ref="H67:I67"/>
+    <mergeCell ref="G42:H42"/>
+    <mergeCell ref="D60:I60"/>
+    <mergeCell ref="D62:I62"/>
+    <mergeCell ref="D61:I61"/>
+    <mergeCell ref="G49:H49"/>
+    <mergeCell ref="D47:I47"/>
+    <mergeCell ref="D55:I55"/>
+    <mergeCell ref="G81:H81"/>
+    <mergeCell ref="D67:F67"/>
+    <mergeCell ref="F68:I68"/>
+    <mergeCell ref="D87:E87"/>
+    <mergeCell ref="G87:I87"/>
+    <mergeCell ref="D74:F74"/>
+    <mergeCell ref="D84:I84"/>
+    <mergeCell ref="D69:I69"/>
+    <mergeCell ref="D8:I8"/>
+    <mergeCell ref="D9:I9"/>
+    <mergeCell ref="D10:I10"/>
+    <mergeCell ref="D11:I11"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="D14:I14"/>
+    <mergeCell ref="G27:H27"/>
+    <mergeCell ref="D25:I25"/>
+    <mergeCell ref="G20:H20"/>
+    <mergeCell ref="D19:I19"/>
+    <mergeCell ref="D18:I18"/>
+    <mergeCell ref="D30:I30"/>
+    <mergeCell ref="G80:H80"/>
+    <mergeCell ref="D78:I78"/>
+    <mergeCell ref="G71:H71"/>
+    <mergeCell ref="D76:I76"/>
+    <mergeCell ref="D66:H66"/>
+    <mergeCell ref="D77:I77"/>
+    <mergeCell ref="D73:I73"/>
+    <mergeCell ref="D70:E70"/>
+    <mergeCell ref="D31:I31"/>
+    <mergeCell ref="G35:H35"/>
+    <mergeCell ref="D40:I40"/>
+    <mergeCell ref="D33:I33"/>
+    <mergeCell ref="D46:I46"/>
+    <mergeCell ref="D43:I43"/>
+    <mergeCell ref="G57:H57"/>
     <mergeCell ref="D106:E106"/>
     <mergeCell ref="D99:G99"/>
     <mergeCell ref="G126:I126"/>
@@ -7291,64 +7348,16 @@
     <mergeCell ref="D120:H120"/>
     <mergeCell ref="G123:J123"/>
     <mergeCell ref="D121:J121"/>
-    <mergeCell ref="D30:I30"/>
-    <mergeCell ref="G80:H80"/>
-    <mergeCell ref="D78:I78"/>
-    <mergeCell ref="G71:H71"/>
-    <mergeCell ref="D76:I76"/>
-    <mergeCell ref="D66:H66"/>
-    <mergeCell ref="D77:I77"/>
-    <mergeCell ref="D73:I73"/>
-    <mergeCell ref="D70:E70"/>
-    <mergeCell ref="D31:I31"/>
-    <mergeCell ref="G35:H35"/>
-    <mergeCell ref="D40:I40"/>
-    <mergeCell ref="D33:I33"/>
-    <mergeCell ref="D46:I46"/>
-    <mergeCell ref="D43:I43"/>
-    <mergeCell ref="G57:H57"/>
-    <mergeCell ref="D14:I14"/>
-    <mergeCell ref="G27:H27"/>
-    <mergeCell ref="D25:I25"/>
-    <mergeCell ref="G20:H20"/>
-    <mergeCell ref="D19:I19"/>
-    <mergeCell ref="D18:I18"/>
-    <mergeCell ref="D8:I8"/>
-    <mergeCell ref="D9:I9"/>
-    <mergeCell ref="D10:I10"/>
-    <mergeCell ref="D11:I11"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="G81:H81"/>
-    <mergeCell ref="D67:F67"/>
-    <mergeCell ref="F68:I68"/>
-    <mergeCell ref="D87:E87"/>
-    <mergeCell ref="G87:I87"/>
-    <mergeCell ref="D74:F74"/>
-    <mergeCell ref="D84:I84"/>
-    <mergeCell ref="D69:I69"/>
-    <mergeCell ref="G42:H42"/>
-    <mergeCell ref="D60:I60"/>
-    <mergeCell ref="D62:I62"/>
-    <mergeCell ref="D61:I61"/>
-    <mergeCell ref="G49:H49"/>
-    <mergeCell ref="D47:I47"/>
-    <mergeCell ref="D55:I55"/>
-    <mergeCell ref="D98:I98"/>
-    <mergeCell ref="D94:I94"/>
-    <mergeCell ref="H89:I89"/>
-    <mergeCell ref="D89:F89"/>
-    <mergeCell ref="G64:H64"/>
-    <mergeCell ref="D96:I96"/>
-    <mergeCell ref="D95:F95"/>
-    <mergeCell ref="G95:H95"/>
-    <mergeCell ref="D92:I92"/>
-    <mergeCell ref="D97:I97"/>
-    <mergeCell ref="D93:I93"/>
-    <mergeCell ref="D90:E90"/>
-    <mergeCell ref="D91:H91"/>
-    <mergeCell ref="E86:G86"/>
-    <mergeCell ref="D88:I88"/>
-    <mergeCell ref="H67:I67"/>
+    <mergeCell ref="D107:E107"/>
+    <mergeCell ref="F118:J118"/>
+    <mergeCell ref="G152:I152"/>
+    <mergeCell ref="D149:J150"/>
+    <mergeCell ref="G146:J146"/>
+    <mergeCell ref="D164:J164"/>
+    <mergeCell ref="D157:J157"/>
+    <mergeCell ref="D143:J143"/>
+    <mergeCell ref="D135:J135"/>
+    <mergeCell ref="F127:J127"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/attendance_sheet.xlsx
+++ b/attendance_sheet.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\repositary\3rd_Year_5th_Semester\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57CDE1BB-9B9F-43C2-8A85-189B090A98E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E224776-834A-4CE8-A923-54EB75EFE8F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{EB654061-A886-47D1-BF86-9B1A84FCE7FB}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="820" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="836" uniqueCount="71">
   <si>
     <t>Date</t>
   </si>
@@ -251,15 +251,12 @@
   <si>
     <t>1 class  p</t>
   </si>
-  <si>
-    <t>DAY</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -293,6 +290,14 @@
       <b/>
       <sz val="22"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -456,7 +461,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -527,23 +532,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -563,11 +556,29 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -970,14 +981,14 @@
       <c r="C8" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D8" s="37" t="s">
+      <c r="D8" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="E8" s="37"/>
-      <c r="F8" s="37"/>
-      <c r="G8" s="37"/>
-      <c r="H8" s="37"/>
-      <c r="I8" s="37"/>
+      <c r="E8" s="25"/>
+      <c r="F8" s="25"/>
+      <c r="G8" s="25"/>
+      <c r="H8" s="25"/>
+      <c r="I8" s="25"/>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B9" s="4">
@@ -986,14 +997,14 @@
       <c r="C9" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D9" s="37" t="s">
+      <c r="D9" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="E9" s="37"/>
-      <c r="F9" s="37"/>
-      <c r="G9" s="37"/>
-      <c r="H9" s="37"/>
-      <c r="I9" s="37"/>
+      <c r="E9" s="25"/>
+      <c r="F9" s="25"/>
+      <c r="G9" s="25"/>
+      <c r="H9" s="25"/>
+      <c r="I9" s="25"/>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B10" s="4">
@@ -1002,14 +1013,14 @@
       <c r="C10" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D10" s="37" t="s">
+      <c r="D10" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="E10" s="37"/>
-      <c r="F10" s="37"/>
-      <c r="G10" s="37"/>
-      <c r="H10" s="37"/>
-      <c r="I10" s="37"/>
+      <c r="E10" s="25"/>
+      <c r="F10" s="25"/>
+      <c r="G10" s="25"/>
+      <c r="H10" s="25"/>
+      <c r="I10" s="25"/>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B11" s="4">
@@ -1018,14 +1029,14 @@
       <c r="C11" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D11" s="37" t="s">
+      <c r="D11" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="E11" s="37"/>
-      <c r="F11" s="37"/>
-      <c r="G11" s="37"/>
-      <c r="H11" s="37"/>
-      <c r="I11" s="37"/>
+      <c r="E11" s="25"/>
+      <c r="F11" s="25"/>
+      <c r="G11" s="25"/>
+      <c r="H11" s="25"/>
+      <c r="I11" s="25"/>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B12" s="4">
@@ -1069,10 +1080,10 @@
       <c r="F13" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="G13" s="37" t="s">
+      <c r="G13" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="H13" s="37"/>
+      <c r="H13" s="25"/>
       <c r="I13" s="1" t="s">
         <v>14</v>
       </c>
@@ -1084,14 +1095,14 @@
       <c r="C14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D14" s="37" t="s">
+      <c r="D14" s="25" t="s">
         <v>19</v>
       </c>
-      <c r="E14" s="37"/>
-      <c r="F14" s="37"/>
-      <c r="G14" s="37"/>
-      <c r="H14" s="37"/>
-      <c r="I14" s="37"/>
+      <c r="E14" s="25"/>
+      <c r="F14" s="25"/>
+      <c r="G14" s="25"/>
+      <c r="H14" s="25"/>
+      <c r="I14" s="25"/>
     </row>
     <row r="15" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B15" s="4">
@@ -1178,14 +1189,14 @@
       <c r="C18" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D18" s="37" t="s">
+      <c r="D18" s="25" t="s">
         <v>23</v>
       </c>
-      <c r="E18" s="37"/>
-      <c r="F18" s="37"/>
-      <c r="G18" s="37"/>
-      <c r="H18" s="37"/>
-      <c r="I18" s="37"/>
+      <c r="E18" s="25"/>
+      <c r="F18" s="25"/>
+      <c r="G18" s="25"/>
+      <c r="H18" s="25"/>
+      <c r="I18" s="25"/>
     </row>
     <row r="19" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B19" s="4">
@@ -1194,14 +1205,14 @@
       <c r="C19" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D19" s="37" t="s">
+      <c r="D19" s="25" t="s">
         <v>23</v>
       </c>
-      <c r="E19" s="37"/>
-      <c r="F19" s="37"/>
-      <c r="G19" s="37"/>
-      <c r="H19" s="37"/>
-      <c r="I19" s="37"/>
+      <c r="E19" s="25"/>
+      <c r="F19" s="25"/>
+      <c r="G19" s="25"/>
+      <c r="H19" s="25"/>
+      <c r="I19" s="25"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B20" s="4">
@@ -1219,10 +1230,10 @@
       <c r="F20" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G20" s="37" t="s">
+      <c r="G20" s="25" t="s">
         <v>15</v>
       </c>
-      <c r="H20" s="37"/>
+      <c r="H20" s="25"/>
       <c r="I20" s="1" t="s">
         <v>14</v>
       </c>
@@ -1338,14 +1349,14 @@
       <c r="C25" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D25" s="37" t="s">
+      <c r="D25" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="E25" s="37"/>
-      <c r="F25" s="37"/>
-      <c r="G25" s="37"/>
-      <c r="H25" s="37"/>
-      <c r="I25" s="37"/>
+      <c r="E25" s="25"/>
+      <c r="F25" s="25"/>
+      <c r="G25" s="25"/>
+      <c r="H25" s="25"/>
+      <c r="I25" s="25"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B26" s="4">
@@ -1389,10 +1400,10 @@
       <c r="F27" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G27" s="37" t="s">
+      <c r="G27" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="H27" s="37"/>
+      <c r="H27" s="25"/>
       <c r="I27" s="1" t="s">
         <v>14</v>
       </c>
@@ -1456,14 +1467,14 @@
       <c r="C30" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D30" s="36" t="s">
+      <c r="D30" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="E30" s="36"/>
-      <c r="F30" s="36"/>
-      <c r="G30" s="36"/>
-      <c r="H30" s="36"/>
-      <c r="I30" s="36"/>
+      <c r="E30" s="24"/>
+      <c r="F30" s="24"/>
+      <c r="G30" s="24"/>
+      <c r="H30" s="24"/>
+      <c r="I30" s="24"/>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B31" s="4">
@@ -1472,14 +1483,14 @@
       <c r="C31" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D31" s="36" t="s">
+      <c r="D31" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="E31" s="36"/>
-      <c r="F31" s="36"/>
-      <c r="G31" s="36"/>
-      <c r="H31" s="36"/>
-      <c r="I31" s="36"/>
+      <c r="E31" s="24"/>
+      <c r="F31" s="24"/>
+      <c r="G31" s="24"/>
+      <c r="H31" s="24"/>
+      <c r="I31" s="24"/>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B32" s="4">
@@ -1514,14 +1525,14 @@
       <c r="C33" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D33" s="36" t="s">
+      <c r="D33" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="E33" s="36"/>
-      <c r="F33" s="36"/>
-      <c r="G33" s="36"/>
-      <c r="H33" s="36"/>
-      <c r="I33" s="36"/>
+      <c r="E33" s="24"/>
+      <c r="F33" s="24"/>
+      <c r="G33" s="24"/>
+      <c r="H33" s="24"/>
+      <c r="I33" s="24"/>
     </row>
     <row r="34" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B34" s="4">
@@ -1565,10 +1576,10 @@
       <c r="F35" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G35" s="36" t="s">
+      <c r="G35" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="H35" s="36"/>
+      <c r="H35" s="24"/>
       <c r="I35" s="1" t="s">
         <v>14</v>
       </c>
@@ -1684,14 +1695,14 @@
       <c r="C40" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D40" s="36" t="s">
+      <c r="D40" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="E40" s="36"/>
-      <c r="F40" s="36"/>
-      <c r="G40" s="36"/>
-      <c r="H40" s="36"/>
-      <c r="I40" s="36"/>
+      <c r="E40" s="24"/>
+      <c r="F40" s="24"/>
+      <c r="G40" s="24"/>
+      <c r="H40" s="24"/>
+      <c r="I40" s="24"/>
     </row>
     <row r="41" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B41" s="4">
@@ -1735,10 +1746,10 @@
       <c r="F42" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G42" s="36" t="s">
+      <c r="G42" s="24" t="s">
         <v>28</v>
       </c>
-      <c r="H42" s="36"/>
+      <c r="H42" s="24"/>
       <c r="I42" s="1" t="s">
         <v>15</v>
       </c>
@@ -1750,14 +1761,14 @@
       <c r="C43" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D43" s="36" t="s">
+      <c r="D43" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="E43" s="36"/>
-      <c r="F43" s="36"/>
-      <c r="G43" s="36"/>
-      <c r="H43" s="36"/>
-      <c r="I43" s="36"/>
+      <c r="E43" s="24"/>
+      <c r="F43" s="24"/>
+      <c r="G43" s="24"/>
+      <c r="H43" s="24"/>
+      <c r="I43" s="24"/>
     </row>
     <row r="44" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B44" s="4">
@@ -1821,14 +1832,14 @@
       <c r="C46" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D46" s="36" t="s">
+      <c r="D46" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="E46" s="36"/>
-      <c r="F46" s="36"/>
-      <c r="G46" s="36"/>
-      <c r="H46" s="36"/>
-      <c r="I46" s="36"/>
+      <c r="E46" s="24"/>
+      <c r="F46" s="24"/>
+      <c r="G46" s="24"/>
+      <c r="H46" s="24"/>
+      <c r="I46" s="24"/>
     </row>
     <row r="47" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B47" s="4">
@@ -3114,28 +3125,28 @@
       <c r="I111" s="20"/>
     </row>
     <row r="112" spans="2:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B112" s="30" t="s">
+      <c r="B112" s="26" t="s">
         <v>57</v>
       </c>
-      <c r="C112" s="31"/>
-      <c r="D112" s="31"/>
-      <c r="E112" s="31"/>
-      <c r="F112" s="31"/>
-      <c r="G112" s="31"/>
-      <c r="H112" s="31"/>
-      <c r="I112" s="31"/>
-      <c r="J112" s="32"/>
+      <c r="C112" s="27"/>
+      <c r="D112" s="27"/>
+      <c r="E112" s="27"/>
+      <c r="F112" s="27"/>
+      <c r="G112" s="27"/>
+      <c r="H112" s="27"/>
+      <c r="I112" s="27"/>
+      <c r="J112" s="28"/>
     </row>
     <row r="113" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B113" s="33"/>
-      <c r="C113" s="34"/>
-      <c r="D113" s="34"/>
-      <c r="E113" s="34"/>
-      <c r="F113" s="34"/>
-      <c r="G113" s="34"/>
-      <c r="H113" s="34"/>
-      <c r="I113" s="34"/>
-      <c r="J113" s="35"/>
+      <c r="B113" s="29"/>
+      <c r="C113" s="30"/>
+      <c r="D113" s="30"/>
+      <c r="E113" s="30"/>
+      <c r="F113" s="30"/>
+      <c r="G113" s="30"/>
+      <c r="H113" s="30"/>
+      <c r="I113" s="30"/>
+      <c r="J113" s="31"/>
     </row>
     <row r="114" spans="2:10" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B114" s="8" t="s">
@@ -4057,15 +4068,15 @@
       <c r="C149" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D149" s="24" t="s">
+      <c r="D149" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="E149" s="25"/>
-      <c r="F149" s="25"/>
-      <c r="G149" s="25"/>
-      <c r="H149" s="25"/>
-      <c r="I149" s="25"/>
-      <c r="J149" s="26"/>
+      <c r="E149" s="33"/>
+      <c r="F149" s="33"/>
+      <c r="G149" s="33"/>
+      <c r="H149" s="33"/>
+      <c r="I149" s="33"/>
+      <c r="J149" s="34"/>
     </row>
     <row r="150" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B150" s="4">
@@ -4074,13 +4085,13 @@
       <c r="C150" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D150" s="27"/>
-      <c r="E150" s="28"/>
-      <c r="F150" s="28"/>
-      <c r="G150" s="28"/>
-      <c r="H150" s="28"/>
-      <c r="I150" s="28"/>
-      <c r="J150" s="29"/>
+      <c r="D150" s="35"/>
+      <c r="E150" s="36"/>
+      <c r="F150" s="36"/>
+      <c r="G150" s="36"/>
+      <c r="H150" s="36"/>
+      <c r="I150" s="36"/>
+      <c r="J150" s="37"/>
     </row>
     <row r="151" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B151" s="4">
@@ -4531,29 +4542,63 @@
       <c r="I167" s="1"/>
       <c r="J167" s="1"/>
     </row>
-    <row r="168" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B168" s="3"/>
-      <c r="C168" s="3"/>
-      <c r="D168" s="3"/>
-      <c r="E168" s="3"/>
-      <c r="F168" s="3"/>
-      <c r="G168" s="3"/>
-      <c r="H168" s="3"/>
-      <c r="I168" s="1"/>
-      <c r="J168" s="1"/>
+    <row r="168" spans="2:10" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B168" s="38" t="s">
+        <v>0</v>
+      </c>
+      <c r="C168" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="D168" s="39" t="s">
+        <v>58</v>
+      </c>
+      <c r="E168" s="39" t="s">
+        <v>59</v>
+      </c>
+      <c r="F168" s="39" t="s">
+        <v>60</v>
+      </c>
+      <c r="G168" s="39" t="s">
+        <v>62</v>
+      </c>
+      <c r="H168" s="39" t="s">
+        <v>63</v>
+      </c>
+      <c r="I168" s="39" t="s">
+        <v>61</v>
+      </c>
+      <c r="J168" s="39" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="169" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B169" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="C169" s="3"/>
-      <c r="D169" s="3"/>
-      <c r="E169" s="3"/>
-      <c r="F169" s="3"/>
-      <c r="G169" s="3"/>
-      <c r="H169" s="3"/>
-      <c r="I169" s="1"/>
-      <c r="J169" s="1"/>
+      <c r="B169" s="4">
+        <v>45897</v>
+      </c>
+      <c r="C169" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D169" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E169" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F169" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G169" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H169" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I169" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="J169" s="1" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="170" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B170" s="3"/>
@@ -7274,6 +7319,74 @@
     </row>
   </sheetData>
   <mergeCells count="84">
+    <mergeCell ref="D164:J164"/>
+    <mergeCell ref="D157:J157"/>
+    <mergeCell ref="D143:J143"/>
+    <mergeCell ref="D135:J135"/>
+    <mergeCell ref="F127:J127"/>
+    <mergeCell ref="D107:E107"/>
+    <mergeCell ref="F118:J118"/>
+    <mergeCell ref="G152:I152"/>
+    <mergeCell ref="D149:J150"/>
+    <mergeCell ref="G146:J146"/>
+    <mergeCell ref="D106:E106"/>
+    <mergeCell ref="D99:G99"/>
+    <mergeCell ref="G126:I126"/>
+    <mergeCell ref="F125:J125"/>
+    <mergeCell ref="D128:J128"/>
+    <mergeCell ref="D103:E103"/>
+    <mergeCell ref="D104:E104"/>
+    <mergeCell ref="D105:E105"/>
+    <mergeCell ref="G100:I100"/>
+    <mergeCell ref="B101:I101"/>
+    <mergeCell ref="D108:E108"/>
+    <mergeCell ref="B112:J113"/>
+    <mergeCell ref="G124:J124"/>
+    <mergeCell ref="D120:H120"/>
+    <mergeCell ref="G123:J123"/>
+    <mergeCell ref="D121:J121"/>
+    <mergeCell ref="D30:I30"/>
+    <mergeCell ref="G80:H80"/>
+    <mergeCell ref="D78:I78"/>
+    <mergeCell ref="G71:H71"/>
+    <mergeCell ref="D76:I76"/>
+    <mergeCell ref="D66:H66"/>
+    <mergeCell ref="D77:I77"/>
+    <mergeCell ref="D73:I73"/>
+    <mergeCell ref="D70:E70"/>
+    <mergeCell ref="D31:I31"/>
+    <mergeCell ref="G35:H35"/>
+    <mergeCell ref="D40:I40"/>
+    <mergeCell ref="D33:I33"/>
+    <mergeCell ref="D46:I46"/>
+    <mergeCell ref="D43:I43"/>
+    <mergeCell ref="G57:H57"/>
+    <mergeCell ref="D14:I14"/>
+    <mergeCell ref="G27:H27"/>
+    <mergeCell ref="D25:I25"/>
+    <mergeCell ref="G20:H20"/>
+    <mergeCell ref="D19:I19"/>
+    <mergeCell ref="D18:I18"/>
+    <mergeCell ref="D8:I8"/>
+    <mergeCell ref="D9:I9"/>
+    <mergeCell ref="D10:I10"/>
+    <mergeCell ref="D11:I11"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="G81:H81"/>
+    <mergeCell ref="D67:F67"/>
+    <mergeCell ref="F68:I68"/>
+    <mergeCell ref="D87:E87"/>
+    <mergeCell ref="G87:I87"/>
+    <mergeCell ref="D74:F74"/>
+    <mergeCell ref="D84:I84"/>
+    <mergeCell ref="D69:I69"/>
+    <mergeCell ref="G42:H42"/>
+    <mergeCell ref="D60:I60"/>
+    <mergeCell ref="D62:I62"/>
+    <mergeCell ref="D61:I61"/>
+    <mergeCell ref="G49:H49"/>
+    <mergeCell ref="D47:I47"/>
+    <mergeCell ref="D55:I55"/>
     <mergeCell ref="D98:I98"/>
     <mergeCell ref="D94:I94"/>
     <mergeCell ref="H89:I89"/>
@@ -7290,74 +7403,6 @@
     <mergeCell ref="E86:G86"/>
     <mergeCell ref="D88:I88"/>
     <mergeCell ref="H67:I67"/>
-    <mergeCell ref="G42:H42"/>
-    <mergeCell ref="D60:I60"/>
-    <mergeCell ref="D62:I62"/>
-    <mergeCell ref="D61:I61"/>
-    <mergeCell ref="G49:H49"/>
-    <mergeCell ref="D47:I47"/>
-    <mergeCell ref="D55:I55"/>
-    <mergeCell ref="G81:H81"/>
-    <mergeCell ref="D67:F67"/>
-    <mergeCell ref="F68:I68"/>
-    <mergeCell ref="D87:E87"/>
-    <mergeCell ref="G87:I87"/>
-    <mergeCell ref="D74:F74"/>
-    <mergeCell ref="D84:I84"/>
-    <mergeCell ref="D69:I69"/>
-    <mergeCell ref="D8:I8"/>
-    <mergeCell ref="D9:I9"/>
-    <mergeCell ref="D10:I10"/>
-    <mergeCell ref="D11:I11"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="D14:I14"/>
-    <mergeCell ref="G27:H27"/>
-    <mergeCell ref="D25:I25"/>
-    <mergeCell ref="G20:H20"/>
-    <mergeCell ref="D19:I19"/>
-    <mergeCell ref="D18:I18"/>
-    <mergeCell ref="D30:I30"/>
-    <mergeCell ref="G80:H80"/>
-    <mergeCell ref="D78:I78"/>
-    <mergeCell ref="G71:H71"/>
-    <mergeCell ref="D76:I76"/>
-    <mergeCell ref="D66:H66"/>
-    <mergeCell ref="D77:I77"/>
-    <mergeCell ref="D73:I73"/>
-    <mergeCell ref="D70:E70"/>
-    <mergeCell ref="D31:I31"/>
-    <mergeCell ref="G35:H35"/>
-    <mergeCell ref="D40:I40"/>
-    <mergeCell ref="D33:I33"/>
-    <mergeCell ref="D46:I46"/>
-    <mergeCell ref="D43:I43"/>
-    <mergeCell ref="G57:H57"/>
-    <mergeCell ref="D106:E106"/>
-    <mergeCell ref="D99:G99"/>
-    <mergeCell ref="G126:I126"/>
-    <mergeCell ref="F125:J125"/>
-    <mergeCell ref="D128:J128"/>
-    <mergeCell ref="D103:E103"/>
-    <mergeCell ref="D104:E104"/>
-    <mergeCell ref="D105:E105"/>
-    <mergeCell ref="G100:I100"/>
-    <mergeCell ref="B101:I101"/>
-    <mergeCell ref="D108:E108"/>
-    <mergeCell ref="B112:J113"/>
-    <mergeCell ref="G124:J124"/>
-    <mergeCell ref="D120:H120"/>
-    <mergeCell ref="G123:J123"/>
-    <mergeCell ref="D121:J121"/>
-    <mergeCell ref="D107:E107"/>
-    <mergeCell ref="F118:J118"/>
-    <mergeCell ref="G152:I152"/>
-    <mergeCell ref="D149:J150"/>
-    <mergeCell ref="G146:J146"/>
-    <mergeCell ref="D164:J164"/>
-    <mergeCell ref="D157:J157"/>
-    <mergeCell ref="D143:J143"/>
-    <mergeCell ref="D135:J135"/>
-    <mergeCell ref="F127:J127"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/attendance_sheet.xlsx
+++ b/attendance_sheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\repositary\3rd_Year_5th_Semester\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E224776-834A-4CE8-A923-54EB75EFE8F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AE1DC0E-0A91-4966-B845-F94DEE3479CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{EB654061-A886-47D1-BF86-9B1A84FCE7FB}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="836" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="844" uniqueCount="71">
   <si>
     <t>Date</t>
   </si>
@@ -523,6 +523,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -530,30 +536,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
@@ -574,11 +556,29 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -981,14 +981,14 @@
       <c r="C8" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D8" s="25" t="s">
+      <c r="D8" s="39" t="s">
         <v>20</v>
       </c>
-      <c r="E8" s="25"/>
-      <c r="F8" s="25"/>
-      <c r="G8" s="25"/>
-      <c r="H8" s="25"/>
-      <c r="I8" s="25"/>
+      <c r="E8" s="39"/>
+      <c r="F8" s="39"/>
+      <c r="G8" s="39"/>
+      <c r="H8" s="39"/>
+      <c r="I8" s="39"/>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B9" s="4">
@@ -997,14 +997,14 @@
       <c r="C9" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D9" s="25" t="s">
+      <c r="D9" s="39" t="s">
         <v>20</v>
       </c>
-      <c r="E9" s="25"/>
-      <c r="F9" s="25"/>
-      <c r="G9" s="25"/>
-      <c r="H9" s="25"/>
-      <c r="I9" s="25"/>
+      <c r="E9" s="39"/>
+      <c r="F9" s="39"/>
+      <c r="G9" s="39"/>
+      <c r="H9" s="39"/>
+      <c r="I9" s="39"/>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B10" s="4">
@@ -1013,14 +1013,14 @@
       <c r="C10" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D10" s="25" t="s">
+      <c r="D10" s="39" t="s">
         <v>20</v>
       </c>
-      <c r="E10" s="25"/>
-      <c r="F10" s="25"/>
-      <c r="G10" s="25"/>
-      <c r="H10" s="25"/>
-      <c r="I10" s="25"/>
+      <c r="E10" s="39"/>
+      <c r="F10" s="39"/>
+      <c r="G10" s="39"/>
+      <c r="H10" s="39"/>
+      <c r="I10" s="39"/>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B11" s="4">
@@ -1029,14 +1029,14 @@
       <c r="C11" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D11" s="25" t="s">
+      <c r="D11" s="39" t="s">
         <v>20</v>
       </c>
-      <c r="E11" s="25"/>
-      <c r="F11" s="25"/>
-      <c r="G11" s="25"/>
-      <c r="H11" s="25"/>
-      <c r="I11" s="25"/>
+      <c r="E11" s="39"/>
+      <c r="F11" s="39"/>
+      <c r="G11" s="39"/>
+      <c r="H11" s="39"/>
+      <c r="I11" s="39"/>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B12" s="4">
@@ -1080,10 +1080,10 @@
       <c r="F13" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="G13" s="25" t="s">
+      <c r="G13" s="39" t="s">
         <v>18</v>
       </c>
-      <c r="H13" s="25"/>
+      <c r="H13" s="39"/>
       <c r="I13" s="1" t="s">
         <v>14</v>
       </c>
@@ -1095,14 +1095,14 @@
       <c r="C14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D14" s="25" t="s">
+      <c r="D14" s="39" t="s">
         <v>19</v>
       </c>
-      <c r="E14" s="25"/>
-      <c r="F14" s="25"/>
-      <c r="G14" s="25"/>
-      <c r="H14" s="25"/>
-      <c r="I14" s="25"/>
+      <c r="E14" s="39"/>
+      <c r="F14" s="39"/>
+      <c r="G14" s="39"/>
+      <c r="H14" s="39"/>
+      <c r="I14" s="39"/>
     </row>
     <row r="15" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B15" s="4">
@@ -1189,14 +1189,14 @@
       <c r="C18" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D18" s="25" t="s">
+      <c r="D18" s="39" t="s">
         <v>23</v>
       </c>
-      <c r="E18" s="25"/>
-      <c r="F18" s="25"/>
-      <c r="G18" s="25"/>
-      <c r="H18" s="25"/>
-      <c r="I18" s="25"/>
+      <c r="E18" s="39"/>
+      <c r="F18" s="39"/>
+      <c r="G18" s="39"/>
+      <c r="H18" s="39"/>
+      <c r="I18" s="39"/>
     </row>
     <row r="19" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B19" s="4">
@@ -1205,14 +1205,14 @@
       <c r="C19" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D19" s="25" t="s">
+      <c r="D19" s="39" t="s">
         <v>23</v>
       </c>
-      <c r="E19" s="25"/>
-      <c r="F19" s="25"/>
-      <c r="G19" s="25"/>
-      <c r="H19" s="25"/>
-      <c r="I19" s="25"/>
+      <c r="E19" s="39"/>
+      <c r="F19" s="39"/>
+      <c r="G19" s="39"/>
+      <c r="H19" s="39"/>
+      <c r="I19" s="39"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B20" s="4">
@@ -1230,10 +1230,10 @@
       <c r="F20" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G20" s="25" t="s">
+      <c r="G20" s="39" t="s">
         <v>15</v>
       </c>
-      <c r="H20" s="25"/>
+      <c r="H20" s="39"/>
       <c r="I20" s="1" t="s">
         <v>14</v>
       </c>
@@ -1349,14 +1349,14 @@
       <c r="C25" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D25" s="25" t="s">
+      <c r="D25" s="39" t="s">
         <v>26</v>
       </c>
-      <c r="E25" s="25"/>
-      <c r="F25" s="25"/>
-      <c r="G25" s="25"/>
-      <c r="H25" s="25"/>
-      <c r="I25" s="25"/>
+      <c r="E25" s="39"/>
+      <c r="F25" s="39"/>
+      <c r="G25" s="39"/>
+      <c r="H25" s="39"/>
+      <c r="I25" s="39"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B26" s="4">
@@ -1400,10 +1400,10 @@
       <c r="F27" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G27" s="25" t="s">
+      <c r="G27" s="39" t="s">
         <v>18</v>
       </c>
-      <c r="H27" s="25"/>
+      <c r="H27" s="39"/>
       <c r="I27" s="1" t="s">
         <v>14</v>
       </c>
@@ -1467,14 +1467,14 @@
       <c r="C30" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D30" s="24" t="s">
+      <c r="D30" s="38" t="s">
         <v>20</v>
       </c>
-      <c r="E30" s="24"/>
-      <c r="F30" s="24"/>
-      <c r="G30" s="24"/>
-      <c r="H30" s="24"/>
-      <c r="I30" s="24"/>
+      <c r="E30" s="38"/>
+      <c r="F30" s="38"/>
+      <c r="G30" s="38"/>
+      <c r="H30" s="38"/>
+      <c r="I30" s="38"/>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B31" s="4">
@@ -1483,14 +1483,14 @@
       <c r="C31" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D31" s="24" t="s">
+      <c r="D31" s="38" t="s">
         <v>20</v>
       </c>
-      <c r="E31" s="24"/>
-      <c r="F31" s="24"/>
-      <c r="G31" s="24"/>
-      <c r="H31" s="24"/>
-      <c r="I31" s="24"/>
+      <c r="E31" s="38"/>
+      <c r="F31" s="38"/>
+      <c r="G31" s="38"/>
+      <c r="H31" s="38"/>
+      <c r="I31" s="38"/>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B32" s="4">
@@ -1525,14 +1525,14 @@
       <c r="C33" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D33" s="24" t="s">
+      <c r="D33" s="38" t="s">
         <v>20</v>
       </c>
-      <c r="E33" s="24"/>
-      <c r="F33" s="24"/>
-      <c r="G33" s="24"/>
-      <c r="H33" s="24"/>
-      <c r="I33" s="24"/>
+      <c r="E33" s="38"/>
+      <c r="F33" s="38"/>
+      <c r="G33" s="38"/>
+      <c r="H33" s="38"/>
+      <c r="I33" s="38"/>
     </row>
     <row r="34" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B34" s="4">
@@ -1576,10 +1576,10 @@
       <c r="F35" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G35" s="24" t="s">
+      <c r="G35" s="38" t="s">
         <v>18</v>
       </c>
-      <c r="H35" s="24"/>
+      <c r="H35" s="38"/>
       <c r="I35" s="1" t="s">
         <v>14</v>
       </c>
@@ -1695,14 +1695,14 @@
       <c r="C40" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D40" s="24" t="s">
+      <c r="D40" s="38" t="s">
         <v>20</v>
       </c>
-      <c r="E40" s="24"/>
-      <c r="F40" s="24"/>
-      <c r="G40" s="24"/>
-      <c r="H40" s="24"/>
-      <c r="I40" s="24"/>
+      <c r="E40" s="38"/>
+      <c r="F40" s="38"/>
+      <c r="G40" s="38"/>
+      <c r="H40" s="38"/>
+      <c r="I40" s="38"/>
     </row>
     <row r="41" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B41" s="4">
@@ -1746,10 +1746,10 @@
       <c r="F42" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G42" s="24" t="s">
+      <c r="G42" s="38" t="s">
         <v>28</v>
       </c>
-      <c r="H42" s="24"/>
+      <c r="H42" s="38"/>
       <c r="I42" s="1" t="s">
         <v>15</v>
       </c>
@@ -1761,14 +1761,14 @@
       <c r="C43" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D43" s="24" t="s">
+      <c r="D43" s="38" t="s">
         <v>20</v>
       </c>
-      <c r="E43" s="24"/>
-      <c r="F43" s="24"/>
-      <c r="G43" s="24"/>
-      <c r="H43" s="24"/>
-      <c r="I43" s="24"/>
+      <c r="E43" s="38"/>
+      <c r="F43" s="38"/>
+      <c r="G43" s="38"/>
+      <c r="H43" s="38"/>
+      <c r="I43" s="38"/>
     </row>
     <row r="44" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B44" s="4">
@@ -1832,14 +1832,14 @@
       <c r="C46" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D46" s="24" t="s">
+      <c r="D46" s="38" t="s">
         <v>20</v>
       </c>
-      <c r="E46" s="24"/>
-      <c r="F46" s="24"/>
-      <c r="G46" s="24"/>
-      <c r="H46" s="24"/>
-      <c r="I46" s="24"/>
+      <c r="E46" s="38"/>
+      <c r="F46" s="38"/>
+      <c r="G46" s="38"/>
+      <c r="H46" s="38"/>
+      <c r="I46" s="38"/>
     </row>
     <row r="47" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B47" s="4">
@@ -1848,14 +1848,14 @@
       <c r="C47" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D47" s="21" t="s">
+      <c r="D47" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E47" s="22"/>
-      <c r="F47" s="22"/>
-      <c r="G47" s="22"/>
-      <c r="H47" s="22"/>
-      <c r="I47" s="23"/>
+      <c r="E47" s="24"/>
+      <c r="F47" s="24"/>
+      <c r="G47" s="24"/>
+      <c r="H47" s="24"/>
+      <c r="I47" s="25"/>
     </row>
     <row r="48" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B48" s="4">
@@ -1899,10 +1899,10 @@
       <c r="F49" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G49" s="21" t="s">
+      <c r="G49" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="H49" s="23"/>
+      <c r="H49" s="25"/>
       <c r="I49" s="1" t="s">
         <v>30</v>
       </c>
@@ -2044,14 +2044,14 @@
       <c r="C55" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="D55" s="22" t="s">
+      <c r="D55" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="E55" s="22"/>
-      <c r="F55" s="22"/>
-      <c r="G55" s="22"/>
-      <c r="H55" s="22"/>
-      <c r="I55" s="22"/>
+      <c r="E55" s="24"/>
+      <c r="F55" s="24"/>
+      <c r="G55" s="24"/>
+      <c r="H55" s="24"/>
+      <c r="I55" s="24"/>
     </row>
     <row r="56" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B56" s="4">
@@ -2095,10 +2095,10 @@
       <c r="F57" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G57" s="21" t="s">
+      <c r="G57" s="23" t="s">
         <v>37</v>
       </c>
-      <c r="H57" s="23"/>
+      <c r="H57" s="25"/>
       <c r="I57" s="1" t="s">
         <v>36</v>
       </c>
@@ -2162,14 +2162,14 @@
       <c r="C60" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D60" s="21" t="s">
+      <c r="D60" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E60" s="22"/>
-      <c r="F60" s="22"/>
-      <c r="G60" s="22"/>
-      <c r="H60" s="22"/>
-      <c r="I60" s="23"/>
+      <c r="E60" s="24"/>
+      <c r="F60" s="24"/>
+      <c r="G60" s="24"/>
+      <c r="H60" s="24"/>
+      <c r="I60" s="25"/>
     </row>
     <row r="61" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B61" s="4">
@@ -2178,14 +2178,14 @@
       <c r="C61" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D61" s="21" t="s">
+      <c r="D61" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E61" s="22"/>
-      <c r="F61" s="22"/>
-      <c r="G61" s="22"/>
-      <c r="H61" s="22"/>
-      <c r="I61" s="23"/>
+      <c r="E61" s="24"/>
+      <c r="F61" s="24"/>
+      <c r="G61" s="24"/>
+      <c r="H61" s="24"/>
+      <c r="I61" s="25"/>
     </row>
     <row r="62" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B62" s="4">
@@ -2194,14 +2194,14 @@
       <c r="C62" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D62" s="21" t="s">
+      <c r="D62" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E62" s="22"/>
-      <c r="F62" s="22"/>
-      <c r="G62" s="22"/>
-      <c r="H62" s="22"/>
-      <c r="I62" s="23"/>
+      <c r="E62" s="24"/>
+      <c r="F62" s="24"/>
+      <c r="G62" s="24"/>
+      <c r="H62" s="24"/>
+      <c r="I62" s="25"/>
     </row>
     <row r="63" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B63" s="4">
@@ -2245,10 +2245,10 @@
       <c r="F64" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G64" s="21" t="s">
+      <c r="G64" s="23" t="s">
         <v>37</v>
       </c>
-      <c r="H64" s="23"/>
+      <c r="H64" s="25"/>
       <c r="I64" s="1" t="s">
         <v>14</v>
       </c>
@@ -2286,13 +2286,13 @@
       <c r="C66" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D66" s="21" t="s">
-        <v>14</v>
-      </c>
-      <c r="E66" s="22"/>
-      <c r="F66" s="22"/>
-      <c r="G66" s="22"/>
-      <c r="H66" s="23"/>
+      <c r="D66" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="E66" s="24"/>
+      <c r="F66" s="24"/>
+      <c r="G66" s="24"/>
+      <c r="H66" s="25"/>
       <c r="I66" s="1" t="s">
         <v>16</v>
       </c>
@@ -2304,18 +2304,18 @@
       <c r="C67" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D67" s="21" t="s">
-        <v>14</v>
-      </c>
-      <c r="E67" s="22"/>
-      <c r="F67" s="23"/>
+      <c r="D67" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="E67" s="24"/>
+      <c r="F67" s="25"/>
       <c r="G67" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="H67" s="21" t="s">
-        <v>14</v>
-      </c>
-      <c r="I67" s="23"/>
+      <c r="H67" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="I67" s="25"/>
     </row>
     <row r="68" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B68" s="4">
@@ -2330,12 +2330,12 @@
       <c r="E68" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F68" s="21" t="s">
-        <v>14</v>
-      </c>
-      <c r="G68" s="22"/>
-      <c r="H68" s="22"/>
-      <c r="I68" s="23"/>
+      <c r="F68" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="G68" s="24"/>
+      <c r="H68" s="24"/>
+      <c r="I68" s="25"/>
     </row>
     <row r="69" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B69" s="4">
@@ -2344,14 +2344,14 @@
       <c r="C69" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D69" s="21" t="s">
+      <c r="D69" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E69" s="22"/>
-      <c r="F69" s="22"/>
-      <c r="G69" s="22"/>
-      <c r="H69" s="22"/>
-      <c r="I69" s="23"/>
+      <c r="E69" s="24"/>
+      <c r="F69" s="24"/>
+      <c r="G69" s="24"/>
+      <c r="H69" s="24"/>
+      <c r="I69" s="25"/>
     </row>
     <row r="70" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B70" s="4">
@@ -2360,10 +2360,10 @@
       <c r="C70" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D70" s="21" t="s">
-        <v>14</v>
-      </c>
-      <c r="E70" s="23"/>
+      <c r="D70" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="E70" s="25"/>
       <c r="F70" s="3" t="s">
         <v>15</v>
       </c>
@@ -2393,10 +2393,10 @@
       <c r="F71" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G71" s="21" t="s">
+      <c r="G71" s="23" t="s">
         <v>37</v>
       </c>
-      <c r="H71" s="23"/>
+      <c r="H71" s="25"/>
       <c r="I71" s="1" t="s">
         <v>14</v>
       </c>
@@ -2434,14 +2434,14 @@
       <c r="C73" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D73" s="21" t="s">
+      <c r="D73" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E73" s="22"/>
-      <c r="F73" s="22"/>
-      <c r="G73" s="22"/>
-      <c r="H73" s="22"/>
-      <c r="I73" s="23"/>
+      <c r="E73" s="24"/>
+      <c r="F73" s="24"/>
+      <c r="G73" s="24"/>
+      <c r="H73" s="24"/>
+      <c r="I73" s="25"/>
     </row>
     <row r="74" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B74" s="4">
@@ -2450,11 +2450,11 @@
       <c r="C74" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D74" s="21" t="s">
-        <v>14</v>
-      </c>
-      <c r="E74" s="22"/>
-      <c r="F74" s="23"/>
+      <c r="D74" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="E74" s="24"/>
+      <c r="F74" s="25"/>
       <c r="G74" s="3" t="s">
         <v>16</v>
       </c>
@@ -2490,14 +2490,14 @@
       <c r="C76" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D76" s="21" t="s">
+      <c r="D76" s="23" t="s">
         <v>39</v>
       </c>
-      <c r="E76" s="22"/>
-      <c r="F76" s="22"/>
-      <c r="G76" s="22"/>
-      <c r="H76" s="22"/>
-      <c r="I76" s="23"/>
+      <c r="E76" s="24"/>
+      <c r="F76" s="24"/>
+      <c r="G76" s="24"/>
+      <c r="H76" s="24"/>
+      <c r="I76" s="25"/>
     </row>
     <row r="77" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B77" s="4">
@@ -2506,14 +2506,14 @@
       <c r="C77" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D77" s="21" t="s">
+      <c r="D77" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E77" s="22"/>
-      <c r="F77" s="22"/>
-      <c r="G77" s="22"/>
-      <c r="H77" s="22"/>
-      <c r="I77" s="23"/>
+      <c r="E77" s="24"/>
+      <c r="F77" s="24"/>
+      <c r="G77" s="24"/>
+      <c r="H77" s="24"/>
+      <c r="I77" s="25"/>
     </row>
     <row r="78" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B78" s="4">
@@ -2522,14 +2522,14 @@
       <c r="C78" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D78" s="21" t="s">
+      <c r="D78" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E78" s="22"/>
-      <c r="F78" s="22"/>
-      <c r="G78" s="22"/>
-      <c r="H78" s="22"/>
-      <c r="I78" s="23"/>
+      <c r="E78" s="24"/>
+      <c r="F78" s="24"/>
+      <c r="G78" s="24"/>
+      <c r="H78" s="24"/>
+      <c r="I78" s="25"/>
     </row>
     <row r="79" spans="2:9" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B79" s="16" t="s">
@@ -2573,10 +2573,10 @@
       <c r="F80" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G80" s="21" t="s">
+      <c r="G80" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="H80" s="23"/>
+      <c r="H80" s="25"/>
       <c r="I80" s="1" t="s">
         <v>14</v>
       </c>
@@ -2597,10 +2597,10 @@
       <c r="F81" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="G81" s="21" t="s">
-        <v>14</v>
-      </c>
-      <c r="H81" s="23"/>
+      <c r="G81" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="H81" s="25"/>
       <c r="I81" s="1" t="s">
         <v>16</v>
       </c>
@@ -2664,14 +2664,14 @@
       <c r="C84" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D84" s="21" t="s">
+      <c r="D84" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E84" s="22"/>
-      <c r="F84" s="22"/>
-      <c r="G84" s="22"/>
-      <c r="H84" s="22"/>
-      <c r="I84" s="23"/>
+      <c r="E84" s="24"/>
+      <c r="F84" s="24"/>
+      <c r="G84" s="24"/>
+      <c r="H84" s="24"/>
+      <c r="I84" s="25"/>
     </row>
     <row r="85" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B85" s="4">
@@ -2709,11 +2709,11 @@
       <c r="D86" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="E86" s="21" t="s">
+      <c r="E86" s="23" t="s">
         <v>43</v>
       </c>
-      <c r="F86" s="22"/>
-      <c r="G86" s="23"/>
+      <c r="F86" s="24"/>
+      <c r="G86" s="25"/>
       <c r="H86" s="3" t="s">
         <v>14</v>
       </c>
@@ -2728,18 +2728,18 @@
       <c r="C87" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D87" s="21" t="s">
-        <v>14</v>
-      </c>
-      <c r="E87" s="23"/>
+      <c r="D87" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="E87" s="25"/>
       <c r="F87" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G87" s="21" t="s">
-        <v>14</v>
-      </c>
-      <c r="H87" s="22"/>
-      <c r="I87" s="23"/>
+      <c r="G87" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="H87" s="24"/>
+      <c r="I87" s="25"/>
     </row>
     <row r="88" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B88" s="4">
@@ -2748,14 +2748,14 @@
       <c r="C88" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D88" s="21" t="s">
+      <c r="D88" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E88" s="22"/>
-      <c r="F88" s="22"/>
-      <c r="G88" s="22"/>
-      <c r="H88" s="22"/>
-      <c r="I88" s="23"/>
+      <c r="E88" s="24"/>
+      <c r="F88" s="24"/>
+      <c r="G88" s="24"/>
+      <c r="H88" s="24"/>
+      <c r="I88" s="25"/>
     </row>
     <row r="89" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B89" s="4">
@@ -2764,18 +2764,18 @@
       <c r="C89" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D89" s="21" t="s">
+      <c r="D89" s="23" t="s">
         <v>44</v>
       </c>
-      <c r="E89" s="22"/>
-      <c r="F89" s="23"/>
+      <c r="E89" s="24"/>
+      <c r="F89" s="25"/>
       <c r="G89" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="H89" s="21" t="s">
-        <v>14</v>
-      </c>
-      <c r="I89" s="23"/>
+      <c r="H89" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="I89" s="25"/>
     </row>
     <row r="90" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B90" s="4">
@@ -2784,10 +2784,10 @@
       <c r="C90" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D90" s="21" t="s">
-        <v>14</v>
-      </c>
-      <c r="E90" s="23"/>
+      <c r="D90" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="E90" s="25"/>
       <c r="F90" s="3" t="s">
         <v>16</v>
       </c>
@@ -2809,13 +2809,13 @@
       <c r="C91" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D91" s="21" t="s">
+      <c r="D91" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E91" s="22"/>
-      <c r="F91" s="22"/>
-      <c r="G91" s="22"/>
-      <c r="H91" s="23"/>
+      <c r="E91" s="24"/>
+      <c r="F91" s="24"/>
+      <c r="G91" s="24"/>
+      <c r="H91" s="25"/>
       <c r="I91" s="18" t="s">
         <v>45</v>
       </c>
@@ -2827,14 +2827,14 @@
       <c r="C92" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D92" s="21" t="s">
+      <c r="D92" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E92" s="22"/>
-      <c r="F92" s="22"/>
-      <c r="G92" s="22"/>
-      <c r="H92" s="22"/>
-      <c r="I92" s="23"/>
+      <c r="E92" s="24"/>
+      <c r="F92" s="24"/>
+      <c r="G92" s="24"/>
+      <c r="H92" s="24"/>
+      <c r="I92" s="25"/>
     </row>
     <row r="93" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B93" s="4">
@@ -2843,14 +2843,14 @@
       <c r="C93" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D93" s="21" t="s">
+      <c r="D93" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="E93" s="22"/>
-      <c r="F93" s="22"/>
-      <c r="G93" s="22"/>
-      <c r="H93" s="22"/>
-      <c r="I93" s="23"/>
+      <c r="E93" s="24"/>
+      <c r="F93" s="24"/>
+      <c r="G93" s="24"/>
+      <c r="H93" s="24"/>
+      <c r="I93" s="25"/>
     </row>
     <row r="94" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B94" s="4">
@@ -2859,14 +2859,14 @@
       <c r="C94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D94" s="21" t="s">
-        <v>14</v>
-      </c>
-      <c r="E94" s="22"/>
-      <c r="F94" s="22"/>
-      <c r="G94" s="22"/>
-      <c r="H94" s="22"/>
-      <c r="I94" s="23"/>
+      <c r="D94" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="E94" s="24"/>
+      <c r="F94" s="24"/>
+      <c r="G94" s="24"/>
+      <c r="H94" s="24"/>
+      <c r="I94" s="25"/>
     </row>
     <row r="95" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B95" s="4">
@@ -2875,15 +2875,15 @@
       <c r="C95" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D95" s="21" t="s">
+      <c r="D95" s="23" t="s">
         <v>47</v>
       </c>
-      <c r="E95" s="22"/>
-      <c r="F95" s="23"/>
-      <c r="G95" s="21" t="s">
+      <c r="E95" s="24"/>
+      <c r="F95" s="25"/>
+      <c r="G95" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="H95" s="23"/>
+      <c r="H95" s="25"/>
       <c r="I95" s="1" t="s">
         <v>14</v>
       </c>
@@ -2895,14 +2895,14 @@
       <c r="C96" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D96" s="21" t="s">
+      <c r="D96" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E96" s="22"/>
-      <c r="F96" s="22"/>
-      <c r="G96" s="22"/>
-      <c r="H96" s="22"/>
-      <c r="I96" s="23"/>
+      <c r="E96" s="24"/>
+      <c r="F96" s="24"/>
+      <c r="G96" s="24"/>
+      <c r="H96" s="24"/>
+      <c r="I96" s="25"/>
     </row>
     <row r="97" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B97" s="4">
@@ -2911,14 +2911,14 @@
       <c r="C97" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D97" s="21" t="s">
-        <v>14</v>
-      </c>
-      <c r="E97" s="22"/>
-      <c r="F97" s="22"/>
-      <c r="G97" s="22"/>
-      <c r="H97" s="22"/>
-      <c r="I97" s="23"/>
+      <c r="D97" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="E97" s="24"/>
+      <c r="F97" s="24"/>
+      <c r="G97" s="24"/>
+      <c r="H97" s="24"/>
+      <c r="I97" s="25"/>
     </row>
     <row r="98" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B98" s="4">
@@ -2927,14 +2927,14 @@
       <c r="C98" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D98" s="21" t="s">
+      <c r="D98" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E98" s="22"/>
-      <c r="F98" s="22"/>
-      <c r="G98" s="22"/>
-      <c r="H98" s="22"/>
-      <c r="I98" s="23"/>
+      <c r="E98" s="24"/>
+      <c r="F98" s="24"/>
+      <c r="G98" s="24"/>
+      <c r="H98" s="24"/>
+      <c r="I98" s="25"/>
     </row>
     <row r="99" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B99" s="4">
@@ -2943,12 +2943,12 @@
       <c r="C99" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D99" s="21" t="s">
-        <v>14</v>
-      </c>
-      <c r="E99" s="22"/>
-      <c r="F99" s="22"/>
-      <c r="G99" s="23"/>
+      <c r="D99" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="E99" s="24"/>
+      <c r="F99" s="24"/>
+      <c r="G99" s="25"/>
       <c r="H99" s="3" t="s">
         <v>49</v>
       </c>
@@ -2972,21 +2972,21 @@
       <c r="F100" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="G100" s="21" t="s">
-        <v>14</v>
-      </c>
-      <c r="H100" s="22"/>
-      <c r="I100" s="23"/>
+      <c r="G100" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="H100" s="24"/>
+      <c r="I100" s="25"/>
     </row>
     <row r="101" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B101" s="21"/>
-      <c r="C101" s="22"/>
-      <c r="D101" s="22"/>
-      <c r="E101" s="22"/>
-      <c r="F101" s="22"/>
-      <c r="G101" s="22"/>
-      <c r="H101" s="22"/>
-      <c r="I101" s="23"/>
+      <c r="B101" s="23"/>
+      <c r="C101" s="24"/>
+      <c r="D101" s="24"/>
+      <c r="E101" s="24"/>
+      <c r="F101" s="24"/>
+      <c r="G101" s="24"/>
+      <c r="H101" s="24"/>
+      <c r="I101" s="25"/>
     </row>
     <row r="102" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B102" s="3"/>
@@ -3005,10 +3005,10 @@
       <c r="C103" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D103" s="21" t="s">
+      <c r="D103" s="23" t="s">
         <v>51</v>
       </c>
-      <c r="E103" s="23"/>
+      <c r="E103" s="25"/>
       <c r="F103" s="3"/>
       <c r="G103" s="3"/>
       <c r="H103" s="3"/>
@@ -3021,10 +3021,10 @@
       <c r="C104" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D104" s="21" t="s">
+      <c r="D104" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="E104" s="23"/>
+      <c r="E104" s="25"/>
       <c r="F104" s="3"/>
       <c r="G104" s="3"/>
       <c r="H104" s="3"/>
@@ -3037,10 +3037,10 @@
       <c r="C105" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D105" s="21" t="s">
+      <c r="D105" s="23" t="s">
         <v>53</v>
       </c>
-      <c r="E105" s="23"/>
+      <c r="E105" s="25"/>
       <c r="F105" s="3"/>
       <c r="G105" s="3"/>
       <c r="H105" s="3"/>
@@ -3053,10 +3053,10 @@
       <c r="C106" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D106" s="21" t="s">
+      <c r="D106" s="23" t="s">
         <v>54</v>
       </c>
-      <c r="E106" s="23"/>
+      <c r="E106" s="25"/>
       <c r="F106" s="3"/>
       <c r="G106" s="3"/>
       <c r="H106" s="3"/>
@@ -3069,10 +3069,10 @@
       <c r="C107" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D107" s="21" t="s">
+      <c r="D107" s="23" t="s">
         <v>55</v>
       </c>
-      <c r="E107" s="23"/>
+      <c r="E107" s="25"/>
       <c r="F107" s="3"/>
       <c r="G107" s="3"/>
       <c r="H107" s="3"/>
@@ -3085,10 +3085,10 @@
       <c r="C108" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D108" s="21" t="s">
+      <c r="D108" s="23" t="s">
         <v>56</v>
       </c>
-      <c r="E108" s="23"/>
+      <c r="E108" s="25"/>
       <c r="F108" s="3"/>
       <c r="G108" s="3"/>
       <c r="H108" s="3"/>
@@ -3125,28 +3125,28 @@
       <c r="I111" s="20"/>
     </row>
     <row r="112" spans="2:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B112" s="26" t="s">
+      <c r="B112" s="32" t="s">
         <v>57</v>
       </c>
-      <c r="C112" s="27"/>
-      <c r="D112" s="27"/>
-      <c r="E112" s="27"/>
-      <c r="F112" s="27"/>
-      <c r="G112" s="27"/>
-      <c r="H112" s="27"/>
-      <c r="I112" s="27"/>
-      <c r="J112" s="28"/>
+      <c r="C112" s="33"/>
+      <c r="D112" s="33"/>
+      <c r="E112" s="33"/>
+      <c r="F112" s="33"/>
+      <c r="G112" s="33"/>
+      <c r="H112" s="33"/>
+      <c r="I112" s="33"/>
+      <c r="J112" s="34"/>
     </row>
     <row r="113" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B113" s="29"/>
-      <c r="C113" s="30"/>
-      <c r="D113" s="30"/>
-      <c r="E113" s="30"/>
-      <c r="F113" s="30"/>
-      <c r="G113" s="30"/>
-      <c r="H113" s="30"/>
-      <c r="I113" s="30"/>
-      <c r="J113" s="31"/>
+      <c r="B113" s="35"/>
+      <c r="C113" s="36"/>
+      <c r="D113" s="36"/>
+      <c r="E113" s="36"/>
+      <c r="F113" s="36"/>
+      <c r="G113" s="36"/>
+      <c r="H113" s="36"/>
+      <c r="I113" s="36"/>
+      <c r="J113" s="37"/>
     </row>
     <row r="114" spans="2:10" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B114" s="8" t="s">
@@ -3277,13 +3277,13 @@
       <c r="E118" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="F118" s="21" t="s">
-        <v>14</v>
-      </c>
-      <c r="G118" s="22"/>
-      <c r="H118" s="22"/>
-      <c r="I118" s="22"/>
-      <c r="J118" s="23"/>
+      <c r="F118" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="G118" s="24"/>
+      <c r="H118" s="24"/>
+      <c r="I118" s="24"/>
+      <c r="J118" s="25"/>
     </row>
     <row r="119" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B119" s="4">
@@ -3321,13 +3321,13 @@
       <c r="C120" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D120" s="21" t="s">
-        <v>14</v>
-      </c>
-      <c r="E120" s="22"/>
-      <c r="F120" s="22"/>
-      <c r="G120" s="22"/>
-      <c r="H120" s="23"/>
+      <c r="D120" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="E120" s="24"/>
+      <c r="F120" s="24"/>
+      <c r="G120" s="24"/>
+      <c r="H120" s="25"/>
       <c r="I120" s="1" t="s">
         <v>16</v>
       </c>
@@ -3342,15 +3342,15 @@
       <c r="C121" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D121" s="21" t="s">
+      <c r="D121" s="23" t="s">
         <v>65</v>
       </c>
-      <c r="E121" s="22"/>
-      <c r="F121" s="22"/>
-      <c r="G121" s="22"/>
-      <c r="H121" s="22"/>
-      <c r="I121" s="22"/>
-      <c r="J121" s="23"/>
+      <c r="E121" s="24"/>
+      <c r="F121" s="24"/>
+      <c r="G121" s="24"/>
+      <c r="H121" s="24"/>
+      <c r="I121" s="24"/>
+      <c r="J121" s="25"/>
     </row>
     <row r="122" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B122" s="4">
@@ -3397,12 +3397,12 @@
       <c r="F123" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="G123" s="21" t="s">
-        <v>14</v>
-      </c>
-      <c r="H123" s="22"/>
-      <c r="I123" s="22"/>
-      <c r="J123" s="23"/>
+      <c r="G123" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="H123" s="24"/>
+      <c r="I123" s="24"/>
+      <c r="J123" s="25"/>
     </row>
     <row r="124" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B124" s="4">
@@ -3420,12 +3420,12 @@
       <c r="F124" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="G124" s="21" t="s">
-        <v>14</v>
-      </c>
-      <c r="H124" s="22"/>
-      <c r="I124" s="22"/>
-      <c r="J124" s="23"/>
+      <c r="G124" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="H124" s="24"/>
+      <c r="I124" s="24"/>
+      <c r="J124" s="25"/>
     </row>
     <row r="125" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B125" s="4">
@@ -3440,13 +3440,13 @@
       <c r="E125" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="F125" s="21" t="s">
-        <v>14</v>
-      </c>
-      <c r="G125" s="22"/>
-      <c r="H125" s="22"/>
-      <c r="I125" s="22"/>
-      <c r="J125" s="23"/>
+      <c r="F125" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="G125" s="24"/>
+      <c r="H125" s="24"/>
+      <c r="I125" s="24"/>
+      <c r="J125" s="25"/>
     </row>
     <row r="126" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B126" s="4">
@@ -3464,11 +3464,11 @@
       <c r="F126" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="G126" s="21" t="s">
-        <v>14</v>
-      </c>
-      <c r="H126" s="22"/>
-      <c r="I126" s="23"/>
+      <c r="G126" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="H126" s="24"/>
+      <c r="I126" s="25"/>
       <c r="J126" s="1" t="s">
         <v>16</v>
       </c>
@@ -3486,13 +3486,13 @@
       <c r="E127" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="F127" s="21" t="s">
-        <v>14</v>
-      </c>
-      <c r="G127" s="22"/>
-      <c r="H127" s="22"/>
-      <c r="I127" s="22"/>
-      <c r="J127" s="23"/>
+      <c r="F127" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="G127" s="24"/>
+      <c r="H127" s="24"/>
+      <c r="I127" s="24"/>
+      <c r="J127" s="25"/>
     </row>
     <row r="128" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B128" s="4">
@@ -3501,15 +3501,15 @@
       <c r="C128" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D128" s="21" t="s">
+      <c r="D128" s="23" t="s">
         <v>65</v>
       </c>
-      <c r="E128" s="22"/>
-      <c r="F128" s="22"/>
-      <c r="G128" s="22"/>
-      <c r="H128" s="22"/>
-      <c r="I128" s="22"/>
-      <c r="J128" s="23"/>
+      <c r="E128" s="24"/>
+      <c r="F128" s="24"/>
+      <c r="G128" s="24"/>
+      <c r="H128" s="24"/>
+      <c r="I128" s="24"/>
+      <c r="J128" s="25"/>
     </row>
     <row r="129" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B129" s="4">
@@ -3692,15 +3692,15 @@
       <c r="C135" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D135" s="21" t="s">
+      <c r="D135" s="23" t="s">
         <v>65</v>
       </c>
-      <c r="E135" s="22"/>
-      <c r="F135" s="22"/>
-      <c r="G135" s="22"/>
-      <c r="H135" s="22"/>
-      <c r="I135" s="22"/>
-      <c r="J135" s="23"/>
+      <c r="E135" s="24"/>
+      <c r="F135" s="24"/>
+      <c r="G135" s="24"/>
+      <c r="H135" s="24"/>
+      <c r="I135" s="24"/>
+      <c r="J135" s="25"/>
     </row>
     <row r="136" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B136" s="4">
@@ -3912,15 +3912,15 @@
       <c r="C143" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D143" s="21" t="s">
+      <c r="D143" s="23" t="s">
         <v>65</v>
       </c>
-      <c r="E143" s="22"/>
-      <c r="F143" s="22"/>
-      <c r="G143" s="22"/>
-      <c r="H143" s="22"/>
-      <c r="I143" s="22"/>
-      <c r="J143" s="23"/>
+      <c r="E143" s="24"/>
+      <c r="F143" s="24"/>
+      <c r="G143" s="24"/>
+      <c r="H143" s="24"/>
+      <c r="I143" s="24"/>
+      <c r="J143" s="25"/>
     </row>
     <row r="144" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B144" s="4">
@@ -3996,12 +3996,12 @@
       <c r="F146" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="G146" s="21" t="s">
-        <v>14</v>
-      </c>
-      <c r="H146" s="22"/>
-      <c r="I146" s="22"/>
-      <c r="J146" s="23"/>
+      <c r="G146" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="H146" s="24"/>
+      <c r="I146" s="24"/>
+      <c r="J146" s="25"/>
     </row>
     <row r="147" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B147" s="4">
@@ -4068,15 +4068,15 @@
       <c r="C149" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D149" s="32" t="s">
+      <c r="D149" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="E149" s="33"/>
-      <c r="F149" s="33"/>
-      <c r="G149" s="33"/>
-      <c r="H149" s="33"/>
-      <c r="I149" s="33"/>
-      <c r="J149" s="34"/>
+      <c r="E149" s="27"/>
+      <c r="F149" s="27"/>
+      <c r="G149" s="27"/>
+      <c r="H149" s="27"/>
+      <c r="I149" s="27"/>
+      <c r="J149" s="28"/>
     </row>
     <row r="150" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B150" s="4">
@@ -4085,13 +4085,13 @@
       <c r="C150" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D150" s="35"/>
-      <c r="E150" s="36"/>
-      <c r="F150" s="36"/>
-      <c r="G150" s="36"/>
-      <c r="H150" s="36"/>
-      <c r="I150" s="36"/>
-      <c r="J150" s="37"/>
+      <c r="D150" s="29"/>
+      <c r="E150" s="30"/>
+      <c r="F150" s="30"/>
+      <c r="G150" s="30"/>
+      <c r="H150" s="30"/>
+      <c r="I150" s="30"/>
+      <c r="J150" s="31"/>
     </row>
     <row r="151" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B151" s="4">
@@ -4138,11 +4138,11 @@
       <c r="F152" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="G152" s="21" t="s">
-        <v>14</v>
-      </c>
-      <c r="H152" s="22"/>
-      <c r="I152" s="23"/>
+      <c r="G152" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="H152" s="24"/>
+      <c r="I152" s="25"/>
       <c r="J152" s="1" t="s">
         <v>69</v>
       </c>
@@ -4270,15 +4270,15 @@
       <c r="C157" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D157" s="21" t="s">
+      <c r="D157" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E157" s="22"/>
-      <c r="F157" s="22"/>
-      <c r="G157" s="22"/>
-      <c r="H157" s="22"/>
-      <c r="I157" s="22"/>
-      <c r="J157" s="23"/>
+      <c r="E157" s="24"/>
+      <c r="F157" s="24"/>
+      <c r="G157" s="24"/>
+      <c r="H157" s="24"/>
+      <c r="I157" s="24"/>
+      <c r="J157" s="25"/>
     </row>
     <row r="158" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B158" s="4">
@@ -4459,15 +4459,15 @@
       <c r="C164" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D164" s="21" t="s">
+      <c r="D164" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E164" s="22"/>
-      <c r="F164" s="22"/>
-      <c r="G164" s="22"/>
-      <c r="H164" s="22"/>
-      <c r="I164" s="22"/>
-      <c r="J164" s="23"/>
+      <c r="E164" s="24"/>
+      <c r="F164" s="24"/>
+      <c r="G164" s="24"/>
+      <c r="H164" s="24"/>
+      <c r="I164" s="24"/>
+      <c r="J164" s="25"/>
     </row>
     <row r="165" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B165" s="4">
@@ -4543,31 +4543,31 @@
       <c r="J167" s="1"/>
     </row>
     <row r="168" spans="2:10" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B168" s="38" t="s">
+      <c r="B168" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="C168" s="39" t="s">
+      <c r="C168" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="D168" s="39" t="s">
+      <c r="D168" s="22" t="s">
         <v>58</v>
       </c>
-      <c r="E168" s="39" t="s">
+      <c r="E168" s="22" t="s">
         <v>59</v>
       </c>
-      <c r="F168" s="39" t="s">
+      <c r="F168" s="22" t="s">
         <v>60</v>
       </c>
-      <c r="G168" s="39" t="s">
+      <c r="G168" s="22" t="s">
         <v>62</v>
       </c>
-      <c r="H168" s="39" t="s">
+      <c r="H168" s="22" t="s">
         <v>63</v>
       </c>
-      <c r="I168" s="39" t="s">
+      <c r="I168" s="22" t="s">
         <v>61</v>
       </c>
-      <c r="J168" s="39" t="s">
+      <c r="J168" s="22" t="s">
         <v>64</v>
       </c>
     </row>
@@ -4601,15 +4601,33 @@
       </c>
     </row>
     <row r="170" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B170" s="3"/>
-      <c r="C170" s="3"/>
-      <c r="D170" s="3"/>
-      <c r="E170" s="3"/>
-      <c r="F170" s="3"/>
-      <c r="G170" s="3"/>
-      <c r="H170" s="3"/>
-      <c r="I170" s="1"/>
-      <c r="J170" s="1"/>
+      <c r="B170" s="4">
+        <v>45898</v>
+      </c>
+      <c r="C170" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D170" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E170" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F170" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="G170" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H170" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I170" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J170" s="1" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="171" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B171" s="3"/>
@@ -7319,16 +7337,64 @@
     </row>
   </sheetData>
   <mergeCells count="84">
-    <mergeCell ref="D164:J164"/>
-    <mergeCell ref="D157:J157"/>
-    <mergeCell ref="D143:J143"/>
-    <mergeCell ref="D135:J135"/>
-    <mergeCell ref="F127:J127"/>
-    <mergeCell ref="D107:E107"/>
-    <mergeCell ref="F118:J118"/>
-    <mergeCell ref="G152:I152"/>
-    <mergeCell ref="D149:J150"/>
-    <mergeCell ref="G146:J146"/>
+    <mergeCell ref="D98:I98"/>
+    <mergeCell ref="D94:I94"/>
+    <mergeCell ref="H89:I89"/>
+    <mergeCell ref="D89:F89"/>
+    <mergeCell ref="G64:H64"/>
+    <mergeCell ref="D96:I96"/>
+    <mergeCell ref="D95:F95"/>
+    <mergeCell ref="G95:H95"/>
+    <mergeCell ref="D92:I92"/>
+    <mergeCell ref="D97:I97"/>
+    <mergeCell ref="D93:I93"/>
+    <mergeCell ref="D90:E90"/>
+    <mergeCell ref="D91:H91"/>
+    <mergeCell ref="E86:G86"/>
+    <mergeCell ref="D88:I88"/>
+    <mergeCell ref="H67:I67"/>
+    <mergeCell ref="G42:H42"/>
+    <mergeCell ref="D60:I60"/>
+    <mergeCell ref="D62:I62"/>
+    <mergeCell ref="D61:I61"/>
+    <mergeCell ref="G49:H49"/>
+    <mergeCell ref="D47:I47"/>
+    <mergeCell ref="D55:I55"/>
+    <mergeCell ref="G81:H81"/>
+    <mergeCell ref="D67:F67"/>
+    <mergeCell ref="F68:I68"/>
+    <mergeCell ref="D87:E87"/>
+    <mergeCell ref="G87:I87"/>
+    <mergeCell ref="D74:F74"/>
+    <mergeCell ref="D84:I84"/>
+    <mergeCell ref="D69:I69"/>
+    <mergeCell ref="D8:I8"/>
+    <mergeCell ref="D9:I9"/>
+    <mergeCell ref="D10:I10"/>
+    <mergeCell ref="D11:I11"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="D14:I14"/>
+    <mergeCell ref="G27:H27"/>
+    <mergeCell ref="D25:I25"/>
+    <mergeCell ref="G20:H20"/>
+    <mergeCell ref="D19:I19"/>
+    <mergeCell ref="D18:I18"/>
+    <mergeCell ref="D30:I30"/>
+    <mergeCell ref="G80:H80"/>
+    <mergeCell ref="D78:I78"/>
+    <mergeCell ref="G71:H71"/>
+    <mergeCell ref="D76:I76"/>
+    <mergeCell ref="D66:H66"/>
+    <mergeCell ref="D77:I77"/>
+    <mergeCell ref="D73:I73"/>
+    <mergeCell ref="D70:E70"/>
+    <mergeCell ref="D31:I31"/>
+    <mergeCell ref="G35:H35"/>
+    <mergeCell ref="D40:I40"/>
+    <mergeCell ref="D33:I33"/>
+    <mergeCell ref="D46:I46"/>
+    <mergeCell ref="D43:I43"/>
+    <mergeCell ref="G57:H57"/>
     <mergeCell ref="D106:E106"/>
     <mergeCell ref="D99:G99"/>
     <mergeCell ref="G126:I126"/>
@@ -7345,64 +7411,16 @@
     <mergeCell ref="D120:H120"/>
     <mergeCell ref="G123:J123"/>
     <mergeCell ref="D121:J121"/>
-    <mergeCell ref="D30:I30"/>
-    <mergeCell ref="G80:H80"/>
-    <mergeCell ref="D78:I78"/>
-    <mergeCell ref="G71:H71"/>
-    <mergeCell ref="D76:I76"/>
-    <mergeCell ref="D66:H66"/>
-    <mergeCell ref="D77:I77"/>
-    <mergeCell ref="D73:I73"/>
-    <mergeCell ref="D70:E70"/>
-    <mergeCell ref="D31:I31"/>
-    <mergeCell ref="G35:H35"/>
-    <mergeCell ref="D40:I40"/>
-    <mergeCell ref="D33:I33"/>
-    <mergeCell ref="D46:I46"/>
-    <mergeCell ref="D43:I43"/>
-    <mergeCell ref="G57:H57"/>
-    <mergeCell ref="D14:I14"/>
-    <mergeCell ref="G27:H27"/>
-    <mergeCell ref="D25:I25"/>
-    <mergeCell ref="G20:H20"/>
-    <mergeCell ref="D19:I19"/>
-    <mergeCell ref="D18:I18"/>
-    <mergeCell ref="D8:I8"/>
-    <mergeCell ref="D9:I9"/>
-    <mergeCell ref="D10:I10"/>
-    <mergeCell ref="D11:I11"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="G81:H81"/>
-    <mergeCell ref="D67:F67"/>
-    <mergeCell ref="F68:I68"/>
-    <mergeCell ref="D87:E87"/>
-    <mergeCell ref="G87:I87"/>
-    <mergeCell ref="D74:F74"/>
-    <mergeCell ref="D84:I84"/>
-    <mergeCell ref="D69:I69"/>
-    <mergeCell ref="G42:H42"/>
-    <mergeCell ref="D60:I60"/>
-    <mergeCell ref="D62:I62"/>
-    <mergeCell ref="D61:I61"/>
-    <mergeCell ref="G49:H49"/>
-    <mergeCell ref="D47:I47"/>
-    <mergeCell ref="D55:I55"/>
-    <mergeCell ref="D98:I98"/>
-    <mergeCell ref="D94:I94"/>
-    <mergeCell ref="H89:I89"/>
-    <mergeCell ref="D89:F89"/>
-    <mergeCell ref="G64:H64"/>
-    <mergeCell ref="D96:I96"/>
-    <mergeCell ref="D95:F95"/>
-    <mergeCell ref="G95:H95"/>
-    <mergeCell ref="D92:I92"/>
-    <mergeCell ref="D97:I97"/>
-    <mergeCell ref="D93:I93"/>
-    <mergeCell ref="D90:E90"/>
-    <mergeCell ref="D91:H91"/>
-    <mergeCell ref="E86:G86"/>
-    <mergeCell ref="D88:I88"/>
-    <mergeCell ref="H67:I67"/>
+    <mergeCell ref="D107:E107"/>
+    <mergeCell ref="F118:J118"/>
+    <mergeCell ref="G152:I152"/>
+    <mergeCell ref="D149:J150"/>
+    <mergeCell ref="G146:J146"/>
+    <mergeCell ref="D164:J164"/>
+    <mergeCell ref="D157:J157"/>
+    <mergeCell ref="D143:J143"/>
+    <mergeCell ref="D135:J135"/>
+    <mergeCell ref="F127:J127"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/attendance_sheet.xlsx
+++ b/attendance_sheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\repositary\3rd_Year_5th_Semester\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AE1DC0E-0A91-4966-B845-F94DEE3479CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35C855F6-0F6F-4AF9-80CE-7FA09F1C2224}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{EB654061-A886-47D1-BF86-9B1A84FCE7FB}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="844" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="852" uniqueCount="71">
   <si>
     <t>Date</t>
   </si>
@@ -538,23 +538,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -574,11 +562,23 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -981,14 +981,14 @@
       <c r="C8" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D8" s="39" t="s">
+      <c r="D8" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="E8" s="39"/>
-      <c r="F8" s="39"/>
-      <c r="G8" s="39"/>
-      <c r="H8" s="39"/>
-      <c r="I8" s="39"/>
+      <c r="E8" s="27"/>
+      <c r="F8" s="27"/>
+      <c r="G8" s="27"/>
+      <c r="H8" s="27"/>
+      <c r="I8" s="27"/>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B9" s="4">
@@ -997,14 +997,14 @@
       <c r="C9" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D9" s="39" t="s">
+      <c r="D9" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="E9" s="39"/>
-      <c r="F9" s="39"/>
-      <c r="G9" s="39"/>
-      <c r="H9" s="39"/>
-      <c r="I9" s="39"/>
+      <c r="E9" s="27"/>
+      <c r="F9" s="27"/>
+      <c r="G9" s="27"/>
+      <c r="H9" s="27"/>
+      <c r="I9" s="27"/>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B10" s="4">
@@ -1013,14 +1013,14 @@
       <c r="C10" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D10" s="39" t="s">
+      <c r="D10" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="E10" s="39"/>
-      <c r="F10" s="39"/>
-      <c r="G10" s="39"/>
-      <c r="H10" s="39"/>
-      <c r="I10" s="39"/>
+      <c r="E10" s="27"/>
+      <c r="F10" s="27"/>
+      <c r="G10" s="27"/>
+      <c r="H10" s="27"/>
+      <c r="I10" s="27"/>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B11" s="4">
@@ -1029,14 +1029,14 @@
       <c r="C11" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D11" s="39" t="s">
+      <c r="D11" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="E11" s="39"/>
-      <c r="F11" s="39"/>
-      <c r="G11" s="39"/>
-      <c r="H11" s="39"/>
-      <c r="I11" s="39"/>
+      <c r="E11" s="27"/>
+      <c r="F11" s="27"/>
+      <c r="G11" s="27"/>
+      <c r="H11" s="27"/>
+      <c r="I11" s="27"/>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B12" s="4">
@@ -1080,10 +1080,10 @@
       <c r="F13" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="G13" s="39" t="s">
+      <c r="G13" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="H13" s="39"/>
+      <c r="H13" s="27"/>
       <c r="I13" s="1" t="s">
         <v>14</v>
       </c>
@@ -1095,14 +1095,14 @@
       <c r="C14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D14" s="39" t="s">
+      <c r="D14" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="E14" s="39"/>
-      <c r="F14" s="39"/>
-      <c r="G14" s="39"/>
-      <c r="H14" s="39"/>
-      <c r="I14" s="39"/>
+      <c r="E14" s="27"/>
+      <c r="F14" s="27"/>
+      <c r="G14" s="27"/>
+      <c r="H14" s="27"/>
+      <c r="I14" s="27"/>
     </row>
     <row r="15" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B15" s="4">
@@ -1189,14 +1189,14 @@
       <c r="C18" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D18" s="39" t="s">
+      <c r="D18" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="E18" s="39"/>
-      <c r="F18" s="39"/>
-      <c r="G18" s="39"/>
-      <c r="H18" s="39"/>
-      <c r="I18" s="39"/>
+      <c r="E18" s="27"/>
+      <c r="F18" s="27"/>
+      <c r="G18" s="27"/>
+      <c r="H18" s="27"/>
+      <c r="I18" s="27"/>
     </row>
     <row r="19" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B19" s="4">
@@ -1205,14 +1205,14 @@
       <c r="C19" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D19" s="39" t="s">
+      <c r="D19" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="E19" s="39"/>
-      <c r="F19" s="39"/>
-      <c r="G19" s="39"/>
-      <c r="H19" s="39"/>
-      <c r="I19" s="39"/>
+      <c r="E19" s="27"/>
+      <c r="F19" s="27"/>
+      <c r="G19" s="27"/>
+      <c r="H19" s="27"/>
+      <c r="I19" s="27"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B20" s="4">
@@ -1230,10 +1230,10 @@
       <c r="F20" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G20" s="39" t="s">
+      <c r="G20" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="H20" s="39"/>
+      <c r="H20" s="27"/>
       <c r="I20" s="1" t="s">
         <v>14</v>
       </c>
@@ -1349,14 +1349,14 @@
       <c r="C25" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D25" s="39" t="s">
+      <c r="D25" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="E25" s="39"/>
-      <c r="F25" s="39"/>
-      <c r="G25" s="39"/>
-      <c r="H25" s="39"/>
-      <c r="I25" s="39"/>
+      <c r="E25" s="27"/>
+      <c r="F25" s="27"/>
+      <c r="G25" s="27"/>
+      <c r="H25" s="27"/>
+      <c r="I25" s="27"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B26" s="4">
@@ -1400,10 +1400,10 @@
       <c r="F27" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G27" s="39" t="s">
+      <c r="G27" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="H27" s="39"/>
+      <c r="H27" s="27"/>
       <c r="I27" s="1" t="s">
         <v>14</v>
       </c>
@@ -1467,14 +1467,14 @@
       <c r="C30" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D30" s="38" t="s">
+      <c r="D30" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="E30" s="38"/>
-      <c r="F30" s="38"/>
-      <c r="G30" s="38"/>
-      <c r="H30" s="38"/>
-      <c r="I30" s="38"/>
+      <c r="E30" s="26"/>
+      <c r="F30" s="26"/>
+      <c r="G30" s="26"/>
+      <c r="H30" s="26"/>
+      <c r="I30" s="26"/>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B31" s="4">
@@ -1483,14 +1483,14 @@
       <c r="C31" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D31" s="38" t="s">
+      <c r="D31" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="E31" s="38"/>
-      <c r="F31" s="38"/>
-      <c r="G31" s="38"/>
-      <c r="H31" s="38"/>
-      <c r="I31" s="38"/>
+      <c r="E31" s="26"/>
+      <c r="F31" s="26"/>
+      <c r="G31" s="26"/>
+      <c r="H31" s="26"/>
+      <c r="I31" s="26"/>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B32" s="4">
@@ -1525,14 +1525,14 @@
       <c r="C33" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D33" s="38" t="s">
+      <c r="D33" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="E33" s="38"/>
-      <c r="F33" s="38"/>
-      <c r="G33" s="38"/>
-      <c r="H33" s="38"/>
-      <c r="I33" s="38"/>
+      <c r="E33" s="26"/>
+      <c r="F33" s="26"/>
+      <c r="G33" s="26"/>
+      <c r="H33" s="26"/>
+      <c r="I33" s="26"/>
     </row>
     <row r="34" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B34" s="4">
@@ -1576,10 +1576,10 @@
       <c r="F35" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G35" s="38" t="s">
+      <c r="G35" s="26" t="s">
         <v>18</v>
       </c>
-      <c r="H35" s="38"/>
+      <c r="H35" s="26"/>
       <c r="I35" s="1" t="s">
         <v>14</v>
       </c>
@@ -1695,14 +1695,14 @@
       <c r="C40" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D40" s="38" t="s">
+      <c r="D40" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="E40" s="38"/>
-      <c r="F40" s="38"/>
-      <c r="G40" s="38"/>
-      <c r="H40" s="38"/>
-      <c r="I40" s="38"/>
+      <c r="E40" s="26"/>
+      <c r="F40" s="26"/>
+      <c r="G40" s="26"/>
+      <c r="H40" s="26"/>
+      <c r="I40" s="26"/>
     </row>
     <row r="41" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B41" s="4">
@@ -1746,10 +1746,10 @@
       <c r="F42" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G42" s="38" t="s">
+      <c r="G42" s="26" t="s">
         <v>28</v>
       </c>
-      <c r="H42" s="38"/>
+      <c r="H42" s="26"/>
       <c r="I42" s="1" t="s">
         <v>15</v>
       </c>
@@ -1761,14 +1761,14 @@
       <c r="C43" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D43" s="38" t="s">
+      <c r="D43" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="E43" s="38"/>
-      <c r="F43" s="38"/>
-      <c r="G43" s="38"/>
-      <c r="H43" s="38"/>
-      <c r="I43" s="38"/>
+      <c r="E43" s="26"/>
+      <c r="F43" s="26"/>
+      <c r="G43" s="26"/>
+      <c r="H43" s="26"/>
+      <c r="I43" s="26"/>
     </row>
     <row r="44" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B44" s="4">
@@ -1832,14 +1832,14 @@
       <c r="C46" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D46" s="38" t="s">
+      <c r="D46" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="E46" s="38"/>
-      <c r="F46" s="38"/>
-      <c r="G46" s="38"/>
-      <c r="H46" s="38"/>
-      <c r="I46" s="38"/>
+      <c r="E46" s="26"/>
+      <c r="F46" s="26"/>
+      <c r="G46" s="26"/>
+      <c r="H46" s="26"/>
+      <c r="I46" s="26"/>
     </row>
     <row r="47" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B47" s="4">
@@ -3125,28 +3125,28 @@
       <c r="I111" s="20"/>
     </row>
     <row r="112" spans="2:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B112" s="32" t="s">
+      <c r="B112" s="28" t="s">
         <v>57</v>
       </c>
-      <c r="C112" s="33"/>
-      <c r="D112" s="33"/>
-      <c r="E112" s="33"/>
-      <c r="F112" s="33"/>
-      <c r="G112" s="33"/>
-      <c r="H112" s="33"/>
-      <c r="I112" s="33"/>
-      <c r="J112" s="34"/>
+      <c r="C112" s="29"/>
+      <c r="D112" s="29"/>
+      <c r="E112" s="29"/>
+      <c r="F112" s="29"/>
+      <c r="G112" s="29"/>
+      <c r="H112" s="29"/>
+      <c r="I112" s="29"/>
+      <c r="J112" s="30"/>
     </row>
     <row r="113" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B113" s="35"/>
-      <c r="C113" s="36"/>
-      <c r="D113" s="36"/>
-      <c r="E113" s="36"/>
-      <c r="F113" s="36"/>
-      <c r="G113" s="36"/>
-      <c r="H113" s="36"/>
-      <c r="I113" s="36"/>
-      <c r="J113" s="37"/>
+      <c r="B113" s="31"/>
+      <c r="C113" s="32"/>
+      <c r="D113" s="32"/>
+      <c r="E113" s="32"/>
+      <c r="F113" s="32"/>
+      <c r="G113" s="32"/>
+      <c r="H113" s="32"/>
+      <c r="I113" s="32"/>
+      <c r="J113" s="33"/>
     </row>
     <row r="114" spans="2:10" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B114" s="8" t="s">
@@ -4068,15 +4068,15 @@
       <c r="C149" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D149" s="26" t="s">
+      <c r="D149" s="34" t="s">
         <v>20</v>
       </c>
-      <c r="E149" s="27"/>
-      <c r="F149" s="27"/>
-      <c r="G149" s="27"/>
-      <c r="H149" s="27"/>
-      <c r="I149" s="27"/>
-      <c r="J149" s="28"/>
+      <c r="E149" s="35"/>
+      <c r="F149" s="35"/>
+      <c r="G149" s="35"/>
+      <c r="H149" s="35"/>
+      <c r="I149" s="35"/>
+      <c r="J149" s="36"/>
     </row>
     <row r="150" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B150" s="4">
@@ -4085,13 +4085,13 @@
       <c r="C150" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D150" s="29"/>
-      <c r="E150" s="30"/>
-      <c r="F150" s="30"/>
-      <c r="G150" s="30"/>
-      <c r="H150" s="30"/>
-      <c r="I150" s="30"/>
-      <c r="J150" s="31"/>
+      <c r="D150" s="37"/>
+      <c r="E150" s="38"/>
+      <c r="F150" s="38"/>
+      <c r="G150" s="38"/>
+      <c r="H150" s="38"/>
+      <c r="I150" s="38"/>
+      <c r="J150" s="39"/>
     </row>
     <row r="151" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B151" s="4">
@@ -4630,15 +4630,33 @@
       </c>
     </row>
     <row r="171" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B171" s="3"/>
-      <c r="C171" s="3"/>
-      <c r="D171" s="3"/>
-      <c r="E171" s="3"/>
-      <c r="F171" s="3"/>
-      <c r="G171" s="3"/>
-      <c r="H171" s="3"/>
-      <c r="I171" s="1"/>
-      <c r="J171" s="1"/>
+      <c r="B171" s="4">
+        <v>45899</v>
+      </c>
+      <c r="C171" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D171" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E171" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F171" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G171" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H171" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I171" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="J171" s="1" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="172" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B172" s="3"/>
@@ -7337,6 +7355,74 @@
     </row>
   </sheetData>
   <mergeCells count="84">
+    <mergeCell ref="D164:J164"/>
+    <mergeCell ref="D157:J157"/>
+    <mergeCell ref="D143:J143"/>
+    <mergeCell ref="D135:J135"/>
+    <mergeCell ref="F127:J127"/>
+    <mergeCell ref="D107:E107"/>
+    <mergeCell ref="F118:J118"/>
+    <mergeCell ref="G152:I152"/>
+    <mergeCell ref="D149:J150"/>
+    <mergeCell ref="G146:J146"/>
+    <mergeCell ref="D106:E106"/>
+    <mergeCell ref="D99:G99"/>
+    <mergeCell ref="G126:I126"/>
+    <mergeCell ref="F125:J125"/>
+    <mergeCell ref="D128:J128"/>
+    <mergeCell ref="D103:E103"/>
+    <mergeCell ref="D104:E104"/>
+    <mergeCell ref="D105:E105"/>
+    <mergeCell ref="G100:I100"/>
+    <mergeCell ref="B101:I101"/>
+    <mergeCell ref="D108:E108"/>
+    <mergeCell ref="B112:J113"/>
+    <mergeCell ref="G124:J124"/>
+    <mergeCell ref="D120:H120"/>
+    <mergeCell ref="G123:J123"/>
+    <mergeCell ref="D121:J121"/>
+    <mergeCell ref="D30:I30"/>
+    <mergeCell ref="G80:H80"/>
+    <mergeCell ref="D78:I78"/>
+    <mergeCell ref="G71:H71"/>
+    <mergeCell ref="D76:I76"/>
+    <mergeCell ref="D66:H66"/>
+    <mergeCell ref="D77:I77"/>
+    <mergeCell ref="D73:I73"/>
+    <mergeCell ref="D70:E70"/>
+    <mergeCell ref="D31:I31"/>
+    <mergeCell ref="G35:H35"/>
+    <mergeCell ref="D40:I40"/>
+    <mergeCell ref="D33:I33"/>
+    <mergeCell ref="D46:I46"/>
+    <mergeCell ref="D43:I43"/>
+    <mergeCell ref="G57:H57"/>
+    <mergeCell ref="D14:I14"/>
+    <mergeCell ref="G27:H27"/>
+    <mergeCell ref="D25:I25"/>
+    <mergeCell ref="G20:H20"/>
+    <mergeCell ref="D19:I19"/>
+    <mergeCell ref="D18:I18"/>
+    <mergeCell ref="D8:I8"/>
+    <mergeCell ref="D9:I9"/>
+    <mergeCell ref="D10:I10"/>
+    <mergeCell ref="D11:I11"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="G81:H81"/>
+    <mergeCell ref="D67:F67"/>
+    <mergeCell ref="F68:I68"/>
+    <mergeCell ref="D87:E87"/>
+    <mergeCell ref="G87:I87"/>
+    <mergeCell ref="D74:F74"/>
+    <mergeCell ref="D84:I84"/>
+    <mergeCell ref="D69:I69"/>
+    <mergeCell ref="G42:H42"/>
+    <mergeCell ref="D60:I60"/>
+    <mergeCell ref="D62:I62"/>
+    <mergeCell ref="D61:I61"/>
+    <mergeCell ref="G49:H49"/>
+    <mergeCell ref="D47:I47"/>
+    <mergeCell ref="D55:I55"/>
     <mergeCell ref="D98:I98"/>
     <mergeCell ref="D94:I94"/>
     <mergeCell ref="H89:I89"/>
@@ -7353,74 +7439,6 @@
     <mergeCell ref="E86:G86"/>
     <mergeCell ref="D88:I88"/>
     <mergeCell ref="H67:I67"/>
-    <mergeCell ref="G42:H42"/>
-    <mergeCell ref="D60:I60"/>
-    <mergeCell ref="D62:I62"/>
-    <mergeCell ref="D61:I61"/>
-    <mergeCell ref="G49:H49"/>
-    <mergeCell ref="D47:I47"/>
-    <mergeCell ref="D55:I55"/>
-    <mergeCell ref="G81:H81"/>
-    <mergeCell ref="D67:F67"/>
-    <mergeCell ref="F68:I68"/>
-    <mergeCell ref="D87:E87"/>
-    <mergeCell ref="G87:I87"/>
-    <mergeCell ref="D74:F74"/>
-    <mergeCell ref="D84:I84"/>
-    <mergeCell ref="D69:I69"/>
-    <mergeCell ref="D8:I8"/>
-    <mergeCell ref="D9:I9"/>
-    <mergeCell ref="D10:I10"/>
-    <mergeCell ref="D11:I11"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="D14:I14"/>
-    <mergeCell ref="G27:H27"/>
-    <mergeCell ref="D25:I25"/>
-    <mergeCell ref="G20:H20"/>
-    <mergeCell ref="D19:I19"/>
-    <mergeCell ref="D18:I18"/>
-    <mergeCell ref="D30:I30"/>
-    <mergeCell ref="G80:H80"/>
-    <mergeCell ref="D78:I78"/>
-    <mergeCell ref="G71:H71"/>
-    <mergeCell ref="D76:I76"/>
-    <mergeCell ref="D66:H66"/>
-    <mergeCell ref="D77:I77"/>
-    <mergeCell ref="D73:I73"/>
-    <mergeCell ref="D70:E70"/>
-    <mergeCell ref="D31:I31"/>
-    <mergeCell ref="G35:H35"/>
-    <mergeCell ref="D40:I40"/>
-    <mergeCell ref="D33:I33"/>
-    <mergeCell ref="D46:I46"/>
-    <mergeCell ref="D43:I43"/>
-    <mergeCell ref="G57:H57"/>
-    <mergeCell ref="D106:E106"/>
-    <mergeCell ref="D99:G99"/>
-    <mergeCell ref="G126:I126"/>
-    <mergeCell ref="F125:J125"/>
-    <mergeCell ref="D128:J128"/>
-    <mergeCell ref="D103:E103"/>
-    <mergeCell ref="D104:E104"/>
-    <mergeCell ref="D105:E105"/>
-    <mergeCell ref="G100:I100"/>
-    <mergeCell ref="B101:I101"/>
-    <mergeCell ref="D108:E108"/>
-    <mergeCell ref="B112:J113"/>
-    <mergeCell ref="G124:J124"/>
-    <mergeCell ref="D120:H120"/>
-    <mergeCell ref="G123:J123"/>
-    <mergeCell ref="D121:J121"/>
-    <mergeCell ref="D107:E107"/>
-    <mergeCell ref="F118:J118"/>
-    <mergeCell ref="G152:I152"/>
-    <mergeCell ref="D149:J150"/>
-    <mergeCell ref="G146:J146"/>
-    <mergeCell ref="D164:J164"/>
-    <mergeCell ref="D157:J157"/>
-    <mergeCell ref="D143:J143"/>
-    <mergeCell ref="D135:J135"/>
-    <mergeCell ref="F127:J127"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/attendance_sheet.xlsx
+++ b/attendance_sheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\repositary\3rd_Year_5th_Semester\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35C855F6-0F6F-4AF9-80CE-7FA09F1C2224}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12AD68DC-CADB-487C-98CE-7D3240F0DD63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{EB654061-A886-47D1-BF86-9B1A84FCE7FB}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="852" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="854" uniqueCount="71">
   <si>
     <t>Date</t>
   </si>
@@ -538,11 +538,23 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -562,23 +574,11 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -981,14 +981,14 @@
       <c r="C8" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D8" s="27" t="s">
+      <c r="D8" s="39" t="s">
         <v>20</v>
       </c>
-      <c r="E8" s="27"/>
-      <c r="F8" s="27"/>
-      <c r="G8" s="27"/>
-      <c r="H8" s="27"/>
-      <c r="I8" s="27"/>
+      <c r="E8" s="39"/>
+      <c r="F8" s="39"/>
+      <c r="G8" s="39"/>
+      <c r="H8" s="39"/>
+      <c r="I8" s="39"/>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B9" s="4">
@@ -997,14 +997,14 @@
       <c r="C9" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D9" s="27" t="s">
+      <c r="D9" s="39" t="s">
         <v>20</v>
       </c>
-      <c r="E9" s="27"/>
-      <c r="F9" s="27"/>
-      <c r="G9" s="27"/>
-      <c r="H9" s="27"/>
-      <c r="I9" s="27"/>
+      <c r="E9" s="39"/>
+      <c r="F9" s="39"/>
+      <c r="G9" s="39"/>
+      <c r="H9" s="39"/>
+      <c r="I9" s="39"/>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B10" s="4">
@@ -1013,14 +1013,14 @@
       <c r="C10" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D10" s="27" t="s">
+      <c r="D10" s="39" t="s">
         <v>20</v>
       </c>
-      <c r="E10" s="27"/>
-      <c r="F10" s="27"/>
-      <c r="G10" s="27"/>
-      <c r="H10" s="27"/>
-      <c r="I10" s="27"/>
+      <c r="E10" s="39"/>
+      <c r="F10" s="39"/>
+      <c r="G10" s="39"/>
+      <c r="H10" s="39"/>
+      <c r="I10" s="39"/>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B11" s="4">
@@ -1029,14 +1029,14 @@
       <c r="C11" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D11" s="27" t="s">
+      <c r="D11" s="39" t="s">
         <v>20</v>
       </c>
-      <c r="E11" s="27"/>
-      <c r="F11" s="27"/>
-      <c r="G11" s="27"/>
-      <c r="H11" s="27"/>
-      <c r="I11" s="27"/>
+      <c r="E11" s="39"/>
+      <c r="F11" s="39"/>
+      <c r="G11" s="39"/>
+      <c r="H11" s="39"/>
+      <c r="I11" s="39"/>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B12" s="4">
@@ -1080,10 +1080,10 @@
       <c r="F13" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="G13" s="27" t="s">
+      <c r="G13" s="39" t="s">
         <v>18</v>
       </c>
-      <c r="H13" s="27"/>
+      <c r="H13" s="39"/>
       <c r="I13" s="1" t="s">
         <v>14</v>
       </c>
@@ -1095,14 +1095,14 @@
       <c r="C14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D14" s="27" t="s">
+      <c r="D14" s="39" t="s">
         <v>19</v>
       </c>
-      <c r="E14" s="27"/>
-      <c r="F14" s="27"/>
-      <c r="G14" s="27"/>
-      <c r="H14" s="27"/>
-      <c r="I14" s="27"/>
+      <c r="E14" s="39"/>
+      <c r="F14" s="39"/>
+      <c r="G14" s="39"/>
+      <c r="H14" s="39"/>
+      <c r="I14" s="39"/>
     </row>
     <row r="15" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B15" s="4">
@@ -1189,14 +1189,14 @@
       <c r="C18" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D18" s="27" t="s">
+      <c r="D18" s="39" t="s">
         <v>23</v>
       </c>
-      <c r="E18" s="27"/>
-      <c r="F18" s="27"/>
-      <c r="G18" s="27"/>
-      <c r="H18" s="27"/>
-      <c r="I18" s="27"/>
+      <c r="E18" s="39"/>
+      <c r="F18" s="39"/>
+      <c r="G18" s="39"/>
+      <c r="H18" s="39"/>
+      <c r="I18" s="39"/>
     </row>
     <row r="19" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B19" s="4">
@@ -1205,14 +1205,14 @@
       <c r="C19" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D19" s="27" t="s">
+      <c r="D19" s="39" t="s">
         <v>23</v>
       </c>
-      <c r="E19" s="27"/>
-      <c r="F19" s="27"/>
-      <c r="G19" s="27"/>
-      <c r="H19" s="27"/>
-      <c r="I19" s="27"/>
+      <c r="E19" s="39"/>
+      <c r="F19" s="39"/>
+      <c r="G19" s="39"/>
+      <c r="H19" s="39"/>
+      <c r="I19" s="39"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B20" s="4">
@@ -1230,10 +1230,10 @@
       <c r="F20" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G20" s="27" t="s">
+      <c r="G20" s="39" t="s">
         <v>15</v>
       </c>
-      <c r="H20" s="27"/>
+      <c r="H20" s="39"/>
       <c r="I20" s="1" t="s">
         <v>14</v>
       </c>
@@ -1349,14 +1349,14 @@
       <c r="C25" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D25" s="27" t="s">
+      <c r="D25" s="39" t="s">
         <v>26</v>
       </c>
-      <c r="E25" s="27"/>
-      <c r="F25" s="27"/>
-      <c r="G25" s="27"/>
-      <c r="H25" s="27"/>
-      <c r="I25" s="27"/>
+      <c r="E25" s="39"/>
+      <c r="F25" s="39"/>
+      <c r="G25" s="39"/>
+      <c r="H25" s="39"/>
+      <c r="I25" s="39"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B26" s="4">
@@ -1400,10 +1400,10 @@
       <c r="F27" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G27" s="27" t="s">
+      <c r="G27" s="39" t="s">
         <v>18</v>
       </c>
-      <c r="H27" s="27"/>
+      <c r="H27" s="39"/>
       <c r="I27" s="1" t="s">
         <v>14</v>
       </c>
@@ -1467,14 +1467,14 @@
       <c r="C30" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D30" s="26" t="s">
+      <c r="D30" s="38" t="s">
         <v>20</v>
       </c>
-      <c r="E30" s="26"/>
-      <c r="F30" s="26"/>
-      <c r="G30" s="26"/>
-      <c r="H30" s="26"/>
-      <c r="I30" s="26"/>
+      <c r="E30" s="38"/>
+      <c r="F30" s="38"/>
+      <c r="G30" s="38"/>
+      <c r="H30" s="38"/>
+      <c r="I30" s="38"/>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B31" s="4">
@@ -1483,14 +1483,14 @@
       <c r="C31" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D31" s="26" t="s">
+      <c r="D31" s="38" t="s">
         <v>20</v>
       </c>
-      <c r="E31" s="26"/>
-      <c r="F31" s="26"/>
-      <c r="G31" s="26"/>
-      <c r="H31" s="26"/>
-      <c r="I31" s="26"/>
+      <c r="E31" s="38"/>
+      <c r="F31" s="38"/>
+      <c r="G31" s="38"/>
+      <c r="H31" s="38"/>
+      <c r="I31" s="38"/>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B32" s="4">
@@ -1525,14 +1525,14 @@
       <c r="C33" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D33" s="26" t="s">
+      <c r="D33" s="38" t="s">
         <v>20</v>
       </c>
-      <c r="E33" s="26"/>
-      <c r="F33" s="26"/>
-      <c r="G33" s="26"/>
-      <c r="H33" s="26"/>
-      <c r="I33" s="26"/>
+      <c r="E33" s="38"/>
+      <c r="F33" s="38"/>
+      <c r="G33" s="38"/>
+      <c r="H33" s="38"/>
+      <c r="I33" s="38"/>
     </row>
     <row r="34" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B34" s="4">
@@ -1576,10 +1576,10 @@
       <c r="F35" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G35" s="26" t="s">
+      <c r="G35" s="38" t="s">
         <v>18</v>
       </c>
-      <c r="H35" s="26"/>
+      <c r="H35" s="38"/>
       <c r="I35" s="1" t="s">
         <v>14</v>
       </c>
@@ -1695,14 +1695,14 @@
       <c r="C40" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D40" s="26" t="s">
+      <c r="D40" s="38" t="s">
         <v>20</v>
       </c>
-      <c r="E40" s="26"/>
-      <c r="F40" s="26"/>
-      <c r="G40" s="26"/>
-      <c r="H40" s="26"/>
-      <c r="I40" s="26"/>
+      <c r="E40" s="38"/>
+      <c r="F40" s="38"/>
+      <c r="G40" s="38"/>
+      <c r="H40" s="38"/>
+      <c r="I40" s="38"/>
     </row>
     <row r="41" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B41" s="4">
@@ -1746,10 +1746,10 @@
       <c r="F42" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G42" s="26" t="s">
+      <c r="G42" s="38" t="s">
         <v>28</v>
       </c>
-      <c r="H42" s="26"/>
+      <c r="H42" s="38"/>
       <c r="I42" s="1" t="s">
         <v>15</v>
       </c>
@@ -1761,14 +1761,14 @@
       <c r="C43" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D43" s="26" t="s">
+      <c r="D43" s="38" t="s">
         <v>20</v>
       </c>
-      <c r="E43" s="26"/>
-      <c r="F43" s="26"/>
-      <c r="G43" s="26"/>
-      <c r="H43" s="26"/>
-      <c r="I43" s="26"/>
+      <c r="E43" s="38"/>
+      <c r="F43" s="38"/>
+      <c r="G43" s="38"/>
+      <c r="H43" s="38"/>
+      <c r="I43" s="38"/>
     </row>
     <row r="44" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B44" s="4">
@@ -1832,14 +1832,14 @@
       <c r="C46" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D46" s="26" t="s">
+      <c r="D46" s="38" t="s">
         <v>20</v>
       </c>
-      <c r="E46" s="26"/>
-      <c r="F46" s="26"/>
-      <c r="G46" s="26"/>
-      <c r="H46" s="26"/>
-      <c r="I46" s="26"/>
+      <c r="E46" s="38"/>
+      <c r="F46" s="38"/>
+      <c r="G46" s="38"/>
+      <c r="H46" s="38"/>
+      <c r="I46" s="38"/>
     </row>
     <row r="47" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B47" s="4">
@@ -3125,28 +3125,28 @@
       <c r="I111" s="20"/>
     </row>
     <row r="112" spans="2:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B112" s="28" t="s">
+      <c r="B112" s="32" t="s">
         <v>57</v>
       </c>
-      <c r="C112" s="29"/>
-      <c r="D112" s="29"/>
-      <c r="E112" s="29"/>
-      <c r="F112" s="29"/>
-      <c r="G112" s="29"/>
-      <c r="H112" s="29"/>
-      <c r="I112" s="29"/>
-      <c r="J112" s="30"/>
+      <c r="C112" s="33"/>
+      <c r="D112" s="33"/>
+      <c r="E112" s="33"/>
+      <c r="F112" s="33"/>
+      <c r="G112" s="33"/>
+      <c r="H112" s="33"/>
+      <c r="I112" s="33"/>
+      <c r="J112" s="34"/>
     </row>
     <row r="113" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B113" s="31"/>
-      <c r="C113" s="32"/>
-      <c r="D113" s="32"/>
-      <c r="E113" s="32"/>
-      <c r="F113" s="32"/>
-      <c r="G113" s="32"/>
-      <c r="H113" s="32"/>
-      <c r="I113" s="32"/>
-      <c r="J113" s="33"/>
+      <c r="B113" s="35"/>
+      <c r="C113" s="36"/>
+      <c r="D113" s="36"/>
+      <c r="E113" s="36"/>
+      <c r="F113" s="36"/>
+      <c r="G113" s="36"/>
+      <c r="H113" s="36"/>
+      <c r="I113" s="36"/>
+      <c r="J113" s="37"/>
     </row>
     <row r="114" spans="2:10" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B114" s="8" t="s">
@@ -4068,15 +4068,15 @@
       <c r="C149" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D149" s="34" t="s">
+      <c r="D149" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="E149" s="35"/>
-      <c r="F149" s="35"/>
-      <c r="G149" s="35"/>
-      <c r="H149" s="35"/>
-      <c r="I149" s="35"/>
-      <c r="J149" s="36"/>
+      <c r="E149" s="27"/>
+      <c r="F149" s="27"/>
+      <c r="G149" s="27"/>
+      <c r="H149" s="27"/>
+      <c r="I149" s="27"/>
+      <c r="J149" s="28"/>
     </row>
     <row r="150" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B150" s="4">
@@ -4085,13 +4085,13 @@
       <c r="C150" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D150" s="37"/>
-      <c r="E150" s="38"/>
-      <c r="F150" s="38"/>
-      <c r="G150" s="38"/>
-      <c r="H150" s="38"/>
-      <c r="I150" s="38"/>
-      <c r="J150" s="39"/>
+      <c r="D150" s="29"/>
+      <c r="E150" s="30"/>
+      <c r="F150" s="30"/>
+      <c r="G150" s="30"/>
+      <c r="H150" s="30"/>
+      <c r="I150" s="30"/>
+      <c r="J150" s="31"/>
     </row>
     <row r="151" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B151" s="4">
@@ -4659,15 +4659,21 @@
       </c>
     </row>
     <row r="172" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B172" s="3"/>
-      <c r="C172" s="3"/>
-      <c r="D172" s="3"/>
-      <c r="E172" s="3"/>
-      <c r="F172" s="3"/>
-      <c r="G172" s="3"/>
-      <c r="H172" s="3"/>
-      <c r="I172" s="1"/>
-      <c r="J172" s="1"/>
+      <c r="B172" s="4">
+        <v>45900</v>
+      </c>
+      <c r="C172" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D172" s="23" t="s">
+        <v>20</v>
+      </c>
+      <c r="E172" s="24"/>
+      <c r="F172" s="24"/>
+      <c r="G172" s="24"/>
+      <c r="H172" s="24"/>
+      <c r="I172" s="24"/>
+      <c r="J172" s="25"/>
     </row>
     <row r="173" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B173" s="3"/>
@@ -7354,17 +7360,66 @@
       <c r="J416" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="84">
-    <mergeCell ref="D164:J164"/>
-    <mergeCell ref="D157:J157"/>
-    <mergeCell ref="D143:J143"/>
-    <mergeCell ref="D135:J135"/>
-    <mergeCell ref="F127:J127"/>
-    <mergeCell ref="D107:E107"/>
-    <mergeCell ref="F118:J118"/>
-    <mergeCell ref="G152:I152"/>
-    <mergeCell ref="D149:J150"/>
-    <mergeCell ref="G146:J146"/>
+  <mergeCells count="85">
+    <mergeCell ref="D172:J172"/>
+    <mergeCell ref="D98:I98"/>
+    <mergeCell ref="D94:I94"/>
+    <mergeCell ref="H89:I89"/>
+    <mergeCell ref="D89:F89"/>
+    <mergeCell ref="G64:H64"/>
+    <mergeCell ref="D96:I96"/>
+    <mergeCell ref="D95:F95"/>
+    <mergeCell ref="G95:H95"/>
+    <mergeCell ref="D92:I92"/>
+    <mergeCell ref="D97:I97"/>
+    <mergeCell ref="D93:I93"/>
+    <mergeCell ref="D90:E90"/>
+    <mergeCell ref="D91:H91"/>
+    <mergeCell ref="E86:G86"/>
+    <mergeCell ref="D88:I88"/>
+    <mergeCell ref="H67:I67"/>
+    <mergeCell ref="G42:H42"/>
+    <mergeCell ref="D60:I60"/>
+    <mergeCell ref="D62:I62"/>
+    <mergeCell ref="D61:I61"/>
+    <mergeCell ref="G49:H49"/>
+    <mergeCell ref="D47:I47"/>
+    <mergeCell ref="D55:I55"/>
+    <mergeCell ref="G81:H81"/>
+    <mergeCell ref="D67:F67"/>
+    <mergeCell ref="F68:I68"/>
+    <mergeCell ref="D87:E87"/>
+    <mergeCell ref="G87:I87"/>
+    <mergeCell ref="D74:F74"/>
+    <mergeCell ref="D84:I84"/>
+    <mergeCell ref="D69:I69"/>
+    <mergeCell ref="D8:I8"/>
+    <mergeCell ref="D9:I9"/>
+    <mergeCell ref="D10:I10"/>
+    <mergeCell ref="D11:I11"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="D14:I14"/>
+    <mergeCell ref="G27:H27"/>
+    <mergeCell ref="D25:I25"/>
+    <mergeCell ref="G20:H20"/>
+    <mergeCell ref="D19:I19"/>
+    <mergeCell ref="D18:I18"/>
+    <mergeCell ref="D30:I30"/>
+    <mergeCell ref="G80:H80"/>
+    <mergeCell ref="D78:I78"/>
+    <mergeCell ref="G71:H71"/>
+    <mergeCell ref="D76:I76"/>
+    <mergeCell ref="D66:H66"/>
+    <mergeCell ref="D77:I77"/>
+    <mergeCell ref="D73:I73"/>
+    <mergeCell ref="D70:E70"/>
+    <mergeCell ref="D31:I31"/>
+    <mergeCell ref="G35:H35"/>
+    <mergeCell ref="D40:I40"/>
+    <mergeCell ref="D33:I33"/>
+    <mergeCell ref="D46:I46"/>
+    <mergeCell ref="D43:I43"/>
+    <mergeCell ref="G57:H57"/>
     <mergeCell ref="D106:E106"/>
     <mergeCell ref="D99:G99"/>
     <mergeCell ref="G126:I126"/>
@@ -7381,64 +7436,16 @@
     <mergeCell ref="D120:H120"/>
     <mergeCell ref="G123:J123"/>
     <mergeCell ref="D121:J121"/>
-    <mergeCell ref="D30:I30"/>
-    <mergeCell ref="G80:H80"/>
-    <mergeCell ref="D78:I78"/>
-    <mergeCell ref="G71:H71"/>
-    <mergeCell ref="D76:I76"/>
-    <mergeCell ref="D66:H66"/>
-    <mergeCell ref="D77:I77"/>
-    <mergeCell ref="D73:I73"/>
-    <mergeCell ref="D70:E70"/>
-    <mergeCell ref="D31:I31"/>
-    <mergeCell ref="G35:H35"/>
-    <mergeCell ref="D40:I40"/>
-    <mergeCell ref="D33:I33"/>
-    <mergeCell ref="D46:I46"/>
-    <mergeCell ref="D43:I43"/>
-    <mergeCell ref="G57:H57"/>
-    <mergeCell ref="D14:I14"/>
-    <mergeCell ref="G27:H27"/>
-    <mergeCell ref="D25:I25"/>
-    <mergeCell ref="G20:H20"/>
-    <mergeCell ref="D19:I19"/>
-    <mergeCell ref="D18:I18"/>
-    <mergeCell ref="D8:I8"/>
-    <mergeCell ref="D9:I9"/>
-    <mergeCell ref="D10:I10"/>
-    <mergeCell ref="D11:I11"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="G81:H81"/>
-    <mergeCell ref="D67:F67"/>
-    <mergeCell ref="F68:I68"/>
-    <mergeCell ref="D87:E87"/>
-    <mergeCell ref="G87:I87"/>
-    <mergeCell ref="D74:F74"/>
-    <mergeCell ref="D84:I84"/>
-    <mergeCell ref="D69:I69"/>
-    <mergeCell ref="G42:H42"/>
-    <mergeCell ref="D60:I60"/>
-    <mergeCell ref="D62:I62"/>
-    <mergeCell ref="D61:I61"/>
-    <mergeCell ref="G49:H49"/>
-    <mergeCell ref="D47:I47"/>
-    <mergeCell ref="D55:I55"/>
-    <mergeCell ref="D98:I98"/>
-    <mergeCell ref="D94:I94"/>
-    <mergeCell ref="H89:I89"/>
-    <mergeCell ref="D89:F89"/>
-    <mergeCell ref="G64:H64"/>
-    <mergeCell ref="D96:I96"/>
-    <mergeCell ref="D95:F95"/>
-    <mergeCell ref="G95:H95"/>
-    <mergeCell ref="D92:I92"/>
-    <mergeCell ref="D97:I97"/>
-    <mergeCell ref="D93:I93"/>
-    <mergeCell ref="D90:E90"/>
-    <mergeCell ref="D91:H91"/>
-    <mergeCell ref="E86:G86"/>
-    <mergeCell ref="D88:I88"/>
-    <mergeCell ref="H67:I67"/>
+    <mergeCell ref="D107:E107"/>
+    <mergeCell ref="F118:J118"/>
+    <mergeCell ref="G152:I152"/>
+    <mergeCell ref="D149:J150"/>
+    <mergeCell ref="G146:J146"/>
+    <mergeCell ref="D164:J164"/>
+    <mergeCell ref="D157:J157"/>
+    <mergeCell ref="D143:J143"/>
+    <mergeCell ref="D135:J135"/>
+    <mergeCell ref="F127:J127"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/attendance_sheet.xlsx
+++ b/attendance_sheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\repositary\3rd_Year_5th_Semester\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12AD68DC-CADB-487C-98CE-7D3240F0DD63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{527D696E-48B2-4BAA-9B82-BABA1B4B78F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{EB654061-A886-47D1-BF86-9B1A84FCE7FB}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="854" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="862" uniqueCount="72">
   <si>
     <t>Date</t>
   </si>
@@ -250,6 +250,9 @@
   </si>
   <si>
     <t>1 class  p</t>
+  </si>
+  <si>
+    <t>1 classp</t>
   </si>
 </sst>
 </file>
@@ -538,23 +541,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -574,11 +565,23 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -981,14 +984,14 @@
       <c r="C8" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D8" s="39" t="s">
+      <c r="D8" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="E8" s="39"/>
-      <c r="F8" s="39"/>
-      <c r="G8" s="39"/>
-      <c r="H8" s="39"/>
-      <c r="I8" s="39"/>
+      <c r="E8" s="27"/>
+      <c r="F8" s="27"/>
+      <c r="G8" s="27"/>
+      <c r="H8" s="27"/>
+      <c r="I8" s="27"/>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B9" s="4">
@@ -997,14 +1000,14 @@
       <c r="C9" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D9" s="39" t="s">
+      <c r="D9" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="E9" s="39"/>
-      <c r="F9" s="39"/>
-      <c r="G9" s="39"/>
-      <c r="H9" s="39"/>
-      <c r="I9" s="39"/>
+      <c r="E9" s="27"/>
+      <c r="F9" s="27"/>
+      <c r="G9" s="27"/>
+      <c r="H9" s="27"/>
+      <c r="I9" s="27"/>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B10" s="4">
@@ -1013,14 +1016,14 @@
       <c r="C10" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D10" s="39" t="s">
+      <c r="D10" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="E10" s="39"/>
-      <c r="F10" s="39"/>
-      <c r="G10" s="39"/>
-      <c r="H10" s="39"/>
-      <c r="I10" s="39"/>
+      <c r="E10" s="27"/>
+      <c r="F10" s="27"/>
+      <c r="G10" s="27"/>
+      <c r="H10" s="27"/>
+      <c r="I10" s="27"/>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B11" s="4">
@@ -1029,14 +1032,14 @@
       <c r="C11" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D11" s="39" t="s">
+      <c r="D11" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="E11" s="39"/>
-      <c r="F11" s="39"/>
-      <c r="G11" s="39"/>
-      <c r="H11" s="39"/>
-      <c r="I11" s="39"/>
+      <c r="E11" s="27"/>
+      <c r="F11" s="27"/>
+      <c r="G11" s="27"/>
+      <c r="H11" s="27"/>
+      <c r="I11" s="27"/>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B12" s="4">
@@ -1080,10 +1083,10 @@
       <c r="F13" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="G13" s="39" t="s">
+      <c r="G13" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="H13" s="39"/>
+      <c r="H13" s="27"/>
       <c r="I13" s="1" t="s">
         <v>14</v>
       </c>
@@ -1095,14 +1098,14 @@
       <c r="C14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D14" s="39" t="s">
+      <c r="D14" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="E14" s="39"/>
-      <c r="F14" s="39"/>
-      <c r="G14" s="39"/>
-      <c r="H14" s="39"/>
-      <c r="I14" s="39"/>
+      <c r="E14" s="27"/>
+      <c r="F14" s="27"/>
+      <c r="G14" s="27"/>
+      <c r="H14" s="27"/>
+      <c r="I14" s="27"/>
     </row>
     <row r="15" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B15" s="4">
@@ -1189,14 +1192,14 @@
       <c r="C18" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D18" s="39" t="s">
+      <c r="D18" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="E18" s="39"/>
-      <c r="F18" s="39"/>
-      <c r="G18" s="39"/>
-      <c r="H18" s="39"/>
-      <c r="I18" s="39"/>
+      <c r="E18" s="27"/>
+      <c r="F18" s="27"/>
+      <c r="G18" s="27"/>
+      <c r="H18" s="27"/>
+      <c r="I18" s="27"/>
     </row>
     <row r="19" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B19" s="4">
@@ -1205,14 +1208,14 @@
       <c r="C19" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D19" s="39" t="s">
+      <c r="D19" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="E19" s="39"/>
-      <c r="F19" s="39"/>
-      <c r="G19" s="39"/>
-      <c r="H19" s="39"/>
-      <c r="I19" s="39"/>
+      <c r="E19" s="27"/>
+      <c r="F19" s="27"/>
+      <c r="G19" s="27"/>
+      <c r="H19" s="27"/>
+      <c r="I19" s="27"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B20" s="4">
@@ -1230,10 +1233,10 @@
       <c r="F20" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G20" s="39" t="s">
+      <c r="G20" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="H20" s="39"/>
+      <c r="H20" s="27"/>
       <c r="I20" s="1" t="s">
         <v>14</v>
       </c>
@@ -1349,14 +1352,14 @@
       <c r="C25" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D25" s="39" t="s">
+      <c r="D25" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="E25" s="39"/>
-      <c r="F25" s="39"/>
-      <c r="G25" s="39"/>
-      <c r="H25" s="39"/>
-      <c r="I25" s="39"/>
+      <c r="E25" s="27"/>
+      <c r="F25" s="27"/>
+      <c r="G25" s="27"/>
+      <c r="H25" s="27"/>
+      <c r="I25" s="27"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B26" s="4">
@@ -1400,10 +1403,10 @@
       <c r="F27" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G27" s="39" t="s">
+      <c r="G27" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="H27" s="39"/>
+      <c r="H27" s="27"/>
       <c r="I27" s="1" t="s">
         <v>14</v>
       </c>
@@ -1467,14 +1470,14 @@
       <c r="C30" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D30" s="38" t="s">
+      <c r="D30" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="E30" s="38"/>
-      <c r="F30" s="38"/>
-      <c r="G30" s="38"/>
-      <c r="H30" s="38"/>
-      <c r="I30" s="38"/>
+      <c r="E30" s="26"/>
+      <c r="F30" s="26"/>
+      <c r="G30" s="26"/>
+      <c r="H30" s="26"/>
+      <c r="I30" s="26"/>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B31" s="4">
@@ -1483,14 +1486,14 @@
       <c r="C31" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D31" s="38" t="s">
+      <c r="D31" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="E31" s="38"/>
-      <c r="F31" s="38"/>
-      <c r="G31" s="38"/>
-      <c r="H31" s="38"/>
-      <c r="I31" s="38"/>
+      <c r="E31" s="26"/>
+      <c r="F31" s="26"/>
+      <c r="G31" s="26"/>
+      <c r="H31" s="26"/>
+      <c r="I31" s="26"/>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B32" s="4">
@@ -1525,14 +1528,14 @@
       <c r="C33" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D33" s="38" t="s">
+      <c r="D33" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="E33" s="38"/>
-      <c r="F33" s="38"/>
-      <c r="G33" s="38"/>
-      <c r="H33" s="38"/>
-      <c r="I33" s="38"/>
+      <c r="E33" s="26"/>
+      <c r="F33" s="26"/>
+      <c r="G33" s="26"/>
+      <c r="H33" s="26"/>
+      <c r="I33" s="26"/>
     </row>
     <row r="34" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B34" s="4">
@@ -1576,10 +1579,10 @@
       <c r="F35" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G35" s="38" t="s">
+      <c r="G35" s="26" t="s">
         <v>18</v>
       </c>
-      <c r="H35" s="38"/>
+      <c r="H35" s="26"/>
       <c r="I35" s="1" t="s">
         <v>14</v>
       </c>
@@ -1695,14 +1698,14 @@
       <c r="C40" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D40" s="38" t="s">
+      <c r="D40" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="E40" s="38"/>
-      <c r="F40" s="38"/>
-      <c r="G40" s="38"/>
-      <c r="H40" s="38"/>
-      <c r="I40" s="38"/>
+      <c r="E40" s="26"/>
+      <c r="F40" s="26"/>
+      <c r="G40" s="26"/>
+      <c r="H40" s="26"/>
+      <c r="I40" s="26"/>
     </row>
     <row r="41" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B41" s="4">
@@ -1746,10 +1749,10 @@
       <c r="F42" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G42" s="38" t="s">
+      <c r="G42" s="26" t="s">
         <v>28</v>
       </c>
-      <c r="H42" s="38"/>
+      <c r="H42" s="26"/>
       <c r="I42" s="1" t="s">
         <v>15</v>
       </c>
@@ -1761,14 +1764,14 @@
       <c r="C43" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D43" s="38" t="s">
+      <c r="D43" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="E43" s="38"/>
-      <c r="F43" s="38"/>
-      <c r="G43" s="38"/>
-      <c r="H43" s="38"/>
-      <c r="I43" s="38"/>
+      <c r="E43" s="26"/>
+      <c r="F43" s="26"/>
+      <c r="G43" s="26"/>
+      <c r="H43" s="26"/>
+      <c r="I43" s="26"/>
     </row>
     <row r="44" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B44" s="4">
@@ -1832,14 +1835,14 @@
       <c r="C46" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D46" s="38" t="s">
+      <c r="D46" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="E46" s="38"/>
-      <c r="F46" s="38"/>
-      <c r="G46" s="38"/>
-      <c r="H46" s="38"/>
-      <c r="I46" s="38"/>
+      <c r="E46" s="26"/>
+      <c r="F46" s="26"/>
+      <c r="G46" s="26"/>
+      <c r="H46" s="26"/>
+      <c r="I46" s="26"/>
     </row>
     <row r="47" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B47" s="4">
@@ -3125,28 +3128,28 @@
       <c r="I111" s="20"/>
     </row>
     <row r="112" spans="2:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B112" s="32" t="s">
+      <c r="B112" s="28" t="s">
         <v>57</v>
       </c>
-      <c r="C112" s="33"/>
-      <c r="D112" s="33"/>
-      <c r="E112" s="33"/>
-      <c r="F112" s="33"/>
-      <c r="G112" s="33"/>
-      <c r="H112" s="33"/>
-      <c r="I112" s="33"/>
-      <c r="J112" s="34"/>
+      <c r="C112" s="29"/>
+      <c r="D112" s="29"/>
+      <c r="E112" s="29"/>
+      <c r="F112" s="29"/>
+      <c r="G112" s="29"/>
+      <c r="H112" s="29"/>
+      <c r="I112" s="29"/>
+      <c r="J112" s="30"/>
     </row>
     <row r="113" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B113" s="35"/>
-      <c r="C113" s="36"/>
-      <c r="D113" s="36"/>
-      <c r="E113" s="36"/>
-      <c r="F113" s="36"/>
-      <c r="G113" s="36"/>
-      <c r="H113" s="36"/>
-      <c r="I113" s="36"/>
-      <c r="J113" s="37"/>
+      <c r="B113" s="31"/>
+      <c r="C113" s="32"/>
+      <c r="D113" s="32"/>
+      <c r="E113" s="32"/>
+      <c r="F113" s="32"/>
+      <c r="G113" s="32"/>
+      <c r="H113" s="32"/>
+      <c r="I113" s="32"/>
+      <c r="J113" s="33"/>
     </row>
     <row r="114" spans="2:10" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B114" s="8" t="s">
@@ -4068,15 +4071,15 @@
       <c r="C149" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D149" s="26" t="s">
+      <c r="D149" s="34" t="s">
         <v>20</v>
       </c>
-      <c r="E149" s="27"/>
-      <c r="F149" s="27"/>
-      <c r="G149" s="27"/>
-      <c r="H149" s="27"/>
-      <c r="I149" s="27"/>
-      <c r="J149" s="28"/>
+      <c r="E149" s="35"/>
+      <c r="F149" s="35"/>
+      <c r="G149" s="35"/>
+      <c r="H149" s="35"/>
+      <c r="I149" s="35"/>
+      <c r="J149" s="36"/>
     </row>
     <row r="150" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B150" s="4">
@@ -4085,13 +4088,13 @@
       <c r="C150" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D150" s="29"/>
-      <c r="E150" s="30"/>
-      <c r="F150" s="30"/>
-      <c r="G150" s="30"/>
-      <c r="H150" s="30"/>
-      <c r="I150" s="30"/>
-      <c r="J150" s="31"/>
+      <c r="D150" s="37"/>
+      <c r="E150" s="38"/>
+      <c r="F150" s="38"/>
+      <c r="G150" s="38"/>
+      <c r="H150" s="38"/>
+      <c r="I150" s="38"/>
+      <c r="J150" s="39"/>
     </row>
     <row r="151" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B151" s="4">
@@ -4676,15 +4679,33 @@
       <c r="J172" s="25"/>
     </row>
     <row r="173" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B173" s="3"/>
-      <c r="C173" s="3"/>
-      <c r="D173" s="3"/>
-      <c r="E173" s="3"/>
-      <c r="F173" s="3"/>
-      <c r="G173" s="3"/>
-      <c r="H173" s="3"/>
-      <c r="I173" s="1"/>
-      <c r="J173" s="1"/>
+      <c r="B173" s="4">
+        <v>45901</v>
+      </c>
+      <c r="C173" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D173" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E173" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F173" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G173" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H173" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="I173" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J173" s="1" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="174" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B174" s="3"/>
@@ -7361,35 +7382,35 @@
     </row>
   </sheetData>
   <mergeCells count="85">
-    <mergeCell ref="D172:J172"/>
-    <mergeCell ref="D98:I98"/>
-    <mergeCell ref="D94:I94"/>
-    <mergeCell ref="H89:I89"/>
-    <mergeCell ref="D89:F89"/>
-    <mergeCell ref="G64:H64"/>
-    <mergeCell ref="D96:I96"/>
-    <mergeCell ref="D95:F95"/>
-    <mergeCell ref="G95:H95"/>
-    <mergeCell ref="D92:I92"/>
-    <mergeCell ref="D97:I97"/>
-    <mergeCell ref="D93:I93"/>
-    <mergeCell ref="D90:E90"/>
-    <mergeCell ref="D91:H91"/>
-    <mergeCell ref="E86:G86"/>
-    <mergeCell ref="D88:I88"/>
-    <mergeCell ref="H67:I67"/>
-    <mergeCell ref="G42:H42"/>
-    <mergeCell ref="D60:I60"/>
-    <mergeCell ref="D62:I62"/>
-    <mergeCell ref="D61:I61"/>
-    <mergeCell ref="G49:H49"/>
-    <mergeCell ref="D47:I47"/>
-    <mergeCell ref="D55:I55"/>
-    <mergeCell ref="G81:H81"/>
-    <mergeCell ref="D67:F67"/>
-    <mergeCell ref="F68:I68"/>
-    <mergeCell ref="D87:E87"/>
-    <mergeCell ref="G87:I87"/>
+    <mergeCell ref="D164:J164"/>
+    <mergeCell ref="D157:J157"/>
+    <mergeCell ref="D143:J143"/>
+    <mergeCell ref="D135:J135"/>
+    <mergeCell ref="F127:J127"/>
+    <mergeCell ref="D107:E107"/>
+    <mergeCell ref="F118:J118"/>
+    <mergeCell ref="G152:I152"/>
+    <mergeCell ref="D149:J150"/>
+    <mergeCell ref="G146:J146"/>
+    <mergeCell ref="D108:E108"/>
+    <mergeCell ref="B112:J113"/>
+    <mergeCell ref="G124:J124"/>
+    <mergeCell ref="D120:H120"/>
+    <mergeCell ref="G123:J123"/>
+    <mergeCell ref="D121:J121"/>
+    <mergeCell ref="D31:I31"/>
+    <mergeCell ref="G35:H35"/>
+    <mergeCell ref="D40:I40"/>
+    <mergeCell ref="D33:I33"/>
+    <mergeCell ref="D46:I46"/>
+    <mergeCell ref="D43:I43"/>
+    <mergeCell ref="D78:I78"/>
+    <mergeCell ref="G71:H71"/>
+    <mergeCell ref="D76:I76"/>
+    <mergeCell ref="D66:H66"/>
+    <mergeCell ref="D77:I77"/>
+    <mergeCell ref="D73:I73"/>
+    <mergeCell ref="D70:E70"/>
     <mergeCell ref="D74:F74"/>
     <mergeCell ref="D84:I84"/>
     <mergeCell ref="D69:I69"/>
@@ -7406,20 +7427,36 @@
     <mergeCell ref="D18:I18"/>
     <mergeCell ref="D30:I30"/>
     <mergeCell ref="G80:H80"/>
-    <mergeCell ref="D78:I78"/>
-    <mergeCell ref="G71:H71"/>
-    <mergeCell ref="D76:I76"/>
-    <mergeCell ref="D66:H66"/>
-    <mergeCell ref="D77:I77"/>
-    <mergeCell ref="D73:I73"/>
-    <mergeCell ref="D70:E70"/>
-    <mergeCell ref="D31:I31"/>
-    <mergeCell ref="G35:H35"/>
-    <mergeCell ref="D40:I40"/>
-    <mergeCell ref="D33:I33"/>
-    <mergeCell ref="D46:I46"/>
-    <mergeCell ref="D43:I43"/>
+    <mergeCell ref="G42:H42"/>
+    <mergeCell ref="D60:I60"/>
+    <mergeCell ref="D62:I62"/>
+    <mergeCell ref="D61:I61"/>
+    <mergeCell ref="G49:H49"/>
+    <mergeCell ref="D47:I47"/>
+    <mergeCell ref="D55:I55"/>
     <mergeCell ref="G57:H57"/>
+    <mergeCell ref="G64:H64"/>
+    <mergeCell ref="D96:I96"/>
+    <mergeCell ref="D95:F95"/>
+    <mergeCell ref="G95:H95"/>
+    <mergeCell ref="D92:I92"/>
+    <mergeCell ref="D93:I93"/>
+    <mergeCell ref="D90:E90"/>
+    <mergeCell ref="D91:H91"/>
+    <mergeCell ref="E86:G86"/>
+    <mergeCell ref="D88:I88"/>
+    <mergeCell ref="H67:I67"/>
+    <mergeCell ref="G81:H81"/>
+    <mergeCell ref="D67:F67"/>
+    <mergeCell ref="F68:I68"/>
+    <mergeCell ref="D87:E87"/>
+    <mergeCell ref="G87:I87"/>
+    <mergeCell ref="D172:J172"/>
+    <mergeCell ref="D98:I98"/>
+    <mergeCell ref="D94:I94"/>
+    <mergeCell ref="H89:I89"/>
+    <mergeCell ref="D89:F89"/>
+    <mergeCell ref="D97:I97"/>
     <mergeCell ref="D106:E106"/>
     <mergeCell ref="D99:G99"/>
     <mergeCell ref="G126:I126"/>
@@ -7430,22 +7467,6 @@
     <mergeCell ref="D105:E105"/>
     <mergeCell ref="G100:I100"/>
     <mergeCell ref="B101:I101"/>
-    <mergeCell ref="D108:E108"/>
-    <mergeCell ref="B112:J113"/>
-    <mergeCell ref="G124:J124"/>
-    <mergeCell ref="D120:H120"/>
-    <mergeCell ref="G123:J123"/>
-    <mergeCell ref="D121:J121"/>
-    <mergeCell ref="D107:E107"/>
-    <mergeCell ref="F118:J118"/>
-    <mergeCell ref="G152:I152"/>
-    <mergeCell ref="D149:J150"/>
-    <mergeCell ref="G146:J146"/>
-    <mergeCell ref="D164:J164"/>
-    <mergeCell ref="D157:J157"/>
-    <mergeCell ref="D143:J143"/>
-    <mergeCell ref="D135:J135"/>
-    <mergeCell ref="F127:J127"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/attendance_sheet.xlsx
+++ b/attendance_sheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\repositary\3rd_Year_5th_Semester\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{527D696E-48B2-4BAA-9B82-BABA1B4B78F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{815382CC-BE07-40F6-8C81-408924969829}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{EB654061-A886-47D1-BF86-9B1A84FCE7FB}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="862" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="870" uniqueCount="73">
   <si>
     <t>Date</t>
   </si>
@@ -253,6 +253,9 @@
   </si>
   <si>
     <t>1 classp</t>
+  </si>
+  <si>
+    <t>2 class</t>
   </si>
 </sst>
 </file>
@@ -541,11 +544,23 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -565,23 +580,11 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -984,14 +987,14 @@
       <c r="C8" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D8" s="27" t="s">
+      <c r="D8" s="39" t="s">
         <v>20</v>
       </c>
-      <c r="E8" s="27"/>
-      <c r="F8" s="27"/>
-      <c r="G8" s="27"/>
-      <c r="H8" s="27"/>
-      <c r="I8" s="27"/>
+      <c r="E8" s="39"/>
+      <c r="F8" s="39"/>
+      <c r="G8" s="39"/>
+      <c r="H8" s="39"/>
+      <c r="I8" s="39"/>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B9" s="4">
@@ -1000,14 +1003,14 @@
       <c r="C9" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D9" s="27" t="s">
+      <c r="D9" s="39" t="s">
         <v>20</v>
       </c>
-      <c r="E9" s="27"/>
-      <c r="F9" s="27"/>
-      <c r="G9" s="27"/>
-      <c r="H9" s="27"/>
-      <c r="I9" s="27"/>
+      <c r="E9" s="39"/>
+      <c r="F9" s="39"/>
+      <c r="G9" s="39"/>
+      <c r="H9" s="39"/>
+      <c r="I9" s="39"/>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B10" s="4">
@@ -1016,14 +1019,14 @@
       <c r="C10" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D10" s="27" t="s">
+      <c r="D10" s="39" t="s">
         <v>20</v>
       </c>
-      <c r="E10" s="27"/>
-      <c r="F10" s="27"/>
-      <c r="G10" s="27"/>
-      <c r="H10" s="27"/>
-      <c r="I10" s="27"/>
+      <c r="E10" s="39"/>
+      <c r="F10" s="39"/>
+      <c r="G10" s="39"/>
+      <c r="H10" s="39"/>
+      <c r="I10" s="39"/>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B11" s="4">
@@ -1032,14 +1035,14 @@
       <c r="C11" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D11" s="27" t="s">
+      <c r="D11" s="39" t="s">
         <v>20</v>
       </c>
-      <c r="E11" s="27"/>
-      <c r="F11" s="27"/>
-      <c r="G11" s="27"/>
-      <c r="H11" s="27"/>
-      <c r="I11" s="27"/>
+      <c r="E11" s="39"/>
+      <c r="F11" s="39"/>
+      <c r="G11" s="39"/>
+      <c r="H11" s="39"/>
+      <c r="I11" s="39"/>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B12" s="4">
@@ -1083,10 +1086,10 @@
       <c r="F13" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="G13" s="27" t="s">
+      <c r="G13" s="39" t="s">
         <v>18</v>
       </c>
-      <c r="H13" s="27"/>
+      <c r="H13" s="39"/>
       <c r="I13" s="1" t="s">
         <v>14</v>
       </c>
@@ -1098,14 +1101,14 @@
       <c r="C14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D14" s="27" t="s">
+      <c r="D14" s="39" t="s">
         <v>19</v>
       </c>
-      <c r="E14" s="27"/>
-      <c r="F14" s="27"/>
-      <c r="G14" s="27"/>
-      <c r="H14" s="27"/>
-      <c r="I14" s="27"/>
+      <c r="E14" s="39"/>
+      <c r="F14" s="39"/>
+      <c r="G14" s="39"/>
+      <c r="H14" s="39"/>
+      <c r="I14" s="39"/>
     </row>
     <row r="15" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B15" s="4">
@@ -1192,14 +1195,14 @@
       <c r="C18" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D18" s="27" t="s">
+      <c r="D18" s="39" t="s">
         <v>23</v>
       </c>
-      <c r="E18" s="27"/>
-      <c r="F18" s="27"/>
-      <c r="G18" s="27"/>
-      <c r="H18" s="27"/>
-      <c r="I18" s="27"/>
+      <c r="E18" s="39"/>
+      <c r="F18" s="39"/>
+      <c r="G18" s="39"/>
+      <c r="H18" s="39"/>
+      <c r="I18" s="39"/>
     </row>
     <row r="19" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B19" s="4">
@@ -1208,14 +1211,14 @@
       <c r="C19" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D19" s="27" t="s">
+      <c r="D19" s="39" t="s">
         <v>23</v>
       </c>
-      <c r="E19" s="27"/>
-      <c r="F19" s="27"/>
-      <c r="G19" s="27"/>
-      <c r="H19" s="27"/>
-      <c r="I19" s="27"/>
+      <c r="E19" s="39"/>
+      <c r="F19" s="39"/>
+      <c r="G19" s="39"/>
+      <c r="H19" s="39"/>
+      <c r="I19" s="39"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B20" s="4">
@@ -1233,10 +1236,10 @@
       <c r="F20" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G20" s="27" t="s">
+      <c r="G20" s="39" t="s">
         <v>15</v>
       </c>
-      <c r="H20" s="27"/>
+      <c r="H20" s="39"/>
       <c r="I20" s="1" t="s">
         <v>14</v>
       </c>
@@ -1352,14 +1355,14 @@
       <c r="C25" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D25" s="27" t="s">
+      <c r="D25" s="39" t="s">
         <v>26</v>
       </c>
-      <c r="E25" s="27"/>
-      <c r="F25" s="27"/>
-      <c r="G25" s="27"/>
-      <c r="H25" s="27"/>
-      <c r="I25" s="27"/>
+      <c r="E25" s="39"/>
+      <c r="F25" s="39"/>
+      <c r="G25" s="39"/>
+      <c r="H25" s="39"/>
+      <c r="I25" s="39"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B26" s="4">
@@ -1403,10 +1406,10 @@
       <c r="F27" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G27" s="27" t="s">
+      <c r="G27" s="39" t="s">
         <v>18</v>
       </c>
-      <c r="H27" s="27"/>
+      <c r="H27" s="39"/>
       <c r="I27" s="1" t="s">
         <v>14</v>
       </c>
@@ -1470,14 +1473,14 @@
       <c r="C30" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D30" s="26" t="s">
+      <c r="D30" s="38" t="s">
         <v>20</v>
       </c>
-      <c r="E30" s="26"/>
-      <c r="F30" s="26"/>
-      <c r="G30" s="26"/>
-      <c r="H30" s="26"/>
-      <c r="I30" s="26"/>
+      <c r="E30" s="38"/>
+      <c r="F30" s="38"/>
+      <c r="G30" s="38"/>
+      <c r="H30" s="38"/>
+      <c r="I30" s="38"/>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B31" s="4">
@@ -1486,14 +1489,14 @@
       <c r="C31" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D31" s="26" t="s">
+      <c r="D31" s="38" t="s">
         <v>20</v>
       </c>
-      <c r="E31" s="26"/>
-      <c r="F31" s="26"/>
-      <c r="G31" s="26"/>
-      <c r="H31" s="26"/>
-      <c r="I31" s="26"/>
+      <c r="E31" s="38"/>
+      <c r="F31" s="38"/>
+      <c r="G31" s="38"/>
+      <c r="H31" s="38"/>
+      <c r="I31" s="38"/>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B32" s="4">
@@ -1528,14 +1531,14 @@
       <c r="C33" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D33" s="26" t="s">
+      <c r="D33" s="38" t="s">
         <v>20</v>
       </c>
-      <c r="E33" s="26"/>
-      <c r="F33" s="26"/>
-      <c r="G33" s="26"/>
-      <c r="H33" s="26"/>
-      <c r="I33" s="26"/>
+      <c r="E33" s="38"/>
+      <c r="F33" s="38"/>
+      <c r="G33" s="38"/>
+      <c r="H33" s="38"/>
+      <c r="I33" s="38"/>
     </row>
     <row r="34" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B34" s="4">
@@ -1579,10 +1582,10 @@
       <c r="F35" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G35" s="26" t="s">
+      <c r="G35" s="38" t="s">
         <v>18</v>
       </c>
-      <c r="H35" s="26"/>
+      <c r="H35" s="38"/>
       <c r="I35" s="1" t="s">
         <v>14</v>
       </c>
@@ -1698,14 +1701,14 @@
       <c r="C40" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D40" s="26" t="s">
+      <c r="D40" s="38" t="s">
         <v>20</v>
       </c>
-      <c r="E40" s="26"/>
-      <c r="F40" s="26"/>
-      <c r="G40" s="26"/>
-      <c r="H40" s="26"/>
-      <c r="I40" s="26"/>
+      <c r="E40" s="38"/>
+      <c r="F40" s="38"/>
+      <c r="G40" s="38"/>
+      <c r="H40" s="38"/>
+      <c r="I40" s="38"/>
     </row>
     <row r="41" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B41" s="4">
@@ -1749,10 +1752,10 @@
       <c r="F42" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G42" s="26" t="s">
+      <c r="G42" s="38" t="s">
         <v>28</v>
       </c>
-      <c r="H42" s="26"/>
+      <c r="H42" s="38"/>
       <c r="I42" s="1" t="s">
         <v>15</v>
       </c>
@@ -1764,14 +1767,14 @@
       <c r="C43" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D43" s="26" t="s">
+      <c r="D43" s="38" t="s">
         <v>20</v>
       </c>
-      <c r="E43" s="26"/>
-      <c r="F43" s="26"/>
-      <c r="G43" s="26"/>
-      <c r="H43" s="26"/>
-      <c r="I43" s="26"/>
+      <c r="E43" s="38"/>
+      <c r="F43" s="38"/>
+      <c r="G43" s="38"/>
+      <c r="H43" s="38"/>
+      <c r="I43" s="38"/>
     </row>
     <row r="44" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B44" s="4">
@@ -1835,14 +1838,14 @@
       <c r="C46" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D46" s="26" t="s">
+      <c r="D46" s="38" t="s">
         <v>20</v>
       </c>
-      <c r="E46" s="26"/>
-      <c r="F46" s="26"/>
-      <c r="G46" s="26"/>
-      <c r="H46" s="26"/>
-      <c r="I46" s="26"/>
+      <c r="E46" s="38"/>
+      <c r="F46" s="38"/>
+      <c r="G46" s="38"/>
+      <c r="H46" s="38"/>
+      <c r="I46" s="38"/>
     </row>
     <row r="47" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B47" s="4">
@@ -3128,28 +3131,28 @@
       <c r="I111" s="20"/>
     </row>
     <row r="112" spans="2:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B112" s="28" t="s">
+      <c r="B112" s="32" t="s">
         <v>57</v>
       </c>
-      <c r="C112" s="29"/>
-      <c r="D112" s="29"/>
-      <c r="E112" s="29"/>
-      <c r="F112" s="29"/>
-      <c r="G112" s="29"/>
-      <c r="H112" s="29"/>
-      <c r="I112" s="29"/>
-      <c r="J112" s="30"/>
+      <c r="C112" s="33"/>
+      <c r="D112" s="33"/>
+      <c r="E112" s="33"/>
+      <c r="F112" s="33"/>
+      <c r="G112" s="33"/>
+      <c r="H112" s="33"/>
+      <c r="I112" s="33"/>
+      <c r="J112" s="34"/>
     </row>
     <row r="113" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B113" s="31"/>
-      <c r="C113" s="32"/>
-      <c r="D113" s="32"/>
-      <c r="E113" s="32"/>
-      <c r="F113" s="32"/>
-      <c r="G113" s="32"/>
-      <c r="H113" s="32"/>
-      <c r="I113" s="32"/>
-      <c r="J113" s="33"/>
+      <c r="B113" s="35"/>
+      <c r="C113" s="36"/>
+      <c r="D113" s="36"/>
+      <c r="E113" s="36"/>
+      <c r="F113" s="36"/>
+      <c r="G113" s="36"/>
+      <c r="H113" s="36"/>
+      <c r="I113" s="36"/>
+      <c r="J113" s="37"/>
     </row>
     <row r="114" spans="2:10" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B114" s="8" t="s">
@@ -4071,15 +4074,15 @@
       <c r="C149" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D149" s="34" t="s">
+      <c r="D149" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="E149" s="35"/>
-      <c r="F149" s="35"/>
-      <c r="G149" s="35"/>
-      <c r="H149" s="35"/>
-      <c r="I149" s="35"/>
-      <c r="J149" s="36"/>
+      <c r="E149" s="27"/>
+      <c r="F149" s="27"/>
+      <c r="G149" s="27"/>
+      <c r="H149" s="27"/>
+      <c r="I149" s="27"/>
+      <c r="J149" s="28"/>
     </row>
     <row r="150" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B150" s="4">
@@ -4088,13 +4091,13 @@
       <c r="C150" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D150" s="37"/>
-      <c r="E150" s="38"/>
-      <c r="F150" s="38"/>
-      <c r="G150" s="38"/>
-      <c r="H150" s="38"/>
-      <c r="I150" s="38"/>
-      <c r="J150" s="39"/>
+      <c r="D150" s="29"/>
+      <c r="E150" s="30"/>
+      <c r="F150" s="30"/>
+      <c r="G150" s="30"/>
+      <c r="H150" s="30"/>
+      <c r="I150" s="30"/>
+      <c r="J150" s="31"/>
     </row>
     <row r="151" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B151" s="4">
@@ -4708,15 +4711,33 @@
       </c>
     </row>
     <row r="174" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B174" s="3"/>
-      <c r="C174" s="3"/>
-      <c r="D174" s="3"/>
-      <c r="E174" s="3"/>
-      <c r="F174" s="3"/>
-      <c r="G174" s="3"/>
-      <c r="H174" s="3"/>
-      <c r="I174" s="1"/>
-      <c r="J174" s="1"/>
+      <c r="B174" s="4">
+        <v>45902</v>
+      </c>
+      <c r="C174" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D174" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="E174" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F174" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G174" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H174" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I174" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J174" s="1" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="175" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B175" s="3"/>
@@ -7382,36 +7403,45 @@
     </row>
   </sheetData>
   <mergeCells count="85">
-    <mergeCell ref="D164:J164"/>
-    <mergeCell ref="D157:J157"/>
-    <mergeCell ref="D143:J143"/>
-    <mergeCell ref="D135:J135"/>
-    <mergeCell ref="F127:J127"/>
-    <mergeCell ref="D107:E107"/>
-    <mergeCell ref="F118:J118"/>
-    <mergeCell ref="G152:I152"/>
-    <mergeCell ref="D149:J150"/>
-    <mergeCell ref="G146:J146"/>
-    <mergeCell ref="D108:E108"/>
-    <mergeCell ref="B112:J113"/>
-    <mergeCell ref="G124:J124"/>
-    <mergeCell ref="D120:H120"/>
-    <mergeCell ref="G123:J123"/>
-    <mergeCell ref="D121:J121"/>
-    <mergeCell ref="D31:I31"/>
-    <mergeCell ref="G35:H35"/>
-    <mergeCell ref="D40:I40"/>
-    <mergeCell ref="D33:I33"/>
-    <mergeCell ref="D46:I46"/>
-    <mergeCell ref="D43:I43"/>
-    <mergeCell ref="D78:I78"/>
-    <mergeCell ref="G71:H71"/>
-    <mergeCell ref="D76:I76"/>
-    <mergeCell ref="D66:H66"/>
-    <mergeCell ref="D77:I77"/>
-    <mergeCell ref="D73:I73"/>
-    <mergeCell ref="D70:E70"/>
-    <mergeCell ref="D74:F74"/>
+    <mergeCell ref="D172:J172"/>
+    <mergeCell ref="D98:I98"/>
+    <mergeCell ref="D94:I94"/>
+    <mergeCell ref="H89:I89"/>
+    <mergeCell ref="D89:F89"/>
+    <mergeCell ref="D97:I97"/>
+    <mergeCell ref="D106:E106"/>
+    <mergeCell ref="D99:G99"/>
+    <mergeCell ref="G126:I126"/>
+    <mergeCell ref="F125:J125"/>
+    <mergeCell ref="D128:J128"/>
+    <mergeCell ref="D103:E103"/>
+    <mergeCell ref="D104:E104"/>
+    <mergeCell ref="D105:E105"/>
+    <mergeCell ref="G100:I100"/>
+    <mergeCell ref="B101:I101"/>
+    <mergeCell ref="G64:H64"/>
+    <mergeCell ref="D96:I96"/>
+    <mergeCell ref="D95:F95"/>
+    <mergeCell ref="G95:H95"/>
+    <mergeCell ref="D92:I92"/>
+    <mergeCell ref="D93:I93"/>
+    <mergeCell ref="D90:E90"/>
+    <mergeCell ref="D91:H91"/>
+    <mergeCell ref="E86:G86"/>
+    <mergeCell ref="D88:I88"/>
+    <mergeCell ref="H67:I67"/>
+    <mergeCell ref="G81:H81"/>
+    <mergeCell ref="D67:F67"/>
+    <mergeCell ref="F68:I68"/>
+    <mergeCell ref="D87:E87"/>
+    <mergeCell ref="G87:I87"/>
+    <mergeCell ref="D60:I60"/>
+    <mergeCell ref="D62:I62"/>
+    <mergeCell ref="D61:I61"/>
+    <mergeCell ref="G49:H49"/>
+    <mergeCell ref="D47:I47"/>
+    <mergeCell ref="D55:I55"/>
+    <mergeCell ref="G57:H57"/>
     <mergeCell ref="D84:I84"/>
     <mergeCell ref="D69:I69"/>
     <mergeCell ref="D8:I8"/>
@@ -7428,45 +7458,36 @@
     <mergeCell ref="D30:I30"/>
     <mergeCell ref="G80:H80"/>
     <mergeCell ref="G42:H42"/>
-    <mergeCell ref="D60:I60"/>
-    <mergeCell ref="D62:I62"/>
-    <mergeCell ref="D61:I61"/>
-    <mergeCell ref="G49:H49"/>
-    <mergeCell ref="D47:I47"/>
-    <mergeCell ref="D55:I55"/>
-    <mergeCell ref="G57:H57"/>
-    <mergeCell ref="G64:H64"/>
-    <mergeCell ref="D96:I96"/>
-    <mergeCell ref="D95:F95"/>
-    <mergeCell ref="G95:H95"/>
-    <mergeCell ref="D92:I92"/>
-    <mergeCell ref="D93:I93"/>
-    <mergeCell ref="D90:E90"/>
-    <mergeCell ref="D91:H91"/>
-    <mergeCell ref="E86:G86"/>
-    <mergeCell ref="D88:I88"/>
-    <mergeCell ref="H67:I67"/>
-    <mergeCell ref="G81:H81"/>
-    <mergeCell ref="D67:F67"/>
-    <mergeCell ref="F68:I68"/>
-    <mergeCell ref="D87:E87"/>
-    <mergeCell ref="G87:I87"/>
-    <mergeCell ref="D172:J172"/>
-    <mergeCell ref="D98:I98"/>
-    <mergeCell ref="D94:I94"/>
-    <mergeCell ref="H89:I89"/>
-    <mergeCell ref="D89:F89"/>
-    <mergeCell ref="D97:I97"/>
-    <mergeCell ref="D106:E106"/>
-    <mergeCell ref="D99:G99"/>
-    <mergeCell ref="G126:I126"/>
-    <mergeCell ref="F125:J125"/>
-    <mergeCell ref="D128:J128"/>
-    <mergeCell ref="D103:E103"/>
-    <mergeCell ref="D104:E104"/>
-    <mergeCell ref="D105:E105"/>
-    <mergeCell ref="G100:I100"/>
-    <mergeCell ref="B101:I101"/>
+    <mergeCell ref="D78:I78"/>
+    <mergeCell ref="G71:H71"/>
+    <mergeCell ref="D76:I76"/>
+    <mergeCell ref="D66:H66"/>
+    <mergeCell ref="D77:I77"/>
+    <mergeCell ref="D73:I73"/>
+    <mergeCell ref="D70:E70"/>
+    <mergeCell ref="D74:F74"/>
+    <mergeCell ref="D31:I31"/>
+    <mergeCell ref="G35:H35"/>
+    <mergeCell ref="D40:I40"/>
+    <mergeCell ref="D33:I33"/>
+    <mergeCell ref="D46:I46"/>
+    <mergeCell ref="D43:I43"/>
+    <mergeCell ref="D107:E107"/>
+    <mergeCell ref="F118:J118"/>
+    <mergeCell ref="G152:I152"/>
+    <mergeCell ref="D149:J150"/>
+    <mergeCell ref="G146:J146"/>
+    <mergeCell ref="D108:E108"/>
+    <mergeCell ref="B112:J113"/>
+    <mergeCell ref="G124:J124"/>
+    <mergeCell ref="D120:H120"/>
+    <mergeCell ref="G123:J123"/>
+    <mergeCell ref="D121:J121"/>
+    <mergeCell ref="D164:J164"/>
+    <mergeCell ref="D157:J157"/>
+    <mergeCell ref="D143:J143"/>
+    <mergeCell ref="D135:J135"/>
+    <mergeCell ref="F127:J127"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/attendance_sheet.xlsx
+++ b/attendance_sheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\repositary\3rd_Year_5th_Semester\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{815382CC-BE07-40F6-8C81-408924969829}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E63D263-202E-42C6-B469-690A2BA7C7B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{EB654061-A886-47D1-BF86-9B1A84FCE7FB}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="870" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="871" uniqueCount="73">
   <si>
     <t>Date</t>
   </si>
@@ -544,6 +544,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -579,12 +585,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -987,14 +987,14 @@
       <c r="C8" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D8" s="39" t="s">
+      <c r="D8" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="E8" s="39"/>
-      <c r="F8" s="39"/>
-      <c r="G8" s="39"/>
-      <c r="H8" s="39"/>
-      <c r="I8" s="39"/>
+      <c r="E8" s="26"/>
+      <c r="F8" s="26"/>
+      <c r="G8" s="26"/>
+      <c r="H8" s="26"/>
+      <c r="I8" s="26"/>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B9" s="4">
@@ -1003,14 +1003,14 @@
       <c r="C9" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D9" s="39" t="s">
+      <c r="D9" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="E9" s="39"/>
-      <c r="F9" s="39"/>
-      <c r="G9" s="39"/>
-      <c r="H9" s="39"/>
-      <c r="I9" s="39"/>
+      <c r="E9" s="26"/>
+      <c r="F9" s="26"/>
+      <c r="G9" s="26"/>
+      <c r="H9" s="26"/>
+      <c r="I9" s="26"/>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B10" s="4">
@@ -1019,14 +1019,14 @@
       <c r="C10" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D10" s="39" t="s">
+      <c r="D10" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="E10" s="39"/>
-      <c r="F10" s="39"/>
-      <c r="G10" s="39"/>
-      <c r="H10" s="39"/>
-      <c r="I10" s="39"/>
+      <c r="E10" s="26"/>
+      <c r="F10" s="26"/>
+      <c r="G10" s="26"/>
+      <c r="H10" s="26"/>
+      <c r="I10" s="26"/>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B11" s="4">
@@ -1035,14 +1035,14 @@
       <c r="C11" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D11" s="39" t="s">
+      <c r="D11" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="E11" s="39"/>
-      <c r="F11" s="39"/>
-      <c r="G11" s="39"/>
-      <c r="H11" s="39"/>
-      <c r="I11" s="39"/>
+      <c r="E11" s="26"/>
+      <c r="F11" s="26"/>
+      <c r="G11" s="26"/>
+      <c r="H11" s="26"/>
+      <c r="I11" s="26"/>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B12" s="4">
@@ -1086,10 +1086,10 @@
       <c r="F13" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="G13" s="39" t="s">
+      <c r="G13" s="26" t="s">
         <v>18</v>
       </c>
-      <c r="H13" s="39"/>
+      <c r="H13" s="26"/>
       <c r="I13" s="1" t="s">
         <v>14</v>
       </c>
@@ -1101,14 +1101,14 @@
       <c r="C14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D14" s="39" t="s">
+      <c r="D14" s="26" t="s">
         <v>19</v>
       </c>
-      <c r="E14" s="39"/>
-      <c r="F14" s="39"/>
-      <c r="G14" s="39"/>
-      <c r="H14" s="39"/>
-      <c r="I14" s="39"/>
+      <c r="E14" s="26"/>
+      <c r="F14" s="26"/>
+      <c r="G14" s="26"/>
+      <c r="H14" s="26"/>
+      <c r="I14" s="26"/>
     </row>
     <row r="15" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B15" s="4">
@@ -1195,14 +1195,14 @@
       <c r="C18" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D18" s="39" t="s">
+      <c r="D18" s="26" t="s">
         <v>23</v>
       </c>
-      <c r="E18" s="39"/>
-      <c r="F18" s="39"/>
-      <c r="G18" s="39"/>
-      <c r="H18" s="39"/>
-      <c r="I18" s="39"/>
+      <c r="E18" s="26"/>
+      <c r="F18" s="26"/>
+      <c r="G18" s="26"/>
+      <c r="H18" s="26"/>
+      <c r="I18" s="26"/>
     </row>
     <row r="19" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B19" s="4">
@@ -1211,14 +1211,14 @@
       <c r="C19" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D19" s="39" t="s">
+      <c r="D19" s="26" t="s">
         <v>23</v>
       </c>
-      <c r="E19" s="39"/>
-      <c r="F19" s="39"/>
-      <c r="G19" s="39"/>
-      <c r="H19" s="39"/>
-      <c r="I19" s="39"/>
+      <c r="E19" s="26"/>
+      <c r="F19" s="26"/>
+      <c r="G19" s="26"/>
+      <c r="H19" s="26"/>
+      <c r="I19" s="26"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B20" s="4">
@@ -1236,10 +1236,10 @@
       <c r="F20" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G20" s="39" t="s">
+      <c r="G20" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="H20" s="39"/>
+      <c r="H20" s="26"/>
       <c r="I20" s="1" t="s">
         <v>14</v>
       </c>
@@ -1355,14 +1355,14 @@
       <c r="C25" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D25" s="39" t="s">
+      <c r="D25" s="26" t="s">
         <v>26</v>
       </c>
-      <c r="E25" s="39"/>
-      <c r="F25" s="39"/>
-      <c r="G25" s="39"/>
-      <c r="H25" s="39"/>
-      <c r="I25" s="39"/>
+      <c r="E25" s="26"/>
+      <c r="F25" s="26"/>
+      <c r="G25" s="26"/>
+      <c r="H25" s="26"/>
+      <c r="I25" s="26"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B26" s="4">
@@ -1406,10 +1406,10 @@
       <c r="F27" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G27" s="39" t="s">
+      <c r="G27" s="26" t="s">
         <v>18</v>
       </c>
-      <c r="H27" s="39"/>
+      <c r="H27" s="26"/>
       <c r="I27" s="1" t="s">
         <v>14</v>
       </c>
@@ -1473,14 +1473,14 @@
       <c r="C30" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D30" s="38" t="s">
+      <c r="D30" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="E30" s="38"/>
-      <c r="F30" s="38"/>
-      <c r="G30" s="38"/>
-      <c r="H30" s="38"/>
-      <c r="I30" s="38"/>
+      <c r="E30" s="27"/>
+      <c r="F30" s="27"/>
+      <c r="G30" s="27"/>
+      <c r="H30" s="27"/>
+      <c r="I30" s="27"/>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B31" s="4">
@@ -1489,14 +1489,14 @@
       <c r="C31" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D31" s="38" t="s">
+      <c r="D31" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="E31" s="38"/>
-      <c r="F31" s="38"/>
-      <c r="G31" s="38"/>
-      <c r="H31" s="38"/>
-      <c r="I31" s="38"/>
+      <c r="E31" s="27"/>
+      <c r="F31" s="27"/>
+      <c r="G31" s="27"/>
+      <c r="H31" s="27"/>
+      <c r="I31" s="27"/>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B32" s="4">
@@ -1531,14 +1531,14 @@
       <c r="C33" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D33" s="38" t="s">
+      <c r="D33" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="E33" s="38"/>
-      <c r="F33" s="38"/>
-      <c r="G33" s="38"/>
-      <c r="H33" s="38"/>
-      <c r="I33" s="38"/>
+      <c r="E33" s="27"/>
+      <c r="F33" s="27"/>
+      <c r="G33" s="27"/>
+      <c r="H33" s="27"/>
+      <c r="I33" s="27"/>
     </row>
     <row r="34" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B34" s="4">
@@ -1582,10 +1582,10 @@
       <c r="F35" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G35" s="38" t="s">
+      <c r="G35" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="H35" s="38"/>
+      <c r="H35" s="27"/>
       <c r="I35" s="1" t="s">
         <v>14</v>
       </c>
@@ -1701,14 +1701,14 @@
       <c r="C40" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D40" s="38" t="s">
+      <c r="D40" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="E40" s="38"/>
-      <c r="F40" s="38"/>
-      <c r="G40" s="38"/>
-      <c r="H40" s="38"/>
-      <c r="I40" s="38"/>
+      <c r="E40" s="27"/>
+      <c r="F40" s="27"/>
+      <c r="G40" s="27"/>
+      <c r="H40" s="27"/>
+      <c r="I40" s="27"/>
     </row>
     <row r="41" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B41" s="4">
@@ -1752,10 +1752,10 @@
       <c r="F42" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G42" s="38" t="s">
+      <c r="G42" s="27" t="s">
         <v>28</v>
       </c>
-      <c r="H42" s="38"/>
+      <c r="H42" s="27"/>
       <c r="I42" s="1" t="s">
         <v>15</v>
       </c>
@@ -1767,14 +1767,14 @@
       <c r="C43" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D43" s="38" t="s">
+      <c r="D43" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="E43" s="38"/>
-      <c r="F43" s="38"/>
-      <c r="G43" s="38"/>
-      <c r="H43" s="38"/>
-      <c r="I43" s="38"/>
+      <c r="E43" s="27"/>
+      <c r="F43" s="27"/>
+      <c r="G43" s="27"/>
+      <c r="H43" s="27"/>
+      <c r="I43" s="27"/>
     </row>
     <row r="44" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B44" s="4">
@@ -1838,14 +1838,14 @@
       <c r="C46" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D46" s="38" t="s">
+      <c r="D46" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="E46" s="38"/>
-      <c r="F46" s="38"/>
-      <c r="G46" s="38"/>
-      <c r="H46" s="38"/>
-      <c r="I46" s="38"/>
+      <c r="E46" s="27"/>
+      <c r="F46" s="27"/>
+      <c r="G46" s="27"/>
+      <c r="H46" s="27"/>
+      <c r="I46" s="27"/>
     </row>
     <row r="47" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B47" s="4">
@@ -3131,28 +3131,28 @@
       <c r="I111" s="20"/>
     </row>
     <row r="112" spans="2:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B112" s="32" t="s">
+      <c r="B112" s="34" t="s">
         <v>57</v>
       </c>
-      <c r="C112" s="33"/>
-      <c r="D112" s="33"/>
-      <c r="E112" s="33"/>
-      <c r="F112" s="33"/>
-      <c r="G112" s="33"/>
-      <c r="H112" s="33"/>
-      <c r="I112" s="33"/>
-      <c r="J112" s="34"/>
+      <c r="C112" s="35"/>
+      <c r="D112" s="35"/>
+      <c r="E112" s="35"/>
+      <c r="F112" s="35"/>
+      <c r="G112" s="35"/>
+      <c r="H112" s="35"/>
+      <c r="I112" s="35"/>
+      <c r="J112" s="36"/>
     </row>
     <row r="113" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B113" s="35"/>
-      <c r="C113" s="36"/>
-      <c r="D113" s="36"/>
-      <c r="E113" s="36"/>
-      <c r="F113" s="36"/>
-      <c r="G113" s="36"/>
-      <c r="H113" s="36"/>
-      <c r="I113" s="36"/>
-      <c r="J113" s="37"/>
+      <c r="B113" s="37"/>
+      <c r="C113" s="38"/>
+      <c r="D113" s="38"/>
+      <c r="E113" s="38"/>
+      <c r="F113" s="38"/>
+      <c r="G113" s="38"/>
+      <c r="H113" s="38"/>
+      <c r="I113" s="38"/>
+      <c r="J113" s="39"/>
     </row>
     <row r="114" spans="2:10" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B114" s="8" t="s">
@@ -4074,15 +4074,15 @@
       <c r="C149" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D149" s="26" t="s">
+      <c r="D149" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="E149" s="27"/>
-      <c r="F149" s="27"/>
-      <c r="G149" s="27"/>
-      <c r="H149" s="27"/>
-      <c r="I149" s="27"/>
-      <c r="J149" s="28"/>
+      <c r="E149" s="29"/>
+      <c r="F149" s="29"/>
+      <c r="G149" s="29"/>
+      <c r="H149" s="29"/>
+      <c r="I149" s="29"/>
+      <c r="J149" s="30"/>
     </row>
     <row r="150" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B150" s="4">
@@ -4091,13 +4091,13 @@
       <c r="C150" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D150" s="29"/>
-      <c r="E150" s="30"/>
-      <c r="F150" s="30"/>
-      <c r="G150" s="30"/>
-      <c r="H150" s="30"/>
-      <c r="I150" s="30"/>
-      <c r="J150" s="31"/>
+      <c r="D150" s="31"/>
+      <c r="E150" s="32"/>
+      <c r="F150" s="32"/>
+      <c r="G150" s="32"/>
+      <c r="H150" s="32"/>
+      <c r="I150" s="32"/>
+      <c r="J150" s="33"/>
     </row>
     <row r="151" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B151" s="4">
@@ -4740,26 +4740,32 @@
       </c>
     </row>
     <row r="175" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B175" s="3"/>
-      <c r="C175" s="3"/>
-      <c r="D175" s="3"/>
-      <c r="E175" s="3"/>
-      <c r="F175" s="3"/>
-      <c r="G175" s="3"/>
-      <c r="H175" s="3"/>
-      <c r="I175" s="1"/>
-      <c r="J175" s="1"/>
+      <c r="B175" s="4">
+        <v>45903</v>
+      </c>
+      <c r="C175" s="28" t="s">
+        <v>39</v>
+      </c>
+      <c r="D175" s="29"/>
+      <c r="E175" s="29"/>
+      <c r="F175" s="29"/>
+      <c r="G175" s="29"/>
+      <c r="H175" s="29"/>
+      <c r="I175" s="29"/>
+      <c r="J175" s="29"/>
     </row>
     <row r="176" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B176" s="3"/>
-      <c r="C176" s="3"/>
-      <c r="D176" s="3"/>
-      <c r="E176" s="3"/>
-      <c r="F176" s="3"/>
-      <c r="G176" s="3"/>
-      <c r="H176" s="3"/>
-      <c r="I176" s="1"/>
-      <c r="J176" s="1"/>
+      <c r="B176" s="4">
+        <v>45904</v>
+      </c>
+      <c r="C176" s="31"/>
+      <c r="D176" s="32"/>
+      <c r="E176" s="32"/>
+      <c r="F176" s="32"/>
+      <c r="G176" s="32"/>
+      <c r="H176" s="32"/>
+      <c r="I176" s="32"/>
+      <c r="J176" s="32"/>
     </row>
     <row r="177" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B177" s="3"/>
@@ -7402,7 +7408,77 @@
       <c r="J416" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="85">
+  <mergeCells count="86">
+    <mergeCell ref="C175:J176"/>
+    <mergeCell ref="D164:J164"/>
+    <mergeCell ref="D157:J157"/>
+    <mergeCell ref="D143:J143"/>
+    <mergeCell ref="D135:J135"/>
+    <mergeCell ref="F127:J127"/>
+    <mergeCell ref="D107:E107"/>
+    <mergeCell ref="F118:J118"/>
+    <mergeCell ref="G152:I152"/>
+    <mergeCell ref="D149:J150"/>
+    <mergeCell ref="G146:J146"/>
+    <mergeCell ref="D108:E108"/>
+    <mergeCell ref="B112:J113"/>
+    <mergeCell ref="G124:J124"/>
+    <mergeCell ref="D120:H120"/>
+    <mergeCell ref="G123:J123"/>
+    <mergeCell ref="D121:J121"/>
+    <mergeCell ref="D31:I31"/>
+    <mergeCell ref="G35:H35"/>
+    <mergeCell ref="D40:I40"/>
+    <mergeCell ref="D33:I33"/>
+    <mergeCell ref="D46:I46"/>
+    <mergeCell ref="D43:I43"/>
+    <mergeCell ref="D78:I78"/>
+    <mergeCell ref="G71:H71"/>
+    <mergeCell ref="D76:I76"/>
+    <mergeCell ref="D66:H66"/>
+    <mergeCell ref="D77:I77"/>
+    <mergeCell ref="D73:I73"/>
+    <mergeCell ref="D70:E70"/>
+    <mergeCell ref="D74:F74"/>
+    <mergeCell ref="D84:I84"/>
+    <mergeCell ref="D69:I69"/>
+    <mergeCell ref="D8:I8"/>
+    <mergeCell ref="D9:I9"/>
+    <mergeCell ref="D10:I10"/>
+    <mergeCell ref="D11:I11"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="D14:I14"/>
+    <mergeCell ref="G27:H27"/>
+    <mergeCell ref="D25:I25"/>
+    <mergeCell ref="G20:H20"/>
+    <mergeCell ref="D19:I19"/>
+    <mergeCell ref="D18:I18"/>
+    <mergeCell ref="D30:I30"/>
+    <mergeCell ref="G80:H80"/>
+    <mergeCell ref="G42:H42"/>
+    <mergeCell ref="D60:I60"/>
+    <mergeCell ref="D62:I62"/>
+    <mergeCell ref="D61:I61"/>
+    <mergeCell ref="G49:H49"/>
+    <mergeCell ref="D47:I47"/>
+    <mergeCell ref="D55:I55"/>
+    <mergeCell ref="G57:H57"/>
+    <mergeCell ref="G64:H64"/>
+    <mergeCell ref="D96:I96"/>
+    <mergeCell ref="D95:F95"/>
+    <mergeCell ref="G95:H95"/>
+    <mergeCell ref="D92:I92"/>
+    <mergeCell ref="D93:I93"/>
+    <mergeCell ref="D90:E90"/>
+    <mergeCell ref="D91:H91"/>
+    <mergeCell ref="E86:G86"/>
+    <mergeCell ref="D88:I88"/>
+    <mergeCell ref="H67:I67"/>
+    <mergeCell ref="G81:H81"/>
+    <mergeCell ref="D67:F67"/>
+    <mergeCell ref="F68:I68"/>
+    <mergeCell ref="D87:E87"/>
+    <mergeCell ref="G87:I87"/>
     <mergeCell ref="D172:J172"/>
     <mergeCell ref="D98:I98"/>
     <mergeCell ref="D94:I94"/>
@@ -7419,75 +7495,6 @@
     <mergeCell ref="D105:E105"/>
     <mergeCell ref="G100:I100"/>
     <mergeCell ref="B101:I101"/>
-    <mergeCell ref="G64:H64"/>
-    <mergeCell ref="D96:I96"/>
-    <mergeCell ref="D95:F95"/>
-    <mergeCell ref="G95:H95"/>
-    <mergeCell ref="D92:I92"/>
-    <mergeCell ref="D93:I93"/>
-    <mergeCell ref="D90:E90"/>
-    <mergeCell ref="D91:H91"/>
-    <mergeCell ref="E86:G86"/>
-    <mergeCell ref="D88:I88"/>
-    <mergeCell ref="H67:I67"/>
-    <mergeCell ref="G81:H81"/>
-    <mergeCell ref="D67:F67"/>
-    <mergeCell ref="F68:I68"/>
-    <mergeCell ref="D87:E87"/>
-    <mergeCell ref="G87:I87"/>
-    <mergeCell ref="D60:I60"/>
-    <mergeCell ref="D62:I62"/>
-    <mergeCell ref="D61:I61"/>
-    <mergeCell ref="G49:H49"/>
-    <mergeCell ref="D47:I47"/>
-    <mergeCell ref="D55:I55"/>
-    <mergeCell ref="G57:H57"/>
-    <mergeCell ref="D84:I84"/>
-    <mergeCell ref="D69:I69"/>
-    <mergeCell ref="D8:I8"/>
-    <mergeCell ref="D9:I9"/>
-    <mergeCell ref="D10:I10"/>
-    <mergeCell ref="D11:I11"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="D14:I14"/>
-    <mergeCell ref="G27:H27"/>
-    <mergeCell ref="D25:I25"/>
-    <mergeCell ref="G20:H20"/>
-    <mergeCell ref="D19:I19"/>
-    <mergeCell ref="D18:I18"/>
-    <mergeCell ref="D30:I30"/>
-    <mergeCell ref="G80:H80"/>
-    <mergeCell ref="G42:H42"/>
-    <mergeCell ref="D78:I78"/>
-    <mergeCell ref="G71:H71"/>
-    <mergeCell ref="D76:I76"/>
-    <mergeCell ref="D66:H66"/>
-    <mergeCell ref="D77:I77"/>
-    <mergeCell ref="D73:I73"/>
-    <mergeCell ref="D70:E70"/>
-    <mergeCell ref="D74:F74"/>
-    <mergeCell ref="D31:I31"/>
-    <mergeCell ref="G35:H35"/>
-    <mergeCell ref="D40:I40"/>
-    <mergeCell ref="D33:I33"/>
-    <mergeCell ref="D46:I46"/>
-    <mergeCell ref="D43:I43"/>
-    <mergeCell ref="D107:E107"/>
-    <mergeCell ref="F118:J118"/>
-    <mergeCell ref="G152:I152"/>
-    <mergeCell ref="D149:J150"/>
-    <mergeCell ref="G146:J146"/>
-    <mergeCell ref="D108:E108"/>
-    <mergeCell ref="B112:J113"/>
-    <mergeCell ref="G124:J124"/>
-    <mergeCell ref="D120:H120"/>
-    <mergeCell ref="G123:J123"/>
-    <mergeCell ref="D121:J121"/>
-    <mergeCell ref="D164:J164"/>
-    <mergeCell ref="D157:J157"/>
-    <mergeCell ref="D143:J143"/>
-    <mergeCell ref="D135:J135"/>
-    <mergeCell ref="F127:J127"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/attendance_sheet.xlsx
+++ b/attendance_sheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\repositary\3rd_Year_5th_Semester\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E63D263-202E-42C6-B469-690A2BA7C7B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10B6FCFB-3D86-4150-B724-0D678E6DC81E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{EB654061-A886-47D1-BF86-9B1A84FCE7FB}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="871" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="872" uniqueCount="73">
   <si>
     <t>Date</t>
   </si>
@@ -535,6 +535,18 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -544,25 +556,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
@@ -585,6 +579,12 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -987,14 +987,14 @@
       <c r="C8" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D8" s="26" t="s">
+      <c r="D8" s="39" t="s">
         <v>20</v>
       </c>
-      <c r="E8" s="26"/>
-      <c r="F8" s="26"/>
-      <c r="G8" s="26"/>
-      <c r="H8" s="26"/>
-      <c r="I8" s="26"/>
+      <c r="E8" s="39"/>
+      <c r="F8" s="39"/>
+      <c r="G8" s="39"/>
+      <c r="H8" s="39"/>
+      <c r="I8" s="39"/>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B9" s="4">
@@ -1003,14 +1003,14 @@
       <c r="C9" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D9" s="26" t="s">
+      <c r="D9" s="39" t="s">
         <v>20</v>
       </c>
-      <c r="E9" s="26"/>
-      <c r="F9" s="26"/>
-      <c r="G9" s="26"/>
-      <c r="H9" s="26"/>
-      <c r="I9" s="26"/>
+      <c r="E9" s="39"/>
+      <c r="F9" s="39"/>
+      <c r="G9" s="39"/>
+      <c r="H9" s="39"/>
+      <c r="I9" s="39"/>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B10" s="4">
@@ -1019,14 +1019,14 @@
       <c r="C10" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D10" s="26" t="s">
+      <c r="D10" s="39" t="s">
         <v>20</v>
       </c>
-      <c r="E10" s="26"/>
-      <c r="F10" s="26"/>
-      <c r="G10" s="26"/>
-      <c r="H10" s="26"/>
-      <c r="I10" s="26"/>
+      <c r="E10" s="39"/>
+      <c r="F10" s="39"/>
+      <c r="G10" s="39"/>
+      <c r="H10" s="39"/>
+      <c r="I10" s="39"/>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B11" s="4">
@@ -1035,14 +1035,14 @@
       <c r="C11" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D11" s="26" t="s">
+      <c r="D11" s="39" t="s">
         <v>20</v>
       </c>
-      <c r="E11" s="26"/>
-      <c r="F11" s="26"/>
-      <c r="G11" s="26"/>
-      <c r="H11" s="26"/>
-      <c r="I11" s="26"/>
+      <c r="E11" s="39"/>
+      <c r="F11" s="39"/>
+      <c r="G11" s="39"/>
+      <c r="H11" s="39"/>
+      <c r="I11" s="39"/>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B12" s="4">
@@ -1086,10 +1086,10 @@
       <c r="F13" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="G13" s="26" t="s">
+      <c r="G13" s="39" t="s">
         <v>18</v>
       </c>
-      <c r="H13" s="26"/>
+      <c r="H13" s="39"/>
       <c r="I13" s="1" t="s">
         <v>14</v>
       </c>
@@ -1101,14 +1101,14 @@
       <c r="C14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D14" s="26" t="s">
+      <c r="D14" s="39" t="s">
         <v>19</v>
       </c>
-      <c r="E14" s="26"/>
-      <c r="F14" s="26"/>
-      <c r="G14" s="26"/>
-      <c r="H14" s="26"/>
-      <c r="I14" s="26"/>
+      <c r="E14" s="39"/>
+      <c r="F14" s="39"/>
+      <c r="G14" s="39"/>
+      <c r="H14" s="39"/>
+      <c r="I14" s="39"/>
     </row>
     <row r="15" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B15" s="4">
@@ -1195,14 +1195,14 @@
       <c r="C18" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D18" s="26" t="s">
+      <c r="D18" s="39" t="s">
         <v>23</v>
       </c>
-      <c r="E18" s="26"/>
-      <c r="F18" s="26"/>
-      <c r="G18" s="26"/>
-      <c r="H18" s="26"/>
-      <c r="I18" s="26"/>
+      <c r="E18" s="39"/>
+      <c r="F18" s="39"/>
+      <c r="G18" s="39"/>
+      <c r="H18" s="39"/>
+      <c r="I18" s="39"/>
     </row>
     <row r="19" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B19" s="4">
@@ -1211,14 +1211,14 @@
       <c r="C19" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D19" s="26" t="s">
+      <c r="D19" s="39" t="s">
         <v>23</v>
       </c>
-      <c r="E19" s="26"/>
-      <c r="F19" s="26"/>
-      <c r="G19" s="26"/>
-      <c r="H19" s="26"/>
-      <c r="I19" s="26"/>
+      <c r="E19" s="39"/>
+      <c r="F19" s="39"/>
+      <c r="G19" s="39"/>
+      <c r="H19" s="39"/>
+      <c r="I19" s="39"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B20" s="4">
@@ -1236,10 +1236,10 @@
       <c r="F20" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G20" s="26" t="s">
+      <c r="G20" s="39" t="s">
         <v>15</v>
       </c>
-      <c r="H20" s="26"/>
+      <c r="H20" s="39"/>
       <c r="I20" s="1" t="s">
         <v>14</v>
       </c>
@@ -1355,14 +1355,14 @@
       <c r="C25" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D25" s="26" t="s">
+      <c r="D25" s="39" t="s">
         <v>26</v>
       </c>
-      <c r="E25" s="26"/>
-      <c r="F25" s="26"/>
-      <c r="G25" s="26"/>
-      <c r="H25" s="26"/>
-      <c r="I25" s="26"/>
+      <c r="E25" s="39"/>
+      <c r="F25" s="39"/>
+      <c r="G25" s="39"/>
+      <c r="H25" s="39"/>
+      <c r="I25" s="39"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B26" s="4">
@@ -1406,10 +1406,10 @@
       <c r="F27" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G27" s="26" t="s">
+      <c r="G27" s="39" t="s">
         <v>18</v>
       </c>
-      <c r="H27" s="26"/>
+      <c r="H27" s="39"/>
       <c r="I27" s="1" t="s">
         <v>14</v>
       </c>
@@ -1473,14 +1473,14 @@
       <c r="C30" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D30" s="27" t="s">
+      <c r="D30" s="38" t="s">
         <v>20</v>
       </c>
-      <c r="E30" s="27"/>
-      <c r="F30" s="27"/>
-      <c r="G30" s="27"/>
-      <c r="H30" s="27"/>
-      <c r="I30" s="27"/>
+      <c r="E30" s="38"/>
+      <c r="F30" s="38"/>
+      <c r="G30" s="38"/>
+      <c r="H30" s="38"/>
+      <c r="I30" s="38"/>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B31" s="4">
@@ -1489,14 +1489,14 @@
       <c r="C31" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D31" s="27" t="s">
+      <c r="D31" s="38" t="s">
         <v>20</v>
       </c>
-      <c r="E31" s="27"/>
-      <c r="F31" s="27"/>
-      <c r="G31" s="27"/>
-      <c r="H31" s="27"/>
-      <c r="I31" s="27"/>
+      <c r="E31" s="38"/>
+      <c r="F31" s="38"/>
+      <c r="G31" s="38"/>
+      <c r="H31" s="38"/>
+      <c r="I31" s="38"/>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B32" s="4">
@@ -1531,14 +1531,14 @@
       <c r="C33" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D33" s="27" t="s">
+      <c r="D33" s="38" t="s">
         <v>20</v>
       </c>
-      <c r="E33" s="27"/>
-      <c r="F33" s="27"/>
-      <c r="G33" s="27"/>
-      <c r="H33" s="27"/>
-      <c r="I33" s="27"/>
+      <c r="E33" s="38"/>
+      <c r="F33" s="38"/>
+      <c r="G33" s="38"/>
+      <c r="H33" s="38"/>
+      <c r="I33" s="38"/>
     </row>
     <row r="34" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B34" s="4">
@@ -1582,10 +1582,10 @@
       <c r="F35" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G35" s="27" t="s">
+      <c r="G35" s="38" t="s">
         <v>18</v>
       </c>
-      <c r="H35" s="27"/>
+      <c r="H35" s="38"/>
       <c r="I35" s="1" t="s">
         <v>14</v>
       </c>
@@ -1701,14 +1701,14 @@
       <c r="C40" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D40" s="27" t="s">
+      <c r="D40" s="38" t="s">
         <v>20</v>
       </c>
-      <c r="E40" s="27"/>
-      <c r="F40" s="27"/>
-      <c r="G40" s="27"/>
-      <c r="H40" s="27"/>
-      <c r="I40" s="27"/>
+      <c r="E40" s="38"/>
+      <c r="F40" s="38"/>
+      <c r="G40" s="38"/>
+      <c r="H40" s="38"/>
+      <c r="I40" s="38"/>
     </row>
     <row r="41" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B41" s="4">
@@ -1752,10 +1752,10 @@
       <c r="F42" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G42" s="27" t="s">
+      <c r="G42" s="38" t="s">
         <v>28</v>
       </c>
-      <c r="H42" s="27"/>
+      <c r="H42" s="38"/>
       <c r="I42" s="1" t="s">
         <v>15</v>
       </c>
@@ -1767,14 +1767,14 @@
       <c r="C43" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D43" s="27" t="s">
+      <c r="D43" s="38" t="s">
         <v>20</v>
       </c>
-      <c r="E43" s="27"/>
-      <c r="F43" s="27"/>
-      <c r="G43" s="27"/>
-      <c r="H43" s="27"/>
-      <c r="I43" s="27"/>
+      <c r="E43" s="38"/>
+      <c r="F43" s="38"/>
+      <c r="G43" s="38"/>
+      <c r="H43" s="38"/>
+      <c r="I43" s="38"/>
     </row>
     <row r="44" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B44" s="4">
@@ -1838,14 +1838,14 @@
       <c r="C46" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D46" s="27" t="s">
+      <c r="D46" s="38" t="s">
         <v>20</v>
       </c>
-      <c r="E46" s="27"/>
-      <c r="F46" s="27"/>
-      <c r="G46" s="27"/>
-      <c r="H46" s="27"/>
-      <c r="I46" s="27"/>
+      <c r="E46" s="38"/>
+      <c r="F46" s="38"/>
+      <c r="G46" s="38"/>
+      <c r="H46" s="38"/>
+      <c r="I46" s="38"/>
     </row>
     <row r="47" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B47" s="4">
@@ -1854,14 +1854,14 @@
       <c r="C47" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D47" s="23" t="s">
+      <c r="D47" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="E47" s="24"/>
-      <c r="F47" s="24"/>
-      <c r="G47" s="24"/>
-      <c r="H47" s="24"/>
-      <c r="I47" s="25"/>
+      <c r="E47" s="28"/>
+      <c r="F47" s="28"/>
+      <c r="G47" s="28"/>
+      <c r="H47" s="28"/>
+      <c r="I47" s="29"/>
     </row>
     <row r="48" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B48" s="4">
@@ -1905,10 +1905,10 @@
       <c r="F49" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G49" s="23" t="s">
+      <c r="G49" s="27" t="s">
         <v>29</v>
       </c>
-      <c r="H49" s="25"/>
+      <c r="H49" s="29"/>
       <c r="I49" s="1" t="s">
         <v>30</v>
       </c>
@@ -2050,14 +2050,14 @@
       <c r="C55" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="D55" s="24" t="s">
+      <c r="D55" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="E55" s="24"/>
-      <c r="F55" s="24"/>
-      <c r="G55" s="24"/>
-      <c r="H55" s="24"/>
-      <c r="I55" s="24"/>
+      <c r="E55" s="28"/>
+      <c r="F55" s="28"/>
+      <c r="G55" s="28"/>
+      <c r="H55" s="28"/>
+      <c r="I55" s="28"/>
     </row>
     <row r="56" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B56" s="4">
@@ -2101,10 +2101,10 @@
       <c r="F57" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G57" s="23" t="s">
+      <c r="G57" s="27" t="s">
         <v>37</v>
       </c>
-      <c r="H57" s="25"/>
+      <c r="H57" s="29"/>
       <c r="I57" s="1" t="s">
         <v>36</v>
       </c>
@@ -2168,14 +2168,14 @@
       <c r="C60" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D60" s="23" t="s">
+      <c r="D60" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="E60" s="24"/>
-      <c r="F60" s="24"/>
-      <c r="G60" s="24"/>
-      <c r="H60" s="24"/>
-      <c r="I60" s="25"/>
+      <c r="E60" s="28"/>
+      <c r="F60" s="28"/>
+      <c r="G60" s="28"/>
+      <c r="H60" s="28"/>
+      <c r="I60" s="29"/>
     </row>
     <row r="61" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B61" s="4">
@@ -2184,14 +2184,14 @@
       <c r="C61" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D61" s="23" t="s">
+      <c r="D61" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="E61" s="24"/>
-      <c r="F61" s="24"/>
-      <c r="G61" s="24"/>
-      <c r="H61" s="24"/>
-      <c r="I61" s="25"/>
+      <c r="E61" s="28"/>
+      <c r="F61" s="28"/>
+      <c r="G61" s="28"/>
+      <c r="H61" s="28"/>
+      <c r="I61" s="29"/>
     </row>
     <row r="62" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B62" s="4">
@@ -2200,14 +2200,14 @@
       <c r="C62" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D62" s="23" t="s">
+      <c r="D62" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="E62" s="24"/>
-      <c r="F62" s="24"/>
-      <c r="G62" s="24"/>
-      <c r="H62" s="24"/>
-      <c r="I62" s="25"/>
+      <c r="E62" s="28"/>
+      <c r="F62" s="28"/>
+      <c r="G62" s="28"/>
+      <c r="H62" s="28"/>
+      <c r="I62" s="29"/>
     </row>
     <row r="63" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B63" s="4">
@@ -2251,10 +2251,10 @@
       <c r="F64" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G64" s="23" t="s">
+      <c r="G64" s="27" t="s">
         <v>37</v>
       </c>
-      <c r="H64" s="25"/>
+      <c r="H64" s="29"/>
       <c r="I64" s="1" t="s">
         <v>14</v>
       </c>
@@ -2292,13 +2292,13 @@
       <c r="C66" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D66" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="E66" s="24"/>
-      <c r="F66" s="24"/>
-      <c r="G66" s="24"/>
-      <c r="H66" s="25"/>
+      <c r="D66" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="E66" s="28"/>
+      <c r="F66" s="28"/>
+      <c r="G66" s="28"/>
+      <c r="H66" s="29"/>
       <c r="I66" s="1" t="s">
         <v>16</v>
       </c>
@@ -2310,18 +2310,18 @@
       <c r="C67" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D67" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="E67" s="24"/>
-      <c r="F67" s="25"/>
+      <c r="D67" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="E67" s="28"/>
+      <c r="F67" s="29"/>
       <c r="G67" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="H67" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="I67" s="25"/>
+      <c r="H67" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="I67" s="29"/>
     </row>
     <row r="68" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B68" s="4">
@@ -2336,12 +2336,12 @@
       <c r="E68" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F68" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="G68" s="24"/>
-      <c r="H68" s="24"/>
-      <c r="I68" s="25"/>
+      <c r="F68" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="G68" s="28"/>
+      <c r="H68" s="28"/>
+      <c r="I68" s="29"/>
     </row>
     <row r="69" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B69" s="4">
@@ -2350,14 +2350,14 @@
       <c r="C69" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D69" s="23" t="s">
+      <c r="D69" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="E69" s="24"/>
-      <c r="F69" s="24"/>
-      <c r="G69" s="24"/>
-      <c r="H69" s="24"/>
-      <c r="I69" s="25"/>
+      <c r="E69" s="28"/>
+      <c r="F69" s="28"/>
+      <c r="G69" s="28"/>
+      <c r="H69" s="28"/>
+      <c r="I69" s="29"/>
     </row>
     <row r="70" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B70" s="4">
@@ -2366,10 +2366,10 @@
       <c r="C70" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D70" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="E70" s="25"/>
+      <c r="D70" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="E70" s="29"/>
       <c r="F70" s="3" t="s">
         <v>15</v>
       </c>
@@ -2399,10 +2399,10 @@
       <c r="F71" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G71" s="23" t="s">
+      <c r="G71" s="27" t="s">
         <v>37</v>
       </c>
-      <c r="H71" s="25"/>
+      <c r="H71" s="29"/>
       <c r="I71" s="1" t="s">
         <v>14</v>
       </c>
@@ -2440,14 +2440,14 @@
       <c r="C73" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D73" s="23" t="s">
+      <c r="D73" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="E73" s="24"/>
-      <c r="F73" s="24"/>
-      <c r="G73" s="24"/>
-      <c r="H73" s="24"/>
-      <c r="I73" s="25"/>
+      <c r="E73" s="28"/>
+      <c r="F73" s="28"/>
+      <c r="G73" s="28"/>
+      <c r="H73" s="28"/>
+      <c r="I73" s="29"/>
     </row>
     <row r="74" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B74" s="4">
@@ -2456,11 +2456,11 @@
       <c r="C74" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D74" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="E74" s="24"/>
-      <c r="F74" s="25"/>
+      <c r="D74" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="E74" s="28"/>
+      <c r="F74" s="29"/>
       <c r="G74" s="3" t="s">
         <v>16</v>
       </c>
@@ -2496,14 +2496,14 @@
       <c r="C76" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D76" s="23" t="s">
+      <c r="D76" s="27" t="s">
         <v>39</v>
       </c>
-      <c r="E76" s="24"/>
-      <c r="F76" s="24"/>
-      <c r="G76" s="24"/>
-      <c r="H76" s="24"/>
-      <c r="I76" s="25"/>
+      <c r="E76" s="28"/>
+      <c r="F76" s="28"/>
+      <c r="G76" s="28"/>
+      <c r="H76" s="28"/>
+      <c r="I76" s="29"/>
     </row>
     <row r="77" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B77" s="4">
@@ -2512,14 +2512,14 @@
       <c r="C77" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D77" s="23" t="s">
+      <c r="D77" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="E77" s="24"/>
-      <c r="F77" s="24"/>
-      <c r="G77" s="24"/>
-      <c r="H77" s="24"/>
-      <c r="I77" s="25"/>
+      <c r="E77" s="28"/>
+      <c r="F77" s="28"/>
+      <c r="G77" s="28"/>
+      <c r="H77" s="28"/>
+      <c r="I77" s="29"/>
     </row>
     <row r="78" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B78" s="4">
@@ -2528,14 +2528,14 @@
       <c r="C78" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D78" s="23" t="s">
+      <c r="D78" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="E78" s="24"/>
-      <c r="F78" s="24"/>
-      <c r="G78" s="24"/>
-      <c r="H78" s="24"/>
-      <c r="I78" s="25"/>
+      <c r="E78" s="28"/>
+      <c r="F78" s="28"/>
+      <c r="G78" s="28"/>
+      <c r="H78" s="28"/>
+      <c r="I78" s="29"/>
     </row>
     <row r="79" spans="2:9" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B79" s="16" t="s">
@@ -2579,10 +2579,10 @@
       <c r="F80" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G80" s="23" t="s">
+      <c r="G80" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="H80" s="25"/>
+      <c r="H80" s="29"/>
       <c r="I80" s="1" t="s">
         <v>14</v>
       </c>
@@ -2603,10 +2603,10 @@
       <c r="F81" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="G81" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="H81" s="25"/>
+      <c r="G81" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="H81" s="29"/>
       <c r="I81" s="1" t="s">
         <v>16</v>
       </c>
@@ -2670,14 +2670,14 @@
       <c r="C84" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D84" s="23" t="s">
+      <c r="D84" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="E84" s="24"/>
-      <c r="F84" s="24"/>
-      <c r="G84" s="24"/>
-      <c r="H84" s="24"/>
-      <c r="I84" s="25"/>
+      <c r="E84" s="28"/>
+      <c r="F84" s="28"/>
+      <c r="G84" s="28"/>
+      <c r="H84" s="28"/>
+      <c r="I84" s="29"/>
     </row>
     <row r="85" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B85" s="4">
@@ -2715,11 +2715,11 @@
       <c r="D86" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="E86" s="23" t="s">
+      <c r="E86" s="27" t="s">
         <v>43</v>
       </c>
-      <c r="F86" s="24"/>
-      <c r="G86" s="25"/>
+      <c r="F86" s="28"/>
+      <c r="G86" s="29"/>
       <c r="H86" s="3" t="s">
         <v>14</v>
       </c>
@@ -2734,18 +2734,18 @@
       <c r="C87" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D87" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="E87" s="25"/>
+      <c r="D87" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="E87" s="29"/>
       <c r="F87" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G87" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="H87" s="24"/>
-      <c r="I87" s="25"/>
+      <c r="G87" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="H87" s="28"/>
+      <c r="I87" s="29"/>
     </row>
     <row r="88" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B88" s="4">
@@ -2754,14 +2754,14 @@
       <c r="C88" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D88" s="23" t="s">
+      <c r="D88" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="E88" s="24"/>
-      <c r="F88" s="24"/>
-      <c r="G88" s="24"/>
-      <c r="H88" s="24"/>
-      <c r="I88" s="25"/>
+      <c r="E88" s="28"/>
+      <c r="F88" s="28"/>
+      <c r="G88" s="28"/>
+      <c r="H88" s="28"/>
+      <c r="I88" s="29"/>
     </row>
     <row r="89" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B89" s="4">
@@ -2770,18 +2770,18 @@
       <c r="C89" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D89" s="23" t="s">
+      <c r="D89" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="E89" s="24"/>
-      <c r="F89" s="25"/>
+      <c r="E89" s="28"/>
+      <c r="F89" s="29"/>
       <c r="G89" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="H89" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="I89" s="25"/>
+      <c r="H89" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="I89" s="29"/>
     </row>
     <row r="90" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B90" s="4">
@@ -2790,10 +2790,10 @@
       <c r="C90" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D90" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="E90" s="25"/>
+      <c r="D90" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="E90" s="29"/>
       <c r="F90" s="3" t="s">
         <v>16</v>
       </c>
@@ -2815,13 +2815,13 @@
       <c r="C91" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D91" s="23" t="s">
+      <c r="D91" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="E91" s="24"/>
-      <c r="F91" s="24"/>
-      <c r="G91" s="24"/>
-      <c r="H91" s="25"/>
+      <c r="E91" s="28"/>
+      <c r="F91" s="28"/>
+      <c r="G91" s="28"/>
+      <c r="H91" s="29"/>
       <c r="I91" s="18" t="s">
         <v>45</v>
       </c>
@@ -2833,14 +2833,14 @@
       <c r="C92" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D92" s="23" t="s">
+      <c r="D92" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="E92" s="24"/>
-      <c r="F92" s="24"/>
-      <c r="G92" s="24"/>
-      <c r="H92" s="24"/>
-      <c r="I92" s="25"/>
+      <c r="E92" s="28"/>
+      <c r="F92" s="28"/>
+      <c r="G92" s="28"/>
+      <c r="H92" s="28"/>
+      <c r="I92" s="29"/>
     </row>
     <row r="93" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B93" s="4">
@@ -2849,14 +2849,14 @@
       <c r="C93" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D93" s="23" t="s">
+      <c r="D93" s="27" t="s">
         <v>46</v>
       </c>
-      <c r="E93" s="24"/>
-      <c r="F93" s="24"/>
-      <c r="G93" s="24"/>
-      <c r="H93" s="24"/>
-      <c r="I93" s="25"/>
+      <c r="E93" s="28"/>
+      <c r="F93" s="28"/>
+      <c r="G93" s="28"/>
+      <c r="H93" s="28"/>
+      <c r="I93" s="29"/>
     </row>
     <row r="94" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B94" s="4">
@@ -2865,14 +2865,14 @@
       <c r="C94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D94" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="E94" s="24"/>
-      <c r="F94" s="24"/>
-      <c r="G94" s="24"/>
-      <c r="H94" s="24"/>
-      <c r="I94" s="25"/>
+      <c r="D94" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="E94" s="28"/>
+      <c r="F94" s="28"/>
+      <c r="G94" s="28"/>
+      <c r="H94" s="28"/>
+      <c r="I94" s="29"/>
     </row>
     <row r="95" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B95" s="4">
@@ -2881,15 +2881,15 @@
       <c r="C95" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D95" s="23" t="s">
+      <c r="D95" s="27" t="s">
         <v>47</v>
       </c>
-      <c r="E95" s="24"/>
-      <c r="F95" s="25"/>
-      <c r="G95" s="23" t="s">
+      <c r="E95" s="28"/>
+      <c r="F95" s="29"/>
+      <c r="G95" s="27" t="s">
         <v>48</v>
       </c>
-      <c r="H95" s="25"/>
+      <c r="H95" s="29"/>
       <c r="I95" s="1" t="s">
         <v>14</v>
       </c>
@@ -2901,14 +2901,14 @@
       <c r="C96" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D96" s="23" t="s">
+      <c r="D96" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="E96" s="24"/>
-      <c r="F96" s="24"/>
-      <c r="G96" s="24"/>
-      <c r="H96" s="24"/>
-      <c r="I96" s="25"/>
+      <c r="E96" s="28"/>
+      <c r="F96" s="28"/>
+      <c r="G96" s="28"/>
+      <c r="H96" s="28"/>
+      <c r="I96" s="29"/>
     </row>
     <row r="97" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B97" s="4">
@@ -2917,14 +2917,14 @@
       <c r="C97" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D97" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="E97" s="24"/>
-      <c r="F97" s="24"/>
-      <c r="G97" s="24"/>
-      <c r="H97" s="24"/>
-      <c r="I97" s="25"/>
+      <c r="D97" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="E97" s="28"/>
+      <c r="F97" s="28"/>
+      <c r="G97" s="28"/>
+      <c r="H97" s="28"/>
+      <c r="I97" s="29"/>
     </row>
     <row r="98" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B98" s="4">
@@ -2933,14 +2933,14 @@
       <c r="C98" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D98" s="23" t="s">
+      <c r="D98" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="E98" s="24"/>
-      <c r="F98" s="24"/>
-      <c r="G98" s="24"/>
-      <c r="H98" s="24"/>
-      <c r="I98" s="25"/>
+      <c r="E98" s="28"/>
+      <c r="F98" s="28"/>
+      <c r="G98" s="28"/>
+      <c r="H98" s="28"/>
+      <c r="I98" s="29"/>
     </row>
     <row r="99" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B99" s="4">
@@ -2949,12 +2949,12 @@
       <c r="C99" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D99" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="E99" s="24"/>
-      <c r="F99" s="24"/>
-      <c r="G99" s="25"/>
+      <c r="D99" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="E99" s="28"/>
+      <c r="F99" s="28"/>
+      <c r="G99" s="29"/>
       <c r="H99" s="3" t="s">
         <v>49</v>
       </c>
@@ -2978,21 +2978,21 @@
       <c r="F100" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="G100" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="H100" s="24"/>
-      <c r="I100" s="25"/>
+      <c r="G100" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="H100" s="28"/>
+      <c r="I100" s="29"/>
     </row>
     <row r="101" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B101" s="23"/>
-      <c r="C101" s="24"/>
-      <c r="D101" s="24"/>
-      <c r="E101" s="24"/>
-      <c r="F101" s="24"/>
-      <c r="G101" s="24"/>
-      <c r="H101" s="24"/>
-      <c r="I101" s="25"/>
+      <c r="B101" s="27"/>
+      <c r="C101" s="28"/>
+      <c r="D101" s="28"/>
+      <c r="E101" s="28"/>
+      <c r="F101" s="28"/>
+      <c r="G101" s="28"/>
+      <c r="H101" s="28"/>
+      <c r="I101" s="29"/>
     </row>
     <row r="102" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B102" s="3"/>
@@ -3011,10 +3011,10 @@
       <c r="C103" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D103" s="23" t="s">
+      <c r="D103" s="27" t="s">
         <v>51</v>
       </c>
-      <c r="E103" s="25"/>
+      <c r="E103" s="29"/>
       <c r="F103" s="3"/>
       <c r="G103" s="3"/>
       <c r="H103" s="3"/>
@@ -3027,10 +3027,10 @@
       <c r="C104" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D104" s="23" t="s">
+      <c r="D104" s="27" t="s">
         <v>52</v>
       </c>
-      <c r="E104" s="25"/>
+      <c r="E104" s="29"/>
       <c r="F104" s="3"/>
       <c r="G104" s="3"/>
       <c r="H104" s="3"/>
@@ -3043,10 +3043,10 @@
       <c r="C105" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D105" s="23" t="s">
+      <c r="D105" s="27" t="s">
         <v>53</v>
       </c>
-      <c r="E105" s="25"/>
+      <c r="E105" s="29"/>
       <c r="F105" s="3"/>
       <c r="G105" s="3"/>
       <c r="H105" s="3"/>
@@ -3059,10 +3059,10 @@
       <c r="C106" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D106" s="23" t="s">
+      <c r="D106" s="27" t="s">
         <v>54</v>
       </c>
-      <c r="E106" s="25"/>
+      <c r="E106" s="29"/>
       <c r="F106" s="3"/>
       <c r="G106" s="3"/>
       <c r="H106" s="3"/>
@@ -3075,10 +3075,10 @@
       <c r="C107" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D107" s="23" t="s">
+      <c r="D107" s="27" t="s">
         <v>55</v>
       </c>
-      <c r="E107" s="25"/>
+      <c r="E107" s="29"/>
       <c r="F107" s="3"/>
       <c r="G107" s="3"/>
       <c r="H107" s="3"/>
@@ -3091,10 +3091,10 @@
       <c r="C108" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D108" s="23" t="s">
+      <c r="D108" s="27" t="s">
         <v>56</v>
       </c>
-      <c r="E108" s="25"/>
+      <c r="E108" s="29"/>
       <c r="F108" s="3"/>
       <c r="G108" s="3"/>
       <c r="H108" s="3"/>
@@ -3131,28 +3131,28 @@
       <c r="I111" s="20"/>
     </row>
     <row r="112" spans="2:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B112" s="34" t="s">
+      <c r="B112" s="32" t="s">
         <v>57</v>
       </c>
-      <c r="C112" s="35"/>
-      <c r="D112" s="35"/>
-      <c r="E112" s="35"/>
-      <c r="F112" s="35"/>
-      <c r="G112" s="35"/>
-      <c r="H112" s="35"/>
-      <c r="I112" s="35"/>
-      <c r="J112" s="36"/>
+      <c r="C112" s="33"/>
+      <c r="D112" s="33"/>
+      <c r="E112" s="33"/>
+      <c r="F112" s="33"/>
+      <c r="G112" s="33"/>
+      <c r="H112" s="33"/>
+      <c r="I112" s="33"/>
+      <c r="J112" s="34"/>
     </row>
     <row r="113" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B113" s="37"/>
-      <c r="C113" s="38"/>
-      <c r="D113" s="38"/>
-      <c r="E113" s="38"/>
-      <c r="F113" s="38"/>
-      <c r="G113" s="38"/>
-      <c r="H113" s="38"/>
-      <c r="I113" s="38"/>
-      <c r="J113" s="39"/>
+      <c r="B113" s="35"/>
+      <c r="C113" s="36"/>
+      <c r="D113" s="36"/>
+      <c r="E113" s="36"/>
+      <c r="F113" s="36"/>
+      <c r="G113" s="36"/>
+      <c r="H113" s="36"/>
+      <c r="I113" s="36"/>
+      <c r="J113" s="37"/>
     </row>
     <row r="114" spans="2:10" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B114" s="8" t="s">
@@ -3283,13 +3283,13 @@
       <c r="E118" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="F118" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="G118" s="24"/>
-      <c r="H118" s="24"/>
-      <c r="I118" s="24"/>
-      <c r="J118" s="25"/>
+      <c r="F118" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="G118" s="28"/>
+      <c r="H118" s="28"/>
+      <c r="I118" s="28"/>
+      <c r="J118" s="29"/>
     </row>
     <row r="119" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B119" s="4">
@@ -3327,13 +3327,13 @@
       <c r="C120" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D120" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="E120" s="24"/>
-      <c r="F120" s="24"/>
-      <c r="G120" s="24"/>
-      <c r="H120" s="25"/>
+      <c r="D120" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="E120" s="28"/>
+      <c r="F120" s="28"/>
+      <c r="G120" s="28"/>
+      <c r="H120" s="29"/>
       <c r="I120" s="1" t="s">
         <v>16</v>
       </c>
@@ -3348,15 +3348,15 @@
       <c r="C121" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D121" s="23" t="s">
+      <c r="D121" s="27" t="s">
         <v>65</v>
       </c>
-      <c r="E121" s="24"/>
-      <c r="F121" s="24"/>
-      <c r="G121" s="24"/>
-      <c r="H121" s="24"/>
-      <c r="I121" s="24"/>
-      <c r="J121" s="25"/>
+      <c r="E121" s="28"/>
+      <c r="F121" s="28"/>
+      <c r="G121" s="28"/>
+      <c r="H121" s="28"/>
+      <c r="I121" s="28"/>
+      <c r="J121" s="29"/>
     </row>
     <row r="122" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B122" s="4">
@@ -3403,12 +3403,12 @@
       <c r="F123" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="G123" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="H123" s="24"/>
-      <c r="I123" s="24"/>
-      <c r="J123" s="25"/>
+      <c r="G123" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="H123" s="28"/>
+      <c r="I123" s="28"/>
+      <c r="J123" s="29"/>
     </row>
     <row r="124" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B124" s="4">
@@ -3426,12 +3426,12 @@
       <c r="F124" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="G124" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="H124" s="24"/>
-      <c r="I124" s="24"/>
-      <c r="J124" s="25"/>
+      <c r="G124" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="H124" s="28"/>
+      <c r="I124" s="28"/>
+      <c r="J124" s="29"/>
     </row>
     <row r="125" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B125" s="4">
@@ -3446,13 +3446,13 @@
       <c r="E125" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="F125" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="G125" s="24"/>
-      <c r="H125" s="24"/>
-      <c r="I125" s="24"/>
-      <c r="J125" s="25"/>
+      <c r="F125" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="G125" s="28"/>
+      <c r="H125" s="28"/>
+      <c r="I125" s="28"/>
+      <c r="J125" s="29"/>
     </row>
     <row r="126" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B126" s="4">
@@ -3470,11 +3470,11 @@
       <c r="F126" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="G126" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="H126" s="24"/>
-      <c r="I126" s="25"/>
+      <c r="G126" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="H126" s="28"/>
+      <c r="I126" s="29"/>
       <c r="J126" s="1" t="s">
         <v>16</v>
       </c>
@@ -3492,13 +3492,13 @@
       <c r="E127" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="F127" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="G127" s="24"/>
-      <c r="H127" s="24"/>
-      <c r="I127" s="24"/>
-      <c r="J127" s="25"/>
+      <c r="F127" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="G127" s="28"/>
+      <c r="H127" s="28"/>
+      <c r="I127" s="28"/>
+      <c r="J127" s="29"/>
     </row>
     <row r="128" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B128" s="4">
@@ -3507,15 +3507,15 @@
       <c r="C128" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D128" s="23" t="s">
+      <c r="D128" s="27" t="s">
         <v>65</v>
       </c>
-      <c r="E128" s="24"/>
-      <c r="F128" s="24"/>
-      <c r="G128" s="24"/>
-      <c r="H128" s="24"/>
-      <c r="I128" s="24"/>
-      <c r="J128" s="25"/>
+      <c r="E128" s="28"/>
+      <c r="F128" s="28"/>
+      <c r="G128" s="28"/>
+      <c r="H128" s="28"/>
+      <c r="I128" s="28"/>
+      <c r="J128" s="29"/>
     </row>
     <row r="129" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B129" s="4">
@@ -3698,15 +3698,15 @@
       <c r="C135" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D135" s="23" t="s">
+      <c r="D135" s="27" t="s">
         <v>65</v>
       </c>
-      <c r="E135" s="24"/>
-      <c r="F135" s="24"/>
-      <c r="G135" s="24"/>
-      <c r="H135" s="24"/>
-      <c r="I135" s="24"/>
-      <c r="J135" s="25"/>
+      <c r="E135" s="28"/>
+      <c r="F135" s="28"/>
+      <c r="G135" s="28"/>
+      <c r="H135" s="28"/>
+      <c r="I135" s="28"/>
+      <c r="J135" s="29"/>
     </row>
     <row r="136" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B136" s="4">
@@ -3918,15 +3918,15 @@
       <c r="C143" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D143" s="23" t="s">
+      <c r="D143" s="27" t="s">
         <v>65</v>
       </c>
-      <c r="E143" s="24"/>
-      <c r="F143" s="24"/>
-      <c r="G143" s="24"/>
-      <c r="H143" s="24"/>
-      <c r="I143" s="24"/>
-      <c r="J143" s="25"/>
+      <c r="E143" s="28"/>
+      <c r="F143" s="28"/>
+      <c r="G143" s="28"/>
+      <c r="H143" s="28"/>
+      <c r="I143" s="28"/>
+      <c r="J143" s="29"/>
     </row>
     <row r="144" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B144" s="4">
@@ -4002,12 +4002,12 @@
       <c r="F146" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="G146" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="H146" s="24"/>
-      <c r="I146" s="24"/>
-      <c r="J146" s="25"/>
+      <c r="G146" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="H146" s="28"/>
+      <c r="I146" s="28"/>
+      <c r="J146" s="29"/>
     </row>
     <row r="147" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B147" s="4">
@@ -4074,14 +4074,14 @@
       <c r="C149" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D149" s="28" t="s">
+      <c r="D149" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E149" s="29"/>
-      <c r="F149" s="29"/>
-      <c r="G149" s="29"/>
-      <c r="H149" s="29"/>
-      <c r="I149" s="29"/>
+      <c r="E149" s="24"/>
+      <c r="F149" s="24"/>
+      <c r="G149" s="24"/>
+      <c r="H149" s="24"/>
+      <c r="I149" s="24"/>
       <c r="J149" s="30"/>
     </row>
     <row r="150" spans="2:10" x14ac:dyDescent="0.3">
@@ -4091,13 +4091,13 @@
       <c r="C150" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D150" s="31"/>
-      <c r="E150" s="32"/>
-      <c r="F150" s="32"/>
-      <c r="G150" s="32"/>
-      <c r="H150" s="32"/>
-      <c r="I150" s="32"/>
-      <c r="J150" s="33"/>
+      <c r="D150" s="25"/>
+      <c r="E150" s="26"/>
+      <c r="F150" s="26"/>
+      <c r="G150" s="26"/>
+      <c r="H150" s="26"/>
+      <c r="I150" s="26"/>
+      <c r="J150" s="31"/>
     </row>
     <row r="151" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B151" s="4">
@@ -4144,11 +4144,11 @@
       <c r="F152" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="G152" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="H152" s="24"/>
-      <c r="I152" s="25"/>
+      <c r="G152" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="H152" s="28"/>
+      <c r="I152" s="29"/>
       <c r="J152" s="1" t="s">
         <v>69</v>
       </c>
@@ -4276,15 +4276,15 @@
       <c r="C157" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D157" s="23" t="s">
+      <c r="D157" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="E157" s="24"/>
-      <c r="F157" s="24"/>
-      <c r="G157" s="24"/>
-      <c r="H157" s="24"/>
-      <c r="I157" s="24"/>
-      <c r="J157" s="25"/>
+      <c r="E157" s="28"/>
+      <c r="F157" s="28"/>
+      <c r="G157" s="28"/>
+      <c r="H157" s="28"/>
+      <c r="I157" s="28"/>
+      <c r="J157" s="29"/>
     </row>
     <row r="158" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B158" s="4">
@@ -4465,15 +4465,15 @@
       <c r="C164" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D164" s="23" t="s">
+      <c r="D164" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="E164" s="24"/>
-      <c r="F164" s="24"/>
-      <c r="G164" s="24"/>
-      <c r="H164" s="24"/>
-      <c r="I164" s="24"/>
-      <c r="J164" s="25"/>
+      <c r="E164" s="28"/>
+      <c r="F164" s="28"/>
+      <c r="G164" s="28"/>
+      <c r="H164" s="28"/>
+      <c r="I164" s="28"/>
+      <c r="J164" s="29"/>
     </row>
     <row r="165" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B165" s="4">
@@ -4671,15 +4671,15 @@
       <c r="C172" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D172" s="23" t="s">
+      <c r="D172" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="E172" s="24"/>
-      <c r="F172" s="24"/>
-      <c r="G172" s="24"/>
-      <c r="H172" s="24"/>
-      <c r="I172" s="24"/>
-      <c r="J172" s="25"/>
+      <c r="E172" s="28"/>
+      <c r="F172" s="28"/>
+      <c r="G172" s="28"/>
+      <c r="H172" s="28"/>
+      <c r="I172" s="28"/>
+      <c r="J172" s="29"/>
     </row>
     <row r="173" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B173" s="4">
@@ -4743,40 +4743,44 @@
       <c r="B175" s="4">
         <v>45903</v>
       </c>
-      <c r="C175" s="28" t="s">
+      <c r="C175" s="23" t="s">
         <v>39</v>
       </c>
-      <c r="D175" s="29"/>
-      <c r="E175" s="29"/>
-      <c r="F175" s="29"/>
-      <c r="G175" s="29"/>
-      <c r="H175" s="29"/>
-      <c r="I175" s="29"/>
-      <c r="J175" s="29"/>
+      <c r="D175" s="24"/>
+      <c r="E175" s="24"/>
+      <c r="F175" s="24"/>
+      <c r="G175" s="24"/>
+      <c r="H175" s="24"/>
+      <c r="I175" s="24"/>
+      <c r="J175" s="24"/>
     </row>
     <row r="176" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B176" s="4">
         <v>45904</v>
       </c>
-      <c r="C176" s="31"/>
-      <c r="D176" s="32"/>
-      <c r="E176" s="32"/>
-      <c r="F176" s="32"/>
-      <c r="G176" s="32"/>
-      <c r="H176" s="32"/>
-      <c r="I176" s="32"/>
-      <c r="J176" s="32"/>
+      <c r="C176" s="25"/>
+      <c r="D176" s="26"/>
+      <c r="E176" s="26"/>
+      <c r="F176" s="26"/>
+      <c r="G176" s="26"/>
+      <c r="H176" s="26"/>
+      <c r="I176" s="26"/>
+      <c r="J176" s="26"/>
     </row>
     <row r="177" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B177" s="3"/>
-      <c r="C177" s="3"/>
-      <c r="D177" s="3"/>
-      <c r="E177" s="3"/>
-      <c r="F177" s="3"/>
-      <c r="G177" s="3"/>
-      <c r="H177" s="3"/>
-      <c r="I177" s="1"/>
-      <c r="J177" s="1"/>
+      <c r="B177" s="4">
+        <v>45905</v>
+      </c>
+      <c r="C177" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="D177" s="28"/>
+      <c r="E177" s="28"/>
+      <c r="F177" s="28"/>
+      <c r="G177" s="28"/>
+      <c r="H177" s="28"/>
+      <c r="I177" s="28"/>
+      <c r="J177" s="29"/>
     </row>
     <row r="178" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B178" s="3"/>
@@ -7408,38 +7412,46 @@
       <c r="J416" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="86">
-    <mergeCell ref="C175:J176"/>
-    <mergeCell ref="D164:J164"/>
-    <mergeCell ref="D157:J157"/>
-    <mergeCell ref="D143:J143"/>
-    <mergeCell ref="D135:J135"/>
-    <mergeCell ref="F127:J127"/>
-    <mergeCell ref="D107:E107"/>
-    <mergeCell ref="F118:J118"/>
-    <mergeCell ref="G152:I152"/>
-    <mergeCell ref="D149:J150"/>
-    <mergeCell ref="G146:J146"/>
-    <mergeCell ref="D108:E108"/>
-    <mergeCell ref="B112:J113"/>
-    <mergeCell ref="G124:J124"/>
-    <mergeCell ref="D120:H120"/>
-    <mergeCell ref="G123:J123"/>
-    <mergeCell ref="D121:J121"/>
-    <mergeCell ref="D31:I31"/>
-    <mergeCell ref="G35:H35"/>
-    <mergeCell ref="D40:I40"/>
-    <mergeCell ref="D33:I33"/>
-    <mergeCell ref="D46:I46"/>
-    <mergeCell ref="D43:I43"/>
-    <mergeCell ref="D78:I78"/>
-    <mergeCell ref="G71:H71"/>
-    <mergeCell ref="D76:I76"/>
-    <mergeCell ref="D66:H66"/>
-    <mergeCell ref="D77:I77"/>
-    <mergeCell ref="D73:I73"/>
-    <mergeCell ref="D70:E70"/>
-    <mergeCell ref="D74:F74"/>
+  <mergeCells count="87">
+    <mergeCell ref="C177:J177"/>
+    <mergeCell ref="D106:E106"/>
+    <mergeCell ref="D99:G99"/>
+    <mergeCell ref="G126:I126"/>
+    <mergeCell ref="F125:J125"/>
+    <mergeCell ref="D128:J128"/>
+    <mergeCell ref="D103:E103"/>
+    <mergeCell ref="D104:E104"/>
+    <mergeCell ref="D105:E105"/>
+    <mergeCell ref="G100:I100"/>
+    <mergeCell ref="B101:I101"/>
+    <mergeCell ref="D98:I98"/>
+    <mergeCell ref="D94:I94"/>
+    <mergeCell ref="H89:I89"/>
+    <mergeCell ref="D89:F89"/>
+    <mergeCell ref="D97:I97"/>
+    <mergeCell ref="G64:H64"/>
+    <mergeCell ref="D96:I96"/>
+    <mergeCell ref="D95:F95"/>
+    <mergeCell ref="G95:H95"/>
+    <mergeCell ref="D92:I92"/>
+    <mergeCell ref="D93:I93"/>
+    <mergeCell ref="D90:E90"/>
+    <mergeCell ref="D91:H91"/>
+    <mergeCell ref="E86:G86"/>
+    <mergeCell ref="D88:I88"/>
+    <mergeCell ref="H67:I67"/>
+    <mergeCell ref="G81:H81"/>
+    <mergeCell ref="D67:F67"/>
+    <mergeCell ref="F68:I68"/>
+    <mergeCell ref="D87:E87"/>
+    <mergeCell ref="G87:I87"/>
+    <mergeCell ref="D60:I60"/>
+    <mergeCell ref="D62:I62"/>
+    <mergeCell ref="D61:I61"/>
+    <mergeCell ref="G49:H49"/>
+    <mergeCell ref="D47:I47"/>
+    <mergeCell ref="D55:I55"/>
+    <mergeCell ref="G57:H57"/>
     <mergeCell ref="D84:I84"/>
     <mergeCell ref="D69:I69"/>
     <mergeCell ref="D8:I8"/>
@@ -7456,45 +7468,38 @@
     <mergeCell ref="D30:I30"/>
     <mergeCell ref="G80:H80"/>
     <mergeCell ref="G42:H42"/>
-    <mergeCell ref="D60:I60"/>
-    <mergeCell ref="D62:I62"/>
-    <mergeCell ref="D61:I61"/>
-    <mergeCell ref="G49:H49"/>
-    <mergeCell ref="D47:I47"/>
-    <mergeCell ref="D55:I55"/>
-    <mergeCell ref="G57:H57"/>
-    <mergeCell ref="G64:H64"/>
-    <mergeCell ref="D96:I96"/>
-    <mergeCell ref="D95:F95"/>
-    <mergeCell ref="G95:H95"/>
-    <mergeCell ref="D92:I92"/>
-    <mergeCell ref="D93:I93"/>
-    <mergeCell ref="D90:E90"/>
-    <mergeCell ref="D91:H91"/>
-    <mergeCell ref="E86:G86"/>
-    <mergeCell ref="D88:I88"/>
-    <mergeCell ref="H67:I67"/>
-    <mergeCell ref="G81:H81"/>
-    <mergeCell ref="D67:F67"/>
-    <mergeCell ref="F68:I68"/>
-    <mergeCell ref="D87:E87"/>
-    <mergeCell ref="G87:I87"/>
+    <mergeCell ref="D78:I78"/>
+    <mergeCell ref="G71:H71"/>
+    <mergeCell ref="D76:I76"/>
+    <mergeCell ref="D66:H66"/>
+    <mergeCell ref="D77:I77"/>
+    <mergeCell ref="D73:I73"/>
+    <mergeCell ref="D70:E70"/>
+    <mergeCell ref="D74:F74"/>
+    <mergeCell ref="D31:I31"/>
+    <mergeCell ref="G35:H35"/>
+    <mergeCell ref="D40:I40"/>
+    <mergeCell ref="D33:I33"/>
+    <mergeCell ref="D46:I46"/>
+    <mergeCell ref="D43:I43"/>
+    <mergeCell ref="F127:J127"/>
+    <mergeCell ref="D107:E107"/>
+    <mergeCell ref="F118:J118"/>
+    <mergeCell ref="G152:I152"/>
+    <mergeCell ref="D149:J150"/>
+    <mergeCell ref="G146:J146"/>
+    <mergeCell ref="D108:E108"/>
+    <mergeCell ref="B112:J113"/>
+    <mergeCell ref="G124:J124"/>
+    <mergeCell ref="D120:H120"/>
+    <mergeCell ref="G123:J123"/>
+    <mergeCell ref="D121:J121"/>
+    <mergeCell ref="C175:J176"/>
+    <mergeCell ref="D164:J164"/>
+    <mergeCell ref="D157:J157"/>
+    <mergeCell ref="D143:J143"/>
+    <mergeCell ref="D135:J135"/>
     <mergeCell ref="D172:J172"/>
-    <mergeCell ref="D98:I98"/>
-    <mergeCell ref="D94:I94"/>
-    <mergeCell ref="H89:I89"/>
-    <mergeCell ref="D89:F89"/>
-    <mergeCell ref="D97:I97"/>
-    <mergeCell ref="D106:E106"/>
-    <mergeCell ref="D99:G99"/>
-    <mergeCell ref="G126:I126"/>
-    <mergeCell ref="F125:J125"/>
-    <mergeCell ref="D128:J128"/>
-    <mergeCell ref="D103:E103"/>
-    <mergeCell ref="D104:E104"/>
-    <mergeCell ref="D105:E105"/>
-    <mergeCell ref="G100:I100"/>
-    <mergeCell ref="B101:I101"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/attendance_sheet.xlsx
+++ b/attendance_sheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\repositary\3rd_Year_5th_Semester\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10B6FCFB-3D86-4150-B724-0D678E6DC81E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EC85645-1345-43A8-A07C-3B5CE7F3FFD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{EB654061-A886-47D1-BF86-9B1A84FCE7FB}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="872" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="880" uniqueCount="73">
   <si>
     <t>Date</t>
   </si>
@@ -535,18 +535,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -556,7 +544,25 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
@@ -579,12 +585,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -987,14 +987,14 @@
       <c r="C8" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D8" s="39" t="s">
+      <c r="D8" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="E8" s="39"/>
-      <c r="F8" s="39"/>
-      <c r="G8" s="39"/>
-      <c r="H8" s="39"/>
-      <c r="I8" s="39"/>
+      <c r="E8" s="26"/>
+      <c r="F8" s="26"/>
+      <c r="G8" s="26"/>
+      <c r="H8" s="26"/>
+      <c r="I8" s="26"/>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B9" s="4">
@@ -1003,14 +1003,14 @@
       <c r="C9" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D9" s="39" t="s">
+      <c r="D9" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="E9" s="39"/>
-      <c r="F9" s="39"/>
-      <c r="G9" s="39"/>
-      <c r="H9" s="39"/>
-      <c r="I9" s="39"/>
+      <c r="E9" s="26"/>
+      <c r="F9" s="26"/>
+      <c r="G9" s="26"/>
+      <c r="H9" s="26"/>
+      <c r="I9" s="26"/>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B10" s="4">
@@ -1019,14 +1019,14 @@
       <c r="C10" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D10" s="39" t="s">
+      <c r="D10" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="E10" s="39"/>
-      <c r="F10" s="39"/>
-      <c r="G10" s="39"/>
-      <c r="H10" s="39"/>
-      <c r="I10" s="39"/>
+      <c r="E10" s="26"/>
+      <c r="F10" s="26"/>
+      <c r="G10" s="26"/>
+      <c r="H10" s="26"/>
+      <c r="I10" s="26"/>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B11" s="4">
@@ -1035,14 +1035,14 @@
       <c r="C11" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D11" s="39" t="s">
+      <c r="D11" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="E11" s="39"/>
-      <c r="F11" s="39"/>
-      <c r="G11" s="39"/>
-      <c r="H11" s="39"/>
-      <c r="I11" s="39"/>
+      <c r="E11" s="26"/>
+      <c r="F11" s="26"/>
+      <c r="G11" s="26"/>
+      <c r="H11" s="26"/>
+      <c r="I11" s="26"/>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B12" s="4">
@@ -1086,10 +1086,10 @@
       <c r="F13" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="G13" s="39" t="s">
+      <c r="G13" s="26" t="s">
         <v>18</v>
       </c>
-      <c r="H13" s="39"/>
+      <c r="H13" s="26"/>
       <c r="I13" s="1" t="s">
         <v>14</v>
       </c>
@@ -1101,14 +1101,14 @@
       <c r="C14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D14" s="39" t="s">
+      <c r="D14" s="26" t="s">
         <v>19</v>
       </c>
-      <c r="E14" s="39"/>
-      <c r="F14" s="39"/>
-      <c r="G14" s="39"/>
-      <c r="H14" s="39"/>
-      <c r="I14" s="39"/>
+      <c r="E14" s="26"/>
+      <c r="F14" s="26"/>
+      <c r="G14" s="26"/>
+      <c r="H14" s="26"/>
+      <c r="I14" s="26"/>
     </row>
     <row r="15" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B15" s="4">
@@ -1195,14 +1195,14 @@
       <c r="C18" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D18" s="39" t="s">
+      <c r="D18" s="26" t="s">
         <v>23</v>
       </c>
-      <c r="E18" s="39"/>
-      <c r="F18" s="39"/>
-      <c r="G18" s="39"/>
-      <c r="H18" s="39"/>
-      <c r="I18" s="39"/>
+      <c r="E18" s="26"/>
+      <c r="F18" s="26"/>
+      <c r="G18" s="26"/>
+      <c r="H18" s="26"/>
+      <c r="I18" s="26"/>
     </row>
     <row r="19" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B19" s="4">
@@ -1211,14 +1211,14 @@
       <c r="C19" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D19" s="39" t="s">
+      <c r="D19" s="26" t="s">
         <v>23</v>
       </c>
-      <c r="E19" s="39"/>
-      <c r="F19" s="39"/>
-      <c r="G19" s="39"/>
-      <c r="H19" s="39"/>
-      <c r="I19" s="39"/>
+      <c r="E19" s="26"/>
+      <c r="F19" s="26"/>
+      <c r="G19" s="26"/>
+      <c r="H19" s="26"/>
+      <c r="I19" s="26"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B20" s="4">
@@ -1236,10 +1236,10 @@
       <c r="F20" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G20" s="39" t="s">
+      <c r="G20" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="H20" s="39"/>
+      <c r="H20" s="26"/>
       <c r="I20" s="1" t="s">
         <v>14</v>
       </c>
@@ -1355,14 +1355,14 @@
       <c r="C25" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D25" s="39" t="s">
+      <c r="D25" s="26" t="s">
         <v>26</v>
       </c>
-      <c r="E25" s="39"/>
-      <c r="F25" s="39"/>
-      <c r="G25" s="39"/>
-      <c r="H25" s="39"/>
-      <c r="I25" s="39"/>
+      <c r="E25" s="26"/>
+      <c r="F25" s="26"/>
+      <c r="G25" s="26"/>
+      <c r="H25" s="26"/>
+      <c r="I25" s="26"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B26" s="4">
@@ -1406,10 +1406,10 @@
       <c r="F27" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G27" s="39" t="s">
+      <c r="G27" s="26" t="s">
         <v>18</v>
       </c>
-      <c r="H27" s="39"/>
+      <c r="H27" s="26"/>
       <c r="I27" s="1" t="s">
         <v>14</v>
       </c>
@@ -1473,14 +1473,14 @@
       <c r="C30" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D30" s="38" t="s">
+      <c r="D30" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="E30" s="38"/>
-      <c r="F30" s="38"/>
-      <c r="G30" s="38"/>
-      <c r="H30" s="38"/>
-      <c r="I30" s="38"/>
+      <c r="E30" s="27"/>
+      <c r="F30" s="27"/>
+      <c r="G30" s="27"/>
+      <c r="H30" s="27"/>
+      <c r="I30" s="27"/>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B31" s="4">
@@ -1489,14 +1489,14 @@
       <c r="C31" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D31" s="38" t="s">
+      <c r="D31" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="E31" s="38"/>
-      <c r="F31" s="38"/>
-      <c r="G31" s="38"/>
-      <c r="H31" s="38"/>
-      <c r="I31" s="38"/>
+      <c r="E31" s="27"/>
+      <c r="F31" s="27"/>
+      <c r="G31" s="27"/>
+      <c r="H31" s="27"/>
+      <c r="I31" s="27"/>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B32" s="4">
@@ -1531,14 +1531,14 @@
       <c r="C33" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D33" s="38" t="s">
+      <c r="D33" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="E33" s="38"/>
-      <c r="F33" s="38"/>
-      <c r="G33" s="38"/>
-      <c r="H33" s="38"/>
-      <c r="I33" s="38"/>
+      <c r="E33" s="27"/>
+      <c r="F33" s="27"/>
+      <c r="G33" s="27"/>
+      <c r="H33" s="27"/>
+      <c r="I33" s="27"/>
     </row>
     <row r="34" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B34" s="4">
@@ -1582,10 +1582,10 @@
       <c r="F35" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G35" s="38" t="s">
+      <c r="G35" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="H35" s="38"/>
+      <c r="H35" s="27"/>
       <c r="I35" s="1" t="s">
         <v>14</v>
       </c>
@@ -1701,14 +1701,14 @@
       <c r="C40" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D40" s="38" t="s">
+      <c r="D40" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="E40" s="38"/>
-      <c r="F40" s="38"/>
-      <c r="G40" s="38"/>
-      <c r="H40" s="38"/>
-      <c r="I40" s="38"/>
+      <c r="E40" s="27"/>
+      <c r="F40" s="27"/>
+      <c r="G40" s="27"/>
+      <c r="H40" s="27"/>
+      <c r="I40" s="27"/>
     </row>
     <row r="41" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B41" s="4">
@@ -1752,10 +1752,10 @@
       <c r="F42" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G42" s="38" t="s">
+      <c r="G42" s="27" t="s">
         <v>28</v>
       </c>
-      <c r="H42" s="38"/>
+      <c r="H42" s="27"/>
       <c r="I42" s="1" t="s">
         <v>15</v>
       </c>
@@ -1767,14 +1767,14 @@
       <c r="C43" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D43" s="38" t="s">
+      <c r="D43" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="E43" s="38"/>
-      <c r="F43" s="38"/>
-      <c r="G43" s="38"/>
-      <c r="H43" s="38"/>
-      <c r="I43" s="38"/>
+      <c r="E43" s="27"/>
+      <c r="F43" s="27"/>
+      <c r="G43" s="27"/>
+      <c r="H43" s="27"/>
+      <c r="I43" s="27"/>
     </row>
     <row r="44" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B44" s="4">
@@ -1838,14 +1838,14 @@
       <c r="C46" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D46" s="38" t="s">
+      <c r="D46" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="E46" s="38"/>
-      <c r="F46" s="38"/>
-      <c r="G46" s="38"/>
-      <c r="H46" s="38"/>
-      <c r="I46" s="38"/>
+      <c r="E46" s="27"/>
+      <c r="F46" s="27"/>
+      <c r="G46" s="27"/>
+      <c r="H46" s="27"/>
+      <c r="I46" s="27"/>
     </row>
     <row r="47" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B47" s="4">
@@ -1854,14 +1854,14 @@
       <c r="C47" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D47" s="27" t="s">
+      <c r="D47" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E47" s="28"/>
-      <c r="F47" s="28"/>
-      <c r="G47" s="28"/>
-      <c r="H47" s="28"/>
-      <c r="I47" s="29"/>
+      <c r="E47" s="24"/>
+      <c r="F47" s="24"/>
+      <c r="G47" s="24"/>
+      <c r="H47" s="24"/>
+      <c r="I47" s="25"/>
     </row>
     <row r="48" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B48" s="4">
@@ -1905,10 +1905,10 @@
       <c r="F49" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G49" s="27" t="s">
+      <c r="G49" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="H49" s="29"/>
+      <c r="H49" s="25"/>
       <c r="I49" s="1" t="s">
         <v>30</v>
       </c>
@@ -2050,14 +2050,14 @@
       <c r="C55" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="D55" s="28" t="s">
+      <c r="D55" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="E55" s="28"/>
-      <c r="F55" s="28"/>
-      <c r="G55" s="28"/>
-      <c r="H55" s="28"/>
-      <c r="I55" s="28"/>
+      <c r="E55" s="24"/>
+      <c r="F55" s="24"/>
+      <c r="G55" s="24"/>
+      <c r="H55" s="24"/>
+      <c r="I55" s="24"/>
     </row>
     <row r="56" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B56" s="4">
@@ -2101,10 +2101,10 @@
       <c r="F57" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G57" s="27" t="s">
+      <c r="G57" s="23" t="s">
         <v>37</v>
       </c>
-      <c r="H57" s="29"/>
+      <c r="H57" s="25"/>
       <c r="I57" s="1" t="s">
         <v>36</v>
       </c>
@@ -2168,14 +2168,14 @@
       <c r="C60" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D60" s="27" t="s">
+      <c r="D60" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E60" s="28"/>
-      <c r="F60" s="28"/>
-      <c r="G60" s="28"/>
-      <c r="H60" s="28"/>
-      <c r="I60" s="29"/>
+      <c r="E60" s="24"/>
+      <c r="F60" s="24"/>
+      <c r="G60" s="24"/>
+      <c r="H60" s="24"/>
+      <c r="I60" s="25"/>
     </row>
     <row r="61" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B61" s="4">
@@ -2184,14 +2184,14 @@
       <c r="C61" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D61" s="27" t="s">
+      <c r="D61" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E61" s="28"/>
-      <c r="F61" s="28"/>
-      <c r="G61" s="28"/>
-      <c r="H61" s="28"/>
-      <c r="I61" s="29"/>
+      <c r="E61" s="24"/>
+      <c r="F61" s="24"/>
+      <c r="G61" s="24"/>
+      <c r="H61" s="24"/>
+      <c r="I61" s="25"/>
     </row>
     <row r="62" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B62" s="4">
@@ -2200,14 +2200,14 @@
       <c r="C62" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D62" s="27" t="s">
+      <c r="D62" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E62" s="28"/>
-      <c r="F62" s="28"/>
-      <c r="G62" s="28"/>
-      <c r="H62" s="28"/>
-      <c r="I62" s="29"/>
+      <c r="E62" s="24"/>
+      <c r="F62" s="24"/>
+      <c r="G62" s="24"/>
+      <c r="H62" s="24"/>
+      <c r="I62" s="25"/>
     </row>
     <row r="63" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B63" s="4">
@@ -2251,10 +2251,10 @@
       <c r="F64" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G64" s="27" t="s">
+      <c r="G64" s="23" t="s">
         <v>37</v>
       </c>
-      <c r="H64" s="29"/>
+      <c r="H64" s="25"/>
       <c r="I64" s="1" t="s">
         <v>14</v>
       </c>
@@ -2292,13 +2292,13 @@
       <c r="C66" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D66" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="E66" s="28"/>
-      <c r="F66" s="28"/>
-      <c r="G66" s="28"/>
-      <c r="H66" s="29"/>
+      <c r="D66" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="E66" s="24"/>
+      <c r="F66" s="24"/>
+      <c r="G66" s="24"/>
+      <c r="H66" s="25"/>
       <c r="I66" s="1" t="s">
         <v>16</v>
       </c>
@@ -2310,18 +2310,18 @@
       <c r="C67" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D67" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="E67" s="28"/>
-      <c r="F67" s="29"/>
+      <c r="D67" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="E67" s="24"/>
+      <c r="F67" s="25"/>
       <c r="G67" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="H67" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="I67" s="29"/>
+      <c r="H67" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="I67" s="25"/>
     </row>
     <row r="68" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B68" s="4">
@@ -2336,12 +2336,12 @@
       <c r="E68" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F68" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="G68" s="28"/>
-      <c r="H68" s="28"/>
-      <c r="I68" s="29"/>
+      <c r="F68" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="G68" s="24"/>
+      <c r="H68" s="24"/>
+      <c r="I68" s="25"/>
     </row>
     <row r="69" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B69" s="4">
@@ -2350,14 +2350,14 @@
       <c r="C69" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D69" s="27" t="s">
+      <c r="D69" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E69" s="28"/>
-      <c r="F69" s="28"/>
-      <c r="G69" s="28"/>
-      <c r="H69" s="28"/>
-      <c r="I69" s="29"/>
+      <c r="E69" s="24"/>
+      <c r="F69" s="24"/>
+      <c r="G69" s="24"/>
+      <c r="H69" s="24"/>
+      <c r="I69" s="25"/>
     </row>
     <row r="70" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B70" s="4">
@@ -2366,10 +2366,10 @@
       <c r="C70" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D70" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="E70" s="29"/>
+      <c r="D70" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="E70" s="25"/>
       <c r="F70" s="3" t="s">
         <v>15</v>
       </c>
@@ -2399,10 +2399,10 @@
       <c r="F71" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G71" s="27" t="s">
+      <c r="G71" s="23" t="s">
         <v>37</v>
       </c>
-      <c r="H71" s="29"/>
+      <c r="H71" s="25"/>
       <c r="I71" s="1" t="s">
         <v>14</v>
       </c>
@@ -2440,14 +2440,14 @@
       <c r="C73" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D73" s="27" t="s">
+      <c r="D73" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E73" s="28"/>
-      <c r="F73" s="28"/>
-      <c r="G73" s="28"/>
-      <c r="H73" s="28"/>
-      <c r="I73" s="29"/>
+      <c r="E73" s="24"/>
+      <c r="F73" s="24"/>
+      <c r="G73" s="24"/>
+      <c r="H73" s="24"/>
+      <c r="I73" s="25"/>
     </row>
     <row r="74" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B74" s="4">
@@ -2456,11 +2456,11 @@
       <c r="C74" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D74" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="E74" s="28"/>
-      <c r="F74" s="29"/>
+      <c r="D74" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="E74" s="24"/>
+      <c r="F74" s="25"/>
       <c r="G74" s="3" t="s">
         <v>16</v>
       </c>
@@ -2496,14 +2496,14 @@
       <c r="C76" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D76" s="27" t="s">
+      <c r="D76" s="23" t="s">
         <v>39</v>
       </c>
-      <c r="E76" s="28"/>
-      <c r="F76" s="28"/>
-      <c r="G76" s="28"/>
-      <c r="H76" s="28"/>
-      <c r="I76" s="29"/>
+      <c r="E76" s="24"/>
+      <c r="F76" s="24"/>
+      <c r="G76" s="24"/>
+      <c r="H76" s="24"/>
+      <c r="I76" s="25"/>
     </row>
     <row r="77" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B77" s="4">
@@ -2512,14 +2512,14 @@
       <c r="C77" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D77" s="27" t="s">
+      <c r="D77" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E77" s="28"/>
-      <c r="F77" s="28"/>
-      <c r="G77" s="28"/>
-      <c r="H77" s="28"/>
-      <c r="I77" s="29"/>
+      <c r="E77" s="24"/>
+      <c r="F77" s="24"/>
+      <c r="G77" s="24"/>
+      <c r="H77" s="24"/>
+      <c r="I77" s="25"/>
     </row>
     <row r="78" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B78" s="4">
@@ -2528,14 +2528,14 @@
       <c r="C78" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D78" s="27" t="s">
+      <c r="D78" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E78" s="28"/>
-      <c r="F78" s="28"/>
-      <c r="G78" s="28"/>
-      <c r="H78" s="28"/>
-      <c r="I78" s="29"/>
+      <c r="E78" s="24"/>
+      <c r="F78" s="24"/>
+      <c r="G78" s="24"/>
+      <c r="H78" s="24"/>
+      <c r="I78" s="25"/>
     </row>
     <row r="79" spans="2:9" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B79" s="16" t="s">
@@ -2579,10 +2579,10 @@
       <c r="F80" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G80" s="27" t="s">
+      <c r="G80" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="H80" s="29"/>
+      <c r="H80" s="25"/>
       <c r="I80" s="1" t="s">
         <v>14</v>
       </c>
@@ -2603,10 +2603,10 @@
       <c r="F81" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="G81" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="H81" s="29"/>
+      <c r="G81" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="H81" s="25"/>
       <c r="I81" s="1" t="s">
         <v>16</v>
       </c>
@@ -2670,14 +2670,14 @@
       <c r="C84" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D84" s="27" t="s">
+      <c r="D84" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E84" s="28"/>
-      <c r="F84" s="28"/>
-      <c r="G84" s="28"/>
-      <c r="H84" s="28"/>
-      <c r="I84" s="29"/>
+      <c r="E84" s="24"/>
+      <c r="F84" s="24"/>
+      <c r="G84" s="24"/>
+      <c r="H84" s="24"/>
+      <c r="I84" s="25"/>
     </row>
     <row r="85" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B85" s="4">
@@ -2715,11 +2715,11 @@
       <c r="D86" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="E86" s="27" t="s">
+      <c r="E86" s="23" t="s">
         <v>43</v>
       </c>
-      <c r="F86" s="28"/>
-      <c r="G86" s="29"/>
+      <c r="F86" s="24"/>
+      <c r="G86" s="25"/>
       <c r="H86" s="3" t="s">
         <v>14</v>
       </c>
@@ -2734,18 +2734,18 @@
       <c r="C87" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D87" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="E87" s="29"/>
+      <c r="D87" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="E87" s="25"/>
       <c r="F87" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G87" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="H87" s="28"/>
-      <c r="I87" s="29"/>
+      <c r="G87" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="H87" s="24"/>
+      <c r="I87" s="25"/>
     </row>
     <row r="88" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B88" s="4">
@@ -2754,14 +2754,14 @@
       <c r="C88" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D88" s="27" t="s">
+      <c r="D88" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E88" s="28"/>
-      <c r="F88" s="28"/>
-      <c r="G88" s="28"/>
-      <c r="H88" s="28"/>
-      <c r="I88" s="29"/>
+      <c r="E88" s="24"/>
+      <c r="F88" s="24"/>
+      <c r="G88" s="24"/>
+      <c r="H88" s="24"/>
+      <c r="I88" s="25"/>
     </row>
     <row r="89" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B89" s="4">
@@ -2770,18 +2770,18 @@
       <c r="C89" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D89" s="27" t="s">
+      <c r="D89" s="23" t="s">
         <v>44</v>
       </c>
-      <c r="E89" s="28"/>
-      <c r="F89" s="29"/>
+      <c r="E89" s="24"/>
+      <c r="F89" s="25"/>
       <c r="G89" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="H89" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="I89" s="29"/>
+      <c r="H89" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="I89" s="25"/>
     </row>
     <row r="90" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B90" s="4">
@@ -2790,10 +2790,10 @@
       <c r="C90" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D90" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="E90" s="29"/>
+      <c r="D90" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="E90" s="25"/>
       <c r="F90" s="3" t="s">
         <v>16</v>
       </c>
@@ -2815,13 +2815,13 @@
       <c r="C91" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D91" s="27" t="s">
+      <c r="D91" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E91" s="28"/>
-      <c r="F91" s="28"/>
-      <c r="G91" s="28"/>
-      <c r="H91" s="29"/>
+      <c r="E91" s="24"/>
+      <c r="F91" s="24"/>
+      <c r="G91" s="24"/>
+      <c r="H91" s="25"/>
       <c r="I91" s="18" t="s">
         <v>45</v>
       </c>
@@ -2833,14 +2833,14 @@
       <c r="C92" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D92" s="27" t="s">
+      <c r="D92" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E92" s="28"/>
-      <c r="F92" s="28"/>
-      <c r="G92" s="28"/>
-      <c r="H92" s="28"/>
-      <c r="I92" s="29"/>
+      <c r="E92" s="24"/>
+      <c r="F92" s="24"/>
+      <c r="G92" s="24"/>
+      <c r="H92" s="24"/>
+      <c r="I92" s="25"/>
     </row>
     <row r="93" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B93" s="4">
@@ -2849,14 +2849,14 @@
       <c r="C93" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D93" s="27" t="s">
+      <c r="D93" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="E93" s="28"/>
-      <c r="F93" s="28"/>
-      <c r="G93" s="28"/>
-      <c r="H93" s="28"/>
-      <c r="I93" s="29"/>
+      <c r="E93" s="24"/>
+      <c r="F93" s="24"/>
+      <c r="G93" s="24"/>
+      <c r="H93" s="24"/>
+      <c r="I93" s="25"/>
     </row>
     <row r="94" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B94" s="4">
@@ -2865,14 +2865,14 @@
       <c r="C94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D94" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="E94" s="28"/>
-      <c r="F94" s="28"/>
-      <c r="G94" s="28"/>
-      <c r="H94" s="28"/>
-      <c r="I94" s="29"/>
+      <c r="D94" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="E94" s="24"/>
+      <c r="F94" s="24"/>
+      <c r="G94" s="24"/>
+      <c r="H94" s="24"/>
+      <c r="I94" s="25"/>
     </row>
     <row r="95" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B95" s="4">
@@ -2881,15 +2881,15 @@
       <c r="C95" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D95" s="27" t="s">
+      <c r="D95" s="23" t="s">
         <v>47</v>
       </c>
-      <c r="E95" s="28"/>
-      <c r="F95" s="29"/>
-      <c r="G95" s="27" t="s">
+      <c r="E95" s="24"/>
+      <c r="F95" s="25"/>
+      <c r="G95" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="H95" s="29"/>
+      <c r="H95" s="25"/>
       <c r="I95" s="1" t="s">
         <v>14</v>
       </c>
@@ -2901,14 +2901,14 @@
       <c r="C96" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D96" s="27" t="s">
+      <c r="D96" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E96" s="28"/>
-      <c r="F96" s="28"/>
-      <c r="G96" s="28"/>
-      <c r="H96" s="28"/>
-      <c r="I96" s="29"/>
+      <c r="E96" s="24"/>
+      <c r="F96" s="24"/>
+      <c r="G96" s="24"/>
+      <c r="H96" s="24"/>
+      <c r="I96" s="25"/>
     </row>
     <row r="97" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B97" s="4">
@@ -2917,14 +2917,14 @@
       <c r="C97" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D97" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="E97" s="28"/>
-      <c r="F97" s="28"/>
-      <c r="G97" s="28"/>
-      <c r="H97" s="28"/>
-      <c r="I97" s="29"/>
+      <c r="D97" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="E97" s="24"/>
+      <c r="F97" s="24"/>
+      <c r="G97" s="24"/>
+      <c r="H97" s="24"/>
+      <c r="I97" s="25"/>
     </row>
     <row r="98" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B98" s="4">
@@ -2933,14 +2933,14 @@
       <c r="C98" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D98" s="27" t="s">
+      <c r="D98" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E98" s="28"/>
-      <c r="F98" s="28"/>
-      <c r="G98" s="28"/>
-      <c r="H98" s="28"/>
-      <c r="I98" s="29"/>
+      <c r="E98" s="24"/>
+      <c r="F98" s="24"/>
+      <c r="G98" s="24"/>
+      <c r="H98" s="24"/>
+      <c r="I98" s="25"/>
     </row>
     <row r="99" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B99" s="4">
@@ -2949,12 +2949,12 @@
       <c r="C99" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D99" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="E99" s="28"/>
-      <c r="F99" s="28"/>
-      <c r="G99" s="29"/>
+      <c r="D99" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="E99" s="24"/>
+      <c r="F99" s="24"/>
+      <c r="G99" s="25"/>
       <c r="H99" s="3" t="s">
         <v>49</v>
       </c>
@@ -2978,21 +2978,21 @@
       <c r="F100" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="G100" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="H100" s="28"/>
-      <c r="I100" s="29"/>
+      <c r="G100" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="H100" s="24"/>
+      <c r="I100" s="25"/>
     </row>
     <row r="101" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B101" s="27"/>
-      <c r="C101" s="28"/>
-      <c r="D101" s="28"/>
-      <c r="E101" s="28"/>
-      <c r="F101" s="28"/>
-      <c r="G101" s="28"/>
-      <c r="H101" s="28"/>
-      <c r="I101" s="29"/>
+      <c r="B101" s="23"/>
+      <c r="C101" s="24"/>
+      <c r="D101" s="24"/>
+      <c r="E101" s="24"/>
+      <c r="F101" s="24"/>
+      <c r="G101" s="24"/>
+      <c r="H101" s="24"/>
+      <c r="I101" s="25"/>
     </row>
     <row r="102" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B102" s="3"/>
@@ -3011,10 +3011,10 @@
       <c r="C103" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D103" s="27" t="s">
+      <c r="D103" s="23" t="s">
         <v>51</v>
       </c>
-      <c r="E103" s="29"/>
+      <c r="E103" s="25"/>
       <c r="F103" s="3"/>
       <c r="G103" s="3"/>
       <c r="H103" s="3"/>
@@ -3027,10 +3027,10 @@
       <c r="C104" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D104" s="27" t="s">
+      <c r="D104" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="E104" s="29"/>
+      <c r="E104" s="25"/>
       <c r="F104" s="3"/>
       <c r="G104" s="3"/>
       <c r="H104" s="3"/>
@@ -3043,10 +3043,10 @@
       <c r="C105" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D105" s="27" t="s">
+      <c r="D105" s="23" t="s">
         <v>53</v>
       </c>
-      <c r="E105" s="29"/>
+      <c r="E105" s="25"/>
       <c r="F105" s="3"/>
       <c r="G105" s="3"/>
       <c r="H105" s="3"/>
@@ -3059,10 +3059,10 @@
       <c r="C106" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D106" s="27" t="s">
+      <c r="D106" s="23" t="s">
         <v>54</v>
       </c>
-      <c r="E106" s="29"/>
+      <c r="E106" s="25"/>
       <c r="F106" s="3"/>
       <c r="G106" s="3"/>
       <c r="H106" s="3"/>
@@ -3075,10 +3075,10 @@
       <c r="C107" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D107" s="27" t="s">
+      <c r="D107" s="23" t="s">
         <v>55</v>
       </c>
-      <c r="E107" s="29"/>
+      <c r="E107" s="25"/>
       <c r="F107" s="3"/>
       <c r="G107" s="3"/>
       <c r="H107" s="3"/>
@@ -3091,10 +3091,10 @@
       <c r="C108" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D108" s="27" t="s">
+      <c r="D108" s="23" t="s">
         <v>56</v>
       </c>
-      <c r="E108" s="29"/>
+      <c r="E108" s="25"/>
       <c r="F108" s="3"/>
       <c r="G108" s="3"/>
       <c r="H108" s="3"/>
@@ -3131,28 +3131,28 @@
       <c r="I111" s="20"/>
     </row>
     <row r="112" spans="2:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B112" s="32" t="s">
+      <c r="B112" s="34" t="s">
         <v>57</v>
       </c>
-      <c r="C112" s="33"/>
-      <c r="D112" s="33"/>
-      <c r="E112" s="33"/>
-      <c r="F112" s="33"/>
-      <c r="G112" s="33"/>
-      <c r="H112" s="33"/>
-      <c r="I112" s="33"/>
-      <c r="J112" s="34"/>
+      <c r="C112" s="35"/>
+      <c r="D112" s="35"/>
+      <c r="E112" s="35"/>
+      <c r="F112" s="35"/>
+      <c r="G112" s="35"/>
+      <c r="H112" s="35"/>
+      <c r="I112" s="35"/>
+      <c r="J112" s="36"/>
     </row>
     <row r="113" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B113" s="35"/>
-      <c r="C113" s="36"/>
-      <c r="D113" s="36"/>
-      <c r="E113" s="36"/>
-      <c r="F113" s="36"/>
-      <c r="G113" s="36"/>
-      <c r="H113" s="36"/>
-      <c r="I113" s="36"/>
-      <c r="J113" s="37"/>
+      <c r="B113" s="37"/>
+      <c r="C113" s="38"/>
+      <c r="D113" s="38"/>
+      <c r="E113" s="38"/>
+      <c r="F113" s="38"/>
+      <c r="G113" s="38"/>
+      <c r="H113" s="38"/>
+      <c r="I113" s="38"/>
+      <c r="J113" s="39"/>
     </row>
     <row r="114" spans="2:10" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B114" s="8" t="s">
@@ -3283,13 +3283,13 @@
       <c r="E118" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="F118" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="G118" s="28"/>
-      <c r="H118" s="28"/>
-      <c r="I118" s="28"/>
-      <c r="J118" s="29"/>
+      <c r="F118" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="G118" s="24"/>
+      <c r="H118" s="24"/>
+      <c r="I118" s="24"/>
+      <c r="J118" s="25"/>
     </row>
     <row r="119" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B119" s="4">
@@ -3327,13 +3327,13 @@
       <c r="C120" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D120" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="E120" s="28"/>
-      <c r="F120" s="28"/>
-      <c r="G120" s="28"/>
-      <c r="H120" s="29"/>
+      <c r="D120" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="E120" s="24"/>
+      <c r="F120" s="24"/>
+      <c r="G120" s="24"/>
+      <c r="H120" s="25"/>
       <c r="I120" s="1" t="s">
         <v>16</v>
       </c>
@@ -3348,15 +3348,15 @@
       <c r="C121" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D121" s="27" t="s">
+      <c r="D121" s="23" t="s">
         <v>65</v>
       </c>
-      <c r="E121" s="28"/>
-      <c r="F121" s="28"/>
-      <c r="G121" s="28"/>
-      <c r="H121" s="28"/>
-      <c r="I121" s="28"/>
-      <c r="J121" s="29"/>
+      <c r="E121" s="24"/>
+      <c r="F121" s="24"/>
+      <c r="G121" s="24"/>
+      <c r="H121" s="24"/>
+      <c r="I121" s="24"/>
+      <c r="J121" s="25"/>
     </row>
     <row r="122" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B122" s="4">
@@ -3403,12 +3403,12 @@
       <c r="F123" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="G123" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="H123" s="28"/>
-      <c r="I123" s="28"/>
-      <c r="J123" s="29"/>
+      <c r="G123" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="H123" s="24"/>
+      <c r="I123" s="24"/>
+      <c r="J123" s="25"/>
     </row>
     <row r="124" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B124" s="4">
@@ -3426,12 +3426,12 @@
       <c r="F124" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="G124" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="H124" s="28"/>
-      <c r="I124" s="28"/>
-      <c r="J124" s="29"/>
+      <c r="G124" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="H124" s="24"/>
+      <c r="I124" s="24"/>
+      <c r="J124" s="25"/>
     </row>
     <row r="125" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B125" s="4">
@@ -3446,13 +3446,13 @@
       <c r="E125" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="F125" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="G125" s="28"/>
-      <c r="H125" s="28"/>
-      <c r="I125" s="28"/>
-      <c r="J125" s="29"/>
+      <c r="F125" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="G125" s="24"/>
+      <c r="H125" s="24"/>
+      <c r="I125" s="24"/>
+      <c r="J125" s="25"/>
     </row>
     <row r="126" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B126" s="4">
@@ -3470,11 +3470,11 @@
       <c r="F126" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="G126" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="H126" s="28"/>
-      <c r="I126" s="29"/>
+      <c r="G126" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="H126" s="24"/>
+      <c r="I126" s="25"/>
       <c r="J126" s="1" t="s">
         <v>16</v>
       </c>
@@ -3492,13 +3492,13 @@
       <c r="E127" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="F127" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="G127" s="28"/>
-      <c r="H127" s="28"/>
-      <c r="I127" s="28"/>
-      <c r="J127" s="29"/>
+      <c r="F127" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="G127" s="24"/>
+      <c r="H127" s="24"/>
+      <c r="I127" s="24"/>
+      <c r="J127" s="25"/>
     </row>
     <row r="128" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B128" s="4">
@@ -3507,15 +3507,15 @@
       <c r="C128" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D128" s="27" t="s">
+      <c r="D128" s="23" t="s">
         <v>65</v>
       </c>
-      <c r="E128" s="28"/>
-      <c r="F128" s="28"/>
-      <c r="G128" s="28"/>
-      <c r="H128" s="28"/>
-      <c r="I128" s="28"/>
-      <c r="J128" s="29"/>
+      <c r="E128" s="24"/>
+      <c r="F128" s="24"/>
+      <c r="G128" s="24"/>
+      <c r="H128" s="24"/>
+      <c r="I128" s="24"/>
+      <c r="J128" s="25"/>
     </row>
     <row r="129" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B129" s="4">
@@ -3698,15 +3698,15 @@
       <c r="C135" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D135" s="27" t="s">
+      <c r="D135" s="23" t="s">
         <v>65</v>
       </c>
-      <c r="E135" s="28"/>
-      <c r="F135" s="28"/>
-      <c r="G135" s="28"/>
-      <c r="H135" s="28"/>
-      <c r="I135" s="28"/>
-      <c r="J135" s="29"/>
+      <c r="E135" s="24"/>
+      <c r="F135" s="24"/>
+      <c r="G135" s="24"/>
+      <c r="H135" s="24"/>
+      <c r="I135" s="24"/>
+      <c r="J135" s="25"/>
     </row>
     <row r="136" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B136" s="4">
@@ -3918,15 +3918,15 @@
       <c r="C143" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D143" s="27" t="s">
+      <c r="D143" s="23" t="s">
         <v>65</v>
       </c>
-      <c r="E143" s="28"/>
-      <c r="F143" s="28"/>
-      <c r="G143" s="28"/>
-      <c r="H143" s="28"/>
-      <c r="I143" s="28"/>
-      <c r="J143" s="29"/>
+      <c r="E143" s="24"/>
+      <c r="F143" s="24"/>
+      <c r="G143" s="24"/>
+      <c r="H143" s="24"/>
+      <c r="I143" s="24"/>
+      <c r="J143" s="25"/>
     </row>
     <row r="144" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B144" s="4">
@@ -4002,12 +4002,12 @@
       <c r="F146" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="G146" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="H146" s="28"/>
-      <c r="I146" s="28"/>
-      <c r="J146" s="29"/>
+      <c r="G146" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="H146" s="24"/>
+      <c r="I146" s="24"/>
+      <c r="J146" s="25"/>
     </row>
     <row r="147" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B147" s="4">
@@ -4074,14 +4074,14 @@
       <c r="C149" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D149" s="23" t="s">
+      <c r="D149" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="E149" s="24"/>
-      <c r="F149" s="24"/>
-      <c r="G149" s="24"/>
-      <c r="H149" s="24"/>
-      <c r="I149" s="24"/>
+      <c r="E149" s="29"/>
+      <c r="F149" s="29"/>
+      <c r="G149" s="29"/>
+      <c r="H149" s="29"/>
+      <c r="I149" s="29"/>
       <c r="J149" s="30"/>
     </row>
     <row r="150" spans="2:10" x14ac:dyDescent="0.3">
@@ -4091,13 +4091,13 @@
       <c r="C150" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D150" s="25"/>
-      <c r="E150" s="26"/>
-      <c r="F150" s="26"/>
-      <c r="G150" s="26"/>
-      <c r="H150" s="26"/>
-      <c r="I150" s="26"/>
-      <c r="J150" s="31"/>
+      <c r="D150" s="31"/>
+      <c r="E150" s="32"/>
+      <c r="F150" s="32"/>
+      <c r="G150" s="32"/>
+      <c r="H150" s="32"/>
+      <c r="I150" s="32"/>
+      <c r="J150" s="33"/>
     </row>
     <row r="151" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B151" s="4">
@@ -4144,11 +4144,11 @@
       <c r="F152" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="G152" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="H152" s="28"/>
-      <c r="I152" s="29"/>
+      <c r="G152" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="H152" s="24"/>
+      <c r="I152" s="25"/>
       <c r="J152" s="1" t="s">
         <v>69</v>
       </c>
@@ -4276,15 +4276,15 @@
       <c r="C157" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D157" s="27" t="s">
+      <c r="D157" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E157" s="28"/>
-      <c r="F157" s="28"/>
-      <c r="G157" s="28"/>
-      <c r="H157" s="28"/>
-      <c r="I157" s="28"/>
-      <c r="J157" s="29"/>
+      <c r="E157" s="24"/>
+      <c r="F157" s="24"/>
+      <c r="G157" s="24"/>
+      <c r="H157" s="24"/>
+      <c r="I157" s="24"/>
+      <c r="J157" s="25"/>
     </row>
     <row r="158" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B158" s="4">
@@ -4465,15 +4465,15 @@
       <c r="C164" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D164" s="27" t="s">
+      <c r="D164" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E164" s="28"/>
-      <c r="F164" s="28"/>
-      <c r="G164" s="28"/>
-      <c r="H164" s="28"/>
-      <c r="I164" s="28"/>
-      <c r="J164" s="29"/>
+      <c r="E164" s="24"/>
+      <c r="F164" s="24"/>
+      <c r="G164" s="24"/>
+      <c r="H164" s="24"/>
+      <c r="I164" s="24"/>
+      <c r="J164" s="25"/>
     </row>
     <row r="165" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B165" s="4">
@@ -4671,15 +4671,15 @@
       <c r="C172" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D172" s="27" t="s">
+      <c r="D172" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E172" s="28"/>
-      <c r="F172" s="28"/>
-      <c r="G172" s="28"/>
-      <c r="H172" s="28"/>
-      <c r="I172" s="28"/>
-      <c r="J172" s="29"/>
+      <c r="E172" s="24"/>
+      <c r="F172" s="24"/>
+      <c r="G172" s="24"/>
+      <c r="H172" s="24"/>
+      <c r="I172" s="24"/>
+      <c r="J172" s="25"/>
     </row>
     <row r="173" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B173" s="4">
@@ -4743,55 +4743,73 @@
       <c r="B175" s="4">
         <v>45903</v>
       </c>
-      <c r="C175" s="23" t="s">
+      <c r="C175" s="28" t="s">
         <v>39</v>
       </c>
-      <c r="D175" s="24"/>
-      <c r="E175" s="24"/>
-      <c r="F175" s="24"/>
-      <c r="G175" s="24"/>
-      <c r="H175" s="24"/>
-      <c r="I175" s="24"/>
-      <c r="J175" s="24"/>
+      <c r="D175" s="29"/>
+      <c r="E175" s="29"/>
+      <c r="F175" s="29"/>
+      <c r="G175" s="29"/>
+      <c r="H175" s="29"/>
+      <c r="I175" s="29"/>
+      <c r="J175" s="29"/>
     </row>
     <row r="176" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B176" s="4">
         <v>45904</v>
       </c>
-      <c r="C176" s="25"/>
-      <c r="D176" s="26"/>
-      <c r="E176" s="26"/>
-      <c r="F176" s="26"/>
-      <c r="G176" s="26"/>
-      <c r="H176" s="26"/>
-      <c r="I176" s="26"/>
-      <c r="J176" s="26"/>
+      <c r="C176" s="31"/>
+      <c r="D176" s="32"/>
+      <c r="E176" s="32"/>
+      <c r="F176" s="32"/>
+      <c r="G176" s="32"/>
+      <c r="H176" s="32"/>
+      <c r="I176" s="32"/>
+      <c r="J176" s="32"/>
     </row>
     <row r="177" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B177" s="4">
         <v>45905</v>
       </c>
-      <c r="C177" s="27" t="s">
+      <c r="C177" s="23" t="s">
         <v>39</v>
       </c>
-      <c r="D177" s="28"/>
-      <c r="E177" s="28"/>
-      <c r="F177" s="28"/>
-      <c r="G177" s="28"/>
-      <c r="H177" s="28"/>
-      <c r="I177" s="28"/>
-      <c r="J177" s="29"/>
+      <c r="D177" s="24"/>
+      <c r="E177" s="24"/>
+      <c r="F177" s="24"/>
+      <c r="G177" s="24"/>
+      <c r="H177" s="24"/>
+      <c r="I177" s="24"/>
+      <c r="J177" s="25"/>
     </row>
     <row r="178" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B178" s="3"/>
-      <c r="C178" s="3"/>
-      <c r="D178" s="3"/>
-      <c r="E178" s="3"/>
-      <c r="F178" s="3"/>
-      <c r="G178" s="3"/>
-      <c r="H178" s="3"/>
-      <c r="I178" s="1"/>
-      <c r="J178" s="1"/>
+      <c r="B178" s="4">
+        <v>45906</v>
+      </c>
+      <c r="C178" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D178" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E178" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F178" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G178" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H178" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I178" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="J178" s="1" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="179" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B179" s="3"/>
@@ -7413,22 +7431,56 @@
     </row>
   </sheetData>
   <mergeCells count="87">
-    <mergeCell ref="C177:J177"/>
-    <mergeCell ref="D106:E106"/>
-    <mergeCell ref="D99:G99"/>
-    <mergeCell ref="G126:I126"/>
-    <mergeCell ref="F125:J125"/>
-    <mergeCell ref="D128:J128"/>
-    <mergeCell ref="D103:E103"/>
-    <mergeCell ref="D104:E104"/>
-    <mergeCell ref="D105:E105"/>
-    <mergeCell ref="G100:I100"/>
-    <mergeCell ref="B101:I101"/>
-    <mergeCell ref="D98:I98"/>
-    <mergeCell ref="D94:I94"/>
-    <mergeCell ref="H89:I89"/>
-    <mergeCell ref="D89:F89"/>
-    <mergeCell ref="D97:I97"/>
+    <mergeCell ref="C175:J176"/>
+    <mergeCell ref="D164:J164"/>
+    <mergeCell ref="D157:J157"/>
+    <mergeCell ref="D143:J143"/>
+    <mergeCell ref="D135:J135"/>
+    <mergeCell ref="D172:J172"/>
+    <mergeCell ref="G146:J146"/>
+    <mergeCell ref="D108:E108"/>
+    <mergeCell ref="B112:J113"/>
+    <mergeCell ref="G124:J124"/>
+    <mergeCell ref="D120:H120"/>
+    <mergeCell ref="G123:J123"/>
+    <mergeCell ref="D121:J121"/>
+    <mergeCell ref="D31:I31"/>
+    <mergeCell ref="G35:H35"/>
+    <mergeCell ref="D40:I40"/>
+    <mergeCell ref="D33:I33"/>
+    <mergeCell ref="D46:I46"/>
+    <mergeCell ref="D43:I43"/>
+    <mergeCell ref="D78:I78"/>
+    <mergeCell ref="G71:H71"/>
+    <mergeCell ref="D76:I76"/>
+    <mergeCell ref="D66:H66"/>
+    <mergeCell ref="D77:I77"/>
+    <mergeCell ref="D73:I73"/>
+    <mergeCell ref="D70:E70"/>
+    <mergeCell ref="D74:F74"/>
+    <mergeCell ref="D84:I84"/>
+    <mergeCell ref="D69:I69"/>
+    <mergeCell ref="D8:I8"/>
+    <mergeCell ref="D9:I9"/>
+    <mergeCell ref="D10:I10"/>
+    <mergeCell ref="D11:I11"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="D14:I14"/>
+    <mergeCell ref="G27:H27"/>
+    <mergeCell ref="D25:I25"/>
+    <mergeCell ref="G20:H20"/>
+    <mergeCell ref="D19:I19"/>
+    <mergeCell ref="D18:I18"/>
+    <mergeCell ref="D30:I30"/>
+    <mergeCell ref="G80:H80"/>
+    <mergeCell ref="G42:H42"/>
+    <mergeCell ref="D60:I60"/>
+    <mergeCell ref="D62:I62"/>
+    <mergeCell ref="D61:I61"/>
+    <mergeCell ref="G49:H49"/>
+    <mergeCell ref="D47:I47"/>
+    <mergeCell ref="D55:I55"/>
+    <mergeCell ref="G57:H57"/>
     <mergeCell ref="G64:H64"/>
     <mergeCell ref="D96:I96"/>
     <mergeCell ref="D95:F95"/>
@@ -7445,61 +7497,27 @@
     <mergeCell ref="F68:I68"/>
     <mergeCell ref="D87:E87"/>
     <mergeCell ref="G87:I87"/>
-    <mergeCell ref="D60:I60"/>
-    <mergeCell ref="D62:I62"/>
-    <mergeCell ref="D61:I61"/>
-    <mergeCell ref="G49:H49"/>
-    <mergeCell ref="D47:I47"/>
-    <mergeCell ref="D55:I55"/>
-    <mergeCell ref="G57:H57"/>
-    <mergeCell ref="D84:I84"/>
-    <mergeCell ref="D69:I69"/>
-    <mergeCell ref="D8:I8"/>
-    <mergeCell ref="D9:I9"/>
-    <mergeCell ref="D10:I10"/>
-    <mergeCell ref="D11:I11"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="D14:I14"/>
-    <mergeCell ref="G27:H27"/>
-    <mergeCell ref="D25:I25"/>
-    <mergeCell ref="G20:H20"/>
-    <mergeCell ref="D19:I19"/>
-    <mergeCell ref="D18:I18"/>
-    <mergeCell ref="D30:I30"/>
-    <mergeCell ref="G80:H80"/>
-    <mergeCell ref="G42:H42"/>
-    <mergeCell ref="D78:I78"/>
-    <mergeCell ref="G71:H71"/>
-    <mergeCell ref="D76:I76"/>
-    <mergeCell ref="D66:H66"/>
-    <mergeCell ref="D77:I77"/>
-    <mergeCell ref="D73:I73"/>
-    <mergeCell ref="D70:E70"/>
-    <mergeCell ref="D74:F74"/>
-    <mergeCell ref="D31:I31"/>
-    <mergeCell ref="G35:H35"/>
-    <mergeCell ref="D40:I40"/>
-    <mergeCell ref="D33:I33"/>
-    <mergeCell ref="D46:I46"/>
-    <mergeCell ref="D43:I43"/>
+    <mergeCell ref="D98:I98"/>
+    <mergeCell ref="D94:I94"/>
+    <mergeCell ref="H89:I89"/>
+    <mergeCell ref="D89:F89"/>
+    <mergeCell ref="D97:I97"/>
+    <mergeCell ref="C177:J177"/>
+    <mergeCell ref="D106:E106"/>
+    <mergeCell ref="D99:G99"/>
+    <mergeCell ref="G126:I126"/>
+    <mergeCell ref="F125:J125"/>
+    <mergeCell ref="D128:J128"/>
+    <mergeCell ref="D103:E103"/>
+    <mergeCell ref="D104:E104"/>
+    <mergeCell ref="D105:E105"/>
+    <mergeCell ref="G100:I100"/>
+    <mergeCell ref="B101:I101"/>
     <mergeCell ref="F127:J127"/>
     <mergeCell ref="D107:E107"/>
     <mergeCell ref="F118:J118"/>
     <mergeCell ref="G152:I152"/>
     <mergeCell ref="D149:J150"/>
-    <mergeCell ref="G146:J146"/>
-    <mergeCell ref="D108:E108"/>
-    <mergeCell ref="B112:J113"/>
-    <mergeCell ref="G124:J124"/>
-    <mergeCell ref="D120:H120"/>
-    <mergeCell ref="G123:J123"/>
-    <mergeCell ref="D121:J121"/>
-    <mergeCell ref="C175:J176"/>
-    <mergeCell ref="D164:J164"/>
-    <mergeCell ref="D157:J157"/>
-    <mergeCell ref="D143:J143"/>
-    <mergeCell ref="D135:J135"/>
-    <mergeCell ref="D172:J172"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/attendance_sheet.xlsx
+++ b/attendance_sheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\repositary\3rd_Year_5th_Semester\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EC85645-1345-43A8-A07C-3B5CE7F3FFD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{135F12EB-C0C7-443B-97AA-D793DF977AAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{EB654061-A886-47D1-BF86-9B1A84FCE7FB}"/>
   </bookViews>
@@ -535,28 +535,10 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
@@ -565,7 +547,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -584,6 +572,18 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -987,14 +987,14 @@
       <c r="C8" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D8" s="26" t="s">
+      <c r="D8" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="E8" s="26"/>
-      <c r="F8" s="26"/>
-      <c r="G8" s="26"/>
-      <c r="H8" s="26"/>
-      <c r="I8" s="26"/>
+      <c r="E8" s="37"/>
+      <c r="F8" s="37"/>
+      <c r="G8" s="37"/>
+      <c r="H8" s="37"/>
+      <c r="I8" s="37"/>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B9" s="4">
@@ -1003,14 +1003,14 @@
       <c r="C9" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D9" s="26" t="s">
+      <c r="D9" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="E9" s="26"/>
-      <c r="F9" s="26"/>
-      <c r="G9" s="26"/>
-      <c r="H9" s="26"/>
-      <c r="I9" s="26"/>
+      <c r="E9" s="37"/>
+      <c r="F9" s="37"/>
+      <c r="G9" s="37"/>
+      <c r="H9" s="37"/>
+      <c r="I9" s="37"/>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B10" s="4">
@@ -1019,14 +1019,14 @@
       <c r="C10" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D10" s="26" t="s">
+      <c r="D10" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="E10" s="26"/>
-      <c r="F10" s="26"/>
-      <c r="G10" s="26"/>
-      <c r="H10" s="26"/>
-      <c r="I10" s="26"/>
+      <c r="E10" s="37"/>
+      <c r="F10" s="37"/>
+      <c r="G10" s="37"/>
+      <c r="H10" s="37"/>
+      <c r="I10" s="37"/>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B11" s="4">
@@ -1035,14 +1035,14 @@
       <c r="C11" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D11" s="26" t="s">
+      <c r="D11" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="E11" s="26"/>
-      <c r="F11" s="26"/>
-      <c r="G11" s="26"/>
-      <c r="H11" s="26"/>
-      <c r="I11" s="26"/>
+      <c r="E11" s="37"/>
+      <c r="F11" s="37"/>
+      <c r="G11" s="37"/>
+      <c r="H11" s="37"/>
+      <c r="I11" s="37"/>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B12" s="4">
@@ -1086,10 +1086,10 @@
       <c r="F13" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="G13" s="26" t="s">
+      <c r="G13" s="37" t="s">
         <v>18</v>
       </c>
-      <c r="H13" s="26"/>
+      <c r="H13" s="37"/>
       <c r="I13" s="1" t="s">
         <v>14</v>
       </c>
@@ -1101,14 +1101,14 @@
       <c r="C14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D14" s="26" t="s">
+      <c r="D14" s="37" t="s">
         <v>19</v>
       </c>
-      <c r="E14" s="26"/>
-      <c r="F14" s="26"/>
-      <c r="G14" s="26"/>
-      <c r="H14" s="26"/>
-      <c r="I14" s="26"/>
+      <c r="E14" s="37"/>
+      <c r="F14" s="37"/>
+      <c r="G14" s="37"/>
+      <c r="H14" s="37"/>
+      <c r="I14" s="37"/>
     </row>
     <row r="15" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B15" s="4">
@@ -1195,14 +1195,14 @@
       <c r="C18" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D18" s="26" t="s">
+      <c r="D18" s="37" t="s">
         <v>23</v>
       </c>
-      <c r="E18" s="26"/>
-      <c r="F18" s="26"/>
-      <c r="G18" s="26"/>
-      <c r="H18" s="26"/>
-      <c r="I18" s="26"/>
+      <c r="E18" s="37"/>
+      <c r="F18" s="37"/>
+      <c r="G18" s="37"/>
+      <c r="H18" s="37"/>
+      <c r="I18" s="37"/>
     </row>
     <row r="19" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B19" s="4">
@@ -1211,14 +1211,14 @@
       <c r="C19" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D19" s="26" t="s">
+      <c r="D19" s="37" t="s">
         <v>23</v>
       </c>
-      <c r="E19" s="26"/>
-      <c r="F19" s="26"/>
-      <c r="G19" s="26"/>
-      <c r="H19" s="26"/>
-      <c r="I19" s="26"/>
+      <c r="E19" s="37"/>
+      <c r="F19" s="37"/>
+      <c r="G19" s="37"/>
+      <c r="H19" s="37"/>
+      <c r="I19" s="37"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B20" s="4">
@@ -1236,10 +1236,10 @@
       <c r="F20" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G20" s="26" t="s">
+      <c r="G20" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="H20" s="26"/>
+      <c r="H20" s="37"/>
       <c r="I20" s="1" t="s">
         <v>14</v>
       </c>
@@ -1355,14 +1355,14 @@
       <c r="C25" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D25" s="26" t="s">
+      <c r="D25" s="37" t="s">
         <v>26</v>
       </c>
-      <c r="E25" s="26"/>
-      <c r="F25" s="26"/>
-      <c r="G25" s="26"/>
-      <c r="H25" s="26"/>
-      <c r="I25" s="26"/>
+      <c r="E25" s="37"/>
+      <c r="F25" s="37"/>
+      <c r="G25" s="37"/>
+      <c r="H25" s="37"/>
+      <c r="I25" s="37"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B26" s="4">
@@ -1406,10 +1406,10 @@
       <c r="F27" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G27" s="26" t="s">
+      <c r="G27" s="37" t="s">
         <v>18</v>
       </c>
-      <c r="H27" s="26"/>
+      <c r="H27" s="37"/>
       <c r="I27" s="1" t="s">
         <v>14</v>
       </c>
@@ -1473,14 +1473,14 @@
       <c r="C30" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D30" s="27" t="s">
+      <c r="D30" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="E30" s="27"/>
-      <c r="F30" s="27"/>
-      <c r="G30" s="27"/>
-      <c r="H30" s="27"/>
-      <c r="I30" s="27"/>
+      <c r="E30" s="36"/>
+      <c r="F30" s="36"/>
+      <c r="G30" s="36"/>
+      <c r="H30" s="36"/>
+      <c r="I30" s="36"/>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B31" s="4">
@@ -1489,14 +1489,14 @@
       <c r="C31" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D31" s="27" t="s">
+      <c r="D31" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="E31" s="27"/>
-      <c r="F31" s="27"/>
-      <c r="G31" s="27"/>
-      <c r="H31" s="27"/>
-      <c r="I31" s="27"/>
+      <c r="E31" s="36"/>
+      <c r="F31" s="36"/>
+      <c r="G31" s="36"/>
+      <c r="H31" s="36"/>
+      <c r="I31" s="36"/>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B32" s="4">
@@ -1531,14 +1531,14 @@
       <c r="C33" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D33" s="27" t="s">
+      <c r="D33" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="E33" s="27"/>
-      <c r="F33" s="27"/>
-      <c r="G33" s="27"/>
-      <c r="H33" s="27"/>
-      <c r="I33" s="27"/>
+      <c r="E33" s="36"/>
+      <c r="F33" s="36"/>
+      <c r="G33" s="36"/>
+      <c r="H33" s="36"/>
+      <c r="I33" s="36"/>
     </row>
     <row r="34" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B34" s="4">
@@ -1582,10 +1582,10 @@
       <c r="F35" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G35" s="27" t="s">
+      <c r="G35" s="36" t="s">
         <v>18</v>
       </c>
-      <c r="H35" s="27"/>
+      <c r="H35" s="36"/>
       <c r="I35" s="1" t="s">
         <v>14</v>
       </c>
@@ -1701,14 +1701,14 @@
       <c r="C40" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D40" s="27" t="s">
+      <c r="D40" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="E40" s="27"/>
-      <c r="F40" s="27"/>
-      <c r="G40" s="27"/>
-      <c r="H40" s="27"/>
-      <c r="I40" s="27"/>
+      <c r="E40" s="36"/>
+      <c r="F40" s="36"/>
+      <c r="G40" s="36"/>
+      <c r="H40" s="36"/>
+      <c r="I40" s="36"/>
     </row>
     <row r="41" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B41" s="4">
@@ -1752,10 +1752,10 @@
       <c r="F42" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G42" s="27" t="s">
+      <c r="G42" s="36" t="s">
         <v>28</v>
       </c>
-      <c r="H42" s="27"/>
+      <c r="H42" s="36"/>
       <c r="I42" s="1" t="s">
         <v>15</v>
       </c>
@@ -1767,14 +1767,14 @@
       <c r="C43" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D43" s="27" t="s">
+      <c r="D43" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="E43" s="27"/>
-      <c r="F43" s="27"/>
-      <c r="G43" s="27"/>
-      <c r="H43" s="27"/>
-      <c r="I43" s="27"/>
+      <c r="E43" s="36"/>
+      <c r="F43" s="36"/>
+      <c r="G43" s="36"/>
+      <c r="H43" s="36"/>
+      <c r="I43" s="36"/>
     </row>
     <row r="44" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B44" s="4">
@@ -1838,14 +1838,14 @@
       <c r="C46" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D46" s="27" t="s">
+      <c r="D46" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="E46" s="27"/>
-      <c r="F46" s="27"/>
-      <c r="G46" s="27"/>
-      <c r="H46" s="27"/>
-      <c r="I46" s="27"/>
+      <c r="E46" s="36"/>
+      <c r="F46" s="36"/>
+      <c r="G46" s="36"/>
+      <c r="H46" s="36"/>
+      <c r="I46" s="36"/>
     </row>
     <row r="47" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B47" s="4">
@@ -1854,14 +1854,14 @@
       <c r="C47" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D47" s="23" t="s">
+      <c r="D47" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="E47" s="24"/>
-      <c r="F47" s="24"/>
-      <c r="G47" s="24"/>
-      <c r="H47" s="24"/>
-      <c r="I47" s="25"/>
+      <c r="E47" s="28"/>
+      <c r="F47" s="28"/>
+      <c r="G47" s="28"/>
+      <c r="H47" s="28"/>
+      <c r="I47" s="29"/>
     </row>
     <row r="48" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B48" s="4">
@@ -1905,10 +1905,10 @@
       <c r="F49" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G49" s="23" t="s">
+      <c r="G49" s="27" t="s">
         <v>29</v>
       </c>
-      <c r="H49" s="25"/>
+      <c r="H49" s="29"/>
       <c r="I49" s="1" t="s">
         <v>30</v>
       </c>
@@ -2050,14 +2050,14 @@
       <c r="C55" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="D55" s="24" t="s">
+      <c r="D55" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="E55" s="24"/>
-      <c r="F55" s="24"/>
-      <c r="G55" s="24"/>
-      <c r="H55" s="24"/>
-      <c r="I55" s="24"/>
+      <c r="E55" s="28"/>
+      <c r="F55" s="28"/>
+      <c r="G55" s="28"/>
+      <c r="H55" s="28"/>
+      <c r="I55" s="28"/>
     </row>
     <row r="56" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B56" s="4">
@@ -2101,10 +2101,10 @@
       <c r="F57" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G57" s="23" t="s">
+      <c r="G57" s="27" t="s">
         <v>37</v>
       </c>
-      <c r="H57" s="25"/>
+      <c r="H57" s="29"/>
       <c r="I57" s="1" t="s">
         <v>36</v>
       </c>
@@ -2168,14 +2168,14 @@
       <c r="C60" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D60" s="23" t="s">
+      <c r="D60" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="E60" s="24"/>
-      <c r="F60" s="24"/>
-      <c r="G60" s="24"/>
-      <c r="H60" s="24"/>
-      <c r="I60" s="25"/>
+      <c r="E60" s="28"/>
+      <c r="F60" s="28"/>
+      <c r="G60" s="28"/>
+      <c r="H60" s="28"/>
+      <c r="I60" s="29"/>
     </row>
     <row r="61" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B61" s="4">
@@ -2184,14 +2184,14 @@
       <c r="C61" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D61" s="23" t="s">
+      <c r="D61" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="E61" s="24"/>
-      <c r="F61" s="24"/>
-      <c r="G61" s="24"/>
-      <c r="H61" s="24"/>
-      <c r="I61" s="25"/>
+      <c r="E61" s="28"/>
+      <c r="F61" s="28"/>
+      <c r="G61" s="28"/>
+      <c r="H61" s="28"/>
+      <c r="I61" s="29"/>
     </row>
     <row r="62" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B62" s="4">
@@ -2200,14 +2200,14 @@
       <c r="C62" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D62" s="23" t="s">
+      <c r="D62" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="E62" s="24"/>
-      <c r="F62" s="24"/>
-      <c r="G62" s="24"/>
-      <c r="H62" s="24"/>
-      <c r="I62" s="25"/>
+      <c r="E62" s="28"/>
+      <c r="F62" s="28"/>
+      <c r="G62" s="28"/>
+      <c r="H62" s="28"/>
+      <c r="I62" s="29"/>
     </row>
     <row r="63" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B63" s="4">
@@ -2251,10 +2251,10 @@
       <c r="F64" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G64" s="23" t="s">
+      <c r="G64" s="27" t="s">
         <v>37</v>
       </c>
-      <c r="H64" s="25"/>
+      <c r="H64" s="29"/>
       <c r="I64" s="1" t="s">
         <v>14</v>
       </c>
@@ -2292,13 +2292,13 @@
       <c r="C66" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D66" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="E66" s="24"/>
-      <c r="F66" s="24"/>
-      <c r="G66" s="24"/>
-      <c r="H66" s="25"/>
+      <c r="D66" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="E66" s="28"/>
+      <c r="F66" s="28"/>
+      <c r="G66" s="28"/>
+      <c r="H66" s="29"/>
       <c r="I66" s="1" t="s">
         <v>16</v>
       </c>
@@ -2310,18 +2310,18 @@
       <c r="C67" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D67" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="E67" s="24"/>
-      <c r="F67" s="25"/>
+      <c r="D67" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="E67" s="28"/>
+      <c r="F67" s="29"/>
       <c r="G67" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="H67" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="I67" s="25"/>
+      <c r="H67" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="I67" s="29"/>
     </row>
     <row r="68" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B68" s="4">
@@ -2336,12 +2336,12 @@
       <c r="E68" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F68" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="G68" s="24"/>
-      <c r="H68" s="24"/>
-      <c r="I68" s="25"/>
+      <c r="F68" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="G68" s="28"/>
+      <c r="H68" s="28"/>
+      <c r="I68" s="29"/>
     </row>
     <row r="69" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B69" s="4">
@@ -2350,14 +2350,14 @@
       <c r="C69" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D69" s="23" t="s">
+      <c r="D69" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="E69" s="24"/>
-      <c r="F69" s="24"/>
-      <c r="G69" s="24"/>
-      <c r="H69" s="24"/>
-      <c r="I69" s="25"/>
+      <c r="E69" s="28"/>
+      <c r="F69" s="28"/>
+      <c r="G69" s="28"/>
+      <c r="H69" s="28"/>
+      <c r="I69" s="29"/>
     </row>
     <row r="70" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B70" s="4">
@@ -2366,10 +2366,10 @@
       <c r="C70" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D70" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="E70" s="25"/>
+      <c r="D70" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="E70" s="29"/>
       <c r="F70" s="3" t="s">
         <v>15</v>
       </c>
@@ -2399,10 +2399,10 @@
       <c r="F71" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G71" s="23" t="s">
+      <c r="G71" s="27" t="s">
         <v>37</v>
       </c>
-      <c r="H71" s="25"/>
+      <c r="H71" s="29"/>
       <c r="I71" s="1" t="s">
         <v>14</v>
       </c>
@@ -2440,14 +2440,14 @@
       <c r="C73" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D73" s="23" t="s">
+      <c r="D73" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="E73" s="24"/>
-      <c r="F73" s="24"/>
-      <c r="G73" s="24"/>
-      <c r="H73" s="24"/>
-      <c r="I73" s="25"/>
+      <c r="E73" s="28"/>
+      <c r="F73" s="28"/>
+      <c r="G73" s="28"/>
+      <c r="H73" s="28"/>
+      <c r="I73" s="29"/>
     </row>
     <row r="74" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B74" s="4">
@@ -2456,11 +2456,11 @@
       <c r="C74" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D74" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="E74" s="24"/>
-      <c r="F74" s="25"/>
+      <c r="D74" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="E74" s="28"/>
+      <c r="F74" s="29"/>
       <c r="G74" s="3" t="s">
         <v>16</v>
       </c>
@@ -2496,14 +2496,14 @@
       <c r="C76" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D76" s="23" t="s">
+      <c r="D76" s="27" t="s">
         <v>39</v>
       </c>
-      <c r="E76" s="24"/>
-      <c r="F76" s="24"/>
-      <c r="G76" s="24"/>
-      <c r="H76" s="24"/>
-      <c r="I76" s="25"/>
+      <c r="E76" s="28"/>
+      <c r="F76" s="28"/>
+      <c r="G76" s="28"/>
+      <c r="H76" s="28"/>
+      <c r="I76" s="29"/>
     </row>
     <row r="77" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B77" s="4">
@@ -2512,14 +2512,14 @@
       <c r="C77" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D77" s="23" t="s">
+      <c r="D77" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="E77" s="24"/>
-      <c r="F77" s="24"/>
-      <c r="G77" s="24"/>
-      <c r="H77" s="24"/>
-      <c r="I77" s="25"/>
+      <c r="E77" s="28"/>
+      <c r="F77" s="28"/>
+      <c r="G77" s="28"/>
+      <c r="H77" s="28"/>
+      <c r="I77" s="29"/>
     </row>
     <row r="78" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B78" s="4">
@@ -2528,14 +2528,14 @@
       <c r="C78" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D78" s="23" t="s">
+      <c r="D78" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="E78" s="24"/>
-      <c r="F78" s="24"/>
-      <c r="G78" s="24"/>
-      <c r="H78" s="24"/>
-      <c r="I78" s="25"/>
+      <c r="E78" s="28"/>
+      <c r="F78" s="28"/>
+      <c r="G78" s="28"/>
+      <c r="H78" s="28"/>
+      <c r="I78" s="29"/>
     </row>
     <row r="79" spans="2:9" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B79" s="16" t="s">
@@ -2579,10 +2579,10 @@
       <c r="F80" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G80" s="23" t="s">
+      <c r="G80" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="H80" s="25"/>
+      <c r="H80" s="29"/>
       <c r="I80" s="1" t="s">
         <v>14</v>
       </c>
@@ -2603,10 +2603,10 @@
       <c r="F81" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="G81" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="H81" s="25"/>
+      <c r="G81" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="H81" s="29"/>
       <c r="I81" s="1" t="s">
         <v>16</v>
       </c>
@@ -2670,14 +2670,14 @@
       <c r="C84" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D84" s="23" t="s">
+      <c r="D84" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="E84" s="24"/>
-      <c r="F84" s="24"/>
-      <c r="G84" s="24"/>
-      <c r="H84" s="24"/>
-      <c r="I84" s="25"/>
+      <c r="E84" s="28"/>
+      <c r="F84" s="28"/>
+      <c r="G84" s="28"/>
+      <c r="H84" s="28"/>
+      <c r="I84" s="29"/>
     </row>
     <row r="85" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B85" s="4">
@@ -2715,11 +2715,11 @@
       <c r="D86" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="E86" s="23" t="s">
+      <c r="E86" s="27" t="s">
         <v>43</v>
       </c>
-      <c r="F86" s="24"/>
-      <c r="G86" s="25"/>
+      <c r="F86" s="28"/>
+      <c r="G86" s="29"/>
       <c r="H86" s="3" t="s">
         <v>14</v>
       </c>
@@ -2734,18 +2734,18 @@
       <c r="C87" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D87" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="E87" s="25"/>
+      <c r="D87" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="E87" s="29"/>
       <c r="F87" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G87" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="H87" s="24"/>
-      <c r="I87" s="25"/>
+      <c r="G87" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="H87" s="28"/>
+      <c r="I87" s="29"/>
     </row>
     <row r="88" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B88" s="4">
@@ -2754,14 +2754,14 @@
       <c r="C88" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D88" s="23" t="s">
+      <c r="D88" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="E88" s="24"/>
-      <c r="F88" s="24"/>
-      <c r="G88" s="24"/>
-      <c r="H88" s="24"/>
-      <c r="I88" s="25"/>
+      <c r="E88" s="28"/>
+      <c r="F88" s="28"/>
+      <c r="G88" s="28"/>
+      <c r="H88" s="28"/>
+      <c r="I88" s="29"/>
     </row>
     <row r="89" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B89" s="4">
@@ -2770,18 +2770,18 @@
       <c r="C89" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D89" s="23" t="s">
+      <c r="D89" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="E89" s="24"/>
-      <c r="F89" s="25"/>
+      <c r="E89" s="28"/>
+      <c r="F89" s="29"/>
       <c r="G89" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="H89" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="I89" s="25"/>
+      <c r="H89" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="I89" s="29"/>
     </row>
     <row r="90" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B90" s="4">
@@ -2790,10 +2790,10 @@
       <c r="C90" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D90" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="E90" s="25"/>
+      <c r="D90" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="E90" s="29"/>
       <c r="F90" s="3" t="s">
         <v>16</v>
       </c>
@@ -2815,13 +2815,13 @@
       <c r="C91" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D91" s="23" t="s">
+      <c r="D91" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="E91" s="24"/>
-      <c r="F91" s="24"/>
-      <c r="G91" s="24"/>
-      <c r="H91" s="25"/>
+      <c r="E91" s="28"/>
+      <c r="F91" s="28"/>
+      <c r="G91" s="28"/>
+      <c r="H91" s="29"/>
       <c r="I91" s="18" t="s">
         <v>45</v>
       </c>
@@ -2833,14 +2833,14 @@
       <c r="C92" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D92" s="23" t="s">
+      <c r="D92" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="E92" s="24"/>
-      <c r="F92" s="24"/>
-      <c r="G92" s="24"/>
-      <c r="H92" s="24"/>
-      <c r="I92" s="25"/>
+      <c r="E92" s="28"/>
+      <c r="F92" s="28"/>
+      <c r="G92" s="28"/>
+      <c r="H92" s="28"/>
+      <c r="I92" s="29"/>
     </row>
     <row r="93" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B93" s="4">
@@ -2849,14 +2849,14 @@
       <c r="C93" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D93" s="23" t="s">
+      <c r="D93" s="27" t="s">
         <v>46</v>
       </c>
-      <c r="E93" s="24"/>
-      <c r="F93" s="24"/>
-      <c r="G93" s="24"/>
-      <c r="H93" s="24"/>
-      <c r="I93" s="25"/>
+      <c r="E93" s="28"/>
+      <c r="F93" s="28"/>
+      <c r="G93" s="28"/>
+      <c r="H93" s="28"/>
+      <c r="I93" s="29"/>
     </row>
     <row r="94" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B94" s="4">
@@ -2865,14 +2865,14 @@
       <c r="C94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D94" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="E94" s="24"/>
-      <c r="F94" s="24"/>
-      <c r="G94" s="24"/>
-      <c r="H94" s="24"/>
-      <c r="I94" s="25"/>
+      <c r="D94" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="E94" s="28"/>
+      <c r="F94" s="28"/>
+      <c r="G94" s="28"/>
+      <c r="H94" s="28"/>
+      <c r="I94" s="29"/>
     </row>
     <row r="95" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B95" s="4">
@@ -2881,15 +2881,15 @@
       <c r="C95" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D95" s="23" t="s">
+      <c r="D95" s="27" t="s">
         <v>47</v>
       </c>
-      <c r="E95" s="24"/>
-      <c r="F95" s="25"/>
-      <c r="G95" s="23" t="s">
+      <c r="E95" s="28"/>
+      <c r="F95" s="29"/>
+      <c r="G95" s="27" t="s">
         <v>48</v>
       </c>
-      <c r="H95" s="25"/>
+      <c r="H95" s="29"/>
       <c r="I95" s="1" t="s">
         <v>14</v>
       </c>
@@ -2901,14 +2901,14 @@
       <c r="C96" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D96" s="23" t="s">
+      <c r="D96" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="E96" s="24"/>
-      <c r="F96" s="24"/>
-      <c r="G96" s="24"/>
-      <c r="H96" s="24"/>
-      <c r="I96" s="25"/>
+      <c r="E96" s="28"/>
+      <c r="F96" s="28"/>
+      <c r="G96" s="28"/>
+      <c r="H96" s="28"/>
+      <c r="I96" s="29"/>
     </row>
     <row r="97" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B97" s="4">
@@ -2917,14 +2917,14 @@
       <c r="C97" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D97" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="E97" s="24"/>
-      <c r="F97" s="24"/>
-      <c r="G97" s="24"/>
-      <c r="H97" s="24"/>
-      <c r="I97" s="25"/>
+      <c r="D97" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="E97" s="28"/>
+      <c r="F97" s="28"/>
+      <c r="G97" s="28"/>
+      <c r="H97" s="28"/>
+      <c r="I97" s="29"/>
     </row>
     <row r="98" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B98" s="4">
@@ -2933,14 +2933,14 @@
       <c r="C98" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D98" s="23" t="s">
+      <c r="D98" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="E98" s="24"/>
-      <c r="F98" s="24"/>
-      <c r="G98" s="24"/>
-      <c r="H98" s="24"/>
-      <c r="I98" s="25"/>
+      <c r="E98" s="28"/>
+      <c r="F98" s="28"/>
+      <c r="G98" s="28"/>
+      <c r="H98" s="28"/>
+      <c r="I98" s="29"/>
     </row>
     <row r="99" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B99" s="4">
@@ -2949,12 +2949,12 @@
       <c r="C99" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D99" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="E99" s="24"/>
-      <c r="F99" s="24"/>
-      <c r="G99" s="25"/>
+      <c r="D99" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="E99" s="28"/>
+      <c r="F99" s="28"/>
+      <c r="G99" s="29"/>
       <c r="H99" s="3" t="s">
         <v>49</v>
       </c>
@@ -2978,21 +2978,21 @@
       <c r="F100" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="G100" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="H100" s="24"/>
-      <c r="I100" s="25"/>
+      <c r="G100" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="H100" s="28"/>
+      <c r="I100" s="29"/>
     </row>
     <row r="101" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B101" s="23"/>
-      <c r="C101" s="24"/>
-      <c r="D101" s="24"/>
-      <c r="E101" s="24"/>
-      <c r="F101" s="24"/>
-      <c r="G101" s="24"/>
-      <c r="H101" s="24"/>
-      <c r="I101" s="25"/>
+      <c r="B101" s="27"/>
+      <c r="C101" s="28"/>
+      <c r="D101" s="28"/>
+      <c r="E101" s="28"/>
+      <c r="F101" s="28"/>
+      <c r="G101" s="28"/>
+      <c r="H101" s="28"/>
+      <c r="I101" s="29"/>
     </row>
     <row r="102" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B102" s="3"/>
@@ -3011,10 +3011,10 @@
       <c r="C103" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D103" s="23" t="s">
+      <c r="D103" s="27" t="s">
         <v>51</v>
       </c>
-      <c r="E103" s="25"/>
+      <c r="E103" s="29"/>
       <c r="F103" s="3"/>
       <c r="G103" s="3"/>
       <c r="H103" s="3"/>
@@ -3027,10 +3027,10 @@
       <c r="C104" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D104" s="23" t="s">
+      <c r="D104" s="27" t="s">
         <v>52</v>
       </c>
-      <c r="E104" s="25"/>
+      <c r="E104" s="29"/>
       <c r="F104" s="3"/>
       <c r="G104" s="3"/>
       <c r="H104" s="3"/>
@@ -3043,10 +3043,10 @@
       <c r="C105" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D105" s="23" t="s">
+      <c r="D105" s="27" t="s">
         <v>53</v>
       </c>
-      <c r="E105" s="25"/>
+      <c r="E105" s="29"/>
       <c r="F105" s="3"/>
       <c r="G105" s="3"/>
       <c r="H105" s="3"/>
@@ -3059,10 +3059,10 @@
       <c r="C106" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D106" s="23" t="s">
+      <c r="D106" s="27" t="s">
         <v>54</v>
       </c>
-      <c r="E106" s="25"/>
+      <c r="E106" s="29"/>
       <c r="F106" s="3"/>
       <c r="G106" s="3"/>
       <c r="H106" s="3"/>
@@ -3075,10 +3075,10 @@
       <c r="C107" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D107" s="23" t="s">
+      <c r="D107" s="27" t="s">
         <v>55</v>
       </c>
-      <c r="E107" s="25"/>
+      <c r="E107" s="29"/>
       <c r="F107" s="3"/>
       <c r="G107" s="3"/>
       <c r="H107" s="3"/>
@@ -3091,10 +3091,10 @@
       <c r="C108" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D108" s="23" t="s">
+      <c r="D108" s="27" t="s">
         <v>56</v>
       </c>
-      <c r="E108" s="25"/>
+      <c r="E108" s="29"/>
       <c r="F108" s="3"/>
       <c r="G108" s="3"/>
       <c r="H108" s="3"/>
@@ -3131,28 +3131,28 @@
       <c r="I111" s="20"/>
     </row>
     <row r="112" spans="2:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B112" s="34" t="s">
+      <c r="B112" s="30" t="s">
         <v>57</v>
       </c>
-      <c r="C112" s="35"/>
-      <c r="D112" s="35"/>
-      <c r="E112" s="35"/>
-      <c r="F112" s="35"/>
-      <c r="G112" s="35"/>
-      <c r="H112" s="35"/>
-      <c r="I112" s="35"/>
-      <c r="J112" s="36"/>
+      <c r="C112" s="31"/>
+      <c r="D112" s="31"/>
+      <c r="E112" s="31"/>
+      <c r="F112" s="31"/>
+      <c r="G112" s="31"/>
+      <c r="H112" s="31"/>
+      <c r="I112" s="31"/>
+      <c r="J112" s="32"/>
     </row>
     <row r="113" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B113" s="37"/>
-      <c r="C113" s="38"/>
-      <c r="D113" s="38"/>
-      <c r="E113" s="38"/>
-      <c r="F113" s="38"/>
-      <c r="G113" s="38"/>
-      <c r="H113" s="38"/>
-      <c r="I113" s="38"/>
-      <c r="J113" s="39"/>
+      <c r="B113" s="33"/>
+      <c r="C113" s="34"/>
+      <c r="D113" s="34"/>
+      <c r="E113" s="34"/>
+      <c r="F113" s="34"/>
+      <c r="G113" s="34"/>
+      <c r="H113" s="34"/>
+      <c r="I113" s="34"/>
+      <c r="J113" s="35"/>
     </row>
     <row r="114" spans="2:10" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B114" s="8" t="s">
@@ -3283,13 +3283,13 @@
       <c r="E118" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="F118" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="G118" s="24"/>
-      <c r="H118" s="24"/>
-      <c r="I118" s="24"/>
-      <c r="J118" s="25"/>
+      <c r="F118" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="G118" s="28"/>
+      <c r="H118" s="28"/>
+      <c r="I118" s="28"/>
+      <c r="J118" s="29"/>
     </row>
     <row r="119" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B119" s="4">
@@ -3327,13 +3327,13 @@
       <c r="C120" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D120" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="E120" s="24"/>
-      <c r="F120" s="24"/>
-      <c r="G120" s="24"/>
-      <c r="H120" s="25"/>
+      <c r="D120" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="E120" s="28"/>
+      <c r="F120" s="28"/>
+      <c r="G120" s="28"/>
+      <c r="H120" s="29"/>
       <c r="I120" s="1" t="s">
         <v>16</v>
       </c>
@@ -3348,15 +3348,15 @@
       <c r="C121" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D121" s="23" t="s">
+      <c r="D121" s="27" t="s">
         <v>65</v>
       </c>
-      <c r="E121" s="24"/>
-      <c r="F121" s="24"/>
-      <c r="G121" s="24"/>
-      <c r="H121" s="24"/>
-      <c r="I121" s="24"/>
-      <c r="J121" s="25"/>
+      <c r="E121" s="28"/>
+      <c r="F121" s="28"/>
+      <c r="G121" s="28"/>
+      <c r="H121" s="28"/>
+      <c r="I121" s="28"/>
+      <c r="J121" s="29"/>
     </row>
     <row r="122" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B122" s="4">
@@ -3403,12 +3403,12 @@
       <c r="F123" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="G123" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="H123" s="24"/>
-      <c r="I123" s="24"/>
-      <c r="J123" s="25"/>
+      <c r="G123" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="H123" s="28"/>
+      <c r="I123" s="28"/>
+      <c r="J123" s="29"/>
     </row>
     <row r="124" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B124" s="4">
@@ -3426,12 +3426,12 @@
       <c r="F124" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="G124" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="H124" s="24"/>
-      <c r="I124" s="24"/>
-      <c r="J124" s="25"/>
+      <c r="G124" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="H124" s="28"/>
+      <c r="I124" s="28"/>
+      <c r="J124" s="29"/>
     </row>
     <row r="125" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B125" s="4">
@@ -3446,13 +3446,13 @@
       <c r="E125" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="F125" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="G125" s="24"/>
-      <c r="H125" s="24"/>
-      <c r="I125" s="24"/>
-      <c r="J125" s="25"/>
+      <c r="F125" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="G125" s="28"/>
+      <c r="H125" s="28"/>
+      <c r="I125" s="28"/>
+      <c r="J125" s="29"/>
     </row>
     <row r="126" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B126" s="4">
@@ -3470,11 +3470,11 @@
       <c r="F126" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="G126" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="H126" s="24"/>
-      <c r="I126" s="25"/>
+      <c r="G126" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="H126" s="28"/>
+      <c r="I126" s="29"/>
       <c r="J126" s="1" t="s">
         <v>16</v>
       </c>
@@ -3492,13 +3492,13 @@
       <c r="E127" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="F127" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="G127" s="24"/>
-      <c r="H127" s="24"/>
-      <c r="I127" s="24"/>
-      <c r="J127" s="25"/>
+      <c r="F127" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="G127" s="28"/>
+      <c r="H127" s="28"/>
+      <c r="I127" s="28"/>
+      <c r="J127" s="29"/>
     </row>
     <row r="128" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B128" s="4">
@@ -3507,15 +3507,15 @@
       <c r="C128" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D128" s="23" t="s">
+      <c r="D128" s="27" t="s">
         <v>65</v>
       </c>
-      <c r="E128" s="24"/>
-      <c r="F128" s="24"/>
-      <c r="G128" s="24"/>
-      <c r="H128" s="24"/>
-      <c r="I128" s="24"/>
-      <c r="J128" s="25"/>
+      <c r="E128" s="28"/>
+      <c r="F128" s="28"/>
+      <c r="G128" s="28"/>
+      <c r="H128" s="28"/>
+      <c r="I128" s="28"/>
+      <c r="J128" s="29"/>
     </row>
     <row r="129" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B129" s="4">
@@ -3698,15 +3698,15 @@
       <c r="C135" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D135" s="23" t="s">
+      <c r="D135" s="27" t="s">
         <v>65</v>
       </c>
-      <c r="E135" s="24"/>
-      <c r="F135" s="24"/>
-      <c r="G135" s="24"/>
-      <c r="H135" s="24"/>
-      <c r="I135" s="24"/>
-      <c r="J135" s="25"/>
+      <c r="E135" s="28"/>
+      <c r="F135" s="28"/>
+      <c r="G135" s="28"/>
+      <c r="H135" s="28"/>
+      <c r="I135" s="28"/>
+      <c r="J135" s="29"/>
     </row>
     <row r="136" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B136" s="4">
@@ -3918,15 +3918,15 @@
       <c r="C143" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D143" s="23" t="s">
+      <c r="D143" s="27" t="s">
         <v>65</v>
       </c>
-      <c r="E143" s="24"/>
-      <c r="F143" s="24"/>
-      <c r="G143" s="24"/>
-      <c r="H143" s="24"/>
-      <c r="I143" s="24"/>
-      <c r="J143" s="25"/>
+      <c r="E143" s="28"/>
+      <c r="F143" s="28"/>
+      <c r="G143" s="28"/>
+      <c r="H143" s="28"/>
+      <c r="I143" s="28"/>
+      <c r="J143" s="29"/>
     </row>
     <row r="144" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B144" s="4">
@@ -4002,12 +4002,12 @@
       <c r="F146" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="G146" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="H146" s="24"/>
-      <c r="I146" s="24"/>
-      <c r="J146" s="25"/>
+      <c r="G146" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="H146" s="28"/>
+      <c r="I146" s="28"/>
+      <c r="J146" s="29"/>
     </row>
     <row r="147" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B147" s="4">
@@ -4074,15 +4074,15 @@
       <c r="C149" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D149" s="28" t="s">
+      <c r="D149" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E149" s="29"/>
-      <c r="F149" s="29"/>
-      <c r="G149" s="29"/>
-      <c r="H149" s="29"/>
-      <c r="I149" s="29"/>
-      <c r="J149" s="30"/>
+      <c r="E149" s="24"/>
+      <c r="F149" s="24"/>
+      <c r="G149" s="24"/>
+      <c r="H149" s="24"/>
+      <c r="I149" s="24"/>
+      <c r="J149" s="38"/>
     </row>
     <row r="150" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B150" s="4">
@@ -4091,13 +4091,13 @@
       <c r="C150" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D150" s="31"/>
-      <c r="E150" s="32"/>
-      <c r="F150" s="32"/>
-      <c r="G150" s="32"/>
-      <c r="H150" s="32"/>
-      <c r="I150" s="32"/>
-      <c r="J150" s="33"/>
+      <c r="D150" s="25"/>
+      <c r="E150" s="26"/>
+      <c r="F150" s="26"/>
+      <c r="G150" s="26"/>
+      <c r="H150" s="26"/>
+      <c r="I150" s="26"/>
+      <c r="J150" s="39"/>
     </row>
     <row r="151" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B151" s="4">
@@ -4144,11 +4144,11 @@
       <c r="F152" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="G152" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="H152" s="24"/>
-      <c r="I152" s="25"/>
+      <c r="G152" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="H152" s="28"/>
+      <c r="I152" s="29"/>
       <c r="J152" s="1" t="s">
         <v>69</v>
       </c>
@@ -4276,15 +4276,15 @@
       <c r="C157" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D157" s="23" t="s">
+      <c r="D157" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="E157" s="24"/>
-      <c r="F157" s="24"/>
-      <c r="G157" s="24"/>
-      <c r="H157" s="24"/>
-      <c r="I157" s="24"/>
-      <c r="J157" s="25"/>
+      <c r="E157" s="28"/>
+      <c r="F157" s="28"/>
+      <c r="G157" s="28"/>
+      <c r="H157" s="28"/>
+      <c r="I157" s="28"/>
+      <c r="J157" s="29"/>
     </row>
     <row r="158" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B158" s="4">
@@ -4465,15 +4465,15 @@
       <c r="C164" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D164" s="23" t="s">
+      <c r="D164" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="E164" s="24"/>
-      <c r="F164" s="24"/>
-      <c r="G164" s="24"/>
-      <c r="H164" s="24"/>
-      <c r="I164" s="24"/>
-      <c r="J164" s="25"/>
+      <c r="E164" s="28"/>
+      <c r="F164" s="28"/>
+      <c r="G164" s="28"/>
+      <c r="H164" s="28"/>
+      <c r="I164" s="28"/>
+      <c r="J164" s="29"/>
     </row>
     <row r="165" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B165" s="4">
@@ -4671,15 +4671,15 @@
       <c r="C172" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D172" s="23" t="s">
+      <c r="D172" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="E172" s="24"/>
-      <c r="F172" s="24"/>
-      <c r="G172" s="24"/>
-      <c r="H172" s="24"/>
-      <c r="I172" s="24"/>
-      <c r="J172" s="25"/>
+      <c r="E172" s="28"/>
+      <c r="F172" s="28"/>
+      <c r="G172" s="28"/>
+      <c r="H172" s="28"/>
+      <c r="I172" s="28"/>
+      <c r="J172" s="29"/>
     </row>
     <row r="173" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B173" s="4">
@@ -4743,44 +4743,44 @@
       <c r="B175" s="4">
         <v>45903</v>
       </c>
-      <c r="C175" s="28" t="s">
+      <c r="C175" s="23" t="s">
         <v>39</v>
       </c>
-      <c r="D175" s="29"/>
-      <c r="E175" s="29"/>
-      <c r="F175" s="29"/>
-      <c r="G175" s="29"/>
-      <c r="H175" s="29"/>
-      <c r="I175" s="29"/>
-      <c r="J175" s="29"/>
+      <c r="D175" s="24"/>
+      <c r="E175" s="24"/>
+      <c r="F175" s="24"/>
+      <c r="G175" s="24"/>
+      <c r="H175" s="24"/>
+      <c r="I175" s="24"/>
+      <c r="J175" s="24"/>
     </row>
     <row r="176" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B176" s="4">
         <v>45904</v>
       </c>
-      <c r="C176" s="31"/>
-      <c r="D176" s="32"/>
-      <c r="E176" s="32"/>
-      <c r="F176" s="32"/>
-      <c r="G176" s="32"/>
-      <c r="H176" s="32"/>
-      <c r="I176" s="32"/>
-      <c r="J176" s="32"/>
+      <c r="C176" s="25"/>
+      <c r="D176" s="26"/>
+      <c r="E176" s="26"/>
+      <c r="F176" s="26"/>
+      <c r="G176" s="26"/>
+      <c r="H176" s="26"/>
+      <c r="I176" s="26"/>
+      <c r="J176" s="26"/>
     </row>
     <row r="177" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B177" s="4">
         <v>45905</v>
       </c>
-      <c r="C177" s="23" t="s">
+      <c r="C177" s="27" t="s">
         <v>39</v>
       </c>
-      <c r="D177" s="24"/>
-      <c r="E177" s="24"/>
-      <c r="F177" s="24"/>
-      <c r="G177" s="24"/>
-      <c r="H177" s="24"/>
-      <c r="I177" s="24"/>
-      <c r="J177" s="25"/>
+      <c r="D177" s="28"/>
+      <c r="E177" s="28"/>
+      <c r="F177" s="28"/>
+      <c r="G177" s="28"/>
+      <c r="H177" s="28"/>
+      <c r="I177" s="28"/>
+      <c r="J177" s="29"/>
     </row>
     <row r="178" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B178" s="4">
@@ -4812,7 +4812,9 @@
       </c>
     </row>
     <row r="179" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B179" s="3"/>
+      <c r="B179" s="4">
+        <v>45907</v>
+      </c>
       <c r="C179" s="3"/>
       <c r="D179" s="3"/>
       <c r="E179" s="3"/>
@@ -7431,33 +7433,50 @@
     </row>
   </sheetData>
   <mergeCells count="87">
-    <mergeCell ref="C175:J176"/>
-    <mergeCell ref="D164:J164"/>
-    <mergeCell ref="D157:J157"/>
-    <mergeCell ref="D143:J143"/>
-    <mergeCell ref="D135:J135"/>
-    <mergeCell ref="D172:J172"/>
-    <mergeCell ref="G146:J146"/>
-    <mergeCell ref="D108:E108"/>
-    <mergeCell ref="B112:J113"/>
-    <mergeCell ref="G124:J124"/>
-    <mergeCell ref="D120:H120"/>
-    <mergeCell ref="G123:J123"/>
-    <mergeCell ref="D121:J121"/>
-    <mergeCell ref="D31:I31"/>
-    <mergeCell ref="G35:H35"/>
-    <mergeCell ref="D40:I40"/>
-    <mergeCell ref="D33:I33"/>
-    <mergeCell ref="D46:I46"/>
-    <mergeCell ref="D43:I43"/>
-    <mergeCell ref="D78:I78"/>
-    <mergeCell ref="G71:H71"/>
-    <mergeCell ref="D76:I76"/>
-    <mergeCell ref="D66:H66"/>
-    <mergeCell ref="D77:I77"/>
-    <mergeCell ref="D73:I73"/>
-    <mergeCell ref="D70:E70"/>
-    <mergeCell ref="D74:F74"/>
+    <mergeCell ref="C177:J177"/>
+    <mergeCell ref="D106:E106"/>
+    <mergeCell ref="D99:G99"/>
+    <mergeCell ref="G126:I126"/>
+    <mergeCell ref="F125:J125"/>
+    <mergeCell ref="D128:J128"/>
+    <mergeCell ref="D103:E103"/>
+    <mergeCell ref="D104:E104"/>
+    <mergeCell ref="D105:E105"/>
+    <mergeCell ref="G100:I100"/>
+    <mergeCell ref="B101:I101"/>
+    <mergeCell ref="F127:J127"/>
+    <mergeCell ref="D107:E107"/>
+    <mergeCell ref="F118:J118"/>
+    <mergeCell ref="G152:I152"/>
+    <mergeCell ref="D149:J150"/>
+    <mergeCell ref="D98:I98"/>
+    <mergeCell ref="D94:I94"/>
+    <mergeCell ref="H89:I89"/>
+    <mergeCell ref="D89:F89"/>
+    <mergeCell ref="D97:I97"/>
+    <mergeCell ref="G64:H64"/>
+    <mergeCell ref="D96:I96"/>
+    <mergeCell ref="D95:F95"/>
+    <mergeCell ref="G95:H95"/>
+    <mergeCell ref="D92:I92"/>
+    <mergeCell ref="D93:I93"/>
+    <mergeCell ref="D90:E90"/>
+    <mergeCell ref="D91:H91"/>
+    <mergeCell ref="E86:G86"/>
+    <mergeCell ref="D88:I88"/>
+    <mergeCell ref="H67:I67"/>
+    <mergeCell ref="G81:H81"/>
+    <mergeCell ref="D67:F67"/>
+    <mergeCell ref="F68:I68"/>
+    <mergeCell ref="D87:E87"/>
+    <mergeCell ref="G87:I87"/>
+    <mergeCell ref="D60:I60"/>
+    <mergeCell ref="D62:I62"/>
+    <mergeCell ref="D61:I61"/>
+    <mergeCell ref="G49:H49"/>
+    <mergeCell ref="D47:I47"/>
+    <mergeCell ref="D55:I55"/>
+    <mergeCell ref="G57:H57"/>
     <mergeCell ref="D84:I84"/>
     <mergeCell ref="D69:I69"/>
     <mergeCell ref="D8:I8"/>
@@ -7474,50 +7493,33 @@
     <mergeCell ref="D30:I30"/>
     <mergeCell ref="G80:H80"/>
     <mergeCell ref="G42:H42"/>
-    <mergeCell ref="D60:I60"/>
-    <mergeCell ref="D62:I62"/>
-    <mergeCell ref="D61:I61"/>
-    <mergeCell ref="G49:H49"/>
-    <mergeCell ref="D47:I47"/>
-    <mergeCell ref="D55:I55"/>
-    <mergeCell ref="G57:H57"/>
-    <mergeCell ref="G64:H64"/>
-    <mergeCell ref="D96:I96"/>
-    <mergeCell ref="D95:F95"/>
-    <mergeCell ref="G95:H95"/>
-    <mergeCell ref="D92:I92"/>
-    <mergeCell ref="D93:I93"/>
-    <mergeCell ref="D90:E90"/>
-    <mergeCell ref="D91:H91"/>
-    <mergeCell ref="E86:G86"/>
-    <mergeCell ref="D88:I88"/>
-    <mergeCell ref="H67:I67"/>
-    <mergeCell ref="G81:H81"/>
-    <mergeCell ref="D67:F67"/>
-    <mergeCell ref="F68:I68"/>
-    <mergeCell ref="D87:E87"/>
-    <mergeCell ref="G87:I87"/>
-    <mergeCell ref="D98:I98"/>
-    <mergeCell ref="D94:I94"/>
-    <mergeCell ref="H89:I89"/>
-    <mergeCell ref="D89:F89"/>
-    <mergeCell ref="D97:I97"/>
-    <mergeCell ref="C177:J177"/>
-    <mergeCell ref="D106:E106"/>
-    <mergeCell ref="D99:G99"/>
-    <mergeCell ref="G126:I126"/>
-    <mergeCell ref="F125:J125"/>
-    <mergeCell ref="D128:J128"/>
-    <mergeCell ref="D103:E103"/>
-    <mergeCell ref="D104:E104"/>
-    <mergeCell ref="D105:E105"/>
-    <mergeCell ref="G100:I100"/>
-    <mergeCell ref="B101:I101"/>
-    <mergeCell ref="F127:J127"/>
-    <mergeCell ref="D107:E107"/>
-    <mergeCell ref="F118:J118"/>
-    <mergeCell ref="G152:I152"/>
-    <mergeCell ref="D149:J150"/>
+    <mergeCell ref="D78:I78"/>
+    <mergeCell ref="G71:H71"/>
+    <mergeCell ref="D76:I76"/>
+    <mergeCell ref="D66:H66"/>
+    <mergeCell ref="D77:I77"/>
+    <mergeCell ref="D73:I73"/>
+    <mergeCell ref="D70:E70"/>
+    <mergeCell ref="D74:F74"/>
+    <mergeCell ref="D31:I31"/>
+    <mergeCell ref="G35:H35"/>
+    <mergeCell ref="D40:I40"/>
+    <mergeCell ref="D33:I33"/>
+    <mergeCell ref="D46:I46"/>
+    <mergeCell ref="D43:I43"/>
+    <mergeCell ref="D108:E108"/>
+    <mergeCell ref="B112:J113"/>
+    <mergeCell ref="G124:J124"/>
+    <mergeCell ref="D120:H120"/>
+    <mergeCell ref="G123:J123"/>
+    <mergeCell ref="D121:J121"/>
+    <mergeCell ref="C175:J176"/>
+    <mergeCell ref="D164:J164"/>
+    <mergeCell ref="D157:J157"/>
+    <mergeCell ref="D143:J143"/>
+    <mergeCell ref="D135:J135"/>
+    <mergeCell ref="D172:J172"/>
+    <mergeCell ref="G146:J146"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/attendance_sheet.xlsx
+++ b/attendance_sheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\repositary\3rd_Year_5th_Semester\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{135F12EB-C0C7-443B-97AA-D793DF977AAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33AE0A5C-5C4C-438D-8217-46CECCF33320}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{EB654061-A886-47D1-BF86-9B1A84FCE7FB}"/>
   </bookViews>
@@ -535,10 +535,22 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
@@ -547,13 +559,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -572,18 +584,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -987,14 +987,14 @@
       <c r="C8" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D8" s="37" t="s">
+      <c r="D8" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="E8" s="37"/>
-      <c r="F8" s="37"/>
-      <c r="G8" s="37"/>
-      <c r="H8" s="37"/>
-      <c r="I8" s="37"/>
+      <c r="E8" s="32"/>
+      <c r="F8" s="32"/>
+      <c r="G8" s="32"/>
+      <c r="H8" s="32"/>
+      <c r="I8" s="32"/>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B9" s="4">
@@ -1003,14 +1003,14 @@
       <c r="C9" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D9" s="37" t="s">
+      <c r="D9" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="E9" s="37"/>
-      <c r="F9" s="37"/>
-      <c r="G9" s="37"/>
-      <c r="H9" s="37"/>
-      <c r="I9" s="37"/>
+      <c r="E9" s="32"/>
+      <c r="F9" s="32"/>
+      <c r="G9" s="32"/>
+      <c r="H9" s="32"/>
+      <c r="I9" s="32"/>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B10" s="4">
@@ -1019,14 +1019,14 @@
       <c r="C10" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D10" s="37" t="s">
+      <c r="D10" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="E10" s="37"/>
-      <c r="F10" s="37"/>
-      <c r="G10" s="37"/>
-      <c r="H10" s="37"/>
-      <c r="I10" s="37"/>
+      <c r="E10" s="32"/>
+      <c r="F10" s="32"/>
+      <c r="G10" s="32"/>
+      <c r="H10" s="32"/>
+      <c r="I10" s="32"/>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B11" s="4">
@@ -1035,14 +1035,14 @@
       <c r="C11" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D11" s="37" t="s">
+      <c r="D11" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="E11" s="37"/>
-      <c r="F11" s="37"/>
-      <c r="G11" s="37"/>
-      <c r="H11" s="37"/>
-      <c r="I11" s="37"/>
+      <c r="E11" s="32"/>
+      <c r="F11" s="32"/>
+      <c r="G11" s="32"/>
+      <c r="H11" s="32"/>
+      <c r="I11" s="32"/>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B12" s="4">
@@ -1086,10 +1086,10 @@
       <c r="F13" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="G13" s="37" t="s">
+      <c r="G13" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="H13" s="37"/>
+      <c r="H13" s="32"/>
       <c r="I13" s="1" t="s">
         <v>14</v>
       </c>
@@ -1101,14 +1101,14 @@
       <c r="C14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D14" s="37" t="s">
+      <c r="D14" s="32" t="s">
         <v>19</v>
       </c>
-      <c r="E14" s="37"/>
-      <c r="F14" s="37"/>
-      <c r="G14" s="37"/>
-      <c r="H14" s="37"/>
-      <c r="I14" s="37"/>
+      <c r="E14" s="32"/>
+      <c r="F14" s="32"/>
+      <c r="G14" s="32"/>
+      <c r="H14" s="32"/>
+      <c r="I14" s="32"/>
     </row>
     <row r="15" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B15" s="4">
@@ -1195,14 +1195,14 @@
       <c r="C18" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D18" s="37" t="s">
+      <c r="D18" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="E18" s="37"/>
-      <c r="F18" s="37"/>
-      <c r="G18" s="37"/>
-      <c r="H18" s="37"/>
-      <c r="I18" s="37"/>
+      <c r="E18" s="32"/>
+      <c r="F18" s="32"/>
+      <c r="G18" s="32"/>
+      <c r="H18" s="32"/>
+      <c r="I18" s="32"/>
     </row>
     <row r="19" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B19" s="4">
@@ -1211,14 +1211,14 @@
       <c r="C19" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D19" s="37" t="s">
+      <c r="D19" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="E19" s="37"/>
-      <c r="F19" s="37"/>
-      <c r="G19" s="37"/>
-      <c r="H19" s="37"/>
-      <c r="I19" s="37"/>
+      <c r="E19" s="32"/>
+      <c r="F19" s="32"/>
+      <c r="G19" s="32"/>
+      <c r="H19" s="32"/>
+      <c r="I19" s="32"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B20" s="4">
@@ -1236,10 +1236,10 @@
       <c r="F20" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G20" s="37" t="s">
+      <c r="G20" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="H20" s="37"/>
+      <c r="H20" s="32"/>
       <c r="I20" s="1" t="s">
         <v>14</v>
       </c>
@@ -1355,14 +1355,14 @@
       <c r="C25" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D25" s="37" t="s">
+      <c r="D25" s="32" t="s">
         <v>26</v>
       </c>
-      <c r="E25" s="37"/>
-      <c r="F25" s="37"/>
-      <c r="G25" s="37"/>
-      <c r="H25" s="37"/>
-      <c r="I25" s="37"/>
+      <c r="E25" s="32"/>
+      <c r="F25" s="32"/>
+      <c r="G25" s="32"/>
+      <c r="H25" s="32"/>
+      <c r="I25" s="32"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B26" s="4">
@@ -1406,10 +1406,10 @@
       <c r="F27" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G27" s="37" t="s">
+      <c r="G27" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="H27" s="37"/>
+      <c r="H27" s="32"/>
       <c r="I27" s="1" t="s">
         <v>14</v>
       </c>
@@ -1473,14 +1473,14 @@
       <c r="C30" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D30" s="36" t="s">
+      <c r="D30" s="33" t="s">
         <v>20</v>
       </c>
-      <c r="E30" s="36"/>
-      <c r="F30" s="36"/>
-      <c r="G30" s="36"/>
-      <c r="H30" s="36"/>
-      <c r="I30" s="36"/>
+      <c r="E30" s="33"/>
+      <c r="F30" s="33"/>
+      <c r="G30" s="33"/>
+      <c r="H30" s="33"/>
+      <c r="I30" s="33"/>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B31" s="4">
@@ -1489,14 +1489,14 @@
       <c r="C31" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D31" s="36" t="s">
+      <c r="D31" s="33" t="s">
         <v>20</v>
       </c>
-      <c r="E31" s="36"/>
-      <c r="F31" s="36"/>
-      <c r="G31" s="36"/>
-      <c r="H31" s="36"/>
-      <c r="I31" s="36"/>
+      <c r="E31" s="33"/>
+      <c r="F31" s="33"/>
+      <c r="G31" s="33"/>
+      <c r="H31" s="33"/>
+      <c r="I31" s="33"/>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B32" s="4">
@@ -1531,14 +1531,14 @@
       <c r="C33" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D33" s="36" t="s">
+      <c r="D33" s="33" t="s">
         <v>20</v>
       </c>
-      <c r="E33" s="36"/>
-      <c r="F33" s="36"/>
-      <c r="G33" s="36"/>
-      <c r="H33" s="36"/>
-      <c r="I33" s="36"/>
+      <c r="E33" s="33"/>
+      <c r="F33" s="33"/>
+      <c r="G33" s="33"/>
+      <c r="H33" s="33"/>
+      <c r="I33" s="33"/>
     </row>
     <row r="34" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B34" s="4">
@@ -1582,10 +1582,10 @@
       <c r="F35" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G35" s="36" t="s">
+      <c r="G35" s="33" t="s">
         <v>18</v>
       </c>
-      <c r="H35" s="36"/>
+      <c r="H35" s="33"/>
       <c r="I35" s="1" t="s">
         <v>14</v>
       </c>
@@ -1701,14 +1701,14 @@
       <c r="C40" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D40" s="36" t="s">
+      <c r="D40" s="33" t="s">
         <v>20</v>
       </c>
-      <c r="E40" s="36"/>
-      <c r="F40" s="36"/>
-      <c r="G40" s="36"/>
-      <c r="H40" s="36"/>
-      <c r="I40" s="36"/>
+      <c r="E40" s="33"/>
+      <c r="F40" s="33"/>
+      <c r="G40" s="33"/>
+      <c r="H40" s="33"/>
+      <c r="I40" s="33"/>
     </row>
     <row r="41" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B41" s="4">
@@ -1752,10 +1752,10 @@
       <c r="F42" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G42" s="36" t="s">
+      <c r="G42" s="33" t="s">
         <v>28</v>
       </c>
-      <c r="H42" s="36"/>
+      <c r="H42" s="33"/>
       <c r="I42" s="1" t="s">
         <v>15</v>
       </c>
@@ -1767,14 +1767,14 @@
       <c r="C43" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D43" s="36" t="s">
+      <c r="D43" s="33" t="s">
         <v>20</v>
       </c>
-      <c r="E43" s="36"/>
-      <c r="F43" s="36"/>
-      <c r="G43" s="36"/>
-      <c r="H43" s="36"/>
-      <c r="I43" s="36"/>
+      <c r="E43" s="33"/>
+      <c r="F43" s="33"/>
+      <c r="G43" s="33"/>
+      <c r="H43" s="33"/>
+      <c r="I43" s="33"/>
     </row>
     <row r="44" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B44" s="4">
@@ -1838,14 +1838,14 @@
       <c r="C46" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D46" s="36" t="s">
+      <c r="D46" s="33" t="s">
         <v>20</v>
       </c>
-      <c r="E46" s="36"/>
-      <c r="F46" s="36"/>
-      <c r="G46" s="36"/>
-      <c r="H46" s="36"/>
-      <c r="I46" s="36"/>
+      <c r="E46" s="33"/>
+      <c r="F46" s="33"/>
+      <c r="G46" s="33"/>
+      <c r="H46" s="33"/>
+      <c r="I46" s="33"/>
     </row>
     <row r="47" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B47" s="4">
@@ -1854,14 +1854,14 @@
       <c r="C47" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D47" s="27" t="s">
+      <c r="D47" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E47" s="28"/>
-      <c r="F47" s="28"/>
-      <c r="G47" s="28"/>
-      <c r="H47" s="28"/>
-      <c r="I47" s="29"/>
+      <c r="E47" s="24"/>
+      <c r="F47" s="24"/>
+      <c r="G47" s="24"/>
+      <c r="H47" s="24"/>
+      <c r="I47" s="25"/>
     </row>
     <row r="48" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B48" s="4">
@@ -1905,10 +1905,10 @@
       <c r="F49" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G49" s="27" t="s">
+      <c r="G49" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="H49" s="29"/>
+      <c r="H49" s="25"/>
       <c r="I49" s="1" t="s">
         <v>30</v>
       </c>
@@ -2050,14 +2050,14 @@
       <c r="C55" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="D55" s="28" t="s">
+      <c r="D55" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="E55" s="28"/>
-      <c r="F55" s="28"/>
-      <c r="G55" s="28"/>
-      <c r="H55" s="28"/>
-      <c r="I55" s="28"/>
+      <c r="E55" s="24"/>
+      <c r="F55" s="24"/>
+      <c r="G55" s="24"/>
+      <c r="H55" s="24"/>
+      <c r="I55" s="24"/>
     </row>
     <row r="56" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B56" s="4">
@@ -2101,10 +2101,10 @@
       <c r="F57" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G57" s="27" t="s">
+      <c r="G57" s="23" t="s">
         <v>37</v>
       </c>
-      <c r="H57" s="29"/>
+      <c r="H57" s="25"/>
       <c r="I57" s="1" t="s">
         <v>36</v>
       </c>
@@ -2168,14 +2168,14 @@
       <c r="C60" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D60" s="27" t="s">
+      <c r="D60" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E60" s="28"/>
-      <c r="F60" s="28"/>
-      <c r="G60" s="28"/>
-      <c r="H60" s="28"/>
-      <c r="I60" s="29"/>
+      <c r="E60" s="24"/>
+      <c r="F60" s="24"/>
+      <c r="G60" s="24"/>
+      <c r="H60" s="24"/>
+      <c r="I60" s="25"/>
     </row>
     <row r="61" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B61" s="4">
@@ -2184,14 +2184,14 @@
       <c r="C61" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D61" s="27" t="s">
+      <c r="D61" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E61" s="28"/>
-      <c r="F61" s="28"/>
-      <c r="G61" s="28"/>
-      <c r="H61" s="28"/>
-      <c r="I61" s="29"/>
+      <c r="E61" s="24"/>
+      <c r="F61" s="24"/>
+      <c r="G61" s="24"/>
+      <c r="H61" s="24"/>
+      <c r="I61" s="25"/>
     </row>
     <row r="62" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B62" s="4">
@@ -2200,14 +2200,14 @@
       <c r="C62" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D62" s="27" t="s">
+      <c r="D62" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E62" s="28"/>
-      <c r="F62" s="28"/>
-      <c r="G62" s="28"/>
-      <c r="H62" s="28"/>
-      <c r="I62" s="29"/>
+      <c r="E62" s="24"/>
+      <c r="F62" s="24"/>
+      <c r="G62" s="24"/>
+      <c r="H62" s="24"/>
+      <c r="I62" s="25"/>
     </row>
     <row r="63" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B63" s="4">
@@ -2251,10 +2251,10 @@
       <c r="F64" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G64" s="27" t="s">
+      <c r="G64" s="23" t="s">
         <v>37</v>
       </c>
-      <c r="H64" s="29"/>
+      <c r="H64" s="25"/>
       <c r="I64" s="1" t="s">
         <v>14</v>
       </c>
@@ -2292,13 +2292,13 @@
       <c r="C66" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D66" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="E66" s="28"/>
-      <c r="F66" s="28"/>
-      <c r="G66" s="28"/>
-      <c r="H66" s="29"/>
+      <c r="D66" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="E66" s="24"/>
+      <c r="F66" s="24"/>
+      <c r="G66" s="24"/>
+      <c r="H66" s="25"/>
       <c r="I66" s="1" t="s">
         <v>16</v>
       </c>
@@ -2310,18 +2310,18 @@
       <c r="C67" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D67" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="E67" s="28"/>
-      <c r="F67" s="29"/>
+      <c r="D67" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="E67" s="24"/>
+      <c r="F67" s="25"/>
       <c r="G67" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="H67" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="I67" s="29"/>
+      <c r="H67" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="I67" s="25"/>
     </row>
     <row r="68" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B68" s="4">
@@ -2336,12 +2336,12 @@
       <c r="E68" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F68" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="G68" s="28"/>
-      <c r="H68" s="28"/>
-      <c r="I68" s="29"/>
+      <c r="F68" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="G68" s="24"/>
+      <c r="H68" s="24"/>
+      <c r="I68" s="25"/>
     </row>
     <row r="69" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B69" s="4">
@@ -2350,14 +2350,14 @@
       <c r="C69" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D69" s="27" t="s">
+      <c r="D69" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E69" s="28"/>
-      <c r="F69" s="28"/>
-      <c r="G69" s="28"/>
-      <c r="H69" s="28"/>
-      <c r="I69" s="29"/>
+      <c r="E69" s="24"/>
+      <c r="F69" s="24"/>
+      <c r="G69" s="24"/>
+      <c r="H69" s="24"/>
+      <c r="I69" s="25"/>
     </row>
     <row r="70" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B70" s="4">
@@ -2366,10 +2366,10 @@
       <c r="C70" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D70" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="E70" s="29"/>
+      <c r="D70" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="E70" s="25"/>
       <c r="F70" s="3" t="s">
         <v>15</v>
       </c>
@@ -2399,10 +2399,10 @@
       <c r="F71" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G71" s="27" t="s">
+      <c r="G71" s="23" t="s">
         <v>37</v>
       </c>
-      <c r="H71" s="29"/>
+      <c r="H71" s="25"/>
       <c r="I71" s="1" t="s">
         <v>14</v>
       </c>
@@ -2440,14 +2440,14 @@
       <c r="C73" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D73" s="27" t="s">
+      <c r="D73" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E73" s="28"/>
-      <c r="F73" s="28"/>
-      <c r="G73" s="28"/>
-      <c r="H73" s="28"/>
-      <c r="I73" s="29"/>
+      <c r="E73" s="24"/>
+      <c r="F73" s="24"/>
+      <c r="G73" s="24"/>
+      <c r="H73" s="24"/>
+      <c r="I73" s="25"/>
     </row>
     <row r="74" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B74" s="4">
@@ -2456,11 +2456,11 @@
       <c r="C74" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D74" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="E74" s="28"/>
-      <c r="F74" s="29"/>
+      <c r="D74" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="E74" s="24"/>
+      <c r="F74" s="25"/>
       <c r="G74" s="3" t="s">
         <v>16</v>
       </c>
@@ -2496,14 +2496,14 @@
       <c r="C76" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D76" s="27" t="s">
+      <c r="D76" s="23" t="s">
         <v>39</v>
       </c>
-      <c r="E76" s="28"/>
-      <c r="F76" s="28"/>
-      <c r="G76" s="28"/>
-      <c r="H76" s="28"/>
-      <c r="I76" s="29"/>
+      <c r="E76" s="24"/>
+      <c r="F76" s="24"/>
+      <c r="G76" s="24"/>
+      <c r="H76" s="24"/>
+      <c r="I76" s="25"/>
     </row>
     <row r="77" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B77" s="4">
@@ -2512,14 +2512,14 @@
       <c r="C77" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D77" s="27" t="s">
+      <c r="D77" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E77" s="28"/>
-      <c r="F77" s="28"/>
-      <c r="G77" s="28"/>
-      <c r="H77" s="28"/>
-      <c r="I77" s="29"/>
+      <c r="E77" s="24"/>
+      <c r="F77" s="24"/>
+      <c r="G77" s="24"/>
+      <c r="H77" s="24"/>
+      <c r="I77" s="25"/>
     </row>
     <row r="78" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B78" s="4">
@@ -2528,14 +2528,14 @@
       <c r="C78" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D78" s="27" t="s">
+      <c r="D78" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E78" s="28"/>
-      <c r="F78" s="28"/>
-      <c r="G78" s="28"/>
-      <c r="H78" s="28"/>
-      <c r="I78" s="29"/>
+      <c r="E78" s="24"/>
+      <c r="F78" s="24"/>
+      <c r="G78" s="24"/>
+      <c r="H78" s="24"/>
+      <c r="I78" s="25"/>
     </row>
     <row r="79" spans="2:9" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B79" s="16" t="s">
@@ -2579,10 +2579,10 @@
       <c r="F80" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G80" s="27" t="s">
+      <c r="G80" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="H80" s="29"/>
+      <c r="H80" s="25"/>
       <c r="I80" s="1" t="s">
         <v>14</v>
       </c>
@@ -2603,10 +2603,10 @@
       <c r="F81" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="G81" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="H81" s="29"/>
+      <c r="G81" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="H81" s="25"/>
       <c r="I81" s="1" t="s">
         <v>16</v>
       </c>
@@ -2670,14 +2670,14 @@
       <c r="C84" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D84" s="27" t="s">
+      <c r="D84" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E84" s="28"/>
-      <c r="F84" s="28"/>
-      <c r="G84" s="28"/>
-      <c r="H84" s="28"/>
-      <c r="I84" s="29"/>
+      <c r="E84" s="24"/>
+      <c r="F84" s="24"/>
+      <c r="G84" s="24"/>
+      <c r="H84" s="24"/>
+      <c r="I84" s="25"/>
     </row>
     <row r="85" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B85" s="4">
@@ -2715,11 +2715,11 @@
       <c r="D86" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="E86" s="27" t="s">
+      <c r="E86" s="23" t="s">
         <v>43</v>
       </c>
-      <c r="F86" s="28"/>
-      <c r="G86" s="29"/>
+      <c r="F86" s="24"/>
+      <c r="G86" s="25"/>
       <c r="H86" s="3" t="s">
         <v>14</v>
       </c>
@@ -2734,18 +2734,18 @@
       <c r="C87" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D87" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="E87" s="29"/>
+      <c r="D87" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="E87" s="25"/>
       <c r="F87" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G87" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="H87" s="28"/>
-      <c r="I87" s="29"/>
+      <c r="G87" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="H87" s="24"/>
+      <c r="I87" s="25"/>
     </row>
     <row r="88" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B88" s="4">
@@ -2754,14 +2754,14 @@
       <c r="C88" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D88" s="27" t="s">
+      <c r="D88" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E88" s="28"/>
-      <c r="F88" s="28"/>
-      <c r="G88" s="28"/>
-      <c r="H88" s="28"/>
-      <c r="I88" s="29"/>
+      <c r="E88" s="24"/>
+      <c r="F88" s="24"/>
+      <c r="G88" s="24"/>
+      <c r="H88" s="24"/>
+      <c r="I88" s="25"/>
     </row>
     <row r="89" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B89" s="4">
@@ -2770,18 +2770,18 @@
       <c r="C89" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D89" s="27" t="s">
+      <c r="D89" s="23" t="s">
         <v>44</v>
       </c>
-      <c r="E89" s="28"/>
-      <c r="F89" s="29"/>
+      <c r="E89" s="24"/>
+      <c r="F89" s="25"/>
       <c r="G89" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="H89" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="I89" s="29"/>
+      <c r="H89" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="I89" s="25"/>
     </row>
     <row r="90" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B90" s="4">
@@ -2790,10 +2790,10 @@
       <c r="C90" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D90" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="E90" s="29"/>
+      <c r="D90" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="E90" s="25"/>
       <c r="F90" s="3" t="s">
         <v>16</v>
       </c>
@@ -2815,13 +2815,13 @@
       <c r="C91" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D91" s="27" t="s">
+      <c r="D91" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E91" s="28"/>
-      <c r="F91" s="28"/>
-      <c r="G91" s="28"/>
-      <c r="H91" s="29"/>
+      <c r="E91" s="24"/>
+      <c r="F91" s="24"/>
+      <c r="G91" s="24"/>
+      <c r="H91" s="25"/>
       <c r="I91" s="18" t="s">
         <v>45</v>
       </c>
@@ -2833,14 +2833,14 @@
       <c r="C92" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D92" s="27" t="s">
+      <c r="D92" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E92" s="28"/>
-      <c r="F92" s="28"/>
-      <c r="G92" s="28"/>
-      <c r="H92" s="28"/>
-      <c r="I92" s="29"/>
+      <c r="E92" s="24"/>
+      <c r="F92" s="24"/>
+      <c r="G92" s="24"/>
+      <c r="H92" s="24"/>
+      <c r="I92" s="25"/>
     </row>
     <row r="93" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B93" s="4">
@@ -2849,14 +2849,14 @@
       <c r="C93" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D93" s="27" t="s">
+      <c r="D93" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="E93" s="28"/>
-      <c r="F93" s="28"/>
-      <c r="G93" s="28"/>
-      <c r="H93" s="28"/>
-      <c r="I93" s="29"/>
+      <c r="E93" s="24"/>
+      <c r="F93" s="24"/>
+      <c r="G93" s="24"/>
+      <c r="H93" s="24"/>
+      <c r="I93" s="25"/>
     </row>
     <row r="94" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B94" s="4">
@@ -2865,14 +2865,14 @@
       <c r="C94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D94" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="E94" s="28"/>
-      <c r="F94" s="28"/>
-      <c r="G94" s="28"/>
-      <c r="H94" s="28"/>
-      <c r="I94" s="29"/>
+      <c r="D94" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="E94" s="24"/>
+      <c r="F94" s="24"/>
+      <c r="G94" s="24"/>
+      <c r="H94" s="24"/>
+      <c r="I94" s="25"/>
     </row>
     <row r="95" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B95" s="4">
@@ -2881,15 +2881,15 @@
       <c r="C95" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D95" s="27" t="s">
+      <c r="D95" s="23" t="s">
         <v>47</v>
       </c>
-      <c r="E95" s="28"/>
-      <c r="F95" s="29"/>
-      <c r="G95" s="27" t="s">
+      <c r="E95" s="24"/>
+      <c r="F95" s="25"/>
+      <c r="G95" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="H95" s="29"/>
+      <c r="H95" s="25"/>
       <c r="I95" s="1" t="s">
         <v>14</v>
       </c>
@@ -2901,14 +2901,14 @@
       <c r="C96" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D96" s="27" t="s">
+      <c r="D96" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E96" s="28"/>
-      <c r="F96" s="28"/>
-      <c r="G96" s="28"/>
-      <c r="H96" s="28"/>
-      <c r="I96" s="29"/>
+      <c r="E96" s="24"/>
+      <c r="F96" s="24"/>
+      <c r="G96" s="24"/>
+      <c r="H96" s="24"/>
+      <c r="I96" s="25"/>
     </row>
     <row r="97" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B97" s="4">
@@ -2917,14 +2917,14 @@
       <c r="C97" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D97" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="E97" s="28"/>
-      <c r="F97" s="28"/>
-      <c r="G97" s="28"/>
-      <c r="H97" s="28"/>
-      <c r="I97" s="29"/>
+      <c r="D97" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="E97" s="24"/>
+      <c r="F97" s="24"/>
+      <c r="G97" s="24"/>
+      <c r="H97" s="24"/>
+      <c r="I97" s="25"/>
     </row>
     <row r="98" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B98" s="4">
@@ -2933,14 +2933,14 @@
       <c r="C98" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D98" s="27" t="s">
+      <c r="D98" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E98" s="28"/>
-      <c r="F98" s="28"/>
-      <c r="G98" s="28"/>
-      <c r="H98" s="28"/>
-      <c r="I98" s="29"/>
+      <c r="E98" s="24"/>
+      <c r="F98" s="24"/>
+      <c r="G98" s="24"/>
+      <c r="H98" s="24"/>
+      <c r="I98" s="25"/>
     </row>
     <row r="99" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B99" s="4">
@@ -2949,12 +2949,12 @@
       <c r="C99" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D99" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="E99" s="28"/>
-      <c r="F99" s="28"/>
-      <c r="G99" s="29"/>
+      <c r="D99" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="E99" s="24"/>
+      <c r="F99" s="24"/>
+      <c r="G99" s="25"/>
       <c r="H99" s="3" t="s">
         <v>49</v>
       </c>
@@ -2978,21 +2978,21 @@
       <c r="F100" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="G100" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="H100" s="28"/>
-      <c r="I100" s="29"/>
+      <c r="G100" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="H100" s="24"/>
+      <c r="I100" s="25"/>
     </row>
     <row r="101" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B101" s="27"/>
-      <c r="C101" s="28"/>
-      <c r="D101" s="28"/>
-      <c r="E101" s="28"/>
-      <c r="F101" s="28"/>
-      <c r="G101" s="28"/>
-      <c r="H101" s="28"/>
-      <c r="I101" s="29"/>
+      <c r="B101" s="23"/>
+      <c r="C101" s="24"/>
+      <c r="D101" s="24"/>
+      <c r="E101" s="24"/>
+      <c r="F101" s="24"/>
+      <c r="G101" s="24"/>
+      <c r="H101" s="24"/>
+      <c r="I101" s="25"/>
     </row>
     <row r="102" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B102" s="3"/>
@@ -3011,10 +3011,10 @@
       <c r="C103" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D103" s="27" t="s">
+      <c r="D103" s="23" t="s">
         <v>51</v>
       </c>
-      <c r="E103" s="29"/>
+      <c r="E103" s="25"/>
       <c r="F103" s="3"/>
       <c r="G103" s="3"/>
       <c r="H103" s="3"/>
@@ -3027,10 +3027,10 @@
       <c r="C104" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D104" s="27" t="s">
+      <c r="D104" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="E104" s="29"/>
+      <c r="E104" s="25"/>
       <c r="F104" s="3"/>
       <c r="G104" s="3"/>
       <c r="H104" s="3"/>
@@ -3043,10 +3043,10 @@
       <c r="C105" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D105" s="27" t="s">
+      <c r="D105" s="23" t="s">
         <v>53</v>
       </c>
-      <c r="E105" s="29"/>
+      <c r="E105" s="25"/>
       <c r="F105" s="3"/>
       <c r="G105" s="3"/>
       <c r="H105" s="3"/>
@@ -3059,10 +3059,10 @@
       <c r="C106" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D106" s="27" t="s">
+      <c r="D106" s="23" t="s">
         <v>54</v>
       </c>
-      <c r="E106" s="29"/>
+      <c r="E106" s="25"/>
       <c r="F106" s="3"/>
       <c r="G106" s="3"/>
       <c r="H106" s="3"/>
@@ -3075,10 +3075,10 @@
       <c r="C107" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D107" s="27" t="s">
+      <c r="D107" s="23" t="s">
         <v>55</v>
       </c>
-      <c r="E107" s="29"/>
+      <c r="E107" s="25"/>
       <c r="F107" s="3"/>
       <c r="G107" s="3"/>
       <c r="H107" s="3"/>
@@ -3091,10 +3091,10 @@
       <c r="C108" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D108" s="27" t="s">
+      <c r="D108" s="23" t="s">
         <v>56</v>
       </c>
-      <c r="E108" s="29"/>
+      <c r="E108" s="25"/>
       <c r="F108" s="3"/>
       <c r="G108" s="3"/>
       <c r="H108" s="3"/>
@@ -3131,28 +3131,28 @@
       <c r="I111" s="20"/>
     </row>
     <row r="112" spans="2:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B112" s="30" t="s">
+      <c r="B112" s="34" t="s">
         <v>57</v>
       </c>
-      <c r="C112" s="31"/>
-      <c r="D112" s="31"/>
-      <c r="E112" s="31"/>
-      <c r="F112" s="31"/>
-      <c r="G112" s="31"/>
-      <c r="H112" s="31"/>
-      <c r="I112" s="31"/>
-      <c r="J112" s="32"/>
+      <c r="C112" s="35"/>
+      <c r="D112" s="35"/>
+      <c r="E112" s="35"/>
+      <c r="F112" s="35"/>
+      <c r="G112" s="35"/>
+      <c r="H112" s="35"/>
+      <c r="I112" s="35"/>
+      <c r="J112" s="36"/>
     </row>
     <row r="113" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B113" s="33"/>
-      <c r="C113" s="34"/>
-      <c r="D113" s="34"/>
-      <c r="E113" s="34"/>
-      <c r="F113" s="34"/>
-      <c r="G113" s="34"/>
-      <c r="H113" s="34"/>
-      <c r="I113" s="34"/>
-      <c r="J113" s="35"/>
+      <c r="B113" s="37"/>
+      <c r="C113" s="38"/>
+      <c r="D113" s="38"/>
+      <c r="E113" s="38"/>
+      <c r="F113" s="38"/>
+      <c r="G113" s="38"/>
+      <c r="H113" s="38"/>
+      <c r="I113" s="38"/>
+      <c r="J113" s="39"/>
     </row>
     <row r="114" spans="2:10" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B114" s="8" t="s">
@@ -3283,13 +3283,13 @@
       <c r="E118" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="F118" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="G118" s="28"/>
-      <c r="H118" s="28"/>
-      <c r="I118" s="28"/>
-      <c r="J118" s="29"/>
+      <c r="F118" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="G118" s="24"/>
+      <c r="H118" s="24"/>
+      <c r="I118" s="24"/>
+      <c r="J118" s="25"/>
     </row>
     <row r="119" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B119" s="4">
@@ -3327,13 +3327,13 @@
       <c r="C120" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D120" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="E120" s="28"/>
-      <c r="F120" s="28"/>
-      <c r="G120" s="28"/>
-      <c r="H120" s="29"/>
+      <c r="D120" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="E120" s="24"/>
+      <c r="F120" s="24"/>
+      <c r="G120" s="24"/>
+      <c r="H120" s="25"/>
       <c r="I120" s="1" t="s">
         <v>16</v>
       </c>
@@ -3348,15 +3348,15 @@
       <c r="C121" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D121" s="27" t="s">
+      <c r="D121" s="23" t="s">
         <v>65</v>
       </c>
-      <c r="E121" s="28"/>
-      <c r="F121" s="28"/>
-      <c r="G121" s="28"/>
-      <c r="H121" s="28"/>
-      <c r="I121" s="28"/>
-      <c r="J121" s="29"/>
+      <c r="E121" s="24"/>
+      <c r="F121" s="24"/>
+      <c r="G121" s="24"/>
+      <c r="H121" s="24"/>
+      <c r="I121" s="24"/>
+      <c r="J121" s="25"/>
     </row>
     <row r="122" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B122" s="4">
@@ -3403,12 +3403,12 @@
       <c r="F123" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="G123" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="H123" s="28"/>
-      <c r="I123" s="28"/>
-      <c r="J123" s="29"/>
+      <c r="G123" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="H123" s="24"/>
+      <c r="I123" s="24"/>
+      <c r="J123" s="25"/>
     </row>
     <row r="124" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B124" s="4">
@@ -3426,12 +3426,12 @@
       <c r="F124" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="G124" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="H124" s="28"/>
-      <c r="I124" s="28"/>
-      <c r="J124" s="29"/>
+      <c r="G124" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="H124" s="24"/>
+      <c r="I124" s="24"/>
+      <c r="J124" s="25"/>
     </row>
     <row r="125" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B125" s="4">
@@ -3446,13 +3446,13 @@
       <c r="E125" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="F125" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="G125" s="28"/>
-      <c r="H125" s="28"/>
-      <c r="I125" s="28"/>
-      <c r="J125" s="29"/>
+      <c r="F125" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="G125" s="24"/>
+      <c r="H125" s="24"/>
+      <c r="I125" s="24"/>
+      <c r="J125" s="25"/>
     </row>
     <row r="126" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B126" s="4">
@@ -3470,11 +3470,11 @@
       <c r="F126" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="G126" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="H126" s="28"/>
-      <c r="I126" s="29"/>
+      <c r="G126" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="H126" s="24"/>
+      <c r="I126" s="25"/>
       <c r="J126" s="1" t="s">
         <v>16</v>
       </c>
@@ -3492,13 +3492,13 @@
       <c r="E127" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="F127" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="G127" s="28"/>
-      <c r="H127" s="28"/>
-      <c r="I127" s="28"/>
-      <c r="J127" s="29"/>
+      <c r="F127" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="G127" s="24"/>
+      <c r="H127" s="24"/>
+      <c r="I127" s="24"/>
+      <c r="J127" s="25"/>
     </row>
     <row r="128" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B128" s="4">
@@ -3507,15 +3507,15 @@
       <c r="C128" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D128" s="27" t="s">
+      <c r="D128" s="23" t="s">
         <v>65</v>
       </c>
-      <c r="E128" s="28"/>
-      <c r="F128" s="28"/>
-      <c r="G128" s="28"/>
-      <c r="H128" s="28"/>
-      <c r="I128" s="28"/>
-      <c r="J128" s="29"/>
+      <c r="E128" s="24"/>
+      <c r="F128" s="24"/>
+      <c r="G128" s="24"/>
+      <c r="H128" s="24"/>
+      <c r="I128" s="24"/>
+      <c r="J128" s="25"/>
     </row>
     <row r="129" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B129" s="4">
@@ -3698,15 +3698,15 @@
       <c r="C135" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D135" s="27" t="s">
+      <c r="D135" s="23" t="s">
         <v>65</v>
       </c>
-      <c r="E135" s="28"/>
-      <c r="F135" s="28"/>
-      <c r="G135" s="28"/>
-      <c r="H135" s="28"/>
-      <c r="I135" s="28"/>
-      <c r="J135" s="29"/>
+      <c r="E135" s="24"/>
+      <c r="F135" s="24"/>
+      <c r="G135" s="24"/>
+      <c r="H135" s="24"/>
+      <c r="I135" s="24"/>
+      <c r="J135" s="25"/>
     </row>
     <row r="136" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B136" s="4">
@@ -3918,15 +3918,15 @@
       <c r="C143" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D143" s="27" t="s">
+      <c r="D143" s="23" t="s">
         <v>65</v>
       </c>
-      <c r="E143" s="28"/>
-      <c r="F143" s="28"/>
-      <c r="G143" s="28"/>
-      <c r="H143" s="28"/>
-      <c r="I143" s="28"/>
-      <c r="J143" s="29"/>
+      <c r="E143" s="24"/>
+      <c r="F143" s="24"/>
+      <c r="G143" s="24"/>
+      <c r="H143" s="24"/>
+      <c r="I143" s="24"/>
+      <c r="J143" s="25"/>
     </row>
     <row r="144" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B144" s="4">
@@ -4002,12 +4002,12 @@
       <c r="F146" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="G146" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="H146" s="28"/>
-      <c r="I146" s="28"/>
-      <c r="J146" s="29"/>
+      <c r="G146" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="H146" s="24"/>
+      <c r="I146" s="24"/>
+      <c r="J146" s="25"/>
     </row>
     <row r="147" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B147" s="4">
@@ -4074,15 +4074,15 @@
       <c r="C149" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D149" s="23" t="s">
+      <c r="D149" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="E149" s="24"/>
-      <c r="F149" s="24"/>
-      <c r="G149" s="24"/>
-      <c r="H149" s="24"/>
-      <c r="I149" s="24"/>
-      <c r="J149" s="38"/>
+      <c r="E149" s="27"/>
+      <c r="F149" s="27"/>
+      <c r="G149" s="27"/>
+      <c r="H149" s="27"/>
+      <c r="I149" s="27"/>
+      <c r="J149" s="28"/>
     </row>
     <row r="150" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B150" s="4">
@@ -4091,13 +4091,13 @@
       <c r="C150" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D150" s="25"/>
-      <c r="E150" s="26"/>
-      <c r="F150" s="26"/>
-      <c r="G150" s="26"/>
-      <c r="H150" s="26"/>
-      <c r="I150" s="26"/>
-      <c r="J150" s="39"/>
+      <c r="D150" s="29"/>
+      <c r="E150" s="30"/>
+      <c r="F150" s="30"/>
+      <c r="G150" s="30"/>
+      <c r="H150" s="30"/>
+      <c r="I150" s="30"/>
+      <c r="J150" s="31"/>
     </row>
     <row r="151" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B151" s="4">
@@ -4144,11 +4144,11 @@
       <c r="F152" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="G152" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="H152" s="28"/>
-      <c r="I152" s="29"/>
+      <c r="G152" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="H152" s="24"/>
+      <c r="I152" s="25"/>
       <c r="J152" s="1" t="s">
         <v>69</v>
       </c>
@@ -4276,15 +4276,15 @@
       <c r="C157" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D157" s="27" t="s">
+      <c r="D157" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E157" s="28"/>
-      <c r="F157" s="28"/>
-      <c r="G157" s="28"/>
-      <c r="H157" s="28"/>
-      <c r="I157" s="28"/>
-      <c r="J157" s="29"/>
+      <c r="E157" s="24"/>
+      <c r="F157" s="24"/>
+      <c r="G157" s="24"/>
+      <c r="H157" s="24"/>
+      <c r="I157" s="24"/>
+      <c r="J157" s="25"/>
     </row>
     <row r="158" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B158" s="4">
@@ -4465,15 +4465,15 @@
       <c r="C164" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D164" s="27" t="s">
+      <c r="D164" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E164" s="28"/>
-      <c r="F164" s="28"/>
-      <c r="G164" s="28"/>
-      <c r="H164" s="28"/>
-      <c r="I164" s="28"/>
-      <c r="J164" s="29"/>
+      <c r="E164" s="24"/>
+      <c r="F164" s="24"/>
+      <c r="G164" s="24"/>
+      <c r="H164" s="24"/>
+      <c r="I164" s="24"/>
+      <c r="J164" s="25"/>
     </row>
     <row r="165" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B165" s="4">
@@ -4671,15 +4671,15 @@
       <c r="C172" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D172" s="27" t="s">
+      <c r="D172" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E172" s="28"/>
-      <c r="F172" s="28"/>
-      <c r="G172" s="28"/>
-      <c r="H172" s="28"/>
-      <c r="I172" s="28"/>
-      <c r="J172" s="29"/>
+      <c r="E172" s="24"/>
+      <c r="F172" s="24"/>
+      <c r="G172" s="24"/>
+      <c r="H172" s="24"/>
+      <c r="I172" s="24"/>
+      <c r="J172" s="25"/>
     </row>
     <row r="173" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B173" s="4">
@@ -4743,44 +4743,44 @@
       <c r="B175" s="4">
         <v>45903</v>
       </c>
-      <c r="C175" s="23" t="s">
+      <c r="C175" s="26" t="s">
         <v>39</v>
       </c>
-      <c r="D175" s="24"/>
-      <c r="E175" s="24"/>
-      <c r="F175" s="24"/>
-      <c r="G175" s="24"/>
-      <c r="H175" s="24"/>
-      <c r="I175" s="24"/>
-      <c r="J175" s="24"/>
+      <c r="D175" s="27"/>
+      <c r="E175" s="27"/>
+      <c r="F175" s="27"/>
+      <c r="G175" s="27"/>
+      <c r="H175" s="27"/>
+      <c r="I175" s="27"/>
+      <c r="J175" s="27"/>
     </row>
     <row r="176" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B176" s="4">
         <v>45904</v>
       </c>
-      <c r="C176" s="25"/>
-      <c r="D176" s="26"/>
-      <c r="E176" s="26"/>
-      <c r="F176" s="26"/>
-      <c r="G176" s="26"/>
-      <c r="H176" s="26"/>
-      <c r="I176" s="26"/>
-      <c r="J176" s="26"/>
+      <c r="C176" s="29"/>
+      <c r="D176" s="30"/>
+      <c r="E176" s="30"/>
+      <c r="F176" s="30"/>
+      <c r="G176" s="30"/>
+      <c r="H176" s="30"/>
+      <c r="I176" s="30"/>
+      <c r="J176" s="30"/>
     </row>
     <row r="177" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B177" s="4">
         <v>45905</v>
       </c>
-      <c r="C177" s="27" t="s">
+      <c r="C177" s="23" t="s">
         <v>39</v>
       </c>
-      <c r="D177" s="28"/>
-      <c r="E177" s="28"/>
-      <c r="F177" s="28"/>
-      <c r="G177" s="28"/>
-      <c r="H177" s="28"/>
-      <c r="I177" s="28"/>
-      <c r="J177" s="29"/>
+      <c r="D177" s="24"/>
+      <c r="E177" s="24"/>
+      <c r="F177" s="24"/>
+      <c r="G177" s="24"/>
+      <c r="H177" s="24"/>
+      <c r="I177" s="24"/>
+      <c r="J177" s="25"/>
     </row>
     <row r="178" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B178" s="4">
@@ -4825,7 +4825,9 @@
       <c r="J179" s="1"/>
     </row>
     <row r="180" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B180" s="3"/>
+      <c r="B180" s="4">
+        <v>45908</v>
+      </c>
       <c r="C180" s="3"/>
       <c r="D180" s="3"/>
       <c r="E180" s="3"/>
@@ -4836,7 +4838,9 @@
       <c r="J180" s="1"/>
     </row>
     <row r="181" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B181" s="3"/>
+      <c r="B181" s="4">
+        <v>45909</v>
+      </c>
       <c r="C181" s="3"/>
       <c r="D181" s="3"/>
       <c r="E181" s="3"/>
@@ -4847,7 +4851,9 @@
       <c r="J181" s="1"/>
     </row>
     <row r="182" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B182" s="3"/>
+      <c r="B182" s="4">
+        <v>45910</v>
+      </c>
       <c r="C182" s="3"/>
       <c r="D182" s="3"/>
       <c r="E182" s="3"/>
@@ -4858,7 +4864,9 @@
       <c r="J182" s="1"/>
     </row>
     <row r="183" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B183" s="3"/>
+      <c r="B183" s="4">
+        <v>45911</v>
+      </c>
       <c r="C183" s="3"/>
       <c r="D183" s="3"/>
       <c r="E183" s="3"/>
@@ -7433,6 +7441,77 @@
     </row>
   </sheetData>
   <mergeCells count="87">
+    <mergeCell ref="C175:J176"/>
+    <mergeCell ref="D164:J164"/>
+    <mergeCell ref="D157:J157"/>
+    <mergeCell ref="D143:J143"/>
+    <mergeCell ref="D135:J135"/>
+    <mergeCell ref="D172:J172"/>
+    <mergeCell ref="G146:J146"/>
+    <mergeCell ref="D108:E108"/>
+    <mergeCell ref="B112:J113"/>
+    <mergeCell ref="G124:J124"/>
+    <mergeCell ref="D120:H120"/>
+    <mergeCell ref="G123:J123"/>
+    <mergeCell ref="D121:J121"/>
+    <mergeCell ref="D31:I31"/>
+    <mergeCell ref="G35:H35"/>
+    <mergeCell ref="D40:I40"/>
+    <mergeCell ref="D33:I33"/>
+    <mergeCell ref="D46:I46"/>
+    <mergeCell ref="D43:I43"/>
+    <mergeCell ref="D78:I78"/>
+    <mergeCell ref="G71:H71"/>
+    <mergeCell ref="D76:I76"/>
+    <mergeCell ref="D66:H66"/>
+    <mergeCell ref="D77:I77"/>
+    <mergeCell ref="D73:I73"/>
+    <mergeCell ref="D70:E70"/>
+    <mergeCell ref="D74:F74"/>
+    <mergeCell ref="D84:I84"/>
+    <mergeCell ref="D69:I69"/>
+    <mergeCell ref="D8:I8"/>
+    <mergeCell ref="D9:I9"/>
+    <mergeCell ref="D10:I10"/>
+    <mergeCell ref="D11:I11"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="D14:I14"/>
+    <mergeCell ref="G27:H27"/>
+    <mergeCell ref="D25:I25"/>
+    <mergeCell ref="G20:H20"/>
+    <mergeCell ref="D19:I19"/>
+    <mergeCell ref="D18:I18"/>
+    <mergeCell ref="D30:I30"/>
+    <mergeCell ref="G80:H80"/>
+    <mergeCell ref="G42:H42"/>
+    <mergeCell ref="D60:I60"/>
+    <mergeCell ref="D62:I62"/>
+    <mergeCell ref="D61:I61"/>
+    <mergeCell ref="G49:H49"/>
+    <mergeCell ref="D47:I47"/>
+    <mergeCell ref="D55:I55"/>
+    <mergeCell ref="G57:H57"/>
+    <mergeCell ref="G64:H64"/>
+    <mergeCell ref="D96:I96"/>
+    <mergeCell ref="D95:F95"/>
+    <mergeCell ref="G95:H95"/>
+    <mergeCell ref="D92:I92"/>
+    <mergeCell ref="D93:I93"/>
+    <mergeCell ref="D90:E90"/>
+    <mergeCell ref="D91:H91"/>
+    <mergeCell ref="E86:G86"/>
+    <mergeCell ref="D88:I88"/>
+    <mergeCell ref="H67:I67"/>
+    <mergeCell ref="G81:H81"/>
+    <mergeCell ref="D67:F67"/>
+    <mergeCell ref="F68:I68"/>
+    <mergeCell ref="D87:E87"/>
+    <mergeCell ref="G87:I87"/>
+    <mergeCell ref="D98:I98"/>
+    <mergeCell ref="D94:I94"/>
+    <mergeCell ref="H89:I89"/>
+    <mergeCell ref="D89:F89"/>
+    <mergeCell ref="D97:I97"/>
     <mergeCell ref="C177:J177"/>
     <mergeCell ref="D106:E106"/>
     <mergeCell ref="D99:G99"/>
@@ -7449,77 +7528,6 @@
     <mergeCell ref="F118:J118"/>
     <mergeCell ref="G152:I152"/>
     <mergeCell ref="D149:J150"/>
-    <mergeCell ref="D98:I98"/>
-    <mergeCell ref="D94:I94"/>
-    <mergeCell ref="H89:I89"/>
-    <mergeCell ref="D89:F89"/>
-    <mergeCell ref="D97:I97"/>
-    <mergeCell ref="G64:H64"/>
-    <mergeCell ref="D96:I96"/>
-    <mergeCell ref="D95:F95"/>
-    <mergeCell ref="G95:H95"/>
-    <mergeCell ref="D92:I92"/>
-    <mergeCell ref="D93:I93"/>
-    <mergeCell ref="D90:E90"/>
-    <mergeCell ref="D91:H91"/>
-    <mergeCell ref="E86:G86"/>
-    <mergeCell ref="D88:I88"/>
-    <mergeCell ref="H67:I67"/>
-    <mergeCell ref="G81:H81"/>
-    <mergeCell ref="D67:F67"/>
-    <mergeCell ref="F68:I68"/>
-    <mergeCell ref="D87:E87"/>
-    <mergeCell ref="G87:I87"/>
-    <mergeCell ref="D60:I60"/>
-    <mergeCell ref="D62:I62"/>
-    <mergeCell ref="D61:I61"/>
-    <mergeCell ref="G49:H49"/>
-    <mergeCell ref="D47:I47"/>
-    <mergeCell ref="D55:I55"/>
-    <mergeCell ref="G57:H57"/>
-    <mergeCell ref="D84:I84"/>
-    <mergeCell ref="D69:I69"/>
-    <mergeCell ref="D8:I8"/>
-    <mergeCell ref="D9:I9"/>
-    <mergeCell ref="D10:I10"/>
-    <mergeCell ref="D11:I11"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="D14:I14"/>
-    <mergeCell ref="G27:H27"/>
-    <mergeCell ref="D25:I25"/>
-    <mergeCell ref="G20:H20"/>
-    <mergeCell ref="D19:I19"/>
-    <mergeCell ref="D18:I18"/>
-    <mergeCell ref="D30:I30"/>
-    <mergeCell ref="G80:H80"/>
-    <mergeCell ref="G42:H42"/>
-    <mergeCell ref="D78:I78"/>
-    <mergeCell ref="G71:H71"/>
-    <mergeCell ref="D76:I76"/>
-    <mergeCell ref="D66:H66"/>
-    <mergeCell ref="D77:I77"/>
-    <mergeCell ref="D73:I73"/>
-    <mergeCell ref="D70:E70"/>
-    <mergeCell ref="D74:F74"/>
-    <mergeCell ref="D31:I31"/>
-    <mergeCell ref="G35:H35"/>
-    <mergeCell ref="D40:I40"/>
-    <mergeCell ref="D33:I33"/>
-    <mergeCell ref="D46:I46"/>
-    <mergeCell ref="D43:I43"/>
-    <mergeCell ref="D108:E108"/>
-    <mergeCell ref="B112:J113"/>
-    <mergeCell ref="G124:J124"/>
-    <mergeCell ref="D120:H120"/>
-    <mergeCell ref="G123:J123"/>
-    <mergeCell ref="D121:J121"/>
-    <mergeCell ref="C175:J176"/>
-    <mergeCell ref="D164:J164"/>
-    <mergeCell ref="D157:J157"/>
-    <mergeCell ref="D143:J143"/>
-    <mergeCell ref="D135:J135"/>
-    <mergeCell ref="D172:J172"/>
-    <mergeCell ref="G146:J146"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/attendance_sheet.xlsx
+++ b/attendance_sheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\repositary\3rd_Year_5th_Semester\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33AE0A5C-5C4C-438D-8217-46CECCF33320}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CC595A4-2F2C-4F4F-A4CC-E8D8B10A4F65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{EB654061-A886-47D1-BF86-9B1A84FCE7FB}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="880" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="899" uniqueCount="74">
   <si>
     <t>Date</t>
   </si>
@@ -256,6 +256,9 @@
   </si>
   <si>
     <t>2 class</t>
+  </si>
+  <si>
+    <t>1 class P</t>
   </si>
 </sst>
 </file>
@@ -535,22 +538,10 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
@@ -559,13 +550,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -584,6 +575,18 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -987,14 +990,14 @@
       <c r="C8" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D8" s="32" t="s">
+      <c r="D8" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="E8" s="32"/>
-      <c r="F8" s="32"/>
-      <c r="G8" s="32"/>
-      <c r="H8" s="32"/>
-      <c r="I8" s="32"/>
+      <c r="E8" s="37"/>
+      <c r="F8" s="37"/>
+      <c r="G8" s="37"/>
+      <c r="H8" s="37"/>
+      <c r="I8" s="37"/>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B9" s="4">
@@ -1003,14 +1006,14 @@
       <c r="C9" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D9" s="32" t="s">
+      <c r="D9" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="E9" s="32"/>
-      <c r="F9" s="32"/>
-      <c r="G9" s="32"/>
-      <c r="H9" s="32"/>
-      <c r="I9" s="32"/>
+      <c r="E9" s="37"/>
+      <c r="F9" s="37"/>
+      <c r="G9" s="37"/>
+      <c r="H9" s="37"/>
+      <c r="I9" s="37"/>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B10" s="4">
@@ -1019,14 +1022,14 @@
       <c r="C10" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D10" s="32" t="s">
+      <c r="D10" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="E10" s="32"/>
-      <c r="F10" s="32"/>
-      <c r="G10" s="32"/>
-      <c r="H10" s="32"/>
-      <c r="I10" s="32"/>
+      <c r="E10" s="37"/>
+      <c r="F10" s="37"/>
+      <c r="G10" s="37"/>
+      <c r="H10" s="37"/>
+      <c r="I10" s="37"/>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B11" s="4">
@@ -1035,14 +1038,14 @@
       <c r="C11" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D11" s="32" t="s">
+      <c r="D11" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="E11" s="32"/>
-      <c r="F11" s="32"/>
-      <c r="G11" s="32"/>
-      <c r="H11" s="32"/>
-      <c r="I11" s="32"/>
+      <c r="E11" s="37"/>
+      <c r="F11" s="37"/>
+      <c r="G11" s="37"/>
+      <c r="H11" s="37"/>
+      <c r="I11" s="37"/>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B12" s="4">
@@ -1086,10 +1089,10 @@
       <c r="F13" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="G13" s="32" t="s">
+      <c r="G13" s="37" t="s">
         <v>18</v>
       </c>
-      <c r="H13" s="32"/>
+      <c r="H13" s="37"/>
       <c r="I13" s="1" t="s">
         <v>14</v>
       </c>
@@ -1101,14 +1104,14 @@
       <c r="C14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D14" s="32" t="s">
+      <c r="D14" s="37" t="s">
         <v>19</v>
       </c>
-      <c r="E14" s="32"/>
-      <c r="F14" s="32"/>
-      <c r="G14" s="32"/>
-      <c r="H14" s="32"/>
-      <c r="I14" s="32"/>
+      <c r="E14" s="37"/>
+      <c r="F14" s="37"/>
+      <c r="G14" s="37"/>
+      <c r="H14" s="37"/>
+      <c r="I14" s="37"/>
     </row>
     <row r="15" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B15" s="4">
@@ -1195,14 +1198,14 @@
       <c r="C18" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D18" s="32" t="s">
+      <c r="D18" s="37" t="s">
         <v>23</v>
       </c>
-      <c r="E18" s="32"/>
-      <c r="F18" s="32"/>
-      <c r="G18" s="32"/>
-      <c r="H18" s="32"/>
-      <c r="I18" s="32"/>
+      <c r="E18" s="37"/>
+      <c r="F18" s="37"/>
+      <c r="G18" s="37"/>
+      <c r="H18" s="37"/>
+      <c r="I18" s="37"/>
     </row>
     <row r="19" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B19" s="4">
@@ -1211,14 +1214,14 @@
       <c r="C19" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D19" s="32" t="s">
+      <c r="D19" s="37" t="s">
         <v>23</v>
       </c>
-      <c r="E19" s="32"/>
-      <c r="F19" s="32"/>
-      <c r="G19" s="32"/>
-      <c r="H19" s="32"/>
-      <c r="I19" s="32"/>
+      <c r="E19" s="37"/>
+      <c r="F19" s="37"/>
+      <c r="G19" s="37"/>
+      <c r="H19" s="37"/>
+      <c r="I19" s="37"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B20" s="4">
@@ -1236,10 +1239,10 @@
       <c r="F20" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G20" s="32" t="s">
+      <c r="G20" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="H20" s="32"/>
+      <c r="H20" s="37"/>
       <c r="I20" s="1" t="s">
         <v>14</v>
       </c>
@@ -1355,14 +1358,14 @@
       <c r="C25" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D25" s="32" t="s">
+      <c r="D25" s="37" t="s">
         <v>26</v>
       </c>
-      <c r="E25" s="32"/>
-      <c r="F25" s="32"/>
-      <c r="G25" s="32"/>
-      <c r="H25" s="32"/>
-      <c r="I25" s="32"/>
+      <c r="E25" s="37"/>
+      <c r="F25" s="37"/>
+      <c r="G25" s="37"/>
+      <c r="H25" s="37"/>
+      <c r="I25" s="37"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B26" s="4">
@@ -1406,10 +1409,10 @@
       <c r="F27" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G27" s="32" t="s">
+      <c r="G27" s="37" t="s">
         <v>18</v>
       </c>
-      <c r="H27" s="32"/>
+      <c r="H27" s="37"/>
       <c r="I27" s="1" t="s">
         <v>14</v>
       </c>
@@ -1473,14 +1476,14 @@
       <c r="C30" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D30" s="33" t="s">
+      <c r="D30" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="E30" s="33"/>
-      <c r="F30" s="33"/>
-      <c r="G30" s="33"/>
-      <c r="H30" s="33"/>
-      <c r="I30" s="33"/>
+      <c r="E30" s="36"/>
+      <c r="F30" s="36"/>
+      <c r="G30" s="36"/>
+      <c r="H30" s="36"/>
+      <c r="I30" s="36"/>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B31" s="4">
@@ -1489,14 +1492,14 @@
       <c r="C31" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D31" s="33" t="s">
+      <c r="D31" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="E31" s="33"/>
-      <c r="F31" s="33"/>
-      <c r="G31" s="33"/>
-      <c r="H31" s="33"/>
-      <c r="I31" s="33"/>
+      <c r="E31" s="36"/>
+      <c r="F31" s="36"/>
+      <c r="G31" s="36"/>
+      <c r="H31" s="36"/>
+      <c r="I31" s="36"/>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B32" s="4">
@@ -1531,14 +1534,14 @@
       <c r="C33" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D33" s="33" t="s">
+      <c r="D33" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="E33" s="33"/>
-      <c r="F33" s="33"/>
-      <c r="G33" s="33"/>
-      <c r="H33" s="33"/>
-      <c r="I33" s="33"/>
+      <c r="E33" s="36"/>
+      <c r="F33" s="36"/>
+      <c r="G33" s="36"/>
+      <c r="H33" s="36"/>
+      <c r="I33" s="36"/>
     </row>
     <row r="34" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B34" s="4">
@@ -1582,10 +1585,10 @@
       <c r="F35" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G35" s="33" t="s">
+      <c r="G35" s="36" t="s">
         <v>18</v>
       </c>
-      <c r="H35" s="33"/>
+      <c r="H35" s="36"/>
       <c r="I35" s="1" t="s">
         <v>14</v>
       </c>
@@ -1701,14 +1704,14 @@
       <c r="C40" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D40" s="33" t="s">
+      <c r="D40" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="E40" s="33"/>
-      <c r="F40" s="33"/>
-      <c r="G40" s="33"/>
-      <c r="H40" s="33"/>
-      <c r="I40" s="33"/>
+      <c r="E40" s="36"/>
+      <c r="F40" s="36"/>
+      <c r="G40" s="36"/>
+      <c r="H40" s="36"/>
+      <c r="I40" s="36"/>
     </row>
     <row r="41" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B41" s="4">
@@ -1752,10 +1755,10 @@
       <c r="F42" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G42" s="33" t="s">
+      <c r="G42" s="36" t="s">
         <v>28</v>
       </c>
-      <c r="H42" s="33"/>
+      <c r="H42" s="36"/>
       <c r="I42" s="1" t="s">
         <v>15</v>
       </c>
@@ -1767,14 +1770,14 @@
       <c r="C43" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D43" s="33" t="s">
+      <c r="D43" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="E43" s="33"/>
-      <c r="F43" s="33"/>
-      <c r="G43" s="33"/>
-      <c r="H43" s="33"/>
-      <c r="I43" s="33"/>
+      <c r="E43" s="36"/>
+      <c r="F43" s="36"/>
+      <c r="G43" s="36"/>
+      <c r="H43" s="36"/>
+      <c r="I43" s="36"/>
     </row>
     <row r="44" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B44" s="4">
@@ -1838,14 +1841,14 @@
       <c r="C46" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D46" s="33" t="s">
+      <c r="D46" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="E46" s="33"/>
-      <c r="F46" s="33"/>
-      <c r="G46" s="33"/>
-      <c r="H46" s="33"/>
-      <c r="I46" s="33"/>
+      <c r="E46" s="36"/>
+      <c r="F46" s="36"/>
+      <c r="G46" s="36"/>
+      <c r="H46" s="36"/>
+      <c r="I46" s="36"/>
     </row>
     <row r="47" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B47" s="4">
@@ -1854,14 +1857,14 @@
       <c r="C47" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D47" s="23" t="s">
+      <c r="D47" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="E47" s="24"/>
-      <c r="F47" s="24"/>
-      <c r="G47" s="24"/>
-      <c r="H47" s="24"/>
-      <c r="I47" s="25"/>
+      <c r="E47" s="28"/>
+      <c r="F47" s="28"/>
+      <c r="G47" s="28"/>
+      <c r="H47" s="28"/>
+      <c r="I47" s="29"/>
     </row>
     <row r="48" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B48" s="4">
@@ -1905,10 +1908,10 @@
       <c r="F49" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G49" s="23" t="s">
+      <c r="G49" s="27" t="s">
         <v>29</v>
       </c>
-      <c r="H49" s="25"/>
+      <c r="H49" s="29"/>
       <c r="I49" s="1" t="s">
         <v>30</v>
       </c>
@@ -2050,14 +2053,14 @@
       <c r="C55" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="D55" s="24" t="s">
+      <c r="D55" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="E55" s="24"/>
-      <c r="F55" s="24"/>
-      <c r="G55" s="24"/>
-      <c r="H55" s="24"/>
-      <c r="I55" s="24"/>
+      <c r="E55" s="28"/>
+      <c r="F55" s="28"/>
+      <c r="G55" s="28"/>
+      <c r="H55" s="28"/>
+      <c r="I55" s="28"/>
     </row>
     <row r="56" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B56" s="4">
@@ -2101,10 +2104,10 @@
       <c r="F57" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G57" s="23" t="s">
+      <c r="G57" s="27" t="s">
         <v>37</v>
       </c>
-      <c r="H57" s="25"/>
+      <c r="H57" s="29"/>
       <c r="I57" s="1" t="s">
         <v>36</v>
       </c>
@@ -2168,14 +2171,14 @@
       <c r="C60" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D60" s="23" t="s">
+      <c r="D60" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="E60" s="24"/>
-      <c r="F60" s="24"/>
-      <c r="G60" s="24"/>
-      <c r="H60" s="24"/>
-      <c r="I60" s="25"/>
+      <c r="E60" s="28"/>
+      <c r="F60" s="28"/>
+      <c r="G60" s="28"/>
+      <c r="H60" s="28"/>
+      <c r="I60" s="29"/>
     </row>
     <row r="61" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B61" s="4">
@@ -2184,14 +2187,14 @@
       <c r="C61" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D61" s="23" t="s">
+      <c r="D61" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="E61" s="24"/>
-      <c r="F61" s="24"/>
-      <c r="G61" s="24"/>
-      <c r="H61" s="24"/>
-      <c r="I61" s="25"/>
+      <c r="E61" s="28"/>
+      <c r="F61" s="28"/>
+      <c r="G61" s="28"/>
+      <c r="H61" s="28"/>
+      <c r="I61" s="29"/>
     </row>
     <row r="62" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B62" s="4">
@@ -2200,14 +2203,14 @@
       <c r="C62" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D62" s="23" t="s">
+      <c r="D62" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="E62" s="24"/>
-      <c r="F62" s="24"/>
-      <c r="G62" s="24"/>
-      <c r="H62" s="24"/>
-      <c r="I62" s="25"/>
+      <c r="E62" s="28"/>
+      <c r="F62" s="28"/>
+      <c r="G62" s="28"/>
+      <c r="H62" s="28"/>
+      <c r="I62" s="29"/>
     </row>
     <row r="63" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B63" s="4">
@@ -2251,10 +2254,10 @@
       <c r="F64" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G64" s="23" t="s">
+      <c r="G64" s="27" t="s">
         <v>37</v>
       </c>
-      <c r="H64" s="25"/>
+      <c r="H64" s="29"/>
       <c r="I64" s="1" t="s">
         <v>14</v>
       </c>
@@ -2292,13 +2295,13 @@
       <c r="C66" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D66" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="E66" s="24"/>
-      <c r="F66" s="24"/>
-      <c r="G66" s="24"/>
-      <c r="H66" s="25"/>
+      <c r="D66" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="E66" s="28"/>
+      <c r="F66" s="28"/>
+      <c r="G66" s="28"/>
+      <c r="H66" s="29"/>
       <c r="I66" s="1" t="s">
         <v>16</v>
       </c>
@@ -2310,18 +2313,18 @@
       <c r="C67" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D67" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="E67" s="24"/>
-      <c r="F67" s="25"/>
+      <c r="D67" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="E67" s="28"/>
+      <c r="F67" s="29"/>
       <c r="G67" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="H67" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="I67" s="25"/>
+      <c r="H67" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="I67" s="29"/>
     </row>
     <row r="68" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B68" s="4">
@@ -2336,12 +2339,12 @@
       <c r="E68" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F68" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="G68" s="24"/>
-      <c r="H68" s="24"/>
-      <c r="I68" s="25"/>
+      <c r="F68" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="G68" s="28"/>
+      <c r="H68" s="28"/>
+      <c r="I68" s="29"/>
     </row>
     <row r="69" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B69" s="4">
@@ -2350,14 +2353,14 @@
       <c r="C69" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D69" s="23" t="s">
+      <c r="D69" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="E69" s="24"/>
-      <c r="F69" s="24"/>
-      <c r="G69" s="24"/>
-      <c r="H69" s="24"/>
-      <c r="I69" s="25"/>
+      <c r="E69" s="28"/>
+      <c r="F69" s="28"/>
+      <c r="G69" s="28"/>
+      <c r="H69" s="28"/>
+      <c r="I69" s="29"/>
     </row>
     <row r="70" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B70" s="4">
@@ -2366,10 +2369,10 @@
       <c r="C70" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D70" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="E70" s="25"/>
+      <c r="D70" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="E70" s="29"/>
       <c r="F70" s="3" t="s">
         <v>15</v>
       </c>
@@ -2399,10 +2402,10 @@
       <c r="F71" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G71" s="23" t="s">
+      <c r="G71" s="27" t="s">
         <v>37</v>
       </c>
-      <c r="H71" s="25"/>
+      <c r="H71" s="29"/>
       <c r="I71" s="1" t="s">
         <v>14</v>
       </c>
@@ -2440,14 +2443,14 @@
       <c r="C73" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D73" s="23" t="s">
+      <c r="D73" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="E73" s="24"/>
-      <c r="F73" s="24"/>
-      <c r="G73" s="24"/>
-      <c r="H73" s="24"/>
-      <c r="I73" s="25"/>
+      <c r="E73" s="28"/>
+      <c r="F73" s="28"/>
+      <c r="G73" s="28"/>
+      <c r="H73" s="28"/>
+      <c r="I73" s="29"/>
     </row>
     <row r="74" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B74" s="4">
@@ -2456,11 +2459,11 @@
       <c r="C74" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D74" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="E74" s="24"/>
-      <c r="F74" s="25"/>
+      <c r="D74" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="E74" s="28"/>
+      <c r="F74" s="29"/>
       <c r="G74" s="3" t="s">
         <v>16</v>
       </c>
@@ -2496,14 +2499,14 @@
       <c r="C76" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D76" s="23" t="s">
+      <c r="D76" s="27" t="s">
         <v>39</v>
       </c>
-      <c r="E76" s="24"/>
-      <c r="F76" s="24"/>
-      <c r="G76" s="24"/>
-      <c r="H76" s="24"/>
-      <c r="I76" s="25"/>
+      <c r="E76" s="28"/>
+      <c r="F76" s="28"/>
+      <c r="G76" s="28"/>
+      <c r="H76" s="28"/>
+      <c r="I76" s="29"/>
     </row>
     <row r="77" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B77" s="4">
@@ -2512,14 +2515,14 @@
       <c r="C77" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D77" s="23" t="s">
+      <c r="D77" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="E77" s="24"/>
-      <c r="F77" s="24"/>
-      <c r="G77" s="24"/>
-      <c r="H77" s="24"/>
-      <c r="I77" s="25"/>
+      <c r="E77" s="28"/>
+      <c r="F77" s="28"/>
+      <c r="G77" s="28"/>
+      <c r="H77" s="28"/>
+      <c r="I77" s="29"/>
     </row>
     <row r="78" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B78" s="4">
@@ -2528,14 +2531,14 @@
       <c r="C78" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D78" s="23" t="s">
+      <c r="D78" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="E78" s="24"/>
-      <c r="F78" s="24"/>
-      <c r="G78" s="24"/>
-      <c r="H78" s="24"/>
-      <c r="I78" s="25"/>
+      <c r="E78" s="28"/>
+      <c r="F78" s="28"/>
+      <c r="G78" s="28"/>
+      <c r="H78" s="28"/>
+      <c r="I78" s="29"/>
     </row>
     <row r="79" spans="2:9" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B79" s="16" t="s">
@@ -2579,10 +2582,10 @@
       <c r="F80" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G80" s="23" t="s">
+      <c r="G80" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="H80" s="25"/>
+      <c r="H80" s="29"/>
       <c r="I80" s="1" t="s">
         <v>14</v>
       </c>
@@ -2603,10 +2606,10 @@
       <c r="F81" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="G81" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="H81" s="25"/>
+      <c r="G81" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="H81" s="29"/>
       <c r="I81" s="1" t="s">
         <v>16</v>
       </c>
@@ -2670,14 +2673,14 @@
       <c r="C84" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D84" s="23" t="s">
+      <c r="D84" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="E84" s="24"/>
-      <c r="F84" s="24"/>
-      <c r="G84" s="24"/>
-      <c r="H84" s="24"/>
-      <c r="I84" s="25"/>
+      <c r="E84" s="28"/>
+      <c r="F84" s="28"/>
+      <c r="G84" s="28"/>
+      <c r="H84" s="28"/>
+      <c r="I84" s="29"/>
     </row>
     <row r="85" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B85" s="4">
@@ -2715,11 +2718,11 @@
       <c r="D86" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="E86" s="23" t="s">
+      <c r="E86" s="27" t="s">
         <v>43</v>
       </c>
-      <c r="F86" s="24"/>
-      <c r="G86" s="25"/>
+      <c r="F86" s="28"/>
+      <c r="G86" s="29"/>
       <c r="H86" s="3" t="s">
         <v>14</v>
       </c>
@@ -2734,18 +2737,18 @@
       <c r="C87" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D87" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="E87" s="25"/>
+      <c r="D87" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="E87" s="29"/>
       <c r="F87" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G87" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="H87" s="24"/>
-      <c r="I87" s="25"/>
+      <c r="G87" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="H87" s="28"/>
+      <c r="I87" s="29"/>
     </row>
     <row r="88" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B88" s="4">
@@ -2754,14 +2757,14 @@
       <c r="C88" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D88" s="23" t="s">
+      <c r="D88" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="E88" s="24"/>
-      <c r="F88" s="24"/>
-      <c r="G88" s="24"/>
-      <c r="H88" s="24"/>
-      <c r="I88" s="25"/>
+      <c r="E88" s="28"/>
+      <c r="F88" s="28"/>
+      <c r="G88" s="28"/>
+      <c r="H88" s="28"/>
+      <c r="I88" s="29"/>
     </row>
     <row r="89" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B89" s="4">
@@ -2770,18 +2773,18 @@
       <c r="C89" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D89" s="23" t="s">
+      <c r="D89" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="E89" s="24"/>
-      <c r="F89" s="25"/>
+      <c r="E89" s="28"/>
+      <c r="F89" s="29"/>
       <c r="G89" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="H89" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="I89" s="25"/>
+      <c r="H89" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="I89" s="29"/>
     </row>
     <row r="90" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B90" s="4">
@@ -2790,10 +2793,10 @@
       <c r="C90" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D90" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="E90" s="25"/>
+      <c r="D90" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="E90" s="29"/>
       <c r="F90" s="3" t="s">
         <v>16</v>
       </c>
@@ -2815,13 +2818,13 @@
       <c r="C91" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D91" s="23" t="s">
+      <c r="D91" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="E91" s="24"/>
-      <c r="F91" s="24"/>
-      <c r="G91" s="24"/>
-      <c r="H91" s="25"/>
+      <c r="E91" s="28"/>
+      <c r="F91" s="28"/>
+      <c r="G91" s="28"/>
+      <c r="H91" s="29"/>
       <c r="I91" s="18" t="s">
         <v>45</v>
       </c>
@@ -2833,14 +2836,14 @@
       <c r="C92" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D92" s="23" t="s">
+      <c r="D92" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="E92" s="24"/>
-      <c r="F92" s="24"/>
-      <c r="G92" s="24"/>
-      <c r="H92" s="24"/>
-      <c r="I92" s="25"/>
+      <c r="E92" s="28"/>
+      <c r="F92" s="28"/>
+      <c r="G92" s="28"/>
+      <c r="H92" s="28"/>
+      <c r="I92" s="29"/>
     </row>
     <row r="93" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B93" s="4">
@@ -2849,14 +2852,14 @@
       <c r="C93" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D93" s="23" t="s">
+      <c r="D93" s="27" t="s">
         <v>46</v>
       </c>
-      <c r="E93" s="24"/>
-      <c r="F93" s="24"/>
-      <c r="G93" s="24"/>
-      <c r="H93" s="24"/>
-      <c r="I93" s="25"/>
+      <c r="E93" s="28"/>
+      <c r="F93" s="28"/>
+      <c r="G93" s="28"/>
+      <c r="H93" s="28"/>
+      <c r="I93" s="29"/>
     </row>
     <row r="94" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B94" s="4">
@@ -2865,14 +2868,14 @@
       <c r="C94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D94" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="E94" s="24"/>
-      <c r="F94" s="24"/>
-      <c r="G94" s="24"/>
-      <c r="H94" s="24"/>
-      <c r="I94" s="25"/>
+      <c r="D94" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="E94" s="28"/>
+      <c r="F94" s="28"/>
+      <c r="G94" s="28"/>
+      <c r="H94" s="28"/>
+      <c r="I94" s="29"/>
     </row>
     <row r="95" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B95" s="4">
@@ -2881,15 +2884,15 @@
       <c r="C95" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D95" s="23" t="s">
+      <c r="D95" s="27" t="s">
         <v>47</v>
       </c>
-      <c r="E95" s="24"/>
-      <c r="F95" s="25"/>
-      <c r="G95" s="23" t="s">
+      <c r="E95" s="28"/>
+      <c r="F95" s="29"/>
+      <c r="G95" s="27" t="s">
         <v>48</v>
       </c>
-      <c r="H95" s="25"/>
+      <c r="H95" s="29"/>
       <c r="I95" s="1" t="s">
         <v>14</v>
       </c>
@@ -2901,14 +2904,14 @@
       <c r="C96" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D96" s="23" t="s">
+      <c r="D96" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="E96" s="24"/>
-      <c r="F96" s="24"/>
-      <c r="G96" s="24"/>
-      <c r="H96" s="24"/>
-      <c r="I96" s="25"/>
+      <c r="E96" s="28"/>
+      <c r="F96" s="28"/>
+      <c r="G96" s="28"/>
+      <c r="H96" s="28"/>
+      <c r="I96" s="29"/>
     </row>
     <row r="97" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B97" s="4">
@@ -2917,14 +2920,14 @@
       <c r="C97" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D97" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="E97" s="24"/>
-      <c r="F97" s="24"/>
-      <c r="G97" s="24"/>
-      <c r="H97" s="24"/>
-      <c r="I97" s="25"/>
+      <c r="D97" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="E97" s="28"/>
+      <c r="F97" s="28"/>
+      <c r="G97" s="28"/>
+      <c r="H97" s="28"/>
+      <c r="I97" s="29"/>
     </row>
     <row r="98" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B98" s="4">
@@ -2933,14 +2936,14 @@
       <c r="C98" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D98" s="23" t="s">
+      <c r="D98" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="E98" s="24"/>
-      <c r="F98" s="24"/>
-      <c r="G98" s="24"/>
-      <c r="H98" s="24"/>
-      <c r="I98" s="25"/>
+      <c r="E98" s="28"/>
+      <c r="F98" s="28"/>
+      <c r="G98" s="28"/>
+      <c r="H98" s="28"/>
+      <c r="I98" s="29"/>
     </row>
     <row r="99" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B99" s="4">
@@ -2949,12 +2952,12 @@
       <c r="C99" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D99" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="E99" s="24"/>
-      <c r="F99" s="24"/>
-      <c r="G99" s="25"/>
+      <c r="D99" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="E99" s="28"/>
+      <c r="F99" s="28"/>
+      <c r="G99" s="29"/>
       <c r="H99" s="3" t="s">
         <v>49</v>
       </c>
@@ -2978,21 +2981,21 @@
       <c r="F100" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="G100" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="H100" s="24"/>
-      <c r="I100" s="25"/>
+      <c r="G100" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="H100" s="28"/>
+      <c r="I100" s="29"/>
     </row>
     <row r="101" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B101" s="23"/>
-      <c r="C101" s="24"/>
-      <c r="D101" s="24"/>
-      <c r="E101" s="24"/>
-      <c r="F101" s="24"/>
-      <c r="G101" s="24"/>
-      <c r="H101" s="24"/>
-      <c r="I101" s="25"/>
+      <c r="B101" s="27"/>
+      <c r="C101" s="28"/>
+      <c r="D101" s="28"/>
+      <c r="E101" s="28"/>
+      <c r="F101" s="28"/>
+      <c r="G101" s="28"/>
+      <c r="H101" s="28"/>
+      <c r="I101" s="29"/>
     </row>
     <row r="102" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B102" s="3"/>
@@ -3011,10 +3014,10 @@
       <c r="C103" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D103" s="23" t="s">
+      <c r="D103" s="27" t="s">
         <v>51</v>
       </c>
-      <c r="E103" s="25"/>
+      <c r="E103" s="29"/>
       <c r="F103" s="3"/>
       <c r="G103" s="3"/>
       <c r="H103" s="3"/>
@@ -3027,10 +3030,10 @@
       <c r="C104" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D104" s="23" t="s">
+      <c r="D104" s="27" t="s">
         <v>52</v>
       </c>
-      <c r="E104" s="25"/>
+      <c r="E104" s="29"/>
       <c r="F104" s="3"/>
       <c r="G104" s="3"/>
       <c r="H104" s="3"/>
@@ -3043,10 +3046,10 @@
       <c r="C105" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D105" s="23" t="s">
+      <c r="D105" s="27" t="s">
         <v>53</v>
       </c>
-      <c r="E105" s="25"/>
+      <c r="E105" s="29"/>
       <c r="F105" s="3"/>
       <c r="G105" s="3"/>
       <c r="H105" s="3"/>
@@ -3059,10 +3062,10 @@
       <c r="C106" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D106" s="23" t="s">
+      <c r="D106" s="27" t="s">
         <v>54</v>
       </c>
-      <c r="E106" s="25"/>
+      <c r="E106" s="29"/>
       <c r="F106" s="3"/>
       <c r="G106" s="3"/>
       <c r="H106" s="3"/>
@@ -3075,10 +3078,10 @@
       <c r="C107" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D107" s="23" t="s">
+      <c r="D107" s="27" t="s">
         <v>55</v>
       </c>
-      <c r="E107" s="25"/>
+      <c r="E107" s="29"/>
       <c r="F107" s="3"/>
       <c r="G107" s="3"/>
       <c r="H107" s="3"/>
@@ -3091,10 +3094,10 @@
       <c r="C108" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D108" s="23" t="s">
+      <c r="D108" s="27" t="s">
         <v>56</v>
       </c>
-      <c r="E108" s="25"/>
+      <c r="E108" s="29"/>
       <c r="F108" s="3"/>
       <c r="G108" s="3"/>
       <c r="H108" s="3"/>
@@ -3131,28 +3134,28 @@
       <c r="I111" s="20"/>
     </row>
     <row r="112" spans="2:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B112" s="34" t="s">
+      <c r="B112" s="30" t="s">
         <v>57</v>
       </c>
-      <c r="C112" s="35"/>
-      <c r="D112" s="35"/>
-      <c r="E112" s="35"/>
-      <c r="F112" s="35"/>
-      <c r="G112" s="35"/>
-      <c r="H112" s="35"/>
-      <c r="I112" s="35"/>
-      <c r="J112" s="36"/>
+      <c r="C112" s="31"/>
+      <c r="D112" s="31"/>
+      <c r="E112" s="31"/>
+      <c r="F112" s="31"/>
+      <c r="G112" s="31"/>
+      <c r="H112" s="31"/>
+      <c r="I112" s="31"/>
+      <c r="J112" s="32"/>
     </row>
     <row r="113" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B113" s="37"/>
-      <c r="C113" s="38"/>
-      <c r="D113" s="38"/>
-      <c r="E113" s="38"/>
-      <c r="F113" s="38"/>
-      <c r="G113" s="38"/>
-      <c r="H113" s="38"/>
-      <c r="I113" s="38"/>
-      <c r="J113" s="39"/>
+      <c r="B113" s="33"/>
+      <c r="C113" s="34"/>
+      <c r="D113" s="34"/>
+      <c r="E113" s="34"/>
+      <c r="F113" s="34"/>
+      <c r="G113" s="34"/>
+      <c r="H113" s="34"/>
+      <c r="I113" s="34"/>
+      <c r="J113" s="35"/>
     </row>
     <row r="114" spans="2:10" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B114" s="8" t="s">
@@ -3283,13 +3286,13 @@
       <c r="E118" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="F118" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="G118" s="24"/>
-      <c r="H118" s="24"/>
-      <c r="I118" s="24"/>
-      <c r="J118" s="25"/>
+      <c r="F118" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="G118" s="28"/>
+      <c r="H118" s="28"/>
+      <c r="I118" s="28"/>
+      <c r="J118" s="29"/>
     </row>
     <row r="119" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B119" s="4">
@@ -3327,13 +3330,13 @@
       <c r="C120" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D120" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="E120" s="24"/>
-      <c r="F120" s="24"/>
-      <c r="G120" s="24"/>
-      <c r="H120" s="25"/>
+      <c r="D120" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="E120" s="28"/>
+      <c r="F120" s="28"/>
+      <c r="G120" s="28"/>
+      <c r="H120" s="29"/>
       <c r="I120" s="1" t="s">
         <v>16</v>
       </c>
@@ -3348,15 +3351,15 @@
       <c r="C121" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D121" s="23" t="s">
+      <c r="D121" s="27" t="s">
         <v>65</v>
       </c>
-      <c r="E121" s="24"/>
-      <c r="F121" s="24"/>
-      <c r="G121" s="24"/>
-      <c r="H121" s="24"/>
-      <c r="I121" s="24"/>
-      <c r="J121" s="25"/>
+      <c r="E121" s="28"/>
+      <c r="F121" s="28"/>
+      <c r="G121" s="28"/>
+      <c r="H121" s="28"/>
+      <c r="I121" s="28"/>
+      <c r="J121" s="29"/>
     </row>
     <row r="122" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B122" s="4">
@@ -3403,12 +3406,12 @@
       <c r="F123" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="G123" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="H123" s="24"/>
-      <c r="I123" s="24"/>
-      <c r="J123" s="25"/>
+      <c r="G123" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="H123" s="28"/>
+      <c r="I123" s="28"/>
+      <c r="J123" s="29"/>
     </row>
     <row r="124" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B124" s="4">
@@ -3426,12 +3429,12 @@
       <c r="F124" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="G124" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="H124" s="24"/>
-      <c r="I124" s="24"/>
-      <c r="J124" s="25"/>
+      <c r="G124" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="H124" s="28"/>
+      <c r="I124" s="28"/>
+      <c r="J124" s="29"/>
     </row>
     <row r="125" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B125" s="4">
@@ -3446,13 +3449,13 @@
       <c r="E125" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="F125" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="G125" s="24"/>
-      <c r="H125" s="24"/>
-      <c r="I125" s="24"/>
-      <c r="J125" s="25"/>
+      <c r="F125" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="G125" s="28"/>
+      <c r="H125" s="28"/>
+      <c r="I125" s="28"/>
+      <c r="J125" s="29"/>
     </row>
     <row r="126" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B126" s="4">
@@ -3470,11 +3473,11 @@
       <c r="F126" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="G126" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="H126" s="24"/>
-      <c r="I126" s="25"/>
+      <c r="G126" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="H126" s="28"/>
+      <c r="I126" s="29"/>
       <c r="J126" s="1" t="s">
         <v>16</v>
       </c>
@@ -3492,13 +3495,13 @@
       <c r="E127" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="F127" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="G127" s="24"/>
-      <c r="H127" s="24"/>
-      <c r="I127" s="24"/>
-      <c r="J127" s="25"/>
+      <c r="F127" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="G127" s="28"/>
+      <c r="H127" s="28"/>
+      <c r="I127" s="28"/>
+      <c r="J127" s="29"/>
     </row>
     <row r="128" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B128" s="4">
@@ -3507,15 +3510,15 @@
       <c r="C128" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D128" s="23" t="s">
+      <c r="D128" s="27" t="s">
         <v>65</v>
       </c>
-      <c r="E128" s="24"/>
-      <c r="F128" s="24"/>
-      <c r="G128" s="24"/>
-      <c r="H128" s="24"/>
-      <c r="I128" s="24"/>
-      <c r="J128" s="25"/>
+      <c r="E128" s="28"/>
+      <c r="F128" s="28"/>
+      <c r="G128" s="28"/>
+      <c r="H128" s="28"/>
+      <c r="I128" s="28"/>
+      <c r="J128" s="29"/>
     </row>
     <row r="129" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B129" s="4">
@@ -3698,15 +3701,15 @@
       <c r="C135" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D135" s="23" t="s">
+      <c r="D135" s="27" t="s">
         <v>65</v>
       </c>
-      <c r="E135" s="24"/>
-      <c r="F135" s="24"/>
-      <c r="G135" s="24"/>
-      <c r="H135" s="24"/>
-      <c r="I135" s="24"/>
-      <c r="J135" s="25"/>
+      <c r="E135" s="28"/>
+      <c r="F135" s="28"/>
+      <c r="G135" s="28"/>
+      <c r="H135" s="28"/>
+      <c r="I135" s="28"/>
+      <c r="J135" s="29"/>
     </row>
     <row r="136" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B136" s="4">
@@ -3918,15 +3921,15 @@
       <c r="C143" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D143" s="23" t="s">
+      <c r="D143" s="27" t="s">
         <v>65</v>
       </c>
-      <c r="E143" s="24"/>
-      <c r="F143" s="24"/>
-      <c r="G143" s="24"/>
-      <c r="H143" s="24"/>
-      <c r="I143" s="24"/>
-      <c r="J143" s="25"/>
+      <c r="E143" s="28"/>
+      <c r="F143" s="28"/>
+      <c r="G143" s="28"/>
+      <c r="H143" s="28"/>
+      <c r="I143" s="28"/>
+      <c r="J143" s="29"/>
     </row>
     <row r="144" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B144" s="4">
@@ -4002,12 +4005,12 @@
       <c r="F146" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="G146" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="H146" s="24"/>
-      <c r="I146" s="24"/>
-      <c r="J146" s="25"/>
+      <c r="G146" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="H146" s="28"/>
+      <c r="I146" s="28"/>
+      <c r="J146" s="29"/>
     </row>
     <row r="147" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B147" s="4">
@@ -4074,15 +4077,15 @@
       <c r="C149" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D149" s="26" t="s">
+      <c r="D149" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E149" s="27"/>
-      <c r="F149" s="27"/>
-      <c r="G149" s="27"/>
-      <c r="H149" s="27"/>
-      <c r="I149" s="27"/>
-      <c r="J149" s="28"/>
+      <c r="E149" s="24"/>
+      <c r="F149" s="24"/>
+      <c r="G149" s="24"/>
+      <c r="H149" s="24"/>
+      <c r="I149" s="24"/>
+      <c r="J149" s="38"/>
     </row>
     <row r="150" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B150" s="4">
@@ -4091,13 +4094,13 @@
       <c r="C150" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D150" s="29"/>
-      <c r="E150" s="30"/>
-      <c r="F150" s="30"/>
-      <c r="G150" s="30"/>
-      <c r="H150" s="30"/>
-      <c r="I150" s="30"/>
-      <c r="J150" s="31"/>
+      <c r="D150" s="25"/>
+      <c r="E150" s="26"/>
+      <c r="F150" s="26"/>
+      <c r="G150" s="26"/>
+      <c r="H150" s="26"/>
+      <c r="I150" s="26"/>
+      <c r="J150" s="39"/>
     </row>
     <row r="151" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B151" s="4">
@@ -4144,11 +4147,11 @@
       <c r="F152" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="G152" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="H152" s="24"/>
-      <c r="I152" s="25"/>
+      <c r="G152" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="H152" s="28"/>
+      <c r="I152" s="29"/>
       <c r="J152" s="1" t="s">
         <v>69</v>
       </c>
@@ -4276,15 +4279,15 @@
       <c r="C157" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D157" s="23" t="s">
+      <c r="D157" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="E157" s="24"/>
-      <c r="F157" s="24"/>
-      <c r="G157" s="24"/>
-      <c r="H157" s="24"/>
-      <c r="I157" s="24"/>
-      <c r="J157" s="25"/>
+      <c r="E157" s="28"/>
+      <c r="F157" s="28"/>
+      <c r="G157" s="28"/>
+      <c r="H157" s="28"/>
+      <c r="I157" s="28"/>
+      <c r="J157" s="29"/>
     </row>
     <row r="158" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B158" s="4">
@@ -4465,15 +4468,15 @@
       <c r="C164" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D164" s="23" t="s">
+      <c r="D164" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="E164" s="24"/>
-      <c r="F164" s="24"/>
-      <c r="G164" s="24"/>
-      <c r="H164" s="24"/>
-      <c r="I164" s="24"/>
-      <c r="J164" s="25"/>
+      <c r="E164" s="28"/>
+      <c r="F164" s="28"/>
+      <c r="G164" s="28"/>
+      <c r="H164" s="28"/>
+      <c r="I164" s="28"/>
+      <c r="J164" s="29"/>
     </row>
     <row r="165" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B165" s="4">
@@ -4671,15 +4674,15 @@
       <c r="C172" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D172" s="23" t="s">
+      <c r="D172" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="E172" s="24"/>
-      <c r="F172" s="24"/>
-      <c r="G172" s="24"/>
-      <c r="H172" s="24"/>
-      <c r="I172" s="24"/>
-      <c r="J172" s="25"/>
+      <c r="E172" s="28"/>
+      <c r="F172" s="28"/>
+      <c r="G172" s="28"/>
+      <c r="H172" s="28"/>
+      <c r="I172" s="28"/>
+      <c r="J172" s="29"/>
     </row>
     <row r="173" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B173" s="4">
@@ -4743,44 +4746,44 @@
       <c r="B175" s="4">
         <v>45903</v>
       </c>
-      <c r="C175" s="26" t="s">
+      <c r="C175" s="23" t="s">
         <v>39</v>
       </c>
-      <c r="D175" s="27"/>
-      <c r="E175" s="27"/>
-      <c r="F175" s="27"/>
-      <c r="G175" s="27"/>
-      <c r="H175" s="27"/>
-      <c r="I175" s="27"/>
-      <c r="J175" s="27"/>
+      <c r="D175" s="24"/>
+      <c r="E175" s="24"/>
+      <c r="F175" s="24"/>
+      <c r="G175" s="24"/>
+      <c r="H175" s="24"/>
+      <c r="I175" s="24"/>
+      <c r="J175" s="24"/>
     </row>
     <row r="176" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B176" s="4">
         <v>45904</v>
       </c>
-      <c r="C176" s="29"/>
-      <c r="D176" s="30"/>
-      <c r="E176" s="30"/>
-      <c r="F176" s="30"/>
-      <c r="G176" s="30"/>
-      <c r="H176" s="30"/>
-      <c r="I176" s="30"/>
-      <c r="J176" s="30"/>
+      <c r="C176" s="25"/>
+      <c r="D176" s="26"/>
+      <c r="E176" s="26"/>
+      <c r="F176" s="26"/>
+      <c r="G176" s="26"/>
+      <c r="H176" s="26"/>
+      <c r="I176" s="26"/>
+      <c r="J176" s="26"/>
     </row>
     <row r="177" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B177" s="4">
         <v>45905</v>
       </c>
-      <c r="C177" s="23" t="s">
+      <c r="C177" s="27" t="s">
         <v>39</v>
       </c>
-      <c r="D177" s="24"/>
-      <c r="E177" s="24"/>
-      <c r="F177" s="24"/>
-      <c r="G177" s="24"/>
-      <c r="H177" s="24"/>
-      <c r="I177" s="24"/>
-      <c r="J177" s="25"/>
+      <c r="D177" s="28"/>
+      <c r="E177" s="28"/>
+      <c r="F177" s="28"/>
+      <c r="G177" s="28"/>
+      <c r="H177" s="28"/>
+      <c r="I177" s="28"/>
+      <c r="J177" s="29"/>
     </row>
     <row r="178" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B178" s="4">
@@ -4815,9 +4818,13 @@
       <c r="B179" s="4">
         <v>45907</v>
       </c>
-      <c r="C179" s="3"/>
+      <c r="C179" s="3" t="s">
+        <v>12</v>
+      </c>
       <c r="D179" s="3"/>
-      <c r="E179" s="3"/>
+      <c r="E179" s="3" t="s">
+        <v>14</v>
+      </c>
       <c r="F179" s="3"/>
       <c r="G179" s="3"/>
       <c r="H179" s="3"/>
@@ -4828,33 +4835,67 @@
       <c r="B180" s="4">
         <v>45908</v>
       </c>
-      <c r="C180" s="3"/>
-      <c r="D180" s="3"/>
-      <c r="E180" s="3"/>
-      <c r="F180" s="3"/>
-      <c r="G180" s="3"/>
-      <c r="H180" s="3"/>
-      <c r="I180" s="1"/>
-      <c r="J180" s="1"/>
+      <c r="C180" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D180" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="E180" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F180" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G180" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H180" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I180" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J180" s="1" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="181" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B181" s="4">
         <v>45909</v>
       </c>
-      <c r="C181" s="3"/>
-      <c r="D181" s="3"/>
-      <c r="E181" s="3"/>
-      <c r="F181" s="3"/>
-      <c r="G181" s="3"/>
-      <c r="H181" s="3"/>
-      <c r="I181" s="1"/>
-      <c r="J181" s="1"/>
+      <c r="C181" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D181" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E181" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F181" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G181" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H181" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I181" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J181" s="1" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="182" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B182" s="4">
         <v>45910</v>
       </c>
-      <c r="C182" s="3"/>
+      <c r="C182" s="3" t="s">
+        <v>8</v>
+      </c>
       <c r="D182" s="3"/>
       <c r="E182" s="3"/>
       <c r="F182" s="3"/>
@@ -7441,33 +7482,50 @@
     </row>
   </sheetData>
   <mergeCells count="87">
-    <mergeCell ref="C175:J176"/>
-    <mergeCell ref="D164:J164"/>
-    <mergeCell ref="D157:J157"/>
-    <mergeCell ref="D143:J143"/>
-    <mergeCell ref="D135:J135"/>
-    <mergeCell ref="D172:J172"/>
-    <mergeCell ref="G146:J146"/>
-    <mergeCell ref="D108:E108"/>
-    <mergeCell ref="B112:J113"/>
-    <mergeCell ref="G124:J124"/>
-    <mergeCell ref="D120:H120"/>
-    <mergeCell ref="G123:J123"/>
-    <mergeCell ref="D121:J121"/>
-    <mergeCell ref="D31:I31"/>
-    <mergeCell ref="G35:H35"/>
-    <mergeCell ref="D40:I40"/>
-    <mergeCell ref="D33:I33"/>
-    <mergeCell ref="D46:I46"/>
-    <mergeCell ref="D43:I43"/>
-    <mergeCell ref="D78:I78"/>
-    <mergeCell ref="G71:H71"/>
-    <mergeCell ref="D76:I76"/>
-    <mergeCell ref="D66:H66"/>
-    <mergeCell ref="D77:I77"/>
-    <mergeCell ref="D73:I73"/>
-    <mergeCell ref="D70:E70"/>
-    <mergeCell ref="D74:F74"/>
+    <mergeCell ref="C177:J177"/>
+    <mergeCell ref="D106:E106"/>
+    <mergeCell ref="D99:G99"/>
+    <mergeCell ref="G126:I126"/>
+    <mergeCell ref="F125:J125"/>
+    <mergeCell ref="D128:J128"/>
+    <mergeCell ref="D103:E103"/>
+    <mergeCell ref="D104:E104"/>
+    <mergeCell ref="D105:E105"/>
+    <mergeCell ref="G100:I100"/>
+    <mergeCell ref="B101:I101"/>
+    <mergeCell ref="F127:J127"/>
+    <mergeCell ref="D107:E107"/>
+    <mergeCell ref="F118:J118"/>
+    <mergeCell ref="G152:I152"/>
+    <mergeCell ref="D149:J150"/>
+    <mergeCell ref="D98:I98"/>
+    <mergeCell ref="D94:I94"/>
+    <mergeCell ref="H89:I89"/>
+    <mergeCell ref="D89:F89"/>
+    <mergeCell ref="D97:I97"/>
+    <mergeCell ref="G64:H64"/>
+    <mergeCell ref="D96:I96"/>
+    <mergeCell ref="D95:F95"/>
+    <mergeCell ref="G95:H95"/>
+    <mergeCell ref="D92:I92"/>
+    <mergeCell ref="D93:I93"/>
+    <mergeCell ref="D90:E90"/>
+    <mergeCell ref="D91:H91"/>
+    <mergeCell ref="E86:G86"/>
+    <mergeCell ref="D88:I88"/>
+    <mergeCell ref="H67:I67"/>
+    <mergeCell ref="G81:H81"/>
+    <mergeCell ref="D67:F67"/>
+    <mergeCell ref="F68:I68"/>
+    <mergeCell ref="D87:E87"/>
+    <mergeCell ref="G87:I87"/>
+    <mergeCell ref="D60:I60"/>
+    <mergeCell ref="D62:I62"/>
+    <mergeCell ref="D61:I61"/>
+    <mergeCell ref="G49:H49"/>
+    <mergeCell ref="D47:I47"/>
+    <mergeCell ref="D55:I55"/>
+    <mergeCell ref="G57:H57"/>
     <mergeCell ref="D84:I84"/>
     <mergeCell ref="D69:I69"/>
     <mergeCell ref="D8:I8"/>
@@ -7484,50 +7542,33 @@
     <mergeCell ref="D30:I30"/>
     <mergeCell ref="G80:H80"/>
     <mergeCell ref="G42:H42"/>
-    <mergeCell ref="D60:I60"/>
-    <mergeCell ref="D62:I62"/>
-    <mergeCell ref="D61:I61"/>
-    <mergeCell ref="G49:H49"/>
-    <mergeCell ref="D47:I47"/>
-    <mergeCell ref="D55:I55"/>
-    <mergeCell ref="G57:H57"/>
-    <mergeCell ref="G64:H64"/>
-    <mergeCell ref="D96:I96"/>
-    <mergeCell ref="D95:F95"/>
-    <mergeCell ref="G95:H95"/>
-    <mergeCell ref="D92:I92"/>
-    <mergeCell ref="D93:I93"/>
-    <mergeCell ref="D90:E90"/>
-    <mergeCell ref="D91:H91"/>
-    <mergeCell ref="E86:G86"/>
-    <mergeCell ref="D88:I88"/>
-    <mergeCell ref="H67:I67"/>
-    <mergeCell ref="G81:H81"/>
-    <mergeCell ref="D67:F67"/>
-    <mergeCell ref="F68:I68"/>
-    <mergeCell ref="D87:E87"/>
-    <mergeCell ref="G87:I87"/>
-    <mergeCell ref="D98:I98"/>
-    <mergeCell ref="D94:I94"/>
-    <mergeCell ref="H89:I89"/>
-    <mergeCell ref="D89:F89"/>
-    <mergeCell ref="D97:I97"/>
-    <mergeCell ref="C177:J177"/>
-    <mergeCell ref="D106:E106"/>
-    <mergeCell ref="D99:G99"/>
-    <mergeCell ref="G126:I126"/>
-    <mergeCell ref="F125:J125"/>
-    <mergeCell ref="D128:J128"/>
-    <mergeCell ref="D103:E103"/>
-    <mergeCell ref="D104:E104"/>
-    <mergeCell ref="D105:E105"/>
-    <mergeCell ref="G100:I100"/>
-    <mergeCell ref="B101:I101"/>
-    <mergeCell ref="F127:J127"/>
-    <mergeCell ref="D107:E107"/>
-    <mergeCell ref="F118:J118"/>
-    <mergeCell ref="G152:I152"/>
-    <mergeCell ref="D149:J150"/>
+    <mergeCell ref="D78:I78"/>
+    <mergeCell ref="G71:H71"/>
+    <mergeCell ref="D76:I76"/>
+    <mergeCell ref="D66:H66"/>
+    <mergeCell ref="D77:I77"/>
+    <mergeCell ref="D73:I73"/>
+    <mergeCell ref="D70:E70"/>
+    <mergeCell ref="D74:F74"/>
+    <mergeCell ref="D31:I31"/>
+    <mergeCell ref="G35:H35"/>
+    <mergeCell ref="D40:I40"/>
+    <mergeCell ref="D33:I33"/>
+    <mergeCell ref="D46:I46"/>
+    <mergeCell ref="D43:I43"/>
+    <mergeCell ref="D108:E108"/>
+    <mergeCell ref="B112:J113"/>
+    <mergeCell ref="G124:J124"/>
+    <mergeCell ref="D120:H120"/>
+    <mergeCell ref="G123:J123"/>
+    <mergeCell ref="D121:J121"/>
+    <mergeCell ref="C175:J176"/>
+    <mergeCell ref="D164:J164"/>
+    <mergeCell ref="D157:J157"/>
+    <mergeCell ref="D143:J143"/>
+    <mergeCell ref="D135:J135"/>
+    <mergeCell ref="D172:J172"/>
+    <mergeCell ref="G146:J146"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/attendance_sheet.xlsx
+++ b/attendance_sheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\repositary\3rd_Year_5th_Semester\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CC595A4-2F2C-4F4F-A4CC-E8D8B10A4F65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF4DF54D-989F-4068-AF20-E60243E67003}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{EB654061-A886-47D1-BF86-9B1A84FCE7FB}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="899" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="912" uniqueCount="74">
   <si>
     <t>Date</t>
   </si>
@@ -538,10 +538,22 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
@@ -550,13 +562,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -575,18 +587,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -990,14 +990,14 @@
       <c r="C8" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D8" s="37" t="s">
+      <c r="D8" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="E8" s="37"/>
-      <c r="F8" s="37"/>
-      <c r="G8" s="37"/>
-      <c r="H8" s="37"/>
-      <c r="I8" s="37"/>
+      <c r="E8" s="32"/>
+      <c r="F8" s="32"/>
+      <c r="G8" s="32"/>
+      <c r="H8" s="32"/>
+      <c r="I8" s="32"/>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B9" s="4">
@@ -1006,14 +1006,14 @@
       <c r="C9" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D9" s="37" t="s">
+      <c r="D9" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="E9" s="37"/>
-      <c r="F9" s="37"/>
-      <c r="G9" s="37"/>
-      <c r="H9" s="37"/>
-      <c r="I9" s="37"/>
+      <c r="E9" s="32"/>
+      <c r="F9" s="32"/>
+      <c r="G9" s="32"/>
+      <c r="H9" s="32"/>
+      <c r="I9" s="32"/>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B10" s="4">
@@ -1022,14 +1022,14 @@
       <c r="C10" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D10" s="37" t="s">
+      <c r="D10" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="E10" s="37"/>
-      <c r="F10" s="37"/>
-      <c r="G10" s="37"/>
-      <c r="H10" s="37"/>
-      <c r="I10" s="37"/>
+      <c r="E10" s="32"/>
+      <c r="F10" s="32"/>
+      <c r="G10" s="32"/>
+      <c r="H10" s="32"/>
+      <c r="I10" s="32"/>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B11" s="4">
@@ -1038,14 +1038,14 @@
       <c r="C11" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D11" s="37" t="s">
+      <c r="D11" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="E11" s="37"/>
-      <c r="F11" s="37"/>
-      <c r="G11" s="37"/>
-      <c r="H11" s="37"/>
-      <c r="I11" s="37"/>
+      <c r="E11" s="32"/>
+      <c r="F11" s="32"/>
+      <c r="G11" s="32"/>
+      <c r="H11" s="32"/>
+      <c r="I11" s="32"/>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B12" s="4">
@@ -1089,10 +1089,10 @@
       <c r="F13" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="G13" s="37" t="s">
+      <c r="G13" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="H13" s="37"/>
+      <c r="H13" s="32"/>
       <c r="I13" s="1" t="s">
         <v>14</v>
       </c>
@@ -1104,14 +1104,14 @@
       <c r="C14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D14" s="37" t="s">
+      <c r="D14" s="32" t="s">
         <v>19</v>
       </c>
-      <c r="E14" s="37"/>
-      <c r="F14" s="37"/>
-      <c r="G14" s="37"/>
-      <c r="H14" s="37"/>
-      <c r="I14" s="37"/>
+      <c r="E14" s="32"/>
+      <c r="F14" s="32"/>
+      <c r="G14" s="32"/>
+      <c r="H14" s="32"/>
+      <c r="I14" s="32"/>
     </row>
     <row r="15" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B15" s="4">
@@ -1198,14 +1198,14 @@
       <c r="C18" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D18" s="37" t="s">
+      <c r="D18" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="E18" s="37"/>
-      <c r="F18" s="37"/>
-      <c r="G18" s="37"/>
-      <c r="H18" s="37"/>
-      <c r="I18" s="37"/>
+      <c r="E18" s="32"/>
+      <c r="F18" s="32"/>
+      <c r="G18" s="32"/>
+      <c r="H18" s="32"/>
+      <c r="I18" s="32"/>
     </row>
     <row r="19" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B19" s="4">
@@ -1214,14 +1214,14 @@
       <c r="C19" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D19" s="37" t="s">
+      <c r="D19" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="E19" s="37"/>
-      <c r="F19" s="37"/>
-      <c r="G19" s="37"/>
-      <c r="H19" s="37"/>
-      <c r="I19" s="37"/>
+      <c r="E19" s="32"/>
+      <c r="F19" s="32"/>
+      <c r="G19" s="32"/>
+      <c r="H19" s="32"/>
+      <c r="I19" s="32"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B20" s="4">
@@ -1239,10 +1239,10 @@
       <c r="F20" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G20" s="37" t="s">
+      <c r="G20" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="H20" s="37"/>
+      <c r="H20" s="32"/>
       <c r="I20" s="1" t="s">
         <v>14</v>
       </c>
@@ -1358,14 +1358,14 @@
       <c r="C25" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D25" s="37" t="s">
+      <c r="D25" s="32" t="s">
         <v>26</v>
       </c>
-      <c r="E25" s="37"/>
-      <c r="F25" s="37"/>
-      <c r="G25" s="37"/>
-      <c r="H25" s="37"/>
-      <c r="I25" s="37"/>
+      <c r="E25" s="32"/>
+      <c r="F25" s="32"/>
+      <c r="G25" s="32"/>
+      <c r="H25" s="32"/>
+      <c r="I25" s="32"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B26" s="4">
@@ -1409,10 +1409,10 @@
       <c r="F27" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G27" s="37" t="s">
+      <c r="G27" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="H27" s="37"/>
+      <c r="H27" s="32"/>
       <c r="I27" s="1" t="s">
         <v>14</v>
       </c>
@@ -1476,14 +1476,14 @@
       <c r="C30" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D30" s="36" t="s">
+      <c r="D30" s="33" t="s">
         <v>20</v>
       </c>
-      <c r="E30" s="36"/>
-      <c r="F30" s="36"/>
-      <c r="G30" s="36"/>
-      <c r="H30" s="36"/>
-      <c r="I30" s="36"/>
+      <c r="E30" s="33"/>
+      <c r="F30" s="33"/>
+      <c r="G30" s="33"/>
+      <c r="H30" s="33"/>
+      <c r="I30" s="33"/>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B31" s="4">
@@ -1492,14 +1492,14 @@
       <c r="C31" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D31" s="36" t="s">
+      <c r="D31" s="33" t="s">
         <v>20</v>
       </c>
-      <c r="E31" s="36"/>
-      <c r="F31" s="36"/>
-      <c r="G31" s="36"/>
-      <c r="H31" s="36"/>
-      <c r="I31" s="36"/>
+      <c r="E31" s="33"/>
+      <c r="F31" s="33"/>
+      <c r="G31" s="33"/>
+      <c r="H31" s="33"/>
+      <c r="I31" s="33"/>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B32" s="4">
@@ -1534,14 +1534,14 @@
       <c r="C33" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D33" s="36" t="s">
+      <c r="D33" s="33" t="s">
         <v>20</v>
       </c>
-      <c r="E33" s="36"/>
-      <c r="F33" s="36"/>
-      <c r="G33" s="36"/>
-      <c r="H33" s="36"/>
-      <c r="I33" s="36"/>
+      <c r="E33" s="33"/>
+      <c r="F33" s="33"/>
+      <c r="G33" s="33"/>
+      <c r="H33" s="33"/>
+      <c r="I33" s="33"/>
     </row>
     <row r="34" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B34" s="4">
@@ -1585,10 +1585,10 @@
       <c r="F35" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G35" s="36" t="s">
+      <c r="G35" s="33" t="s">
         <v>18</v>
       </c>
-      <c r="H35" s="36"/>
+      <c r="H35" s="33"/>
       <c r="I35" s="1" t="s">
         <v>14</v>
       </c>
@@ -1704,14 +1704,14 @@
       <c r="C40" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D40" s="36" t="s">
+      <c r="D40" s="33" t="s">
         <v>20</v>
       </c>
-      <c r="E40" s="36"/>
-      <c r="F40" s="36"/>
-      <c r="G40" s="36"/>
-      <c r="H40" s="36"/>
-      <c r="I40" s="36"/>
+      <c r="E40" s="33"/>
+      <c r="F40" s="33"/>
+      <c r="G40" s="33"/>
+      <c r="H40" s="33"/>
+      <c r="I40" s="33"/>
     </row>
     <row r="41" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B41" s="4">
@@ -1755,10 +1755,10 @@
       <c r="F42" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G42" s="36" t="s">
+      <c r="G42" s="33" t="s">
         <v>28</v>
       </c>
-      <c r="H42" s="36"/>
+      <c r="H42" s="33"/>
       <c r="I42" s="1" t="s">
         <v>15</v>
       </c>
@@ -1770,14 +1770,14 @@
       <c r="C43" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D43" s="36" t="s">
+      <c r="D43" s="33" t="s">
         <v>20</v>
       </c>
-      <c r="E43" s="36"/>
-      <c r="F43" s="36"/>
-      <c r="G43" s="36"/>
-      <c r="H43" s="36"/>
-      <c r="I43" s="36"/>
+      <c r="E43" s="33"/>
+      <c r="F43" s="33"/>
+      <c r="G43" s="33"/>
+      <c r="H43" s="33"/>
+      <c r="I43" s="33"/>
     </row>
     <row r="44" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B44" s="4">
@@ -1841,14 +1841,14 @@
       <c r="C46" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D46" s="36" t="s">
+      <c r="D46" s="33" t="s">
         <v>20</v>
       </c>
-      <c r="E46" s="36"/>
-      <c r="F46" s="36"/>
-      <c r="G46" s="36"/>
-      <c r="H46" s="36"/>
-      <c r="I46" s="36"/>
+      <c r="E46" s="33"/>
+      <c r="F46" s="33"/>
+      <c r="G46" s="33"/>
+      <c r="H46" s="33"/>
+      <c r="I46" s="33"/>
     </row>
     <row r="47" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B47" s="4">
@@ -1857,14 +1857,14 @@
       <c r="C47" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D47" s="27" t="s">
+      <c r="D47" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E47" s="28"/>
-      <c r="F47" s="28"/>
-      <c r="G47" s="28"/>
-      <c r="H47" s="28"/>
-      <c r="I47" s="29"/>
+      <c r="E47" s="24"/>
+      <c r="F47" s="24"/>
+      <c r="G47" s="24"/>
+      <c r="H47" s="24"/>
+      <c r="I47" s="25"/>
     </row>
     <row r="48" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B48" s="4">
@@ -1908,10 +1908,10 @@
       <c r="F49" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G49" s="27" t="s">
+      <c r="G49" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="H49" s="29"/>
+      <c r="H49" s="25"/>
       <c r="I49" s="1" t="s">
         <v>30</v>
       </c>
@@ -2053,14 +2053,14 @@
       <c r="C55" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="D55" s="28" t="s">
+      <c r="D55" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="E55" s="28"/>
-      <c r="F55" s="28"/>
-      <c r="G55" s="28"/>
-      <c r="H55" s="28"/>
-      <c r="I55" s="28"/>
+      <c r="E55" s="24"/>
+      <c r="F55" s="24"/>
+      <c r="G55" s="24"/>
+      <c r="H55" s="24"/>
+      <c r="I55" s="24"/>
     </row>
     <row r="56" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B56" s="4">
@@ -2104,10 +2104,10 @@
       <c r="F57" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G57" s="27" t="s">
+      <c r="G57" s="23" t="s">
         <v>37</v>
       </c>
-      <c r="H57" s="29"/>
+      <c r="H57" s="25"/>
       <c r="I57" s="1" t="s">
         <v>36</v>
       </c>
@@ -2171,14 +2171,14 @@
       <c r="C60" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D60" s="27" t="s">
+      <c r="D60" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E60" s="28"/>
-      <c r="F60" s="28"/>
-      <c r="G60" s="28"/>
-      <c r="H60" s="28"/>
-      <c r="I60" s="29"/>
+      <c r="E60" s="24"/>
+      <c r="F60" s="24"/>
+      <c r="G60" s="24"/>
+      <c r="H60" s="24"/>
+      <c r="I60" s="25"/>
     </row>
     <row r="61" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B61" s="4">
@@ -2187,14 +2187,14 @@
       <c r="C61" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D61" s="27" t="s">
+      <c r="D61" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E61" s="28"/>
-      <c r="F61" s="28"/>
-      <c r="G61" s="28"/>
-      <c r="H61" s="28"/>
-      <c r="I61" s="29"/>
+      <c r="E61" s="24"/>
+      <c r="F61" s="24"/>
+      <c r="G61" s="24"/>
+      <c r="H61" s="24"/>
+      <c r="I61" s="25"/>
     </row>
     <row r="62" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B62" s="4">
@@ -2203,14 +2203,14 @@
       <c r="C62" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D62" s="27" t="s">
+      <c r="D62" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E62" s="28"/>
-      <c r="F62" s="28"/>
-      <c r="G62" s="28"/>
-      <c r="H62" s="28"/>
-      <c r="I62" s="29"/>
+      <c r="E62" s="24"/>
+      <c r="F62" s="24"/>
+      <c r="G62" s="24"/>
+      <c r="H62" s="24"/>
+      <c r="I62" s="25"/>
     </row>
     <row r="63" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B63" s="4">
@@ -2254,10 +2254,10 @@
       <c r="F64" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G64" s="27" t="s">
+      <c r="G64" s="23" t="s">
         <v>37</v>
       </c>
-      <c r="H64" s="29"/>
+      <c r="H64" s="25"/>
       <c r="I64" s="1" t="s">
         <v>14</v>
       </c>
@@ -2295,13 +2295,13 @@
       <c r="C66" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D66" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="E66" s="28"/>
-      <c r="F66" s="28"/>
-      <c r="G66" s="28"/>
-      <c r="H66" s="29"/>
+      <c r="D66" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="E66" s="24"/>
+      <c r="F66" s="24"/>
+      <c r="G66" s="24"/>
+      <c r="H66" s="25"/>
       <c r="I66" s="1" t="s">
         <v>16</v>
       </c>
@@ -2313,18 +2313,18 @@
       <c r="C67" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D67" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="E67" s="28"/>
-      <c r="F67" s="29"/>
+      <c r="D67" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="E67" s="24"/>
+      <c r="F67" s="25"/>
       <c r="G67" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="H67" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="I67" s="29"/>
+      <c r="H67" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="I67" s="25"/>
     </row>
     <row r="68" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B68" s="4">
@@ -2339,12 +2339,12 @@
       <c r="E68" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F68" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="G68" s="28"/>
-      <c r="H68" s="28"/>
-      <c r="I68" s="29"/>
+      <c r="F68" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="G68" s="24"/>
+      <c r="H68" s="24"/>
+      <c r="I68" s="25"/>
     </row>
     <row r="69" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B69" s="4">
@@ -2353,14 +2353,14 @@
       <c r="C69" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D69" s="27" t="s">
+      <c r="D69" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E69" s="28"/>
-      <c r="F69" s="28"/>
-      <c r="G69" s="28"/>
-      <c r="H69" s="28"/>
-      <c r="I69" s="29"/>
+      <c r="E69" s="24"/>
+      <c r="F69" s="24"/>
+      <c r="G69" s="24"/>
+      <c r="H69" s="24"/>
+      <c r="I69" s="25"/>
     </row>
     <row r="70" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B70" s="4">
@@ -2369,10 +2369,10 @@
       <c r="C70" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D70" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="E70" s="29"/>
+      <c r="D70" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="E70" s="25"/>
       <c r="F70" s="3" t="s">
         <v>15</v>
       </c>
@@ -2402,10 +2402,10 @@
       <c r="F71" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G71" s="27" t="s">
+      <c r="G71" s="23" t="s">
         <v>37</v>
       </c>
-      <c r="H71" s="29"/>
+      <c r="H71" s="25"/>
       <c r="I71" s="1" t="s">
         <v>14</v>
       </c>
@@ -2443,14 +2443,14 @@
       <c r="C73" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D73" s="27" t="s">
+      <c r="D73" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E73" s="28"/>
-      <c r="F73" s="28"/>
-      <c r="G73" s="28"/>
-      <c r="H73" s="28"/>
-      <c r="I73" s="29"/>
+      <c r="E73" s="24"/>
+      <c r="F73" s="24"/>
+      <c r="G73" s="24"/>
+      <c r="H73" s="24"/>
+      <c r="I73" s="25"/>
     </row>
     <row r="74" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B74" s="4">
@@ -2459,11 +2459,11 @@
       <c r="C74" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D74" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="E74" s="28"/>
-      <c r="F74" s="29"/>
+      <c r="D74" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="E74" s="24"/>
+      <c r="F74" s="25"/>
       <c r="G74" s="3" t="s">
         <v>16</v>
       </c>
@@ -2499,14 +2499,14 @@
       <c r="C76" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D76" s="27" t="s">
+      <c r="D76" s="23" t="s">
         <v>39</v>
       </c>
-      <c r="E76" s="28"/>
-      <c r="F76" s="28"/>
-      <c r="G76" s="28"/>
-      <c r="H76" s="28"/>
-      <c r="I76" s="29"/>
+      <c r="E76" s="24"/>
+      <c r="F76" s="24"/>
+      <c r="G76" s="24"/>
+      <c r="H76" s="24"/>
+      <c r="I76" s="25"/>
     </row>
     <row r="77" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B77" s="4">
@@ -2515,14 +2515,14 @@
       <c r="C77" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D77" s="27" t="s">
+      <c r="D77" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E77" s="28"/>
-      <c r="F77" s="28"/>
-      <c r="G77" s="28"/>
-      <c r="H77" s="28"/>
-      <c r="I77" s="29"/>
+      <c r="E77" s="24"/>
+      <c r="F77" s="24"/>
+      <c r="G77" s="24"/>
+      <c r="H77" s="24"/>
+      <c r="I77" s="25"/>
     </row>
     <row r="78" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B78" s="4">
@@ -2531,14 +2531,14 @@
       <c r="C78" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D78" s="27" t="s">
+      <c r="D78" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E78" s="28"/>
-      <c r="F78" s="28"/>
-      <c r="G78" s="28"/>
-      <c r="H78" s="28"/>
-      <c r="I78" s="29"/>
+      <c r="E78" s="24"/>
+      <c r="F78" s="24"/>
+      <c r="G78" s="24"/>
+      <c r="H78" s="24"/>
+      <c r="I78" s="25"/>
     </row>
     <row r="79" spans="2:9" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B79" s="16" t="s">
@@ -2582,10 +2582,10 @@
       <c r="F80" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G80" s="27" t="s">
+      <c r="G80" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="H80" s="29"/>
+      <c r="H80" s="25"/>
       <c r="I80" s="1" t="s">
         <v>14</v>
       </c>
@@ -2606,10 +2606,10 @@
       <c r="F81" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="G81" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="H81" s="29"/>
+      <c r="G81" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="H81" s="25"/>
       <c r="I81" s="1" t="s">
         <v>16</v>
       </c>
@@ -2673,14 +2673,14 @@
       <c r="C84" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D84" s="27" t="s">
+      <c r="D84" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E84" s="28"/>
-      <c r="F84" s="28"/>
-      <c r="G84" s="28"/>
-      <c r="H84" s="28"/>
-      <c r="I84" s="29"/>
+      <c r="E84" s="24"/>
+      <c r="F84" s="24"/>
+      <c r="G84" s="24"/>
+      <c r="H84" s="24"/>
+      <c r="I84" s="25"/>
     </row>
     <row r="85" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B85" s="4">
@@ -2718,11 +2718,11 @@
       <c r="D86" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="E86" s="27" t="s">
+      <c r="E86" s="23" t="s">
         <v>43</v>
       </c>
-      <c r="F86" s="28"/>
-      <c r="G86" s="29"/>
+      <c r="F86" s="24"/>
+      <c r="G86" s="25"/>
       <c r="H86" s="3" t="s">
         <v>14</v>
       </c>
@@ -2737,18 +2737,18 @@
       <c r="C87" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D87" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="E87" s="29"/>
+      <c r="D87" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="E87" s="25"/>
       <c r="F87" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G87" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="H87" s="28"/>
-      <c r="I87" s="29"/>
+      <c r="G87" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="H87" s="24"/>
+      <c r="I87" s="25"/>
     </row>
     <row r="88" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B88" s="4">
@@ -2757,14 +2757,14 @@
       <c r="C88" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D88" s="27" t="s">
+      <c r="D88" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E88" s="28"/>
-      <c r="F88" s="28"/>
-      <c r="G88" s="28"/>
-      <c r="H88" s="28"/>
-      <c r="I88" s="29"/>
+      <c r="E88" s="24"/>
+      <c r="F88" s="24"/>
+      <c r="G88" s="24"/>
+      <c r="H88" s="24"/>
+      <c r="I88" s="25"/>
     </row>
     <row r="89" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B89" s="4">
@@ -2773,18 +2773,18 @@
       <c r="C89" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D89" s="27" t="s">
+      <c r="D89" s="23" t="s">
         <v>44</v>
       </c>
-      <c r="E89" s="28"/>
-      <c r="F89" s="29"/>
+      <c r="E89" s="24"/>
+      <c r="F89" s="25"/>
       <c r="G89" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="H89" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="I89" s="29"/>
+      <c r="H89" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="I89" s="25"/>
     </row>
     <row r="90" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B90" s="4">
@@ -2793,10 +2793,10 @@
       <c r="C90" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D90" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="E90" s="29"/>
+      <c r="D90" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="E90" s="25"/>
       <c r="F90" s="3" t="s">
         <v>16</v>
       </c>
@@ -2818,13 +2818,13 @@
       <c r="C91" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D91" s="27" t="s">
+      <c r="D91" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E91" s="28"/>
-      <c r="F91" s="28"/>
-      <c r="G91" s="28"/>
-      <c r="H91" s="29"/>
+      <c r="E91" s="24"/>
+      <c r="F91" s="24"/>
+      <c r="G91" s="24"/>
+      <c r="H91" s="25"/>
       <c r="I91" s="18" t="s">
         <v>45</v>
       </c>
@@ -2836,14 +2836,14 @@
       <c r="C92" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D92" s="27" t="s">
+      <c r="D92" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E92" s="28"/>
-      <c r="F92" s="28"/>
-      <c r="G92" s="28"/>
-      <c r="H92" s="28"/>
-      <c r="I92" s="29"/>
+      <c r="E92" s="24"/>
+      <c r="F92" s="24"/>
+      <c r="G92" s="24"/>
+      <c r="H92" s="24"/>
+      <c r="I92" s="25"/>
     </row>
     <row r="93" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B93" s="4">
@@ -2852,14 +2852,14 @@
       <c r="C93" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D93" s="27" t="s">
+      <c r="D93" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="E93" s="28"/>
-      <c r="F93" s="28"/>
-      <c r="G93" s="28"/>
-      <c r="H93" s="28"/>
-      <c r="I93" s="29"/>
+      <c r="E93" s="24"/>
+      <c r="F93" s="24"/>
+      <c r="G93" s="24"/>
+      <c r="H93" s="24"/>
+      <c r="I93" s="25"/>
     </row>
     <row r="94" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B94" s="4">
@@ -2868,14 +2868,14 @@
       <c r="C94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D94" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="E94" s="28"/>
-      <c r="F94" s="28"/>
-      <c r="G94" s="28"/>
-      <c r="H94" s="28"/>
-      <c r="I94" s="29"/>
+      <c r="D94" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="E94" s="24"/>
+      <c r="F94" s="24"/>
+      <c r="G94" s="24"/>
+      <c r="H94" s="24"/>
+      <c r="I94" s="25"/>
     </row>
     <row r="95" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B95" s="4">
@@ -2884,15 +2884,15 @@
       <c r="C95" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D95" s="27" t="s">
+      <c r="D95" s="23" t="s">
         <v>47</v>
       </c>
-      <c r="E95" s="28"/>
-      <c r="F95" s="29"/>
-      <c r="G95" s="27" t="s">
+      <c r="E95" s="24"/>
+      <c r="F95" s="25"/>
+      <c r="G95" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="H95" s="29"/>
+      <c r="H95" s="25"/>
       <c r="I95" s="1" t="s">
         <v>14</v>
       </c>
@@ -2904,14 +2904,14 @@
       <c r="C96" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D96" s="27" t="s">
+      <c r="D96" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E96" s="28"/>
-      <c r="F96" s="28"/>
-      <c r="G96" s="28"/>
-      <c r="H96" s="28"/>
-      <c r="I96" s="29"/>
+      <c r="E96" s="24"/>
+      <c r="F96" s="24"/>
+      <c r="G96" s="24"/>
+      <c r="H96" s="24"/>
+      <c r="I96" s="25"/>
     </row>
     <row r="97" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B97" s="4">
@@ -2920,14 +2920,14 @@
       <c r="C97" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D97" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="E97" s="28"/>
-      <c r="F97" s="28"/>
-      <c r="G97" s="28"/>
-      <c r="H97" s="28"/>
-      <c r="I97" s="29"/>
+      <c r="D97" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="E97" s="24"/>
+      <c r="F97" s="24"/>
+      <c r="G97" s="24"/>
+      <c r="H97" s="24"/>
+      <c r="I97" s="25"/>
     </row>
     <row r="98" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B98" s="4">
@@ -2936,14 +2936,14 @@
       <c r="C98" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D98" s="27" t="s">
+      <c r="D98" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E98" s="28"/>
-      <c r="F98" s="28"/>
-      <c r="G98" s="28"/>
-      <c r="H98" s="28"/>
-      <c r="I98" s="29"/>
+      <c r="E98" s="24"/>
+      <c r="F98" s="24"/>
+      <c r="G98" s="24"/>
+      <c r="H98" s="24"/>
+      <c r="I98" s="25"/>
     </row>
     <row r="99" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B99" s="4">
@@ -2952,12 +2952,12 @@
       <c r="C99" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D99" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="E99" s="28"/>
-      <c r="F99" s="28"/>
-      <c r="G99" s="29"/>
+      <c r="D99" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="E99" s="24"/>
+      <c r="F99" s="24"/>
+      <c r="G99" s="25"/>
       <c r="H99" s="3" t="s">
         <v>49</v>
       </c>
@@ -2981,21 +2981,21 @@
       <c r="F100" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="G100" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="H100" s="28"/>
-      <c r="I100" s="29"/>
+      <c r="G100" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="H100" s="24"/>
+      <c r="I100" s="25"/>
     </row>
     <row r="101" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B101" s="27"/>
-      <c r="C101" s="28"/>
-      <c r="D101" s="28"/>
-      <c r="E101" s="28"/>
-      <c r="F101" s="28"/>
-      <c r="G101" s="28"/>
-      <c r="H101" s="28"/>
-      <c r="I101" s="29"/>
+      <c r="B101" s="23"/>
+      <c r="C101" s="24"/>
+      <c r="D101" s="24"/>
+      <c r="E101" s="24"/>
+      <c r="F101" s="24"/>
+      <c r="G101" s="24"/>
+      <c r="H101" s="24"/>
+      <c r="I101" s="25"/>
     </row>
     <row r="102" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B102" s="3"/>
@@ -3014,10 +3014,10 @@
       <c r="C103" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D103" s="27" t="s">
+      <c r="D103" s="23" t="s">
         <v>51</v>
       </c>
-      <c r="E103" s="29"/>
+      <c r="E103" s="25"/>
       <c r="F103" s="3"/>
       <c r="G103" s="3"/>
       <c r="H103" s="3"/>
@@ -3030,10 +3030,10 @@
       <c r="C104" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D104" s="27" t="s">
+      <c r="D104" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="E104" s="29"/>
+      <c r="E104" s="25"/>
       <c r="F104" s="3"/>
       <c r="G104" s="3"/>
       <c r="H104" s="3"/>
@@ -3046,10 +3046,10 @@
       <c r="C105" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D105" s="27" t="s">
+      <c r="D105" s="23" t="s">
         <v>53</v>
       </c>
-      <c r="E105" s="29"/>
+      <c r="E105" s="25"/>
       <c r="F105" s="3"/>
       <c r="G105" s="3"/>
       <c r="H105" s="3"/>
@@ -3062,10 +3062,10 @@
       <c r="C106" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D106" s="27" t="s">
+      <c r="D106" s="23" t="s">
         <v>54</v>
       </c>
-      <c r="E106" s="29"/>
+      <c r="E106" s="25"/>
       <c r="F106" s="3"/>
       <c r="G106" s="3"/>
       <c r="H106" s="3"/>
@@ -3078,10 +3078,10 @@
       <c r="C107" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D107" s="27" t="s">
+      <c r="D107" s="23" t="s">
         <v>55</v>
       </c>
-      <c r="E107" s="29"/>
+      <c r="E107" s="25"/>
       <c r="F107" s="3"/>
       <c r="G107" s="3"/>
       <c r="H107" s="3"/>
@@ -3094,10 +3094,10 @@
       <c r="C108" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D108" s="27" t="s">
+      <c r="D108" s="23" t="s">
         <v>56</v>
       </c>
-      <c r="E108" s="29"/>
+      <c r="E108" s="25"/>
       <c r="F108" s="3"/>
       <c r="G108" s="3"/>
       <c r="H108" s="3"/>
@@ -3134,28 +3134,28 @@
       <c r="I111" s="20"/>
     </row>
     <row r="112" spans="2:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B112" s="30" t="s">
+      <c r="B112" s="34" t="s">
         <v>57</v>
       </c>
-      <c r="C112" s="31"/>
-      <c r="D112" s="31"/>
-      <c r="E112" s="31"/>
-      <c r="F112" s="31"/>
-      <c r="G112" s="31"/>
-      <c r="H112" s="31"/>
-      <c r="I112" s="31"/>
-      <c r="J112" s="32"/>
+      <c r="C112" s="35"/>
+      <c r="D112" s="35"/>
+      <c r="E112" s="35"/>
+      <c r="F112" s="35"/>
+      <c r="G112" s="35"/>
+      <c r="H112" s="35"/>
+      <c r="I112" s="35"/>
+      <c r="J112" s="36"/>
     </row>
     <row r="113" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B113" s="33"/>
-      <c r="C113" s="34"/>
-      <c r="D113" s="34"/>
-      <c r="E113" s="34"/>
-      <c r="F113" s="34"/>
-      <c r="G113" s="34"/>
-      <c r="H113" s="34"/>
-      <c r="I113" s="34"/>
-      <c r="J113" s="35"/>
+      <c r="B113" s="37"/>
+      <c r="C113" s="38"/>
+      <c r="D113" s="38"/>
+      <c r="E113" s="38"/>
+      <c r="F113" s="38"/>
+      <c r="G113" s="38"/>
+      <c r="H113" s="38"/>
+      <c r="I113" s="38"/>
+      <c r="J113" s="39"/>
     </row>
     <row r="114" spans="2:10" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B114" s="8" t="s">
@@ -3286,13 +3286,13 @@
       <c r="E118" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="F118" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="G118" s="28"/>
-      <c r="H118" s="28"/>
-      <c r="I118" s="28"/>
-      <c r="J118" s="29"/>
+      <c r="F118" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="G118" s="24"/>
+      <c r="H118" s="24"/>
+      <c r="I118" s="24"/>
+      <c r="J118" s="25"/>
     </row>
     <row r="119" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B119" s="4">
@@ -3330,13 +3330,13 @@
       <c r="C120" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D120" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="E120" s="28"/>
-      <c r="F120" s="28"/>
-      <c r="G120" s="28"/>
-      <c r="H120" s="29"/>
+      <c r="D120" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="E120" s="24"/>
+      <c r="F120" s="24"/>
+      <c r="G120" s="24"/>
+      <c r="H120" s="25"/>
       <c r="I120" s="1" t="s">
         <v>16</v>
       </c>
@@ -3351,15 +3351,15 @@
       <c r="C121" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D121" s="27" t="s">
+      <c r="D121" s="23" t="s">
         <v>65</v>
       </c>
-      <c r="E121" s="28"/>
-      <c r="F121" s="28"/>
-      <c r="G121" s="28"/>
-      <c r="H121" s="28"/>
-      <c r="I121" s="28"/>
-      <c r="J121" s="29"/>
+      <c r="E121" s="24"/>
+      <c r="F121" s="24"/>
+      <c r="G121" s="24"/>
+      <c r="H121" s="24"/>
+      <c r="I121" s="24"/>
+      <c r="J121" s="25"/>
     </row>
     <row r="122" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B122" s="4">
@@ -3406,12 +3406,12 @@
       <c r="F123" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="G123" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="H123" s="28"/>
-      <c r="I123" s="28"/>
-      <c r="J123" s="29"/>
+      <c r="G123" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="H123" s="24"/>
+      <c r="I123" s="24"/>
+      <c r="J123" s="25"/>
     </row>
     <row r="124" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B124" s="4">
@@ -3429,12 +3429,12 @@
       <c r="F124" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="G124" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="H124" s="28"/>
-      <c r="I124" s="28"/>
-      <c r="J124" s="29"/>
+      <c r="G124" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="H124" s="24"/>
+      <c r="I124" s="24"/>
+      <c r="J124" s="25"/>
     </row>
     <row r="125" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B125" s="4">
@@ -3449,13 +3449,13 @@
       <c r="E125" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="F125" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="G125" s="28"/>
-      <c r="H125" s="28"/>
-      <c r="I125" s="28"/>
-      <c r="J125" s="29"/>
+      <c r="F125" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="G125" s="24"/>
+      <c r="H125" s="24"/>
+      <c r="I125" s="24"/>
+      <c r="J125" s="25"/>
     </row>
     <row r="126" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B126" s="4">
@@ -3473,11 +3473,11 @@
       <c r="F126" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="G126" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="H126" s="28"/>
-      <c r="I126" s="29"/>
+      <c r="G126" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="H126" s="24"/>
+      <c r="I126" s="25"/>
       <c r="J126" s="1" t="s">
         <v>16</v>
       </c>
@@ -3495,13 +3495,13 @@
       <c r="E127" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="F127" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="G127" s="28"/>
-      <c r="H127" s="28"/>
-      <c r="I127" s="28"/>
-      <c r="J127" s="29"/>
+      <c r="F127" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="G127" s="24"/>
+      <c r="H127" s="24"/>
+      <c r="I127" s="24"/>
+      <c r="J127" s="25"/>
     </row>
     <row r="128" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B128" s="4">
@@ -3510,15 +3510,15 @@
       <c r="C128" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D128" s="27" t="s">
+      <c r="D128" s="23" t="s">
         <v>65</v>
       </c>
-      <c r="E128" s="28"/>
-      <c r="F128" s="28"/>
-      <c r="G128" s="28"/>
-      <c r="H128" s="28"/>
-      <c r="I128" s="28"/>
-      <c r="J128" s="29"/>
+      <c r="E128" s="24"/>
+      <c r="F128" s="24"/>
+      <c r="G128" s="24"/>
+      <c r="H128" s="24"/>
+      <c r="I128" s="24"/>
+      <c r="J128" s="25"/>
     </row>
     <row r="129" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B129" s="4">
@@ -3701,15 +3701,15 @@
       <c r="C135" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D135" s="27" t="s">
+      <c r="D135" s="23" t="s">
         <v>65</v>
       </c>
-      <c r="E135" s="28"/>
-      <c r="F135" s="28"/>
-      <c r="G135" s="28"/>
-      <c r="H135" s="28"/>
-      <c r="I135" s="28"/>
-      <c r="J135" s="29"/>
+      <c r="E135" s="24"/>
+      <c r="F135" s="24"/>
+      <c r="G135" s="24"/>
+      <c r="H135" s="24"/>
+      <c r="I135" s="24"/>
+      <c r="J135" s="25"/>
     </row>
     <row r="136" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B136" s="4">
@@ -3921,15 +3921,15 @@
       <c r="C143" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D143" s="27" t="s">
+      <c r="D143" s="23" t="s">
         <v>65</v>
       </c>
-      <c r="E143" s="28"/>
-      <c r="F143" s="28"/>
-      <c r="G143" s="28"/>
-      <c r="H143" s="28"/>
-      <c r="I143" s="28"/>
-      <c r="J143" s="29"/>
+      <c r="E143" s="24"/>
+      <c r="F143" s="24"/>
+      <c r="G143" s="24"/>
+      <c r="H143" s="24"/>
+      <c r="I143" s="24"/>
+      <c r="J143" s="25"/>
     </row>
     <row r="144" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B144" s="4">
@@ -4005,12 +4005,12 @@
       <c r="F146" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="G146" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="H146" s="28"/>
-      <c r="I146" s="28"/>
-      <c r="J146" s="29"/>
+      <c r="G146" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="H146" s="24"/>
+      <c r="I146" s="24"/>
+      <c r="J146" s="25"/>
     </row>
     <row r="147" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B147" s="4">
@@ -4077,15 +4077,15 @@
       <c r="C149" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D149" s="23" t="s">
+      <c r="D149" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="E149" s="24"/>
-      <c r="F149" s="24"/>
-      <c r="G149" s="24"/>
-      <c r="H149" s="24"/>
-      <c r="I149" s="24"/>
-      <c r="J149" s="38"/>
+      <c r="E149" s="27"/>
+      <c r="F149" s="27"/>
+      <c r="G149" s="27"/>
+      <c r="H149" s="27"/>
+      <c r="I149" s="27"/>
+      <c r="J149" s="28"/>
     </row>
     <row r="150" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B150" s="4">
@@ -4094,13 +4094,13 @@
       <c r="C150" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D150" s="25"/>
-      <c r="E150" s="26"/>
-      <c r="F150" s="26"/>
-      <c r="G150" s="26"/>
-      <c r="H150" s="26"/>
-      <c r="I150" s="26"/>
-      <c r="J150" s="39"/>
+      <c r="D150" s="29"/>
+      <c r="E150" s="30"/>
+      <c r="F150" s="30"/>
+      <c r="G150" s="30"/>
+      <c r="H150" s="30"/>
+      <c r="I150" s="30"/>
+      <c r="J150" s="31"/>
     </row>
     <row r="151" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B151" s="4">
@@ -4147,11 +4147,11 @@
       <c r="F152" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="G152" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="H152" s="28"/>
-      <c r="I152" s="29"/>
+      <c r="G152" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="H152" s="24"/>
+      <c r="I152" s="25"/>
       <c r="J152" s="1" t="s">
         <v>69</v>
       </c>
@@ -4279,15 +4279,15 @@
       <c r="C157" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D157" s="27" t="s">
+      <c r="D157" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E157" s="28"/>
-      <c r="F157" s="28"/>
-      <c r="G157" s="28"/>
-      <c r="H157" s="28"/>
-      <c r="I157" s="28"/>
-      <c r="J157" s="29"/>
+      <c r="E157" s="24"/>
+      <c r="F157" s="24"/>
+      <c r="G157" s="24"/>
+      <c r="H157" s="24"/>
+      <c r="I157" s="24"/>
+      <c r="J157" s="25"/>
     </row>
     <row r="158" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B158" s="4">
@@ -4468,15 +4468,15 @@
       <c r="C164" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D164" s="27" t="s">
+      <c r="D164" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E164" s="28"/>
-      <c r="F164" s="28"/>
-      <c r="G164" s="28"/>
-      <c r="H164" s="28"/>
-      <c r="I164" s="28"/>
-      <c r="J164" s="29"/>
+      <c r="E164" s="24"/>
+      <c r="F164" s="24"/>
+      <c r="G164" s="24"/>
+      <c r="H164" s="24"/>
+      <c r="I164" s="24"/>
+      <c r="J164" s="25"/>
     </row>
     <row r="165" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B165" s="4">
@@ -4674,15 +4674,15 @@
       <c r="C172" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D172" s="27" t="s">
+      <c r="D172" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E172" s="28"/>
-      <c r="F172" s="28"/>
-      <c r="G172" s="28"/>
-      <c r="H172" s="28"/>
-      <c r="I172" s="28"/>
-      <c r="J172" s="29"/>
+      <c r="E172" s="24"/>
+      <c r="F172" s="24"/>
+      <c r="G172" s="24"/>
+      <c r="H172" s="24"/>
+      <c r="I172" s="24"/>
+      <c r="J172" s="25"/>
     </row>
     <row r="173" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B173" s="4">
@@ -4746,44 +4746,44 @@
       <c r="B175" s="4">
         <v>45903</v>
       </c>
-      <c r="C175" s="23" t="s">
+      <c r="C175" s="26" t="s">
         <v>39</v>
       </c>
-      <c r="D175" s="24"/>
-      <c r="E175" s="24"/>
-      <c r="F175" s="24"/>
-      <c r="G175" s="24"/>
-      <c r="H175" s="24"/>
-      <c r="I175" s="24"/>
-      <c r="J175" s="24"/>
+      <c r="D175" s="27"/>
+      <c r="E175" s="27"/>
+      <c r="F175" s="27"/>
+      <c r="G175" s="27"/>
+      <c r="H175" s="27"/>
+      <c r="I175" s="27"/>
+      <c r="J175" s="27"/>
     </row>
     <row r="176" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B176" s="4">
         <v>45904</v>
       </c>
-      <c r="C176" s="25"/>
-      <c r="D176" s="26"/>
-      <c r="E176" s="26"/>
-      <c r="F176" s="26"/>
-      <c r="G176" s="26"/>
-      <c r="H176" s="26"/>
-      <c r="I176" s="26"/>
-      <c r="J176" s="26"/>
+      <c r="C176" s="29"/>
+      <c r="D176" s="30"/>
+      <c r="E176" s="30"/>
+      <c r="F176" s="30"/>
+      <c r="G176" s="30"/>
+      <c r="H176" s="30"/>
+      <c r="I176" s="30"/>
+      <c r="J176" s="30"/>
     </row>
     <row r="177" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B177" s="4">
         <v>45905</v>
       </c>
-      <c r="C177" s="27" t="s">
+      <c r="C177" s="23" t="s">
         <v>39</v>
       </c>
-      <c r="D177" s="28"/>
-      <c r="E177" s="28"/>
-      <c r="F177" s="28"/>
-      <c r="G177" s="28"/>
-      <c r="H177" s="28"/>
-      <c r="I177" s="28"/>
-      <c r="J177" s="29"/>
+      <c r="D177" s="24"/>
+      <c r="E177" s="24"/>
+      <c r="F177" s="24"/>
+      <c r="G177" s="24"/>
+      <c r="H177" s="24"/>
+      <c r="I177" s="24"/>
+      <c r="J177" s="25"/>
     </row>
     <row r="178" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B178" s="4">
@@ -4821,15 +4821,27 @@
       <c r="C179" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D179" s="3"/>
+      <c r="D179" s="3" t="s">
+        <v>14</v>
+      </c>
       <c r="E179" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="F179" s="3"/>
-      <c r="G179" s="3"/>
-      <c r="H179" s="3"/>
-      <c r="I179" s="1"/>
-      <c r="J179" s="1"/>
+      <c r="F179" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G179" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H179" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I179" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="J179" s="1" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="180" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B180" s="4">
@@ -4896,13 +4908,27 @@
       <c r="C182" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D182" s="3"/>
-      <c r="E182" s="3"/>
-      <c r="F182" s="3"/>
-      <c r="G182" s="3"/>
-      <c r="H182" s="3"/>
-      <c r="I182" s="1"/>
-      <c r="J182" s="1"/>
+      <c r="D182" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E182" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F182" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G182" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H182" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I182" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J182" s="1" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="183" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B183" s="4">
@@ -7482,6 +7508,77 @@
     </row>
   </sheetData>
   <mergeCells count="87">
+    <mergeCell ref="C175:J176"/>
+    <mergeCell ref="D164:J164"/>
+    <mergeCell ref="D157:J157"/>
+    <mergeCell ref="D143:J143"/>
+    <mergeCell ref="D135:J135"/>
+    <mergeCell ref="D172:J172"/>
+    <mergeCell ref="G146:J146"/>
+    <mergeCell ref="D108:E108"/>
+    <mergeCell ref="B112:J113"/>
+    <mergeCell ref="G124:J124"/>
+    <mergeCell ref="D120:H120"/>
+    <mergeCell ref="G123:J123"/>
+    <mergeCell ref="D121:J121"/>
+    <mergeCell ref="D31:I31"/>
+    <mergeCell ref="G35:H35"/>
+    <mergeCell ref="D40:I40"/>
+    <mergeCell ref="D33:I33"/>
+    <mergeCell ref="D46:I46"/>
+    <mergeCell ref="D43:I43"/>
+    <mergeCell ref="D78:I78"/>
+    <mergeCell ref="G71:H71"/>
+    <mergeCell ref="D76:I76"/>
+    <mergeCell ref="D66:H66"/>
+    <mergeCell ref="D77:I77"/>
+    <mergeCell ref="D73:I73"/>
+    <mergeCell ref="D70:E70"/>
+    <mergeCell ref="D74:F74"/>
+    <mergeCell ref="D84:I84"/>
+    <mergeCell ref="D69:I69"/>
+    <mergeCell ref="D8:I8"/>
+    <mergeCell ref="D9:I9"/>
+    <mergeCell ref="D10:I10"/>
+    <mergeCell ref="D11:I11"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="D14:I14"/>
+    <mergeCell ref="G27:H27"/>
+    <mergeCell ref="D25:I25"/>
+    <mergeCell ref="G20:H20"/>
+    <mergeCell ref="D19:I19"/>
+    <mergeCell ref="D18:I18"/>
+    <mergeCell ref="D30:I30"/>
+    <mergeCell ref="G80:H80"/>
+    <mergeCell ref="G42:H42"/>
+    <mergeCell ref="D60:I60"/>
+    <mergeCell ref="D62:I62"/>
+    <mergeCell ref="D61:I61"/>
+    <mergeCell ref="G49:H49"/>
+    <mergeCell ref="D47:I47"/>
+    <mergeCell ref="D55:I55"/>
+    <mergeCell ref="G57:H57"/>
+    <mergeCell ref="G64:H64"/>
+    <mergeCell ref="D96:I96"/>
+    <mergeCell ref="D95:F95"/>
+    <mergeCell ref="G95:H95"/>
+    <mergeCell ref="D92:I92"/>
+    <mergeCell ref="D93:I93"/>
+    <mergeCell ref="D90:E90"/>
+    <mergeCell ref="D91:H91"/>
+    <mergeCell ref="E86:G86"/>
+    <mergeCell ref="D88:I88"/>
+    <mergeCell ref="H67:I67"/>
+    <mergeCell ref="G81:H81"/>
+    <mergeCell ref="D67:F67"/>
+    <mergeCell ref="F68:I68"/>
+    <mergeCell ref="D87:E87"/>
+    <mergeCell ref="G87:I87"/>
+    <mergeCell ref="D98:I98"/>
+    <mergeCell ref="D94:I94"/>
+    <mergeCell ref="H89:I89"/>
+    <mergeCell ref="D89:F89"/>
+    <mergeCell ref="D97:I97"/>
     <mergeCell ref="C177:J177"/>
     <mergeCell ref="D106:E106"/>
     <mergeCell ref="D99:G99"/>
@@ -7498,77 +7595,6 @@
     <mergeCell ref="F118:J118"/>
     <mergeCell ref="G152:I152"/>
     <mergeCell ref="D149:J150"/>
-    <mergeCell ref="D98:I98"/>
-    <mergeCell ref="D94:I94"/>
-    <mergeCell ref="H89:I89"/>
-    <mergeCell ref="D89:F89"/>
-    <mergeCell ref="D97:I97"/>
-    <mergeCell ref="G64:H64"/>
-    <mergeCell ref="D96:I96"/>
-    <mergeCell ref="D95:F95"/>
-    <mergeCell ref="G95:H95"/>
-    <mergeCell ref="D92:I92"/>
-    <mergeCell ref="D93:I93"/>
-    <mergeCell ref="D90:E90"/>
-    <mergeCell ref="D91:H91"/>
-    <mergeCell ref="E86:G86"/>
-    <mergeCell ref="D88:I88"/>
-    <mergeCell ref="H67:I67"/>
-    <mergeCell ref="G81:H81"/>
-    <mergeCell ref="D67:F67"/>
-    <mergeCell ref="F68:I68"/>
-    <mergeCell ref="D87:E87"/>
-    <mergeCell ref="G87:I87"/>
-    <mergeCell ref="D60:I60"/>
-    <mergeCell ref="D62:I62"/>
-    <mergeCell ref="D61:I61"/>
-    <mergeCell ref="G49:H49"/>
-    <mergeCell ref="D47:I47"/>
-    <mergeCell ref="D55:I55"/>
-    <mergeCell ref="G57:H57"/>
-    <mergeCell ref="D84:I84"/>
-    <mergeCell ref="D69:I69"/>
-    <mergeCell ref="D8:I8"/>
-    <mergeCell ref="D9:I9"/>
-    <mergeCell ref="D10:I10"/>
-    <mergeCell ref="D11:I11"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="D14:I14"/>
-    <mergeCell ref="G27:H27"/>
-    <mergeCell ref="D25:I25"/>
-    <mergeCell ref="G20:H20"/>
-    <mergeCell ref="D19:I19"/>
-    <mergeCell ref="D18:I18"/>
-    <mergeCell ref="D30:I30"/>
-    <mergeCell ref="G80:H80"/>
-    <mergeCell ref="G42:H42"/>
-    <mergeCell ref="D78:I78"/>
-    <mergeCell ref="G71:H71"/>
-    <mergeCell ref="D76:I76"/>
-    <mergeCell ref="D66:H66"/>
-    <mergeCell ref="D77:I77"/>
-    <mergeCell ref="D73:I73"/>
-    <mergeCell ref="D70:E70"/>
-    <mergeCell ref="D74:F74"/>
-    <mergeCell ref="D31:I31"/>
-    <mergeCell ref="G35:H35"/>
-    <mergeCell ref="D40:I40"/>
-    <mergeCell ref="D33:I33"/>
-    <mergeCell ref="D46:I46"/>
-    <mergeCell ref="D43:I43"/>
-    <mergeCell ref="D108:E108"/>
-    <mergeCell ref="B112:J113"/>
-    <mergeCell ref="G124:J124"/>
-    <mergeCell ref="D120:H120"/>
-    <mergeCell ref="G123:J123"/>
-    <mergeCell ref="D121:J121"/>
-    <mergeCell ref="C175:J176"/>
-    <mergeCell ref="D164:J164"/>
-    <mergeCell ref="D157:J157"/>
-    <mergeCell ref="D143:J143"/>
-    <mergeCell ref="D135:J135"/>
-    <mergeCell ref="D172:J172"/>
-    <mergeCell ref="G146:J146"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/attendance_sheet.xlsx
+++ b/attendance_sheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\repositary\3rd_Year_5th_Semester\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF4DF54D-989F-4068-AF20-E60243E67003}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E234101C-36F6-4704-80B1-63CAA3265F60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{EB654061-A886-47D1-BF86-9B1A84FCE7FB}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="912" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="920" uniqueCount="74">
   <si>
     <t>Date</t>
   </si>
@@ -538,22 +538,10 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
@@ -562,13 +550,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -587,6 +575,18 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -990,14 +990,14 @@
       <c r="C8" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D8" s="32" t="s">
+      <c r="D8" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="E8" s="32"/>
-      <c r="F8" s="32"/>
-      <c r="G8" s="32"/>
-      <c r="H8" s="32"/>
-      <c r="I8" s="32"/>
+      <c r="E8" s="37"/>
+      <c r="F8" s="37"/>
+      <c r="G8" s="37"/>
+      <c r="H8" s="37"/>
+      <c r="I8" s="37"/>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B9" s="4">
@@ -1006,14 +1006,14 @@
       <c r="C9" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D9" s="32" t="s">
+      <c r="D9" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="E9" s="32"/>
-      <c r="F9" s="32"/>
-      <c r="G9" s="32"/>
-      <c r="H9" s="32"/>
-      <c r="I9" s="32"/>
+      <c r="E9" s="37"/>
+      <c r="F9" s="37"/>
+      <c r="G9" s="37"/>
+      <c r="H9" s="37"/>
+      <c r="I9" s="37"/>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B10" s="4">
@@ -1022,14 +1022,14 @@
       <c r="C10" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D10" s="32" t="s">
+      <c r="D10" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="E10" s="32"/>
-      <c r="F10" s="32"/>
-      <c r="G10" s="32"/>
-      <c r="H10" s="32"/>
-      <c r="I10" s="32"/>
+      <c r="E10" s="37"/>
+      <c r="F10" s="37"/>
+      <c r="G10" s="37"/>
+      <c r="H10" s="37"/>
+      <c r="I10" s="37"/>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B11" s="4">
@@ -1038,14 +1038,14 @@
       <c r="C11" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D11" s="32" t="s">
+      <c r="D11" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="E11" s="32"/>
-      <c r="F11" s="32"/>
-      <c r="G11" s="32"/>
-      <c r="H11" s="32"/>
-      <c r="I11" s="32"/>
+      <c r="E11" s="37"/>
+      <c r="F11" s="37"/>
+      <c r="G11" s="37"/>
+      <c r="H11" s="37"/>
+      <c r="I11" s="37"/>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B12" s="4">
@@ -1089,10 +1089,10 @@
       <c r="F13" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="G13" s="32" t="s">
+      <c r="G13" s="37" t="s">
         <v>18</v>
       </c>
-      <c r="H13" s="32"/>
+      <c r="H13" s="37"/>
       <c r="I13" s="1" t="s">
         <v>14</v>
       </c>
@@ -1104,14 +1104,14 @@
       <c r="C14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D14" s="32" t="s">
+      <c r="D14" s="37" t="s">
         <v>19</v>
       </c>
-      <c r="E14" s="32"/>
-      <c r="F14" s="32"/>
-      <c r="G14" s="32"/>
-      <c r="H14" s="32"/>
-      <c r="I14" s="32"/>
+      <c r="E14" s="37"/>
+      <c r="F14" s="37"/>
+      <c r="G14" s="37"/>
+      <c r="H14" s="37"/>
+      <c r="I14" s="37"/>
     </row>
     <row r="15" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B15" s="4">
@@ -1198,14 +1198,14 @@
       <c r="C18" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D18" s="32" t="s">
+      <c r="D18" s="37" t="s">
         <v>23</v>
       </c>
-      <c r="E18" s="32"/>
-      <c r="F18" s="32"/>
-      <c r="G18" s="32"/>
-      <c r="H18" s="32"/>
-      <c r="I18" s="32"/>
+      <c r="E18" s="37"/>
+      <c r="F18" s="37"/>
+      <c r="G18" s="37"/>
+      <c r="H18" s="37"/>
+      <c r="I18" s="37"/>
     </row>
     <row r="19" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B19" s="4">
@@ -1214,14 +1214,14 @@
       <c r="C19" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D19" s="32" t="s">
+      <c r="D19" s="37" t="s">
         <v>23</v>
       </c>
-      <c r="E19" s="32"/>
-      <c r="F19" s="32"/>
-      <c r="G19" s="32"/>
-      <c r="H19" s="32"/>
-      <c r="I19" s="32"/>
+      <c r="E19" s="37"/>
+      <c r="F19" s="37"/>
+      <c r="G19" s="37"/>
+      <c r="H19" s="37"/>
+      <c r="I19" s="37"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B20" s="4">
@@ -1239,10 +1239,10 @@
       <c r="F20" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G20" s="32" t="s">
+      <c r="G20" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="H20" s="32"/>
+      <c r="H20" s="37"/>
       <c r="I20" s="1" t="s">
         <v>14</v>
       </c>
@@ -1358,14 +1358,14 @@
       <c r="C25" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D25" s="32" t="s">
+      <c r="D25" s="37" t="s">
         <v>26</v>
       </c>
-      <c r="E25" s="32"/>
-      <c r="F25" s="32"/>
-      <c r="G25" s="32"/>
-      <c r="H25" s="32"/>
-      <c r="I25" s="32"/>
+      <c r="E25" s="37"/>
+      <c r="F25" s="37"/>
+      <c r="G25" s="37"/>
+      <c r="H25" s="37"/>
+      <c r="I25" s="37"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B26" s="4">
@@ -1409,10 +1409,10 @@
       <c r="F27" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G27" s="32" t="s">
+      <c r="G27" s="37" t="s">
         <v>18</v>
       </c>
-      <c r="H27" s="32"/>
+      <c r="H27" s="37"/>
       <c r="I27" s="1" t="s">
         <v>14</v>
       </c>
@@ -1476,14 +1476,14 @@
       <c r="C30" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D30" s="33" t="s">
+      <c r="D30" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="E30" s="33"/>
-      <c r="F30" s="33"/>
-      <c r="G30" s="33"/>
-      <c r="H30" s="33"/>
-      <c r="I30" s="33"/>
+      <c r="E30" s="36"/>
+      <c r="F30" s="36"/>
+      <c r="G30" s="36"/>
+      <c r="H30" s="36"/>
+      <c r="I30" s="36"/>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B31" s="4">
@@ -1492,14 +1492,14 @@
       <c r="C31" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D31" s="33" t="s">
+      <c r="D31" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="E31" s="33"/>
-      <c r="F31" s="33"/>
-      <c r="G31" s="33"/>
-      <c r="H31" s="33"/>
-      <c r="I31" s="33"/>
+      <c r="E31" s="36"/>
+      <c r="F31" s="36"/>
+      <c r="G31" s="36"/>
+      <c r="H31" s="36"/>
+      <c r="I31" s="36"/>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B32" s="4">
@@ -1534,14 +1534,14 @@
       <c r="C33" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D33" s="33" t="s">
+      <c r="D33" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="E33" s="33"/>
-      <c r="F33" s="33"/>
-      <c r="G33" s="33"/>
-      <c r="H33" s="33"/>
-      <c r="I33" s="33"/>
+      <c r="E33" s="36"/>
+      <c r="F33" s="36"/>
+      <c r="G33" s="36"/>
+      <c r="H33" s="36"/>
+      <c r="I33" s="36"/>
     </row>
     <row r="34" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B34" s="4">
@@ -1585,10 +1585,10 @@
       <c r="F35" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G35" s="33" t="s">
+      <c r="G35" s="36" t="s">
         <v>18</v>
       </c>
-      <c r="H35" s="33"/>
+      <c r="H35" s="36"/>
       <c r="I35" s="1" t="s">
         <v>14</v>
       </c>
@@ -1704,14 +1704,14 @@
       <c r="C40" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D40" s="33" t="s">
+      <c r="D40" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="E40" s="33"/>
-      <c r="F40" s="33"/>
-      <c r="G40" s="33"/>
-      <c r="H40" s="33"/>
-      <c r="I40" s="33"/>
+      <c r="E40" s="36"/>
+      <c r="F40" s="36"/>
+      <c r="G40" s="36"/>
+      <c r="H40" s="36"/>
+      <c r="I40" s="36"/>
     </row>
     <row r="41" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B41" s="4">
@@ -1755,10 +1755,10 @@
       <c r="F42" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G42" s="33" t="s">
+      <c r="G42" s="36" t="s">
         <v>28</v>
       </c>
-      <c r="H42" s="33"/>
+      <c r="H42" s="36"/>
       <c r="I42" s="1" t="s">
         <v>15</v>
       </c>
@@ -1770,14 +1770,14 @@
       <c r="C43" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D43" s="33" t="s">
+      <c r="D43" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="E43" s="33"/>
-      <c r="F43" s="33"/>
-      <c r="G43" s="33"/>
-      <c r="H43" s="33"/>
-      <c r="I43" s="33"/>
+      <c r="E43" s="36"/>
+      <c r="F43" s="36"/>
+      <c r="G43" s="36"/>
+      <c r="H43" s="36"/>
+      <c r="I43" s="36"/>
     </row>
     <row r="44" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B44" s="4">
@@ -1841,14 +1841,14 @@
       <c r="C46" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D46" s="33" t="s">
+      <c r="D46" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="E46" s="33"/>
-      <c r="F46" s="33"/>
-      <c r="G46" s="33"/>
-      <c r="H46" s="33"/>
-      <c r="I46" s="33"/>
+      <c r="E46" s="36"/>
+      <c r="F46" s="36"/>
+      <c r="G46" s="36"/>
+      <c r="H46" s="36"/>
+      <c r="I46" s="36"/>
     </row>
     <row r="47" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B47" s="4">
@@ -1857,14 +1857,14 @@
       <c r="C47" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D47" s="23" t="s">
+      <c r="D47" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="E47" s="24"/>
-      <c r="F47" s="24"/>
-      <c r="G47" s="24"/>
-      <c r="H47" s="24"/>
-      <c r="I47" s="25"/>
+      <c r="E47" s="28"/>
+      <c r="F47" s="28"/>
+      <c r="G47" s="28"/>
+      <c r="H47" s="28"/>
+      <c r="I47" s="29"/>
     </row>
     <row r="48" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B48" s="4">
@@ -1908,10 +1908,10 @@
       <c r="F49" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G49" s="23" t="s">
+      <c r="G49" s="27" t="s">
         <v>29</v>
       </c>
-      <c r="H49" s="25"/>
+      <c r="H49" s="29"/>
       <c r="I49" s="1" t="s">
         <v>30</v>
       </c>
@@ -2053,14 +2053,14 @@
       <c r="C55" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="D55" s="24" t="s">
+      <c r="D55" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="E55" s="24"/>
-      <c r="F55" s="24"/>
-      <c r="G55" s="24"/>
-      <c r="H55" s="24"/>
-      <c r="I55" s="24"/>
+      <c r="E55" s="28"/>
+      <c r="F55" s="28"/>
+      <c r="G55" s="28"/>
+      <c r="H55" s="28"/>
+      <c r="I55" s="28"/>
     </row>
     <row r="56" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B56" s="4">
@@ -2104,10 +2104,10 @@
       <c r="F57" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G57" s="23" t="s">
+      <c r="G57" s="27" t="s">
         <v>37</v>
       </c>
-      <c r="H57" s="25"/>
+      <c r="H57" s="29"/>
       <c r="I57" s="1" t="s">
         <v>36</v>
       </c>
@@ -2171,14 +2171,14 @@
       <c r="C60" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D60" s="23" t="s">
+      <c r="D60" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="E60" s="24"/>
-      <c r="F60" s="24"/>
-      <c r="G60" s="24"/>
-      <c r="H60" s="24"/>
-      <c r="I60" s="25"/>
+      <c r="E60" s="28"/>
+      <c r="F60" s="28"/>
+      <c r="G60" s="28"/>
+      <c r="H60" s="28"/>
+      <c r="I60" s="29"/>
     </row>
     <row r="61" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B61" s="4">
@@ -2187,14 +2187,14 @@
       <c r="C61" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D61" s="23" t="s">
+      <c r="D61" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="E61" s="24"/>
-      <c r="F61" s="24"/>
-      <c r="G61" s="24"/>
-      <c r="H61" s="24"/>
-      <c r="I61" s="25"/>
+      <c r="E61" s="28"/>
+      <c r="F61" s="28"/>
+      <c r="G61" s="28"/>
+      <c r="H61" s="28"/>
+      <c r="I61" s="29"/>
     </row>
     <row r="62" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B62" s="4">
@@ -2203,14 +2203,14 @@
       <c r="C62" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D62" s="23" t="s">
+      <c r="D62" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="E62" s="24"/>
-      <c r="F62" s="24"/>
-      <c r="G62" s="24"/>
-      <c r="H62" s="24"/>
-      <c r="I62" s="25"/>
+      <c r="E62" s="28"/>
+      <c r="F62" s="28"/>
+      <c r="G62" s="28"/>
+      <c r="H62" s="28"/>
+      <c r="I62" s="29"/>
     </row>
     <row r="63" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B63" s="4">
@@ -2254,10 +2254,10 @@
       <c r="F64" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G64" s="23" t="s">
+      <c r="G64" s="27" t="s">
         <v>37</v>
       </c>
-      <c r="H64" s="25"/>
+      <c r="H64" s="29"/>
       <c r="I64" s="1" t="s">
         <v>14</v>
       </c>
@@ -2295,13 +2295,13 @@
       <c r="C66" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D66" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="E66" s="24"/>
-      <c r="F66" s="24"/>
-      <c r="G66" s="24"/>
-      <c r="H66" s="25"/>
+      <c r="D66" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="E66" s="28"/>
+      <c r="F66" s="28"/>
+      <c r="G66" s="28"/>
+      <c r="H66" s="29"/>
       <c r="I66" s="1" t="s">
         <v>16</v>
       </c>
@@ -2313,18 +2313,18 @@
       <c r="C67" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D67" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="E67" s="24"/>
-      <c r="F67" s="25"/>
+      <c r="D67" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="E67" s="28"/>
+      <c r="F67" s="29"/>
       <c r="G67" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="H67" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="I67" s="25"/>
+      <c r="H67" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="I67" s="29"/>
     </row>
     <row r="68" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B68" s="4">
@@ -2339,12 +2339,12 @@
       <c r="E68" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F68" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="G68" s="24"/>
-      <c r="H68" s="24"/>
-      <c r="I68" s="25"/>
+      <c r="F68" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="G68" s="28"/>
+      <c r="H68" s="28"/>
+      <c r="I68" s="29"/>
     </row>
     <row r="69" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B69" s="4">
@@ -2353,14 +2353,14 @@
       <c r="C69" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D69" s="23" t="s">
+      <c r="D69" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="E69" s="24"/>
-      <c r="F69" s="24"/>
-      <c r="G69" s="24"/>
-      <c r="H69" s="24"/>
-      <c r="I69" s="25"/>
+      <c r="E69" s="28"/>
+      <c r="F69" s="28"/>
+      <c r="G69" s="28"/>
+      <c r="H69" s="28"/>
+      <c r="I69" s="29"/>
     </row>
     <row r="70" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B70" s="4">
@@ -2369,10 +2369,10 @@
       <c r="C70" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D70" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="E70" s="25"/>
+      <c r="D70" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="E70" s="29"/>
       <c r="F70" s="3" t="s">
         <v>15</v>
       </c>
@@ -2402,10 +2402,10 @@
       <c r="F71" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G71" s="23" t="s">
+      <c r="G71" s="27" t="s">
         <v>37</v>
       </c>
-      <c r="H71" s="25"/>
+      <c r="H71" s="29"/>
       <c r="I71" s="1" t="s">
         <v>14</v>
       </c>
@@ -2443,14 +2443,14 @@
       <c r="C73" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D73" s="23" t="s">
+      <c r="D73" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="E73" s="24"/>
-      <c r="F73" s="24"/>
-      <c r="G73" s="24"/>
-      <c r="H73" s="24"/>
-      <c r="I73" s="25"/>
+      <c r="E73" s="28"/>
+      <c r="F73" s="28"/>
+      <c r="G73" s="28"/>
+      <c r="H73" s="28"/>
+      <c r="I73" s="29"/>
     </row>
     <row r="74" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B74" s="4">
@@ -2459,11 +2459,11 @@
       <c r="C74" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D74" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="E74" s="24"/>
-      <c r="F74" s="25"/>
+      <c r="D74" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="E74" s="28"/>
+      <c r="F74" s="29"/>
       <c r="G74" s="3" t="s">
         <v>16</v>
       </c>
@@ -2499,14 +2499,14 @@
       <c r="C76" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D76" s="23" t="s">
+      <c r="D76" s="27" t="s">
         <v>39</v>
       </c>
-      <c r="E76" s="24"/>
-      <c r="F76" s="24"/>
-      <c r="G76" s="24"/>
-      <c r="H76" s="24"/>
-      <c r="I76" s="25"/>
+      <c r="E76" s="28"/>
+      <c r="F76" s="28"/>
+      <c r="G76" s="28"/>
+      <c r="H76" s="28"/>
+      <c r="I76" s="29"/>
     </row>
     <row r="77" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B77" s="4">
@@ -2515,14 +2515,14 @@
       <c r="C77" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D77" s="23" t="s">
+      <c r="D77" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="E77" s="24"/>
-      <c r="F77" s="24"/>
-      <c r="G77" s="24"/>
-      <c r="H77" s="24"/>
-      <c r="I77" s="25"/>
+      <c r="E77" s="28"/>
+      <c r="F77" s="28"/>
+      <c r="G77" s="28"/>
+      <c r="H77" s="28"/>
+      <c r="I77" s="29"/>
     </row>
     <row r="78" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B78" s="4">
@@ -2531,14 +2531,14 @@
       <c r="C78" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D78" s="23" t="s">
+      <c r="D78" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="E78" s="24"/>
-      <c r="F78" s="24"/>
-      <c r="G78" s="24"/>
-      <c r="H78" s="24"/>
-      <c r="I78" s="25"/>
+      <c r="E78" s="28"/>
+      <c r="F78" s="28"/>
+      <c r="G78" s="28"/>
+      <c r="H78" s="28"/>
+      <c r="I78" s="29"/>
     </row>
     <row r="79" spans="2:9" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B79" s="16" t="s">
@@ -2582,10 +2582,10 @@
       <c r="F80" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G80" s="23" t="s">
+      <c r="G80" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="H80" s="25"/>
+      <c r="H80" s="29"/>
       <c r="I80" s="1" t="s">
         <v>14</v>
       </c>
@@ -2606,10 +2606,10 @@
       <c r="F81" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="G81" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="H81" s="25"/>
+      <c r="G81" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="H81" s="29"/>
       <c r="I81" s="1" t="s">
         <v>16</v>
       </c>
@@ -2673,14 +2673,14 @@
       <c r="C84" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D84" s="23" t="s">
+      <c r="D84" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="E84" s="24"/>
-      <c r="F84" s="24"/>
-      <c r="G84" s="24"/>
-      <c r="H84" s="24"/>
-      <c r="I84" s="25"/>
+      <c r="E84" s="28"/>
+      <c r="F84" s="28"/>
+      <c r="G84" s="28"/>
+      <c r="H84" s="28"/>
+      <c r="I84" s="29"/>
     </row>
     <row r="85" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B85" s="4">
@@ -2718,11 +2718,11 @@
       <c r="D86" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="E86" s="23" t="s">
+      <c r="E86" s="27" t="s">
         <v>43</v>
       </c>
-      <c r="F86" s="24"/>
-      <c r="G86" s="25"/>
+      <c r="F86" s="28"/>
+      <c r="G86" s="29"/>
       <c r="H86" s="3" t="s">
         <v>14</v>
       </c>
@@ -2737,18 +2737,18 @@
       <c r="C87" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D87" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="E87" s="25"/>
+      <c r="D87" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="E87" s="29"/>
       <c r="F87" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G87" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="H87" s="24"/>
-      <c r="I87" s="25"/>
+      <c r="G87" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="H87" s="28"/>
+      <c r="I87" s="29"/>
     </row>
     <row r="88" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B88" s="4">
@@ -2757,14 +2757,14 @@
       <c r="C88" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D88" s="23" t="s">
+      <c r="D88" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="E88" s="24"/>
-      <c r="F88" s="24"/>
-      <c r="G88" s="24"/>
-      <c r="H88" s="24"/>
-      <c r="I88" s="25"/>
+      <c r="E88" s="28"/>
+      <c r="F88" s="28"/>
+      <c r="G88" s="28"/>
+      <c r="H88" s="28"/>
+      <c r="I88" s="29"/>
     </row>
     <row r="89" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B89" s="4">
@@ -2773,18 +2773,18 @@
       <c r="C89" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D89" s="23" t="s">
+      <c r="D89" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="E89" s="24"/>
-      <c r="F89" s="25"/>
+      <c r="E89" s="28"/>
+      <c r="F89" s="29"/>
       <c r="G89" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="H89" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="I89" s="25"/>
+      <c r="H89" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="I89" s="29"/>
     </row>
     <row r="90" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B90" s="4">
@@ -2793,10 +2793,10 @@
       <c r="C90" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D90" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="E90" s="25"/>
+      <c r="D90" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="E90" s="29"/>
       <c r="F90" s="3" t="s">
         <v>16</v>
       </c>
@@ -2818,13 +2818,13 @@
       <c r="C91" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D91" s="23" t="s">
+      <c r="D91" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="E91" s="24"/>
-      <c r="F91" s="24"/>
-      <c r="G91" s="24"/>
-      <c r="H91" s="25"/>
+      <c r="E91" s="28"/>
+      <c r="F91" s="28"/>
+      <c r="G91" s="28"/>
+      <c r="H91" s="29"/>
       <c r="I91" s="18" t="s">
         <v>45</v>
       </c>
@@ -2836,14 +2836,14 @@
       <c r="C92" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D92" s="23" t="s">
+      <c r="D92" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="E92" s="24"/>
-      <c r="F92" s="24"/>
-      <c r="G92" s="24"/>
-      <c r="H92" s="24"/>
-      <c r="I92" s="25"/>
+      <c r="E92" s="28"/>
+      <c r="F92" s="28"/>
+      <c r="G92" s="28"/>
+      <c r="H92" s="28"/>
+      <c r="I92" s="29"/>
     </row>
     <row r="93" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B93" s="4">
@@ -2852,14 +2852,14 @@
       <c r="C93" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D93" s="23" t="s">
+      <c r="D93" s="27" t="s">
         <v>46</v>
       </c>
-      <c r="E93" s="24"/>
-      <c r="F93" s="24"/>
-      <c r="G93" s="24"/>
-      <c r="H93" s="24"/>
-      <c r="I93" s="25"/>
+      <c r="E93" s="28"/>
+      <c r="F93" s="28"/>
+      <c r="G93" s="28"/>
+      <c r="H93" s="28"/>
+      <c r="I93" s="29"/>
     </row>
     <row r="94" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B94" s="4">
@@ -2868,14 +2868,14 @@
       <c r="C94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D94" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="E94" s="24"/>
-      <c r="F94" s="24"/>
-      <c r="G94" s="24"/>
-      <c r="H94" s="24"/>
-      <c r="I94" s="25"/>
+      <c r="D94" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="E94" s="28"/>
+      <c r="F94" s="28"/>
+      <c r="G94" s="28"/>
+      <c r="H94" s="28"/>
+      <c r="I94" s="29"/>
     </row>
     <row r="95" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B95" s="4">
@@ -2884,15 +2884,15 @@
       <c r="C95" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D95" s="23" t="s">
+      <c r="D95" s="27" t="s">
         <v>47</v>
       </c>
-      <c r="E95" s="24"/>
-      <c r="F95" s="25"/>
-      <c r="G95" s="23" t="s">
+      <c r="E95" s="28"/>
+      <c r="F95" s="29"/>
+      <c r="G95" s="27" t="s">
         <v>48</v>
       </c>
-      <c r="H95" s="25"/>
+      <c r="H95" s="29"/>
       <c r="I95" s="1" t="s">
         <v>14</v>
       </c>
@@ -2904,14 +2904,14 @@
       <c r="C96" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D96" s="23" t="s">
+      <c r="D96" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="E96" s="24"/>
-      <c r="F96" s="24"/>
-      <c r="G96" s="24"/>
-      <c r="H96" s="24"/>
-      <c r="I96" s="25"/>
+      <c r="E96" s="28"/>
+      <c r="F96" s="28"/>
+      <c r="G96" s="28"/>
+      <c r="H96" s="28"/>
+      <c r="I96" s="29"/>
     </row>
     <row r="97" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B97" s="4">
@@ -2920,14 +2920,14 @@
       <c r="C97" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D97" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="E97" s="24"/>
-      <c r="F97" s="24"/>
-      <c r="G97" s="24"/>
-      <c r="H97" s="24"/>
-      <c r="I97" s="25"/>
+      <c r="D97" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="E97" s="28"/>
+      <c r="F97" s="28"/>
+      <c r="G97" s="28"/>
+      <c r="H97" s="28"/>
+      <c r="I97" s="29"/>
     </row>
     <row r="98" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B98" s="4">
@@ -2936,14 +2936,14 @@
       <c r="C98" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D98" s="23" t="s">
+      <c r="D98" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="E98" s="24"/>
-      <c r="F98" s="24"/>
-      <c r="G98" s="24"/>
-      <c r="H98" s="24"/>
-      <c r="I98" s="25"/>
+      <c r="E98" s="28"/>
+      <c r="F98" s="28"/>
+      <c r="G98" s="28"/>
+      <c r="H98" s="28"/>
+      <c r="I98" s="29"/>
     </row>
     <row r="99" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B99" s="4">
@@ -2952,12 +2952,12 @@
       <c r="C99" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D99" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="E99" s="24"/>
-      <c r="F99" s="24"/>
-      <c r="G99" s="25"/>
+      <c r="D99" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="E99" s="28"/>
+      <c r="F99" s="28"/>
+      <c r="G99" s="29"/>
       <c r="H99" s="3" t="s">
         <v>49</v>
       </c>
@@ -2981,21 +2981,21 @@
       <c r="F100" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="G100" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="H100" s="24"/>
-      <c r="I100" s="25"/>
+      <c r="G100" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="H100" s="28"/>
+      <c r="I100" s="29"/>
     </row>
     <row r="101" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B101" s="23"/>
-      <c r="C101" s="24"/>
-      <c r="D101" s="24"/>
-      <c r="E101" s="24"/>
-      <c r="F101" s="24"/>
-      <c r="G101" s="24"/>
-      <c r="H101" s="24"/>
-      <c r="I101" s="25"/>
+      <c r="B101" s="27"/>
+      <c r="C101" s="28"/>
+      <c r="D101" s="28"/>
+      <c r="E101" s="28"/>
+      <c r="F101" s="28"/>
+      <c r="G101" s="28"/>
+      <c r="H101" s="28"/>
+      <c r="I101" s="29"/>
     </row>
     <row r="102" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B102" s="3"/>
@@ -3014,10 +3014,10 @@
       <c r="C103" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D103" s="23" t="s">
+      <c r="D103" s="27" t="s">
         <v>51</v>
       </c>
-      <c r="E103" s="25"/>
+      <c r="E103" s="29"/>
       <c r="F103" s="3"/>
       <c r="G103" s="3"/>
       <c r="H103" s="3"/>
@@ -3030,10 +3030,10 @@
       <c r="C104" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D104" s="23" t="s">
+      <c r="D104" s="27" t="s">
         <v>52</v>
       </c>
-      <c r="E104" s="25"/>
+      <c r="E104" s="29"/>
       <c r="F104" s="3"/>
       <c r="G104" s="3"/>
       <c r="H104" s="3"/>
@@ -3046,10 +3046,10 @@
       <c r="C105" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D105" s="23" t="s">
+      <c r="D105" s="27" t="s">
         <v>53</v>
       </c>
-      <c r="E105" s="25"/>
+      <c r="E105" s="29"/>
       <c r="F105" s="3"/>
       <c r="G105" s="3"/>
       <c r="H105" s="3"/>
@@ -3062,10 +3062,10 @@
       <c r="C106" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D106" s="23" t="s">
+      <c r="D106" s="27" t="s">
         <v>54</v>
       </c>
-      <c r="E106" s="25"/>
+      <c r="E106" s="29"/>
       <c r="F106" s="3"/>
       <c r="G106" s="3"/>
       <c r="H106" s="3"/>
@@ -3078,10 +3078,10 @@
       <c r="C107" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D107" s="23" t="s">
+      <c r="D107" s="27" t="s">
         <v>55</v>
       </c>
-      <c r="E107" s="25"/>
+      <c r="E107" s="29"/>
       <c r="F107" s="3"/>
       <c r="G107" s="3"/>
       <c r="H107" s="3"/>
@@ -3094,10 +3094,10 @@
       <c r="C108" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D108" s="23" t="s">
+      <c r="D108" s="27" t="s">
         <v>56</v>
       </c>
-      <c r="E108" s="25"/>
+      <c r="E108" s="29"/>
       <c r="F108" s="3"/>
       <c r="G108" s="3"/>
       <c r="H108" s="3"/>
@@ -3134,28 +3134,28 @@
       <c r="I111" s="20"/>
     </row>
     <row r="112" spans="2:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B112" s="34" t="s">
+      <c r="B112" s="30" t="s">
         <v>57</v>
       </c>
-      <c r="C112" s="35"/>
-      <c r="D112" s="35"/>
-      <c r="E112" s="35"/>
-      <c r="F112" s="35"/>
-      <c r="G112" s="35"/>
-      <c r="H112" s="35"/>
-      <c r="I112" s="35"/>
-      <c r="J112" s="36"/>
+      <c r="C112" s="31"/>
+      <c r="D112" s="31"/>
+      <c r="E112" s="31"/>
+      <c r="F112" s="31"/>
+      <c r="G112" s="31"/>
+      <c r="H112" s="31"/>
+      <c r="I112" s="31"/>
+      <c r="J112" s="32"/>
     </row>
     <row r="113" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B113" s="37"/>
-      <c r="C113" s="38"/>
-      <c r="D113" s="38"/>
-      <c r="E113" s="38"/>
-      <c r="F113" s="38"/>
-      <c r="G113" s="38"/>
-      <c r="H113" s="38"/>
-      <c r="I113" s="38"/>
-      <c r="J113" s="39"/>
+      <c r="B113" s="33"/>
+      <c r="C113" s="34"/>
+      <c r="D113" s="34"/>
+      <c r="E113" s="34"/>
+      <c r="F113" s="34"/>
+      <c r="G113" s="34"/>
+      <c r="H113" s="34"/>
+      <c r="I113" s="34"/>
+      <c r="J113" s="35"/>
     </row>
     <row r="114" spans="2:10" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B114" s="8" t="s">
@@ -3286,13 +3286,13 @@
       <c r="E118" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="F118" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="G118" s="24"/>
-      <c r="H118" s="24"/>
-      <c r="I118" s="24"/>
-      <c r="J118" s="25"/>
+      <c r="F118" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="G118" s="28"/>
+      <c r="H118" s="28"/>
+      <c r="I118" s="28"/>
+      <c r="J118" s="29"/>
     </row>
     <row r="119" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B119" s="4">
@@ -3330,13 +3330,13 @@
       <c r="C120" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D120" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="E120" s="24"/>
-      <c r="F120" s="24"/>
-      <c r="G120" s="24"/>
-      <c r="H120" s="25"/>
+      <c r="D120" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="E120" s="28"/>
+      <c r="F120" s="28"/>
+      <c r="G120" s="28"/>
+      <c r="H120" s="29"/>
       <c r="I120" s="1" t="s">
         <v>16</v>
       </c>
@@ -3351,15 +3351,15 @@
       <c r="C121" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D121" s="23" t="s">
+      <c r="D121" s="27" t="s">
         <v>65</v>
       </c>
-      <c r="E121" s="24"/>
-      <c r="F121" s="24"/>
-      <c r="G121" s="24"/>
-      <c r="H121" s="24"/>
-      <c r="I121" s="24"/>
-      <c r="J121" s="25"/>
+      <c r="E121" s="28"/>
+      <c r="F121" s="28"/>
+      <c r="G121" s="28"/>
+      <c r="H121" s="28"/>
+      <c r="I121" s="28"/>
+      <c r="J121" s="29"/>
     </row>
     <row r="122" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B122" s="4">
@@ -3406,12 +3406,12 @@
       <c r="F123" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="G123" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="H123" s="24"/>
-      <c r="I123" s="24"/>
-      <c r="J123" s="25"/>
+      <c r="G123" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="H123" s="28"/>
+      <c r="I123" s="28"/>
+      <c r="J123" s="29"/>
     </row>
     <row r="124" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B124" s="4">
@@ -3429,12 +3429,12 @@
       <c r="F124" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="G124" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="H124" s="24"/>
-      <c r="I124" s="24"/>
-      <c r="J124" s="25"/>
+      <c r="G124" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="H124" s="28"/>
+      <c r="I124" s="28"/>
+      <c r="J124" s="29"/>
     </row>
     <row r="125" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B125" s="4">
@@ -3449,13 +3449,13 @@
       <c r="E125" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="F125" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="G125" s="24"/>
-      <c r="H125" s="24"/>
-      <c r="I125" s="24"/>
-      <c r="J125" s="25"/>
+      <c r="F125" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="G125" s="28"/>
+      <c r="H125" s="28"/>
+      <c r="I125" s="28"/>
+      <c r="J125" s="29"/>
     </row>
     <row r="126" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B126" s="4">
@@ -3473,11 +3473,11 @@
       <c r="F126" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="G126" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="H126" s="24"/>
-      <c r="I126" s="25"/>
+      <c r="G126" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="H126" s="28"/>
+      <c r="I126" s="29"/>
       <c r="J126" s="1" t="s">
         <v>16</v>
       </c>
@@ -3495,13 +3495,13 @@
       <c r="E127" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="F127" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="G127" s="24"/>
-      <c r="H127" s="24"/>
-      <c r="I127" s="24"/>
-      <c r="J127" s="25"/>
+      <c r="F127" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="G127" s="28"/>
+      <c r="H127" s="28"/>
+      <c r="I127" s="28"/>
+      <c r="J127" s="29"/>
     </row>
     <row r="128" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B128" s="4">
@@ -3510,15 +3510,15 @@
       <c r="C128" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D128" s="23" t="s">
+      <c r="D128" s="27" t="s">
         <v>65</v>
       </c>
-      <c r="E128" s="24"/>
-      <c r="F128" s="24"/>
-      <c r="G128" s="24"/>
-      <c r="H128" s="24"/>
-      <c r="I128" s="24"/>
-      <c r="J128" s="25"/>
+      <c r="E128" s="28"/>
+      <c r="F128" s="28"/>
+      <c r="G128" s="28"/>
+      <c r="H128" s="28"/>
+      <c r="I128" s="28"/>
+      <c r="J128" s="29"/>
     </row>
     <row r="129" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B129" s="4">
@@ -3701,15 +3701,15 @@
       <c r="C135" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D135" s="23" t="s">
+      <c r="D135" s="27" t="s">
         <v>65</v>
       </c>
-      <c r="E135" s="24"/>
-      <c r="F135" s="24"/>
-      <c r="G135" s="24"/>
-      <c r="H135" s="24"/>
-      <c r="I135" s="24"/>
-      <c r="J135" s="25"/>
+      <c r="E135" s="28"/>
+      <c r="F135" s="28"/>
+      <c r="G135" s="28"/>
+      <c r="H135" s="28"/>
+      <c r="I135" s="28"/>
+      <c r="J135" s="29"/>
     </row>
     <row r="136" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B136" s="4">
@@ -3921,15 +3921,15 @@
       <c r="C143" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D143" s="23" t="s">
+      <c r="D143" s="27" t="s">
         <v>65</v>
       </c>
-      <c r="E143" s="24"/>
-      <c r="F143" s="24"/>
-      <c r="G143" s="24"/>
-      <c r="H143" s="24"/>
-      <c r="I143" s="24"/>
-      <c r="J143" s="25"/>
+      <c r="E143" s="28"/>
+      <c r="F143" s="28"/>
+      <c r="G143" s="28"/>
+      <c r="H143" s="28"/>
+      <c r="I143" s="28"/>
+      <c r="J143" s="29"/>
     </row>
     <row r="144" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B144" s="4">
@@ -4005,12 +4005,12 @@
       <c r="F146" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="G146" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="H146" s="24"/>
-      <c r="I146" s="24"/>
-      <c r="J146" s="25"/>
+      <c r="G146" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="H146" s="28"/>
+      <c r="I146" s="28"/>
+      <c r="J146" s="29"/>
     </row>
     <row r="147" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B147" s="4">
@@ -4077,15 +4077,15 @@
       <c r="C149" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D149" s="26" t="s">
+      <c r="D149" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E149" s="27"/>
-      <c r="F149" s="27"/>
-      <c r="G149" s="27"/>
-      <c r="H149" s="27"/>
-      <c r="I149" s="27"/>
-      <c r="J149" s="28"/>
+      <c r="E149" s="24"/>
+      <c r="F149" s="24"/>
+      <c r="G149" s="24"/>
+      <c r="H149" s="24"/>
+      <c r="I149" s="24"/>
+      <c r="J149" s="38"/>
     </row>
     <row r="150" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B150" s="4">
@@ -4094,13 +4094,13 @@
       <c r="C150" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D150" s="29"/>
-      <c r="E150" s="30"/>
-      <c r="F150" s="30"/>
-      <c r="G150" s="30"/>
-      <c r="H150" s="30"/>
-      <c r="I150" s="30"/>
-      <c r="J150" s="31"/>
+      <c r="D150" s="25"/>
+      <c r="E150" s="26"/>
+      <c r="F150" s="26"/>
+      <c r="G150" s="26"/>
+      <c r="H150" s="26"/>
+      <c r="I150" s="26"/>
+      <c r="J150" s="39"/>
     </row>
     <row r="151" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B151" s="4">
@@ -4147,11 +4147,11 @@
       <c r="F152" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="G152" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="H152" s="24"/>
-      <c r="I152" s="25"/>
+      <c r="G152" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="H152" s="28"/>
+      <c r="I152" s="29"/>
       <c r="J152" s="1" t="s">
         <v>69</v>
       </c>
@@ -4279,15 +4279,15 @@
       <c r="C157" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D157" s="23" t="s">
+      <c r="D157" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="E157" s="24"/>
-      <c r="F157" s="24"/>
-      <c r="G157" s="24"/>
-      <c r="H157" s="24"/>
-      <c r="I157" s="24"/>
-      <c r="J157" s="25"/>
+      <c r="E157" s="28"/>
+      <c r="F157" s="28"/>
+      <c r="G157" s="28"/>
+      <c r="H157" s="28"/>
+      <c r="I157" s="28"/>
+      <c r="J157" s="29"/>
     </row>
     <row r="158" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B158" s="4">
@@ -4468,15 +4468,15 @@
       <c r="C164" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D164" s="23" t="s">
+      <c r="D164" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="E164" s="24"/>
-      <c r="F164" s="24"/>
-      <c r="G164" s="24"/>
-      <c r="H164" s="24"/>
-      <c r="I164" s="24"/>
-      <c r="J164" s="25"/>
+      <c r="E164" s="28"/>
+      <c r="F164" s="28"/>
+      <c r="G164" s="28"/>
+      <c r="H164" s="28"/>
+      <c r="I164" s="28"/>
+      <c r="J164" s="29"/>
     </row>
     <row r="165" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B165" s="4">
@@ -4674,15 +4674,15 @@
       <c r="C172" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D172" s="23" t="s">
+      <c r="D172" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="E172" s="24"/>
-      <c r="F172" s="24"/>
-      <c r="G172" s="24"/>
-      <c r="H172" s="24"/>
-      <c r="I172" s="24"/>
-      <c r="J172" s="25"/>
+      <c r="E172" s="28"/>
+      <c r="F172" s="28"/>
+      <c r="G172" s="28"/>
+      <c r="H172" s="28"/>
+      <c r="I172" s="28"/>
+      <c r="J172" s="29"/>
     </row>
     <row r="173" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B173" s="4">
@@ -4746,44 +4746,44 @@
       <c r="B175" s="4">
         <v>45903</v>
       </c>
-      <c r="C175" s="26" t="s">
+      <c r="C175" s="23" t="s">
         <v>39</v>
       </c>
-      <c r="D175" s="27"/>
-      <c r="E175" s="27"/>
-      <c r="F175" s="27"/>
-      <c r="G175" s="27"/>
-      <c r="H175" s="27"/>
-      <c r="I175" s="27"/>
-      <c r="J175" s="27"/>
+      <c r="D175" s="24"/>
+      <c r="E175" s="24"/>
+      <c r="F175" s="24"/>
+      <c r="G175" s="24"/>
+      <c r="H175" s="24"/>
+      <c r="I175" s="24"/>
+      <c r="J175" s="24"/>
     </row>
     <row r="176" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B176" s="4">
         <v>45904</v>
       </c>
-      <c r="C176" s="29"/>
-      <c r="D176" s="30"/>
-      <c r="E176" s="30"/>
-      <c r="F176" s="30"/>
-      <c r="G176" s="30"/>
-      <c r="H176" s="30"/>
-      <c r="I176" s="30"/>
-      <c r="J176" s="30"/>
+      <c r="C176" s="25"/>
+      <c r="D176" s="26"/>
+      <c r="E176" s="26"/>
+      <c r="F176" s="26"/>
+      <c r="G176" s="26"/>
+      <c r="H176" s="26"/>
+      <c r="I176" s="26"/>
+      <c r="J176" s="26"/>
     </row>
     <row r="177" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B177" s="4">
         <v>45905</v>
       </c>
-      <c r="C177" s="23" t="s">
+      <c r="C177" s="27" t="s">
         <v>39</v>
       </c>
-      <c r="D177" s="24"/>
-      <c r="E177" s="24"/>
-      <c r="F177" s="24"/>
-      <c r="G177" s="24"/>
-      <c r="H177" s="24"/>
-      <c r="I177" s="24"/>
-      <c r="J177" s="25"/>
+      <c r="D177" s="28"/>
+      <c r="E177" s="28"/>
+      <c r="F177" s="28"/>
+      <c r="G177" s="28"/>
+      <c r="H177" s="28"/>
+      <c r="I177" s="28"/>
+      <c r="J177" s="29"/>
     </row>
     <row r="178" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B178" s="4">
@@ -4944,15 +4944,33 @@
       <c r="J183" s="1"/>
     </row>
     <row r="184" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B184" s="3"/>
-      <c r="C184" s="3"/>
-      <c r="D184" s="3"/>
-      <c r="E184" s="3"/>
-      <c r="F184" s="3"/>
-      <c r="G184" s="3"/>
-      <c r="H184" s="3"/>
-      <c r="I184" s="1"/>
-      <c r="J184" s="1"/>
+      <c r="B184" s="4">
+        <v>45918</v>
+      </c>
+      <c r="C184" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D184" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E184" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F184" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G184" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H184" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I184" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="J184" s="1" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="185" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B185" s="3"/>
@@ -7508,33 +7526,50 @@
     </row>
   </sheetData>
   <mergeCells count="87">
-    <mergeCell ref="C175:J176"/>
-    <mergeCell ref="D164:J164"/>
-    <mergeCell ref="D157:J157"/>
-    <mergeCell ref="D143:J143"/>
-    <mergeCell ref="D135:J135"/>
-    <mergeCell ref="D172:J172"/>
-    <mergeCell ref="G146:J146"/>
-    <mergeCell ref="D108:E108"/>
-    <mergeCell ref="B112:J113"/>
-    <mergeCell ref="G124:J124"/>
-    <mergeCell ref="D120:H120"/>
-    <mergeCell ref="G123:J123"/>
-    <mergeCell ref="D121:J121"/>
-    <mergeCell ref="D31:I31"/>
-    <mergeCell ref="G35:H35"/>
-    <mergeCell ref="D40:I40"/>
-    <mergeCell ref="D33:I33"/>
-    <mergeCell ref="D46:I46"/>
-    <mergeCell ref="D43:I43"/>
-    <mergeCell ref="D78:I78"/>
-    <mergeCell ref="G71:H71"/>
-    <mergeCell ref="D76:I76"/>
-    <mergeCell ref="D66:H66"/>
-    <mergeCell ref="D77:I77"/>
-    <mergeCell ref="D73:I73"/>
-    <mergeCell ref="D70:E70"/>
-    <mergeCell ref="D74:F74"/>
+    <mergeCell ref="C177:J177"/>
+    <mergeCell ref="D106:E106"/>
+    <mergeCell ref="D99:G99"/>
+    <mergeCell ref="G126:I126"/>
+    <mergeCell ref="F125:J125"/>
+    <mergeCell ref="D128:J128"/>
+    <mergeCell ref="D103:E103"/>
+    <mergeCell ref="D104:E104"/>
+    <mergeCell ref="D105:E105"/>
+    <mergeCell ref="G100:I100"/>
+    <mergeCell ref="B101:I101"/>
+    <mergeCell ref="F127:J127"/>
+    <mergeCell ref="D107:E107"/>
+    <mergeCell ref="F118:J118"/>
+    <mergeCell ref="G152:I152"/>
+    <mergeCell ref="D149:J150"/>
+    <mergeCell ref="D98:I98"/>
+    <mergeCell ref="D94:I94"/>
+    <mergeCell ref="H89:I89"/>
+    <mergeCell ref="D89:F89"/>
+    <mergeCell ref="D97:I97"/>
+    <mergeCell ref="G64:H64"/>
+    <mergeCell ref="D96:I96"/>
+    <mergeCell ref="D95:F95"/>
+    <mergeCell ref="G95:H95"/>
+    <mergeCell ref="D92:I92"/>
+    <mergeCell ref="D93:I93"/>
+    <mergeCell ref="D90:E90"/>
+    <mergeCell ref="D91:H91"/>
+    <mergeCell ref="E86:G86"/>
+    <mergeCell ref="D88:I88"/>
+    <mergeCell ref="H67:I67"/>
+    <mergeCell ref="G81:H81"/>
+    <mergeCell ref="D67:F67"/>
+    <mergeCell ref="F68:I68"/>
+    <mergeCell ref="D87:E87"/>
+    <mergeCell ref="G87:I87"/>
+    <mergeCell ref="D60:I60"/>
+    <mergeCell ref="D62:I62"/>
+    <mergeCell ref="D61:I61"/>
+    <mergeCell ref="G49:H49"/>
+    <mergeCell ref="D47:I47"/>
+    <mergeCell ref="D55:I55"/>
+    <mergeCell ref="G57:H57"/>
     <mergeCell ref="D84:I84"/>
     <mergeCell ref="D69:I69"/>
     <mergeCell ref="D8:I8"/>
@@ -7551,50 +7586,33 @@
     <mergeCell ref="D30:I30"/>
     <mergeCell ref="G80:H80"/>
     <mergeCell ref="G42:H42"/>
-    <mergeCell ref="D60:I60"/>
-    <mergeCell ref="D62:I62"/>
-    <mergeCell ref="D61:I61"/>
-    <mergeCell ref="G49:H49"/>
-    <mergeCell ref="D47:I47"/>
-    <mergeCell ref="D55:I55"/>
-    <mergeCell ref="G57:H57"/>
-    <mergeCell ref="G64:H64"/>
-    <mergeCell ref="D96:I96"/>
-    <mergeCell ref="D95:F95"/>
-    <mergeCell ref="G95:H95"/>
-    <mergeCell ref="D92:I92"/>
-    <mergeCell ref="D93:I93"/>
-    <mergeCell ref="D90:E90"/>
-    <mergeCell ref="D91:H91"/>
-    <mergeCell ref="E86:G86"/>
-    <mergeCell ref="D88:I88"/>
-    <mergeCell ref="H67:I67"/>
-    <mergeCell ref="G81:H81"/>
-    <mergeCell ref="D67:F67"/>
-    <mergeCell ref="F68:I68"/>
-    <mergeCell ref="D87:E87"/>
-    <mergeCell ref="G87:I87"/>
-    <mergeCell ref="D98:I98"/>
-    <mergeCell ref="D94:I94"/>
-    <mergeCell ref="H89:I89"/>
-    <mergeCell ref="D89:F89"/>
-    <mergeCell ref="D97:I97"/>
-    <mergeCell ref="C177:J177"/>
-    <mergeCell ref="D106:E106"/>
-    <mergeCell ref="D99:G99"/>
-    <mergeCell ref="G126:I126"/>
-    <mergeCell ref="F125:J125"/>
-    <mergeCell ref="D128:J128"/>
-    <mergeCell ref="D103:E103"/>
-    <mergeCell ref="D104:E104"/>
-    <mergeCell ref="D105:E105"/>
-    <mergeCell ref="G100:I100"/>
-    <mergeCell ref="B101:I101"/>
-    <mergeCell ref="F127:J127"/>
-    <mergeCell ref="D107:E107"/>
-    <mergeCell ref="F118:J118"/>
-    <mergeCell ref="G152:I152"/>
-    <mergeCell ref="D149:J150"/>
+    <mergeCell ref="D78:I78"/>
+    <mergeCell ref="G71:H71"/>
+    <mergeCell ref="D76:I76"/>
+    <mergeCell ref="D66:H66"/>
+    <mergeCell ref="D77:I77"/>
+    <mergeCell ref="D73:I73"/>
+    <mergeCell ref="D70:E70"/>
+    <mergeCell ref="D74:F74"/>
+    <mergeCell ref="D31:I31"/>
+    <mergeCell ref="G35:H35"/>
+    <mergeCell ref="D40:I40"/>
+    <mergeCell ref="D33:I33"/>
+    <mergeCell ref="D46:I46"/>
+    <mergeCell ref="D43:I43"/>
+    <mergeCell ref="D108:E108"/>
+    <mergeCell ref="B112:J113"/>
+    <mergeCell ref="G124:J124"/>
+    <mergeCell ref="D120:H120"/>
+    <mergeCell ref="G123:J123"/>
+    <mergeCell ref="D121:J121"/>
+    <mergeCell ref="C175:J176"/>
+    <mergeCell ref="D164:J164"/>
+    <mergeCell ref="D157:J157"/>
+    <mergeCell ref="D143:J143"/>
+    <mergeCell ref="D135:J135"/>
+    <mergeCell ref="D172:J172"/>
+    <mergeCell ref="G146:J146"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/attendance_sheet.xlsx
+++ b/attendance_sheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\repositary\3rd_Year_5th_Semester\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E234101C-36F6-4704-80B1-63CAA3265F60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7E75742-95B5-4BC8-BC21-90F1B3C18D72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{EB654061-A886-47D1-BF86-9B1A84FCE7FB}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="920" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="922" uniqueCount="75">
   <si>
     <t>Date</t>
   </si>
@@ -259,6 +259,9 @@
   </si>
   <si>
     <t>1 class P</t>
+  </si>
+  <si>
+    <t>Mahalaya</t>
   </si>
 </sst>
 </file>
@@ -538,10 +541,22 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
@@ -550,13 +565,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -575,18 +590,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -990,14 +993,14 @@
       <c r="C8" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D8" s="37" t="s">
+      <c r="D8" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="E8" s="37"/>
-      <c r="F8" s="37"/>
-      <c r="G8" s="37"/>
-      <c r="H8" s="37"/>
-      <c r="I8" s="37"/>
+      <c r="E8" s="32"/>
+      <c r="F8" s="32"/>
+      <c r="G8" s="32"/>
+      <c r="H8" s="32"/>
+      <c r="I8" s="32"/>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B9" s="4">
@@ -1006,14 +1009,14 @@
       <c r="C9" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D9" s="37" t="s">
+      <c r="D9" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="E9" s="37"/>
-      <c r="F9" s="37"/>
-      <c r="G9" s="37"/>
-      <c r="H9" s="37"/>
-      <c r="I9" s="37"/>
+      <c r="E9" s="32"/>
+      <c r="F9" s="32"/>
+      <c r="G9" s="32"/>
+      <c r="H9" s="32"/>
+      <c r="I9" s="32"/>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B10" s="4">
@@ -1022,14 +1025,14 @@
       <c r="C10" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D10" s="37" t="s">
+      <c r="D10" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="E10" s="37"/>
-      <c r="F10" s="37"/>
-      <c r="G10" s="37"/>
-      <c r="H10" s="37"/>
-      <c r="I10" s="37"/>
+      <c r="E10" s="32"/>
+      <c r="F10" s="32"/>
+      <c r="G10" s="32"/>
+      <c r="H10" s="32"/>
+      <c r="I10" s="32"/>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B11" s="4">
@@ -1038,14 +1041,14 @@
       <c r="C11" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D11" s="37" t="s">
+      <c r="D11" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="E11" s="37"/>
-      <c r="F11" s="37"/>
-      <c r="G11" s="37"/>
-      <c r="H11" s="37"/>
-      <c r="I11" s="37"/>
+      <c r="E11" s="32"/>
+      <c r="F11" s="32"/>
+      <c r="G11" s="32"/>
+      <c r="H11" s="32"/>
+      <c r="I11" s="32"/>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B12" s="4">
@@ -1089,10 +1092,10 @@
       <c r="F13" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="G13" s="37" t="s">
+      <c r="G13" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="H13" s="37"/>
+      <c r="H13" s="32"/>
       <c r="I13" s="1" t="s">
         <v>14</v>
       </c>
@@ -1104,14 +1107,14 @@
       <c r="C14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D14" s="37" t="s">
+      <c r="D14" s="32" t="s">
         <v>19</v>
       </c>
-      <c r="E14" s="37"/>
-      <c r="F14" s="37"/>
-      <c r="G14" s="37"/>
-      <c r="H14" s="37"/>
-      <c r="I14" s="37"/>
+      <c r="E14" s="32"/>
+      <c r="F14" s="32"/>
+      <c r="G14" s="32"/>
+      <c r="H14" s="32"/>
+      <c r="I14" s="32"/>
     </row>
     <row r="15" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B15" s="4">
@@ -1198,14 +1201,14 @@
       <c r="C18" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D18" s="37" t="s">
+      <c r="D18" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="E18" s="37"/>
-      <c r="F18" s="37"/>
-      <c r="G18" s="37"/>
-      <c r="H18" s="37"/>
-      <c r="I18" s="37"/>
+      <c r="E18" s="32"/>
+      <c r="F18" s="32"/>
+      <c r="G18" s="32"/>
+      <c r="H18" s="32"/>
+      <c r="I18" s="32"/>
     </row>
     <row r="19" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B19" s="4">
@@ -1214,14 +1217,14 @@
       <c r="C19" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D19" s="37" t="s">
+      <c r="D19" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="E19" s="37"/>
-      <c r="F19" s="37"/>
-      <c r="G19" s="37"/>
-      <c r="H19" s="37"/>
-      <c r="I19" s="37"/>
+      <c r="E19" s="32"/>
+      <c r="F19" s="32"/>
+      <c r="G19" s="32"/>
+      <c r="H19" s="32"/>
+      <c r="I19" s="32"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B20" s="4">
@@ -1239,10 +1242,10 @@
       <c r="F20" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G20" s="37" t="s">
+      <c r="G20" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="H20" s="37"/>
+      <c r="H20" s="32"/>
       <c r="I20" s="1" t="s">
         <v>14</v>
       </c>
@@ -1358,14 +1361,14 @@
       <c r="C25" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D25" s="37" t="s">
+      <c r="D25" s="32" t="s">
         <v>26</v>
       </c>
-      <c r="E25" s="37"/>
-      <c r="F25" s="37"/>
-      <c r="G25" s="37"/>
-      <c r="H25" s="37"/>
-      <c r="I25" s="37"/>
+      <c r="E25" s="32"/>
+      <c r="F25" s="32"/>
+      <c r="G25" s="32"/>
+      <c r="H25" s="32"/>
+      <c r="I25" s="32"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B26" s="4">
@@ -1409,10 +1412,10 @@
       <c r="F27" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G27" s="37" t="s">
+      <c r="G27" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="H27" s="37"/>
+      <c r="H27" s="32"/>
       <c r="I27" s="1" t="s">
         <v>14</v>
       </c>
@@ -1476,14 +1479,14 @@
       <c r="C30" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D30" s="36" t="s">
+      <c r="D30" s="33" t="s">
         <v>20</v>
       </c>
-      <c r="E30" s="36"/>
-      <c r="F30" s="36"/>
-      <c r="G30" s="36"/>
-      <c r="H30" s="36"/>
-      <c r="I30" s="36"/>
+      <c r="E30" s="33"/>
+      <c r="F30" s="33"/>
+      <c r="G30" s="33"/>
+      <c r="H30" s="33"/>
+      <c r="I30" s="33"/>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B31" s="4">
@@ -1492,14 +1495,14 @@
       <c r="C31" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D31" s="36" t="s">
+      <c r="D31" s="33" t="s">
         <v>20</v>
       </c>
-      <c r="E31" s="36"/>
-      <c r="F31" s="36"/>
-      <c r="G31" s="36"/>
-      <c r="H31" s="36"/>
-      <c r="I31" s="36"/>
+      <c r="E31" s="33"/>
+      <c r="F31" s="33"/>
+      <c r="G31" s="33"/>
+      <c r="H31" s="33"/>
+      <c r="I31" s="33"/>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B32" s="4">
@@ -1534,14 +1537,14 @@
       <c r="C33" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D33" s="36" t="s">
+      <c r="D33" s="33" t="s">
         <v>20</v>
       </c>
-      <c r="E33" s="36"/>
-      <c r="F33" s="36"/>
-      <c r="G33" s="36"/>
-      <c r="H33" s="36"/>
-      <c r="I33" s="36"/>
+      <c r="E33" s="33"/>
+      <c r="F33" s="33"/>
+      <c r="G33" s="33"/>
+      <c r="H33" s="33"/>
+      <c r="I33" s="33"/>
     </row>
     <row r="34" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B34" s="4">
@@ -1585,10 +1588,10 @@
       <c r="F35" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G35" s="36" t="s">
+      <c r="G35" s="33" t="s">
         <v>18</v>
       </c>
-      <c r="H35" s="36"/>
+      <c r="H35" s="33"/>
       <c r="I35" s="1" t="s">
         <v>14</v>
       </c>
@@ -1704,14 +1707,14 @@
       <c r="C40" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D40" s="36" t="s">
+      <c r="D40" s="33" t="s">
         <v>20</v>
       </c>
-      <c r="E40" s="36"/>
-      <c r="F40" s="36"/>
-      <c r="G40" s="36"/>
-      <c r="H40" s="36"/>
-      <c r="I40" s="36"/>
+      <c r="E40" s="33"/>
+      <c r="F40" s="33"/>
+      <c r="G40" s="33"/>
+      <c r="H40" s="33"/>
+      <c r="I40" s="33"/>
     </row>
     <row r="41" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B41" s="4">
@@ -1755,10 +1758,10 @@
       <c r="F42" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G42" s="36" t="s">
+      <c r="G42" s="33" t="s">
         <v>28</v>
       </c>
-      <c r="H42" s="36"/>
+      <c r="H42" s="33"/>
       <c r="I42" s="1" t="s">
         <v>15</v>
       </c>
@@ -1770,14 +1773,14 @@
       <c r="C43" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D43" s="36" t="s">
+      <c r="D43" s="33" t="s">
         <v>20</v>
       </c>
-      <c r="E43" s="36"/>
-      <c r="F43" s="36"/>
-      <c r="G43" s="36"/>
-      <c r="H43" s="36"/>
-      <c r="I43" s="36"/>
+      <c r="E43" s="33"/>
+      <c r="F43" s="33"/>
+      <c r="G43" s="33"/>
+      <c r="H43" s="33"/>
+      <c r="I43" s="33"/>
     </row>
     <row r="44" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B44" s="4">
@@ -1841,14 +1844,14 @@
       <c r="C46" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D46" s="36" t="s">
+      <c r="D46" s="33" t="s">
         <v>20</v>
       </c>
-      <c r="E46" s="36"/>
-      <c r="F46" s="36"/>
-      <c r="G46" s="36"/>
-      <c r="H46" s="36"/>
-      <c r="I46" s="36"/>
+      <c r="E46" s="33"/>
+      <c r="F46" s="33"/>
+      <c r="G46" s="33"/>
+      <c r="H46" s="33"/>
+      <c r="I46" s="33"/>
     </row>
     <row r="47" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B47" s="4">
@@ -1857,14 +1860,14 @@
       <c r="C47" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D47" s="27" t="s">
+      <c r="D47" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E47" s="28"/>
-      <c r="F47" s="28"/>
-      <c r="G47" s="28"/>
-      <c r="H47" s="28"/>
-      <c r="I47" s="29"/>
+      <c r="E47" s="24"/>
+      <c r="F47" s="24"/>
+      <c r="G47" s="24"/>
+      <c r="H47" s="24"/>
+      <c r="I47" s="25"/>
     </row>
     <row r="48" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B48" s="4">
@@ -1908,10 +1911,10 @@
       <c r="F49" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G49" s="27" t="s">
+      <c r="G49" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="H49" s="29"/>
+      <c r="H49" s="25"/>
       <c r="I49" s="1" t="s">
         <v>30</v>
       </c>
@@ -2053,14 +2056,14 @@
       <c r="C55" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="D55" s="28" t="s">
+      <c r="D55" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="E55" s="28"/>
-      <c r="F55" s="28"/>
-      <c r="G55" s="28"/>
-      <c r="H55" s="28"/>
-      <c r="I55" s="28"/>
+      <c r="E55" s="24"/>
+      <c r="F55" s="24"/>
+      <c r="G55" s="24"/>
+      <c r="H55" s="24"/>
+      <c r="I55" s="24"/>
     </row>
     <row r="56" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B56" s="4">
@@ -2104,10 +2107,10 @@
       <c r="F57" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G57" s="27" t="s">
+      <c r="G57" s="23" t="s">
         <v>37</v>
       </c>
-      <c r="H57" s="29"/>
+      <c r="H57" s="25"/>
       <c r="I57" s="1" t="s">
         <v>36</v>
       </c>
@@ -2171,14 +2174,14 @@
       <c r="C60" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D60" s="27" t="s">
+      <c r="D60" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E60" s="28"/>
-      <c r="F60" s="28"/>
-      <c r="G60" s="28"/>
-      <c r="H60" s="28"/>
-      <c r="I60" s="29"/>
+      <c r="E60" s="24"/>
+      <c r="F60" s="24"/>
+      <c r="G60" s="24"/>
+      <c r="H60" s="24"/>
+      <c r="I60" s="25"/>
     </row>
     <row r="61" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B61" s="4">
@@ -2187,14 +2190,14 @@
       <c r="C61" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D61" s="27" t="s">
+      <c r="D61" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E61" s="28"/>
-      <c r="F61" s="28"/>
-      <c r="G61" s="28"/>
-      <c r="H61" s="28"/>
-      <c r="I61" s="29"/>
+      <c r="E61" s="24"/>
+      <c r="F61" s="24"/>
+      <c r="G61" s="24"/>
+      <c r="H61" s="24"/>
+      <c r="I61" s="25"/>
     </row>
     <row r="62" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B62" s="4">
@@ -2203,14 +2206,14 @@
       <c r="C62" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D62" s="27" t="s">
+      <c r="D62" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E62" s="28"/>
-      <c r="F62" s="28"/>
-      <c r="G62" s="28"/>
-      <c r="H62" s="28"/>
-      <c r="I62" s="29"/>
+      <c r="E62" s="24"/>
+      <c r="F62" s="24"/>
+      <c r="G62" s="24"/>
+      <c r="H62" s="24"/>
+      <c r="I62" s="25"/>
     </row>
     <row r="63" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B63" s="4">
@@ -2254,10 +2257,10 @@
       <c r="F64" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G64" s="27" t="s">
+      <c r="G64" s="23" t="s">
         <v>37</v>
       </c>
-      <c r="H64" s="29"/>
+      <c r="H64" s="25"/>
       <c r="I64" s="1" t="s">
         <v>14</v>
       </c>
@@ -2295,13 +2298,13 @@
       <c r="C66" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D66" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="E66" s="28"/>
-      <c r="F66" s="28"/>
-      <c r="G66" s="28"/>
-      <c r="H66" s="29"/>
+      <c r="D66" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="E66" s="24"/>
+      <c r="F66" s="24"/>
+      <c r="G66" s="24"/>
+      <c r="H66" s="25"/>
       <c r="I66" s="1" t="s">
         <v>16</v>
       </c>
@@ -2313,18 +2316,18 @@
       <c r="C67" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D67" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="E67" s="28"/>
-      <c r="F67" s="29"/>
+      <c r="D67" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="E67" s="24"/>
+      <c r="F67" s="25"/>
       <c r="G67" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="H67" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="I67" s="29"/>
+      <c r="H67" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="I67" s="25"/>
     </row>
     <row r="68" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B68" s="4">
@@ -2339,12 +2342,12 @@
       <c r="E68" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F68" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="G68" s="28"/>
-      <c r="H68" s="28"/>
-      <c r="I68" s="29"/>
+      <c r="F68" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="G68" s="24"/>
+      <c r="H68" s="24"/>
+      <c r="I68" s="25"/>
     </row>
     <row r="69" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B69" s="4">
@@ -2353,14 +2356,14 @@
       <c r="C69" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D69" s="27" t="s">
+      <c r="D69" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E69" s="28"/>
-      <c r="F69" s="28"/>
-      <c r="G69" s="28"/>
-      <c r="H69" s="28"/>
-      <c r="I69" s="29"/>
+      <c r="E69" s="24"/>
+      <c r="F69" s="24"/>
+      <c r="G69" s="24"/>
+      <c r="H69" s="24"/>
+      <c r="I69" s="25"/>
     </row>
     <row r="70" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B70" s="4">
@@ -2369,10 +2372,10 @@
       <c r="C70" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D70" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="E70" s="29"/>
+      <c r="D70" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="E70" s="25"/>
       <c r="F70" s="3" t="s">
         <v>15</v>
       </c>
@@ -2402,10 +2405,10 @@
       <c r="F71" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G71" s="27" t="s">
+      <c r="G71" s="23" t="s">
         <v>37</v>
       </c>
-      <c r="H71" s="29"/>
+      <c r="H71" s="25"/>
       <c r="I71" s="1" t="s">
         <v>14</v>
       </c>
@@ -2443,14 +2446,14 @@
       <c r="C73" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D73" s="27" t="s">
+      <c r="D73" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E73" s="28"/>
-      <c r="F73" s="28"/>
-      <c r="G73" s="28"/>
-      <c r="H73" s="28"/>
-      <c r="I73" s="29"/>
+      <c r="E73" s="24"/>
+      <c r="F73" s="24"/>
+      <c r="G73" s="24"/>
+      <c r="H73" s="24"/>
+      <c r="I73" s="25"/>
     </row>
     <row r="74" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B74" s="4">
@@ -2459,11 +2462,11 @@
       <c r="C74" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D74" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="E74" s="28"/>
-      <c r="F74" s="29"/>
+      <c r="D74" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="E74" s="24"/>
+      <c r="F74" s="25"/>
       <c r="G74" s="3" t="s">
         <v>16</v>
       </c>
@@ -2499,14 +2502,14 @@
       <c r="C76" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D76" s="27" t="s">
+      <c r="D76" s="23" t="s">
         <v>39</v>
       </c>
-      <c r="E76" s="28"/>
-      <c r="F76" s="28"/>
-      <c r="G76" s="28"/>
-      <c r="H76" s="28"/>
-      <c r="I76" s="29"/>
+      <c r="E76" s="24"/>
+      <c r="F76" s="24"/>
+      <c r="G76" s="24"/>
+      <c r="H76" s="24"/>
+      <c r="I76" s="25"/>
     </row>
     <row r="77" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B77" s="4">
@@ -2515,14 +2518,14 @@
       <c r="C77" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D77" s="27" t="s">
+      <c r="D77" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E77" s="28"/>
-      <c r="F77" s="28"/>
-      <c r="G77" s="28"/>
-      <c r="H77" s="28"/>
-      <c r="I77" s="29"/>
+      <c r="E77" s="24"/>
+      <c r="F77" s="24"/>
+      <c r="G77" s="24"/>
+      <c r="H77" s="24"/>
+      <c r="I77" s="25"/>
     </row>
     <row r="78" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B78" s="4">
@@ -2531,14 +2534,14 @@
       <c r="C78" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D78" s="27" t="s">
+      <c r="D78" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E78" s="28"/>
-      <c r="F78" s="28"/>
-      <c r="G78" s="28"/>
-      <c r="H78" s="28"/>
-      <c r="I78" s="29"/>
+      <c r="E78" s="24"/>
+      <c r="F78" s="24"/>
+      <c r="G78" s="24"/>
+      <c r="H78" s="24"/>
+      <c r="I78" s="25"/>
     </row>
     <row r="79" spans="2:9" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B79" s="16" t="s">
@@ -2582,10 +2585,10 @@
       <c r="F80" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G80" s="27" t="s">
+      <c r="G80" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="H80" s="29"/>
+      <c r="H80" s="25"/>
       <c r="I80" s="1" t="s">
         <v>14</v>
       </c>
@@ -2606,10 +2609,10 @@
       <c r="F81" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="G81" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="H81" s="29"/>
+      <c r="G81" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="H81" s="25"/>
       <c r="I81" s="1" t="s">
         <v>16</v>
       </c>
@@ -2673,14 +2676,14 @@
       <c r="C84" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D84" s="27" t="s">
+      <c r="D84" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E84" s="28"/>
-      <c r="F84" s="28"/>
-      <c r="G84" s="28"/>
-      <c r="H84" s="28"/>
-      <c r="I84" s="29"/>
+      <c r="E84" s="24"/>
+      <c r="F84" s="24"/>
+      <c r="G84" s="24"/>
+      <c r="H84" s="24"/>
+      <c r="I84" s="25"/>
     </row>
     <row r="85" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B85" s="4">
@@ -2718,11 +2721,11 @@
       <c r="D86" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="E86" s="27" t="s">
+      <c r="E86" s="23" t="s">
         <v>43</v>
       </c>
-      <c r="F86" s="28"/>
-      <c r="G86" s="29"/>
+      <c r="F86" s="24"/>
+      <c r="G86" s="25"/>
       <c r="H86" s="3" t="s">
         <v>14</v>
       </c>
@@ -2737,18 +2740,18 @@
       <c r="C87" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D87" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="E87" s="29"/>
+      <c r="D87" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="E87" s="25"/>
       <c r="F87" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G87" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="H87" s="28"/>
-      <c r="I87" s="29"/>
+      <c r="G87" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="H87" s="24"/>
+      <c r="I87" s="25"/>
     </row>
     <row r="88" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B88" s="4">
@@ -2757,14 +2760,14 @@
       <c r="C88" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D88" s="27" t="s">
+      <c r="D88" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E88" s="28"/>
-      <c r="F88" s="28"/>
-      <c r="G88" s="28"/>
-      <c r="H88" s="28"/>
-      <c r="I88" s="29"/>
+      <c r="E88" s="24"/>
+      <c r="F88" s="24"/>
+      <c r="G88" s="24"/>
+      <c r="H88" s="24"/>
+      <c r="I88" s="25"/>
     </row>
     <row r="89" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B89" s="4">
@@ -2773,18 +2776,18 @@
       <c r="C89" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D89" s="27" t="s">
+      <c r="D89" s="23" t="s">
         <v>44</v>
       </c>
-      <c r="E89" s="28"/>
-      <c r="F89" s="29"/>
+      <c r="E89" s="24"/>
+      <c r="F89" s="25"/>
       <c r="G89" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="H89" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="I89" s="29"/>
+      <c r="H89" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="I89" s="25"/>
     </row>
     <row r="90" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B90" s="4">
@@ -2793,10 +2796,10 @@
       <c r="C90" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D90" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="E90" s="29"/>
+      <c r="D90" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="E90" s="25"/>
       <c r="F90" s="3" t="s">
         <v>16</v>
       </c>
@@ -2818,13 +2821,13 @@
       <c r="C91" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D91" s="27" t="s">
+      <c r="D91" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E91" s="28"/>
-      <c r="F91" s="28"/>
-      <c r="G91" s="28"/>
-      <c r="H91" s="29"/>
+      <c r="E91" s="24"/>
+      <c r="F91" s="24"/>
+      <c r="G91" s="24"/>
+      <c r="H91" s="25"/>
       <c r="I91" s="18" t="s">
         <v>45</v>
       </c>
@@ -2836,14 +2839,14 @@
       <c r="C92" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D92" s="27" t="s">
+      <c r="D92" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E92" s="28"/>
-      <c r="F92" s="28"/>
-      <c r="G92" s="28"/>
-      <c r="H92" s="28"/>
-      <c r="I92" s="29"/>
+      <c r="E92" s="24"/>
+      <c r="F92" s="24"/>
+      <c r="G92" s="24"/>
+      <c r="H92" s="24"/>
+      <c r="I92" s="25"/>
     </row>
     <row r="93" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B93" s="4">
@@ -2852,14 +2855,14 @@
       <c r="C93" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D93" s="27" t="s">
+      <c r="D93" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="E93" s="28"/>
-      <c r="F93" s="28"/>
-      <c r="G93" s="28"/>
-      <c r="H93" s="28"/>
-      <c r="I93" s="29"/>
+      <c r="E93" s="24"/>
+      <c r="F93" s="24"/>
+      <c r="G93" s="24"/>
+      <c r="H93" s="24"/>
+      <c r="I93" s="25"/>
     </row>
     <row r="94" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B94" s="4">
@@ -2868,14 +2871,14 @@
       <c r="C94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D94" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="E94" s="28"/>
-      <c r="F94" s="28"/>
-      <c r="G94" s="28"/>
-      <c r="H94" s="28"/>
-      <c r="I94" s="29"/>
+      <c r="D94" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="E94" s="24"/>
+      <c r="F94" s="24"/>
+      <c r="G94" s="24"/>
+      <c r="H94" s="24"/>
+      <c r="I94" s="25"/>
     </row>
     <row r="95" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B95" s="4">
@@ -2884,15 +2887,15 @@
       <c r="C95" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D95" s="27" t="s">
+      <c r="D95" s="23" t="s">
         <v>47</v>
       </c>
-      <c r="E95" s="28"/>
-      <c r="F95" s="29"/>
-      <c r="G95" s="27" t="s">
+      <c r="E95" s="24"/>
+      <c r="F95" s="25"/>
+      <c r="G95" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="H95" s="29"/>
+      <c r="H95" s="25"/>
       <c r="I95" s="1" t="s">
         <v>14</v>
       </c>
@@ -2904,14 +2907,14 @@
       <c r="C96" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D96" s="27" t="s">
+      <c r="D96" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E96" s="28"/>
-      <c r="F96" s="28"/>
-      <c r="G96" s="28"/>
-      <c r="H96" s="28"/>
-      <c r="I96" s="29"/>
+      <c r="E96" s="24"/>
+      <c r="F96" s="24"/>
+      <c r="G96" s="24"/>
+      <c r="H96" s="24"/>
+      <c r="I96" s="25"/>
     </row>
     <row r="97" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B97" s="4">
@@ -2920,14 +2923,14 @@
       <c r="C97" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D97" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="E97" s="28"/>
-      <c r="F97" s="28"/>
-      <c r="G97" s="28"/>
-      <c r="H97" s="28"/>
-      <c r="I97" s="29"/>
+      <c r="D97" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="E97" s="24"/>
+      <c r="F97" s="24"/>
+      <c r="G97" s="24"/>
+      <c r="H97" s="24"/>
+      <c r="I97" s="25"/>
     </row>
     <row r="98" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B98" s="4">
@@ -2936,14 +2939,14 @@
       <c r="C98" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D98" s="27" t="s">
+      <c r="D98" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E98" s="28"/>
-      <c r="F98" s="28"/>
-      <c r="G98" s="28"/>
-      <c r="H98" s="28"/>
-      <c r="I98" s="29"/>
+      <c r="E98" s="24"/>
+      <c r="F98" s="24"/>
+      <c r="G98" s="24"/>
+      <c r="H98" s="24"/>
+      <c r="I98" s="25"/>
     </row>
     <row r="99" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B99" s="4">
@@ -2952,12 +2955,12 @@
       <c r="C99" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D99" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="E99" s="28"/>
-      <c r="F99" s="28"/>
-      <c r="G99" s="29"/>
+      <c r="D99" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="E99" s="24"/>
+      <c r="F99" s="24"/>
+      <c r="G99" s="25"/>
       <c r="H99" s="3" t="s">
         <v>49</v>
       </c>
@@ -2981,21 +2984,21 @@
       <c r="F100" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="G100" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="H100" s="28"/>
-      <c r="I100" s="29"/>
+      <c r="G100" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="H100" s="24"/>
+      <c r="I100" s="25"/>
     </row>
     <row r="101" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B101" s="27"/>
-      <c r="C101" s="28"/>
-      <c r="D101" s="28"/>
-      <c r="E101" s="28"/>
-      <c r="F101" s="28"/>
-      <c r="G101" s="28"/>
-      <c r="H101" s="28"/>
-      <c r="I101" s="29"/>
+      <c r="B101" s="23"/>
+      <c r="C101" s="24"/>
+      <c r="D101" s="24"/>
+      <c r="E101" s="24"/>
+      <c r="F101" s="24"/>
+      <c r="G101" s="24"/>
+      <c r="H101" s="24"/>
+      <c r="I101" s="25"/>
     </row>
     <row r="102" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B102" s="3"/>
@@ -3014,10 +3017,10 @@
       <c r="C103" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D103" s="27" t="s">
+      <c r="D103" s="23" t="s">
         <v>51</v>
       </c>
-      <c r="E103" s="29"/>
+      <c r="E103" s="25"/>
       <c r="F103" s="3"/>
       <c r="G103" s="3"/>
       <c r="H103" s="3"/>
@@ -3030,10 +3033,10 @@
       <c r="C104" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D104" s="27" t="s">
+      <c r="D104" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="E104" s="29"/>
+      <c r="E104" s="25"/>
       <c r="F104" s="3"/>
       <c r="G104" s="3"/>
       <c r="H104" s="3"/>
@@ -3046,10 +3049,10 @@
       <c r="C105" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D105" s="27" t="s">
+      <c r="D105" s="23" t="s">
         <v>53</v>
       </c>
-      <c r="E105" s="29"/>
+      <c r="E105" s="25"/>
       <c r="F105" s="3"/>
       <c r="G105" s="3"/>
       <c r="H105" s="3"/>
@@ -3062,10 +3065,10 @@
       <c r="C106" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D106" s="27" t="s">
+      <c r="D106" s="23" t="s">
         <v>54</v>
       </c>
-      <c r="E106" s="29"/>
+      <c r="E106" s="25"/>
       <c r="F106" s="3"/>
       <c r="G106" s="3"/>
       <c r="H106" s="3"/>
@@ -3078,10 +3081,10 @@
       <c r="C107" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D107" s="27" t="s">
+      <c r="D107" s="23" t="s">
         <v>55</v>
       </c>
-      <c r="E107" s="29"/>
+      <c r="E107" s="25"/>
       <c r="F107" s="3"/>
       <c r="G107" s="3"/>
       <c r="H107" s="3"/>
@@ -3094,10 +3097,10 @@
       <c r="C108" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D108" s="27" t="s">
+      <c r="D108" s="23" t="s">
         <v>56</v>
       </c>
-      <c r="E108" s="29"/>
+      <c r="E108" s="25"/>
       <c r="F108" s="3"/>
       <c r="G108" s="3"/>
       <c r="H108" s="3"/>
@@ -3134,28 +3137,28 @@
       <c r="I111" s="20"/>
     </row>
     <row r="112" spans="2:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B112" s="30" t="s">
+      <c r="B112" s="34" t="s">
         <v>57</v>
       </c>
-      <c r="C112" s="31"/>
-      <c r="D112" s="31"/>
-      <c r="E112" s="31"/>
-      <c r="F112" s="31"/>
-      <c r="G112" s="31"/>
-      <c r="H112" s="31"/>
-      <c r="I112" s="31"/>
-      <c r="J112" s="32"/>
+      <c r="C112" s="35"/>
+      <c r="D112" s="35"/>
+      <c r="E112" s="35"/>
+      <c r="F112" s="35"/>
+      <c r="G112" s="35"/>
+      <c r="H112" s="35"/>
+      <c r="I112" s="35"/>
+      <c r="J112" s="36"/>
     </row>
     <row r="113" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B113" s="33"/>
-      <c r="C113" s="34"/>
-      <c r="D113" s="34"/>
-      <c r="E113" s="34"/>
-      <c r="F113" s="34"/>
-      <c r="G113" s="34"/>
-      <c r="H113" s="34"/>
-      <c r="I113" s="34"/>
-      <c r="J113" s="35"/>
+      <c r="B113" s="37"/>
+      <c r="C113" s="38"/>
+      <c r="D113" s="38"/>
+      <c r="E113" s="38"/>
+      <c r="F113" s="38"/>
+      <c r="G113" s="38"/>
+      <c r="H113" s="38"/>
+      <c r="I113" s="38"/>
+      <c r="J113" s="39"/>
     </row>
     <row r="114" spans="2:10" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B114" s="8" t="s">
@@ -3286,13 +3289,13 @@
       <c r="E118" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="F118" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="G118" s="28"/>
-      <c r="H118" s="28"/>
-      <c r="I118" s="28"/>
-      <c r="J118" s="29"/>
+      <c r="F118" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="G118" s="24"/>
+      <c r="H118" s="24"/>
+      <c r="I118" s="24"/>
+      <c r="J118" s="25"/>
     </row>
     <row r="119" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B119" s="4">
@@ -3330,13 +3333,13 @@
       <c r="C120" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D120" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="E120" s="28"/>
-      <c r="F120" s="28"/>
-      <c r="G120" s="28"/>
-      <c r="H120" s="29"/>
+      <c r="D120" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="E120" s="24"/>
+      <c r="F120" s="24"/>
+      <c r="G120" s="24"/>
+      <c r="H120" s="25"/>
       <c r="I120" s="1" t="s">
         <v>16</v>
       </c>
@@ -3351,15 +3354,15 @@
       <c r="C121" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D121" s="27" t="s">
+      <c r="D121" s="23" t="s">
         <v>65</v>
       </c>
-      <c r="E121" s="28"/>
-      <c r="F121" s="28"/>
-      <c r="G121" s="28"/>
-      <c r="H121" s="28"/>
-      <c r="I121" s="28"/>
-      <c r="J121" s="29"/>
+      <c r="E121" s="24"/>
+      <c r="F121" s="24"/>
+      <c r="G121" s="24"/>
+      <c r="H121" s="24"/>
+      <c r="I121" s="24"/>
+      <c r="J121" s="25"/>
     </row>
     <row r="122" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B122" s="4">
@@ -3406,12 +3409,12 @@
       <c r="F123" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="G123" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="H123" s="28"/>
-      <c r="I123" s="28"/>
-      <c r="J123" s="29"/>
+      <c r="G123" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="H123" s="24"/>
+      <c r="I123" s="24"/>
+      <c r="J123" s="25"/>
     </row>
     <row r="124" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B124" s="4">
@@ -3429,12 +3432,12 @@
       <c r="F124" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="G124" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="H124" s="28"/>
-      <c r="I124" s="28"/>
-      <c r="J124" s="29"/>
+      <c r="G124" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="H124" s="24"/>
+      <c r="I124" s="24"/>
+      <c r="J124" s="25"/>
     </row>
     <row r="125" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B125" s="4">
@@ -3449,13 +3452,13 @@
       <c r="E125" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="F125" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="G125" s="28"/>
-      <c r="H125" s="28"/>
-      <c r="I125" s="28"/>
-      <c r="J125" s="29"/>
+      <c r="F125" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="G125" s="24"/>
+      <c r="H125" s="24"/>
+      <c r="I125" s="24"/>
+      <c r="J125" s="25"/>
     </row>
     <row r="126" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B126" s="4">
@@ -3473,11 +3476,11 @@
       <c r="F126" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="G126" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="H126" s="28"/>
-      <c r="I126" s="29"/>
+      <c r="G126" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="H126" s="24"/>
+      <c r="I126" s="25"/>
       <c r="J126" s="1" t="s">
         <v>16</v>
       </c>
@@ -3495,13 +3498,13 @@
       <c r="E127" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="F127" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="G127" s="28"/>
-      <c r="H127" s="28"/>
-      <c r="I127" s="28"/>
-      <c r="J127" s="29"/>
+      <c r="F127" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="G127" s="24"/>
+      <c r="H127" s="24"/>
+      <c r="I127" s="24"/>
+      <c r="J127" s="25"/>
     </row>
     <row r="128" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B128" s="4">
@@ -3510,15 +3513,15 @@
       <c r="C128" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D128" s="27" t="s">
+      <c r="D128" s="23" t="s">
         <v>65</v>
       </c>
-      <c r="E128" s="28"/>
-      <c r="F128" s="28"/>
-      <c r="G128" s="28"/>
-      <c r="H128" s="28"/>
-      <c r="I128" s="28"/>
-      <c r="J128" s="29"/>
+      <c r="E128" s="24"/>
+      <c r="F128" s="24"/>
+      <c r="G128" s="24"/>
+      <c r="H128" s="24"/>
+      <c r="I128" s="24"/>
+      <c r="J128" s="25"/>
     </row>
     <row r="129" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B129" s="4">
@@ -3701,15 +3704,15 @@
       <c r="C135" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D135" s="27" t="s">
+      <c r="D135" s="23" t="s">
         <v>65</v>
       </c>
-      <c r="E135" s="28"/>
-      <c r="F135" s="28"/>
-      <c r="G135" s="28"/>
-      <c r="H135" s="28"/>
-      <c r="I135" s="28"/>
-      <c r="J135" s="29"/>
+      <c r="E135" s="24"/>
+      <c r="F135" s="24"/>
+      <c r="G135" s="24"/>
+      <c r="H135" s="24"/>
+      <c r="I135" s="24"/>
+      <c r="J135" s="25"/>
     </row>
     <row r="136" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B136" s="4">
@@ -3921,15 +3924,15 @@
       <c r="C143" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D143" s="27" t="s">
+      <c r="D143" s="23" t="s">
         <v>65</v>
       </c>
-      <c r="E143" s="28"/>
-      <c r="F143" s="28"/>
-      <c r="G143" s="28"/>
-      <c r="H143" s="28"/>
-      <c r="I143" s="28"/>
-      <c r="J143" s="29"/>
+      <c r="E143" s="24"/>
+      <c r="F143" s="24"/>
+      <c r="G143" s="24"/>
+      <c r="H143" s="24"/>
+      <c r="I143" s="24"/>
+      <c r="J143" s="25"/>
     </row>
     <row r="144" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B144" s="4">
@@ -4005,12 +4008,12 @@
       <c r="F146" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="G146" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="H146" s="28"/>
-      <c r="I146" s="28"/>
-      <c r="J146" s="29"/>
+      <c r="G146" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="H146" s="24"/>
+      <c r="I146" s="24"/>
+      <c r="J146" s="25"/>
     </row>
     <row r="147" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B147" s="4">
@@ -4077,15 +4080,15 @@
       <c r="C149" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D149" s="23" t="s">
+      <c r="D149" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="E149" s="24"/>
-      <c r="F149" s="24"/>
-      <c r="G149" s="24"/>
-      <c r="H149" s="24"/>
-      <c r="I149" s="24"/>
-      <c r="J149" s="38"/>
+      <c r="E149" s="27"/>
+      <c r="F149" s="27"/>
+      <c r="G149" s="27"/>
+      <c r="H149" s="27"/>
+      <c r="I149" s="27"/>
+      <c r="J149" s="28"/>
     </row>
     <row r="150" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B150" s="4">
@@ -4094,13 +4097,13 @@
       <c r="C150" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D150" s="25"/>
-      <c r="E150" s="26"/>
-      <c r="F150" s="26"/>
-      <c r="G150" s="26"/>
-      <c r="H150" s="26"/>
-      <c r="I150" s="26"/>
-      <c r="J150" s="39"/>
+      <c r="D150" s="29"/>
+      <c r="E150" s="30"/>
+      <c r="F150" s="30"/>
+      <c r="G150" s="30"/>
+      <c r="H150" s="30"/>
+      <c r="I150" s="30"/>
+      <c r="J150" s="31"/>
     </row>
     <row r="151" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B151" s="4">
@@ -4147,11 +4150,11 @@
       <c r="F152" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="G152" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="H152" s="28"/>
-      <c r="I152" s="29"/>
+      <c r="G152" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="H152" s="24"/>
+      <c r="I152" s="25"/>
       <c r="J152" s="1" t="s">
         <v>69</v>
       </c>
@@ -4279,15 +4282,15 @@
       <c r="C157" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D157" s="27" t="s">
+      <c r="D157" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E157" s="28"/>
-      <c r="F157" s="28"/>
-      <c r="G157" s="28"/>
-      <c r="H157" s="28"/>
-      <c r="I157" s="28"/>
-      <c r="J157" s="29"/>
+      <c r="E157" s="24"/>
+      <c r="F157" s="24"/>
+      <c r="G157" s="24"/>
+      <c r="H157" s="24"/>
+      <c r="I157" s="24"/>
+      <c r="J157" s="25"/>
     </row>
     <row r="158" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B158" s="4">
@@ -4468,15 +4471,15 @@
       <c r="C164" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D164" s="27" t="s">
+      <c r="D164" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E164" s="28"/>
-      <c r="F164" s="28"/>
-      <c r="G164" s="28"/>
-      <c r="H164" s="28"/>
-      <c r="I164" s="28"/>
-      <c r="J164" s="29"/>
+      <c r="E164" s="24"/>
+      <c r="F164" s="24"/>
+      <c r="G164" s="24"/>
+      <c r="H164" s="24"/>
+      <c r="I164" s="24"/>
+      <c r="J164" s="25"/>
     </row>
     <row r="165" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B165" s="4">
@@ -4674,15 +4677,15 @@
       <c r="C172" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D172" s="27" t="s">
+      <c r="D172" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E172" s="28"/>
-      <c r="F172" s="28"/>
-      <c r="G172" s="28"/>
-      <c r="H172" s="28"/>
-      <c r="I172" s="28"/>
-      <c r="J172" s="29"/>
+      <c r="E172" s="24"/>
+      <c r="F172" s="24"/>
+      <c r="G172" s="24"/>
+      <c r="H172" s="24"/>
+      <c r="I172" s="24"/>
+      <c r="J172" s="25"/>
     </row>
     <row r="173" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B173" s="4">
@@ -4746,44 +4749,44 @@
       <c r="B175" s="4">
         <v>45903</v>
       </c>
-      <c r="C175" s="23" t="s">
+      <c r="C175" s="26" t="s">
         <v>39</v>
       </c>
-      <c r="D175" s="24"/>
-      <c r="E175" s="24"/>
-      <c r="F175" s="24"/>
-      <c r="G175" s="24"/>
-      <c r="H175" s="24"/>
-      <c r="I175" s="24"/>
-      <c r="J175" s="24"/>
+      <c r="D175" s="27"/>
+      <c r="E175" s="27"/>
+      <c r="F175" s="27"/>
+      <c r="G175" s="27"/>
+      <c r="H175" s="27"/>
+      <c r="I175" s="27"/>
+      <c r="J175" s="27"/>
     </row>
     <row r="176" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B176" s="4">
         <v>45904</v>
       </c>
-      <c r="C176" s="25"/>
-      <c r="D176" s="26"/>
-      <c r="E176" s="26"/>
-      <c r="F176" s="26"/>
-      <c r="G176" s="26"/>
-      <c r="H176" s="26"/>
-      <c r="I176" s="26"/>
-      <c r="J176" s="26"/>
+      <c r="C176" s="29"/>
+      <c r="D176" s="30"/>
+      <c r="E176" s="30"/>
+      <c r="F176" s="30"/>
+      <c r="G176" s="30"/>
+      <c r="H176" s="30"/>
+      <c r="I176" s="30"/>
+      <c r="J176" s="30"/>
     </row>
     <row r="177" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B177" s="4">
         <v>45905</v>
       </c>
-      <c r="C177" s="27" t="s">
+      <c r="C177" s="23" t="s">
         <v>39</v>
       </c>
-      <c r="D177" s="28"/>
-      <c r="E177" s="28"/>
-      <c r="F177" s="28"/>
-      <c r="G177" s="28"/>
-      <c r="H177" s="28"/>
-      <c r="I177" s="28"/>
-      <c r="J177" s="29"/>
+      <c r="D177" s="24"/>
+      <c r="E177" s="24"/>
+      <c r="F177" s="24"/>
+      <c r="G177" s="24"/>
+      <c r="H177" s="24"/>
+      <c r="I177" s="24"/>
+      <c r="J177" s="25"/>
     </row>
     <row r="178" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B178" s="4">
@@ -4973,15 +4976,21 @@
       </c>
     </row>
     <row r="185" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B185" s="3"/>
-      <c r="C185" s="3"/>
-      <c r="D185" s="3"/>
-      <c r="E185" s="3"/>
-      <c r="F185" s="3"/>
-      <c r="G185" s="3"/>
-      <c r="H185" s="3"/>
-      <c r="I185" s="1"/>
-      <c r="J185" s="1"/>
+      <c r="B185" s="4">
+        <v>45921</v>
+      </c>
+      <c r="C185" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D185" s="23" t="s">
+        <v>74</v>
+      </c>
+      <c r="E185" s="24"/>
+      <c r="F185" s="24"/>
+      <c r="G185" s="24"/>
+      <c r="H185" s="24"/>
+      <c r="I185" s="24"/>
+      <c r="J185" s="25"/>
     </row>
     <row r="186" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B186" s="3"/>
@@ -7525,7 +7534,79 @@
       <c r="J416" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="87">
+  <mergeCells count="88">
+    <mergeCell ref="D185:J185"/>
+    <mergeCell ref="C175:J176"/>
+    <mergeCell ref="D164:J164"/>
+    <mergeCell ref="D157:J157"/>
+    <mergeCell ref="D143:J143"/>
+    <mergeCell ref="D135:J135"/>
+    <mergeCell ref="D172:J172"/>
+    <mergeCell ref="G146:J146"/>
+    <mergeCell ref="D108:E108"/>
+    <mergeCell ref="B112:J113"/>
+    <mergeCell ref="G124:J124"/>
+    <mergeCell ref="D120:H120"/>
+    <mergeCell ref="G123:J123"/>
+    <mergeCell ref="D121:J121"/>
+    <mergeCell ref="D31:I31"/>
+    <mergeCell ref="G35:H35"/>
+    <mergeCell ref="D40:I40"/>
+    <mergeCell ref="D33:I33"/>
+    <mergeCell ref="D46:I46"/>
+    <mergeCell ref="D43:I43"/>
+    <mergeCell ref="D78:I78"/>
+    <mergeCell ref="G71:H71"/>
+    <mergeCell ref="D76:I76"/>
+    <mergeCell ref="D66:H66"/>
+    <mergeCell ref="D77:I77"/>
+    <mergeCell ref="D73:I73"/>
+    <mergeCell ref="D70:E70"/>
+    <mergeCell ref="D74:F74"/>
+    <mergeCell ref="D84:I84"/>
+    <mergeCell ref="D69:I69"/>
+    <mergeCell ref="D8:I8"/>
+    <mergeCell ref="D9:I9"/>
+    <mergeCell ref="D10:I10"/>
+    <mergeCell ref="D11:I11"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="D14:I14"/>
+    <mergeCell ref="G27:H27"/>
+    <mergeCell ref="D25:I25"/>
+    <mergeCell ref="G20:H20"/>
+    <mergeCell ref="D19:I19"/>
+    <mergeCell ref="D18:I18"/>
+    <mergeCell ref="D30:I30"/>
+    <mergeCell ref="G80:H80"/>
+    <mergeCell ref="G42:H42"/>
+    <mergeCell ref="D60:I60"/>
+    <mergeCell ref="D62:I62"/>
+    <mergeCell ref="D61:I61"/>
+    <mergeCell ref="G49:H49"/>
+    <mergeCell ref="D47:I47"/>
+    <mergeCell ref="D55:I55"/>
+    <mergeCell ref="G57:H57"/>
+    <mergeCell ref="G64:H64"/>
+    <mergeCell ref="D96:I96"/>
+    <mergeCell ref="D95:F95"/>
+    <mergeCell ref="G95:H95"/>
+    <mergeCell ref="D92:I92"/>
+    <mergeCell ref="D93:I93"/>
+    <mergeCell ref="D90:E90"/>
+    <mergeCell ref="D91:H91"/>
+    <mergeCell ref="E86:G86"/>
+    <mergeCell ref="D88:I88"/>
+    <mergeCell ref="H67:I67"/>
+    <mergeCell ref="G81:H81"/>
+    <mergeCell ref="D67:F67"/>
+    <mergeCell ref="F68:I68"/>
+    <mergeCell ref="D87:E87"/>
+    <mergeCell ref="G87:I87"/>
+    <mergeCell ref="D98:I98"/>
+    <mergeCell ref="D94:I94"/>
+    <mergeCell ref="H89:I89"/>
+    <mergeCell ref="D89:F89"/>
+    <mergeCell ref="D97:I97"/>
     <mergeCell ref="C177:J177"/>
     <mergeCell ref="D106:E106"/>
     <mergeCell ref="D99:G99"/>
@@ -7542,77 +7623,6 @@
     <mergeCell ref="F118:J118"/>
     <mergeCell ref="G152:I152"/>
     <mergeCell ref="D149:J150"/>
-    <mergeCell ref="D98:I98"/>
-    <mergeCell ref="D94:I94"/>
-    <mergeCell ref="H89:I89"/>
-    <mergeCell ref="D89:F89"/>
-    <mergeCell ref="D97:I97"/>
-    <mergeCell ref="G64:H64"/>
-    <mergeCell ref="D96:I96"/>
-    <mergeCell ref="D95:F95"/>
-    <mergeCell ref="G95:H95"/>
-    <mergeCell ref="D92:I92"/>
-    <mergeCell ref="D93:I93"/>
-    <mergeCell ref="D90:E90"/>
-    <mergeCell ref="D91:H91"/>
-    <mergeCell ref="E86:G86"/>
-    <mergeCell ref="D88:I88"/>
-    <mergeCell ref="H67:I67"/>
-    <mergeCell ref="G81:H81"/>
-    <mergeCell ref="D67:F67"/>
-    <mergeCell ref="F68:I68"/>
-    <mergeCell ref="D87:E87"/>
-    <mergeCell ref="G87:I87"/>
-    <mergeCell ref="D60:I60"/>
-    <mergeCell ref="D62:I62"/>
-    <mergeCell ref="D61:I61"/>
-    <mergeCell ref="G49:H49"/>
-    <mergeCell ref="D47:I47"/>
-    <mergeCell ref="D55:I55"/>
-    <mergeCell ref="G57:H57"/>
-    <mergeCell ref="D84:I84"/>
-    <mergeCell ref="D69:I69"/>
-    <mergeCell ref="D8:I8"/>
-    <mergeCell ref="D9:I9"/>
-    <mergeCell ref="D10:I10"/>
-    <mergeCell ref="D11:I11"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="D14:I14"/>
-    <mergeCell ref="G27:H27"/>
-    <mergeCell ref="D25:I25"/>
-    <mergeCell ref="G20:H20"/>
-    <mergeCell ref="D19:I19"/>
-    <mergeCell ref="D18:I18"/>
-    <mergeCell ref="D30:I30"/>
-    <mergeCell ref="G80:H80"/>
-    <mergeCell ref="G42:H42"/>
-    <mergeCell ref="D78:I78"/>
-    <mergeCell ref="G71:H71"/>
-    <mergeCell ref="D76:I76"/>
-    <mergeCell ref="D66:H66"/>
-    <mergeCell ref="D77:I77"/>
-    <mergeCell ref="D73:I73"/>
-    <mergeCell ref="D70:E70"/>
-    <mergeCell ref="D74:F74"/>
-    <mergeCell ref="D31:I31"/>
-    <mergeCell ref="G35:H35"/>
-    <mergeCell ref="D40:I40"/>
-    <mergeCell ref="D33:I33"/>
-    <mergeCell ref="D46:I46"/>
-    <mergeCell ref="D43:I43"/>
-    <mergeCell ref="D108:E108"/>
-    <mergeCell ref="B112:J113"/>
-    <mergeCell ref="G124:J124"/>
-    <mergeCell ref="D120:H120"/>
-    <mergeCell ref="G123:J123"/>
-    <mergeCell ref="D121:J121"/>
-    <mergeCell ref="C175:J176"/>
-    <mergeCell ref="D164:J164"/>
-    <mergeCell ref="D157:J157"/>
-    <mergeCell ref="D143:J143"/>
-    <mergeCell ref="D135:J135"/>
-    <mergeCell ref="D172:J172"/>
-    <mergeCell ref="G146:J146"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/attendance_sheet.xlsx
+++ b/attendance_sheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\repositary\3rd_Year_5th_Semester\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7E75742-95B5-4BC8-BC21-90F1B3C18D72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7125557-3EC2-4154-AFDE-6AF73401A3D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{EB654061-A886-47D1-BF86-9B1A84FCE7FB}"/>
+    <workbookView xWindow="4932" yWindow="3264" windowWidth="15000" windowHeight="7632" xr2:uid="{EB654061-A886-47D1-BF86-9B1A84FCE7FB}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="922" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="925" uniqueCount="75">
   <si>
     <t>Date</t>
   </si>
@@ -556,22 +556,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -590,6 +578,18 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -993,14 +993,14 @@
       <c r="C8" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D8" s="32" t="s">
+      <c r="D8" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="E8" s="32"/>
-      <c r="F8" s="32"/>
-      <c r="G8" s="32"/>
-      <c r="H8" s="32"/>
-      <c r="I8" s="32"/>
+      <c r="E8" s="37"/>
+      <c r="F8" s="37"/>
+      <c r="G8" s="37"/>
+      <c r="H8" s="37"/>
+      <c r="I8" s="37"/>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B9" s="4">
@@ -1009,14 +1009,14 @@
       <c r="C9" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D9" s="32" t="s">
+      <c r="D9" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="E9" s="32"/>
-      <c r="F9" s="32"/>
-      <c r="G9" s="32"/>
-      <c r="H9" s="32"/>
-      <c r="I9" s="32"/>
+      <c r="E9" s="37"/>
+      <c r="F9" s="37"/>
+      <c r="G9" s="37"/>
+      <c r="H9" s="37"/>
+      <c r="I9" s="37"/>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B10" s="4">
@@ -1025,14 +1025,14 @@
       <c r="C10" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D10" s="32" t="s">
+      <c r="D10" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="E10" s="32"/>
-      <c r="F10" s="32"/>
-      <c r="G10" s="32"/>
-      <c r="H10" s="32"/>
-      <c r="I10" s="32"/>
+      <c r="E10" s="37"/>
+      <c r="F10" s="37"/>
+      <c r="G10" s="37"/>
+      <c r="H10" s="37"/>
+      <c r="I10" s="37"/>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B11" s="4">
@@ -1041,14 +1041,14 @@
       <c r="C11" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D11" s="32" t="s">
+      <c r="D11" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="E11" s="32"/>
-      <c r="F11" s="32"/>
-      <c r="G11" s="32"/>
-      <c r="H11" s="32"/>
-      <c r="I11" s="32"/>
+      <c r="E11" s="37"/>
+      <c r="F11" s="37"/>
+      <c r="G11" s="37"/>
+      <c r="H11" s="37"/>
+      <c r="I11" s="37"/>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B12" s="4">
@@ -1092,10 +1092,10 @@
       <c r="F13" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="G13" s="32" t="s">
+      <c r="G13" s="37" t="s">
         <v>18</v>
       </c>
-      <c r="H13" s="32"/>
+      <c r="H13" s="37"/>
       <c r="I13" s="1" t="s">
         <v>14</v>
       </c>
@@ -1107,14 +1107,14 @@
       <c r="C14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D14" s="32" t="s">
+      <c r="D14" s="37" t="s">
         <v>19</v>
       </c>
-      <c r="E14" s="32"/>
-      <c r="F14" s="32"/>
-      <c r="G14" s="32"/>
-      <c r="H14" s="32"/>
-      <c r="I14" s="32"/>
+      <c r="E14" s="37"/>
+      <c r="F14" s="37"/>
+      <c r="G14" s="37"/>
+      <c r="H14" s="37"/>
+      <c r="I14" s="37"/>
     </row>
     <row r="15" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B15" s="4">
@@ -1201,14 +1201,14 @@
       <c r="C18" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D18" s="32" t="s">
+      <c r="D18" s="37" t="s">
         <v>23</v>
       </c>
-      <c r="E18" s="32"/>
-      <c r="F18" s="32"/>
-      <c r="G18" s="32"/>
-      <c r="H18" s="32"/>
-      <c r="I18" s="32"/>
+      <c r="E18" s="37"/>
+      <c r="F18" s="37"/>
+      <c r="G18" s="37"/>
+      <c r="H18" s="37"/>
+      <c r="I18" s="37"/>
     </row>
     <row r="19" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B19" s="4">
@@ -1217,14 +1217,14 @@
       <c r="C19" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D19" s="32" t="s">
+      <c r="D19" s="37" t="s">
         <v>23</v>
       </c>
-      <c r="E19" s="32"/>
-      <c r="F19" s="32"/>
-      <c r="G19" s="32"/>
-      <c r="H19" s="32"/>
-      <c r="I19" s="32"/>
+      <c r="E19" s="37"/>
+      <c r="F19" s="37"/>
+      <c r="G19" s="37"/>
+      <c r="H19" s="37"/>
+      <c r="I19" s="37"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B20" s="4">
@@ -1242,10 +1242,10 @@
       <c r="F20" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G20" s="32" t="s">
+      <c r="G20" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="H20" s="32"/>
+      <c r="H20" s="37"/>
       <c r="I20" s="1" t="s">
         <v>14</v>
       </c>
@@ -1361,14 +1361,14 @@
       <c r="C25" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D25" s="32" t="s">
+      <c r="D25" s="37" t="s">
         <v>26</v>
       </c>
-      <c r="E25" s="32"/>
-      <c r="F25" s="32"/>
-      <c r="G25" s="32"/>
-      <c r="H25" s="32"/>
-      <c r="I25" s="32"/>
+      <c r="E25" s="37"/>
+      <c r="F25" s="37"/>
+      <c r="G25" s="37"/>
+      <c r="H25" s="37"/>
+      <c r="I25" s="37"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B26" s="4">
@@ -1412,10 +1412,10 @@
       <c r="F27" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G27" s="32" t="s">
+      <c r="G27" s="37" t="s">
         <v>18</v>
       </c>
-      <c r="H27" s="32"/>
+      <c r="H27" s="37"/>
       <c r="I27" s="1" t="s">
         <v>14</v>
       </c>
@@ -1479,14 +1479,14 @@
       <c r="C30" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D30" s="33" t="s">
+      <c r="D30" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="E30" s="33"/>
-      <c r="F30" s="33"/>
-      <c r="G30" s="33"/>
-      <c r="H30" s="33"/>
-      <c r="I30" s="33"/>
+      <c r="E30" s="36"/>
+      <c r="F30" s="36"/>
+      <c r="G30" s="36"/>
+      <c r="H30" s="36"/>
+      <c r="I30" s="36"/>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B31" s="4">
@@ -1495,14 +1495,14 @@
       <c r="C31" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D31" s="33" t="s">
+      <c r="D31" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="E31" s="33"/>
-      <c r="F31" s="33"/>
-      <c r="G31" s="33"/>
-      <c r="H31" s="33"/>
-      <c r="I31" s="33"/>
+      <c r="E31" s="36"/>
+      <c r="F31" s="36"/>
+      <c r="G31" s="36"/>
+      <c r="H31" s="36"/>
+      <c r="I31" s="36"/>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B32" s="4">
@@ -1537,14 +1537,14 @@
       <c r="C33" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D33" s="33" t="s">
+      <c r="D33" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="E33" s="33"/>
-      <c r="F33" s="33"/>
-      <c r="G33" s="33"/>
-      <c r="H33" s="33"/>
-      <c r="I33" s="33"/>
+      <c r="E33" s="36"/>
+      <c r="F33" s="36"/>
+      <c r="G33" s="36"/>
+      <c r="H33" s="36"/>
+      <c r="I33" s="36"/>
     </row>
     <row r="34" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B34" s="4">
@@ -1588,10 +1588,10 @@
       <c r="F35" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G35" s="33" t="s">
+      <c r="G35" s="36" t="s">
         <v>18</v>
       </c>
-      <c r="H35" s="33"/>
+      <c r="H35" s="36"/>
       <c r="I35" s="1" t="s">
         <v>14</v>
       </c>
@@ -1707,14 +1707,14 @@
       <c r="C40" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D40" s="33" t="s">
+      <c r="D40" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="E40" s="33"/>
-      <c r="F40" s="33"/>
-      <c r="G40" s="33"/>
-      <c r="H40" s="33"/>
-      <c r="I40" s="33"/>
+      <c r="E40" s="36"/>
+      <c r="F40" s="36"/>
+      <c r="G40" s="36"/>
+      <c r="H40" s="36"/>
+      <c r="I40" s="36"/>
     </row>
     <row r="41" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B41" s="4">
@@ -1758,10 +1758,10 @@
       <c r="F42" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G42" s="33" t="s">
+      <c r="G42" s="36" t="s">
         <v>28</v>
       </c>
-      <c r="H42" s="33"/>
+      <c r="H42" s="36"/>
       <c r="I42" s="1" t="s">
         <v>15</v>
       </c>
@@ -1773,14 +1773,14 @@
       <c r="C43" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D43" s="33" t="s">
+      <c r="D43" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="E43" s="33"/>
-      <c r="F43" s="33"/>
-      <c r="G43" s="33"/>
-      <c r="H43" s="33"/>
-      <c r="I43" s="33"/>
+      <c r="E43" s="36"/>
+      <c r="F43" s="36"/>
+      <c r="G43" s="36"/>
+      <c r="H43" s="36"/>
+      <c r="I43" s="36"/>
     </row>
     <row r="44" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B44" s="4">
@@ -1844,14 +1844,14 @@
       <c r="C46" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D46" s="33" t="s">
+      <c r="D46" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="E46" s="33"/>
-      <c r="F46" s="33"/>
-      <c r="G46" s="33"/>
-      <c r="H46" s="33"/>
-      <c r="I46" s="33"/>
+      <c r="E46" s="36"/>
+      <c r="F46" s="36"/>
+      <c r="G46" s="36"/>
+      <c r="H46" s="36"/>
+      <c r="I46" s="36"/>
     </row>
     <row r="47" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B47" s="4">
@@ -3137,28 +3137,28 @@
       <c r="I111" s="20"/>
     </row>
     <row r="112" spans="2:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B112" s="34" t="s">
+      <c r="B112" s="30" t="s">
         <v>57</v>
       </c>
-      <c r="C112" s="35"/>
-      <c r="D112" s="35"/>
-      <c r="E112" s="35"/>
-      <c r="F112" s="35"/>
-      <c r="G112" s="35"/>
-      <c r="H112" s="35"/>
-      <c r="I112" s="35"/>
-      <c r="J112" s="36"/>
+      <c r="C112" s="31"/>
+      <c r="D112" s="31"/>
+      <c r="E112" s="31"/>
+      <c r="F112" s="31"/>
+      <c r="G112" s="31"/>
+      <c r="H112" s="31"/>
+      <c r="I112" s="31"/>
+      <c r="J112" s="32"/>
     </row>
     <row r="113" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B113" s="37"/>
-      <c r="C113" s="38"/>
-      <c r="D113" s="38"/>
-      <c r="E113" s="38"/>
-      <c r="F113" s="38"/>
-      <c r="G113" s="38"/>
-      <c r="H113" s="38"/>
-      <c r="I113" s="38"/>
-      <c r="J113" s="39"/>
+      <c r="B113" s="33"/>
+      <c r="C113" s="34"/>
+      <c r="D113" s="34"/>
+      <c r="E113" s="34"/>
+      <c r="F113" s="34"/>
+      <c r="G113" s="34"/>
+      <c r="H113" s="34"/>
+      <c r="I113" s="34"/>
+      <c r="J113" s="35"/>
     </row>
     <row r="114" spans="2:10" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B114" s="8" t="s">
@@ -4088,7 +4088,7 @@
       <c r="G149" s="27"/>
       <c r="H149" s="27"/>
       <c r="I149" s="27"/>
-      <c r="J149" s="28"/>
+      <c r="J149" s="38"/>
     </row>
     <row r="150" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B150" s="4">
@@ -4097,13 +4097,13 @@
       <c r="C150" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D150" s="29"/>
-      <c r="E150" s="30"/>
-      <c r="F150" s="30"/>
-      <c r="G150" s="30"/>
-      <c r="H150" s="30"/>
-      <c r="I150" s="30"/>
-      <c r="J150" s="31"/>
+      <c r="D150" s="28"/>
+      <c r="E150" s="29"/>
+      <c r="F150" s="29"/>
+      <c r="G150" s="29"/>
+      <c r="H150" s="29"/>
+      <c r="I150" s="29"/>
+      <c r="J150" s="39"/>
     </row>
     <row r="151" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B151" s="4">
@@ -4764,14 +4764,14 @@
       <c r="B176" s="4">
         <v>45904</v>
       </c>
-      <c r="C176" s="29"/>
-      <c r="D176" s="30"/>
-      <c r="E176" s="30"/>
-      <c r="F176" s="30"/>
-      <c r="G176" s="30"/>
-      <c r="H176" s="30"/>
-      <c r="I176" s="30"/>
-      <c r="J176" s="30"/>
+      <c r="C176" s="28"/>
+      <c r="D176" s="29"/>
+      <c r="E176" s="29"/>
+      <c r="F176" s="29"/>
+      <c r="G176" s="29"/>
+      <c r="H176" s="29"/>
+      <c r="I176" s="29"/>
+      <c r="J176" s="29"/>
     </row>
     <row r="177" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B177" s="4">
@@ -4993,15 +4993,23 @@
       <c r="J185" s="25"/>
     </row>
     <row r="186" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B186" s="3"/>
-      <c r="C186" s="3"/>
-      <c r="D186" s="3"/>
+      <c r="B186" s="4">
+        <v>45922</v>
+      </c>
+      <c r="C186" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D186" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="E186" s="3"/>
       <c r="F186" s="3"/>
       <c r="G186" s="3"/>
       <c r="H186" s="3"/>
       <c r="I186" s="1"/>
-      <c r="J186" s="1"/>
+      <c r="J186" s="1" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="187" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B187" s="3"/>
@@ -7535,34 +7543,47 @@
     </row>
   </sheetData>
   <mergeCells count="88">
-    <mergeCell ref="D185:J185"/>
-    <mergeCell ref="C175:J176"/>
-    <mergeCell ref="D164:J164"/>
-    <mergeCell ref="D157:J157"/>
-    <mergeCell ref="D143:J143"/>
-    <mergeCell ref="D135:J135"/>
-    <mergeCell ref="D172:J172"/>
-    <mergeCell ref="G146:J146"/>
-    <mergeCell ref="D108:E108"/>
-    <mergeCell ref="B112:J113"/>
-    <mergeCell ref="G124:J124"/>
-    <mergeCell ref="D120:H120"/>
-    <mergeCell ref="G123:J123"/>
-    <mergeCell ref="D121:J121"/>
-    <mergeCell ref="D31:I31"/>
-    <mergeCell ref="G35:H35"/>
-    <mergeCell ref="D40:I40"/>
-    <mergeCell ref="D33:I33"/>
-    <mergeCell ref="D46:I46"/>
-    <mergeCell ref="D43:I43"/>
-    <mergeCell ref="D78:I78"/>
-    <mergeCell ref="G71:H71"/>
-    <mergeCell ref="D76:I76"/>
-    <mergeCell ref="D66:H66"/>
-    <mergeCell ref="D77:I77"/>
-    <mergeCell ref="D73:I73"/>
-    <mergeCell ref="D70:E70"/>
-    <mergeCell ref="D74:F74"/>
+    <mergeCell ref="D106:E106"/>
+    <mergeCell ref="D99:G99"/>
+    <mergeCell ref="G126:I126"/>
+    <mergeCell ref="F125:J125"/>
+    <mergeCell ref="D128:J128"/>
+    <mergeCell ref="D103:E103"/>
+    <mergeCell ref="D104:E104"/>
+    <mergeCell ref="D105:E105"/>
+    <mergeCell ref="G100:I100"/>
+    <mergeCell ref="B101:I101"/>
+    <mergeCell ref="F127:J127"/>
+    <mergeCell ref="D107:E107"/>
+    <mergeCell ref="F118:J118"/>
+    <mergeCell ref="D98:I98"/>
+    <mergeCell ref="D94:I94"/>
+    <mergeCell ref="H89:I89"/>
+    <mergeCell ref="D89:F89"/>
+    <mergeCell ref="D97:I97"/>
+    <mergeCell ref="G64:H64"/>
+    <mergeCell ref="D96:I96"/>
+    <mergeCell ref="D95:F95"/>
+    <mergeCell ref="G95:H95"/>
+    <mergeCell ref="D92:I92"/>
+    <mergeCell ref="D93:I93"/>
+    <mergeCell ref="D90:E90"/>
+    <mergeCell ref="D91:H91"/>
+    <mergeCell ref="E86:G86"/>
+    <mergeCell ref="D88:I88"/>
+    <mergeCell ref="H67:I67"/>
+    <mergeCell ref="G81:H81"/>
+    <mergeCell ref="D67:F67"/>
+    <mergeCell ref="F68:I68"/>
+    <mergeCell ref="D87:E87"/>
+    <mergeCell ref="G87:I87"/>
+    <mergeCell ref="D60:I60"/>
+    <mergeCell ref="D62:I62"/>
+    <mergeCell ref="D61:I61"/>
+    <mergeCell ref="G49:H49"/>
+    <mergeCell ref="D47:I47"/>
+    <mergeCell ref="D55:I55"/>
+    <mergeCell ref="G57:H57"/>
     <mergeCell ref="D84:I84"/>
     <mergeCell ref="D69:I69"/>
     <mergeCell ref="D8:I8"/>
@@ -7579,50 +7600,37 @@
     <mergeCell ref="D30:I30"/>
     <mergeCell ref="G80:H80"/>
     <mergeCell ref="G42:H42"/>
-    <mergeCell ref="D60:I60"/>
-    <mergeCell ref="D62:I62"/>
-    <mergeCell ref="D61:I61"/>
-    <mergeCell ref="G49:H49"/>
-    <mergeCell ref="D47:I47"/>
-    <mergeCell ref="D55:I55"/>
-    <mergeCell ref="G57:H57"/>
-    <mergeCell ref="G64:H64"/>
-    <mergeCell ref="D96:I96"/>
-    <mergeCell ref="D95:F95"/>
-    <mergeCell ref="G95:H95"/>
-    <mergeCell ref="D92:I92"/>
-    <mergeCell ref="D93:I93"/>
-    <mergeCell ref="D90:E90"/>
-    <mergeCell ref="D91:H91"/>
-    <mergeCell ref="E86:G86"/>
-    <mergeCell ref="D88:I88"/>
-    <mergeCell ref="H67:I67"/>
-    <mergeCell ref="G81:H81"/>
-    <mergeCell ref="D67:F67"/>
-    <mergeCell ref="F68:I68"/>
-    <mergeCell ref="D87:E87"/>
-    <mergeCell ref="G87:I87"/>
-    <mergeCell ref="D98:I98"/>
-    <mergeCell ref="D94:I94"/>
-    <mergeCell ref="H89:I89"/>
-    <mergeCell ref="D89:F89"/>
-    <mergeCell ref="D97:I97"/>
-    <mergeCell ref="C177:J177"/>
-    <mergeCell ref="D106:E106"/>
-    <mergeCell ref="D99:G99"/>
-    <mergeCell ref="G126:I126"/>
-    <mergeCell ref="F125:J125"/>
-    <mergeCell ref="D128:J128"/>
-    <mergeCell ref="D103:E103"/>
-    <mergeCell ref="D104:E104"/>
-    <mergeCell ref="D105:E105"/>
-    <mergeCell ref="G100:I100"/>
-    <mergeCell ref="B101:I101"/>
-    <mergeCell ref="F127:J127"/>
-    <mergeCell ref="D107:E107"/>
-    <mergeCell ref="F118:J118"/>
+    <mergeCell ref="D78:I78"/>
+    <mergeCell ref="G71:H71"/>
+    <mergeCell ref="D76:I76"/>
+    <mergeCell ref="D66:H66"/>
+    <mergeCell ref="D77:I77"/>
+    <mergeCell ref="D73:I73"/>
+    <mergeCell ref="D70:E70"/>
+    <mergeCell ref="D74:F74"/>
+    <mergeCell ref="D31:I31"/>
+    <mergeCell ref="G35:H35"/>
+    <mergeCell ref="D40:I40"/>
+    <mergeCell ref="D33:I33"/>
+    <mergeCell ref="D46:I46"/>
+    <mergeCell ref="D43:I43"/>
+    <mergeCell ref="D135:J135"/>
+    <mergeCell ref="D172:J172"/>
+    <mergeCell ref="G146:J146"/>
+    <mergeCell ref="D108:E108"/>
+    <mergeCell ref="B112:J113"/>
+    <mergeCell ref="G124:J124"/>
+    <mergeCell ref="D120:H120"/>
+    <mergeCell ref="G123:J123"/>
+    <mergeCell ref="D121:J121"/>
     <mergeCell ref="G152:I152"/>
     <mergeCell ref="D149:J150"/>
+    <mergeCell ref="D185:J185"/>
+    <mergeCell ref="C175:J176"/>
+    <mergeCell ref="D164:J164"/>
+    <mergeCell ref="D157:J157"/>
+    <mergeCell ref="D143:J143"/>
+    <mergeCell ref="C177:J177"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/attendance_sheet.xlsx
+++ b/attendance_sheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\repositary\3rd_Year_5th_Semester\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7125557-3EC2-4154-AFDE-6AF73401A3D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B709C9C8-0D5B-466E-BB72-D25D88277FF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4932" yWindow="3264" windowWidth="15000" windowHeight="7632" xr2:uid="{EB654061-A886-47D1-BF86-9B1A84FCE7FB}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{EB654061-A886-47D1-BF86-9B1A84FCE7FB}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="925" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="927" uniqueCount="75">
   <si>
     <t>Date</t>
   </si>
@@ -544,22 +544,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -580,13 +574,19 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
@@ -993,14 +993,14 @@
       <c r="C8" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D8" s="37" t="s">
+      <c r="D8" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="E8" s="37"/>
-      <c r="F8" s="37"/>
-      <c r="G8" s="37"/>
-      <c r="H8" s="37"/>
-      <c r="I8" s="37"/>
+      <c r="E8" s="26"/>
+      <c r="F8" s="26"/>
+      <c r="G8" s="26"/>
+      <c r="H8" s="26"/>
+      <c r="I8" s="26"/>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B9" s="4">
@@ -1009,14 +1009,14 @@
       <c r="C9" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D9" s="37" t="s">
+      <c r="D9" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="E9" s="37"/>
-      <c r="F9" s="37"/>
-      <c r="G9" s="37"/>
-      <c r="H9" s="37"/>
-      <c r="I9" s="37"/>
+      <c r="E9" s="26"/>
+      <c r="F9" s="26"/>
+      <c r="G9" s="26"/>
+      <c r="H9" s="26"/>
+      <c r="I9" s="26"/>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B10" s="4">
@@ -1025,14 +1025,14 @@
       <c r="C10" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D10" s="37" t="s">
+      <c r="D10" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="E10" s="37"/>
-      <c r="F10" s="37"/>
-      <c r="G10" s="37"/>
-      <c r="H10" s="37"/>
-      <c r="I10" s="37"/>
+      <c r="E10" s="26"/>
+      <c r="F10" s="26"/>
+      <c r="G10" s="26"/>
+      <c r="H10" s="26"/>
+      <c r="I10" s="26"/>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B11" s="4">
@@ -1041,14 +1041,14 @@
       <c r="C11" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D11" s="37" t="s">
+      <c r="D11" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="E11" s="37"/>
-      <c r="F11" s="37"/>
-      <c r="G11" s="37"/>
-      <c r="H11" s="37"/>
-      <c r="I11" s="37"/>
+      <c r="E11" s="26"/>
+      <c r="F11" s="26"/>
+      <c r="G11" s="26"/>
+      <c r="H11" s="26"/>
+      <c r="I11" s="26"/>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B12" s="4">
@@ -1092,10 +1092,10 @@
       <c r="F13" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="G13" s="37" t="s">
+      <c r="G13" s="26" t="s">
         <v>18</v>
       </c>
-      <c r="H13" s="37"/>
+      <c r="H13" s="26"/>
       <c r="I13" s="1" t="s">
         <v>14</v>
       </c>
@@ -1107,14 +1107,14 @@
       <c r="C14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D14" s="37" t="s">
+      <c r="D14" s="26" t="s">
         <v>19</v>
       </c>
-      <c r="E14" s="37"/>
-      <c r="F14" s="37"/>
-      <c r="G14" s="37"/>
-      <c r="H14" s="37"/>
-      <c r="I14" s="37"/>
+      <c r="E14" s="26"/>
+      <c r="F14" s="26"/>
+      <c r="G14" s="26"/>
+      <c r="H14" s="26"/>
+      <c r="I14" s="26"/>
     </row>
     <row r="15" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B15" s="4">
@@ -1201,14 +1201,14 @@
       <c r="C18" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D18" s="37" t="s">
+      <c r="D18" s="26" t="s">
         <v>23</v>
       </c>
-      <c r="E18" s="37"/>
-      <c r="F18" s="37"/>
-      <c r="G18" s="37"/>
-      <c r="H18" s="37"/>
-      <c r="I18" s="37"/>
+      <c r="E18" s="26"/>
+      <c r="F18" s="26"/>
+      <c r="G18" s="26"/>
+      <c r="H18" s="26"/>
+      <c r="I18" s="26"/>
     </row>
     <row r="19" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B19" s="4">
@@ -1217,14 +1217,14 @@
       <c r="C19" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D19" s="37" t="s">
+      <c r="D19" s="26" t="s">
         <v>23</v>
       </c>
-      <c r="E19" s="37"/>
-      <c r="F19" s="37"/>
-      <c r="G19" s="37"/>
-      <c r="H19" s="37"/>
-      <c r="I19" s="37"/>
+      <c r="E19" s="26"/>
+      <c r="F19" s="26"/>
+      <c r="G19" s="26"/>
+      <c r="H19" s="26"/>
+      <c r="I19" s="26"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B20" s="4">
@@ -1242,10 +1242,10 @@
       <c r="F20" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G20" s="37" t="s">
+      <c r="G20" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="H20" s="37"/>
+      <c r="H20" s="26"/>
       <c r="I20" s="1" t="s">
         <v>14</v>
       </c>
@@ -1361,14 +1361,14 @@
       <c r="C25" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D25" s="37" t="s">
+      <c r="D25" s="26" t="s">
         <v>26</v>
       </c>
-      <c r="E25" s="37"/>
-      <c r="F25" s="37"/>
-      <c r="G25" s="37"/>
-      <c r="H25" s="37"/>
-      <c r="I25" s="37"/>
+      <c r="E25" s="26"/>
+      <c r="F25" s="26"/>
+      <c r="G25" s="26"/>
+      <c r="H25" s="26"/>
+      <c r="I25" s="26"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B26" s="4">
@@ -1412,10 +1412,10 @@
       <c r="F27" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G27" s="37" t="s">
+      <c r="G27" s="26" t="s">
         <v>18</v>
       </c>
-      <c r="H27" s="37"/>
+      <c r="H27" s="26"/>
       <c r="I27" s="1" t="s">
         <v>14</v>
       </c>
@@ -1479,14 +1479,14 @@
       <c r="C30" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D30" s="36" t="s">
+      <c r="D30" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="E30" s="36"/>
-      <c r="F30" s="36"/>
-      <c r="G30" s="36"/>
-      <c r="H30" s="36"/>
-      <c r="I30" s="36"/>
+      <c r="E30" s="27"/>
+      <c r="F30" s="27"/>
+      <c r="G30" s="27"/>
+      <c r="H30" s="27"/>
+      <c r="I30" s="27"/>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B31" s="4">
@@ -1495,14 +1495,14 @@
       <c r="C31" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D31" s="36" t="s">
+      <c r="D31" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="E31" s="36"/>
-      <c r="F31" s="36"/>
-      <c r="G31" s="36"/>
-      <c r="H31" s="36"/>
-      <c r="I31" s="36"/>
+      <c r="E31" s="27"/>
+      <c r="F31" s="27"/>
+      <c r="G31" s="27"/>
+      <c r="H31" s="27"/>
+      <c r="I31" s="27"/>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B32" s="4">
@@ -1537,14 +1537,14 @@
       <c r="C33" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D33" s="36" t="s">
+      <c r="D33" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="E33" s="36"/>
-      <c r="F33" s="36"/>
-      <c r="G33" s="36"/>
-      <c r="H33" s="36"/>
-      <c r="I33" s="36"/>
+      <c r="E33" s="27"/>
+      <c r="F33" s="27"/>
+      <c r="G33" s="27"/>
+      <c r="H33" s="27"/>
+      <c r="I33" s="27"/>
     </row>
     <row r="34" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B34" s="4">
@@ -1588,10 +1588,10 @@
       <c r="F35" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G35" s="36" t="s">
+      <c r="G35" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="H35" s="36"/>
+      <c r="H35" s="27"/>
       <c r="I35" s="1" t="s">
         <v>14</v>
       </c>
@@ -1707,14 +1707,14 @@
       <c r="C40" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D40" s="36" t="s">
+      <c r="D40" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="E40" s="36"/>
-      <c r="F40" s="36"/>
-      <c r="G40" s="36"/>
-      <c r="H40" s="36"/>
-      <c r="I40" s="36"/>
+      <c r="E40" s="27"/>
+      <c r="F40" s="27"/>
+      <c r="G40" s="27"/>
+      <c r="H40" s="27"/>
+      <c r="I40" s="27"/>
     </row>
     <row r="41" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B41" s="4">
@@ -1758,10 +1758,10 @@
       <c r="F42" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G42" s="36" t="s">
+      <c r="G42" s="27" t="s">
         <v>28</v>
       </c>
-      <c r="H42" s="36"/>
+      <c r="H42" s="27"/>
       <c r="I42" s="1" t="s">
         <v>15</v>
       </c>
@@ -1773,14 +1773,14 @@
       <c r="C43" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D43" s="36" t="s">
+      <c r="D43" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="E43" s="36"/>
-      <c r="F43" s="36"/>
-      <c r="G43" s="36"/>
-      <c r="H43" s="36"/>
-      <c r="I43" s="36"/>
+      <c r="E43" s="27"/>
+      <c r="F43" s="27"/>
+      <c r="G43" s="27"/>
+      <c r="H43" s="27"/>
+      <c r="I43" s="27"/>
     </row>
     <row r="44" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B44" s="4">
@@ -1844,14 +1844,14 @@
       <c r="C46" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D46" s="36" t="s">
+      <c r="D46" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="E46" s="36"/>
-      <c r="F46" s="36"/>
-      <c r="G46" s="36"/>
-      <c r="H46" s="36"/>
-      <c r="I46" s="36"/>
+      <c r="E46" s="27"/>
+      <c r="F46" s="27"/>
+      <c r="G46" s="27"/>
+      <c r="H46" s="27"/>
+      <c r="I46" s="27"/>
     </row>
     <row r="47" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B47" s="4">
@@ -1863,11 +1863,11 @@
       <c r="D47" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E47" s="24"/>
-      <c r="F47" s="24"/>
-      <c r="G47" s="24"/>
-      <c r="H47" s="24"/>
-      <c r="I47" s="25"/>
+      <c r="E47" s="25"/>
+      <c r="F47" s="25"/>
+      <c r="G47" s="25"/>
+      <c r="H47" s="25"/>
+      <c r="I47" s="24"/>
     </row>
     <row r="48" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B48" s="4">
@@ -1914,7 +1914,7 @@
       <c r="G49" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="H49" s="25"/>
+      <c r="H49" s="24"/>
       <c r="I49" s="1" t="s">
         <v>30</v>
       </c>
@@ -2056,14 +2056,14 @@
       <c r="C55" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="D55" s="24" t="s">
+      <c r="D55" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="E55" s="24"/>
-      <c r="F55" s="24"/>
-      <c r="G55" s="24"/>
-      <c r="H55" s="24"/>
-      <c r="I55" s="24"/>
+      <c r="E55" s="25"/>
+      <c r="F55" s="25"/>
+      <c r="G55" s="25"/>
+      <c r="H55" s="25"/>
+      <c r="I55" s="25"/>
     </row>
     <row r="56" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B56" s="4">
@@ -2110,7 +2110,7 @@
       <c r="G57" s="23" t="s">
         <v>37</v>
       </c>
-      <c r="H57" s="25"/>
+      <c r="H57" s="24"/>
       <c r="I57" s="1" t="s">
         <v>36</v>
       </c>
@@ -2177,11 +2177,11 @@
       <c r="D60" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E60" s="24"/>
-      <c r="F60" s="24"/>
-      <c r="G60" s="24"/>
-      <c r="H60" s="24"/>
-      <c r="I60" s="25"/>
+      <c r="E60" s="25"/>
+      <c r="F60" s="25"/>
+      <c r="G60" s="25"/>
+      <c r="H60" s="25"/>
+      <c r="I60" s="24"/>
     </row>
     <row r="61" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B61" s="4">
@@ -2193,11 +2193,11 @@
       <c r="D61" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E61" s="24"/>
-      <c r="F61" s="24"/>
-      <c r="G61" s="24"/>
-      <c r="H61" s="24"/>
-      <c r="I61" s="25"/>
+      <c r="E61" s="25"/>
+      <c r="F61" s="25"/>
+      <c r="G61" s="25"/>
+      <c r="H61" s="25"/>
+      <c r="I61" s="24"/>
     </row>
     <row r="62" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B62" s="4">
@@ -2209,11 +2209,11 @@
       <c r="D62" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E62" s="24"/>
-      <c r="F62" s="24"/>
-      <c r="G62" s="24"/>
-      <c r="H62" s="24"/>
-      <c r="I62" s="25"/>
+      <c r="E62" s="25"/>
+      <c r="F62" s="25"/>
+      <c r="G62" s="25"/>
+      <c r="H62" s="25"/>
+      <c r="I62" s="24"/>
     </row>
     <row r="63" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B63" s="4">
@@ -2260,7 +2260,7 @@
       <c r="G64" s="23" t="s">
         <v>37</v>
       </c>
-      <c r="H64" s="25"/>
+      <c r="H64" s="24"/>
       <c r="I64" s="1" t="s">
         <v>14</v>
       </c>
@@ -2301,10 +2301,10 @@
       <c r="D66" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="E66" s="24"/>
-      <c r="F66" s="24"/>
-      <c r="G66" s="24"/>
-      <c r="H66" s="25"/>
+      <c r="E66" s="25"/>
+      <c r="F66" s="25"/>
+      <c r="G66" s="25"/>
+      <c r="H66" s="24"/>
       <c r="I66" s="1" t="s">
         <v>16</v>
       </c>
@@ -2319,15 +2319,15 @@
       <c r="D67" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="E67" s="24"/>
-      <c r="F67" s="25"/>
+      <c r="E67" s="25"/>
+      <c r="F67" s="24"/>
       <c r="G67" s="3" t="s">
         <v>16</v>
       </c>
       <c r="H67" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="I67" s="25"/>
+      <c r="I67" s="24"/>
     </row>
     <row r="68" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B68" s="4">
@@ -2345,9 +2345,9 @@
       <c r="F68" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="G68" s="24"/>
-      <c r="H68" s="24"/>
-      <c r="I68" s="25"/>
+      <c r="G68" s="25"/>
+      <c r="H68" s="25"/>
+      <c r="I68" s="24"/>
     </row>
     <row r="69" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B69" s="4">
@@ -2359,11 +2359,11 @@
       <c r="D69" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E69" s="24"/>
-      <c r="F69" s="24"/>
-      <c r="G69" s="24"/>
-      <c r="H69" s="24"/>
-      <c r="I69" s="25"/>
+      <c r="E69" s="25"/>
+      <c r="F69" s="25"/>
+      <c r="G69" s="25"/>
+      <c r="H69" s="25"/>
+      <c r="I69" s="24"/>
     </row>
     <row r="70" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B70" s="4">
@@ -2375,7 +2375,7 @@
       <c r="D70" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="E70" s="25"/>
+      <c r="E70" s="24"/>
       <c r="F70" s="3" t="s">
         <v>15</v>
       </c>
@@ -2408,7 +2408,7 @@
       <c r="G71" s="23" t="s">
         <v>37</v>
       </c>
-      <c r="H71" s="25"/>
+      <c r="H71" s="24"/>
       <c r="I71" s="1" t="s">
         <v>14</v>
       </c>
@@ -2449,11 +2449,11 @@
       <c r="D73" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E73" s="24"/>
-      <c r="F73" s="24"/>
-      <c r="G73" s="24"/>
-      <c r="H73" s="24"/>
-      <c r="I73" s="25"/>
+      <c r="E73" s="25"/>
+      <c r="F73" s="25"/>
+      <c r="G73" s="25"/>
+      <c r="H73" s="25"/>
+      <c r="I73" s="24"/>
     </row>
     <row r="74" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B74" s="4">
@@ -2465,8 +2465,8 @@
       <c r="D74" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="E74" s="24"/>
-      <c r="F74" s="25"/>
+      <c r="E74" s="25"/>
+      <c r="F74" s="24"/>
       <c r="G74" s="3" t="s">
         <v>16</v>
       </c>
@@ -2505,11 +2505,11 @@
       <c r="D76" s="23" t="s">
         <v>39</v>
       </c>
-      <c r="E76" s="24"/>
-      <c r="F76" s="24"/>
-      <c r="G76" s="24"/>
-      <c r="H76" s="24"/>
-      <c r="I76" s="25"/>
+      <c r="E76" s="25"/>
+      <c r="F76" s="25"/>
+      <c r="G76" s="25"/>
+      <c r="H76" s="25"/>
+      <c r="I76" s="24"/>
     </row>
     <row r="77" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B77" s="4">
@@ -2521,11 +2521,11 @@
       <c r="D77" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E77" s="24"/>
-      <c r="F77" s="24"/>
-      <c r="G77" s="24"/>
-      <c r="H77" s="24"/>
-      <c r="I77" s="25"/>
+      <c r="E77" s="25"/>
+      <c r="F77" s="25"/>
+      <c r="G77" s="25"/>
+      <c r="H77" s="25"/>
+      <c r="I77" s="24"/>
     </row>
     <row r="78" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B78" s="4">
@@ -2537,11 +2537,11 @@
       <c r="D78" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E78" s="24"/>
-      <c r="F78" s="24"/>
-      <c r="G78" s="24"/>
-      <c r="H78" s="24"/>
-      <c r="I78" s="25"/>
+      <c r="E78" s="25"/>
+      <c r="F78" s="25"/>
+      <c r="G78" s="25"/>
+      <c r="H78" s="25"/>
+      <c r="I78" s="24"/>
     </row>
     <row r="79" spans="2:9" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B79" s="16" t="s">
@@ -2588,7 +2588,7 @@
       <c r="G80" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="H80" s="25"/>
+      <c r="H80" s="24"/>
       <c r="I80" s="1" t="s">
         <v>14</v>
       </c>
@@ -2612,7 +2612,7 @@
       <c r="G81" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="H81" s="25"/>
+      <c r="H81" s="24"/>
       <c r="I81" s="1" t="s">
         <v>16</v>
       </c>
@@ -2679,11 +2679,11 @@
       <c r="D84" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E84" s="24"/>
-      <c r="F84" s="24"/>
-      <c r="G84" s="24"/>
-      <c r="H84" s="24"/>
-      <c r="I84" s="25"/>
+      <c r="E84" s="25"/>
+      <c r="F84" s="25"/>
+      <c r="G84" s="25"/>
+      <c r="H84" s="25"/>
+      <c r="I84" s="24"/>
     </row>
     <row r="85" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B85" s="4">
@@ -2724,8 +2724,8 @@
       <c r="E86" s="23" t="s">
         <v>43</v>
       </c>
-      <c r="F86" s="24"/>
-      <c r="G86" s="25"/>
+      <c r="F86" s="25"/>
+      <c r="G86" s="24"/>
       <c r="H86" s="3" t="s">
         <v>14</v>
       </c>
@@ -2743,15 +2743,15 @@
       <c r="D87" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="E87" s="25"/>
+      <c r="E87" s="24"/>
       <c r="F87" s="3" t="s">
         <v>16</v>
       </c>
       <c r="G87" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="H87" s="24"/>
-      <c r="I87" s="25"/>
+      <c r="H87" s="25"/>
+      <c r="I87" s="24"/>
     </row>
     <row r="88" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B88" s="4">
@@ -2763,11 +2763,11 @@
       <c r="D88" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E88" s="24"/>
-      <c r="F88" s="24"/>
-      <c r="G88" s="24"/>
-      <c r="H88" s="24"/>
-      <c r="I88" s="25"/>
+      <c r="E88" s="25"/>
+      <c r="F88" s="25"/>
+      <c r="G88" s="25"/>
+      <c r="H88" s="25"/>
+      <c r="I88" s="24"/>
     </row>
     <row r="89" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B89" s="4">
@@ -2779,15 +2779,15 @@
       <c r="D89" s="23" t="s">
         <v>44</v>
       </c>
-      <c r="E89" s="24"/>
-      <c r="F89" s="25"/>
+      <c r="E89" s="25"/>
+      <c r="F89" s="24"/>
       <c r="G89" s="3" t="s">
         <v>16</v>
       </c>
       <c r="H89" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="I89" s="25"/>
+      <c r="I89" s="24"/>
     </row>
     <row r="90" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B90" s="4">
@@ -2799,7 +2799,7 @@
       <c r="D90" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="E90" s="25"/>
+      <c r="E90" s="24"/>
       <c r="F90" s="3" t="s">
         <v>16</v>
       </c>
@@ -2824,10 +2824,10 @@
       <c r="D91" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E91" s="24"/>
-      <c r="F91" s="24"/>
-      <c r="G91" s="24"/>
-      <c r="H91" s="25"/>
+      <c r="E91" s="25"/>
+      <c r="F91" s="25"/>
+      <c r="G91" s="25"/>
+      <c r="H91" s="24"/>
       <c r="I91" s="18" t="s">
         <v>45</v>
       </c>
@@ -2842,11 +2842,11 @@
       <c r="D92" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E92" s="24"/>
-      <c r="F92" s="24"/>
-      <c r="G92" s="24"/>
-      <c r="H92" s="24"/>
-      <c r="I92" s="25"/>
+      <c r="E92" s="25"/>
+      <c r="F92" s="25"/>
+      <c r="G92" s="25"/>
+      <c r="H92" s="25"/>
+      <c r="I92" s="24"/>
     </row>
     <row r="93" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B93" s="4">
@@ -2858,11 +2858,11 @@
       <c r="D93" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="E93" s="24"/>
-      <c r="F93" s="24"/>
-      <c r="G93" s="24"/>
-      <c r="H93" s="24"/>
-      <c r="I93" s="25"/>
+      <c r="E93" s="25"/>
+      <c r="F93" s="25"/>
+      <c r="G93" s="25"/>
+      <c r="H93" s="25"/>
+      <c r="I93" s="24"/>
     </row>
     <row r="94" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B94" s="4">
@@ -2874,11 +2874,11 @@
       <c r="D94" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="E94" s="24"/>
-      <c r="F94" s="24"/>
-      <c r="G94" s="24"/>
-      <c r="H94" s="24"/>
-      <c r="I94" s="25"/>
+      <c r="E94" s="25"/>
+      <c r="F94" s="25"/>
+      <c r="G94" s="25"/>
+      <c r="H94" s="25"/>
+      <c r="I94" s="24"/>
     </row>
     <row r="95" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B95" s="4">
@@ -2890,12 +2890,12 @@
       <c r="D95" s="23" t="s">
         <v>47</v>
       </c>
-      <c r="E95" s="24"/>
-      <c r="F95" s="25"/>
+      <c r="E95" s="25"/>
+      <c r="F95" s="24"/>
       <c r="G95" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="H95" s="25"/>
+      <c r="H95" s="24"/>
       <c r="I95" s="1" t="s">
         <v>14</v>
       </c>
@@ -2910,11 +2910,11 @@
       <c r="D96" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E96" s="24"/>
-      <c r="F96" s="24"/>
-      <c r="G96" s="24"/>
-      <c r="H96" s="24"/>
-      <c r="I96" s="25"/>
+      <c r="E96" s="25"/>
+      <c r="F96" s="25"/>
+      <c r="G96" s="25"/>
+      <c r="H96" s="25"/>
+      <c r="I96" s="24"/>
     </row>
     <row r="97" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B97" s="4">
@@ -2926,11 +2926,11 @@
       <c r="D97" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="E97" s="24"/>
-      <c r="F97" s="24"/>
-      <c r="G97" s="24"/>
-      <c r="H97" s="24"/>
-      <c r="I97" s="25"/>
+      <c r="E97" s="25"/>
+      <c r="F97" s="25"/>
+      <c r="G97" s="25"/>
+      <c r="H97" s="25"/>
+      <c r="I97" s="24"/>
     </row>
     <row r="98" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B98" s="4">
@@ -2942,11 +2942,11 @@
       <c r="D98" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E98" s="24"/>
-      <c r="F98" s="24"/>
-      <c r="G98" s="24"/>
-      <c r="H98" s="24"/>
-      <c r="I98" s="25"/>
+      <c r="E98" s="25"/>
+      <c r="F98" s="25"/>
+      <c r="G98" s="25"/>
+      <c r="H98" s="25"/>
+      <c r="I98" s="24"/>
     </row>
     <row r="99" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B99" s="4">
@@ -2958,9 +2958,9 @@
       <c r="D99" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="E99" s="24"/>
-      <c r="F99" s="24"/>
-      <c r="G99" s="25"/>
+      <c r="E99" s="25"/>
+      <c r="F99" s="25"/>
+      <c r="G99" s="24"/>
       <c r="H99" s="3" t="s">
         <v>49</v>
       </c>
@@ -2987,18 +2987,18 @@
       <c r="G100" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="H100" s="24"/>
-      <c r="I100" s="25"/>
+      <c r="H100" s="25"/>
+      <c r="I100" s="24"/>
     </row>
     <row r="101" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B101" s="23"/>
-      <c r="C101" s="24"/>
-      <c r="D101" s="24"/>
-      <c r="E101" s="24"/>
-      <c r="F101" s="24"/>
-      <c r="G101" s="24"/>
-      <c r="H101" s="24"/>
-      <c r="I101" s="25"/>
+      <c r="C101" s="25"/>
+      <c r="D101" s="25"/>
+      <c r="E101" s="25"/>
+      <c r="F101" s="25"/>
+      <c r="G101" s="25"/>
+      <c r="H101" s="25"/>
+      <c r="I101" s="24"/>
     </row>
     <row r="102" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B102" s="3"/>
@@ -3020,7 +3020,7 @@
       <c r="D103" s="23" t="s">
         <v>51</v>
       </c>
-      <c r="E103" s="25"/>
+      <c r="E103" s="24"/>
       <c r="F103" s="3"/>
       <c r="G103" s="3"/>
       <c r="H103" s="3"/>
@@ -3036,7 +3036,7 @@
       <c r="D104" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="E104" s="25"/>
+      <c r="E104" s="24"/>
       <c r="F104" s="3"/>
       <c r="G104" s="3"/>
       <c r="H104" s="3"/>
@@ -3052,7 +3052,7 @@
       <c r="D105" s="23" t="s">
         <v>53</v>
       </c>
-      <c r="E105" s="25"/>
+      <c r="E105" s="24"/>
       <c r="F105" s="3"/>
       <c r="G105" s="3"/>
       <c r="H105" s="3"/>
@@ -3068,7 +3068,7 @@
       <c r="D106" s="23" t="s">
         <v>54</v>
       </c>
-      <c r="E106" s="25"/>
+      <c r="E106" s="24"/>
       <c r="F106" s="3"/>
       <c r="G106" s="3"/>
       <c r="H106" s="3"/>
@@ -3084,7 +3084,7 @@
       <c r="D107" s="23" t="s">
         <v>55</v>
       </c>
-      <c r="E107" s="25"/>
+      <c r="E107" s="24"/>
       <c r="F107" s="3"/>
       <c r="G107" s="3"/>
       <c r="H107" s="3"/>
@@ -3100,7 +3100,7 @@
       <c r="D108" s="23" t="s">
         <v>56</v>
       </c>
-      <c r="E108" s="25"/>
+      <c r="E108" s="24"/>
       <c r="F108" s="3"/>
       <c r="G108" s="3"/>
       <c r="H108" s="3"/>
@@ -3137,28 +3137,28 @@
       <c r="I111" s="20"/>
     </row>
     <row r="112" spans="2:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B112" s="30" t="s">
+      <c r="B112" s="28" t="s">
         <v>57</v>
       </c>
-      <c r="C112" s="31"/>
-      <c r="D112" s="31"/>
-      <c r="E112" s="31"/>
-      <c r="F112" s="31"/>
-      <c r="G112" s="31"/>
-      <c r="H112" s="31"/>
-      <c r="I112" s="31"/>
-      <c r="J112" s="32"/>
+      <c r="C112" s="29"/>
+      <c r="D112" s="29"/>
+      <c r="E112" s="29"/>
+      <c r="F112" s="29"/>
+      <c r="G112" s="29"/>
+      <c r="H112" s="29"/>
+      <c r="I112" s="29"/>
+      <c r="J112" s="30"/>
     </row>
     <row r="113" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B113" s="33"/>
-      <c r="C113" s="34"/>
-      <c r="D113" s="34"/>
-      <c r="E113" s="34"/>
-      <c r="F113" s="34"/>
-      <c r="G113" s="34"/>
-      <c r="H113" s="34"/>
-      <c r="I113" s="34"/>
-      <c r="J113" s="35"/>
+      <c r="B113" s="31"/>
+      <c r="C113" s="32"/>
+      <c r="D113" s="32"/>
+      <c r="E113" s="32"/>
+      <c r="F113" s="32"/>
+      <c r="G113" s="32"/>
+      <c r="H113" s="32"/>
+      <c r="I113" s="32"/>
+      <c r="J113" s="33"/>
     </row>
     <row r="114" spans="2:10" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B114" s="8" t="s">
@@ -3292,10 +3292,10 @@
       <c r="F118" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="G118" s="24"/>
-      <c r="H118" s="24"/>
-      <c r="I118" s="24"/>
-      <c r="J118" s="25"/>
+      <c r="G118" s="25"/>
+      <c r="H118" s="25"/>
+      <c r="I118" s="25"/>
+      <c r="J118" s="24"/>
     </row>
     <row r="119" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B119" s="4">
@@ -3336,10 +3336,10 @@
       <c r="D120" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="E120" s="24"/>
-      <c r="F120" s="24"/>
-      <c r="G120" s="24"/>
-      <c r="H120" s="25"/>
+      <c r="E120" s="25"/>
+      <c r="F120" s="25"/>
+      <c r="G120" s="25"/>
+      <c r="H120" s="24"/>
       <c r="I120" s="1" t="s">
         <v>16</v>
       </c>
@@ -3357,12 +3357,12 @@
       <c r="D121" s="23" t="s">
         <v>65</v>
       </c>
-      <c r="E121" s="24"/>
-      <c r="F121" s="24"/>
-      <c r="G121" s="24"/>
-      <c r="H121" s="24"/>
-      <c r="I121" s="24"/>
-      <c r="J121" s="25"/>
+      <c r="E121" s="25"/>
+      <c r="F121" s="25"/>
+      <c r="G121" s="25"/>
+      <c r="H121" s="25"/>
+      <c r="I121" s="25"/>
+      <c r="J121" s="24"/>
     </row>
     <row r="122" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B122" s="4">
@@ -3412,9 +3412,9 @@
       <c r="G123" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="H123" s="24"/>
-      <c r="I123" s="24"/>
-      <c r="J123" s="25"/>
+      <c r="H123" s="25"/>
+      <c r="I123" s="25"/>
+      <c r="J123" s="24"/>
     </row>
     <row r="124" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B124" s="4">
@@ -3435,9 +3435,9 @@
       <c r="G124" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="H124" s="24"/>
-      <c r="I124" s="24"/>
-      <c r="J124" s="25"/>
+      <c r="H124" s="25"/>
+      <c r="I124" s="25"/>
+      <c r="J124" s="24"/>
     </row>
     <row r="125" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B125" s="4">
@@ -3455,10 +3455,10 @@
       <c r="F125" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="G125" s="24"/>
-      <c r="H125" s="24"/>
-      <c r="I125" s="24"/>
-      <c r="J125" s="25"/>
+      <c r="G125" s="25"/>
+      <c r="H125" s="25"/>
+      <c r="I125" s="25"/>
+      <c r="J125" s="24"/>
     </row>
     <row r="126" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B126" s="4">
@@ -3479,8 +3479,8 @@
       <c r="G126" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="H126" s="24"/>
-      <c r="I126" s="25"/>
+      <c r="H126" s="25"/>
+      <c r="I126" s="24"/>
       <c r="J126" s="1" t="s">
         <v>16</v>
       </c>
@@ -3501,10 +3501,10 @@
       <c r="F127" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="G127" s="24"/>
-      <c r="H127" s="24"/>
-      <c r="I127" s="24"/>
-      <c r="J127" s="25"/>
+      <c r="G127" s="25"/>
+      <c r="H127" s="25"/>
+      <c r="I127" s="25"/>
+      <c r="J127" s="24"/>
     </row>
     <row r="128" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B128" s="4">
@@ -3516,12 +3516,12 @@
       <c r="D128" s="23" t="s">
         <v>65</v>
       </c>
-      <c r="E128" s="24"/>
-      <c r="F128" s="24"/>
-      <c r="G128" s="24"/>
-      <c r="H128" s="24"/>
-      <c r="I128" s="24"/>
-      <c r="J128" s="25"/>
+      <c r="E128" s="25"/>
+      <c r="F128" s="25"/>
+      <c r="G128" s="25"/>
+      <c r="H128" s="25"/>
+      <c r="I128" s="25"/>
+      <c r="J128" s="24"/>
     </row>
     <row r="129" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B129" s="4">
@@ -3707,12 +3707,12 @@
       <c r="D135" s="23" t="s">
         <v>65</v>
       </c>
-      <c r="E135" s="24"/>
-      <c r="F135" s="24"/>
-      <c r="G135" s="24"/>
-      <c r="H135" s="24"/>
-      <c r="I135" s="24"/>
-      <c r="J135" s="25"/>
+      <c r="E135" s="25"/>
+      <c r="F135" s="25"/>
+      <c r="G135" s="25"/>
+      <c r="H135" s="25"/>
+      <c r="I135" s="25"/>
+      <c r="J135" s="24"/>
     </row>
     <row r="136" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B136" s="4">
@@ -3927,12 +3927,12 @@
       <c r="D143" s="23" t="s">
         <v>65</v>
       </c>
-      <c r="E143" s="24"/>
-      <c r="F143" s="24"/>
-      <c r="G143" s="24"/>
-      <c r="H143" s="24"/>
-      <c r="I143" s="24"/>
-      <c r="J143" s="25"/>
+      <c r="E143" s="25"/>
+      <c r="F143" s="25"/>
+      <c r="G143" s="25"/>
+      <c r="H143" s="25"/>
+      <c r="I143" s="25"/>
+      <c r="J143" s="24"/>
     </row>
     <row r="144" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B144" s="4">
@@ -4011,9 +4011,9 @@
       <c r="G146" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="H146" s="24"/>
-      <c r="I146" s="24"/>
-      <c r="J146" s="25"/>
+      <c r="H146" s="25"/>
+      <c r="I146" s="25"/>
+      <c r="J146" s="24"/>
     </row>
     <row r="147" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B147" s="4">
@@ -4080,15 +4080,15 @@
       <c r="C149" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D149" s="26" t="s">
+      <c r="D149" s="34" t="s">
         <v>20</v>
       </c>
-      <c r="E149" s="27"/>
-      <c r="F149" s="27"/>
-      <c r="G149" s="27"/>
-      <c r="H149" s="27"/>
-      <c r="I149" s="27"/>
-      <c r="J149" s="38"/>
+      <c r="E149" s="35"/>
+      <c r="F149" s="35"/>
+      <c r="G149" s="35"/>
+      <c r="H149" s="35"/>
+      <c r="I149" s="35"/>
+      <c r="J149" s="36"/>
     </row>
     <row r="150" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B150" s="4">
@@ -4097,12 +4097,12 @@
       <c r="C150" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D150" s="28"/>
-      <c r="E150" s="29"/>
-      <c r="F150" s="29"/>
-      <c r="G150" s="29"/>
-      <c r="H150" s="29"/>
-      <c r="I150" s="29"/>
+      <c r="D150" s="37"/>
+      <c r="E150" s="38"/>
+      <c r="F150" s="38"/>
+      <c r="G150" s="38"/>
+      <c r="H150" s="38"/>
+      <c r="I150" s="38"/>
       <c r="J150" s="39"/>
     </row>
     <row r="151" spans="2:10" x14ac:dyDescent="0.3">
@@ -4153,8 +4153,8 @@
       <c r="G152" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="H152" s="24"/>
-      <c r="I152" s="25"/>
+      <c r="H152" s="25"/>
+      <c r="I152" s="24"/>
       <c r="J152" s="1" t="s">
         <v>69</v>
       </c>
@@ -4285,12 +4285,12 @@
       <c r="D157" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E157" s="24"/>
-      <c r="F157" s="24"/>
-      <c r="G157" s="24"/>
-      <c r="H157" s="24"/>
-      <c r="I157" s="24"/>
-      <c r="J157" s="25"/>
+      <c r="E157" s="25"/>
+      <c r="F157" s="25"/>
+      <c r="G157" s="25"/>
+      <c r="H157" s="25"/>
+      <c r="I157" s="25"/>
+      <c r="J157" s="24"/>
     </row>
     <row r="158" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B158" s="4">
@@ -4474,12 +4474,12 @@
       <c r="D164" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E164" s="24"/>
-      <c r="F164" s="24"/>
-      <c r="G164" s="24"/>
-      <c r="H164" s="24"/>
-      <c r="I164" s="24"/>
-      <c r="J164" s="25"/>
+      <c r="E164" s="25"/>
+      <c r="F164" s="25"/>
+      <c r="G164" s="25"/>
+      <c r="H164" s="25"/>
+      <c r="I164" s="25"/>
+      <c r="J164" s="24"/>
     </row>
     <row r="165" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B165" s="4">
@@ -4680,12 +4680,12 @@
       <c r="D172" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E172" s="24"/>
-      <c r="F172" s="24"/>
-      <c r="G172" s="24"/>
-      <c r="H172" s="24"/>
-      <c r="I172" s="24"/>
-      <c r="J172" s="25"/>
+      <c r="E172" s="25"/>
+      <c r="F172" s="25"/>
+      <c r="G172" s="25"/>
+      <c r="H172" s="25"/>
+      <c r="I172" s="25"/>
+      <c r="J172" s="24"/>
     </row>
     <row r="173" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B173" s="4">
@@ -4749,29 +4749,29 @@
       <c r="B175" s="4">
         <v>45903</v>
       </c>
-      <c r="C175" s="26" t="s">
+      <c r="C175" s="34" t="s">
         <v>39</v>
       </c>
-      <c r="D175" s="27"/>
-      <c r="E175" s="27"/>
-      <c r="F175" s="27"/>
-      <c r="G175" s="27"/>
-      <c r="H175" s="27"/>
-      <c r="I175" s="27"/>
-      <c r="J175" s="27"/>
+      <c r="D175" s="35"/>
+      <c r="E175" s="35"/>
+      <c r="F175" s="35"/>
+      <c r="G175" s="35"/>
+      <c r="H175" s="35"/>
+      <c r="I175" s="35"/>
+      <c r="J175" s="35"/>
     </row>
     <row r="176" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B176" s="4">
         <v>45904</v>
       </c>
-      <c r="C176" s="28"/>
-      <c r="D176" s="29"/>
-      <c r="E176" s="29"/>
-      <c r="F176" s="29"/>
-      <c r="G176" s="29"/>
-      <c r="H176" s="29"/>
-      <c r="I176" s="29"/>
-      <c r="J176" s="29"/>
+      <c r="C176" s="37"/>
+      <c r="D176" s="38"/>
+      <c r="E176" s="38"/>
+      <c r="F176" s="38"/>
+      <c r="G176" s="38"/>
+      <c r="H176" s="38"/>
+      <c r="I176" s="38"/>
+      <c r="J176" s="38"/>
     </row>
     <row r="177" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B177" s="4">
@@ -4780,13 +4780,13 @@
       <c r="C177" s="23" t="s">
         <v>39</v>
       </c>
-      <c r="D177" s="24"/>
-      <c r="E177" s="24"/>
-      <c r="F177" s="24"/>
-      <c r="G177" s="24"/>
-      <c r="H177" s="24"/>
-      <c r="I177" s="24"/>
-      <c r="J177" s="25"/>
+      <c r="D177" s="25"/>
+      <c r="E177" s="25"/>
+      <c r="F177" s="25"/>
+      <c r="G177" s="25"/>
+      <c r="H177" s="25"/>
+      <c r="I177" s="25"/>
+      <c r="J177" s="24"/>
     </row>
     <row r="178" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B178" s="4">
@@ -4985,12 +4985,12 @@
       <c r="D185" s="23" t="s">
         <v>74</v>
       </c>
-      <c r="E185" s="24"/>
-      <c r="F185" s="24"/>
-      <c r="G185" s="24"/>
-      <c r="H185" s="24"/>
-      <c r="I185" s="24"/>
-      <c r="J185" s="25"/>
+      <c r="E185" s="25"/>
+      <c r="F185" s="25"/>
+      <c r="G185" s="25"/>
+      <c r="H185" s="25"/>
+      <c r="I185" s="25"/>
+      <c r="J185" s="24"/>
     </row>
     <row r="186" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B186" s="4">
@@ -5012,15 +5012,21 @@
       </c>
     </row>
     <row r="187" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B187" s="3"/>
-      <c r="C187" s="3"/>
-      <c r="D187" s="3"/>
-      <c r="E187" s="3"/>
-      <c r="F187" s="3"/>
-      <c r="G187" s="3"/>
-      <c r="H187" s="3"/>
-      <c r="I187" s="1"/>
-      <c r="J187" s="1"/>
+      <c r="B187" s="4">
+        <v>45926</v>
+      </c>
+      <c r="C187" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D187" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="E187" s="25"/>
+      <c r="F187" s="25"/>
+      <c r="G187" s="25"/>
+      <c r="H187" s="25"/>
+      <c r="I187" s="25"/>
+      <c r="J187" s="24"/>
     </row>
     <row r="188" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B188" s="3"/>
@@ -7542,25 +7548,62 @@
       <c r="J416" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="88">
-    <mergeCell ref="D106:E106"/>
-    <mergeCell ref="D99:G99"/>
-    <mergeCell ref="G126:I126"/>
-    <mergeCell ref="F125:J125"/>
-    <mergeCell ref="D128:J128"/>
-    <mergeCell ref="D103:E103"/>
-    <mergeCell ref="D104:E104"/>
-    <mergeCell ref="D105:E105"/>
-    <mergeCell ref="G100:I100"/>
-    <mergeCell ref="B101:I101"/>
-    <mergeCell ref="F127:J127"/>
-    <mergeCell ref="D107:E107"/>
-    <mergeCell ref="F118:J118"/>
-    <mergeCell ref="D98:I98"/>
-    <mergeCell ref="D94:I94"/>
-    <mergeCell ref="H89:I89"/>
-    <mergeCell ref="D89:F89"/>
-    <mergeCell ref="D97:I97"/>
+  <mergeCells count="89">
+    <mergeCell ref="D187:J187"/>
+    <mergeCell ref="D185:J185"/>
+    <mergeCell ref="C175:J176"/>
+    <mergeCell ref="D164:J164"/>
+    <mergeCell ref="D157:J157"/>
+    <mergeCell ref="D143:J143"/>
+    <mergeCell ref="C177:J177"/>
+    <mergeCell ref="D135:J135"/>
+    <mergeCell ref="D172:J172"/>
+    <mergeCell ref="G146:J146"/>
+    <mergeCell ref="D108:E108"/>
+    <mergeCell ref="B112:J113"/>
+    <mergeCell ref="G124:J124"/>
+    <mergeCell ref="D120:H120"/>
+    <mergeCell ref="G123:J123"/>
+    <mergeCell ref="D121:J121"/>
+    <mergeCell ref="G152:I152"/>
+    <mergeCell ref="D149:J150"/>
+    <mergeCell ref="D31:I31"/>
+    <mergeCell ref="G35:H35"/>
+    <mergeCell ref="D40:I40"/>
+    <mergeCell ref="D33:I33"/>
+    <mergeCell ref="D46:I46"/>
+    <mergeCell ref="D43:I43"/>
+    <mergeCell ref="D78:I78"/>
+    <mergeCell ref="G71:H71"/>
+    <mergeCell ref="D76:I76"/>
+    <mergeCell ref="D66:H66"/>
+    <mergeCell ref="D77:I77"/>
+    <mergeCell ref="D73:I73"/>
+    <mergeCell ref="D70:E70"/>
+    <mergeCell ref="D74:F74"/>
+    <mergeCell ref="D84:I84"/>
+    <mergeCell ref="D69:I69"/>
+    <mergeCell ref="D8:I8"/>
+    <mergeCell ref="D9:I9"/>
+    <mergeCell ref="D10:I10"/>
+    <mergeCell ref="D11:I11"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="D14:I14"/>
+    <mergeCell ref="G27:H27"/>
+    <mergeCell ref="D25:I25"/>
+    <mergeCell ref="G20:H20"/>
+    <mergeCell ref="D19:I19"/>
+    <mergeCell ref="D18:I18"/>
+    <mergeCell ref="D30:I30"/>
+    <mergeCell ref="G80:H80"/>
+    <mergeCell ref="G42:H42"/>
+    <mergeCell ref="D60:I60"/>
+    <mergeCell ref="D62:I62"/>
+    <mergeCell ref="D61:I61"/>
+    <mergeCell ref="G49:H49"/>
+    <mergeCell ref="D47:I47"/>
+    <mergeCell ref="D55:I55"/>
+    <mergeCell ref="G57:H57"/>
     <mergeCell ref="G64:H64"/>
     <mergeCell ref="D96:I96"/>
     <mergeCell ref="D95:F95"/>
@@ -7577,60 +7620,24 @@
     <mergeCell ref="F68:I68"/>
     <mergeCell ref="D87:E87"/>
     <mergeCell ref="G87:I87"/>
-    <mergeCell ref="D60:I60"/>
-    <mergeCell ref="D62:I62"/>
-    <mergeCell ref="D61:I61"/>
-    <mergeCell ref="G49:H49"/>
-    <mergeCell ref="D47:I47"/>
-    <mergeCell ref="D55:I55"/>
-    <mergeCell ref="G57:H57"/>
-    <mergeCell ref="D84:I84"/>
-    <mergeCell ref="D69:I69"/>
-    <mergeCell ref="D8:I8"/>
-    <mergeCell ref="D9:I9"/>
-    <mergeCell ref="D10:I10"/>
-    <mergeCell ref="D11:I11"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="D14:I14"/>
-    <mergeCell ref="G27:H27"/>
-    <mergeCell ref="D25:I25"/>
-    <mergeCell ref="G20:H20"/>
-    <mergeCell ref="D19:I19"/>
-    <mergeCell ref="D18:I18"/>
-    <mergeCell ref="D30:I30"/>
-    <mergeCell ref="G80:H80"/>
-    <mergeCell ref="G42:H42"/>
-    <mergeCell ref="D78:I78"/>
-    <mergeCell ref="G71:H71"/>
-    <mergeCell ref="D76:I76"/>
-    <mergeCell ref="D66:H66"/>
-    <mergeCell ref="D77:I77"/>
-    <mergeCell ref="D73:I73"/>
-    <mergeCell ref="D70:E70"/>
-    <mergeCell ref="D74:F74"/>
-    <mergeCell ref="D31:I31"/>
-    <mergeCell ref="G35:H35"/>
-    <mergeCell ref="D40:I40"/>
-    <mergeCell ref="D33:I33"/>
-    <mergeCell ref="D46:I46"/>
-    <mergeCell ref="D43:I43"/>
-    <mergeCell ref="D135:J135"/>
-    <mergeCell ref="D172:J172"/>
-    <mergeCell ref="G146:J146"/>
-    <mergeCell ref="D108:E108"/>
-    <mergeCell ref="B112:J113"/>
-    <mergeCell ref="G124:J124"/>
-    <mergeCell ref="D120:H120"/>
-    <mergeCell ref="G123:J123"/>
-    <mergeCell ref="D121:J121"/>
-    <mergeCell ref="G152:I152"/>
-    <mergeCell ref="D149:J150"/>
-    <mergeCell ref="D185:J185"/>
-    <mergeCell ref="C175:J176"/>
-    <mergeCell ref="D164:J164"/>
-    <mergeCell ref="D157:J157"/>
-    <mergeCell ref="D143:J143"/>
-    <mergeCell ref="C177:J177"/>
+    <mergeCell ref="D98:I98"/>
+    <mergeCell ref="D94:I94"/>
+    <mergeCell ref="H89:I89"/>
+    <mergeCell ref="D89:F89"/>
+    <mergeCell ref="D97:I97"/>
+    <mergeCell ref="D106:E106"/>
+    <mergeCell ref="D99:G99"/>
+    <mergeCell ref="G126:I126"/>
+    <mergeCell ref="F125:J125"/>
+    <mergeCell ref="D128:J128"/>
+    <mergeCell ref="D103:E103"/>
+    <mergeCell ref="D104:E104"/>
+    <mergeCell ref="D105:E105"/>
+    <mergeCell ref="G100:I100"/>
+    <mergeCell ref="B101:I101"/>
+    <mergeCell ref="F127:J127"/>
+    <mergeCell ref="D107:E107"/>
+    <mergeCell ref="F118:J118"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/attendance_sheet.xlsx
+++ b/attendance_sheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\repositary\3rd_Year_5th_Semester\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B709C9C8-0D5B-466E-BB72-D25D88277FF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9B974C0-062D-44B0-BA9B-0FCC12B28667}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{EB654061-A886-47D1-BF86-9B1A84FCE7FB}"/>
   </bookViews>
@@ -544,16 +544,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -574,23 +580,17 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -993,14 +993,14 @@
       <c r="C8" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D8" s="26" t="s">
+      <c r="D8" s="39" t="s">
         <v>20</v>
       </c>
-      <c r="E8" s="26"/>
-      <c r="F8" s="26"/>
-      <c r="G8" s="26"/>
-      <c r="H8" s="26"/>
-      <c r="I8" s="26"/>
+      <c r="E8" s="39"/>
+      <c r="F8" s="39"/>
+      <c r="G8" s="39"/>
+      <c r="H8" s="39"/>
+      <c r="I8" s="39"/>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B9" s="4">
@@ -1009,14 +1009,14 @@
       <c r="C9" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D9" s="26" t="s">
+      <c r="D9" s="39" t="s">
         <v>20</v>
       </c>
-      <c r="E9" s="26"/>
-      <c r="F9" s="26"/>
-      <c r="G9" s="26"/>
-      <c r="H9" s="26"/>
-      <c r="I9" s="26"/>
+      <c r="E9" s="39"/>
+      <c r="F9" s="39"/>
+      <c r="G9" s="39"/>
+      <c r="H9" s="39"/>
+      <c r="I9" s="39"/>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B10" s="4">
@@ -1025,14 +1025,14 @@
       <c r="C10" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D10" s="26" t="s">
+      <c r="D10" s="39" t="s">
         <v>20</v>
       </c>
-      <c r="E10" s="26"/>
-      <c r="F10" s="26"/>
-      <c r="G10" s="26"/>
-      <c r="H10" s="26"/>
-      <c r="I10" s="26"/>
+      <c r="E10" s="39"/>
+      <c r="F10" s="39"/>
+      <c r="G10" s="39"/>
+      <c r="H10" s="39"/>
+      <c r="I10" s="39"/>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B11" s="4">
@@ -1041,14 +1041,14 @@
       <c r="C11" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D11" s="26" t="s">
+      <c r="D11" s="39" t="s">
         <v>20</v>
       </c>
-      <c r="E11" s="26"/>
-      <c r="F11" s="26"/>
-      <c r="G11" s="26"/>
-      <c r="H11" s="26"/>
-      <c r="I11" s="26"/>
+      <c r="E11" s="39"/>
+      <c r="F11" s="39"/>
+      <c r="G11" s="39"/>
+      <c r="H11" s="39"/>
+      <c r="I11" s="39"/>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B12" s="4">
@@ -1092,10 +1092,10 @@
       <c r="F13" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="G13" s="26" t="s">
+      <c r="G13" s="39" t="s">
         <v>18</v>
       </c>
-      <c r="H13" s="26"/>
+      <c r="H13" s="39"/>
       <c r="I13" s="1" t="s">
         <v>14</v>
       </c>
@@ -1107,14 +1107,14 @@
       <c r="C14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D14" s="26" t="s">
+      <c r="D14" s="39" t="s">
         <v>19</v>
       </c>
-      <c r="E14" s="26"/>
-      <c r="F14" s="26"/>
-      <c r="G14" s="26"/>
-      <c r="H14" s="26"/>
-      <c r="I14" s="26"/>
+      <c r="E14" s="39"/>
+      <c r="F14" s="39"/>
+      <c r="G14" s="39"/>
+      <c r="H14" s="39"/>
+      <c r="I14" s="39"/>
     </row>
     <row r="15" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B15" s="4">
@@ -1201,14 +1201,14 @@
       <c r="C18" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D18" s="26" t="s">
+      <c r="D18" s="39" t="s">
         <v>23</v>
       </c>
-      <c r="E18" s="26"/>
-      <c r="F18" s="26"/>
-      <c r="G18" s="26"/>
-      <c r="H18" s="26"/>
-      <c r="I18" s="26"/>
+      <c r="E18" s="39"/>
+      <c r="F18" s="39"/>
+      <c r="G18" s="39"/>
+      <c r="H18" s="39"/>
+      <c r="I18" s="39"/>
     </row>
     <row r="19" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B19" s="4">
@@ -1217,14 +1217,14 @@
       <c r="C19" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D19" s="26" t="s">
+      <c r="D19" s="39" t="s">
         <v>23</v>
       </c>
-      <c r="E19" s="26"/>
-      <c r="F19" s="26"/>
-      <c r="G19" s="26"/>
-      <c r="H19" s="26"/>
-      <c r="I19" s="26"/>
+      <c r="E19" s="39"/>
+      <c r="F19" s="39"/>
+      <c r="G19" s="39"/>
+      <c r="H19" s="39"/>
+      <c r="I19" s="39"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B20" s="4">
@@ -1242,10 +1242,10 @@
       <c r="F20" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G20" s="26" t="s">
+      <c r="G20" s="39" t="s">
         <v>15</v>
       </c>
-      <c r="H20" s="26"/>
+      <c r="H20" s="39"/>
       <c r="I20" s="1" t="s">
         <v>14</v>
       </c>
@@ -1361,14 +1361,14 @@
       <c r="C25" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D25" s="26" t="s">
+      <c r="D25" s="39" t="s">
         <v>26</v>
       </c>
-      <c r="E25" s="26"/>
-      <c r="F25" s="26"/>
-      <c r="G25" s="26"/>
-      <c r="H25" s="26"/>
-      <c r="I25" s="26"/>
+      <c r="E25" s="39"/>
+      <c r="F25" s="39"/>
+      <c r="G25" s="39"/>
+      <c r="H25" s="39"/>
+      <c r="I25" s="39"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B26" s="4">
@@ -1412,10 +1412,10 @@
       <c r="F27" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G27" s="26" t="s">
+      <c r="G27" s="39" t="s">
         <v>18</v>
       </c>
-      <c r="H27" s="26"/>
+      <c r="H27" s="39"/>
       <c r="I27" s="1" t="s">
         <v>14</v>
       </c>
@@ -1479,14 +1479,14 @@
       <c r="C30" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D30" s="27" t="s">
+      <c r="D30" s="38" t="s">
         <v>20</v>
       </c>
-      <c r="E30" s="27"/>
-      <c r="F30" s="27"/>
-      <c r="G30" s="27"/>
-      <c r="H30" s="27"/>
-      <c r="I30" s="27"/>
+      <c r="E30" s="38"/>
+      <c r="F30" s="38"/>
+      <c r="G30" s="38"/>
+      <c r="H30" s="38"/>
+      <c r="I30" s="38"/>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B31" s="4">
@@ -1495,14 +1495,14 @@
       <c r="C31" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D31" s="27" t="s">
+      <c r="D31" s="38" t="s">
         <v>20</v>
       </c>
-      <c r="E31" s="27"/>
-      <c r="F31" s="27"/>
-      <c r="G31" s="27"/>
-      <c r="H31" s="27"/>
-      <c r="I31" s="27"/>
+      <c r="E31" s="38"/>
+      <c r="F31" s="38"/>
+      <c r="G31" s="38"/>
+      <c r="H31" s="38"/>
+      <c r="I31" s="38"/>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B32" s="4">
@@ -1537,14 +1537,14 @@
       <c r="C33" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D33" s="27" t="s">
+      <c r="D33" s="38" t="s">
         <v>20</v>
       </c>
-      <c r="E33" s="27"/>
-      <c r="F33" s="27"/>
-      <c r="G33" s="27"/>
-      <c r="H33" s="27"/>
-      <c r="I33" s="27"/>
+      <c r="E33" s="38"/>
+      <c r="F33" s="38"/>
+      <c r="G33" s="38"/>
+      <c r="H33" s="38"/>
+      <c r="I33" s="38"/>
     </row>
     <row r="34" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B34" s="4">
@@ -1588,10 +1588,10 @@
       <c r="F35" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G35" s="27" t="s">
+      <c r="G35" s="38" t="s">
         <v>18</v>
       </c>
-      <c r="H35" s="27"/>
+      <c r="H35" s="38"/>
       <c r="I35" s="1" t="s">
         <v>14</v>
       </c>
@@ -1707,14 +1707,14 @@
       <c r="C40" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D40" s="27" t="s">
+      <c r="D40" s="38" t="s">
         <v>20</v>
       </c>
-      <c r="E40" s="27"/>
-      <c r="F40" s="27"/>
-      <c r="G40" s="27"/>
-      <c r="H40" s="27"/>
-      <c r="I40" s="27"/>
+      <c r="E40" s="38"/>
+      <c r="F40" s="38"/>
+      <c r="G40" s="38"/>
+      <c r="H40" s="38"/>
+      <c r="I40" s="38"/>
     </row>
     <row r="41" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B41" s="4">
@@ -1758,10 +1758,10 @@
       <c r="F42" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G42" s="27" t="s">
+      <c r="G42" s="38" t="s">
         <v>28</v>
       </c>
-      <c r="H42" s="27"/>
+      <c r="H42" s="38"/>
       <c r="I42" s="1" t="s">
         <v>15</v>
       </c>
@@ -1773,14 +1773,14 @@
       <c r="C43" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D43" s="27" t="s">
+      <c r="D43" s="38" t="s">
         <v>20</v>
       </c>
-      <c r="E43" s="27"/>
-      <c r="F43" s="27"/>
-      <c r="G43" s="27"/>
-      <c r="H43" s="27"/>
-      <c r="I43" s="27"/>
+      <c r="E43" s="38"/>
+      <c r="F43" s="38"/>
+      <c r="G43" s="38"/>
+      <c r="H43" s="38"/>
+      <c r="I43" s="38"/>
     </row>
     <row r="44" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B44" s="4">
@@ -1844,14 +1844,14 @@
       <c r="C46" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D46" s="27" t="s">
+      <c r="D46" s="38" t="s">
         <v>20</v>
       </c>
-      <c r="E46" s="27"/>
-      <c r="F46" s="27"/>
-      <c r="G46" s="27"/>
-      <c r="H46" s="27"/>
-      <c r="I46" s="27"/>
+      <c r="E46" s="38"/>
+      <c r="F46" s="38"/>
+      <c r="G46" s="38"/>
+      <c r="H46" s="38"/>
+      <c r="I46" s="38"/>
     </row>
     <row r="47" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B47" s="4">
@@ -1863,11 +1863,11 @@
       <c r="D47" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E47" s="25"/>
-      <c r="F47" s="25"/>
-      <c r="G47" s="25"/>
-      <c r="H47" s="25"/>
-      <c r="I47" s="24"/>
+      <c r="E47" s="24"/>
+      <c r="F47" s="24"/>
+      <c r="G47" s="24"/>
+      <c r="H47" s="24"/>
+      <c r="I47" s="25"/>
     </row>
     <row r="48" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B48" s="4">
@@ -1914,7 +1914,7 @@
       <c r="G49" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="H49" s="24"/>
+      <c r="H49" s="25"/>
       <c r="I49" s="1" t="s">
         <v>30</v>
       </c>
@@ -2056,14 +2056,14 @@
       <c r="C55" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="D55" s="25" t="s">
+      <c r="D55" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="E55" s="25"/>
-      <c r="F55" s="25"/>
-      <c r="G55" s="25"/>
-      <c r="H55" s="25"/>
-      <c r="I55" s="25"/>
+      <c r="E55" s="24"/>
+      <c r="F55" s="24"/>
+      <c r="G55" s="24"/>
+      <c r="H55" s="24"/>
+      <c r="I55" s="24"/>
     </row>
     <row r="56" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B56" s="4">
@@ -2110,7 +2110,7 @@
       <c r="G57" s="23" t="s">
         <v>37</v>
       </c>
-      <c r="H57" s="24"/>
+      <c r="H57" s="25"/>
       <c r="I57" s="1" t="s">
         <v>36</v>
       </c>
@@ -2177,11 +2177,11 @@
       <c r="D60" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E60" s="25"/>
-      <c r="F60" s="25"/>
-      <c r="G60" s="25"/>
-      <c r="H60" s="25"/>
-      <c r="I60" s="24"/>
+      <c r="E60" s="24"/>
+      <c r="F60" s="24"/>
+      <c r="G60" s="24"/>
+      <c r="H60" s="24"/>
+      <c r="I60" s="25"/>
     </row>
     <row r="61" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B61" s="4">
@@ -2193,11 +2193,11 @@
       <c r="D61" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E61" s="25"/>
-      <c r="F61" s="25"/>
-      <c r="G61" s="25"/>
-      <c r="H61" s="25"/>
-      <c r="I61" s="24"/>
+      <c r="E61" s="24"/>
+      <c r="F61" s="24"/>
+      <c r="G61" s="24"/>
+      <c r="H61" s="24"/>
+      <c r="I61" s="25"/>
     </row>
     <row r="62" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B62" s="4">
@@ -2209,11 +2209,11 @@
       <c r="D62" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E62" s="25"/>
-      <c r="F62" s="25"/>
-      <c r="G62" s="25"/>
-      <c r="H62" s="25"/>
-      <c r="I62" s="24"/>
+      <c r="E62" s="24"/>
+      <c r="F62" s="24"/>
+      <c r="G62" s="24"/>
+      <c r="H62" s="24"/>
+      <c r="I62" s="25"/>
     </row>
     <row r="63" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B63" s="4">
@@ -2260,7 +2260,7 @@
       <c r="G64" s="23" t="s">
         <v>37</v>
       </c>
-      <c r="H64" s="24"/>
+      <c r="H64" s="25"/>
       <c r="I64" s="1" t="s">
         <v>14</v>
       </c>
@@ -2301,10 +2301,10 @@
       <c r="D66" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="E66" s="25"/>
-      <c r="F66" s="25"/>
-      <c r="G66" s="25"/>
-      <c r="H66" s="24"/>
+      <c r="E66" s="24"/>
+      <c r="F66" s="24"/>
+      <c r="G66" s="24"/>
+      <c r="H66" s="25"/>
       <c r="I66" s="1" t="s">
         <v>16</v>
       </c>
@@ -2319,15 +2319,15 @@
       <c r="D67" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="E67" s="25"/>
-      <c r="F67" s="24"/>
+      <c r="E67" s="24"/>
+      <c r="F67" s="25"/>
       <c r="G67" s="3" t="s">
         <v>16</v>
       </c>
       <c r="H67" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="I67" s="24"/>
+      <c r="I67" s="25"/>
     </row>
     <row r="68" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B68" s="4">
@@ -2345,9 +2345,9 @@
       <c r="F68" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="G68" s="25"/>
-      <c r="H68" s="25"/>
-      <c r="I68" s="24"/>
+      <c r="G68" s="24"/>
+      <c r="H68" s="24"/>
+      <c r="I68" s="25"/>
     </row>
     <row r="69" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B69" s="4">
@@ -2359,11 +2359,11 @@
       <c r="D69" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E69" s="25"/>
-      <c r="F69" s="25"/>
-      <c r="G69" s="25"/>
-      <c r="H69" s="25"/>
-      <c r="I69" s="24"/>
+      <c r="E69" s="24"/>
+      <c r="F69" s="24"/>
+      <c r="G69" s="24"/>
+      <c r="H69" s="24"/>
+      <c r="I69" s="25"/>
     </row>
     <row r="70" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B70" s="4">
@@ -2375,7 +2375,7 @@
       <c r="D70" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="E70" s="24"/>
+      <c r="E70" s="25"/>
       <c r="F70" s="3" t="s">
         <v>15</v>
       </c>
@@ -2408,7 +2408,7 @@
       <c r="G71" s="23" t="s">
         <v>37</v>
       </c>
-      <c r="H71" s="24"/>
+      <c r="H71" s="25"/>
       <c r="I71" s="1" t="s">
         <v>14</v>
       </c>
@@ -2449,11 +2449,11 @@
       <c r="D73" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E73" s="25"/>
-      <c r="F73" s="25"/>
-      <c r="G73" s="25"/>
-      <c r="H73" s="25"/>
-      <c r="I73" s="24"/>
+      <c r="E73" s="24"/>
+      <c r="F73" s="24"/>
+      <c r="G73" s="24"/>
+      <c r="H73" s="24"/>
+      <c r="I73" s="25"/>
     </row>
     <row r="74" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B74" s="4">
@@ -2465,8 +2465,8 @@
       <c r="D74" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="E74" s="25"/>
-      <c r="F74" s="24"/>
+      <c r="E74" s="24"/>
+      <c r="F74" s="25"/>
       <c r="G74" s="3" t="s">
         <v>16</v>
       </c>
@@ -2505,11 +2505,11 @@
       <c r="D76" s="23" t="s">
         <v>39</v>
       </c>
-      <c r="E76" s="25"/>
-      <c r="F76" s="25"/>
-      <c r="G76" s="25"/>
-      <c r="H76" s="25"/>
-      <c r="I76" s="24"/>
+      <c r="E76" s="24"/>
+      <c r="F76" s="24"/>
+      <c r="G76" s="24"/>
+      <c r="H76" s="24"/>
+      <c r="I76" s="25"/>
     </row>
     <row r="77" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B77" s="4">
@@ -2521,11 +2521,11 @@
       <c r="D77" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E77" s="25"/>
-      <c r="F77" s="25"/>
-      <c r="G77" s="25"/>
-      <c r="H77" s="25"/>
-      <c r="I77" s="24"/>
+      <c r="E77" s="24"/>
+      <c r="F77" s="24"/>
+      <c r="G77" s="24"/>
+      <c r="H77" s="24"/>
+      <c r="I77" s="25"/>
     </row>
     <row r="78" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B78" s="4">
@@ -2537,11 +2537,11 @@
       <c r="D78" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E78" s="25"/>
-      <c r="F78" s="25"/>
-      <c r="G78" s="25"/>
-      <c r="H78" s="25"/>
-      <c r="I78" s="24"/>
+      <c r="E78" s="24"/>
+      <c r="F78" s="24"/>
+      <c r="G78" s="24"/>
+      <c r="H78" s="24"/>
+      <c r="I78" s="25"/>
     </row>
     <row r="79" spans="2:9" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B79" s="16" t="s">
@@ -2588,7 +2588,7 @@
       <c r="G80" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="H80" s="24"/>
+      <c r="H80" s="25"/>
       <c r="I80" s="1" t="s">
         <v>14</v>
       </c>
@@ -2612,7 +2612,7 @@
       <c r="G81" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="H81" s="24"/>
+      <c r="H81" s="25"/>
       <c r="I81" s="1" t="s">
         <v>16</v>
       </c>
@@ -2679,11 +2679,11 @@
       <c r="D84" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E84" s="25"/>
-      <c r="F84" s="25"/>
-      <c r="G84" s="25"/>
-      <c r="H84" s="25"/>
-      <c r="I84" s="24"/>
+      <c r="E84" s="24"/>
+      <c r="F84" s="24"/>
+      <c r="G84" s="24"/>
+      <c r="H84" s="24"/>
+      <c r="I84" s="25"/>
     </row>
     <row r="85" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B85" s="4">
@@ -2724,8 +2724,8 @@
       <c r="E86" s="23" t="s">
         <v>43</v>
       </c>
-      <c r="F86" s="25"/>
-      <c r="G86" s="24"/>
+      <c r="F86" s="24"/>
+      <c r="G86" s="25"/>
       <c r="H86" s="3" t="s">
         <v>14</v>
       </c>
@@ -2743,15 +2743,15 @@
       <c r="D87" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="E87" s="24"/>
+      <c r="E87" s="25"/>
       <c r="F87" s="3" t="s">
         <v>16</v>
       </c>
       <c r="G87" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="H87" s="25"/>
-      <c r="I87" s="24"/>
+      <c r="H87" s="24"/>
+      <c r="I87" s="25"/>
     </row>
     <row r="88" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B88" s="4">
@@ -2763,11 +2763,11 @@
       <c r="D88" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E88" s="25"/>
-      <c r="F88" s="25"/>
-      <c r="G88" s="25"/>
-      <c r="H88" s="25"/>
-      <c r="I88" s="24"/>
+      <c r="E88" s="24"/>
+      <c r="F88" s="24"/>
+      <c r="G88" s="24"/>
+      <c r="H88" s="24"/>
+      <c r="I88" s="25"/>
     </row>
     <row r="89" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B89" s="4">
@@ -2779,15 +2779,15 @@
       <c r="D89" s="23" t="s">
         <v>44</v>
       </c>
-      <c r="E89" s="25"/>
-      <c r="F89" s="24"/>
+      <c r="E89" s="24"/>
+      <c r="F89" s="25"/>
       <c r="G89" s="3" t="s">
         <v>16</v>
       </c>
       <c r="H89" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="I89" s="24"/>
+      <c r="I89" s="25"/>
     </row>
     <row r="90" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B90" s="4">
@@ -2799,7 +2799,7 @@
       <c r="D90" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="E90" s="24"/>
+      <c r="E90" s="25"/>
       <c r="F90" s="3" t="s">
         <v>16</v>
       </c>
@@ -2824,10 +2824,10 @@
       <c r="D91" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E91" s="25"/>
-      <c r="F91" s="25"/>
-      <c r="G91" s="25"/>
-      <c r="H91" s="24"/>
+      <c r="E91" s="24"/>
+      <c r="F91" s="24"/>
+      <c r="G91" s="24"/>
+      <c r="H91" s="25"/>
       <c r="I91" s="18" t="s">
         <v>45</v>
       </c>
@@ -2842,11 +2842,11 @@
       <c r="D92" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E92" s="25"/>
-      <c r="F92" s="25"/>
-      <c r="G92" s="25"/>
-      <c r="H92" s="25"/>
-      <c r="I92" s="24"/>
+      <c r="E92" s="24"/>
+      <c r="F92" s="24"/>
+      <c r="G92" s="24"/>
+      <c r="H92" s="24"/>
+      <c r="I92" s="25"/>
     </row>
     <row r="93" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B93" s="4">
@@ -2858,11 +2858,11 @@
       <c r="D93" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="E93" s="25"/>
-      <c r="F93" s="25"/>
-      <c r="G93" s="25"/>
-      <c r="H93" s="25"/>
-      <c r="I93" s="24"/>
+      <c r="E93" s="24"/>
+      <c r="F93" s="24"/>
+      <c r="G93" s="24"/>
+      <c r="H93" s="24"/>
+      <c r="I93" s="25"/>
     </row>
     <row r="94" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B94" s="4">
@@ -2874,11 +2874,11 @@
       <c r="D94" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="E94" s="25"/>
-      <c r="F94" s="25"/>
-      <c r="G94" s="25"/>
-      <c r="H94" s="25"/>
-      <c r="I94" s="24"/>
+      <c r="E94" s="24"/>
+      <c r="F94" s="24"/>
+      <c r="G94" s="24"/>
+      <c r="H94" s="24"/>
+      <c r="I94" s="25"/>
     </row>
     <row r="95" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B95" s="4">
@@ -2890,12 +2890,12 @@
       <c r="D95" s="23" t="s">
         <v>47</v>
       </c>
-      <c r="E95" s="25"/>
-      <c r="F95" s="24"/>
+      <c r="E95" s="24"/>
+      <c r="F95" s="25"/>
       <c r="G95" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="H95" s="24"/>
+      <c r="H95" s="25"/>
       <c r="I95" s="1" t="s">
         <v>14</v>
       </c>
@@ -2910,11 +2910,11 @@
       <c r="D96" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E96" s="25"/>
-      <c r="F96" s="25"/>
-      <c r="G96" s="25"/>
-      <c r="H96" s="25"/>
-      <c r="I96" s="24"/>
+      <c r="E96" s="24"/>
+      <c r="F96" s="24"/>
+      <c r="G96" s="24"/>
+      <c r="H96" s="24"/>
+      <c r="I96" s="25"/>
     </row>
     <row r="97" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B97" s="4">
@@ -2926,11 +2926,11 @@
       <c r="D97" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="E97" s="25"/>
-      <c r="F97" s="25"/>
-      <c r="G97" s="25"/>
-      <c r="H97" s="25"/>
-      <c r="I97" s="24"/>
+      <c r="E97" s="24"/>
+      <c r="F97" s="24"/>
+      <c r="G97" s="24"/>
+      <c r="H97" s="24"/>
+      <c r="I97" s="25"/>
     </row>
     <row r="98" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B98" s="4">
@@ -2942,11 +2942,11 @@
       <c r="D98" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E98" s="25"/>
-      <c r="F98" s="25"/>
-      <c r="G98" s="25"/>
-      <c r="H98" s="25"/>
-      <c r="I98" s="24"/>
+      <c r="E98" s="24"/>
+      <c r="F98" s="24"/>
+      <c r="G98" s="24"/>
+      <c r="H98" s="24"/>
+      <c r="I98" s="25"/>
     </row>
     <row r="99" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B99" s="4">
@@ -2958,9 +2958,9 @@
       <c r="D99" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="E99" s="25"/>
-      <c r="F99" s="25"/>
-      <c r="G99" s="24"/>
+      <c r="E99" s="24"/>
+      <c r="F99" s="24"/>
+      <c r="G99" s="25"/>
       <c r="H99" s="3" t="s">
         <v>49</v>
       </c>
@@ -2987,18 +2987,18 @@
       <c r="G100" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="H100" s="25"/>
-      <c r="I100" s="24"/>
+      <c r="H100" s="24"/>
+      <c r="I100" s="25"/>
     </row>
     <row r="101" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B101" s="23"/>
-      <c r="C101" s="25"/>
-      <c r="D101" s="25"/>
-      <c r="E101" s="25"/>
-      <c r="F101" s="25"/>
-      <c r="G101" s="25"/>
-      <c r="H101" s="25"/>
-      <c r="I101" s="24"/>
+      <c r="C101" s="24"/>
+      <c r="D101" s="24"/>
+      <c r="E101" s="24"/>
+      <c r="F101" s="24"/>
+      <c r="G101" s="24"/>
+      <c r="H101" s="24"/>
+      <c r="I101" s="25"/>
     </row>
     <row r="102" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B102" s="3"/>
@@ -3020,7 +3020,7 @@
       <c r="D103" s="23" t="s">
         <v>51</v>
       </c>
-      <c r="E103" s="24"/>
+      <c r="E103" s="25"/>
       <c r="F103" s="3"/>
       <c r="G103" s="3"/>
       <c r="H103" s="3"/>
@@ -3036,7 +3036,7 @@
       <c r="D104" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="E104" s="24"/>
+      <c r="E104" s="25"/>
       <c r="F104" s="3"/>
       <c r="G104" s="3"/>
       <c r="H104" s="3"/>
@@ -3052,7 +3052,7 @@
       <c r="D105" s="23" t="s">
         <v>53</v>
       </c>
-      <c r="E105" s="24"/>
+      <c r="E105" s="25"/>
       <c r="F105" s="3"/>
       <c r="G105" s="3"/>
       <c r="H105" s="3"/>
@@ -3068,7 +3068,7 @@
       <c r="D106" s="23" t="s">
         <v>54</v>
       </c>
-      <c r="E106" s="24"/>
+      <c r="E106" s="25"/>
       <c r="F106" s="3"/>
       <c r="G106" s="3"/>
       <c r="H106" s="3"/>
@@ -3084,7 +3084,7 @@
       <c r="D107" s="23" t="s">
         <v>55</v>
       </c>
-      <c r="E107" s="24"/>
+      <c r="E107" s="25"/>
       <c r="F107" s="3"/>
       <c r="G107" s="3"/>
       <c r="H107" s="3"/>
@@ -3100,7 +3100,7 @@
       <c r="D108" s="23" t="s">
         <v>56</v>
       </c>
-      <c r="E108" s="24"/>
+      <c r="E108" s="25"/>
       <c r="F108" s="3"/>
       <c r="G108" s="3"/>
       <c r="H108" s="3"/>
@@ -3137,28 +3137,28 @@
       <c r="I111" s="20"/>
     </row>
     <row r="112" spans="2:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B112" s="28" t="s">
+      <c r="B112" s="30" t="s">
         <v>57</v>
       </c>
-      <c r="C112" s="29"/>
-      <c r="D112" s="29"/>
-      <c r="E112" s="29"/>
-      <c r="F112" s="29"/>
-      <c r="G112" s="29"/>
-      <c r="H112" s="29"/>
-      <c r="I112" s="29"/>
-      <c r="J112" s="30"/>
+      <c r="C112" s="31"/>
+      <c r="D112" s="31"/>
+      <c r="E112" s="31"/>
+      <c r="F112" s="31"/>
+      <c r="G112" s="31"/>
+      <c r="H112" s="31"/>
+      <c r="I112" s="31"/>
+      <c r="J112" s="32"/>
     </row>
     <row r="113" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B113" s="31"/>
-      <c r="C113" s="32"/>
-      <c r="D113" s="32"/>
-      <c r="E113" s="32"/>
-      <c r="F113" s="32"/>
-      <c r="G113" s="32"/>
-      <c r="H113" s="32"/>
-      <c r="I113" s="32"/>
-      <c r="J113" s="33"/>
+      <c r="B113" s="33"/>
+      <c r="C113" s="34"/>
+      <c r="D113" s="34"/>
+      <c r="E113" s="34"/>
+      <c r="F113" s="34"/>
+      <c r="G113" s="34"/>
+      <c r="H113" s="34"/>
+      <c r="I113" s="34"/>
+      <c r="J113" s="35"/>
     </row>
     <row r="114" spans="2:10" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B114" s="8" t="s">
@@ -3292,10 +3292,10 @@
       <c r="F118" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="G118" s="25"/>
-      <c r="H118" s="25"/>
-      <c r="I118" s="25"/>
-      <c r="J118" s="24"/>
+      <c r="G118" s="24"/>
+      <c r="H118" s="24"/>
+      <c r="I118" s="24"/>
+      <c r="J118" s="25"/>
     </row>
     <row r="119" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B119" s="4">
@@ -3336,10 +3336,10 @@
       <c r="D120" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="E120" s="25"/>
-      <c r="F120" s="25"/>
-      <c r="G120" s="25"/>
-      <c r="H120" s="24"/>
+      <c r="E120" s="24"/>
+      <c r="F120" s="24"/>
+      <c r="G120" s="24"/>
+      <c r="H120" s="25"/>
       <c r="I120" s="1" t="s">
         <v>16</v>
       </c>
@@ -3357,12 +3357,12 @@
       <c r="D121" s="23" t="s">
         <v>65</v>
       </c>
-      <c r="E121" s="25"/>
-      <c r="F121" s="25"/>
-      <c r="G121" s="25"/>
-      <c r="H121" s="25"/>
-      <c r="I121" s="25"/>
-      <c r="J121" s="24"/>
+      <c r="E121" s="24"/>
+      <c r="F121" s="24"/>
+      <c r="G121" s="24"/>
+      <c r="H121" s="24"/>
+      <c r="I121" s="24"/>
+      <c r="J121" s="25"/>
     </row>
     <row r="122" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B122" s="4">
@@ -3412,9 +3412,9 @@
       <c r="G123" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="H123" s="25"/>
-      <c r="I123" s="25"/>
-      <c r="J123" s="24"/>
+      <c r="H123" s="24"/>
+      <c r="I123" s="24"/>
+      <c r="J123" s="25"/>
     </row>
     <row r="124" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B124" s="4">
@@ -3435,9 +3435,9 @@
       <c r="G124" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="H124" s="25"/>
-      <c r="I124" s="25"/>
-      <c r="J124" s="24"/>
+      <c r="H124" s="24"/>
+      <c r="I124" s="24"/>
+      <c r="J124" s="25"/>
     </row>
     <row r="125" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B125" s="4">
@@ -3455,10 +3455,10 @@
       <c r="F125" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="G125" s="25"/>
-      <c r="H125" s="25"/>
-      <c r="I125" s="25"/>
-      <c r="J125" s="24"/>
+      <c r="G125" s="24"/>
+      <c r="H125" s="24"/>
+      <c r="I125" s="24"/>
+      <c r="J125" s="25"/>
     </row>
     <row r="126" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B126" s="4">
@@ -3479,8 +3479,8 @@
       <c r="G126" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="H126" s="25"/>
-      <c r="I126" s="24"/>
+      <c r="H126" s="24"/>
+      <c r="I126" s="25"/>
       <c r="J126" s="1" t="s">
         <v>16</v>
       </c>
@@ -3501,10 +3501,10 @@
       <c r="F127" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="G127" s="25"/>
-      <c r="H127" s="25"/>
-      <c r="I127" s="25"/>
-      <c r="J127" s="24"/>
+      <c r="G127" s="24"/>
+      <c r="H127" s="24"/>
+      <c r="I127" s="24"/>
+      <c r="J127" s="25"/>
     </row>
     <row r="128" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B128" s="4">
@@ -3516,12 +3516,12 @@
       <c r="D128" s="23" t="s">
         <v>65</v>
       </c>
-      <c r="E128" s="25"/>
-      <c r="F128" s="25"/>
-      <c r="G128" s="25"/>
-      <c r="H128" s="25"/>
-      <c r="I128" s="25"/>
-      <c r="J128" s="24"/>
+      <c r="E128" s="24"/>
+      <c r="F128" s="24"/>
+      <c r="G128" s="24"/>
+      <c r="H128" s="24"/>
+      <c r="I128" s="24"/>
+      <c r="J128" s="25"/>
     </row>
     <row r="129" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B129" s="4">
@@ -3707,12 +3707,12 @@
       <c r="D135" s="23" t="s">
         <v>65</v>
       </c>
-      <c r="E135" s="25"/>
-      <c r="F135" s="25"/>
-      <c r="G135" s="25"/>
-      <c r="H135" s="25"/>
-      <c r="I135" s="25"/>
-      <c r="J135" s="24"/>
+      <c r="E135" s="24"/>
+      <c r="F135" s="24"/>
+      <c r="G135" s="24"/>
+      <c r="H135" s="24"/>
+      <c r="I135" s="24"/>
+      <c r="J135" s="25"/>
     </row>
     <row r="136" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B136" s="4">
@@ -3927,12 +3927,12 @@
       <c r="D143" s="23" t="s">
         <v>65</v>
       </c>
-      <c r="E143" s="25"/>
-      <c r="F143" s="25"/>
-      <c r="G143" s="25"/>
-      <c r="H143" s="25"/>
-      <c r="I143" s="25"/>
-      <c r="J143" s="24"/>
+      <c r="E143" s="24"/>
+      <c r="F143" s="24"/>
+      <c r="G143" s="24"/>
+      <c r="H143" s="24"/>
+      <c r="I143" s="24"/>
+      <c r="J143" s="25"/>
     </row>
     <row r="144" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B144" s="4">
@@ -4011,9 +4011,9 @@
       <c r="G146" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="H146" s="25"/>
-      <c r="I146" s="25"/>
-      <c r="J146" s="24"/>
+      <c r="H146" s="24"/>
+      <c r="I146" s="24"/>
+      <c r="J146" s="25"/>
     </row>
     <row r="147" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B147" s="4">
@@ -4080,14 +4080,14 @@
       <c r="C149" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D149" s="34" t="s">
+      <c r="D149" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="E149" s="35"/>
-      <c r="F149" s="35"/>
-      <c r="G149" s="35"/>
-      <c r="H149" s="35"/>
-      <c r="I149" s="35"/>
+      <c r="E149" s="27"/>
+      <c r="F149" s="27"/>
+      <c r="G149" s="27"/>
+      <c r="H149" s="27"/>
+      <c r="I149" s="27"/>
       <c r="J149" s="36"/>
     </row>
     <row r="150" spans="2:10" x14ac:dyDescent="0.3">
@@ -4097,13 +4097,13 @@
       <c r="C150" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D150" s="37"/>
-      <c r="E150" s="38"/>
-      <c r="F150" s="38"/>
-      <c r="G150" s="38"/>
-      <c r="H150" s="38"/>
-      <c r="I150" s="38"/>
-      <c r="J150" s="39"/>
+      <c r="D150" s="28"/>
+      <c r="E150" s="29"/>
+      <c r="F150" s="29"/>
+      <c r="G150" s="29"/>
+      <c r="H150" s="29"/>
+      <c r="I150" s="29"/>
+      <c r="J150" s="37"/>
     </row>
     <row r="151" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B151" s="4">
@@ -4153,8 +4153,8 @@
       <c r="G152" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="H152" s="25"/>
-      <c r="I152" s="24"/>
+      <c r="H152" s="24"/>
+      <c r="I152" s="25"/>
       <c r="J152" s="1" t="s">
         <v>69</v>
       </c>
@@ -4285,12 +4285,12 @@
       <c r="D157" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E157" s="25"/>
-      <c r="F157" s="25"/>
-      <c r="G157" s="25"/>
-      <c r="H157" s="25"/>
-      <c r="I157" s="25"/>
-      <c r="J157" s="24"/>
+      <c r="E157" s="24"/>
+      <c r="F157" s="24"/>
+      <c r="G157" s="24"/>
+      <c r="H157" s="24"/>
+      <c r="I157" s="24"/>
+      <c r="J157" s="25"/>
     </row>
     <row r="158" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B158" s="4">
@@ -4474,12 +4474,12 @@
       <c r="D164" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E164" s="25"/>
-      <c r="F164" s="25"/>
-      <c r="G164" s="25"/>
-      <c r="H164" s="25"/>
-      <c r="I164" s="25"/>
-      <c r="J164" s="24"/>
+      <c r="E164" s="24"/>
+      <c r="F164" s="24"/>
+      <c r="G164" s="24"/>
+      <c r="H164" s="24"/>
+      <c r="I164" s="24"/>
+      <c r="J164" s="25"/>
     </row>
     <row r="165" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B165" s="4">
@@ -4680,12 +4680,12 @@
       <c r="D172" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E172" s="25"/>
-      <c r="F172" s="25"/>
-      <c r="G172" s="25"/>
-      <c r="H172" s="25"/>
-      <c r="I172" s="25"/>
-      <c r="J172" s="24"/>
+      <c r="E172" s="24"/>
+      <c r="F172" s="24"/>
+      <c r="G172" s="24"/>
+      <c r="H172" s="24"/>
+      <c r="I172" s="24"/>
+      <c r="J172" s="25"/>
     </row>
     <row r="173" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B173" s="4">
@@ -4749,29 +4749,29 @@
       <c r="B175" s="4">
         <v>45903</v>
       </c>
-      <c r="C175" s="34" t="s">
+      <c r="C175" s="26" t="s">
         <v>39</v>
       </c>
-      <c r="D175" s="35"/>
-      <c r="E175" s="35"/>
-      <c r="F175" s="35"/>
-      <c r="G175" s="35"/>
-      <c r="H175" s="35"/>
-      <c r="I175" s="35"/>
-      <c r="J175" s="35"/>
+      <c r="D175" s="27"/>
+      <c r="E175" s="27"/>
+      <c r="F175" s="27"/>
+      <c r="G175" s="27"/>
+      <c r="H175" s="27"/>
+      <c r="I175" s="27"/>
+      <c r="J175" s="27"/>
     </row>
     <row r="176" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B176" s="4">
         <v>45904</v>
       </c>
-      <c r="C176" s="37"/>
-      <c r="D176" s="38"/>
-      <c r="E176" s="38"/>
-      <c r="F176" s="38"/>
-      <c r="G176" s="38"/>
-      <c r="H176" s="38"/>
-      <c r="I176" s="38"/>
-      <c r="J176" s="38"/>
+      <c r="C176" s="28"/>
+      <c r="D176" s="29"/>
+      <c r="E176" s="29"/>
+      <c r="F176" s="29"/>
+      <c r="G176" s="29"/>
+      <c r="H176" s="29"/>
+      <c r="I176" s="29"/>
+      <c r="J176" s="29"/>
     </row>
     <row r="177" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B177" s="4">
@@ -4780,13 +4780,13 @@
       <c r="C177" s="23" t="s">
         <v>39</v>
       </c>
-      <c r="D177" s="25"/>
-      <c r="E177" s="25"/>
-      <c r="F177" s="25"/>
-      <c r="G177" s="25"/>
-      <c r="H177" s="25"/>
-      <c r="I177" s="25"/>
-      <c r="J177" s="24"/>
+      <c r="D177" s="24"/>
+      <c r="E177" s="24"/>
+      <c r="F177" s="24"/>
+      <c r="G177" s="24"/>
+      <c r="H177" s="24"/>
+      <c r="I177" s="24"/>
+      <c r="J177" s="25"/>
     </row>
     <row r="178" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B178" s="4">
@@ -4985,12 +4985,12 @@
       <c r="D185" s="23" t="s">
         <v>74</v>
       </c>
-      <c r="E185" s="25"/>
-      <c r="F185" s="25"/>
-      <c r="G185" s="25"/>
-      <c r="H185" s="25"/>
-      <c r="I185" s="25"/>
-      <c r="J185" s="24"/>
+      <c r="E185" s="24"/>
+      <c r="F185" s="24"/>
+      <c r="G185" s="24"/>
+      <c r="H185" s="24"/>
+      <c r="I185" s="24"/>
+      <c r="J185" s="25"/>
     </row>
     <row r="186" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B186" s="4">
@@ -5021,12 +5021,12 @@
       <c r="D187" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="E187" s="25"/>
-      <c r="F187" s="25"/>
-      <c r="G187" s="25"/>
-      <c r="H187" s="25"/>
-      <c r="I187" s="25"/>
-      <c r="J187" s="24"/>
+      <c r="E187" s="24"/>
+      <c r="F187" s="24"/>
+      <c r="G187" s="24"/>
+      <c r="H187" s="24"/>
+      <c r="I187" s="24"/>
+      <c r="J187" s="25"/>
     </row>
     <row r="188" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B188" s="3"/>
@@ -7549,38 +7549,47 @@
     </row>
   </sheetData>
   <mergeCells count="89">
-    <mergeCell ref="D187:J187"/>
-    <mergeCell ref="D185:J185"/>
-    <mergeCell ref="C175:J176"/>
-    <mergeCell ref="D164:J164"/>
-    <mergeCell ref="D157:J157"/>
-    <mergeCell ref="D143:J143"/>
-    <mergeCell ref="C177:J177"/>
-    <mergeCell ref="D135:J135"/>
-    <mergeCell ref="D172:J172"/>
-    <mergeCell ref="G146:J146"/>
-    <mergeCell ref="D108:E108"/>
-    <mergeCell ref="B112:J113"/>
-    <mergeCell ref="G124:J124"/>
-    <mergeCell ref="D120:H120"/>
-    <mergeCell ref="G123:J123"/>
-    <mergeCell ref="D121:J121"/>
-    <mergeCell ref="G152:I152"/>
-    <mergeCell ref="D149:J150"/>
-    <mergeCell ref="D31:I31"/>
-    <mergeCell ref="G35:H35"/>
-    <mergeCell ref="D40:I40"/>
-    <mergeCell ref="D33:I33"/>
-    <mergeCell ref="D46:I46"/>
-    <mergeCell ref="D43:I43"/>
-    <mergeCell ref="D78:I78"/>
-    <mergeCell ref="G71:H71"/>
-    <mergeCell ref="D76:I76"/>
-    <mergeCell ref="D66:H66"/>
-    <mergeCell ref="D77:I77"/>
-    <mergeCell ref="D73:I73"/>
-    <mergeCell ref="D70:E70"/>
-    <mergeCell ref="D74:F74"/>
+    <mergeCell ref="D106:E106"/>
+    <mergeCell ref="D99:G99"/>
+    <mergeCell ref="G126:I126"/>
+    <mergeCell ref="F125:J125"/>
+    <mergeCell ref="D128:J128"/>
+    <mergeCell ref="D103:E103"/>
+    <mergeCell ref="D104:E104"/>
+    <mergeCell ref="D105:E105"/>
+    <mergeCell ref="G100:I100"/>
+    <mergeCell ref="B101:I101"/>
+    <mergeCell ref="F127:J127"/>
+    <mergeCell ref="D107:E107"/>
+    <mergeCell ref="F118:J118"/>
+    <mergeCell ref="D98:I98"/>
+    <mergeCell ref="D94:I94"/>
+    <mergeCell ref="H89:I89"/>
+    <mergeCell ref="D89:F89"/>
+    <mergeCell ref="D97:I97"/>
+    <mergeCell ref="G64:H64"/>
+    <mergeCell ref="D96:I96"/>
+    <mergeCell ref="D95:F95"/>
+    <mergeCell ref="G95:H95"/>
+    <mergeCell ref="D92:I92"/>
+    <mergeCell ref="D93:I93"/>
+    <mergeCell ref="D90:E90"/>
+    <mergeCell ref="D91:H91"/>
+    <mergeCell ref="E86:G86"/>
+    <mergeCell ref="D88:I88"/>
+    <mergeCell ref="H67:I67"/>
+    <mergeCell ref="G81:H81"/>
+    <mergeCell ref="D67:F67"/>
+    <mergeCell ref="F68:I68"/>
+    <mergeCell ref="D87:E87"/>
+    <mergeCell ref="G87:I87"/>
+    <mergeCell ref="D60:I60"/>
+    <mergeCell ref="D62:I62"/>
+    <mergeCell ref="D61:I61"/>
+    <mergeCell ref="G49:H49"/>
+    <mergeCell ref="D47:I47"/>
+    <mergeCell ref="D55:I55"/>
+    <mergeCell ref="G57:H57"/>
     <mergeCell ref="D84:I84"/>
     <mergeCell ref="D69:I69"/>
     <mergeCell ref="D8:I8"/>
@@ -7597,47 +7606,38 @@
     <mergeCell ref="D30:I30"/>
     <mergeCell ref="G80:H80"/>
     <mergeCell ref="G42:H42"/>
-    <mergeCell ref="D60:I60"/>
-    <mergeCell ref="D62:I62"/>
-    <mergeCell ref="D61:I61"/>
-    <mergeCell ref="G49:H49"/>
-    <mergeCell ref="D47:I47"/>
-    <mergeCell ref="D55:I55"/>
-    <mergeCell ref="G57:H57"/>
-    <mergeCell ref="G64:H64"/>
-    <mergeCell ref="D96:I96"/>
-    <mergeCell ref="D95:F95"/>
-    <mergeCell ref="G95:H95"/>
-    <mergeCell ref="D92:I92"/>
-    <mergeCell ref="D93:I93"/>
-    <mergeCell ref="D90:E90"/>
-    <mergeCell ref="D91:H91"/>
-    <mergeCell ref="E86:G86"/>
-    <mergeCell ref="D88:I88"/>
-    <mergeCell ref="H67:I67"/>
-    <mergeCell ref="G81:H81"/>
-    <mergeCell ref="D67:F67"/>
-    <mergeCell ref="F68:I68"/>
-    <mergeCell ref="D87:E87"/>
-    <mergeCell ref="G87:I87"/>
-    <mergeCell ref="D98:I98"/>
-    <mergeCell ref="D94:I94"/>
-    <mergeCell ref="H89:I89"/>
-    <mergeCell ref="D89:F89"/>
-    <mergeCell ref="D97:I97"/>
-    <mergeCell ref="D106:E106"/>
-    <mergeCell ref="D99:G99"/>
-    <mergeCell ref="G126:I126"/>
-    <mergeCell ref="F125:J125"/>
-    <mergeCell ref="D128:J128"/>
-    <mergeCell ref="D103:E103"/>
-    <mergeCell ref="D104:E104"/>
-    <mergeCell ref="D105:E105"/>
-    <mergeCell ref="G100:I100"/>
-    <mergeCell ref="B101:I101"/>
-    <mergeCell ref="F127:J127"/>
-    <mergeCell ref="D107:E107"/>
-    <mergeCell ref="F118:J118"/>
+    <mergeCell ref="D78:I78"/>
+    <mergeCell ref="G71:H71"/>
+    <mergeCell ref="D76:I76"/>
+    <mergeCell ref="D66:H66"/>
+    <mergeCell ref="D77:I77"/>
+    <mergeCell ref="D73:I73"/>
+    <mergeCell ref="D70:E70"/>
+    <mergeCell ref="D74:F74"/>
+    <mergeCell ref="D31:I31"/>
+    <mergeCell ref="G35:H35"/>
+    <mergeCell ref="D40:I40"/>
+    <mergeCell ref="D33:I33"/>
+    <mergeCell ref="D46:I46"/>
+    <mergeCell ref="D43:I43"/>
+    <mergeCell ref="D108:E108"/>
+    <mergeCell ref="B112:J113"/>
+    <mergeCell ref="G124:J124"/>
+    <mergeCell ref="D120:H120"/>
+    <mergeCell ref="G123:J123"/>
+    <mergeCell ref="D121:J121"/>
+    <mergeCell ref="D143:J143"/>
+    <mergeCell ref="C177:J177"/>
+    <mergeCell ref="D135:J135"/>
+    <mergeCell ref="D172:J172"/>
+    <mergeCell ref="G146:J146"/>
+    <mergeCell ref="G152:I152"/>
+    <mergeCell ref="D149:J150"/>
+    <mergeCell ref="D187:J187"/>
+    <mergeCell ref="D185:J185"/>
+    <mergeCell ref="C175:J176"/>
+    <mergeCell ref="D164:J164"/>
+    <mergeCell ref="D157:J157"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/attendance_sheet.xlsx
+++ b/attendance_sheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\repositary\3rd_Year_5th_Semester\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9B974C0-062D-44B0-BA9B-0FCC12B28667}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CED02F2-9B1E-42FC-834F-A1703DFE790A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{EB654061-A886-47D1-BF86-9B1A84FCE7FB}"/>
   </bookViews>
@@ -544,22 +544,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -580,17 +574,23 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -993,14 +993,14 @@
       <c r="C8" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D8" s="39" t="s">
+      <c r="D8" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="E8" s="39"/>
-      <c r="F8" s="39"/>
-      <c r="G8" s="39"/>
-      <c r="H8" s="39"/>
-      <c r="I8" s="39"/>
+      <c r="E8" s="26"/>
+      <c r="F8" s="26"/>
+      <c r="G8" s="26"/>
+      <c r="H8" s="26"/>
+      <c r="I8" s="26"/>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B9" s="4">
@@ -1009,14 +1009,14 @@
       <c r="C9" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D9" s="39" t="s">
+      <c r="D9" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="E9" s="39"/>
-      <c r="F9" s="39"/>
-      <c r="G9" s="39"/>
-      <c r="H9" s="39"/>
-      <c r="I9" s="39"/>
+      <c r="E9" s="26"/>
+      <c r="F9" s="26"/>
+      <c r="G9" s="26"/>
+      <c r="H9" s="26"/>
+      <c r="I9" s="26"/>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B10" s="4">
@@ -1025,14 +1025,14 @@
       <c r="C10" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D10" s="39" t="s">
+      <c r="D10" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="E10" s="39"/>
-      <c r="F10" s="39"/>
-      <c r="G10" s="39"/>
-      <c r="H10" s="39"/>
-      <c r="I10" s="39"/>
+      <c r="E10" s="26"/>
+      <c r="F10" s="26"/>
+      <c r="G10" s="26"/>
+      <c r="H10" s="26"/>
+      <c r="I10" s="26"/>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B11" s="4">
@@ -1041,14 +1041,14 @@
       <c r="C11" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D11" s="39" t="s">
+      <c r="D11" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="E11" s="39"/>
-      <c r="F11" s="39"/>
-      <c r="G11" s="39"/>
-      <c r="H11" s="39"/>
-      <c r="I11" s="39"/>
+      <c r="E11" s="26"/>
+      <c r="F11" s="26"/>
+      <c r="G11" s="26"/>
+      <c r="H11" s="26"/>
+      <c r="I11" s="26"/>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B12" s="4">
@@ -1092,10 +1092,10 @@
       <c r="F13" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="G13" s="39" t="s">
+      <c r="G13" s="26" t="s">
         <v>18</v>
       </c>
-      <c r="H13" s="39"/>
+      <c r="H13" s="26"/>
       <c r="I13" s="1" t="s">
         <v>14</v>
       </c>
@@ -1107,14 +1107,14 @@
       <c r="C14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D14" s="39" t="s">
+      <c r="D14" s="26" t="s">
         <v>19</v>
       </c>
-      <c r="E14" s="39"/>
-      <c r="F14" s="39"/>
-      <c r="G14" s="39"/>
-      <c r="H14" s="39"/>
-      <c r="I14" s="39"/>
+      <c r="E14" s="26"/>
+      <c r="F14" s="26"/>
+      <c r="G14" s="26"/>
+      <c r="H14" s="26"/>
+      <c r="I14" s="26"/>
     </row>
     <row r="15" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B15" s="4">
@@ -1201,14 +1201,14 @@
       <c r="C18" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D18" s="39" t="s">
+      <c r="D18" s="26" t="s">
         <v>23</v>
       </c>
-      <c r="E18" s="39"/>
-      <c r="F18" s="39"/>
-      <c r="G18" s="39"/>
-      <c r="H18" s="39"/>
-      <c r="I18" s="39"/>
+      <c r="E18" s="26"/>
+      <c r="F18" s="26"/>
+      <c r="G18" s="26"/>
+      <c r="H18" s="26"/>
+      <c r="I18" s="26"/>
     </row>
     <row r="19" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B19" s="4">
@@ -1217,14 +1217,14 @@
       <c r="C19" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D19" s="39" t="s">
+      <c r="D19" s="26" t="s">
         <v>23</v>
       </c>
-      <c r="E19" s="39"/>
-      <c r="F19" s="39"/>
-      <c r="G19" s="39"/>
-      <c r="H19" s="39"/>
-      <c r="I19" s="39"/>
+      <c r="E19" s="26"/>
+      <c r="F19" s="26"/>
+      <c r="G19" s="26"/>
+      <c r="H19" s="26"/>
+      <c r="I19" s="26"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B20" s="4">
@@ -1242,10 +1242,10 @@
       <c r="F20" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G20" s="39" t="s">
+      <c r="G20" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="H20" s="39"/>
+      <c r="H20" s="26"/>
       <c r="I20" s="1" t="s">
         <v>14</v>
       </c>
@@ -1361,14 +1361,14 @@
       <c r="C25" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D25" s="39" t="s">
+      <c r="D25" s="26" t="s">
         <v>26</v>
       </c>
-      <c r="E25" s="39"/>
-      <c r="F25" s="39"/>
-      <c r="G25" s="39"/>
-      <c r="H25" s="39"/>
-      <c r="I25" s="39"/>
+      <c r="E25" s="26"/>
+      <c r="F25" s="26"/>
+      <c r="G25" s="26"/>
+      <c r="H25" s="26"/>
+      <c r="I25" s="26"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B26" s="4">
@@ -1412,10 +1412,10 @@
       <c r="F27" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G27" s="39" t="s">
+      <c r="G27" s="26" t="s">
         <v>18</v>
       </c>
-      <c r="H27" s="39"/>
+      <c r="H27" s="26"/>
       <c r="I27" s="1" t="s">
         <v>14</v>
       </c>
@@ -1479,14 +1479,14 @@
       <c r="C30" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D30" s="38" t="s">
+      <c r="D30" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="E30" s="38"/>
-      <c r="F30" s="38"/>
-      <c r="G30" s="38"/>
-      <c r="H30" s="38"/>
-      <c r="I30" s="38"/>
+      <c r="E30" s="27"/>
+      <c r="F30" s="27"/>
+      <c r="G30" s="27"/>
+      <c r="H30" s="27"/>
+      <c r="I30" s="27"/>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B31" s="4">
@@ -1495,14 +1495,14 @@
       <c r="C31" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D31" s="38" t="s">
+      <c r="D31" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="E31" s="38"/>
-      <c r="F31" s="38"/>
-      <c r="G31" s="38"/>
-      <c r="H31" s="38"/>
-      <c r="I31" s="38"/>
+      <c r="E31" s="27"/>
+      <c r="F31" s="27"/>
+      <c r="G31" s="27"/>
+      <c r="H31" s="27"/>
+      <c r="I31" s="27"/>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B32" s="4">
@@ -1537,14 +1537,14 @@
       <c r="C33" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D33" s="38" t="s">
+      <c r="D33" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="E33" s="38"/>
-      <c r="F33" s="38"/>
-      <c r="G33" s="38"/>
-      <c r="H33" s="38"/>
-      <c r="I33" s="38"/>
+      <c r="E33" s="27"/>
+      <c r="F33" s="27"/>
+      <c r="G33" s="27"/>
+      <c r="H33" s="27"/>
+      <c r="I33" s="27"/>
     </row>
     <row r="34" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B34" s="4">
@@ -1588,10 +1588,10 @@
       <c r="F35" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G35" s="38" t="s">
+      <c r="G35" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="H35" s="38"/>
+      <c r="H35" s="27"/>
       <c r="I35" s="1" t="s">
         <v>14</v>
       </c>
@@ -1707,14 +1707,14 @@
       <c r="C40" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D40" s="38" t="s">
+      <c r="D40" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="E40" s="38"/>
-      <c r="F40" s="38"/>
-      <c r="G40" s="38"/>
-      <c r="H40" s="38"/>
-      <c r="I40" s="38"/>
+      <c r="E40" s="27"/>
+      <c r="F40" s="27"/>
+      <c r="G40" s="27"/>
+      <c r="H40" s="27"/>
+      <c r="I40" s="27"/>
     </row>
     <row r="41" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B41" s="4">
@@ -1758,10 +1758,10 @@
       <c r="F42" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G42" s="38" t="s">
+      <c r="G42" s="27" t="s">
         <v>28</v>
       </c>
-      <c r="H42" s="38"/>
+      <c r="H42" s="27"/>
       <c r="I42" s="1" t="s">
         <v>15</v>
       </c>
@@ -1773,14 +1773,14 @@
       <c r="C43" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D43" s="38" t="s">
+      <c r="D43" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="E43" s="38"/>
-      <c r="F43" s="38"/>
-      <c r="G43" s="38"/>
-      <c r="H43" s="38"/>
-      <c r="I43" s="38"/>
+      <c r="E43" s="27"/>
+      <c r="F43" s="27"/>
+      <c r="G43" s="27"/>
+      <c r="H43" s="27"/>
+      <c r="I43" s="27"/>
     </row>
     <row r="44" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B44" s="4">
@@ -1844,14 +1844,14 @@
       <c r="C46" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D46" s="38" t="s">
+      <c r="D46" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="E46" s="38"/>
-      <c r="F46" s="38"/>
-      <c r="G46" s="38"/>
-      <c r="H46" s="38"/>
-      <c r="I46" s="38"/>
+      <c r="E46" s="27"/>
+      <c r="F46" s="27"/>
+      <c r="G46" s="27"/>
+      <c r="H46" s="27"/>
+      <c r="I46" s="27"/>
     </row>
     <row r="47" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B47" s="4">
@@ -1863,11 +1863,11 @@
       <c r="D47" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E47" s="24"/>
-      <c r="F47" s="24"/>
-      <c r="G47" s="24"/>
-      <c r="H47" s="24"/>
-      <c r="I47" s="25"/>
+      <c r="E47" s="25"/>
+      <c r="F47" s="25"/>
+      <c r="G47" s="25"/>
+      <c r="H47" s="25"/>
+      <c r="I47" s="24"/>
     </row>
     <row r="48" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B48" s="4">
@@ -1914,7 +1914,7 @@
       <c r="G49" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="H49" s="25"/>
+      <c r="H49" s="24"/>
       <c r="I49" s="1" t="s">
         <v>30</v>
       </c>
@@ -2056,14 +2056,14 @@
       <c r="C55" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="D55" s="24" t="s">
+      <c r="D55" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="E55" s="24"/>
-      <c r="F55" s="24"/>
-      <c r="G55" s="24"/>
-      <c r="H55" s="24"/>
-      <c r="I55" s="24"/>
+      <c r="E55" s="25"/>
+      <c r="F55" s="25"/>
+      <c r="G55" s="25"/>
+      <c r="H55" s="25"/>
+      <c r="I55" s="25"/>
     </row>
     <row r="56" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B56" s="4">
@@ -2110,7 +2110,7 @@
       <c r="G57" s="23" t="s">
         <v>37</v>
       </c>
-      <c r="H57" s="25"/>
+      <c r="H57" s="24"/>
       <c r="I57" s="1" t="s">
         <v>36</v>
       </c>
@@ -2177,11 +2177,11 @@
       <c r="D60" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E60" s="24"/>
-      <c r="F60" s="24"/>
-      <c r="G60" s="24"/>
-      <c r="H60" s="24"/>
-      <c r="I60" s="25"/>
+      <c r="E60" s="25"/>
+      <c r="F60" s="25"/>
+      <c r="G60" s="25"/>
+      <c r="H60" s="25"/>
+      <c r="I60" s="24"/>
     </row>
     <row r="61" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B61" s="4">
@@ -2193,11 +2193,11 @@
       <c r="D61" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E61" s="24"/>
-      <c r="F61" s="24"/>
-      <c r="G61" s="24"/>
-      <c r="H61" s="24"/>
-      <c r="I61" s="25"/>
+      <c r="E61" s="25"/>
+      <c r="F61" s="25"/>
+      <c r="G61" s="25"/>
+      <c r="H61" s="25"/>
+      <c r="I61" s="24"/>
     </row>
     <row r="62" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B62" s="4">
@@ -2209,11 +2209,11 @@
       <c r="D62" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E62" s="24"/>
-      <c r="F62" s="24"/>
-      <c r="G62" s="24"/>
-      <c r="H62" s="24"/>
-      <c r="I62" s="25"/>
+      <c r="E62" s="25"/>
+      <c r="F62" s="25"/>
+      <c r="G62" s="25"/>
+      <c r="H62" s="25"/>
+      <c r="I62" s="24"/>
     </row>
     <row r="63" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B63" s="4">
@@ -2260,7 +2260,7 @@
       <c r="G64" s="23" t="s">
         <v>37</v>
       </c>
-      <c r="H64" s="25"/>
+      <c r="H64" s="24"/>
       <c r="I64" s="1" t="s">
         <v>14</v>
       </c>
@@ -2301,10 +2301,10 @@
       <c r="D66" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="E66" s="24"/>
-      <c r="F66" s="24"/>
-      <c r="G66" s="24"/>
-      <c r="H66" s="25"/>
+      <c r="E66" s="25"/>
+      <c r="F66" s="25"/>
+      <c r="G66" s="25"/>
+      <c r="H66" s="24"/>
       <c r="I66" s="1" t="s">
         <v>16</v>
       </c>
@@ -2319,15 +2319,15 @@
       <c r="D67" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="E67" s="24"/>
-      <c r="F67" s="25"/>
+      <c r="E67" s="25"/>
+      <c r="F67" s="24"/>
       <c r="G67" s="3" t="s">
         <v>16</v>
       </c>
       <c r="H67" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="I67" s="25"/>
+      <c r="I67" s="24"/>
     </row>
     <row r="68" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B68" s="4">
@@ -2345,9 +2345,9 @@
       <c r="F68" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="G68" s="24"/>
-      <c r="H68" s="24"/>
-      <c r="I68" s="25"/>
+      <c r="G68" s="25"/>
+      <c r="H68" s="25"/>
+      <c r="I68" s="24"/>
     </row>
     <row r="69" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B69" s="4">
@@ -2359,11 +2359,11 @@
       <c r="D69" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E69" s="24"/>
-      <c r="F69" s="24"/>
-      <c r="G69" s="24"/>
-      <c r="H69" s="24"/>
-      <c r="I69" s="25"/>
+      <c r="E69" s="25"/>
+      <c r="F69" s="25"/>
+      <c r="G69" s="25"/>
+      <c r="H69" s="25"/>
+      <c r="I69" s="24"/>
     </row>
     <row r="70" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B70" s="4">
@@ -2375,7 +2375,7 @@
       <c r="D70" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="E70" s="25"/>
+      <c r="E70" s="24"/>
       <c r="F70" s="3" t="s">
         <v>15</v>
       </c>
@@ -2408,7 +2408,7 @@
       <c r="G71" s="23" t="s">
         <v>37</v>
       </c>
-      <c r="H71" s="25"/>
+      <c r="H71" s="24"/>
       <c r="I71" s="1" t="s">
         <v>14</v>
       </c>
@@ -2449,11 +2449,11 @@
       <c r="D73" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E73" s="24"/>
-      <c r="F73" s="24"/>
-      <c r="G73" s="24"/>
-      <c r="H73" s="24"/>
-      <c r="I73" s="25"/>
+      <c r="E73" s="25"/>
+      <c r="F73" s="25"/>
+      <c r="G73" s="25"/>
+      <c r="H73" s="25"/>
+      <c r="I73" s="24"/>
     </row>
     <row r="74" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B74" s="4">
@@ -2465,8 +2465,8 @@
       <c r="D74" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="E74" s="24"/>
-      <c r="F74" s="25"/>
+      <c r="E74" s="25"/>
+      <c r="F74" s="24"/>
       <c r="G74" s="3" t="s">
         <v>16</v>
       </c>
@@ -2505,11 +2505,11 @@
       <c r="D76" s="23" t="s">
         <v>39</v>
       </c>
-      <c r="E76" s="24"/>
-      <c r="F76" s="24"/>
-      <c r="G76" s="24"/>
-      <c r="H76" s="24"/>
-      <c r="I76" s="25"/>
+      <c r="E76" s="25"/>
+      <c r="F76" s="25"/>
+      <c r="G76" s="25"/>
+      <c r="H76" s="25"/>
+      <c r="I76" s="24"/>
     </row>
     <row r="77" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B77" s="4">
@@ -2521,11 +2521,11 @@
       <c r="D77" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E77" s="24"/>
-      <c r="F77" s="24"/>
-      <c r="G77" s="24"/>
-      <c r="H77" s="24"/>
-      <c r="I77" s="25"/>
+      <c r="E77" s="25"/>
+      <c r="F77" s="25"/>
+      <c r="G77" s="25"/>
+      <c r="H77" s="25"/>
+      <c r="I77" s="24"/>
     </row>
     <row r="78" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B78" s="4">
@@ -2537,11 +2537,11 @@
       <c r="D78" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E78" s="24"/>
-      <c r="F78" s="24"/>
-      <c r="G78" s="24"/>
-      <c r="H78" s="24"/>
-      <c r="I78" s="25"/>
+      <c r="E78" s="25"/>
+      <c r="F78" s="25"/>
+      <c r="G78" s="25"/>
+      <c r="H78" s="25"/>
+      <c r="I78" s="24"/>
     </row>
     <row r="79" spans="2:9" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B79" s="16" t="s">
@@ -2588,7 +2588,7 @@
       <c r="G80" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="H80" s="25"/>
+      <c r="H80" s="24"/>
       <c r="I80" s="1" t="s">
         <v>14</v>
       </c>
@@ -2612,7 +2612,7 @@
       <c r="G81" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="H81" s="25"/>
+      <c r="H81" s="24"/>
       <c r="I81" s="1" t="s">
         <v>16</v>
       </c>
@@ -2679,11 +2679,11 @@
       <c r="D84" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E84" s="24"/>
-      <c r="F84" s="24"/>
-      <c r="G84" s="24"/>
-      <c r="H84" s="24"/>
-      <c r="I84" s="25"/>
+      <c r="E84" s="25"/>
+      <c r="F84" s="25"/>
+      <c r="G84" s="25"/>
+      <c r="H84" s="25"/>
+      <c r="I84" s="24"/>
     </row>
     <row r="85" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B85" s="4">
@@ -2724,8 +2724,8 @@
       <c r="E86" s="23" t="s">
         <v>43</v>
       </c>
-      <c r="F86" s="24"/>
-      <c r="G86" s="25"/>
+      <c r="F86" s="25"/>
+      <c r="G86" s="24"/>
       <c r="H86" s="3" t="s">
         <v>14</v>
       </c>
@@ -2743,15 +2743,15 @@
       <c r="D87" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="E87" s="25"/>
+      <c r="E87" s="24"/>
       <c r="F87" s="3" t="s">
         <v>16</v>
       </c>
       <c r="G87" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="H87" s="24"/>
-      <c r="I87" s="25"/>
+      <c r="H87" s="25"/>
+      <c r="I87" s="24"/>
     </row>
     <row r="88" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B88" s="4">
@@ -2763,11 +2763,11 @@
       <c r="D88" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E88" s="24"/>
-      <c r="F88" s="24"/>
-      <c r="G88" s="24"/>
-      <c r="H88" s="24"/>
-      <c r="I88" s="25"/>
+      <c r="E88" s="25"/>
+      <c r="F88" s="25"/>
+      <c r="G88" s="25"/>
+      <c r="H88" s="25"/>
+      <c r="I88" s="24"/>
     </row>
     <row r="89" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B89" s="4">
@@ -2779,15 +2779,15 @@
       <c r="D89" s="23" t="s">
         <v>44</v>
       </c>
-      <c r="E89" s="24"/>
-      <c r="F89" s="25"/>
+      <c r="E89" s="25"/>
+      <c r="F89" s="24"/>
       <c r="G89" s="3" t="s">
         <v>16</v>
       </c>
       <c r="H89" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="I89" s="25"/>
+      <c r="I89" s="24"/>
     </row>
     <row r="90" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B90" s="4">
@@ -2799,7 +2799,7 @@
       <c r="D90" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="E90" s="25"/>
+      <c r="E90" s="24"/>
       <c r="F90" s="3" t="s">
         <v>16</v>
       </c>
@@ -2824,10 +2824,10 @@
       <c r="D91" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E91" s="24"/>
-      <c r="F91" s="24"/>
-      <c r="G91" s="24"/>
-      <c r="H91" s="25"/>
+      <c r="E91" s="25"/>
+      <c r="F91" s="25"/>
+      <c r="G91" s="25"/>
+      <c r="H91" s="24"/>
       <c r="I91" s="18" t="s">
         <v>45</v>
       </c>
@@ -2842,11 +2842,11 @@
       <c r="D92" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E92" s="24"/>
-      <c r="F92" s="24"/>
-      <c r="G92" s="24"/>
-      <c r="H92" s="24"/>
-      <c r="I92" s="25"/>
+      <c r="E92" s="25"/>
+      <c r="F92" s="25"/>
+      <c r="G92" s="25"/>
+      <c r="H92" s="25"/>
+      <c r="I92" s="24"/>
     </row>
     <row r="93" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B93" s="4">
@@ -2858,11 +2858,11 @@
       <c r="D93" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="E93" s="24"/>
-      <c r="F93" s="24"/>
-      <c r="G93" s="24"/>
-      <c r="H93" s="24"/>
-      <c r="I93" s="25"/>
+      <c r="E93" s="25"/>
+      <c r="F93" s="25"/>
+      <c r="G93" s="25"/>
+      <c r="H93" s="25"/>
+      <c r="I93" s="24"/>
     </row>
     <row r="94" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B94" s="4">
@@ -2874,11 +2874,11 @@
       <c r="D94" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="E94" s="24"/>
-      <c r="F94" s="24"/>
-      <c r="G94" s="24"/>
-      <c r="H94" s="24"/>
-      <c r="I94" s="25"/>
+      <c r="E94" s="25"/>
+      <c r="F94" s="25"/>
+      <c r="G94" s="25"/>
+      <c r="H94" s="25"/>
+      <c r="I94" s="24"/>
     </row>
     <row r="95" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B95" s="4">
@@ -2890,12 +2890,12 @@
       <c r="D95" s="23" t="s">
         <v>47</v>
       </c>
-      <c r="E95" s="24"/>
-      <c r="F95" s="25"/>
+      <c r="E95" s="25"/>
+      <c r="F95" s="24"/>
       <c r="G95" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="H95" s="25"/>
+      <c r="H95" s="24"/>
       <c r="I95" s="1" t="s">
         <v>14</v>
       </c>
@@ -2910,11 +2910,11 @@
       <c r="D96" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E96" s="24"/>
-      <c r="F96" s="24"/>
-      <c r="G96" s="24"/>
-      <c r="H96" s="24"/>
-      <c r="I96" s="25"/>
+      <c r="E96" s="25"/>
+      <c r="F96" s="25"/>
+      <c r="G96" s="25"/>
+      <c r="H96" s="25"/>
+      <c r="I96" s="24"/>
     </row>
     <row r="97" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B97" s="4">
@@ -2926,11 +2926,11 @@
       <c r="D97" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="E97" s="24"/>
-      <c r="F97" s="24"/>
-      <c r="G97" s="24"/>
-      <c r="H97" s="24"/>
-      <c r="I97" s="25"/>
+      <c r="E97" s="25"/>
+      <c r="F97" s="25"/>
+      <c r="G97" s="25"/>
+      <c r="H97" s="25"/>
+      <c r="I97" s="24"/>
     </row>
     <row r="98" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B98" s="4">
@@ -2942,11 +2942,11 @@
       <c r="D98" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E98" s="24"/>
-      <c r="F98" s="24"/>
-      <c r="G98" s="24"/>
-      <c r="H98" s="24"/>
-      <c r="I98" s="25"/>
+      <c r="E98" s="25"/>
+      <c r="F98" s="25"/>
+      <c r="G98" s="25"/>
+      <c r="H98" s="25"/>
+      <c r="I98" s="24"/>
     </row>
     <row r="99" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B99" s="4">
@@ -2958,9 +2958,9 @@
       <c r="D99" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="E99" s="24"/>
-      <c r="F99" s="24"/>
-      <c r="G99" s="25"/>
+      <c r="E99" s="25"/>
+      <c r="F99" s="25"/>
+      <c r="G99" s="24"/>
       <c r="H99" s="3" t="s">
         <v>49</v>
       </c>
@@ -2987,18 +2987,18 @@
       <c r="G100" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="H100" s="24"/>
-      <c r="I100" s="25"/>
+      <c r="H100" s="25"/>
+      <c r="I100" s="24"/>
     </row>
     <row r="101" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B101" s="23"/>
-      <c r="C101" s="24"/>
-      <c r="D101" s="24"/>
-      <c r="E101" s="24"/>
-      <c r="F101" s="24"/>
-      <c r="G101" s="24"/>
-      <c r="H101" s="24"/>
-      <c r="I101" s="25"/>
+      <c r="C101" s="25"/>
+      <c r="D101" s="25"/>
+      <c r="E101" s="25"/>
+      <c r="F101" s="25"/>
+      <c r="G101" s="25"/>
+      <c r="H101" s="25"/>
+      <c r="I101" s="24"/>
     </row>
     <row r="102" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B102" s="3"/>
@@ -3020,7 +3020,7 @@
       <c r="D103" s="23" t="s">
         <v>51</v>
       </c>
-      <c r="E103" s="25"/>
+      <c r="E103" s="24"/>
       <c r="F103" s="3"/>
       <c r="G103" s="3"/>
       <c r="H103" s="3"/>
@@ -3036,7 +3036,7 @@
       <c r="D104" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="E104" s="25"/>
+      <c r="E104" s="24"/>
       <c r="F104" s="3"/>
       <c r="G104" s="3"/>
       <c r="H104" s="3"/>
@@ -3052,7 +3052,7 @@
       <c r="D105" s="23" t="s">
         <v>53</v>
       </c>
-      <c r="E105" s="25"/>
+      <c r="E105" s="24"/>
       <c r="F105" s="3"/>
       <c r="G105" s="3"/>
       <c r="H105" s="3"/>
@@ -3068,7 +3068,7 @@
       <c r="D106" s="23" t="s">
         <v>54</v>
       </c>
-      <c r="E106" s="25"/>
+      <c r="E106" s="24"/>
       <c r="F106" s="3"/>
       <c r="G106" s="3"/>
       <c r="H106" s="3"/>
@@ -3084,7 +3084,7 @@
       <c r="D107" s="23" t="s">
         <v>55</v>
       </c>
-      <c r="E107" s="25"/>
+      <c r="E107" s="24"/>
       <c r="F107" s="3"/>
       <c r="G107" s="3"/>
       <c r="H107" s="3"/>
@@ -3100,7 +3100,7 @@
       <c r="D108" s="23" t="s">
         <v>56</v>
       </c>
-      <c r="E108" s="25"/>
+      <c r="E108" s="24"/>
       <c r="F108" s="3"/>
       <c r="G108" s="3"/>
       <c r="H108" s="3"/>
@@ -3137,28 +3137,28 @@
       <c r="I111" s="20"/>
     </row>
     <row r="112" spans="2:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B112" s="30" t="s">
+      <c r="B112" s="28" t="s">
         <v>57</v>
       </c>
-      <c r="C112" s="31"/>
-      <c r="D112" s="31"/>
-      <c r="E112" s="31"/>
-      <c r="F112" s="31"/>
-      <c r="G112" s="31"/>
-      <c r="H112" s="31"/>
-      <c r="I112" s="31"/>
-      <c r="J112" s="32"/>
+      <c r="C112" s="29"/>
+      <c r="D112" s="29"/>
+      <c r="E112" s="29"/>
+      <c r="F112" s="29"/>
+      <c r="G112" s="29"/>
+      <c r="H112" s="29"/>
+      <c r="I112" s="29"/>
+      <c r="J112" s="30"/>
     </row>
     <row r="113" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B113" s="33"/>
-      <c r="C113" s="34"/>
-      <c r="D113" s="34"/>
-      <c r="E113" s="34"/>
-      <c r="F113" s="34"/>
-      <c r="G113" s="34"/>
-      <c r="H113" s="34"/>
-      <c r="I113" s="34"/>
-      <c r="J113" s="35"/>
+      <c r="B113" s="31"/>
+      <c r="C113" s="32"/>
+      <c r="D113" s="32"/>
+      <c r="E113" s="32"/>
+      <c r="F113" s="32"/>
+      <c r="G113" s="32"/>
+      <c r="H113" s="32"/>
+      <c r="I113" s="32"/>
+      <c r="J113" s="33"/>
     </row>
     <row r="114" spans="2:10" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B114" s="8" t="s">
@@ -3292,10 +3292,10 @@
       <c r="F118" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="G118" s="24"/>
-      <c r="H118" s="24"/>
-      <c r="I118" s="24"/>
-      <c r="J118" s="25"/>
+      <c r="G118" s="25"/>
+      <c r="H118" s="25"/>
+      <c r="I118" s="25"/>
+      <c r="J118" s="24"/>
     </row>
     <row r="119" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B119" s="4">
@@ -3336,10 +3336,10 @@
       <c r="D120" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="E120" s="24"/>
-      <c r="F120" s="24"/>
-      <c r="G120" s="24"/>
-      <c r="H120" s="25"/>
+      <c r="E120" s="25"/>
+      <c r="F120" s="25"/>
+      <c r="G120" s="25"/>
+      <c r="H120" s="24"/>
       <c r="I120" s="1" t="s">
         <v>16</v>
       </c>
@@ -3357,12 +3357,12 @@
       <c r="D121" s="23" t="s">
         <v>65</v>
       </c>
-      <c r="E121" s="24"/>
-      <c r="F121" s="24"/>
-      <c r="G121" s="24"/>
-      <c r="H121" s="24"/>
-      <c r="I121" s="24"/>
-      <c r="J121" s="25"/>
+      <c r="E121" s="25"/>
+      <c r="F121" s="25"/>
+      <c r="G121" s="25"/>
+      <c r="H121" s="25"/>
+      <c r="I121" s="25"/>
+      <c r="J121" s="24"/>
     </row>
     <row r="122" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B122" s="4">
@@ -3412,9 +3412,9 @@
       <c r="G123" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="H123" s="24"/>
-      <c r="I123" s="24"/>
-      <c r="J123" s="25"/>
+      <c r="H123" s="25"/>
+      <c r="I123" s="25"/>
+      <c r="J123" s="24"/>
     </row>
     <row r="124" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B124" s="4">
@@ -3435,9 +3435,9 @@
       <c r="G124" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="H124" s="24"/>
-      <c r="I124" s="24"/>
-      <c r="J124" s="25"/>
+      <c r="H124" s="25"/>
+      <c r="I124" s="25"/>
+      <c r="J124" s="24"/>
     </row>
     <row r="125" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B125" s="4">
@@ -3455,10 +3455,10 @@
       <c r="F125" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="G125" s="24"/>
-      <c r="H125" s="24"/>
-      <c r="I125" s="24"/>
-      <c r="J125" s="25"/>
+      <c r="G125" s="25"/>
+      <c r="H125" s="25"/>
+      <c r="I125" s="25"/>
+      <c r="J125" s="24"/>
     </row>
     <row r="126" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B126" s="4">
@@ -3479,8 +3479,8 @@
       <c r="G126" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="H126" s="24"/>
-      <c r="I126" s="25"/>
+      <c r="H126" s="25"/>
+      <c r="I126" s="24"/>
       <c r="J126" s="1" t="s">
         <v>16</v>
       </c>
@@ -3501,10 +3501,10 @@
       <c r="F127" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="G127" s="24"/>
-      <c r="H127" s="24"/>
-      <c r="I127" s="24"/>
-      <c r="J127" s="25"/>
+      <c r="G127" s="25"/>
+      <c r="H127" s="25"/>
+      <c r="I127" s="25"/>
+      <c r="J127" s="24"/>
     </row>
     <row r="128" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B128" s="4">
@@ -3516,12 +3516,12 @@
       <c r="D128" s="23" t="s">
         <v>65</v>
       </c>
-      <c r="E128" s="24"/>
-      <c r="F128" s="24"/>
-      <c r="G128" s="24"/>
-      <c r="H128" s="24"/>
-      <c r="I128" s="24"/>
-      <c r="J128" s="25"/>
+      <c r="E128" s="25"/>
+      <c r="F128" s="25"/>
+      <c r="G128" s="25"/>
+      <c r="H128" s="25"/>
+      <c r="I128" s="25"/>
+      <c r="J128" s="24"/>
     </row>
     <row r="129" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B129" s="4">
@@ -3707,12 +3707,12 @@
       <c r="D135" s="23" t="s">
         <v>65</v>
       </c>
-      <c r="E135" s="24"/>
-      <c r="F135" s="24"/>
-      <c r="G135" s="24"/>
-      <c r="H135" s="24"/>
-      <c r="I135" s="24"/>
-      <c r="J135" s="25"/>
+      <c r="E135" s="25"/>
+      <c r="F135" s="25"/>
+      <c r="G135" s="25"/>
+      <c r="H135" s="25"/>
+      <c r="I135" s="25"/>
+      <c r="J135" s="24"/>
     </row>
     <row r="136" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B136" s="4">
@@ -3927,12 +3927,12 @@
       <c r="D143" s="23" t="s">
         <v>65</v>
       </c>
-      <c r="E143" s="24"/>
-      <c r="F143" s="24"/>
-      <c r="G143" s="24"/>
-      <c r="H143" s="24"/>
-      <c r="I143" s="24"/>
-      <c r="J143" s="25"/>
+      <c r="E143" s="25"/>
+      <c r="F143" s="25"/>
+      <c r="G143" s="25"/>
+      <c r="H143" s="25"/>
+      <c r="I143" s="25"/>
+      <c r="J143" s="24"/>
     </row>
     <row r="144" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B144" s="4">
@@ -4011,9 +4011,9 @@
       <c r="G146" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="H146" s="24"/>
-      <c r="I146" s="24"/>
-      <c r="J146" s="25"/>
+      <c r="H146" s="25"/>
+      <c r="I146" s="25"/>
+      <c r="J146" s="24"/>
     </row>
     <row r="147" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B147" s="4">
@@ -4080,14 +4080,14 @@
       <c r="C149" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D149" s="26" t="s">
+      <c r="D149" s="34" t="s">
         <v>20</v>
       </c>
-      <c r="E149" s="27"/>
-      <c r="F149" s="27"/>
-      <c r="G149" s="27"/>
-      <c r="H149" s="27"/>
-      <c r="I149" s="27"/>
+      <c r="E149" s="35"/>
+      <c r="F149" s="35"/>
+      <c r="G149" s="35"/>
+      <c r="H149" s="35"/>
+      <c r="I149" s="35"/>
       <c r="J149" s="36"/>
     </row>
     <row r="150" spans="2:10" x14ac:dyDescent="0.3">
@@ -4097,13 +4097,13 @@
       <c r="C150" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D150" s="28"/>
-      <c r="E150" s="29"/>
-      <c r="F150" s="29"/>
-      <c r="G150" s="29"/>
-      <c r="H150" s="29"/>
-      <c r="I150" s="29"/>
-      <c r="J150" s="37"/>
+      <c r="D150" s="37"/>
+      <c r="E150" s="38"/>
+      <c r="F150" s="38"/>
+      <c r="G150" s="38"/>
+      <c r="H150" s="38"/>
+      <c r="I150" s="38"/>
+      <c r="J150" s="39"/>
     </row>
     <row r="151" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B151" s="4">
@@ -4153,8 +4153,8 @@
       <c r="G152" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="H152" s="24"/>
-      <c r="I152" s="25"/>
+      <c r="H152" s="25"/>
+      <c r="I152" s="24"/>
       <c r="J152" s="1" t="s">
         <v>69</v>
       </c>
@@ -4285,12 +4285,12 @@
       <c r="D157" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E157" s="24"/>
-      <c r="F157" s="24"/>
-      <c r="G157" s="24"/>
-      <c r="H157" s="24"/>
-      <c r="I157" s="24"/>
-      <c r="J157" s="25"/>
+      <c r="E157" s="25"/>
+      <c r="F157" s="25"/>
+      <c r="G157" s="25"/>
+      <c r="H157" s="25"/>
+      <c r="I157" s="25"/>
+      <c r="J157" s="24"/>
     </row>
     <row r="158" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B158" s="4">
@@ -4474,12 +4474,12 @@
       <c r="D164" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E164" s="24"/>
-      <c r="F164" s="24"/>
-      <c r="G164" s="24"/>
-      <c r="H164" s="24"/>
-      <c r="I164" s="24"/>
-      <c r="J164" s="25"/>
+      <c r="E164" s="25"/>
+      <c r="F164" s="25"/>
+      <c r="G164" s="25"/>
+      <c r="H164" s="25"/>
+      <c r="I164" s="25"/>
+      <c r="J164" s="24"/>
     </row>
     <row r="165" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B165" s="4">
@@ -4680,12 +4680,12 @@
       <c r="D172" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E172" s="24"/>
-      <c r="F172" s="24"/>
-      <c r="G172" s="24"/>
-      <c r="H172" s="24"/>
-      <c r="I172" s="24"/>
-      <c r="J172" s="25"/>
+      <c r="E172" s="25"/>
+      <c r="F172" s="25"/>
+      <c r="G172" s="25"/>
+      <c r="H172" s="25"/>
+      <c r="I172" s="25"/>
+      <c r="J172" s="24"/>
     </row>
     <row r="173" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B173" s="4">
@@ -4749,29 +4749,29 @@
       <c r="B175" s="4">
         <v>45903</v>
       </c>
-      <c r="C175" s="26" t="s">
+      <c r="C175" s="34" t="s">
         <v>39</v>
       </c>
-      <c r="D175" s="27"/>
-      <c r="E175" s="27"/>
-      <c r="F175" s="27"/>
-      <c r="G175" s="27"/>
-      <c r="H175" s="27"/>
-      <c r="I175" s="27"/>
-      <c r="J175" s="27"/>
+      <c r="D175" s="35"/>
+      <c r="E175" s="35"/>
+      <c r="F175" s="35"/>
+      <c r="G175" s="35"/>
+      <c r="H175" s="35"/>
+      <c r="I175" s="35"/>
+      <c r="J175" s="35"/>
     </row>
     <row r="176" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B176" s="4">
         <v>45904</v>
       </c>
-      <c r="C176" s="28"/>
-      <c r="D176" s="29"/>
-      <c r="E176" s="29"/>
-      <c r="F176" s="29"/>
-      <c r="G176" s="29"/>
-      <c r="H176" s="29"/>
-      <c r="I176" s="29"/>
-      <c r="J176" s="29"/>
+      <c r="C176" s="37"/>
+      <c r="D176" s="38"/>
+      <c r="E176" s="38"/>
+      <c r="F176" s="38"/>
+      <c r="G176" s="38"/>
+      <c r="H176" s="38"/>
+      <c r="I176" s="38"/>
+      <c r="J176" s="38"/>
     </row>
     <row r="177" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B177" s="4">
@@ -4780,13 +4780,13 @@
       <c r="C177" s="23" t="s">
         <v>39</v>
       </c>
-      <c r="D177" s="24"/>
-      <c r="E177" s="24"/>
-      <c r="F177" s="24"/>
-      <c r="G177" s="24"/>
-      <c r="H177" s="24"/>
-      <c r="I177" s="24"/>
-      <c r="J177" s="25"/>
+      <c r="D177" s="25"/>
+      <c r="E177" s="25"/>
+      <c r="F177" s="25"/>
+      <c r="G177" s="25"/>
+      <c r="H177" s="25"/>
+      <c r="I177" s="25"/>
+      <c r="J177" s="24"/>
     </row>
     <row r="178" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B178" s="4">
@@ -4985,12 +4985,12 @@
       <c r="D185" s="23" t="s">
         <v>74</v>
       </c>
-      <c r="E185" s="24"/>
-      <c r="F185" s="24"/>
-      <c r="G185" s="24"/>
-      <c r="H185" s="24"/>
-      <c r="I185" s="24"/>
-      <c r="J185" s="25"/>
+      <c r="E185" s="25"/>
+      <c r="F185" s="25"/>
+      <c r="G185" s="25"/>
+      <c r="H185" s="25"/>
+      <c r="I185" s="25"/>
+      <c r="J185" s="24"/>
     </row>
     <row r="186" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B186" s="4">
@@ -5021,12 +5021,12 @@
       <c r="D187" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="E187" s="24"/>
-      <c r="F187" s="24"/>
-      <c r="G187" s="24"/>
-      <c r="H187" s="24"/>
-      <c r="I187" s="24"/>
-      <c r="J187" s="25"/>
+      <c r="E187" s="25"/>
+      <c r="F187" s="25"/>
+      <c r="G187" s="25"/>
+      <c r="H187" s="25"/>
+      <c r="I187" s="25"/>
+      <c r="J187" s="24"/>
     </row>
     <row r="188" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B188" s="3"/>
@@ -7549,24 +7549,58 @@
     </row>
   </sheetData>
   <mergeCells count="89">
-    <mergeCell ref="D106:E106"/>
-    <mergeCell ref="D99:G99"/>
-    <mergeCell ref="G126:I126"/>
-    <mergeCell ref="F125:J125"/>
-    <mergeCell ref="D128:J128"/>
-    <mergeCell ref="D103:E103"/>
-    <mergeCell ref="D104:E104"/>
-    <mergeCell ref="D105:E105"/>
-    <mergeCell ref="G100:I100"/>
-    <mergeCell ref="B101:I101"/>
-    <mergeCell ref="F127:J127"/>
-    <mergeCell ref="D107:E107"/>
-    <mergeCell ref="F118:J118"/>
-    <mergeCell ref="D98:I98"/>
-    <mergeCell ref="D94:I94"/>
-    <mergeCell ref="H89:I89"/>
-    <mergeCell ref="D89:F89"/>
-    <mergeCell ref="D97:I97"/>
+    <mergeCell ref="D187:J187"/>
+    <mergeCell ref="D185:J185"/>
+    <mergeCell ref="C175:J176"/>
+    <mergeCell ref="D164:J164"/>
+    <mergeCell ref="D157:J157"/>
+    <mergeCell ref="D120:H120"/>
+    <mergeCell ref="G123:J123"/>
+    <mergeCell ref="D121:J121"/>
+    <mergeCell ref="D143:J143"/>
+    <mergeCell ref="C177:J177"/>
+    <mergeCell ref="D135:J135"/>
+    <mergeCell ref="D172:J172"/>
+    <mergeCell ref="G146:J146"/>
+    <mergeCell ref="G152:I152"/>
+    <mergeCell ref="D149:J150"/>
+    <mergeCell ref="D31:I31"/>
+    <mergeCell ref="G35:H35"/>
+    <mergeCell ref="D40:I40"/>
+    <mergeCell ref="D33:I33"/>
+    <mergeCell ref="D46:I46"/>
+    <mergeCell ref="D43:I43"/>
+    <mergeCell ref="D78:I78"/>
+    <mergeCell ref="G71:H71"/>
+    <mergeCell ref="D76:I76"/>
+    <mergeCell ref="D66:H66"/>
+    <mergeCell ref="D77:I77"/>
+    <mergeCell ref="D73:I73"/>
+    <mergeCell ref="D70:E70"/>
+    <mergeCell ref="D74:F74"/>
+    <mergeCell ref="D84:I84"/>
+    <mergeCell ref="D69:I69"/>
+    <mergeCell ref="D8:I8"/>
+    <mergeCell ref="D9:I9"/>
+    <mergeCell ref="D10:I10"/>
+    <mergeCell ref="D11:I11"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="D14:I14"/>
+    <mergeCell ref="G27:H27"/>
+    <mergeCell ref="D25:I25"/>
+    <mergeCell ref="G20:H20"/>
+    <mergeCell ref="D19:I19"/>
+    <mergeCell ref="D18:I18"/>
+    <mergeCell ref="D30:I30"/>
+    <mergeCell ref="G80:H80"/>
+    <mergeCell ref="G42:H42"/>
+    <mergeCell ref="D60:I60"/>
+    <mergeCell ref="D62:I62"/>
+    <mergeCell ref="D61:I61"/>
+    <mergeCell ref="G49:H49"/>
+    <mergeCell ref="D47:I47"/>
+    <mergeCell ref="D55:I55"/>
+    <mergeCell ref="G57:H57"/>
     <mergeCell ref="G64:H64"/>
     <mergeCell ref="D96:I96"/>
     <mergeCell ref="D95:F95"/>
@@ -7583,61 +7617,27 @@
     <mergeCell ref="F68:I68"/>
     <mergeCell ref="D87:E87"/>
     <mergeCell ref="G87:I87"/>
-    <mergeCell ref="D60:I60"/>
-    <mergeCell ref="D62:I62"/>
-    <mergeCell ref="D61:I61"/>
-    <mergeCell ref="G49:H49"/>
-    <mergeCell ref="D47:I47"/>
-    <mergeCell ref="D55:I55"/>
-    <mergeCell ref="G57:H57"/>
-    <mergeCell ref="D84:I84"/>
-    <mergeCell ref="D69:I69"/>
-    <mergeCell ref="D8:I8"/>
-    <mergeCell ref="D9:I9"/>
-    <mergeCell ref="D10:I10"/>
-    <mergeCell ref="D11:I11"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="D14:I14"/>
-    <mergeCell ref="G27:H27"/>
-    <mergeCell ref="D25:I25"/>
-    <mergeCell ref="G20:H20"/>
-    <mergeCell ref="D19:I19"/>
-    <mergeCell ref="D18:I18"/>
-    <mergeCell ref="D30:I30"/>
-    <mergeCell ref="G80:H80"/>
-    <mergeCell ref="G42:H42"/>
-    <mergeCell ref="D78:I78"/>
-    <mergeCell ref="G71:H71"/>
-    <mergeCell ref="D76:I76"/>
-    <mergeCell ref="D66:H66"/>
-    <mergeCell ref="D77:I77"/>
-    <mergeCell ref="D73:I73"/>
-    <mergeCell ref="D70:E70"/>
-    <mergeCell ref="D74:F74"/>
-    <mergeCell ref="D31:I31"/>
-    <mergeCell ref="G35:H35"/>
-    <mergeCell ref="D40:I40"/>
-    <mergeCell ref="D33:I33"/>
-    <mergeCell ref="D46:I46"/>
-    <mergeCell ref="D43:I43"/>
+    <mergeCell ref="D98:I98"/>
+    <mergeCell ref="D94:I94"/>
+    <mergeCell ref="H89:I89"/>
+    <mergeCell ref="D89:F89"/>
+    <mergeCell ref="D97:I97"/>
+    <mergeCell ref="D106:E106"/>
+    <mergeCell ref="D99:G99"/>
+    <mergeCell ref="G126:I126"/>
+    <mergeCell ref="F125:J125"/>
+    <mergeCell ref="D128:J128"/>
+    <mergeCell ref="D103:E103"/>
+    <mergeCell ref="D104:E104"/>
+    <mergeCell ref="D105:E105"/>
+    <mergeCell ref="G100:I100"/>
+    <mergeCell ref="B101:I101"/>
+    <mergeCell ref="F127:J127"/>
+    <mergeCell ref="D107:E107"/>
+    <mergeCell ref="F118:J118"/>
     <mergeCell ref="D108:E108"/>
     <mergeCell ref="B112:J113"/>
     <mergeCell ref="G124:J124"/>
-    <mergeCell ref="D120:H120"/>
-    <mergeCell ref="G123:J123"/>
-    <mergeCell ref="D121:J121"/>
-    <mergeCell ref="D143:J143"/>
-    <mergeCell ref="C177:J177"/>
-    <mergeCell ref="D135:J135"/>
-    <mergeCell ref="D172:J172"/>
-    <mergeCell ref="G146:J146"/>
-    <mergeCell ref="G152:I152"/>
-    <mergeCell ref="D149:J150"/>
-    <mergeCell ref="D187:J187"/>
-    <mergeCell ref="D185:J185"/>
-    <mergeCell ref="C175:J176"/>
-    <mergeCell ref="D164:J164"/>
-    <mergeCell ref="D157:J157"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/attendance_sheet.xlsx
+++ b/attendance_sheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\repositary\3rd_Year_5th_Semester\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CED02F2-9B1E-42FC-834F-A1703DFE790A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56CD425A-8727-4D13-8A91-840C5566A4BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{EB654061-A886-47D1-BF86-9B1A84FCE7FB}"/>
   </bookViews>
@@ -544,17 +544,35 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -572,24 +590,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -993,14 +993,14 @@
       <c r="C8" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D8" s="26" t="s">
+      <c r="D8" s="33" t="s">
         <v>20</v>
       </c>
-      <c r="E8" s="26"/>
-      <c r="F8" s="26"/>
-      <c r="G8" s="26"/>
-      <c r="H8" s="26"/>
-      <c r="I8" s="26"/>
+      <c r="E8" s="33"/>
+      <c r="F8" s="33"/>
+      <c r="G8" s="33"/>
+      <c r="H8" s="33"/>
+      <c r="I8" s="33"/>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B9" s="4">
@@ -1009,14 +1009,14 @@
       <c r="C9" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D9" s="26" t="s">
+      <c r="D9" s="33" t="s">
         <v>20</v>
       </c>
-      <c r="E9" s="26"/>
-      <c r="F9" s="26"/>
-      <c r="G9" s="26"/>
-      <c r="H9" s="26"/>
-      <c r="I9" s="26"/>
+      <c r="E9" s="33"/>
+      <c r="F9" s="33"/>
+      <c r="G9" s="33"/>
+      <c r="H9" s="33"/>
+      <c r="I9" s="33"/>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B10" s="4">
@@ -1025,14 +1025,14 @@
       <c r="C10" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D10" s="26" t="s">
+      <c r="D10" s="33" t="s">
         <v>20</v>
       </c>
-      <c r="E10" s="26"/>
-      <c r="F10" s="26"/>
-      <c r="G10" s="26"/>
-      <c r="H10" s="26"/>
-      <c r="I10" s="26"/>
+      <c r="E10" s="33"/>
+      <c r="F10" s="33"/>
+      <c r="G10" s="33"/>
+      <c r="H10" s="33"/>
+      <c r="I10" s="33"/>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B11" s="4">
@@ -1041,14 +1041,14 @@
       <c r="C11" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D11" s="26" t="s">
+      <c r="D11" s="33" t="s">
         <v>20</v>
       </c>
-      <c r="E11" s="26"/>
-      <c r="F11" s="26"/>
-      <c r="G11" s="26"/>
-      <c r="H11" s="26"/>
-      <c r="I11" s="26"/>
+      <c r="E11" s="33"/>
+      <c r="F11" s="33"/>
+      <c r="G11" s="33"/>
+      <c r="H11" s="33"/>
+      <c r="I11" s="33"/>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B12" s="4">
@@ -1092,10 +1092,10 @@
       <c r="F13" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="G13" s="26" t="s">
+      <c r="G13" s="33" t="s">
         <v>18</v>
       </c>
-      <c r="H13" s="26"/>
+      <c r="H13" s="33"/>
       <c r="I13" s="1" t="s">
         <v>14</v>
       </c>
@@ -1107,14 +1107,14 @@
       <c r="C14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D14" s="26" t="s">
+      <c r="D14" s="33" t="s">
         <v>19</v>
       </c>
-      <c r="E14" s="26"/>
-      <c r="F14" s="26"/>
-      <c r="G14" s="26"/>
-      <c r="H14" s="26"/>
-      <c r="I14" s="26"/>
+      <c r="E14" s="33"/>
+      <c r="F14" s="33"/>
+      <c r="G14" s="33"/>
+      <c r="H14" s="33"/>
+      <c r="I14" s="33"/>
     </row>
     <row r="15" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B15" s="4">
@@ -1201,14 +1201,14 @@
       <c r="C18" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D18" s="26" t="s">
+      <c r="D18" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="E18" s="26"/>
-      <c r="F18" s="26"/>
-      <c r="G18" s="26"/>
-      <c r="H18" s="26"/>
-      <c r="I18" s="26"/>
+      <c r="E18" s="33"/>
+      <c r="F18" s="33"/>
+      <c r="G18" s="33"/>
+      <c r="H18" s="33"/>
+      <c r="I18" s="33"/>
     </row>
     <row r="19" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B19" s="4">
@@ -1217,14 +1217,14 @@
       <c r="C19" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D19" s="26" t="s">
+      <c r="D19" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="E19" s="26"/>
-      <c r="F19" s="26"/>
-      <c r="G19" s="26"/>
-      <c r="H19" s="26"/>
-      <c r="I19" s="26"/>
+      <c r="E19" s="33"/>
+      <c r="F19" s="33"/>
+      <c r="G19" s="33"/>
+      <c r="H19" s="33"/>
+      <c r="I19" s="33"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B20" s="4">
@@ -1242,10 +1242,10 @@
       <c r="F20" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G20" s="26" t="s">
+      <c r="G20" s="33" t="s">
         <v>15</v>
       </c>
-      <c r="H20" s="26"/>
+      <c r="H20" s="33"/>
       <c r="I20" s="1" t="s">
         <v>14</v>
       </c>
@@ -1361,14 +1361,14 @@
       <c r="C25" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D25" s="26" t="s">
+      <c r="D25" s="33" t="s">
         <v>26</v>
       </c>
-      <c r="E25" s="26"/>
-      <c r="F25" s="26"/>
-      <c r="G25" s="26"/>
-      <c r="H25" s="26"/>
-      <c r="I25" s="26"/>
+      <c r="E25" s="33"/>
+      <c r="F25" s="33"/>
+      <c r="G25" s="33"/>
+      <c r="H25" s="33"/>
+      <c r="I25" s="33"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B26" s="4">
@@ -1412,10 +1412,10 @@
       <c r="F27" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G27" s="26" t="s">
+      <c r="G27" s="33" t="s">
         <v>18</v>
       </c>
-      <c r="H27" s="26"/>
+      <c r="H27" s="33"/>
       <c r="I27" s="1" t="s">
         <v>14</v>
       </c>
@@ -1479,14 +1479,14 @@
       <c r="C30" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D30" s="27" t="s">
+      <c r="D30" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="E30" s="27"/>
-      <c r="F30" s="27"/>
-      <c r="G30" s="27"/>
-      <c r="H30" s="27"/>
-      <c r="I30" s="27"/>
+      <c r="E30" s="32"/>
+      <c r="F30" s="32"/>
+      <c r="G30" s="32"/>
+      <c r="H30" s="32"/>
+      <c r="I30" s="32"/>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B31" s="4">
@@ -1495,14 +1495,14 @@
       <c r="C31" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D31" s="27" t="s">
+      <c r="D31" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="E31" s="27"/>
-      <c r="F31" s="27"/>
-      <c r="G31" s="27"/>
-      <c r="H31" s="27"/>
-      <c r="I31" s="27"/>
+      <c r="E31" s="32"/>
+      <c r="F31" s="32"/>
+      <c r="G31" s="32"/>
+      <c r="H31" s="32"/>
+      <c r="I31" s="32"/>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B32" s="4">
@@ -1537,14 +1537,14 @@
       <c r="C33" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D33" s="27" t="s">
+      <c r="D33" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="E33" s="27"/>
-      <c r="F33" s="27"/>
-      <c r="G33" s="27"/>
-      <c r="H33" s="27"/>
-      <c r="I33" s="27"/>
+      <c r="E33" s="32"/>
+      <c r="F33" s="32"/>
+      <c r="G33" s="32"/>
+      <c r="H33" s="32"/>
+      <c r="I33" s="32"/>
     </row>
     <row r="34" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B34" s="4">
@@ -1588,10 +1588,10 @@
       <c r="F35" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G35" s="27" t="s">
+      <c r="G35" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="H35" s="27"/>
+      <c r="H35" s="32"/>
       <c r="I35" s="1" t="s">
         <v>14</v>
       </c>
@@ -1707,14 +1707,14 @@
       <c r="C40" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D40" s="27" t="s">
+      <c r="D40" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="E40" s="27"/>
-      <c r="F40" s="27"/>
-      <c r="G40" s="27"/>
-      <c r="H40" s="27"/>
-      <c r="I40" s="27"/>
+      <c r="E40" s="32"/>
+      <c r="F40" s="32"/>
+      <c r="G40" s="32"/>
+      <c r="H40" s="32"/>
+      <c r="I40" s="32"/>
     </row>
     <row r="41" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B41" s="4">
@@ -1758,10 +1758,10 @@
       <c r="F42" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G42" s="27" t="s">
+      <c r="G42" s="32" t="s">
         <v>28</v>
       </c>
-      <c r="H42" s="27"/>
+      <c r="H42" s="32"/>
       <c r="I42" s="1" t="s">
         <v>15</v>
       </c>
@@ -1773,14 +1773,14 @@
       <c r="C43" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D43" s="27" t="s">
+      <c r="D43" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="E43" s="27"/>
-      <c r="F43" s="27"/>
-      <c r="G43" s="27"/>
-      <c r="H43" s="27"/>
-      <c r="I43" s="27"/>
+      <c r="E43" s="32"/>
+      <c r="F43" s="32"/>
+      <c r="G43" s="32"/>
+      <c r="H43" s="32"/>
+      <c r="I43" s="32"/>
     </row>
     <row r="44" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B44" s="4">
@@ -1844,14 +1844,14 @@
       <c r="C46" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D46" s="27" t="s">
+      <c r="D46" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="E46" s="27"/>
-      <c r="F46" s="27"/>
-      <c r="G46" s="27"/>
-      <c r="H46" s="27"/>
-      <c r="I46" s="27"/>
+      <c r="E46" s="32"/>
+      <c r="F46" s="32"/>
+      <c r="G46" s="32"/>
+      <c r="H46" s="32"/>
+      <c r="I46" s="32"/>
     </row>
     <row r="47" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B47" s="4">
@@ -1863,11 +1863,11 @@
       <c r="D47" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E47" s="25"/>
-      <c r="F47" s="25"/>
-      <c r="G47" s="25"/>
-      <c r="H47" s="25"/>
-      <c r="I47" s="24"/>
+      <c r="E47" s="24"/>
+      <c r="F47" s="24"/>
+      <c r="G47" s="24"/>
+      <c r="H47" s="24"/>
+      <c r="I47" s="25"/>
     </row>
     <row r="48" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B48" s="4">
@@ -1914,7 +1914,7 @@
       <c r="G49" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="H49" s="24"/>
+      <c r="H49" s="25"/>
       <c r="I49" s="1" t="s">
         <v>30</v>
       </c>
@@ -2056,14 +2056,14 @@
       <c r="C55" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="D55" s="25" t="s">
+      <c r="D55" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="E55" s="25"/>
-      <c r="F55" s="25"/>
-      <c r="G55" s="25"/>
-      <c r="H55" s="25"/>
-      <c r="I55" s="25"/>
+      <c r="E55" s="24"/>
+      <c r="F55" s="24"/>
+      <c r="G55" s="24"/>
+      <c r="H55" s="24"/>
+      <c r="I55" s="24"/>
     </row>
     <row r="56" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B56" s="4">
@@ -2110,7 +2110,7 @@
       <c r="G57" s="23" t="s">
         <v>37</v>
       </c>
-      <c r="H57" s="24"/>
+      <c r="H57" s="25"/>
       <c r="I57" s="1" t="s">
         <v>36</v>
       </c>
@@ -2177,11 +2177,11 @@
       <c r="D60" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E60" s="25"/>
-      <c r="F60" s="25"/>
-      <c r="G60" s="25"/>
-      <c r="H60" s="25"/>
-      <c r="I60" s="24"/>
+      <c r="E60" s="24"/>
+      <c r="F60" s="24"/>
+      <c r="G60" s="24"/>
+      <c r="H60" s="24"/>
+      <c r="I60" s="25"/>
     </row>
     <row r="61" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B61" s="4">
@@ -2193,11 +2193,11 @@
       <c r="D61" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E61" s="25"/>
-      <c r="F61" s="25"/>
-      <c r="G61" s="25"/>
-      <c r="H61" s="25"/>
-      <c r="I61" s="24"/>
+      <c r="E61" s="24"/>
+      <c r="F61" s="24"/>
+      <c r="G61" s="24"/>
+      <c r="H61" s="24"/>
+      <c r="I61" s="25"/>
     </row>
     <row r="62" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B62" s="4">
@@ -2209,11 +2209,11 @@
       <c r="D62" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E62" s="25"/>
-      <c r="F62" s="25"/>
-      <c r="G62" s="25"/>
-      <c r="H62" s="25"/>
-      <c r="I62" s="24"/>
+      <c r="E62" s="24"/>
+      <c r="F62" s="24"/>
+      <c r="G62" s="24"/>
+      <c r="H62" s="24"/>
+      <c r="I62" s="25"/>
     </row>
     <row r="63" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B63" s="4">
@@ -2260,7 +2260,7 @@
       <c r="G64" s="23" t="s">
         <v>37</v>
       </c>
-      <c r="H64" s="24"/>
+      <c r="H64" s="25"/>
       <c r="I64" s="1" t="s">
         <v>14</v>
       </c>
@@ -2301,10 +2301,10 @@
       <c r="D66" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="E66" s="25"/>
-      <c r="F66" s="25"/>
-      <c r="G66" s="25"/>
-      <c r="H66" s="24"/>
+      <c r="E66" s="24"/>
+      <c r="F66" s="24"/>
+      <c r="G66" s="24"/>
+      <c r="H66" s="25"/>
       <c r="I66" s="1" t="s">
         <v>16</v>
       </c>
@@ -2319,15 +2319,15 @@
       <c r="D67" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="E67" s="25"/>
-      <c r="F67" s="24"/>
+      <c r="E67" s="24"/>
+      <c r="F67" s="25"/>
       <c r="G67" s="3" t="s">
         <v>16</v>
       </c>
       <c r="H67" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="I67" s="24"/>
+      <c r="I67" s="25"/>
     </row>
     <row r="68" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B68" s="4">
@@ -2345,9 +2345,9 @@
       <c r="F68" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="G68" s="25"/>
-      <c r="H68" s="25"/>
-      <c r="I68" s="24"/>
+      <c r="G68" s="24"/>
+      <c r="H68" s="24"/>
+      <c r="I68" s="25"/>
     </row>
     <row r="69" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B69" s="4">
@@ -2359,11 +2359,11 @@
       <c r="D69" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E69" s="25"/>
-      <c r="F69" s="25"/>
-      <c r="G69" s="25"/>
-      <c r="H69" s="25"/>
-      <c r="I69" s="24"/>
+      <c r="E69" s="24"/>
+      <c r="F69" s="24"/>
+      <c r="G69" s="24"/>
+      <c r="H69" s="24"/>
+      <c r="I69" s="25"/>
     </row>
     <row r="70" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B70" s="4">
@@ -2375,7 +2375,7 @@
       <c r="D70" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="E70" s="24"/>
+      <c r="E70" s="25"/>
       <c r="F70" s="3" t="s">
         <v>15</v>
       </c>
@@ -2408,7 +2408,7 @@
       <c r="G71" s="23" t="s">
         <v>37</v>
       </c>
-      <c r="H71" s="24"/>
+      <c r="H71" s="25"/>
       <c r="I71" s="1" t="s">
         <v>14</v>
       </c>
@@ -2449,11 +2449,11 @@
       <c r="D73" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E73" s="25"/>
-      <c r="F73" s="25"/>
-      <c r="G73" s="25"/>
-      <c r="H73" s="25"/>
-      <c r="I73" s="24"/>
+      <c r="E73" s="24"/>
+      <c r="F73" s="24"/>
+      <c r="G73" s="24"/>
+      <c r="H73" s="24"/>
+      <c r="I73" s="25"/>
     </row>
     <row r="74" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B74" s="4">
@@ -2465,8 +2465,8 @@
       <c r="D74" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="E74" s="25"/>
-      <c r="F74" s="24"/>
+      <c r="E74" s="24"/>
+      <c r="F74" s="25"/>
       <c r="G74" s="3" t="s">
         <v>16</v>
       </c>
@@ -2505,11 +2505,11 @@
       <c r="D76" s="23" t="s">
         <v>39</v>
       </c>
-      <c r="E76" s="25"/>
-      <c r="F76" s="25"/>
-      <c r="G76" s="25"/>
-      <c r="H76" s="25"/>
-      <c r="I76" s="24"/>
+      <c r="E76" s="24"/>
+      <c r="F76" s="24"/>
+      <c r="G76" s="24"/>
+      <c r="H76" s="24"/>
+      <c r="I76" s="25"/>
     </row>
     <row r="77" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B77" s="4">
@@ -2521,11 +2521,11 @@
       <c r="D77" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E77" s="25"/>
-      <c r="F77" s="25"/>
-      <c r="G77" s="25"/>
-      <c r="H77" s="25"/>
-      <c r="I77" s="24"/>
+      <c r="E77" s="24"/>
+      <c r="F77" s="24"/>
+      <c r="G77" s="24"/>
+      <c r="H77" s="24"/>
+      <c r="I77" s="25"/>
     </row>
     <row r="78" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B78" s="4">
@@ -2537,11 +2537,11 @@
       <c r="D78" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E78" s="25"/>
-      <c r="F78" s="25"/>
-      <c r="G78" s="25"/>
-      <c r="H78" s="25"/>
-      <c r="I78" s="24"/>
+      <c r="E78" s="24"/>
+      <c r="F78" s="24"/>
+      <c r="G78" s="24"/>
+      <c r="H78" s="24"/>
+      <c r="I78" s="25"/>
     </row>
     <row r="79" spans="2:9" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B79" s="16" t="s">
@@ -2588,7 +2588,7 @@
       <c r="G80" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="H80" s="24"/>
+      <c r="H80" s="25"/>
       <c r="I80" s="1" t="s">
         <v>14</v>
       </c>
@@ -2612,7 +2612,7 @@
       <c r="G81" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="H81" s="24"/>
+      <c r="H81" s="25"/>
       <c r="I81" s="1" t="s">
         <v>16</v>
       </c>
@@ -2679,11 +2679,11 @@
       <c r="D84" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E84" s="25"/>
-      <c r="F84" s="25"/>
-      <c r="G84" s="25"/>
-      <c r="H84" s="25"/>
-      <c r="I84" s="24"/>
+      <c r="E84" s="24"/>
+      <c r="F84" s="24"/>
+      <c r="G84" s="24"/>
+      <c r="H84" s="24"/>
+      <c r="I84" s="25"/>
     </row>
     <row r="85" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B85" s="4">
@@ -2724,8 +2724,8 @@
       <c r="E86" s="23" t="s">
         <v>43</v>
       </c>
-      <c r="F86" s="25"/>
-      <c r="G86" s="24"/>
+      <c r="F86" s="24"/>
+      <c r="G86" s="25"/>
       <c r="H86" s="3" t="s">
         <v>14</v>
       </c>
@@ -2743,15 +2743,15 @@
       <c r="D87" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="E87" s="24"/>
+      <c r="E87" s="25"/>
       <c r="F87" s="3" t="s">
         <v>16</v>
       </c>
       <c r="G87" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="H87" s="25"/>
-      <c r="I87" s="24"/>
+      <c r="H87" s="24"/>
+      <c r="I87" s="25"/>
     </row>
     <row r="88" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B88" s="4">
@@ -2763,11 +2763,11 @@
       <c r="D88" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E88" s="25"/>
-      <c r="F88" s="25"/>
-      <c r="G88" s="25"/>
-      <c r="H88" s="25"/>
-      <c r="I88" s="24"/>
+      <c r="E88" s="24"/>
+      <c r="F88" s="24"/>
+      <c r="G88" s="24"/>
+      <c r="H88" s="24"/>
+      <c r="I88" s="25"/>
     </row>
     <row r="89" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B89" s="4">
@@ -2779,15 +2779,15 @@
       <c r="D89" s="23" t="s">
         <v>44</v>
       </c>
-      <c r="E89" s="25"/>
-      <c r="F89" s="24"/>
+      <c r="E89" s="24"/>
+      <c r="F89" s="25"/>
       <c r="G89" s="3" t="s">
         <v>16</v>
       </c>
       <c r="H89" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="I89" s="24"/>
+      <c r="I89" s="25"/>
     </row>
     <row r="90" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B90" s="4">
@@ -2799,7 +2799,7 @@
       <c r="D90" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="E90" s="24"/>
+      <c r="E90" s="25"/>
       <c r="F90" s="3" t="s">
         <v>16</v>
       </c>
@@ -2824,10 +2824,10 @@
       <c r="D91" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E91" s="25"/>
-      <c r="F91" s="25"/>
-      <c r="G91" s="25"/>
-      <c r="H91" s="24"/>
+      <c r="E91" s="24"/>
+      <c r="F91" s="24"/>
+      <c r="G91" s="24"/>
+      <c r="H91" s="25"/>
       <c r="I91" s="18" t="s">
         <v>45</v>
       </c>
@@ -2842,11 +2842,11 @@
       <c r="D92" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E92" s="25"/>
-      <c r="F92" s="25"/>
-      <c r="G92" s="25"/>
-      <c r="H92" s="25"/>
-      <c r="I92" s="24"/>
+      <c r="E92" s="24"/>
+      <c r="F92" s="24"/>
+      <c r="G92" s="24"/>
+      <c r="H92" s="24"/>
+      <c r="I92" s="25"/>
     </row>
     <row r="93" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B93" s="4">
@@ -2858,11 +2858,11 @@
       <c r="D93" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="E93" s="25"/>
-      <c r="F93" s="25"/>
-      <c r="G93" s="25"/>
-      <c r="H93" s="25"/>
-      <c r="I93" s="24"/>
+      <c r="E93" s="24"/>
+      <c r="F93" s="24"/>
+      <c r="G93" s="24"/>
+      <c r="H93" s="24"/>
+      <c r="I93" s="25"/>
     </row>
     <row r="94" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B94" s="4">
@@ -2874,11 +2874,11 @@
       <c r="D94" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="E94" s="25"/>
-      <c r="F94" s="25"/>
-      <c r="G94" s="25"/>
-      <c r="H94" s="25"/>
-      <c r="I94" s="24"/>
+      <c r="E94" s="24"/>
+      <c r="F94" s="24"/>
+      <c r="G94" s="24"/>
+      <c r="H94" s="24"/>
+      <c r="I94" s="25"/>
     </row>
     <row r="95" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B95" s="4">
@@ -2890,12 +2890,12 @@
       <c r="D95" s="23" t="s">
         <v>47</v>
       </c>
-      <c r="E95" s="25"/>
-      <c r="F95" s="24"/>
+      <c r="E95" s="24"/>
+      <c r="F95" s="25"/>
       <c r="G95" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="H95" s="24"/>
+      <c r="H95" s="25"/>
       <c r="I95" s="1" t="s">
         <v>14</v>
       </c>
@@ -2910,11 +2910,11 @@
       <c r="D96" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E96" s="25"/>
-      <c r="F96" s="25"/>
-      <c r="G96" s="25"/>
-      <c r="H96" s="25"/>
-      <c r="I96" s="24"/>
+      <c r="E96" s="24"/>
+      <c r="F96" s="24"/>
+      <c r="G96" s="24"/>
+      <c r="H96" s="24"/>
+      <c r="I96" s="25"/>
     </row>
     <row r="97" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B97" s="4">
@@ -2926,11 +2926,11 @@
       <c r="D97" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="E97" s="25"/>
-      <c r="F97" s="25"/>
-      <c r="G97" s="25"/>
-      <c r="H97" s="25"/>
-      <c r="I97" s="24"/>
+      <c r="E97" s="24"/>
+      <c r="F97" s="24"/>
+      <c r="G97" s="24"/>
+      <c r="H97" s="24"/>
+      <c r="I97" s="25"/>
     </row>
     <row r="98" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B98" s="4">
@@ -2942,11 +2942,11 @@
       <c r="D98" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E98" s="25"/>
-      <c r="F98" s="25"/>
-      <c r="G98" s="25"/>
-      <c r="H98" s="25"/>
-      <c r="I98" s="24"/>
+      <c r="E98" s="24"/>
+      <c r="F98" s="24"/>
+      <c r="G98" s="24"/>
+      <c r="H98" s="24"/>
+      <c r="I98" s="25"/>
     </row>
     <row r="99" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B99" s="4">
@@ -2958,9 +2958,9 @@
       <c r="D99" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="E99" s="25"/>
-      <c r="F99" s="25"/>
-      <c r="G99" s="24"/>
+      <c r="E99" s="24"/>
+      <c r="F99" s="24"/>
+      <c r="G99" s="25"/>
       <c r="H99" s="3" t="s">
         <v>49</v>
       </c>
@@ -2987,18 +2987,18 @@
       <c r="G100" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="H100" s="25"/>
-      <c r="I100" s="24"/>
+      <c r="H100" s="24"/>
+      <c r="I100" s="25"/>
     </row>
     <row r="101" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B101" s="23"/>
-      <c r="C101" s="25"/>
-      <c r="D101" s="25"/>
-      <c r="E101" s="25"/>
-      <c r="F101" s="25"/>
-      <c r="G101" s="25"/>
-      <c r="H101" s="25"/>
-      <c r="I101" s="24"/>
+      <c r="C101" s="24"/>
+      <c r="D101" s="24"/>
+      <c r="E101" s="24"/>
+      <c r="F101" s="24"/>
+      <c r="G101" s="24"/>
+      <c r="H101" s="24"/>
+      <c r="I101" s="25"/>
     </row>
     <row r="102" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B102" s="3"/>
@@ -3020,7 +3020,7 @@
       <c r="D103" s="23" t="s">
         <v>51</v>
       </c>
-      <c r="E103" s="24"/>
+      <c r="E103" s="25"/>
       <c r="F103" s="3"/>
       <c r="G103" s="3"/>
       <c r="H103" s="3"/>
@@ -3036,7 +3036,7 @@
       <c r="D104" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="E104" s="24"/>
+      <c r="E104" s="25"/>
       <c r="F104" s="3"/>
       <c r="G104" s="3"/>
       <c r="H104" s="3"/>
@@ -3052,7 +3052,7 @@
       <c r="D105" s="23" t="s">
         <v>53</v>
       </c>
-      <c r="E105" s="24"/>
+      <c r="E105" s="25"/>
       <c r="F105" s="3"/>
       <c r="G105" s="3"/>
       <c r="H105" s="3"/>
@@ -3068,7 +3068,7 @@
       <c r="D106" s="23" t="s">
         <v>54</v>
       </c>
-      <c r="E106" s="24"/>
+      <c r="E106" s="25"/>
       <c r="F106" s="3"/>
       <c r="G106" s="3"/>
       <c r="H106" s="3"/>
@@ -3084,7 +3084,7 @@
       <c r="D107" s="23" t="s">
         <v>55</v>
       </c>
-      <c r="E107" s="24"/>
+      <c r="E107" s="25"/>
       <c r="F107" s="3"/>
       <c r="G107" s="3"/>
       <c r="H107" s="3"/>
@@ -3100,7 +3100,7 @@
       <c r="D108" s="23" t="s">
         <v>56</v>
       </c>
-      <c r="E108" s="24"/>
+      <c r="E108" s="25"/>
       <c r="F108" s="3"/>
       <c r="G108" s="3"/>
       <c r="H108" s="3"/>
@@ -3137,28 +3137,28 @@
       <c r="I111" s="20"/>
     </row>
     <row r="112" spans="2:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B112" s="28" t="s">
+      <c r="B112" s="34" t="s">
         <v>57</v>
       </c>
-      <c r="C112" s="29"/>
-      <c r="D112" s="29"/>
-      <c r="E112" s="29"/>
-      <c r="F112" s="29"/>
-      <c r="G112" s="29"/>
-      <c r="H112" s="29"/>
-      <c r="I112" s="29"/>
-      <c r="J112" s="30"/>
+      <c r="C112" s="35"/>
+      <c r="D112" s="35"/>
+      <c r="E112" s="35"/>
+      <c r="F112" s="35"/>
+      <c r="G112" s="35"/>
+      <c r="H112" s="35"/>
+      <c r="I112" s="35"/>
+      <c r="J112" s="36"/>
     </row>
     <row r="113" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B113" s="31"/>
-      <c r="C113" s="32"/>
-      <c r="D113" s="32"/>
-      <c r="E113" s="32"/>
-      <c r="F113" s="32"/>
-      <c r="G113" s="32"/>
-      <c r="H113" s="32"/>
-      <c r="I113" s="32"/>
-      <c r="J113" s="33"/>
+      <c r="B113" s="37"/>
+      <c r="C113" s="38"/>
+      <c r="D113" s="38"/>
+      <c r="E113" s="38"/>
+      <c r="F113" s="38"/>
+      <c r="G113" s="38"/>
+      <c r="H113" s="38"/>
+      <c r="I113" s="38"/>
+      <c r="J113" s="39"/>
     </row>
     <row r="114" spans="2:10" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B114" s="8" t="s">
@@ -3292,10 +3292,10 @@
       <c r="F118" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="G118" s="25"/>
-      <c r="H118" s="25"/>
-      <c r="I118" s="25"/>
-      <c r="J118" s="24"/>
+      <c r="G118" s="24"/>
+      <c r="H118" s="24"/>
+      <c r="I118" s="24"/>
+      <c r="J118" s="25"/>
     </row>
     <row r="119" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B119" s="4">
@@ -3336,10 +3336,10 @@
       <c r="D120" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="E120" s="25"/>
-      <c r="F120" s="25"/>
-      <c r="G120" s="25"/>
-      <c r="H120" s="24"/>
+      <c r="E120" s="24"/>
+      <c r="F120" s="24"/>
+      <c r="G120" s="24"/>
+      <c r="H120" s="25"/>
       <c r="I120" s="1" t="s">
         <v>16</v>
       </c>
@@ -3357,12 +3357,12 @@
       <c r="D121" s="23" t="s">
         <v>65</v>
       </c>
-      <c r="E121" s="25"/>
-      <c r="F121" s="25"/>
-      <c r="G121" s="25"/>
-      <c r="H121" s="25"/>
-      <c r="I121" s="25"/>
-      <c r="J121" s="24"/>
+      <c r="E121" s="24"/>
+      <c r="F121" s="24"/>
+      <c r="G121" s="24"/>
+      <c r="H121" s="24"/>
+      <c r="I121" s="24"/>
+      <c r="J121" s="25"/>
     </row>
     <row r="122" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B122" s="4">
@@ -3412,9 +3412,9 @@
       <c r="G123" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="H123" s="25"/>
-      <c r="I123" s="25"/>
-      <c r="J123" s="24"/>
+      <c r="H123" s="24"/>
+      <c r="I123" s="24"/>
+      <c r="J123" s="25"/>
     </row>
     <row r="124" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B124" s="4">
@@ -3435,9 +3435,9 @@
       <c r="G124" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="H124" s="25"/>
-      <c r="I124" s="25"/>
-      <c r="J124" s="24"/>
+      <c r="H124" s="24"/>
+      <c r="I124" s="24"/>
+      <c r="J124" s="25"/>
     </row>
     <row r="125" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B125" s="4">
@@ -3455,10 +3455,10 @@
       <c r="F125" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="G125" s="25"/>
-      <c r="H125" s="25"/>
-      <c r="I125" s="25"/>
-      <c r="J125" s="24"/>
+      <c r="G125" s="24"/>
+      <c r="H125" s="24"/>
+      <c r="I125" s="24"/>
+      <c r="J125" s="25"/>
     </row>
     <row r="126" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B126" s="4">
@@ -3479,8 +3479,8 @@
       <c r="G126" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="H126" s="25"/>
-      <c r="I126" s="24"/>
+      <c r="H126" s="24"/>
+      <c r="I126" s="25"/>
       <c r="J126" s="1" t="s">
         <v>16</v>
       </c>
@@ -3501,10 +3501,10 @@
       <c r="F127" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="G127" s="25"/>
-      <c r="H127" s="25"/>
-      <c r="I127" s="25"/>
-      <c r="J127" s="24"/>
+      <c r="G127" s="24"/>
+      <c r="H127" s="24"/>
+      <c r="I127" s="24"/>
+      <c r="J127" s="25"/>
     </row>
     <row r="128" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B128" s="4">
@@ -3516,12 +3516,12 @@
       <c r="D128" s="23" t="s">
         <v>65</v>
       </c>
-      <c r="E128" s="25"/>
-      <c r="F128" s="25"/>
-      <c r="G128" s="25"/>
-      <c r="H128" s="25"/>
-      <c r="I128" s="25"/>
-      <c r="J128" s="24"/>
+      <c r="E128" s="24"/>
+      <c r="F128" s="24"/>
+      <c r="G128" s="24"/>
+      <c r="H128" s="24"/>
+      <c r="I128" s="24"/>
+      <c r="J128" s="25"/>
     </row>
     <row r="129" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B129" s="4">
@@ -3707,12 +3707,12 @@
       <c r="D135" s="23" t="s">
         <v>65</v>
       </c>
-      <c r="E135" s="25"/>
-      <c r="F135" s="25"/>
-      <c r="G135" s="25"/>
-      <c r="H135" s="25"/>
-      <c r="I135" s="25"/>
-      <c r="J135" s="24"/>
+      <c r="E135" s="24"/>
+      <c r="F135" s="24"/>
+      <c r="G135" s="24"/>
+      <c r="H135" s="24"/>
+      <c r="I135" s="24"/>
+      <c r="J135" s="25"/>
     </row>
     <row r="136" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B136" s="4">
@@ -3927,12 +3927,12 @@
       <c r="D143" s="23" t="s">
         <v>65</v>
       </c>
-      <c r="E143" s="25"/>
-      <c r="F143" s="25"/>
-      <c r="G143" s="25"/>
-      <c r="H143" s="25"/>
-      <c r="I143" s="25"/>
-      <c r="J143" s="24"/>
+      <c r="E143" s="24"/>
+      <c r="F143" s="24"/>
+      <c r="G143" s="24"/>
+      <c r="H143" s="24"/>
+      <c r="I143" s="24"/>
+      <c r="J143" s="25"/>
     </row>
     <row r="144" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B144" s="4">
@@ -4011,9 +4011,9 @@
       <c r="G146" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="H146" s="25"/>
-      <c r="I146" s="25"/>
-      <c r="J146" s="24"/>
+      <c r="H146" s="24"/>
+      <c r="I146" s="24"/>
+      <c r="J146" s="25"/>
     </row>
     <row r="147" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B147" s="4">
@@ -4080,15 +4080,15 @@
       <c r="C149" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D149" s="34" t="s">
+      <c r="D149" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="E149" s="35"/>
-      <c r="F149" s="35"/>
-      <c r="G149" s="35"/>
-      <c r="H149" s="35"/>
-      <c r="I149" s="35"/>
-      <c r="J149" s="36"/>
+      <c r="E149" s="27"/>
+      <c r="F149" s="27"/>
+      <c r="G149" s="27"/>
+      <c r="H149" s="27"/>
+      <c r="I149" s="27"/>
+      <c r="J149" s="30"/>
     </row>
     <row r="150" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B150" s="4">
@@ -4097,13 +4097,13 @@
       <c r="C150" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D150" s="37"/>
-      <c r="E150" s="38"/>
-      <c r="F150" s="38"/>
-      <c r="G150" s="38"/>
-      <c r="H150" s="38"/>
-      <c r="I150" s="38"/>
-      <c r="J150" s="39"/>
+      <c r="D150" s="28"/>
+      <c r="E150" s="29"/>
+      <c r="F150" s="29"/>
+      <c r="G150" s="29"/>
+      <c r="H150" s="29"/>
+      <c r="I150" s="29"/>
+      <c r="J150" s="31"/>
     </row>
     <row r="151" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B151" s="4">
@@ -4153,8 +4153,8 @@
       <c r="G152" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="H152" s="25"/>
-      <c r="I152" s="24"/>
+      <c r="H152" s="24"/>
+      <c r="I152" s="25"/>
       <c r="J152" s="1" t="s">
         <v>69</v>
       </c>
@@ -4285,12 +4285,12 @@
       <c r="D157" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E157" s="25"/>
-      <c r="F157" s="25"/>
-      <c r="G157" s="25"/>
-      <c r="H157" s="25"/>
-      <c r="I157" s="25"/>
-      <c r="J157" s="24"/>
+      <c r="E157" s="24"/>
+      <c r="F157" s="24"/>
+      <c r="G157" s="24"/>
+      <c r="H157" s="24"/>
+      <c r="I157" s="24"/>
+      <c r="J157" s="25"/>
     </row>
     <row r="158" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B158" s="4">
@@ -4474,12 +4474,12 @@
       <c r="D164" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E164" s="25"/>
-      <c r="F164" s="25"/>
-      <c r="G164" s="25"/>
-      <c r="H164" s="25"/>
-      <c r="I164" s="25"/>
-      <c r="J164" s="24"/>
+      <c r="E164" s="24"/>
+      <c r="F164" s="24"/>
+      <c r="G164" s="24"/>
+      <c r="H164" s="24"/>
+      <c r="I164" s="24"/>
+      <c r="J164" s="25"/>
     </row>
     <row r="165" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B165" s="4">
@@ -4680,12 +4680,12 @@
       <c r="D172" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E172" s="25"/>
-      <c r="F172" s="25"/>
-      <c r="G172" s="25"/>
-      <c r="H172" s="25"/>
-      <c r="I172" s="25"/>
-      <c r="J172" s="24"/>
+      <c r="E172" s="24"/>
+      <c r="F172" s="24"/>
+      <c r="G172" s="24"/>
+      <c r="H172" s="24"/>
+      <c r="I172" s="24"/>
+      <c r="J172" s="25"/>
     </row>
     <row r="173" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B173" s="4">
@@ -4749,29 +4749,29 @@
       <c r="B175" s="4">
         <v>45903</v>
       </c>
-      <c r="C175" s="34" t="s">
+      <c r="C175" s="26" t="s">
         <v>39</v>
       </c>
-      <c r="D175" s="35"/>
-      <c r="E175" s="35"/>
-      <c r="F175" s="35"/>
-      <c r="G175" s="35"/>
-      <c r="H175" s="35"/>
-      <c r="I175" s="35"/>
-      <c r="J175" s="35"/>
+      <c r="D175" s="27"/>
+      <c r="E175" s="27"/>
+      <c r="F175" s="27"/>
+      <c r="G175" s="27"/>
+      <c r="H175" s="27"/>
+      <c r="I175" s="27"/>
+      <c r="J175" s="27"/>
     </row>
     <row r="176" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B176" s="4">
         <v>45904</v>
       </c>
-      <c r="C176" s="37"/>
-      <c r="D176" s="38"/>
-      <c r="E176" s="38"/>
-      <c r="F176" s="38"/>
-      <c r="G176" s="38"/>
-      <c r="H176" s="38"/>
-      <c r="I176" s="38"/>
-      <c r="J176" s="38"/>
+      <c r="C176" s="28"/>
+      <c r="D176" s="29"/>
+      <c r="E176" s="29"/>
+      <c r="F176" s="29"/>
+      <c r="G176" s="29"/>
+      <c r="H176" s="29"/>
+      <c r="I176" s="29"/>
+      <c r="J176" s="29"/>
     </row>
     <row r="177" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B177" s="4">
@@ -4780,13 +4780,13 @@
       <c r="C177" s="23" t="s">
         <v>39</v>
       </c>
-      <c r="D177" s="25"/>
-      <c r="E177" s="25"/>
-      <c r="F177" s="25"/>
-      <c r="G177" s="25"/>
-      <c r="H177" s="25"/>
-      <c r="I177" s="25"/>
-      <c r="J177" s="24"/>
+      <c r="D177" s="24"/>
+      <c r="E177" s="24"/>
+      <c r="F177" s="24"/>
+      <c r="G177" s="24"/>
+      <c r="H177" s="24"/>
+      <c r="I177" s="24"/>
+      <c r="J177" s="25"/>
     </row>
     <row r="178" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B178" s="4">
@@ -4985,12 +4985,12 @@
       <c r="D185" s="23" t="s">
         <v>74</v>
       </c>
-      <c r="E185" s="25"/>
-      <c r="F185" s="25"/>
-      <c r="G185" s="25"/>
-      <c r="H185" s="25"/>
-      <c r="I185" s="25"/>
-      <c r="J185" s="24"/>
+      <c r="E185" s="24"/>
+      <c r="F185" s="24"/>
+      <c r="G185" s="24"/>
+      <c r="H185" s="24"/>
+      <c r="I185" s="24"/>
+      <c r="J185" s="25"/>
     </row>
     <row r="186" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B186" s="4">
@@ -5021,12 +5021,12 @@
       <c r="D187" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="E187" s="25"/>
-      <c r="F187" s="25"/>
-      <c r="G187" s="25"/>
-      <c r="H187" s="25"/>
-      <c r="I187" s="25"/>
-      <c r="J187" s="24"/>
+      <c r="E187" s="24"/>
+      <c r="F187" s="24"/>
+      <c r="G187" s="24"/>
+      <c r="H187" s="24"/>
+      <c r="I187" s="24"/>
+      <c r="J187" s="25"/>
     </row>
     <row r="188" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B188" s="3"/>
@@ -7549,35 +7549,50 @@
     </row>
   </sheetData>
   <mergeCells count="89">
-    <mergeCell ref="D187:J187"/>
-    <mergeCell ref="D185:J185"/>
-    <mergeCell ref="C175:J176"/>
-    <mergeCell ref="D164:J164"/>
-    <mergeCell ref="D157:J157"/>
-    <mergeCell ref="D120:H120"/>
-    <mergeCell ref="G123:J123"/>
-    <mergeCell ref="D121:J121"/>
-    <mergeCell ref="D143:J143"/>
-    <mergeCell ref="C177:J177"/>
-    <mergeCell ref="D135:J135"/>
-    <mergeCell ref="D172:J172"/>
-    <mergeCell ref="G146:J146"/>
-    <mergeCell ref="G152:I152"/>
-    <mergeCell ref="D149:J150"/>
-    <mergeCell ref="D31:I31"/>
-    <mergeCell ref="G35:H35"/>
-    <mergeCell ref="D40:I40"/>
-    <mergeCell ref="D33:I33"/>
-    <mergeCell ref="D46:I46"/>
-    <mergeCell ref="D43:I43"/>
-    <mergeCell ref="D78:I78"/>
-    <mergeCell ref="G71:H71"/>
-    <mergeCell ref="D76:I76"/>
-    <mergeCell ref="D66:H66"/>
-    <mergeCell ref="D77:I77"/>
-    <mergeCell ref="D73:I73"/>
-    <mergeCell ref="D70:E70"/>
-    <mergeCell ref="D74:F74"/>
+    <mergeCell ref="D106:E106"/>
+    <mergeCell ref="D99:G99"/>
+    <mergeCell ref="G126:I126"/>
+    <mergeCell ref="F125:J125"/>
+    <mergeCell ref="D128:J128"/>
+    <mergeCell ref="D103:E103"/>
+    <mergeCell ref="D104:E104"/>
+    <mergeCell ref="D105:E105"/>
+    <mergeCell ref="G100:I100"/>
+    <mergeCell ref="B101:I101"/>
+    <mergeCell ref="F127:J127"/>
+    <mergeCell ref="D107:E107"/>
+    <mergeCell ref="F118:J118"/>
+    <mergeCell ref="D108:E108"/>
+    <mergeCell ref="B112:J113"/>
+    <mergeCell ref="G124:J124"/>
+    <mergeCell ref="D98:I98"/>
+    <mergeCell ref="D94:I94"/>
+    <mergeCell ref="H89:I89"/>
+    <mergeCell ref="D89:F89"/>
+    <mergeCell ref="D97:I97"/>
+    <mergeCell ref="G64:H64"/>
+    <mergeCell ref="D96:I96"/>
+    <mergeCell ref="D95:F95"/>
+    <mergeCell ref="G95:H95"/>
+    <mergeCell ref="D92:I92"/>
+    <mergeCell ref="D93:I93"/>
+    <mergeCell ref="D90:E90"/>
+    <mergeCell ref="D91:H91"/>
+    <mergeCell ref="E86:G86"/>
+    <mergeCell ref="D88:I88"/>
+    <mergeCell ref="H67:I67"/>
+    <mergeCell ref="G81:H81"/>
+    <mergeCell ref="D67:F67"/>
+    <mergeCell ref="F68:I68"/>
+    <mergeCell ref="D87:E87"/>
+    <mergeCell ref="G87:I87"/>
+    <mergeCell ref="D60:I60"/>
+    <mergeCell ref="D62:I62"/>
+    <mergeCell ref="D61:I61"/>
+    <mergeCell ref="G49:H49"/>
+    <mergeCell ref="D47:I47"/>
+    <mergeCell ref="D55:I55"/>
+    <mergeCell ref="G57:H57"/>
     <mergeCell ref="D84:I84"/>
     <mergeCell ref="D69:I69"/>
     <mergeCell ref="D8:I8"/>
@@ -7594,50 +7609,35 @@
     <mergeCell ref="D30:I30"/>
     <mergeCell ref="G80:H80"/>
     <mergeCell ref="G42:H42"/>
-    <mergeCell ref="D60:I60"/>
-    <mergeCell ref="D62:I62"/>
-    <mergeCell ref="D61:I61"/>
-    <mergeCell ref="G49:H49"/>
-    <mergeCell ref="D47:I47"/>
-    <mergeCell ref="D55:I55"/>
-    <mergeCell ref="G57:H57"/>
-    <mergeCell ref="G64:H64"/>
-    <mergeCell ref="D96:I96"/>
-    <mergeCell ref="D95:F95"/>
-    <mergeCell ref="G95:H95"/>
-    <mergeCell ref="D92:I92"/>
-    <mergeCell ref="D93:I93"/>
-    <mergeCell ref="D90:E90"/>
-    <mergeCell ref="D91:H91"/>
-    <mergeCell ref="E86:G86"/>
-    <mergeCell ref="D88:I88"/>
-    <mergeCell ref="H67:I67"/>
-    <mergeCell ref="G81:H81"/>
-    <mergeCell ref="D67:F67"/>
-    <mergeCell ref="F68:I68"/>
-    <mergeCell ref="D87:E87"/>
-    <mergeCell ref="G87:I87"/>
-    <mergeCell ref="D98:I98"/>
-    <mergeCell ref="D94:I94"/>
-    <mergeCell ref="H89:I89"/>
-    <mergeCell ref="D89:F89"/>
-    <mergeCell ref="D97:I97"/>
-    <mergeCell ref="D106:E106"/>
-    <mergeCell ref="D99:G99"/>
-    <mergeCell ref="G126:I126"/>
-    <mergeCell ref="F125:J125"/>
-    <mergeCell ref="D128:J128"/>
-    <mergeCell ref="D103:E103"/>
-    <mergeCell ref="D104:E104"/>
-    <mergeCell ref="D105:E105"/>
-    <mergeCell ref="G100:I100"/>
-    <mergeCell ref="B101:I101"/>
-    <mergeCell ref="F127:J127"/>
-    <mergeCell ref="D107:E107"/>
-    <mergeCell ref="F118:J118"/>
-    <mergeCell ref="D108:E108"/>
-    <mergeCell ref="B112:J113"/>
-    <mergeCell ref="G124:J124"/>
+    <mergeCell ref="D78:I78"/>
+    <mergeCell ref="G71:H71"/>
+    <mergeCell ref="D76:I76"/>
+    <mergeCell ref="D66:H66"/>
+    <mergeCell ref="D77:I77"/>
+    <mergeCell ref="D73:I73"/>
+    <mergeCell ref="D70:E70"/>
+    <mergeCell ref="D74:F74"/>
+    <mergeCell ref="D31:I31"/>
+    <mergeCell ref="G35:H35"/>
+    <mergeCell ref="D40:I40"/>
+    <mergeCell ref="D33:I33"/>
+    <mergeCell ref="D46:I46"/>
+    <mergeCell ref="D43:I43"/>
+    <mergeCell ref="D120:H120"/>
+    <mergeCell ref="G123:J123"/>
+    <mergeCell ref="D121:J121"/>
+    <mergeCell ref="D143:J143"/>
+    <mergeCell ref="C177:J177"/>
+    <mergeCell ref="D135:J135"/>
+    <mergeCell ref="D172:J172"/>
+    <mergeCell ref="G146:J146"/>
+    <mergeCell ref="G152:I152"/>
+    <mergeCell ref="D149:J150"/>
+    <mergeCell ref="D187:J187"/>
+    <mergeCell ref="D185:J185"/>
+    <mergeCell ref="C175:J176"/>
+    <mergeCell ref="D164:J164"/>
+    <mergeCell ref="D157:J157"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/attendance_sheet.xlsx
+++ b/attendance_sheet.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\repositary\3rd_Year_5th_Semester\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56CD425A-8727-4D13-8A91-840C5566A4BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5B5A91C-554C-4E64-9F8C-B4D7725BDBE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{EB654061-A886-47D1-BF86-9B1A84FCE7FB}"/>
   </bookViews>
@@ -544,35 +544,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -590,6 +566,30 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -993,14 +993,14 @@
       <c r="C8" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D8" s="33" t="s">
+      <c r="D8" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="E8" s="33"/>
-      <c r="F8" s="33"/>
-      <c r="G8" s="33"/>
-      <c r="H8" s="33"/>
-      <c r="I8" s="33"/>
+      <c r="E8" s="32"/>
+      <c r="F8" s="32"/>
+      <c r="G8" s="32"/>
+      <c r="H8" s="32"/>
+      <c r="I8" s="32"/>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B9" s="4">
@@ -1009,14 +1009,14 @@
       <c r="C9" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D9" s="33" t="s">
+      <c r="D9" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="E9" s="33"/>
-      <c r="F9" s="33"/>
-      <c r="G9" s="33"/>
-      <c r="H9" s="33"/>
-      <c r="I9" s="33"/>
+      <c r="E9" s="32"/>
+      <c r="F9" s="32"/>
+      <c r="G9" s="32"/>
+      <c r="H9" s="32"/>
+      <c r="I9" s="32"/>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B10" s="4">
@@ -1025,14 +1025,14 @@
       <c r="C10" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D10" s="33" t="s">
+      <c r="D10" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="E10" s="33"/>
-      <c r="F10" s="33"/>
-      <c r="G10" s="33"/>
-      <c r="H10" s="33"/>
-      <c r="I10" s="33"/>
+      <c r="E10" s="32"/>
+      <c r="F10" s="32"/>
+      <c r="G10" s="32"/>
+      <c r="H10" s="32"/>
+      <c r="I10" s="32"/>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B11" s="4">
@@ -1041,14 +1041,14 @@
       <c r="C11" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D11" s="33" t="s">
+      <c r="D11" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="E11" s="33"/>
-      <c r="F11" s="33"/>
-      <c r="G11" s="33"/>
-      <c r="H11" s="33"/>
-      <c r="I11" s="33"/>
+      <c r="E11" s="32"/>
+      <c r="F11" s="32"/>
+      <c r="G11" s="32"/>
+      <c r="H11" s="32"/>
+      <c r="I11" s="32"/>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B12" s="4">
@@ -1092,10 +1092,10 @@
       <c r="F13" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="G13" s="33" t="s">
+      <c r="G13" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="H13" s="33"/>
+      <c r="H13" s="32"/>
       <c r="I13" s="1" t="s">
         <v>14</v>
       </c>
@@ -1107,14 +1107,14 @@
       <c r="C14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D14" s="33" t="s">
+      <c r="D14" s="32" t="s">
         <v>19</v>
       </c>
-      <c r="E14" s="33"/>
-      <c r="F14" s="33"/>
-      <c r="G14" s="33"/>
-      <c r="H14" s="33"/>
-      <c r="I14" s="33"/>
+      <c r="E14" s="32"/>
+      <c r="F14" s="32"/>
+      <c r="G14" s="32"/>
+      <c r="H14" s="32"/>
+      <c r="I14" s="32"/>
     </row>
     <row r="15" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B15" s="4">
@@ -1201,14 +1201,14 @@
       <c r="C18" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D18" s="33" t="s">
+      <c r="D18" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="E18" s="33"/>
-      <c r="F18" s="33"/>
-      <c r="G18" s="33"/>
-      <c r="H18" s="33"/>
-      <c r="I18" s="33"/>
+      <c r="E18" s="32"/>
+      <c r="F18" s="32"/>
+      <c r="G18" s="32"/>
+      <c r="H18" s="32"/>
+      <c r="I18" s="32"/>
     </row>
     <row r="19" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B19" s="4">
@@ -1217,14 +1217,14 @@
       <c r="C19" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D19" s="33" t="s">
+      <c r="D19" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="E19" s="33"/>
-      <c r="F19" s="33"/>
-      <c r="G19" s="33"/>
-      <c r="H19" s="33"/>
-      <c r="I19" s="33"/>
+      <c r="E19" s="32"/>
+      <c r="F19" s="32"/>
+      <c r="G19" s="32"/>
+      <c r="H19" s="32"/>
+      <c r="I19" s="32"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B20" s="4">
@@ -1242,10 +1242,10 @@
       <c r="F20" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G20" s="33" t="s">
+      <c r="G20" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="H20" s="33"/>
+      <c r="H20" s="32"/>
       <c r="I20" s="1" t="s">
         <v>14</v>
       </c>
@@ -1361,14 +1361,14 @@
       <c r="C25" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D25" s="33" t="s">
+      <c r="D25" s="32" t="s">
         <v>26</v>
       </c>
-      <c r="E25" s="33"/>
-      <c r="F25" s="33"/>
-      <c r="G25" s="33"/>
-      <c r="H25" s="33"/>
-      <c r="I25" s="33"/>
+      <c r="E25" s="32"/>
+      <c r="F25" s="32"/>
+      <c r="G25" s="32"/>
+      <c r="H25" s="32"/>
+      <c r="I25" s="32"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B26" s="4">
@@ -1412,10 +1412,10 @@
       <c r="F27" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G27" s="33" t="s">
+      <c r="G27" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="H27" s="33"/>
+      <c r="H27" s="32"/>
       <c r="I27" s="1" t="s">
         <v>14</v>
       </c>
@@ -1479,14 +1479,14 @@
       <c r="C30" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D30" s="32" t="s">
+      <c r="D30" s="33" t="s">
         <v>20</v>
       </c>
-      <c r="E30" s="32"/>
-      <c r="F30" s="32"/>
-      <c r="G30" s="32"/>
-      <c r="H30" s="32"/>
-      <c r="I30" s="32"/>
+      <c r="E30" s="33"/>
+      <c r="F30" s="33"/>
+      <c r="G30" s="33"/>
+      <c r="H30" s="33"/>
+      <c r="I30" s="33"/>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B31" s="4">
@@ -1495,14 +1495,14 @@
       <c r="C31" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D31" s="32" t="s">
+      <c r="D31" s="33" t="s">
         <v>20</v>
       </c>
-      <c r="E31" s="32"/>
-      <c r="F31" s="32"/>
-      <c r="G31" s="32"/>
-      <c r="H31" s="32"/>
-      <c r="I31" s="32"/>
+      <c r="E31" s="33"/>
+      <c r="F31" s="33"/>
+      <c r="G31" s="33"/>
+      <c r="H31" s="33"/>
+      <c r="I31" s="33"/>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B32" s="4">
@@ -1537,14 +1537,14 @@
       <c r="C33" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D33" s="32" t="s">
+      <c r="D33" s="33" t="s">
         <v>20</v>
       </c>
-      <c r="E33" s="32"/>
-      <c r="F33" s="32"/>
-      <c r="G33" s="32"/>
-      <c r="H33" s="32"/>
-      <c r="I33" s="32"/>
+      <c r="E33" s="33"/>
+      <c r="F33" s="33"/>
+      <c r="G33" s="33"/>
+      <c r="H33" s="33"/>
+      <c r="I33" s="33"/>
     </row>
     <row r="34" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B34" s="4">
@@ -1588,10 +1588,10 @@
       <c r="F35" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G35" s="32" t="s">
+      <c r="G35" s="33" t="s">
         <v>18</v>
       </c>
-      <c r="H35" s="32"/>
+      <c r="H35" s="33"/>
       <c r="I35" s="1" t="s">
         <v>14</v>
       </c>
@@ -1707,14 +1707,14 @@
       <c r="C40" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D40" s="32" t="s">
+      <c r="D40" s="33" t="s">
         <v>20</v>
       </c>
-      <c r="E40" s="32"/>
-      <c r="F40" s="32"/>
-      <c r="G40" s="32"/>
-      <c r="H40" s="32"/>
-      <c r="I40" s="32"/>
+      <c r="E40" s="33"/>
+      <c r="F40" s="33"/>
+      <c r="G40" s="33"/>
+      <c r="H40" s="33"/>
+      <c r="I40" s="33"/>
     </row>
     <row r="41" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B41" s="4">
@@ -1758,10 +1758,10 @@
       <c r="F42" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G42" s="32" t="s">
+      <c r="G42" s="33" t="s">
         <v>28</v>
       </c>
-      <c r="H42" s="32"/>
+      <c r="H42" s="33"/>
       <c r="I42" s="1" t="s">
         <v>15</v>
       </c>
@@ -1773,14 +1773,14 @@
       <c r="C43" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D43" s="32" t="s">
+      <c r="D43" s="33" t="s">
         <v>20</v>
       </c>
-      <c r="E43" s="32"/>
-      <c r="F43" s="32"/>
-      <c r="G43" s="32"/>
-      <c r="H43" s="32"/>
-      <c r="I43" s="32"/>
+      <c r="E43" s="33"/>
+      <c r="F43" s="33"/>
+      <c r="G43" s="33"/>
+      <c r="H43" s="33"/>
+      <c r="I43" s="33"/>
     </row>
     <row r="44" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B44" s="4">
@@ -1844,14 +1844,14 @@
       <c r="C46" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D46" s="32" t="s">
+      <c r="D46" s="33" t="s">
         <v>20</v>
       </c>
-      <c r="E46" s="32"/>
-      <c r="F46" s="32"/>
-      <c r="G46" s="32"/>
-      <c r="H46" s="32"/>
-      <c r="I46" s="32"/>
+      <c r="E46" s="33"/>
+      <c r="F46" s="33"/>
+      <c r="G46" s="33"/>
+      <c r="H46" s="33"/>
+      <c r="I46" s="33"/>
     </row>
     <row r="47" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B47" s="4">
@@ -1863,11 +1863,11 @@
       <c r="D47" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E47" s="24"/>
-      <c r="F47" s="24"/>
-      <c r="G47" s="24"/>
-      <c r="H47" s="24"/>
-      <c r="I47" s="25"/>
+      <c r="E47" s="25"/>
+      <c r="F47" s="25"/>
+      <c r="G47" s="25"/>
+      <c r="H47" s="25"/>
+      <c r="I47" s="24"/>
     </row>
     <row r="48" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B48" s="4">
@@ -1914,7 +1914,7 @@
       <c r="G49" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="H49" s="25"/>
+      <c r="H49" s="24"/>
       <c r="I49" s="1" t="s">
         <v>30</v>
       </c>
@@ -2056,14 +2056,14 @@
       <c r="C55" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="D55" s="24" t="s">
+      <c r="D55" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="E55" s="24"/>
-      <c r="F55" s="24"/>
-      <c r="G55" s="24"/>
-      <c r="H55" s="24"/>
-      <c r="I55" s="24"/>
+      <c r="E55" s="25"/>
+      <c r="F55" s="25"/>
+      <c r="G55" s="25"/>
+      <c r="H55" s="25"/>
+      <c r="I55" s="25"/>
     </row>
     <row r="56" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B56" s="4">
@@ -2110,7 +2110,7 @@
       <c r="G57" s="23" t="s">
         <v>37</v>
       </c>
-      <c r="H57" s="25"/>
+      <c r="H57" s="24"/>
       <c r="I57" s="1" t="s">
         <v>36</v>
       </c>
@@ -2177,11 +2177,11 @@
       <c r="D60" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E60" s="24"/>
-      <c r="F60" s="24"/>
-      <c r="G60" s="24"/>
-      <c r="H60" s="24"/>
-      <c r="I60" s="25"/>
+      <c r="E60" s="25"/>
+      <c r="F60" s="25"/>
+      <c r="G60" s="25"/>
+      <c r="H60" s="25"/>
+      <c r="I60" s="24"/>
     </row>
     <row r="61" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B61" s="4">
@@ -2193,11 +2193,11 @@
       <c r="D61" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E61" s="24"/>
-      <c r="F61" s="24"/>
-      <c r="G61" s="24"/>
-      <c r="H61" s="24"/>
-      <c r="I61" s="25"/>
+      <c r="E61" s="25"/>
+      <c r="F61" s="25"/>
+      <c r="G61" s="25"/>
+      <c r="H61" s="25"/>
+      <c r="I61" s="24"/>
     </row>
     <row r="62" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B62" s="4">
@@ -2209,11 +2209,11 @@
       <c r="D62" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E62" s="24"/>
-      <c r="F62" s="24"/>
-      <c r="G62" s="24"/>
-      <c r="H62" s="24"/>
-      <c r="I62" s="25"/>
+      <c r="E62" s="25"/>
+      <c r="F62" s="25"/>
+      <c r="G62" s="25"/>
+      <c r="H62" s="25"/>
+      <c r="I62" s="24"/>
     </row>
     <row r="63" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B63" s="4">
@@ -2260,7 +2260,7 @@
       <c r="G64" s="23" t="s">
         <v>37</v>
       </c>
-      <c r="H64" s="25"/>
+      <c r="H64" s="24"/>
       <c r="I64" s="1" t="s">
         <v>14</v>
       </c>
@@ -2301,10 +2301,10 @@
       <c r="D66" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="E66" s="24"/>
-      <c r="F66" s="24"/>
-      <c r="G66" s="24"/>
-      <c r="H66" s="25"/>
+      <c r="E66" s="25"/>
+      <c r="F66" s="25"/>
+      <c r="G66" s="25"/>
+      <c r="H66" s="24"/>
       <c r="I66" s="1" t="s">
         <v>16</v>
       </c>
@@ -2319,15 +2319,15 @@
       <c r="D67" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="E67" s="24"/>
-      <c r="F67" s="25"/>
+      <c r="E67" s="25"/>
+      <c r="F67" s="24"/>
       <c r="G67" s="3" t="s">
         <v>16</v>
       </c>
       <c r="H67" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="I67" s="25"/>
+      <c r="I67" s="24"/>
     </row>
     <row r="68" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B68" s="4">
@@ -2345,9 +2345,9 @@
       <c r="F68" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="G68" s="24"/>
-      <c r="H68" s="24"/>
-      <c r="I68" s="25"/>
+      <c r="G68" s="25"/>
+      <c r="H68" s="25"/>
+      <c r="I68" s="24"/>
     </row>
     <row r="69" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B69" s="4">
@@ -2359,11 +2359,11 @@
       <c r="D69" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E69" s="24"/>
-      <c r="F69" s="24"/>
-      <c r="G69" s="24"/>
-      <c r="H69" s="24"/>
-      <c r="I69" s="25"/>
+      <c r="E69" s="25"/>
+      <c r="F69" s="25"/>
+      <c r="G69" s="25"/>
+      <c r="H69" s="25"/>
+      <c r="I69" s="24"/>
     </row>
     <row r="70" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B70" s="4">
@@ -2375,7 +2375,7 @@
       <c r="D70" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="E70" s="25"/>
+      <c r="E70" s="24"/>
       <c r="F70" s="3" t="s">
         <v>15</v>
       </c>
@@ -2408,7 +2408,7 @@
       <c r="G71" s="23" t="s">
         <v>37</v>
       </c>
-      <c r="H71" s="25"/>
+      <c r="H71" s="24"/>
       <c r="I71" s="1" t="s">
         <v>14</v>
       </c>
@@ -2449,11 +2449,11 @@
       <c r="D73" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E73" s="24"/>
-      <c r="F73" s="24"/>
-      <c r="G73" s="24"/>
-      <c r="H73" s="24"/>
-      <c r="I73" s="25"/>
+      <c r="E73" s="25"/>
+      <c r="F73" s="25"/>
+      <c r="G73" s="25"/>
+      <c r="H73" s="25"/>
+      <c r="I73" s="24"/>
     </row>
     <row r="74" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B74" s="4">
@@ -2465,8 +2465,8 @@
       <c r="D74" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="E74" s="24"/>
-      <c r="F74" s="25"/>
+      <c r="E74" s="25"/>
+      <c r="F74" s="24"/>
       <c r="G74" s="3" t="s">
         <v>16</v>
       </c>
@@ -2505,11 +2505,11 @@
       <c r="D76" s="23" t="s">
         <v>39</v>
       </c>
-      <c r="E76" s="24"/>
-      <c r="F76" s="24"/>
-      <c r="G76" s="24"/>
-      <c r="H76" s="24"/>
-      <c r="I76" s="25"/>
+      <c r="E76" s="25"/>
+      <c r="F76" s="25"/>
+      <c r="G76" s="25"/>
+      <c r="H76" s="25"/>
+      <c r="I76" s="24"/>
     </row>
     <row r="77" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B77" s="4">
@@ -2521,11 +2521,11 @@
       <c r="D77" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E77" s="24"/>
-      <c r="F77" s="24"/>
-      <c r="G77" s="24"/>
-      <c r="H77" s="24"/>
-      <c r="I77" s="25"/>
+      <c r="E77" s="25"/>
+      <c r="F77" s="25"/>
+      <c r="G77" s="25"/>
+      <c r="H77" s="25"/>
+      <c r="I77" s="24"/>
     </row>
     <row r="78" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B78" s="4">
@@ -2537,11 +2537,11 @@
       <c r="D78" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E78" s="24"/>
-      <c r="F78" s="24"/>
-      <c r="G78" s="24"/>
-      <c r="H78" s="24"/>
-      <c r="I78" s="25"/>
+      <c r="E78" s="25"/>
+      <c r="F78" s="25"/>
+      <c r="G78" s="25"/>
+      <c r="H78" s="25"/>
+      <c r="I78" s="24"/>
     </row>
     <row r="79" spans="2:9" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B79" s="16" t="s">
@@ -2588,7 +2588,7 @@
       <c r="G80" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="H80" s="25"/>
+      <c r="H80" s="24"/>
       <c r="I80" s="1" t="s">
         <v>14</v>
       </c>
@@ -2612,7 +2612,7 @@
       <c r="G81" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="H81" s="25"/>
+      <c r="H81" s="24"/>
       <c r="I81" s="1" t="s">
         <v>16</v>
       </c>
@@ -2679,11 +2679,11 @@
       <c r="D84" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E84" s="24"/>
-      <c r="F84" s="24"/>
-      <c r="G84" s="24"/>
-      <c r="H84" s="24"/>
-      <c r="I84" s="25"/>
+      <c r="E84" s="25"/>
+      <c r="F84" s="25"/>
+      <c r="G84" s="25"/>
+      <c r="H84" s="25"/>
+      <c r="I84" s="24"/>
     </row>
     <row r="85" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B85" s="4">
@@ -2724,8 +2724,8 @@
       <c r="E86" s="23" t="s">
         <v>43</v>
       </c>
-      <c r="F86" s="24"/>
-      <c r="G86" s="25"/>
+      <c r="F86" s="25"/>
+      <c r="G86" s="24"/>
       <c r="H86" s="3" t="s">
         <v>14</v>
       </c>
@@ -2743,15 +2743,15 @@
       <c r="D87" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="E87" s="25"/>
+      <c r="E87" s="24"/>
       <c r="F87" s="3" t="s">
         <v>16</v>
       </c>
       <c r="G87" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="H87" s="24"/>
-      <c r="I87" s="25"/>
+      <c r="H87" s="25"/>
+      <c r="I87" s="24"/>
     </row>
     <row r="88" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B88" s="4">
@@ -2763,11 +2763,11 @@
       <c r="D88" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E88" s="24"/>
-      <c r="F88" s="24"/>
-      <c r="G88" s="24"/>
-      <c r="H88" s="24"/>
-      <c r="I88" s="25"/>
+      <c r="E88" s="25"/>
+      <c r="F88" s="25"/>
+      <c r="G88" s="25"/>
+      <c r="H88" s="25"/>
+      <c r="I88" s="24"/>
     </row>
     <row r="89" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B89" s="4">
@@ -2779,15 +2779,15 @@
       <c r="D89" s="23" t="s">
         <v>44</v>
       </c>
-      <c r="E89" s="24"/>
-      <c r="F89" s="25"/>
+      <c r="E89" s="25"/>
+      <c r="F89" s="24"/>
       <c r="G89" s="3" t="s">
         <v>16</v>
       </c>
       <c r="H89" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="I89" s="25"/>
+      <c r="I89" s="24"/>
     </row>
     <row r="90" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B90" s="4">
@@ -2799,7 +2799,7 @@
       <c r="D90" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="E90" s="25"/>
+      <c r="E90" s="24"/>
       <c r="F90" s="3" t="s">
         <v>16</v>
       </c>
@@ -2824,10 +2824,10 @@
       <c r="D91" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E91" s="24"/>
-      <c r="F91" s="24"/>
-      <c r="G91" s="24"/>
-      <c r="H91" s="25"/>
+      <c r="E91" s="25"/>
+      <c r="F91" s="25"/>
+      <c r="G91" s="25"/>
+      <c r="H91" s="24"/>
       <c r="I91" s="18" t="s">
         <v>45</v>
       </c>
@@ -2842,11 +2842,11 @@
       <c r="D92" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E92" s="24"/>
-      <c r="F92" s="24"/>
-      <c r="G92" s="24"/>
-      <c r="H92" s="24"/>
-      <c r="I92" s="25"/>
+      <c r="E92" s="25"/>
+      <c r="F92" s="25"/>
+      <c r="G92" s="25"/>
+      <c r="H92" s="25"/>
+      <c r="I92" s="24"/>
     </row>
     <row r="93" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B93" s="4">
@@ -2858,11 +2858,11 @@
       <c r="D93" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="E93" s="24"/>
-      <c r="F93" s="24"/>
-      <c r="G93" s="24"/>
-      <c r="H93" s="24"/>
-      <c r="I93" s="25"/>
+      <c r="E93" s="25"/>
+      <c r="F93" s="25"/>
+      <c r="G93" s="25"/>
+      <c r="H93" s="25"/>
+      <c r="I93" s="24"/>
     </row>
     <row r="94" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B94" s="4">
@@ -2874,11 +2874,11 @@
       <c r="D94" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="E94" s="24"/>
-      <c r="F94" s="24"/>
-      <c r="G94" s="24"/>
-      <c r="H94" s="24"/>
-      <c r="I94" s="25"/>
+      <c r="E94" s="25"/>
+      <c r="F94" s="25"/>
+      <c r="G94" s="25"/>
+      <c r="H94" s="25"/>
+      <c r="I94" s="24"/>
     </row>
     <row r="95" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B95" s="4">
@@ -2890,12 +2890,12 @@
       <c r="D95" s="23" t="s">
         <v>47</v>
       </c>
-      <c r="E95" s="24"/>
-      <c r="F95" s="25"/>
+      <c r="E95" s="25"/>
+      <c r="F95" s="24"/>
       <c r="G95" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="H95" s="25"/>
+      <c r="H95" s="24"/>
       <c r="I95" s="1" t="s">
         <v>14</v>
       </c>
@@ -2910,11 +2910,11 @@
       <c r="D96" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E96" s="24"/>
-      <c r="F96" s="24"/>
-      <c r="G96" s="24"/>
-      <c r="H96" s="24"/>
-      <c r="I96" s="25"/>
+      <c r="E96" s="25"/>
+      <c r="F96" s="25"/>
+      <c r="G96" s="25"/>
+      <c r="H96" s="25"/>
+      <c r="I96" s="24"/>
     </row>
     <row r="97" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B97" s="4">
@@ -2926,11 +2926,11 @@
       <c r="D97" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="E97" s="24"/>
-      <c r="F97" s="24"/>
-      <c r="G97" s="24"/>
-      <c r="H97" s="24"/>
-      <c r="I97" s="25"/>
+      <c r="E97" s="25"/>
+      <c r="F97" s="25"/>
+      <c r="G97" s="25"/>
+      <c r="H97" s="25"/>
+      <c r="I97" s="24"/>
     </row>
     <row r="98" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B98" s="4">
@@ -2942,11 +2942,11 @@
       <c r="D98" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E98" s="24"/>
-      <c r="F98" s="24"/>
-      <c r="G98" s="24"/>
-      <c r="H98" s="24"/>
-      <c r="I98" s="25"/>
+      <c r="E98" s="25"/>
+      <c r="F98" s="25"/>
+      <c r="G98" s="25"/>
+      <c r="H98" s="25"/>
+      <c r="I98" s="24"/>
     </row>
     <row r="99" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B99" s="4">
@@ -2958,9 +2958,9 @@
       <c r="D99" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="E99" s="24"/>
-      <c r="F99" s="24"/>
-      <c r="G99" s="25"/>
+      <c r="E99" s="25"/>
+      <c r="F99" s="25"/>
+      <c r="G99" s="24"/>
       <c r="H99" s="3" t="s">
         <v>49</v>
       </c>
@@ -2987,18 +2987,18 @@
       <c r="G100" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="H100" s="24"/>
-      <c r="I100" s="25"/>
+      <c r="H100" s="25"/>
+      <c r="I100" s="24"/>
     </row>
     <row r="101" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B101" s="23"/>
-      <c r="C101" s="24"/>
-      <c r="D101" s="24"/>
-      <c r="E101" s="24"/>
-      <c r="F101" s="24"/>
-      <c r="G101" s="24"/>
-      <c r="H101" s="24"/>
-      <c r="I101" s="25"/>
+      <c r="C101" s="25"/>
+      <c r="D101" s="25"/>
+      <c r="E101" s="25"/>
+      <c r="F101" s="25"/>
+      <c r="G101" s="25"/>
+      <c r="H101" s="25"/>
+      <c r="I101" s="24"/>
     </row>
     <row r="102" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B102" s="3"/>
@@ -3020,7 +3020,7 @@
       <c r="D103" s="23" t="s">
         <v>51</v>
       </c>
-      <c r="E103" s="25"/>
+      <c r="E103" s="24"/>
       <c r="F103" s="3"/>
       <c r="G103" s="3"/>
       <c r="H103" s="3"/>
@@ -3036,7 +3036,7 @@
       <c r="D104" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="E104" s="25"/>
+      <c r="E104" s="24"/>
       <c r="F104" s="3"/>
       <c r="G104" s="3"/>
       <c r="H104" s="3"/>
@@ -3052,7 +3052,7 @@
       <c r="D105" s="23" t="s">
         <v>53</v>
       </c>
-      <c r="E105" s="25"/>
+      <c r="E105" s="24"/>
       <c r="F105" s="3"/>
       <c r="G105" s="3"/>
       <c r="H105" s="3"/>
@@ -3068,7 +3068,7 @@
       <c r="D106" s="23" t="s">
         <v>54</v>
       </c>
-      <c r="E106" s="25"/>
+      <c r="E106" s="24"/>
       <c r="F106" s="3"/>
       <c r="G106" s="3"/>
       <c r="H106" s="3"/>
@@ -3084,7 +3084,7 @@
       <c r="D107" s="23" t="s">
         <v>55</v>
       </c>
-      <c r="E107" s="25"/>
+      <c r="E107" s="24"/>
       <c r="F107" s="3"/>
       <c r="G107" s="3"/>
       <c r="H107" s="3"/>
@@ -3100,7 +3100,7 @@
       <c r="D108" s="23" t="s">
         <v>56</v>
       </c>
-      <c r="E108" s="25"/>
+      <c r="E108" s="24"/>
       <c r="F108" s="3"/>
       <c r="G108" s="3"/>
       <c r="H108" s="3"/>
@@ -3137,28 +3137,28 @@
       <c r="I111" s="20"/>
     </row>
     <row r="112" spans="2:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B112" s="34" t="s">
+      <c r="B112" s="26" t="s">
         <v>57</v>
       </c>
-      <c r="C112" s="35"/>
-      <c r="D112" s="35"/>
-      <c r="E112" s="35"/>
-      <c r="F112" s="35"/>
-      <c r="G112" s="35"/>
-      <c r="H112" s="35"/>
-      <c r="I112" s="35"/>
-      <c r="J112" s="36"/>
+      <c r="C112" s="27"/>
+      <c r="D112" s="27"/>
+      <c r="E112" s="27"/>
+      <c r="F112" s="27"/>
+      <c r="G112" s="27"/>
+      <c r="H112" s="27"/>
+      <c r="I112" s="27"/>
+      <c r="J112" s="28"/>
     </row>
     <row r="113" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B113" s="37"/>
-      <c r="C113" s="38"/>
-      <c r="D113" s="38"/>
-      <c r="E113" s="38"/>
-      <c r="F113" s="38"/>
-      <c r="G113" s="38"/>
-      <c r="H113" s="38"/>
-      <c r="I113" s="38"/>
-      <c r="J113" s="39"/>
+      <c r="B113" s="29"/>
+      <c r="C113" s="30"/>
+      <c r="D113" s="30"/>
+      <c r="E113" s="30"/>
+      <c r="F113" s="30"/>
+      <c r="G113" s="30"/>
+      <c r="H113" s="30"/>
+      <c r="I113" s="30"/>
+      <c r="J113" s="31"/>
     </row>
     <row r="114" spans="2:10" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B114" s="8" t="s">
@@ -3292,10 +3292,10 @@
       <c r="F118" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="G118" s="24"/>
-      <c r="H118" s="24"/>
-      <c r="I118" s="24"/>
-      <c r="J118" s="25"/>
+      <c r="G118" s="25"/>
+      <c r="H118" s="25"/>
+      <c r="I118" s="25"/>
+      <c r="J118" s="24"/>
     </row>
     <row r="119" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B119" s="4">
@@ -3336,10 +3336,10 @@
       <c r="D120" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="E120" s="24"/>
-      <c r="F120" s="24"/>
-      <c r="G120" s="24"/>
-      <c r="H120" s="25"/>
+      <c r="E120" s="25"/>
+      <c r="F120" s="25"/>
+      <c r="G120" s="25"/>
+      <c r="H120" s="24"/>
       <c r="I120" s="1" t="s">
         <v>16</v>
       </c>
@@ -3357,12 +3357,12 @@
       <c r="D121" s="23" t="s">
         <v>65</v>
       </c>
-      <c r="E121" s="24"/>
-      <c r="F121" s="24"/>
-      <c r="G121" s="24"/>
-      <c r="H121" s="24"/>
-      <c r="I121" s="24"/>
-      <c r="J121" s="25"/>
+      <c r="E121" s="25"/>
+      <c r="F121" s="25"/>
+      <c r="G121" s="25"/>
+      <c r="H121" s="25"/>
+      <c r="I121" s="25"/>
+      <c r="J121" s="24"/>
     </row>
     <row r="122" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B122" s="4">
@@ -3412,9 +3412,9 @@
       <c r="G123" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="H123" s="24"/>
-      <c r="I123" s="24"/>
-      <c r="J123" s="25"/>
+      <c r="H123" s="25"/>
+      <c r="I123" s="25"/>
+      <c r="J123" s="24"/>
     </row>
     <row r="124" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B124" s="4">
@@ -3435,9 +3435,9 @@
       <c r="G124" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="H124" s="24"/>
-      <c r="I124" s="24"/>
-      <c r="J124" s="25"/>
+      <c r="H124" s="25"/>
+      <c r="I124" s="25"/>
+      <c r="J124" s="24"/>
     </row>
     <row r="125" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B125" s="4">
@@ -3455,10 +3455,10 @@
       <c r="F125" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="G125" s="24"/>
-      <c r="H125" s="24"/>
-      <c r="I125" s="24"/>
-      <c r="J125" s="25"/>
+      <c r="G125" s="25"/>
+      <c r="H125" s="25"/>
+      <c r="I125" s="25"/>
+      <c r="J125" s="24"/>
     </row>
     <row r="126" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B126" s="4">
@@ -3479,8 +3479,8 @@
       <c r="G126" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="H126" s="24"/>
-      <c r="I126" s="25"/>
+      <c r="H126" s="25"/>
+      <c r="I126" s="24"/>
       <c r="J126" s="1" t="s">
         <v>16</v>
       </c>
@@ -3501,10 +3501,10 @@
       <c r="F127" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="G127" s="24"/>
-      <c r="H127" s="24"/>
-      <c r="I127" s="24"/>
-      <c r="J127" s="25"/>
+      <c r="G127" s="25"/>
+      <c r="H127" s="25"/>
+      <c r="I127" s="25"/>
+      <c r="J127" s="24"/>
     </row>
     <row r="128" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B128" s="4">
@@ -3516,12 +3516,12 @@
       <c r="D128" s="23" t="s">
         <v>65</v>
       </c>
-      <c r="E128" s="24"/>
-      <c r="F128" s="24"/>
-      <c r="G128" s="24"/>
-      <c r="H128" s="24"/>
-      <c r="I128" s="24"/>
-      <c r="J128" s="25"/>
+      <c r="E128" s="25"/>
+      <c r="F128" s="25"/>
+      <c r="G128" s="25"/>
+      <c r="H128" s="25"/>
+      <c r="I128" s="25"/>
+      <c r="J128" s="24"/>
     </row>
     <row r="129" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B129" s="4">
@@ -3707,12 +3707,12 @@
       <c r="D135" s="23" t="s">
         <v>65</v>
       </c>
-      <c r="E135" s="24"/>
-      <c r="F135" s="24"/>
-      <c r="G135" s="24"/>
-      <c r="H135" s="24"/>
-      <c r="I135" s="24"/>
-      <c r="J135" s="25"/>
+      <c r="E135" s="25"/>
+      <c r="F135" s="25"/>
+      <c r="G135" s="25"/>
+      <c r="H135" s="25"/>
+      <c r="I135" s="25"/>
+      <c r="J135" s="24"/>
     </row>
     <row r="136" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B136" s="4">
@@ -3927,12 +3927,12 @@
       <c r="D143" s="23" t="s">
         <v>65</v>
       </c>
-      <c r="E143" s="24"/>
-      <c r="F143" s="24"/>
-      <c r="G143" s="24"/>
-      <c r="H143" s="24"/>
-      <c r="I143" s="24"/>
-      <c r="J143" s="25"/>
+      <c r="E143" s="25"/>
+      <c r="F143" s="25"/>
+      <c r="G143" s="25"/>
+      <c r="H143" s="25"/>
+      <c r="I143" s="25"/>
+      <c r="J143" s="24"/>
     </row>
     <row r="144" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B144" s="4">
@@ -4011,9 +4011,9 @@
       <c r="G146" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="H146" s="24"/>
-      <c r="I146" s="24"/>
-      <c r="J146" s="25"/>
+      <c r="H146" s="25"/>
+      <c r="I146" s="25"/>
+      <c r="J146" s="24"/>
     </row>
     <row r="147" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B147" s="4">
@@ -4080,15 +4080,15 @@
       <c r="C149" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D149" s="26" t="s">
+      <c r="D149" s="34" t="s">
         <v>20</v>
       </c>
-      <c r="E149" s="27"/>
-      <c r="F149" s="27"/>
-      <c r="G149" s="27"/>
-      <c r="H149" s="27"/>
-      <c r="I149" s="27"/>
-      <c r="J149" s="30"/>
+      <c r="E149" s="35"/>
+      <c r="F149" s="35"/>
+      <c r="G149" s="35"/>
+      <c r="H149" s="35"/>
+      <c r="I149" s="35"/>
+      <c r="J149" s="36"/>
     </row>
     <row r="150" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B150" s="4">
@@ -4097,13 +4097,13 @@
       <c r="C150" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D150" s="28"/>
-      <c r="E150" s="29"/>
-      <c r="F150" s="29"/>
-      <c r="G150" s="29"/>
-      <c r="H150" s="29"/>
-      <c r="I150" s="29"/>
-      <c r="J150" s="31"/>
+      <c r="D150" s="37"/>
+      <c r="E150" s="38"/>
+      <c r="F150" s="38"/>
+      <c r="G150" s="38"/>
+      <c r="H150" s="38"/>
+      <c r="I150" s="38"/>
+      <c r="J150" s="39"/>
     </row>
     <row r="151" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B151" s="4">
@@ -4153,8 +4153,8 @@
       <c r="G152" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="H152" s="24"/>
-      <c r="I152" s="25"/>
+      <c r="H152" s="25"/>
+      <c r="I152" s="24"/>
       <c r="J152" s="1" t="s">
         <v>69</v>
       </c>
@@ -4285,12 +4285,12 @@
       <c r="D157" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E157" s="24"/>
-      <c r="F157" s="24"/>
-      <c r="G157" s="24"/>
-      <c r="H157" s="24"/>
-      <c r="I157" s="24"/>
-      <c r="J157" s="25"/>
+      <c r="E157" s="25"/>
+      <c r="F157" s="25"/>
+      <c r="G157" s="25"/>
+      <c r="H157" s="25"/>
+      <c r="I157" s="25"/>
+      <c r="J157" s="24"/>
     </row>
     <row r="158" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B158" s="4">
@@ -4474,12 +4474,12 @@
       <c r="D164" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E164" s="24"/>
-      <c r="F164" s="24"/>
-      <c r="G164" s="24"/>
-      <c r="H164" s="24"/>
-      <c r="I164" s="24"/>
-      <c r="J164" s="25"/>
+      <c r="E164" s="25"/>
+      <c r="F164" s="25"/>
+      <c r="G164" s="25"/>
+      <c r="H164" s="25"/>
+      <c r="I164" s="25"/>
+      <c r="J164" s="24"/>
     </row>
     <row r="165" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B165" s="4">
@@ -4680,12 +4680,12 @@
       <c r="D172" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E172" s="24"/>
-      <c r="F172" s="24"/>
-      <c r="G172" s="24"/>
-      <c r="H172" s="24"/>
-      <c r="I172" s="24"/>
-      <c r="J172" s="25"/>
+      <c r="E172" s="25"/>
+      <c r="F172" s="25"/>
+      <c r="G172" s="25"/>
+      <c r="H172" s="25"/>
+      <c r="I172" s="25"/>
+      <c r="J172" s="24"/>
     </row>
     <row r="173" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B173" s="4">
@@ -4749,29 +4749,29 @@
       <c r="B175" s="4">
         <v>45903</v>
       </c>
-      <c r="C175" s="26" t="s">
+      <c r="C175" s="34" t="s">
         <v>39</v>
       </c>
-      <c r="D175" s="27"/>
-      <c r="E175" s="27"/>
-      <c r="F175" s="27"/>
-      <c r="G175" s="27"/>
-      <c r="H175" s="27"/>
-      <c r="I175" s="27"/>
-      <c r="J175" s="27"/>
+      <c r="D175" s="35"/>
+      <c r="E175" s="35"/>
+      <c r="F175" s="35"/>
+      <c r="G175" s="35"/>
+      <c r="H175" s="35"/>
+      <c r="I175" s="35"/>
+      <c r="J175" s="35"/>
     </row>
     <row r="176" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B176" s="4">
         <v>45904</v>
       </c>
-      <c r="C176" s="28"/>
-      <c r="D176" s="29"/>
-      <c r="E176" s="29"/>
-      <c r="F176" s="29"/>
-      <c r="G176" s="29"/>
-      <c r="H176" s="29"/>
-      <c r="I176" s="29"/>
-      <c r="J176" s="29"/>
+      <c r="C176" s="37"/>
+      <c r="D176" s="38"/>
+      <c r="E176" s="38"/>
+      <c r="F176" s="38"/>
+      <c r="G176" s="38"/>
+      <c r="H176" s="38"/>
+      <c r="I176" s="38"/>
+      <c r="J176" s="38"/>
     </row>
     <row r="177" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B177" s="4">
@@ -4780,13 +4780,13 @@
       <c r="C177" s="23" t="s">
         <v>39</v>
       </c>
-      <c r="D177" s="24"/>
-      <c r="E177" s="24"/>
-      <c r="F177" s="24"/>
-      <c r="G177" s="24"/>
-      <c r="H177" s="24"/>
-      <c r="I177" s="24"/>
-      <c r="J177" s="25"/>
+      <c r="D177" s="25"/>
+      <c r="E177" s="25"/>
+      <c r="F177" s="25"/>
+      <c r="G177" s="25"/>
+      <c r="H177" s="25"/>
+      <c r="I177" s="25"/>
+      <c r="J177" s="24"/>
     </row>
     <row r="178" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B178" s="4">
@@ -4985,12 +4985,12 @@
       <c r="D185" s="23" t="s">
         <v>74</v>
       </c>
-      <c r="E185" s="24"/>
-      <c r="F185" s="24"/>
-      <c r="G185" s="24"/>
-      <c r="H185" s="24"/>
-      <c r="I185" s="24"/>
-      <c r="J185" s="25"/>
+      <c r="E185" s="25"/>
+      <c r="F185" s="25"/>
+      <c r="G185" s="25"/>
+      <c r="H185" s="25"/>
+      <c r="I185" s="25"/>
+      <c r="J185" s="24"/>
     </row>
     <row r="186" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B186" s="4">
@@ -5021,12 +5021,12 @@
       <c r="D187" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="E187" s="24"/>
-      <c r="F187" s="24"/>
-      <c r="G187" s="24"/>
-      <c r="H187" s="24"/>
-      <c r="I187" s="24"/>
-      <c r="J187" s="25"/>
+      <c r="E187" s="25"/>
+      <c r="F187" s="25"/>
+      <c r="G187" s="25"/>
+      <c r="H187" s="25"/>
+      <c r="I187" s="25"/>
+      <c r="J187" s="24"/>
     </row>
     <row r="188" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B188" s="3"/>
@@ -7549,6 +7549,79 @@
     </row>
   </sheetData>
   <mergeCells count="89">
+    <mergeCell ref="D187:J187"/>
+    <mergeCell ref="D185:J185"/>
+    <mergeCell ref="C175:J176"/>
+    <mergeCell ref="D164:J164"/>
+    <mergeCell ref="D157:J157"/>
+    <mergeCell ref="D120:H120"/>
+    <mergeCell ref="G123:J123"/>
+    <mergeCell ref="D121:J121"/>
+    <mergeCell ref="D143:J143"/>
+    <mergeCell ref="C177:J177"/>
+    <mergeCell ref="D135:J135"/>
+    <mergeCell ref="D172:J172"/>
+    <mergeCell ref="G146:J146"/>
+    <mergeCell ref="G152:I152"/>
+    <mergeCell ref="D149:J150"/>
+    <mergeCell ref="D31:I31"/>
+    <mergeCell ref="G35:H35"/>
+    <mergeCell ref="D40:I40"/>
+    <mergeCell ref="D33:I33"/>
+    <mergeCell ref="D46:I46"/>
+    <mergeCell ref="D43:I43"/>
+    <mergeCell ref="D78:I78"/>
+    <mergeCell ref="G71:H71"/>
+    <mergeCell ref="D76:I76"/>
+    <mergeCell ref="D66:H66"/>
+    <mergeCell ref="D77:I77"/>
+    <mergeCell ref="D73:I73"/>
+    <mergeCell ref="D70:E70"/>
+    <mergeCell ref="D74:F74"/>
+    <mergeCell ref="D84:I84"/>
+    <mergeCell ref="D69:I69"/>
+    <mergeCell ref="D8:I8"/>
+    <mergeCell ref="D9:I9"/>
+    <mergeCell ref="D10:I10"/>
+    <mergeCell ref="D11:I11"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="D14:I14"/>
+    <mergeCell ref="G27:H27"/>
+    <mergeCell ref="D25:I25"/>
+    <mergeCell ref="G20:H20"/>
+    <mergeCell ref="D19:I19"/>
+    <mergeCell ref="D18:I18"/>
+    <mergeCell ref="D30:I30"/>
+    <mergeCell ref="G80:H80"/>
+    <mergeCell ref="G42:H42"/>
+    <mergeCell ref="D60:I60"/>
+    <mergeCell ref="D62:I62"/>
+    <mergeCell ref="D61:I61"/>
+    <mergeCell ref="G49:H49"/>
+    <mergeCell ref="D47:I47"/>
+    <mergeCell ref="D55:I55"/>
+    <mergeCell ref="G57:H57"/>
+    <mergeCell ref="G64:H64"/>
+    <mergeCell ref="D96:I96"/>
+    <mergeCell ref="D95:F95"/>
+    <mergeCell ref="G95:H95"/>
+    <mergeCell ref="D92:I92"/>
+    <mergeCell ref="D93:I93"/>
+    <mergeCell ref="D90:E90"/>
+    <mergeCell ref="D91:H91"/>
+    <mergeCell ref="E86:G86"/>
+    <mergeCell ref="D88:I88"/>
+    <mergeCell ref="H67:I67"/>
+    <mergeCell ref="G81:H81"/>
+    <mergeCell ref="D67:F67"/>
+    <mergeCell ref="F68:I68"/>
+    <mergeCell ref="D87:E87"/>
+    <mergeCell ref="G87:I87"/>
+    <mergeCell ref="D98:I98"/>
+    <mergeCell ref="D94:I94"/>
+    <mergeCell ref="H89:I89"/>
+    <mergeCell ref="D89:F89"/>
+    <mergeCell ref="D97:I97"/>
     <mergeCell ref="D106:E106"/>
     <mergeCell ref="D99:G99"/>
     <mergeCell ref="G126:I126"/>
@@ -7565,79 +7638,6 @@
     <mergeCell ref="D108:E108"/>
     <mergeCell ref="B112:J113"/>
     <mergeCell ref="G124:J124"/>
-    <mergeCell ref="D98:I98"/>
-    <mergeCell ref="D94:I94"/>
-    <mergeCell ref="H89:I89"/>
-    <mergeCell ref="D89:F89"/>
-    <mergeCell ref="D97:I97"/>
-    <mergeCell ref="G64:H64"/>
-    <mergeCell ref="D96:I96"/>
-    <mergeCell ref="D95:F95"/>
-    <mergeCell ref="G95:H95"/>
-    <mergeCell ref="D92:I92"/>
-    <mergeCell ref="D93:I93"/>
-    <mergeCell ref="D90:E90"/>
-    <mergeCell ref="D91:H91"/>
-    <mergeCell ref="E86:G86"/>
-    <mergeCell ref="D88:I88"/>
-    <mergeCell ref="H67:I67"/>
-    <mergeCell ref="G81:H81"/>
-    <mergeCell ref="D67:F67"/>
-    <mergeCell ref="F68:I68"/>
-    <mergeCell ref="D87:E87"/>
-    <mergeCell ref="G87:I87"/>
-    <mergeCell ref="D60:I60"/>
-    <mergeCell ref="D62:I62"/>
-    <mergeCell ref="D61:I61"/>
-    <mergeCell ref="G49:H49"/>
-    <mergeCell ref="D47:I47"/>
-    <mergeCell ref="D55:I55"/>
-    <mergeCell ref="G57:H57"/>
-    <mergeCell ref="D84:I84"/>
-    <mergeCell ref="D69:I69"/>
-    <mergeCell ref="D8:I8"/>
-    <mergeCell ref="D9:I9"/>
-    <mergeCell ref="D10:I10"/>
-    <mergeCell ref="D11:I11"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="D14:I14"/>
-    <mergeCell ref="G27:H27"/>
-    <mergeCell ref="D25:I25"/>
-    <mergeCell ref="G20:H20"/>
-    <mergeCell ref="D19:I19"/>
-    <mergeCell ref="D18:I18"/>
-    <mergeCell ref="D30:I30"/>
-    <mergeCell ref="G80:H80"/>
-    <mergeCell ref="G42:H42"/>
-    <mergeCell ref="D78:I78"/>
-    <mergeCell ref="G71:H71"/>
-    <mergeCell ref="D76:I76"/>
-    <mergeCell ref="D66:H66"/>
-    <mergeCell ref="D77:I77"/>
-    <mergeCell ref="D73:I73"/>
-    <mergeCell ref="D70:E70"/>
-    <mergeCell ref="D74:F74"/>
-    <mergeCell ref="D31:I31"/>
-    <mergeCell ref="G35:H35"/>
-    <mergeCell ref="D40:I40"/>
-    <mergeCell ref="D33:I33"/>
-    <mergeCell ref="D46:I46"/>
-    <mergeCell ref="D43:I43"/>
-    <mergeCell ref="D120:H120"/>
-    <mergeCell ref="G123:J123"/>
-    <mergeCell ref="D121:J121"/>
-    <mergeCell ref="D143:J143"/>
-    <mergeCell ref="C177:J177"/>
-    <mergeCell ref="D135:J135"/>
-    <mergeCell ref="D172:J172"/>
-    <mergeCell ref="G146:J146"/>
-    <mergeCell ref="G152:I152"/>
-    <mergeCell ref="D149:J150"/>
-    <mergeCell ref="D187:J187"/>
-    <mergeCell ref="D185:J185"/>
-    <mergeCell ref="C175:J176"/>
-    <mergeCell ref="D164:J164"/>
-    <mergeCell ref="D157:J157"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/attendance_sheet.xlsx
+++ b/attendance_sheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\repositary\3rd_Year_5th_Semester\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5B5A91C-554C-4E64-9F8C-B4D7725BDBE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B223750E-3FD4-4F5D-85F4-E1F7C93F1F94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{EB654061-A886-47D1-BF86-9B1A84FCE7FB}"/>
   </bookViews>
@@ -544,11 +544,35 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -566,30 +590,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -993,14 +993,14 @@
       <c r="C8" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D8" s="32" t="s">
+      <c r="D8" s="33" t="s">
         <v>20</v>
       </c>
-      <c r="E8" s="32"/>
-      <c r="F8" s="32"/>
-      <c r="G8" s="32"/>
-      <c r="H8" s="32"/>
-      <c r="I8" s="32"/>
+      <c r="E8" s="33"/>
+      <c r="F8" s="33"/>
+      <c r="G8" s="33"/>
+      <c r="H8" s="33"/>
+      <c r="I8" s="33"/>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B9" s="4">
@@ -1009,14 +1009,14 @@
       <c r="C9" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D9" s="32" t="s">
+      <c r="D9" s="33" t="s">
         <v>20</v>
       </c>
-      <c r="E9" s="32"/>
-      <c r="F9" s="32"/>
-      <c r="G9" s="32"/>
-      <c r="H9" s="32"/>
-      <c r="I9" s="32"/>
+      <c r="E9" s="33"/>
+      <c r="F9" s="33"/>
+      <c r="G9" s="33"/>
+      <c r="H9" s="33"/>
+      <c r="I9" s="33"/>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B10" s="4">
@@ -1025,14 +1025,14 @@
       <c r="C10" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D10" s="32" t="s">
+      <c r="D10" s="33" t="s">
         <v>20</v>
       </c>
-      <c r="E10" s="32"/>
-      <c r="F10" s="32"/>
-      <c r="G10" s="32"/>
-      <c r="H10" s="32"/>
-      <c r="I10" s="32"/>
+      <c r="E10" s="33"/>
+      <c r="F10" s="33"/>
+      <c r="G10" s="33"/>
+      <c r="H10" s="33"/>
+      <c r="I10" s="33"/>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B11" s="4">
@@ -1041,14 +1041,14 @@
       <c r="C11" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D11" s="32" t="s">
+      <c r="D11" s="33" t="s">
         <v>20</v>
       </c>
-      <c r="E11" s="32"/>
-      <c r="F11" s="32"/>
-      <c r="G11" s="32"/>
-      <c r="H11" s="32"/>
-      <c r="I11" s="32"/>
+      <c r="E11" s="33"/>
+      <c r="F11" s="33"/>
+      <c r="G11" s="33"/>
+      <c r="H11" s="33"/>
+      <c r="I11" s="33"/>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B12" s="4">
@@ -1092,10 +1092,10 @@
       <c r="F13" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="G13" s="32" t="s">
+      <c r="G13" s="33" t="s">
         <v>18</v>
       </c>
-      <c r="H13" s="32"/>
+      <c r="H13" s="33"/>
       <c r="I13" s="1" t="s">
         <v>14</v>
       </c>
@@ -1107,14 +1107,14 @@
       <c r="C14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D14" s="32" t="s">
+      <c r="D14" s="33" t="s">
         <v>19</v>
       </c>
-      <c r="E14" s="32"/>
-      <c r="F14" s="32"/>
-      <c r="G14" s="32"/>
-      <c r="H14" s="32"/>
-      <c r="I14" s="32"/>
+      <c r="E14" s="33"/>
+      <c r="F14" s="33"/>
+      <c r="G14" s="33"/>
+      <c r="H14" s="33"/>
+      <c r="I14" s="33"/>
     </row>
     <row r="15" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B15" s="4">
@@ -1201,14 +1201,14 @@
       <c r="C18" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D18" s="32" t="s">
+      <c r="D18" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="E18" s="32"/>
-      <c r="F18" s="32"/>
-      <c r="G18" s="32"/>
-      <c r="H18" s="32"/>
-      <c r="I18" s="32"/>
+      <c r="E18" s="33"/>
+      <c r="F18" s="33"/>
+      <c r="G18" s="33"/>
+      <c r="H18" s="33"/>
+      <c r="I18" s="33"/>
     </row>
     <row r="19" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B19" s="4">
@@ -1217,14 +1217,14 @@
       <c r="C19" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D19" s="32" t="s">
+      <c r="D19" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="E19" s="32"/>
-      <c r="F19" s="32"/>
-      <c r="G19" s="32"/>
-      <c r="H19" s="32"/>
-      <c r="I19" s="32"/>
+      <c r="E19" s="33"/>
+      <c r="F19" s="33"/>
+      <c r="G19" s="33"/>
+      <c r="H19" s="33"/>
+      <c r="I19" s="33"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B20" s="4">
@@ -1242,10 +1242,10 @@
       <c r="F20" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G20" s="32" t="s">
+      <c r="G20" s="33" t="s">
         <v>15</v>
       </c>
-      <c r="H20" s="32"/>
+      <c r="H20" s="33"/>
       <c r="I20" s="1" t="s">
         <v>14</v>
       </c>
@@ -1361,14 +1361,14 @@
       <c r="C25" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D25" s="32" t="s">
+      <c r="D25" s="33" t="s">
         <v>26</v>
       </c>
-      <c r="E25" s="32"/>
-      <c r="F25" s="32"/>
-      <c r="G25" s="32"/>
-      <c r="H25" s="32"/>
-      <c r="I25" s="32"/>
+      <c r="E25" s="33"/>
+      <c r="F25" s="33"/>
+      <c r="G25" s="33"/>
+      <c r="H25" s="33"/>
+      <c r="I25" s="33"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B26" s="4">
@@ -1412,10 +1412,10 @@
       <c r="F27" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G27" s="32" t="s">
+      <c r="G27" s="33" t="s">
         <v>18</v>
       </c>
-      <c r="H27" s="32"/>
+      <c r="H27" s="33"/>
       <c r="I27" s="1" t="s">
         <v>14</v>
       </c>
@@ -1479,14 +1479,14 @@
       <c r="C30" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D30" s="33" t="s">
+      <c r="D30" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="E30" s="33"/>
-      <c r="F30" s="33"/>
-      <c r="G30" s="33"/>
-      <c r="H30" s="33"/>
-      <c r="I30" s="33"/>
+      <c r="E30" s="32"/>
+      <c r="F30" s="32"/>
+      <c r="G30" s="32"/>
+      <c r="H30" s="32"/>
+      <c r="I30" s="32"/>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B31" s="4">
@@ -1495,14 +1495,14 @@
       <c r="C31" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D31" s="33" t="s">
+      <c r="D31" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="E31" s="33"/>
-      <c r="F31" s="33"/>
-      <c r="G31" s="33"/>
-      <c r="H31" s="33"/>
-      <c r="I31" s="33"/>
+      <c r="E31" s="32"/>
+      <c r="F31" s="32"/>
+      <c r="G31" s="32"/>
+      <c r="H31" s="32"/>
+      <c r="I31" s="32"/>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B32" s="4">
@@ -1537,14 +1537,14 @@
       <c r="C33" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D33" s="33" t="s">
+      <c r="D33" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="E33" s="33"/>
-      <c r="F33" s="33"/>
-      <c r="G33" s="33"/>
-      <c r="H33" s="33"/>
-      <c r="I33" s="33"/>
+      <c r="E33" s="32"/>
+      <c r="F33" s="32"/>
+      <c r="G33" s="32"/>
+      <c r="H33" s="32"/>
+      <c r="I33" s="32"/>
     </row>
     <row r="34" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B34" s="4">
@@ -1588,10 +1588,10 @@
       <c r="F35" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G35" s="33" t="s">
+      <c r="G35" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="H35" s="33"/>
+      <c r="H35" s="32"/>
       <c r="I35" s="1" t="s">
         <v>14</v>
       </c>
@@ -1707,14 +1707,14 @@
       <c r="C40" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D40" s="33" t="s">
+      <c r="D40" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="E40" s="33"/>
-      <c r="F40" s="33"/>
-      <c r="G40" s="33"/>
-      <c r="H40" s="33"/>
-      <c r="I40" s="33"/>
+      <c r="E40" s="32"/>
+      <c r="F40" s="32"/>
+      <c r="G40" s="32"/>
+      <c r="H40" s="32"/>
+      <c r="I40" s="32"/>
     </row>
     <row r="41" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B41" s="4">
@@ -1758,10 +1758,10 @@
       <c r="F42" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G42" s="33" t="s">
+      <c r="G42" s="32" t="s">
         <v>28</v>
       </c>
-      <c r="H42" s="33"/>
+      <c r="H42" s="32"/>
       <c r="I42" s="1" t="s">
         <v>15</v>
       </c>
@@ -1773,14 +1773,14 @@
       <c r="C43" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D43" s="33" t="s">
+      <c r="D43" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="E43" s="33"/>
-      <c r="F43" s="33"/>
-      <c r="G43" s="33"/>
-      <c r="H43" s="33"/>
-      <c r="I43" s="33"/>
+      <c r="E43" s="32"/>
+      <c r="F43" s="32"/>
+      <c r="G43" s="32"/>
+      <c r="H43" s="32"/>
+      <c r="I43" s="32"/>
     </row>
     <row r="44" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B44" s="4">
@@ -1844,14 +1844,14 @@
       <c r="C46" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D46" s="33" t="s">
+      <c r="D46" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="E46" s="33"/>
-      <c r="F46" s="33"/>
-      <c r="G46" s="33"/>
-      <c r="H46" s="33"/>
-      <c r="I46" s="33"/>
+      <c r="E46" s="32"/>
+      <c r="F46" s="32"/>
+      <c r="G46" s="32"/>
+      <c r="H46" s="32"/>
+      <c r="I46" s="32"/>
     </row>
     <row r="47" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B47" s="4">
@@ -1863,11 +1863,11 @@
       <c r="D47" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E47" s="25"/>
-      <c r="F47" s="25"/>
-      <c r="G47" s="25"/>
-      <c r="H47" s="25"/>
-      <c r="I47" s="24"/>
+      <c r="E47" s="24"/>
+      <c r="F47" s="24"/>
+      <c r="G47" s="24"/>
+      <c r="H47" s="24"/>
+      <c r="I47" s="25"/>
     </row>
     <row r="48" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B48" s="4">
@@ -1914,7 +1914,7 @@
       <c r="G49" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="H49" s="24"/>
+      <c r="H49" s="25"/>
       <c r="I49" s="1" t="s">
         <v>30</v>
       </c>
@@ -2056,14 +2056,14 @@
       <c r="C55" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="D55" s="25" t="s">
+      <c r="D55" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="E55" s="25"/>
-      <c r="F55" s="25"/>
-      <c r="G55" s="25"/>
-      <c r="H55" s="25"/>
-      <c r="I55" s="25"/>
+      <c r="E55" s="24"/>
+      <c r="F55" s="24"/>
+      <c r="G55" s="24"/>
+      <c r="H55" s="24"/>
+      <c r="I55" s="24"/>
     </row>
     <row r="56" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B56" s="4">
@@ -2110,7 +2110,7 @@
       <c r="G57" s="23" t="s">
         <v>37</v>
       </c>
-      <c r="H57" s="24"/>
+      <c r="H57" s="25"/>
       <c r="I57" s="1" t="s">
         <v>36</v>
       </c>
@@ -2177,11 +2177,11 @@
       <c r="D60" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E60" s="25"/>
-      <c r="F60" s="25"/>
-      <c r="G60" s="25"/>
-      <c r="H60" s="25"/>
-      <c r="I60" s="24"/>
+      <c r="E60" s="24"/>
+      <c r="F60" s="24"/>
+      <c r="G60" s="24"/>
+      <c r="H60" s="24"/>
+      <c r="I60" s="25"/>
     </row>
     <row r="61" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B61" s="4">
@@ -2193,11 +2193,11 @@
       <c r="D61" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E61" s="25"/>
-      <c r="F61" s="25"/>
-      <c r="G61" s="25"/>
-      <c r="H61" s="25"/>
-      <c r="I61" s="24"/>
+      <c r="E61" s="24"/>
+      <c r="F61" s="24"/>
+      <c r="G61" s="24"/>
+      <c r="H61" s="24"/>
+      <c r="I61" s="25"/>
     </row>
     <row r="62" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B62" s="4">
@@ -2209,11 +2209,11 @@
       <c r="D62" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E62" s="25"/>
-      <c r="F62" s="25"/>
-      <c r="G62" s="25"/>
-      <c r="H62" s="25"/>
-      <c r="I62" s="24"/>
+      <c r="E62" s="24"/>
+      <c r="F62" s="24"/>
+      <c r="G62" s="24"/>
+      <c r="H62" s="24"/>
+      <c r="I62" s="25"/>
     </row>
     <row r="63" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B63" s="4">
@@ -2260,7 +2260,7 @@
       <c r="G64" s="23" t="s">
         <v>37</v>
       </c>
-      <c r="H64" s="24"/>
+      <c r="H64" s="25"/>
       <c r="I64" s="1" t="s">
         <v>14</v>
       </c>
@@ -2301,10 +2301,10 @@
       <c r="D66" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="E66" s="25"/>
-      <c r="F66" s="25"/>
-      <c r="G66" s="25"/>
-      <c r="H66" s="24"/>
+      <c r="E66" s="24"/>
+      <c r="F66" s="24"/>
+      <c r="G66" s="24"/>
+      <c r="H66" s="25"/>
       <c r="I66" s="1" t="s">
         <v>16</v>
       </c>
@@ -2319,15 +2319,15 @@
       <c r="D67" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="E67" s="25"/>
-      <c r="F67" s="24"/>
+      <c r="E67" s="24"/>
+      <c r="F67" s="25"/>
       <c r="G67" s="3" t="s">
         <v>16</v>
       </c>
       <c r="H67" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="I67" s="24"/>
+      <c r="I67" s="25"/>
     </row>
     <row r="68" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B68" s="4">
@@ -2345,9 +2345,9 @@
       <c r="F68" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="G68" s="25"/>
-      <c r="H68" s="25"/>
-      <c r="I68" s="24"/>
+      <c r="G68" s="24"/>
+      <c r="H68" s="24"/>
+      <c r="I68" s="25"/>
     </row>
     <row r="69" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B69" s="4">
@@ -2359,11 +2359,11 @@
       <c r="D69" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E69" s="25"/>
-      <c r="F69" s="25"/>
-      <c r="G69" s="25"/>
-      <c r="H69" s="25"/>
-      <c r="I69" s="24"/>
+      <c r="E69" s="24"/>
+      <c r="F69" s="24"/>
+      <c r="G69" s="24"/>
+      <c r="H69" s="24"/>
+      <c r="I69" s="25"/>
     </row>
     <row r="70" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B70" s="4">
@@ -2375,7 +2375,7 @@
       <c r="D70" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="E70" s="24"/>
+      <c r="E70" s="25"/>
       <c r="F70" s="3" t="s">
         <v>15</v>
       </c>
@@ -2408,7 +2408,7 @@
       <c r="G71" s="23" t="s">
         <v>37</v>
       </c>
-      <c r="H71" s="24"/>
+      <c r="H71" s="25"/>
       <c r="I71" s="1" t="s">
         <v>14</v>
       </c>
@@ -2449,11 +2449,11 @@
       <c r="D73" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E73" s="25"/>
-      <c r="F73" s="25"/>
-      <c r="G73" s="25"/>
-      <c r="H73" s="25"/>
-      <c r="I73" s="24"/>
+      <c r="E73" s="24"/>
+      <c r="F73" s="24"/>
+      <c r="G73" s="24"/>
+      <c r="H73" s="24"/>
+      <c r="I73" s="25"/>
     </row>
     <row r="74" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B74" s="4">
@@ -2465,8 +2465,8 @@
       <c r="D74" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="E74" s="25"/>
-      <c r="F74" s="24"/>
+      <c r="E74" s="24"/>
+      <c r="F74" s="25"/>
       <c r="G74" s="3" t="s">
         <v>16</v>
       </c>
@@ -2505,11 +2505,11 @@
       <c r="D76" s="23" t="s">
         <v>39</v>
       </c>
-      <c r="E76" s="25"/>
-      <c r="F76" s="25"/>
-      <c r="G76" s="25"/>
-      <c r="H76" s="25"/>
-      <c r="I76" s="24"/>
+      <c r="E76" s="24"/>
+      <c r="F76" s="24"/>
+      <c r="G76" s="24"/>
+      <c r="H76" s="24"/>
+      <c r="I76" s="25"/>
     </row>
     <row r="77" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B77" s="4">
@@ -2521,11 +2521,11 @@
       <c r="D77" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E77" s="25"/>
-      <c r="F77" s="25"/>
-      <c r="G77" s="25"/>
-      <c r="H77" s="25"/>
-      <c r="I77" s="24"/>
+      <c r="E77" s="24"/>
+      <c r="F77" s="24"/>
+      <c r="G77" s="24"/>
+      <c r="H77" s="24"/>
+      <c r="I77" s="25"/>
     </row>
     <row r="78" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B78" s="4">
@@ -2537,11 +2537,11 @@
       <c r="D78" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E78" s="25"/>
-      <c r="F78" s="25"/>
-      <c r="G78" s="25"/>
-      <c r="H78" s="25"/>
-      <c r="I78" s="24"/>
+      <c r="E78" s="24"/>
+      <c r="F78" s="24"/>
+      <c r="G78" s="24"/>
+      <c r="H78" s="24"/>
+      <c r="I78" s="25"/>
     </row>
     <row r="79" spans="2:9" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B79" s="16" t="s">
@@ -2588,7 +2588,7 @@
       <c r="G80" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="H80" s="24"/>
+      <c r="H80" s="25"/>
       <c r="I80" s="1" t="s">
         <v>14</v>
       </c>
@@ -2612,7 +2612,7 @@
       <c r="G81" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="H81" s="24"/>
+      <c r="H81" s="25"/>
       <c r="I81" s="1" t="s">
         <v>16</v>
       </c>
@@ -2679,11 +2679,11 @@
       <c r="D84" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E84" s="25"/>
-      <c r="F84" s="25"/>
-      <c r="G84" s="25"/>
-      <c r="H84" s="25"/>
-      <c r="I84" s="24"/>
+      <c r="E84" s="24"/>
+      <c r="F84" s="24"/>
+      <c r="G84" s="24"/>
+      <c r="H84" s="24"/>
+      <c r="I84" s="25"/>
     </row>
     <row r="85" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B85" s="4">
@@ -2724,8 +2724,8 @@
       <c r="E86" s="23" t="s">
         <v>43</v>
       </c>
-      <c r="F86" s="25"/>
-      <c r="G86" s="24"/>
+      <c r="F86" s="24"/>
+      <c r="G86" s="25"/>
       <c r="H86" s="3" t="s">
         <v>14</v>
       </c>
@@ -2743,15 +2743,15 @@
       <c r="D87" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="E87" s="24"/>
+      <c r="E87" s="25"/>
       <c r="F87" s="3" t="s">
         <v>16</v>
       </c>
       <c r="G87" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="H87" s="25"/>
-      <c r="I87" s="24"/>
+      <c r="H87" s="24"/>
+      <c r="I87" s="25"/>
     </row>
     <row r="88" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B88" s="4">
@@ -2763,11 +2763,11 @@
       <c r="D88" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E88" s="25"/>
-      <c r="F88" s="25"/>
-      <c r="G88" s="25"/>
-      <c r="H88" s="25"/>
-      <c r="I88" s="24"/>
+      <c r="E88" s="24"/>
+      <c r="F88" s="24"/>
+      <c r="G88" s="24"/>
+      <c r="H88" s="24"/>
+      <c r="I88" s="25"/>
     </row>
     <row r="89" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B89" s="4">
@@ -2779,15 +2779,15 @@
       <c r="D89" s="23" t="s">
         <v>44</v>
       </c>
-      <c r="E89" s="25"/>
-      <c r="F89" s="24"/>
+      <c r="E89" s="24"/>
+      <c r="F89" s="25"/>
       <c r="G89" s="3" t="s">
         <v>16</v>
       </c>
       <c r="H89" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="I89" s="24"/>
+      <c r="I89" s="25"/>
     </row>
     <row r="90" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B90" s="4">
@@ -2799,7 +2799,7 @@
       <c r="D90" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="E90" s="24"/>
+      <c r="E90" s="25"/>
       <c r="F90" s="3" t="s">
         <v>16</v>
       </c>
@@ -2824,10 +2824,10 @@
       <c r="D91" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E91" s="25"/>
-      <c r="F91" s="25"/>
-      <c r="G91" s="25"/>
-      <c r="H91" s="24"/>
+      <c r="E91" s="24"/>
+      <c r="F91" s="24"/>
+      <c r="G91" s="24"/>
+      <c r="H91" s="25"/>
       <c r="I91" s="18" t="s">
         <v>45</v>
       </c>
@@ -2842,11 +2842,11 @@
       <c r="D92" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E92" s="25"/>
-      <c r="F92" s="25"/>
-      <c r="G92" s="25"/>
-      <c r="H92" s="25"/>
-      <c r="I92" s="24"/>
+      <c r="E92" s="24"/>
+      <c r="F92" s="24"/>
+      <c r="G92" s="24"/>
+      <c r="H92" s="24"/>
+      <c r="I92" s="25"/>
     </row>
     <row r="93" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B93" s="4">
@@ -2858,11 +2858,11 @@
       <c r="D93" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="E93" s="25"/>
-      <c r="F93" s="25"/>
-      <c r="G93" s="25"/>
-      <c r="H93" s="25"/>
-      <c r="I93" s="24"/>
+      <c r="E93" s="24"/>
+      <c r="F93" s="24"/>
+      <c r="G93" s="24"/>
+      <c r="H93" s="24"/>
+      <c r="I93" s="25"/>
     </row>
     <row r="94" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B94" s="4">
@@ -2874,11 +2874,11 @@
       <c r="D94" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="E94" s="25"/>
-      <c r="F94" s="25"/>
-      <c r="G94" s="25"/>
-      <c r="H94" s="25"/>
-      <c r="I94" s="24"/>
+      <c r="E94" s="24"/>
+      <c r="F94" s="24"/>
+      <c r="G94" s="24"/>
+      <c r="H94" s="24"/>
+      <c r="I94" s="25"/>
     </row>
     <row r="95" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B95" s="4">
@@ -2890,12 +2890,12 @@
       <c r="D95" s="23" t="s">
         <v>47</v>
       </c>
-      <c r="E95" s="25"/>
-      <c r="F95" s="24"/>
+      <c r="E95" s="24"/>
+      <c r="F95" s="25"/>
       <c r="G95" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="H95" s="24"/>
+      <c r="H95" s="25"/>
       <c r="I95" s="1" t="s">
         <v>14</v>
       </c>
@@ -2910,11 +2910,11 @@
       <c r="D96" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E96" s="25"/>
-      <c r="F96" s="25"/>
-      <c r="G96" s="25"/>
-      <c r="H96" s="25"/>
-      <c r="I96" s="24"/>
+      <c r="E96" s="24"/>
+      <c r="F96" s="24"/>
+      <c r="G96" s="24"/>
+      <c r="H96" s="24"/>
+      <c r="I96" s="25"/>
     </row>
     <row r="97" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B97" s="4">
@@ -2926,11 +2926,11 @@
       <c r="D97" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="E97" s="25"/>
-      <c r="F97" s="25"/>
-      <c r="G97" s="25"/>
-      <c r="H97" s="25"/>
-      <c r="I97" s="24"/>
+      <c r="E97" s="24"/>
+      <c r="F97" s="24"/>
+      <c r="G97" s="24"/>
+      <c r="H97" s="24"/>
+      <c r="I97" s="25"/>
     </row>
     <row r="98" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B98" s="4">
@@ -2942,11 +2942,11 @@
       <c r="D98" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E98" s="25"/>
-      <c r="F98" s="25"/>
-      <c r="G98" s="25"/>
-      <c r="H98" s="25"/>
-      <c r="I98" s="24"/>
+      <c r="E98" s="24"/>
+      <c r="F98" s="24"/>
+      <c r="G98" s="24"/>
+      <c r="H98" s="24"/>
+      <c r="I98" s="25"/>
     </row>
     <row r="99" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B99" s="4">
@@ -2958,9 +2958,9 @@
       <c r="D99" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="E99" s="25"/>
-      <c r="F99" s="25"/>
-      <c r="G99" s="24"/>
+      <c r="E99" s="24"/>
+      <c r="F99" s="24"/>
+      <c r="G99" s="25"/>
       <c r="H99" s="3" t="s">
         <v>49</v>
       </c>
@@ -2987,18 +2987,18 @@
       <c r="G100" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="H100" s="25"/>
-      <c r="I100" s="24"/>
+      <c r="H100" s="24"/>
+      <c r="I100" s="25"/>
     </row>
     <row r="101" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B101" s="23"/>
-      <c r="C101" s="25"/>
-      <c r="D101" s="25"/>
-      <c r="E101" s="25"/>
-      <c r="F101" s="25"/>
-      <c r="G101" s="25"/>
-      <c r="H101" s="25"/>
-      <c r="I101" s="24"/>
+      <c r="C101" s="24"/>
+      <c r="D101" s="24"/>
+      <c r="E101" s="24"/>
+      <c r="F101" s="24"/>
+      <c r="G101" s="24"/>
+      <c r="H101" s="24"/>
+      <c r="I101" s="25"/>
     </row>
     <row r="102" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B102" s="3"/>
@@ -3020,7 +3020,7 @@
       <c r="D103" s="23" t="s">
         <v>51</v>
       </c>
-      <c r="E103" s="24"/>
+      <c r="E103" s="25"/>
       <c r="F103" s="3"/>
       <c r="G103" s="3"/>
       <c r="H103" s="3"/>
@@ -3036,7 +3036,7 @@
       <c r="D104" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="E104" s="24"/>
+      <c r="E104" s="25"/>
       <c r="F104" s="3"/>
       <c r="G104" s="3"/>
       <c r="H104" s="3"/>
@@ -3052,7 +3052,7 @@
       <c r="D105" s="23" t="s">
         <v>53</v>
       </c>
-      <c r="E105" s="24"/>
+      <c r="E105" s="25"/>
       <c r="F105" s="3"/>
       <c r="G105" s="3"/>
       <c r="H105" s="3"/>
@@ -3068,7 +3068,7 @@
       <c r="D106" s="23" t="s">
         <v>54</v>
       </c>
-      <c r="E106" s="24"/>
+      <c r="E106" s="25"/>
       <c r="F106" s="3"/>
       <c r="G106" s="3"/>
       <c r="H106" s="3"/>
@@ -3084,7 +3084,7 @@
       <c r="D107" s="23" t="s">
         <v>55</v>
       </c>
-      <c r="E107" s="24"/>
+      <c r="E107" s="25"/>
       <c r="F107" s="3"/>
       <c r="G107" s="3"/>
       <c r="H107" s="3"/>
@@ -3100,7 +3100,7 @@
       <c r="D108" s="23" t="s">
         <v>56</v>
       </c>
-      <c r="E108" s="24"/>
+      <c r="E108" s="25"/>
       <c r="F108" s="3"/>
       <c r="G108" s="3"/>
       <c r="H108" s="3"/>
@@ -3137,28 +3137,28 @@
       <c r="I111" s="20"/>
     </row>
     <row r="112" spans="2:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B112" s="26" t="s">
+      <c r="B112" s="34" t="s">
         <v>57</v>
       </c>
-      <c r="C112" s="27"/>
-      <c r="D112" s="27"/>
-      <c r="E112" s="27"/>
-      <c r="F112" s="27"/>
-      <c r="G112" s="27"/>
-      <c r="H112" s="27"/>
-      <c r="I112" s="27"/>
-      <c r="J112" s="28"/>
+      <c r="C112" s="35"/>
+      <c r="D112" s="35"/>
+      <c r="E112" s="35"/>
+      <c r="F112" s="35"/>
+      <c r="G112" s="35"/>
+      <c r="H112" s="35"/>
+      <c r="I112" s="35"/>
+      <c r="J112" s="36"/>
     </row>
     <row r="113" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B113" s="29"/>
-      <c r="C113" s="30"/>
-      <c r="D113" s="30"/>
-      <c r="E113" s="30"/>
-      <c r="F113" s="30"/>
-      <c r="G113" s="30"/>
-      <c r="H113" s="30"/>
-      <c r="I113" s="30"/>
-      <c r="J113" s="31"/>
+      <c r="B113" s="37"/>
+      <c r="C113" s="38"/>
+      <c r="D113" s="38"/>
+      <c r="E113" s="38"/>
+      <c r="F113" s="38"/>
+      <c r="G113" s="38"/>
+      <c r="H113" s="38"/>
+      <c r="I113" s="38"/>
+      <c r="J113" s="39"/>
     </row>
     <row r="114" spans="2:10" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B114" s="8" t="s">
@@ -3292,10 +3292,10 @@
       <c r="F118" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="G118" s="25"/>
-      <c r="H118" s="25"/>
-      <c r="I118" s="25"/>
-      <c r="J118" s="24"/>
+      <c r="G118" s="24"/>
+      <c r="H118" s="24"/>
+      <c r="I118" s="24"/>
+      <c r="J118" s="25"/>
     </row>
     <row r="119" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B119" s="4">
@@ -3336,10 +3336,10 @@
       <c r="D120" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="E120" s="25"/>
-      <c r="F120" s="25"/>
-      <c r="G120" s="25"/>
-      <c r="H120" s="24"/>
+      <c r="E120" s="24"/>
+      <c r="F120" s="24"/>
+      <c r="G120" s="24"/>
+      <c r="H120" s="25"/>
       <c r="I120" s="1" t="s">
         <v>16</v>
       </c>
@@ -3357,12 +3357,12 @@
       <c r="D121" s="23" t="s">
         <v>65</v>
       </c>
-      <c r="E121" s="25"/>
-      <c r="F121" s="25"/>
-      <c r="G121" s="25"/>
-      <c r="H121" s="25"/>
-      <c r="I121" s="25"/>
-      <c r="J121" s="24"/>
+      <c r="E121" s="24"/>
+      <c r="F121" s="24"/>
+      <c r="G121" s="24"/>
+      <c r="H121" s="24"/>
+      <c r="I121" s="24"/>
+      <c r="J121" s="25"/>
     </row>
     <row r="122" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B122" s="4">
@@ -3412,9 +3412,9 @@
       <c r="G123" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="H123" s="25"/>
-      <c r="I123" s="25"/>
-      <c r="J123" s="24"/>
+      <c r="H123" s="24"/>
+      <c r="I123" s="24"/>
+      <c r="J123" s="25"/>
     </row>
     <row r="124" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B124" s="4">
@@ -3435,9 +3435,9 @@
       <c r="G124" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="H124" s="25"/>
-      <c r="I124" s="25"/>
-      <c r="J124" s="24"/>
+      <c r="H124" s="24"/>
+      <c r="I124" s="24"/>
+      <c r="J124" s="25"/>
     </row>
     <row r="125" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B125" s="4">
@@ -3455,10 +3455,10 @@
       <c r="F125" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="G125" s="25"/>
-      <c r="H125" s="25"/>
-      <c r="I125" s="25"/>
-      <c r="J125" s="24"/>
+      <c r="G125" s="24"/>
+      <c r="H125" s="24"/>
+      <c r="I125" s="24"/>
+      <c r="J125" s="25"/>
     </row>
     <row r="126" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B126" s="4">
@@ -3479,8 +3479,8 @@
       <c r="G126" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="H126" s="25"/>
-      <c r="I126" s="24"/>
+      <c r="H126" s="24"/>
+      <c r="I126" s="25"/>
       <c r="J126" s="1" t="s">
         <v>16</v>
       </c>
@@ -3501,10 +3501,10 @@
       <c r="F127" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="G127" s="25"/>
-      <c r="H127" s="25"/>
-      <c r="I127" s="25"/>
-      <c r="J127" s="24"/>
+      <c r="G127" s="24"/>
+      <c r="H127" s="24"/>
+      <c r="I127" s="24"/>
+      <c r="J127" s="25"/>
     </row>
     <row r="128" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B128" s="4">
@@ -3516,12 +3516,12 @@
       <c r="D128" s="23" t="s">
         <v>65</v>
       </c>
-      <c r="E128" s="25"/>
-      <c r="F128" s="25"/>
-      <c r="G128" s="25"/>
-      <c r="H128" s="25"/>
-      <c r="I128" s="25"/>
-      <c r="J128" s="24"/>
+      <c r="E128" s="24"/>
+      <c r="F128" s="24"/>
+      <c r="G128" s="24"/>
+      <c r="H128" s="24"/>
+      <c r="I128" s="24"/>
+      <c r="J128" s="25"/>
     </row>
     <row r="129" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B129" s="4">
@@ -3707,12 +3707,12 @@
       <c r="D135" s="23" t="s">
         <v>65</v>
       </c>
-      <c r="E135" s="25"/>
-      <c r="F135" s="25"/>
-      <c r="G135" s="25"/>
-      <c r="H135" s="25"/>
-      <c r="I135" s="25"/>
-      <c r="J135" s="24"/>
+      <c r="E135" s="24"/>
+      <c r="F135" s="24"/>
+      <c r="G135" s="24"/>
+      <c r="H135" s="24"/>
+      <c r="I135" s="24"/>
+      <c r="J135" s="25"/>
     </row>
     <row r="136" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B136" s="4">
@@ -3927,12 +3927,12 @@
       <c r="D143" s="23" t="s">
         <v>65</v>
       </c>
-      <c r="E143" s="25"/>
-      <c r="F143" s="25"/>
-      <c r="G143" s="25"/>
-      <c r="H143" s="25"/>
-      <c r="I143" s="25"/>
-      <c r="J143" s="24"/>
+      <c r="E143" s="24"/>
+      <c r="F143" s="24"/>
+      <c r="G143" s="24"/>
+      <c r="H143" s="24"/>
+      <c r="I143" s="24"/>
+      <c r="J143" s="25"/>
     </row>
     <row r="144" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B144" s="4">
@@ -4011,9 +4011,9 @@
       <c r="G146" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="H146" s="25"/>
-      <c r="I146" s="25"/>
-      <c r="J146" s="24"/>
+      <c r="H146" s="24"/>
+      <c r="I146" s="24"/>
+      <c r="J146" s="25"/>
     </row>
     <row r="147" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B147" s="4">
@@ -4080,15 +4080,15 @@
       <c r="C149" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D149" s="34" t="s">
+      <c r="D149" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="E149" s="35"/>
-      <c r="F149" s="35"/>
-      <c r="G149" s="35"/>
-      <c r="H149" s="35"/>
-      <c r="I149" s="35"/>
-      <c r="J149" s="36"/>
+      <c r="E149" s="27"/>
+      <c r="F149" s="27"/>
+      <c r="G149" s="27"/>
+      <c r="H149" s="27"/>
+      <c r="I149" s="27"/>
+      <c r="J149" s="30"/>
     </row>
     <row r="150" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B150" s="4">
@@ -4097,13 +4097,13 @@
       <c r="C150" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D150" s="37"/>
-      <c r="E150" s="38"/>
-      <c r="F150" s="38"/>
-      <c r="G150" s="38"/>
-      <c r="H150" s="38"/>
-      <c r="I150" s="38"/>
-      <c r="J150" s="39"/>
+      <c r="D150" s="28"/>
+      <c r="E150" s="29"/>
+      <c r="F150" s="29"/>
+      <c r="G150" s="29"/>
+      <c r="H150" s="29"/>
+      <c r="I150" s="29"/>
+      <c r="J150" s="31"/>
     </row>
     <row r="151" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B151" s="4">
@@ -4153,8 +4153,8 @@
       <c r="G152" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="H152" s="25"/>
-      <c r="I152" s="24"/>
+      <c r="H152" s="24"/>
+      <c r="I152" s="25"/>
       <c r="J152" s="1" t="s">
         <v>69</v>
       </c>
@@ -4285,12 +4285,12 @@
       <c r="D157" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E157" s="25"/>
-      <c r="F157" s="25"/>
-      <c r="G157" s="25"/>
-      <c r="H157" s="25"/>
-      <c r="I157" s="25"/>
-      <c r="J157" s="24"/>
+      <c r="E157" s="24"/>
+      <c r="F157" s="24"/>
+      <c r="G157" s="24"/>
+      <c r="H157" s="24"/>
+      <c r="I157" s="24"/>
+      <c r="J157" s="25"/>
     </row>
     <row r="158" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B158" s="4">
@@ -4474,12 +4474,12 @@
       <c r="D164" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E164" s="25"/>
-      <c r="F164" s="25"/>
-      <c r="G164" s="25"/>
-      <c r="H164" s="25"/>
-      <c r="I164" s="25"/>
-      <c r="J164" s="24"/>
+      <c r="E164" s="24"/>
+      <c r="F164" s="24"/>
+      <c r="G164" s="24"/>
+      <c r="H164" s="24"/>
+      <c r="I164" s="24"/>
+      <c r="J164" s="25"/>
     </row>
     <row r="165" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B165" s="4">
@@ -4680,12 +4680,12 @@
       <c r="D172" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E172" s="25"/>
-      <c r="F172" s="25"/>
-      <c r="G172" s="25"/>
-      <c r="H172" s="25"/>
-      <c r="I172" s="25"/>
-      <c r="J172" s="24"/>
+      <c r="E172" s="24"/>
+      <c r="F172" s="24"/>
+      <c r="G172" s="24"/>
+      <c r="H172" s="24"/>
+      <c r="I172" s="24"/>
+      <c r="J172" s="25"/>
     </row>
     <row r="173" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B173" s="4">
@@ -4749,29 +4749,29 @@
       <c r="B175" s="4">
         <v>45903</v>
       </c>
-      <c r="C175" s="34" t="s">
+      <c r="C175" s="26" t="s">
         <v>39</v>
       </c>
-      <c r="D175" s="35"/>
-      <c r="E175" s="35"/>
-      <c r="F175" s="35"/>
-      <c r="G175" s="35"/>
-      <c r="H175" s="35"/>
-      <c r="I175" s="35"/>
-      <c r="J175" s="35"/>
+      <c r="D175" s="27"/>
+      <c r="E175" s="27"/>
+      <c r="F175" s="27"/>
+      <c r="G175" s="27"/>
+      <c r="H175" s="27"/>
+      <c r="I175" s="27"/>
+      <c r="J175" s="27"/>
     </row>
     <row r="176" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B176" s="4">
         <v>45904</v>
       </c>
-      <c r="C176" s="37"/>
-      <c r="D176" s="38"/>
-      <c r="E176" s="38"/>
-      <c r="F176" s="38"/>
-      <c r="G176" s="38"/>
-      <c r="H176" s="38"/>
-      <c r="I176" s="38"/>
-      <c r="J176" s="38"/>
+      <c r="C176" s="28"/>
+      <c r="D176" s="29"/>
+      <c r="E176" s="29"/>
+      <c r="F176" s="29"/>
+      <c r="G176" s="29"/>
+      <c r="H176" s="29"/>
+      <c r="I176" s="29"/>
+      <c r="J176" s="29"/>
     </row>
     <row r="177" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B177" s="4">
@@ -4780,13 +4780,13 @@
       <c r="C177" s="23" t="s">
         <v>39</v>
       </c>
-      <c r="D177" s="25"/>
-      <c r="E177" s="25"/>
-      <c r="F177" s="25"/>
-      <c r="G177" s="25"/>
-      <c r="H177" s="25"/>
-      <c r="I177" s="25"/>
-      <c r="J177" s="24"/>
+      <c r="D177" s="24"/>
+      <c r="E177" s="24"/>
+      <c r="F177" s="24"/>
+      <c r="G177" s="24"/>
+      <c r="H177" s="24"/>
+      <c r="I177" s="24"/>
+      <c r="J177" s="25"/>
     </row>
     <row r="178" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B178" s="4">
@@ -4985,12 +4985,12 @@
       <c r="D185" s="23" t="s">
         <v>74</v>
       </c>
-      <c r="E185" s="25"/>
-      <c r="F185" s="25"/>
-      <c r="G185" s="25"/>
-      <c r="H185" s="25"/>
-      <c r="I185" s="25"/>
-      <c r="J185" s="24"/>
+      <c r="E185" s="24"/>
+      <c r="F185" s="24"/>
+      <c r="G185" s="24"/>
+      <c r="H185" s="24"/>
+      <c r="I185" s="24"/>
+      <c r="J185" s="25"/>
     </row>
     <row r="186" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B186" s="4">
@@ -5021,12 +5021,12 @@
       <c r="D187" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="E187" s="25"/>
-      <c r="F187" s="25"/>
-      <c r="G187" s="25"/>
-      <c r="H187" s="25"/>
-      <c r="I187" s="25"/>
-      <c r="J187" s="24"/>
+      <c r="E187" s="24"/>
+      <c r="F187" s="24"/>
+      <c r="G187" s="24"/>
+      <c r="H187" s="24"/>
+      <c r="I187" s="24"/>
+      <c r="J187" s="25"/>
     </row>
     <row r="188" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B188" s="3"/>
@@ -7549,35 +7549,50 @@
     </row>
   </sheetData>
   <mergeCells count="89">
-    <mergeCell ref="D187:J187"/>
-    <mergeCell ref="D185:J185"/>
-    <mergeCell ref="C175:J176"/>
-    <mergeCell ref="D164:J164"/>
-    <mergeCell ref="D157:J157"/>
-    <mergeCell ref="D120:H120"/>
-    <mergeCell ref="G123:J123"/>
-    <mergeCell ref="D121:J121"/>
-    <mergeCell ref="D143:J143"/>
-    <mergeCell ref="C177:J177"/>
-    <mergeCell ref="D135:J135"/>
-    <mergeCell ref="D172:J172"/>
-    <mergeCell ref="G146:J146"/>
-    <mergeCell ref="G152:I152"/>
-    <mergeCell ref="D149:J150"/>
-    <mergeCell ref="D31:I31"/>
-    <mergeCell ref="G35:H35"/>
-    <mergeCell ref="D40:I40"/>
-    <mergeCell ref="D33:I33"/>
-    <mergeCell ref="D46:I46"/>
-    <mergeCell ref="D43:I43"/>
-    <mergeCell ref="D78:I78"/>
-    <mergeCell ref="G71:H71"/>
-    <mergeCell ref="D76:I76"/>
-    <mergeCell ref="D66:H66"/>
-    <mergeCell ref="D77:I77"/>
-    <mergeCell ref="D73:I73"/>
-    <mergeCell ref="D70:E70"/>
-    <mergeCell ref="D74:F74"/>
+    <mergeCell ref="D106:E106"/>
+    <mergeCell ref="D99:G99"/>
+    <mergeCell ref="G126:I126"/>
+    <mergeCell ref="F125:J125"/>
+    <mergeCell ref="D128:J128"/>
+    <mergeCell ref="D103:E103"/>
+    <mergeCell ref="D104:E104"/>
+    <mergeCell ref="D105:E105"/>
+    <mergeCell ref="G100:I100"/>
+    <mergeCell ref="B101:I101"/>
+    <mergeCell ref="F127:J127"/>
+    <mergeCell ref="D107:E107"/>
+    <mergeCell ref="F118:J118"/>
+    <mergeCell ref="D108:E108"/>
+    <mergeCell ref="B112:J113"/>
+    <mergeCell ref="G124:J124"/>
+    <mergeCell ref="D98:I98"/>
+    <mergeCell ref="D94:I94"/>
+    <mergeCell ref="H89:I89"/>
+    <mergeCell ref="D89:F89"/>
+    <mergeCell ref="D97:I97"/>
+    <mergeCell ref="G64:H64"/>
+    <mergeCell ref="D96:I96"/>
+    <mergeCell ref="D95:F95"/>
+    <mergeCell ref="G95:H95"/>
+    <mergeCell ref="D92:I92"/>
+    <mergeCell ref="D93:I93"/>
+    <mergeCell ref="D90:E90"/>
+    <mergeCell ref="D91:H91"/>
+    <mergeCell ref="E86:G86"/>
+    <mergeCell ref="D88:I88"/>
+    <mergeCell ref="H67:I67"/>
+    <mergeCell ref="G81:H81"/>
+    <mergeCell ref="D67:F67"/>
+    <mergeCell ref="F68:I68"/>
+    <mergeCell ref="D87:E87"/>
+    <mergeCell ref="G87:I87"/>
+    <mergeCell ref="D60:I60"/>
+    <mergeCell ref="D62:I62"/>
+    <mergeCell ref="D61:I61"/>
+    <mergeCell ref="G49:H49"/>
+    <mergeCell ref="D47:I47"/>
+    <mergeCell ref="D55:I55"/>
+    <mergeCell ref="G57:H57"/>
     <mergeCell ref="D84:I84"/>
     <mergeCell ref="D69:I69"/>
     <mergeCell ref="D8:I8"/>
@@ -7594,50 +7609,35 @@
     <mergeCell ref="D30:I30"/>
     <mergeCell ref="G80:H80"/>
     <mergeCell ref="G42:H42"/>
-    <mergeCell ref="D60:I60"/>
-    <mergeCell ref="D62:I62"/>
-    <mergeCell ref="D61:I61"/>
-    <mergeCell ref="G49:H49"/>
-    <mergeCell ref="D47:I47"/>
-    <mergeCell ref="D55:I55"/>
-    <mergeCell ref="G57:H57"/>
-    <mergeCell ref="G64:H64"/>
-    <mergeCell ref="D96:I96"/>
-    <mergeCell ref="D95:F95"/>
-    <mergeCell ref="G95:H95"/>
-    <mergeCell ref="D92:I92"/>
-    <mergeCell ref="D93:I93"/>
-    <mergeCell ref="D90:E90"/>
-    <mergeCell ref="D91:H91"/>
-    <mergeCell ref="E86:G86"/>
-    <mergeCell ref="D88:I88"/>
-    <mergeCell ref="H67:I67"/>
-    <mergeCell ref="G81:H81"/>
-    <mergeCell ref="D67:F67"/>
-    <mergeCell ref="F68:I68"/>
-    <mergeCell ref="D87:E87"/>
-    <mergeCell ref="G87:I87"/>
-    <mergeCell ref="D98:I98"/>
-    <mergeCell ref="D94:I94"/>
-    <mergeCell ref="H89:I89"/>
-    <mergeCell ref="D89:F89"/>
-    <mergeCell ref="D97:I97"/>
-    <mergeCell ref="D106:E106"/>
-    <mergeCell ref="D99:G99"/>
-    <mergeCell ref="G126:I126"/>
-    <mergeCell ref="F125:J125"/>
-    <mergeCell ref="D128:J128"/>
-    <mergeCell ref="D103:E103"/>
-    <mergeCell ref="D104:E104"/>
-    <mergeCell ref="D105:E105"/>
-    <mergeCell ref="G100:I100"/>
-    <mergeCell ref="B101:I101"/>
-    <mergeCell ref="F127:J127"/>
-    <mergeCell ref="D107:E107"/>
-    <mergeCell ref="F118:J118"/>
-    <mergeCell ref="D108:E108"/>
-    <mergeCell ref="B112:J113"/>
-    <mergeCell ref="G124:J124"/>
+    <mergeCell ref="D78:I78"/>
+    <mergeCell ref="G71:H71"/>
+    <mergeCell ref="D76:I76"/>
+    <mergeCell ref="D66:H66"/>
+    <mergeCell ref="D77:I77"/>
+    <mergeCell ref="D73:I73"/>
+    <mergeCell ref="D70:E70"/>
+    <mergeCell ref="D74:F74"/>
+    <mergeCell ref="D31:I31"/>
+    <mergeCell ref="G35:H35"/>
+    <mergeCell ref="D40:I40"/>
+    <mergeCell ref="D33:I33"/>
+    <mergeCell ref="D46:I46"/>
+    <mergeCell ref="D43:I43"/>
+    <mergeCell ref="D120:H120"/>
+    <mergeCell ref="G123:J123"/>
+    <mergeCell ref="D121:J121"/>
+    <mergeCell ref="D143:J143"/>
+    <mergeCell ref="C177:J177"/>
+    <mergeCell ref="D135:J135"/>
+    <mergeCell ref="D172:J172"/>
+    <mergeCell ref="G146:J146"/>
+    <mergeCell ref="G152:I152"/>
+    <mergeCell ref="D149:J150"/>
+    <mergeCell ref="D187:J187"/>
+    <mergeCell ref="D185:J185"/>
+    <mergeCell ref="C175:J176"/>
+    <mergeCell ref="D164:J164"/>
+    <mergeCell ref="D157:J157"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/attendance_sheet.xlsx
+++ b/attendance_sheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\repositary\3rd_Year_5th_Semester\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B223750E-3FD4-4F5D-85F4-E1F7C93F1F94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23405FE1-719C-4CF6-A7E4-F732CF516206}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{EB654061-A886-47D1-BF86-9B1A84FCE7FB}"/>
   </bookViews>
@@ -544,35 +544,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -590,6 +566,30 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -993,14 +993,14 @@
       <c r="C8" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D8" s="33" t="s">
+      <c r="D8" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="E8" s="33"/>
-      <c r="F8" s="33"/>
-      <c r="G8" s="33"/>
-      <c r="H8" s="33"/>
-      <c r="I8" s="33"/>
+      <c r="E8" s="32"/>
+      <c r="F8" s="32"/>
+      <c r="G8" s="32"/>
+      <c r="H8" s="32"/>
+      <c r="I8" s="32"/>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B9" s="4">
@@ -1009,14 +1009,14 @@
       <c r="C9" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D9" s="33" t="s">
+      <c r="D9" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="E9" s="33"/>
-      <c r="F9" s="33"/>
-      <c r="G9" s="33"/>
-      <c r="H9" s="33"/>
-      <c r="I9" s="33"/>
+      <c r="E9" s="32"/>
+      <c r="F9" s="32"/>
+      <c r="G9" s="32"/>
+      <c r="H9" s="32"/>
+      <c r="I9" s="32"/>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B10" s="4">
@@ -1025,14 +1025,14 @@
       <c r="C10" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D10" s="33" t="s">
+      <c r="D10" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="E10" s="33"/>
-      <c r="F10" s="33"/>
-      <c r="G10" s="33"/>
-      <c r="H10" s="33"/>
-      <c r="I10" s="33"/>
+      <c r="E10" s="32"/>
+      <c r="F10" s="32"/>
+      <c r="G10" s="32"/>
+      <c r="H10" s="32"/>
+      <c r="I10" s="32"/>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B11" s="4">
@@ -1041,14 +1041,14 @@
       <c r="C11" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D11" s="33" t="s">
+      <c r="D11" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="E11" s="33"/>
-      <c r="F11" s="33"/>
-      <c r="G11" s="33"/>
-      <c r="H11" s="33"/>
-      <c r="I11" s="33"/>
+      <c r="E11" s="32"/>
+      <c r="F11" s="32"/>
+      <c r="G11" s="32"/>
+      <c r="H11" s="32"/>
+      <c r="I11" s="32"/>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B12" s="4">
@@ -1092,10 +1092,10 @@
       <c r="F13" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="G13" s="33" t="s">
+      <c r="G13" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="H13" s="33"/>
+      <c r="H13" s="32"/>
       <c r="I13" s="1" t="s">
         <v>14</v>
       </c>
@@ -1107,14 +1107,14 @@
       <c r="C14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D14" s="33" t="s">
+      <c r="D14" s="32" t="s">
         <v>19</v>
       </c>
-      <c r="E14" s="33"/>
-      <c r="F14" s="33"/>
-      <c r="G14" s="33"/>
-      <c r="H14" s="33"/>
-      <c r="I14" s="33"/>
+      <c r="E14" s="32"/>
+      <c r="F14" s="32"/>
+      <c r="G14" s="32"/>
+      <c r="H14" s="32"/>
+      <c r="I14" s="32"/>
     </row>
     <row r="15" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B15" s="4">
@@ -1201,14 +1201,14 @@
       <c r="C18" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D18" s="33" t="s">
+      <c r="D18" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="E18" s="33"/>
-      <c r="F18" s="33"/>
-      <c r="G18" s="33"/>
-      <c r="H18" s="33"/>
-      <c r="I18" s="33"/>
+      <c r="E18" s="32"/>
+      <c r="F18" s="32"/>
+      <c r="G18" s="32"/>
+      <c r="H18" s="32"/>
+      <c r="I18" s="32"/>
     </row>
     <row r="19" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B19" s="4">
@@ -1217,14 +1217,14 @@
       <c r="C19" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D19" s="33" t="s">
+      <c r="D19" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="E19" s="33"/>
-      <c r="F19" s="33"/>
-      <c r="G19" s="33"/>
-      <c r="H19" s="33"/>
-      <c r="I19" s="33"/>
+      <c r="E19" s="32"/>
+      <c r="F19" s="32"/>
+      <c r="G19" s="32"/>
+      <c r="H19" s="32"/>
+      <c r="I19" s="32"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B20" s="4">
@@ -1242,10 +1242,10 @@
       <c r="F20" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G20" s="33" t="s">
+      <c r="G20" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="H20" s="33"/>
+      <c r="H20" s="32"/>
       <c r="I20" s="1" t="s">
         <v>14</v>
       </c>
@@ -1361,14 +1361,14 @@
       <c r="C25" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D25" s="33" t="s">
+      <c r="D25" s="32" t="s">
         <v>26</v>
       </c>
-      <c r="E25" s="33"/>
-      <c r="F25" s="33"/>
-      <c r="G25" s="33"/>
-      <c r="H25" s="33"/>
-      <c r="I25" s="33"/>
+      <c r="E25" s="32"/>
+      <c r="F25" s="32"/>
+      <c r="G25" s="32"/>
+      <c r="H25" s="32"/>
+      <c r="I25" s="32"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B26" s="4">
@@ -1412,10 +1412,10 @@
       <c r="F27" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G27" s="33" t="s">
+      <c r="G27" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="H27" s="33"/>
+      <c r="H27" s="32"/>
       <c r="I27" s="1" t="s">
         <v>14</v>
       </c>
@@ -1479,14 +1479,14 @@
       <c r="C30" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D30" s="32" t="s">
+      <c r="D30" s="33" t="s">
         <v>20</v>
       </c>
-      <c r="E30" s="32"/>
-      <c r="F30" s="32"/>
-      <c r="G30" s="32"/>
-      <c r="H30" s="32"/>
-      <c r="I30" s="32"/>
+      <c r="E30" s="33"/>
+      <c r="F30" s="33"/>
+      <c r="G30" s="33"/>
+      <c r="H30" s="33"/>
+      <c r="I30" s="33"/>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B31" s="4">
@@ -1495,14 +1495,14 @@
       <c r="C31" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D31" s="32" t="s">
+      <c r="D31" s="33" t="s">
         <v>20</v>
       </c>
-      <c r="E31" s="32"/>
-      <c r="F31" s="32"/>
-      <c r="G31" s="32"/>
-      <c r="H31" s="32"/>
-      <c r="I31" s="32"/>
+      <c r="E31" s="33"/>
+      <c r="F31" s="33"/>
+      <c r="G31" s="33"/>
+      <c r="H31" s="33"/>
+      <c r="I31" s="33"/>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B32" s="4">
@@ -1537,14 +1537,14 @@
       <c r="C33" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D33" s="32" t="s">
+      <c r="D33" s="33" t="s">
         <v>20</v>
       </c>
-      <c r="E33" s="32"/>
-      <c r="F33" s="32"/>
-      <c r="G33" s="32"/>
-      <c r="H33" s="32"/>
-      <c r="I33" s="32"/>
+      <c r="E33" s="33"/>
+      <c r="F33" s="33"/>
+      <c r="G33" s="33"/>
+      <c r="H33" s="33"/>
+      <c r="I33" s="33"/>
     </row>
     <row r="34" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B34" s="4">
@@ -1588,10 +1588,10 @@
       <c r="F35" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G35" s="32" t="s">
+      <c r="G35" s="33" t="s">
         <v>18</v>
       </c>
-      <c r="H35" s="32"/>
+      <c r="H35" s="33"/>
       <c r="I35" s="1" t="s">
         <v>14</v>
       </c>
@@ -1707,14 +1707,14 @@
       <c r="C40" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D40" s="32" t="s">
+      <c r="D40" s="33" t="s">
         <v>20</v>
       </c>
-      <c r="E40" s="32"/>
-      <c r="F40" s="32"/>
-      <c r="G40" s="32"/>
-      <c r="H40" s="32"/>
-      <c r="I40" s="32"/>
+      <c r="E40" s="33"/>
+      <c r="F40" s="33"/>
+      <c r="G40" s="33"/>
+      <c r="H40" s="33"/>
+      <c r="I40" s="33"/>
     </row>
     <row r="41" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B41" s="4">
@@ -1758,10 +1758,10 @@
       <c r="F42" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G42" s="32" t="s">
+      <c r="G42" s="33" t="s">
         <v>28</v>
       </c>
-      <c r="H42" s="32"/>
+      <c r="H42" s="33"/>
       <c r="I42" s="1" t="s">
         <v>15</v>
       </c>
@@ -1773,14 +1773,14 @@
       <c r="C43" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D43" s="32" t="s">
+      <c r="D43" s="33" t="s">
         <v>20</v>
       </c>
-      <c r="E43" s="32"/>
-      <c r="F43" s="32"/>
-      <c r="G43" s="32"/>
-      <c r="H43" s="32"/>
-      <c r="I43" s="32"/>
+      <c r="E43" s="33"/>
+      <c r="F43" s="33"/>
+      <c r="G43" s="33"/>
+      <c r="H43" s="33"/>
+      <c r="I43" s="33"/>
     </row>
     <row r="44" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B44" s="4">
@@ -1844,14 +1844,14 @@
       <c r="C46" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D46" s="32" t="s">
+      <c r="D46" s="33" t="s">
         <v>20</v>
       </c>
-      <c r="E46" s="32"/>
-      <c r="F46" s="32"/>
-      <c r="G46" s="32"/>
-      <c r="H46" s="32"/>
-      <c r="I46" s="32"/>
+      <c r="E46" s="33"/>
+      <c r="F46" s="33"/>
+      <c r="G46" s="33"/>
+      <c r="H46" s="33"/>
+      <c r="I46" s="33"/>
     </row>
     <row r="47" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B47" s="4">
@@ -1863,11 +1863,11 @@
       <c r="D47" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E47" s="24"/>
-      <c r="F47" s="24"/>
-      <c r="G47" s="24"/>
-      <c r="H47" s="24"/>
-      <c r="I47" s="25"/>
+      <c r="E47" s="25"/>
+      <c r="F47" s="25"/>
+      <c r="G47" s="25"/>
+      <c r="H47" s="25"/>
+      <c r="I47" s="24"/>
     </row>
     <row r="48" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B48" s="4">
@@ -1914,7 +1914,7 @@
       <c r="G49" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="H49" s="25"/>
+      <c r="H49" s="24"/>
       <c r="I49" s="1" t="s">
         <v>30</v>
       </c>
@@ -2056,14 +2056,14 @@
       <c r="C55" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="D55" s="24" t="s">
+      <c r="D55" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="E55" s="24"/>
-      <c r="F55" s="24"/>
-      <c r="G55" s="24"/>
-      <c r="H55" s="24"/>
-      <c r="I55" s="24"/>
+      <c r="E55" s="25"/>
+      <c r="F55" s="25"/>
+      <c r="G55" s="25"/>
+      <c r="H55" s="25"/>
+      <c r="I55" s="25"/>
     </row>
     <row r="56" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B56" s="4">
@@ -2110,7 +2110,7 @@
       <c r="G57" s="23" t="s">
         <v>37</v>
       </c>
-      <c r="H57" s="25"/>
+      <c r="H57" s="24"/>
       <c r="I57" s="1" t="s">
         <v>36</v>
       </c>
@@ -2177,11 +2177,11 @@
       <c r="D60" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E60" s="24"/>
-      <c r="F60" s="24"/>
-      <c r="G60" s="24"/>
-      <c r="H60" s="24"/>
-      <c r="I60" s="25"/>
+      <c r="E60" s="25"/>
+      <c r="F60" s="25"/>
+      <c r="G60" s="25"/>
+      <c r="H60" s="25"/>
+      <c r="I60" s="24"/>
     </row>
     <row r="61" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B61" s="4">
@@ -2193,11 +2193,11 @@
       <c r="D61" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E61" s="24"/>
-      <c r="F61" s="24"/>
-      <c r="G61" s="24"/>
-      <c r="H61" s="24"/>
-      <c r="I61" s="25"/>
+      <c r="E61" s="25"/>
+      <c r="F61" s="25"/>
+      <c r="G61" s="25"/>
+      <c r="H61" s="25"/>
+      <c r="I61" s="24"/>
     </row>
     <row r="62" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B62" s="4">
@@ -2209,11 +2209,11 @@
       <c r="D62" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E62" s="24"/>
-      <c r="F62" s="24"/>
-      <c r="G62" s="24"/>
-      <c r="H62" s="24"/>
-      <c r="I62" s="25"/>
+      <c r="E62" s="25"/>
+      <c r="F62" s="25"/>
+      <c r="G62" s="25"/>
+      <c r="H62" s="25"/>
+      <c r="I62" s="24"/>
     </row>
     <row r="63" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B63" s="4">
@@ -2260,7 +2260,7 @@
       <c r="G64" s="23" t="s">
         <v>37</v>
       </c>
-      <c r="H64" s="25"/>
+      <c r="H64" s="24"/>
       <c r="I64" s="1" t="s">
         <v>14</v>
       </c>
@@ -2301,10 +2301,10 @@
       <c r="D66" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="E66" s="24"/>
-      <c r="F66" s="24"/>
-      <c r="G66" s="24"/>
-      <c r="H66" s="25"/>
+      <c r="E66" s="25"/>
+      <c r="F66" s="25"/>
+      <c r="G66" s="25"/>
+      <c r="H66" s="24"/>
       <c r="I66" s="1" t="s">
         <v>16</v>
       </c>
@@ -2319,15 +2319,15 @@
       <c r="D67" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="E67" s="24"/>
-      <c r="F67" s="25"/>
+      <c r="E67" s="25"/>
+      <c r="F67" s="24"/>
       <c r="G67" s="3" t="s">
         <v>16</v>
       </c>
       <c r="H67" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="I67" s="25"/>
+      <c r="I67" s="24"/>
     </row>
     <row r="68" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B68" s="4">
@@ -2345,9 +2345,9 @@
       <c r="F68" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="G68" s="24"/>
-      <c r="H68" s="24"/>
-      <c r="I68" s="25"/>
+      <c r="G68" s="25"/>
+      <c r="H68" s="25"/>
+      <c r="I68" s="24"/>
     </row>
     <row r="69" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B69" s="4">
@@ -2359,11 +2359,11 @@
       <c r="D69" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E69" s="24"/>
-      <c r="F69" s="24"/>
-      <c r="G69" s="24"/>
-      <c r="H69" s="24"/>
-      <c r="I69" s="25"/>
+      <c r="E69" s="25"/>
+      <c r="F69" s="25"/>
+      <c r="G69" s="25"/>
+      <c r="H69" s="25"/>
+      <c r="I69" s="24"/>
     </row>
     <row r="70" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B70" s="4">
@@ -2375,7 +2375,7 @@
       <c r="D70" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="E70" s="25"/>
+      <c r="E70" s="24"/>
       <c r="F70" s="3" t="s">
         <v>15</v>
       </c>
@@ -2408,7 +2408,7 @@
       <c r="G71" s="23" t="s">
         <v>37</v>
       </c>
-      <c r="H71" s="25"/>
+      <c r="H71" s="24"/>
       <c r="I71" s="1" t="s">
         <v>14</v>
       </c>
@@ -2449,11 +2449,11 @@
       <c r="D73" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E73" s="24"/>
-      <c r="F73" s="24"/>
-      <c r="G73" s="24"/>
-      <c r="H73" s="24"/>
-      <c r="I73" s="25"/>
+      <c r="E73" s="25"/>
+      <c r="F73" s="25"/>
+      <c r="G73" s="25"/>
+      <c r="H73" s="25"/>
+      <c r="I73" s="24"/>
     </row>
     <row r="74" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B74" s="4">
@@ -2465,8 +2465,8 @@
       <c r="D74" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="E74" s="24"/>
-      <c r="F74" s="25"/>
+      <c r="E74" s="25"/>
+      <c r="F74" s="24"/>
       <c r="G74" s="3" t="s">
         <v>16</v>
       </c>
@@ -2505,11 +2505,11 @@
       <c r="D76" s="23" t="s">
         <v>39</v>
       </c>
-      <c r="E76" s="24"/>
-      <c r="F76" s="24"/>
-      <c r="G76" s="24"/>
-      <c r="H76" s="24"/>
-      <c r="I76" s="25"/>
+      <c r="E76" s="25"/>
+      <c r="F76" s="25"/>
+      <c r="G76" s="25"/>
+      <c r="H76" s="25"/>
+      <c r="I76" s="24"/>
     </row>
     <row r="77" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B77" s="4">
@@ -2521,11 +2521,11 @@
       <c r="D77" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E77" s="24"/>
-      <c r="F77" s="24"/>
-      <c r="G77" s="24"/>
-      <c r="H77" s="24"/>
-      <c r="I77" s="25"/>
+      <c r="E77" s="25"/>
+      <c r="F77" s="25"/>
+      <c r="G77" s="25"/>
+      <c r="H77" s="25"/>
+      <c r="I77" s="24"/>
     </row>
     <row r="78" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B78" s="4">
@@ -2537,11 +2537,11 @@
       <c r="D78" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E78" s="24"/>
-      <c r="F78" s="24"/>
-      <c r="G78" s="24"/>
-      <c r="H78" s="24"/>
-      <c r="I78" s="25"/>
+      <c r="E78" s="25"/>
+      <c r="F78" s="25"/>
+      <c r="G78" s="25"/>
+      <c r="H78" s="25"/>
+      <c r="I78" s="24"/>
     </row>
     <row r="79" spans="2:9" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B79" s="16" t="s">
@@ -2588,7 +2588,7 @@
       <c r="G80" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="H80" s="25"/>
+      <c r="H80" s="24"/>
       <c r="I80" s="1" t="s">
         <v>14</v>
       </c>
@@ -2612,7 +2612,7 @@
       <c r="G81" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="H81" s="25"/>
+      <c r="H81" s="24"/>
       <c r="I81" s="1" t="s">
         <v>16</v>
       </c>
@@ -2679,11 +2679,11 @@
       <c r="D84" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E84" s="24"/>
-      <c r="F84" s="24"/>
-      <c r="G84" s="24"/>
-      <c r="H84" s="24"/>
-      <c r="I84" s="25"/>
+      <c r="E84" s="25"/>
+      <c r="F84" s="25"/>
+      <c r="G84" s="25"/>
+      <c r="H84" s="25"/>
+      <c r="I84" s="24"/>
     </row>
     <row r="85" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B85" s="4">
@@ -2724,8 +2724,8 @@
       <c r="E86" s="23" t="s">
         <v>43</v>
       </c>
-      <c r="F86" s="24"/>
-      <c r="G86" s="25"/>
+      <c r="F86" s="25"/>
+      <c r="G86" s="24"/>
       <c r="H86" s="3" t="s">
         <v>14</v>
       </c>
@@ -2743,15 +2743,15 @@
       <c r="D87" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="E87" s="25"/>
+      <c r="E87" s="24"/>
       <c r="F87" s="3" t="s">
         <v>16</v>
       </c>
       <c r="G87" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="H87" s="24"/>
-      <c r="I87" s="25"/>
+      <c r="H87" s="25"/>
+      <c r="I87" s="24"/>
     </row>
     <row r="88" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B88" s="4">
@@ -2763,11 +2763,11 @@
       <c r="D88" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E88" s="24"/>
-      <c r="F88" s="24"/>
-      <c r="G88" s="24"/>
-      <c r="H88" s="24"/>
-      <c r="I88" s="25"/>
+      <c r="E88" s="25"/>
+      <c r="F88" s="25"/>
+      <c r="G88" s="25"/>
+      <c r="H88" s="25"/>
+      <c r="I88" s="24"/>
     </row>
     <row r="89" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B89" s="4">
@@ -2779,15 +2779,15 @@
       <c r="D89" s="23" t="s">
         <v>44</v>
       </c>
-      <c r="E89" s="24"/>
-      <c r="F89" s="25"/>
+      <c r="E89" s="25"/>
+      <c r="F89" s="24"/>
       <c r="G89" s="3" t="s">
         <v>16</v>
       </c>
       <c r="H89" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="I89" s="25"/>
+      <c r="I89" s="24"/>
     </row>
     <row r="90" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B90" s="4">
@@ -2799,7 +2799,7 @@
       <c r="D90" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="E90" s="25"/>
+      <c r="E90" s="24"/>
       <c r="F90" s="3" t="s">
         <v>16</v>
       </c>
@@ -2824,10 +2824,10 @@
       <c r="D91" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E91" s="24"/>
-      <c r="F91" s="24"/>
-      <c r="G91" s="24"/>
-      <c r="H91" s="25"/>
+      <c r="E91" s="25"/>
+      <c r="F91" s="25"/>
+      <c r="G91" s="25"/>
+      <c r="H91" s="24"/>
       <c r="I91" s="18" t="s">
         <v>45</v>
       </c>
@@ -2842,11 +2842,11 @@
       <c r="D92" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E92" s="24"/>
-      <c r="F92" s="24"/>
-      <c r="G92" s="24"/>
-      <c r="H92" s="24"/>
-      <c r="I92" s="25"/>
+      <c r="E92" s="25"/>
+      <c r="F92" s="25"/>
+      <c r="G92" s="25"/>
+      <c r="H92" s="25"/>
+      <c r="I92" s="24"/>
     </row>
     <row r="93" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B93" s="4">
@@ -2858,11 +2858,11 @@
       <c r="D93" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="E93" s="24"/>
-      <c r="F93" s="24"/>
-      <c r="G93" s="24"/>
-      <c r="H93" s="24"/>
-      <c r="I93" s="25"/>
+      <c r="E93" s="25"/>
+      <c r="F93" s="25"/>
+      <c r="G93" s="25"/>
+      <c r="H93" s="25"/>
+      <c r="I93" s="24"/>
     </row>
     <row r="94" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B94" s="4">
@@ -2874,11 +2874,11 @@
       <c r="D94" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="E94" s="24"/>
-      <c r="F94" s="24"/>
-      <c r="G94" s="24"/>
-      <c r="H94" s="24"/>
-      <c r="I94" s="25"/>
+      <c r="E94" s="25"/>
+      <c r="F94" s="25"/>
+      <c r="G94" s="25"/>
+      <c r="H94" s="25"/>
+      <c r="I94" s="24"/>
     </row>
     <row r="95" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B95" s="4">
@@ -2890,12 +2890,12 @@
       <c r="D95" s="23" t="s">
         <v>47</v>
       </c>
-      <c r="E95" s="24"/>
-      <c r="F95" s="25"/>
+      <c r="E95" s="25"/>
+      <c r="F95" s="24"/>
       <c r="G95" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="H95" s="25"/>
+      <c r="H95" s="24"/>
       <c r="I95" s="1" t="s">
         <v>14</v>
       </c>
@@ -2910,11 +2910,11 @@
       <c r="D96" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E96" s="24"/>
-      <c r="F96" s="24"/>
-      <c r="G96" s="24"/>
-      <c r="H96" s="24"/>
-      <c r="I96" s="25"/>
+      <c r="E96" s="25"/>
+      <c r="F96" s="25"/>
+      <c r="G96" s="25"/>
+      <c r="H96" s="25"/>
+      <c r="I96" s="24"/>
     </row>
     <row r="97" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B97" s="4">
@@ -2926,11 +2926,11 @@
       <c r="D97" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="E97" s="24"/>
-      <c r="F97" s="24"/>
-      <c r="G97" s="24"/>
-      <c r="H97" s="24"/>
-      <c r="I97" s="25"/>
+      <c r="E97" s="25"/>
+      <c r="F97" s="25"/>
+      <c r="G97" s="25"/>
+      <c r="H97" s="25"/>
+      <c r="I97" s="24"/>
     </row>
     <row r="98" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B98" s="4">
@@ -2942,11 +2942,11 @@
       <c r="D98" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E98" s="24"/>
-      <c r="F98" s="24"/>
-      <c r="G98" s="24"/>
-      <c r="H98" s="24"/>
-      <c r="I98" s="25"/>
+      <c r="E98" s="25"/>
+      <c r="F98" s="25"/>
+      <c r="G98" s="25"/>
+      <c r="H98" s="25"/>
+      <c r="I98" s="24"/>
     </row>
     <row r="99" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B99" s="4">
@@ -2958,9 +2958,9 @@
       <c r="D99" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="E99" s="24"/>
-      <c r="F99" s="24"/>
-      <c r="G99" s="25"/>
+      <c r="E99" s="25"/>
+      <c r="F99" s="25"/>
+      <c r="G99" s="24"/>
       <c r="H99" s="3" t="s">
         <v>49</v>
       </c>
@@ -2987,18 +2987,18 @@
       <c r="G100" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="H100" s="24"/>
-      <c r="I100" s="25"/>
+      <c r="H100" s="25"/>
+      <c r="I100" s="24"/>
     </row>
     <row r="101" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B101" s="23"/>
-      <c r="C101" s="24"/>
-      <c r="D101" s="24"/>
-      <c r="E101" s="24"/>
-      <c r="F101" s="24"/>
-      <c r="G101" s="24"/>
-      <c r="H101" s="24"/>
-      <c r="I101" s="25"/>
+      <c r="C101" s="25"/>
+      <c r="D101" s="25"/>
+      <c r="E101" s="25"/>
+      <c r="F101" s="25"/>
+      <c r="G101" s="25"/>
+      <c r="H101" s="25"/>
+      <c r="I101" s="24"/>
     </row>
     <row r="102" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B102" s="3"/>
@@ -3020,7 +3020,7 @@
       <c r="D103" s="23" t="s">
         <v>51</v>
       </c>
-      <c r="E103" s="25"/>
+      <c r="E103" s="24"/>
       <c r="F103" s="3"/>
       <c r="G103" s="3"/>
       <c r="H103" s="3"/>
@@ -3036,7 +3036,7 @@
       <c r="D104" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="E104" s="25"/>
+      <c r="E104" s="24"/>
       <c r="F104" s="3"/>
       <c r="G104" s="3"/>
       <c r="H104" s="3"/>
@@ -3052,7 +3052,7 @@
       <c r="D105" s="23" t="s">
         <v>53</v>
       </c>
-      <c r="E105" s="25"/>
+      <c r="E105" s="24"/>
       <c r="F105" s="3"/>
       <c r="G105" s="3"/>
       <c r="H105" s="3"/>
@@ -3068,7 +3068,7 @@
       <c r="D106" s="23" t="s">
         <v>54</v>
       </c>
-      <c r="E106" s="25"/>
+      <c r="E106" s="24"/>
       <c r="F106" s="3"/>
       <c r="G106" s="3"/>
       <c r="H106" s="3"/>
@@ -3084,7 +3084,7 @@
       <c r="D107" s="23" t="s">
         <v>55</v>
       </c>
-      <c r="E107" s="25"/>
+      <c r="E107" s="24"/>
       <c r="F107" s="3"/>
       <c r="G107" s="3"/>
       <c r="H107" s="3"/>
@@ -3100,7 +3100,7 @@
       <c r="D108" s="23" t="s">
         <v>56</v>
       </c>
-      <c r="E108" s="25"/>
+      <c r="E108" s="24"/>
       <c r="F108" s="3"/>
       <c r="G108" s="3"/>
       <c r="H108" s="3"/>
@@ -3137,28 +3137,28 @@
       <c r="I111" s="20"/>
     </row>
     <row r="112" spans="2:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B112" s="34" t="s">
+      <c r="B112" s="26" t="s">
         <v>57</v>
       </c>
-      <c r="C112" s="35"/>
-      <c r="D112" s="35"/>
-      <c r="E112" s="35"/>
-      <c r="F112" s="35"/>
-      <c r="G112" s="35"/>
-      <c r="H112" s="35"/>
-      <c r="I112" s="35"/>
-      <c r="J112" s="36"/>
+      <c r="C112" s="27"/>
+      <c r="D112" s="27"/>
+      <c r="E112" s="27"/>
+      <c r="F112" s="27"/>
+      <c r="G112" s="27"/>
+      <c r="H112" s="27"/>
+      <c r="I112" s="27"/>
+      <c r="J112" s="28"/>
     </row>
     <row r="113" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B113" s="37"/>
-      <c r="C113" s="38"/>
-      <c r="D113" s="38"/>
-      <c r="E113" s="38"/>
-      <c r="F113" s="38"/>
-      <c r="G113" s="38"/>
-      <c r="H113" s="38"/>
-      <c r="I113" s="38"/>
-      <c r="J113" s="39"/>
+      <c r="B113" s="29"/>
+      <c r="C113" s="30"/>
+      <c r="D113" s="30"/>
+      <c r="E113" s="30"/>
+      <c r="F113" s="30"/>
+      <c r="G113" s="30"/>
+      <c r="H113" s="30"/>
+      <c r="I113" s="30"/>
+      <c r="J113" s="31"/>
     </row>
     <row r="114" spans="2:10" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B114" s="8" t="s">
@@ -3292,10 +3292,10 @@
       <c r="F118" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="G118" s="24"/>
-      <c r="H118" s="24"/>
-      <c r="I118" s="24"/>
-      <c r="J118" s="25"/>
+      <c r="G118" s="25"/>
+      <c r="H118" s="25"/>
+      <c r="I118" s="25"/>
+      <c r="J118" s="24"/>
     </row>
     <row r="119" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B119" s="4">
@@ -3336,10 +3336,10 @@
       <c r="D120" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="E120" s="24"/>
-      <c r="F120" s="24"/>
-      <c r="G120" s="24"/>
-      <c r="H120" s="25"/>
+      <c r="E120" s="25"/>
+      <c r="F120" s="25"/>
+      <c r="G120" s="25"/>
+      <c r="H120" s="24"/>
       <c r="I120" s="1" t="s">
         <v>16</v>
       </c>
@@ -3357,12 +3357,12 @@
       <c r="D121" s="23" t="s">
         <v>65</v>
       </c>
-      <c r="E121" s="24"/>
-      <c r="F121" s="24"/>
-      <c r="G121" s="24"/>
-      <c r="H121" s="24"/>
-      <c r="I121" s="24"/>
-      <c r="J121" s="25"/>
+      <c r="E121" s="25"/>
+      <c r="F121" s="25"/>
+      <c r="G121" s="25"/>
+      <c r="H121" s="25"/>
+      <c r="I121" s="25"/>
+      <c r="J121" s="24"/>
     </row>
     <row r="122" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B122" s="4">
@@ -3412,9 +3412,9 @@
       <c r="G123" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="H123" s="24"/>
-      <c r="I123" s="24"/>
-      <c r="J123" s="25"/>
+      <c r="H123" s="25"/>
+      <c r="I123" s="25"/>
+      <c r="J123" s="24"/>
     </row>
     <row r="124" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B124" s="4">
@@ -3435,9 +3435,9 @@
       <c r="G124" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="H124" s="24"/>
-      <c r="I124" s="24"/>
-      <c r="J124" s="25"/>
+      <c r="H124" s="25"/>
+      <c r="I124" s="25"/>
+      <c r="J124" s="24"/>
     </row>
     <row r="125" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B125" s="4">
@@ -3455,10 +3455,10 @@
       <c r="F125" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="G125" s="24"/>
-      <c r="H125" s="24"/>
-      <c r="I125" s="24"/>
-      <c r="J125" s="25"/>
+      <c r="G125" s="25"/>
+      <c r="H125" s="25"/>
+      <c r="I125" s="25"/>
+      <c r="J125" s="24"/>
     </row>
     <row r="126" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B126" s="4">
@@ -3479,8 +3479,8 @@
       <c r="G126" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="H126" s="24"/>
-      <c r="I126" s="25"/>
+      <c r="H126" s="25"/>
+      <c r="I126" s="24"/>
       <c r="J126" s="1" t="s">
         <v>16</v>
       </c>
@@ -3501,10 +3501,10 @@
       <c r="F127" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="G127" s="24"/>
-      <c r="H127" s="24"/>
-      <c r="I127" s="24"/>
-      <c r="J127" s="25"/>
+      <c r="G127" s="25"/>
+      <c r="H127" s="25"/>
+      <c r="I127" s="25"/>
+      <c r="J127" s="24"/>
     </row>
     <row r="128" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B128" s="4">
@@ -3516,12 +3516,12 @@
       <c r="D128" s="23" t="s">
         <v>65</v>
       </c>
-      <c r="E128" s="24"/>
-      <c r="F128" s="24"/>
-      <c r="G128" s="24"/>
-      <c r="H128" s="24"/>
-      <c r="I128" s="24"/>
-      <c r="J128" s="25"/>
+      <c r="E128" s="25"/>
+      <c r="F128" s="25"/>
+      <c r="G128" s="25"/>
+      <c r="H128" s="25"/>
+      <c r="I128" s="25"/>
+      <c r="J128" s="24"/>
     </row>
     <row r="129" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B129" s="4">
@@ -3707,12 +3707,12 @@
       <c r="D135" s="23" t="s">
         <v>65</v>
       </c>
-      <c r="E135" s="24"/>
-      <c r="F135" s="24"/>
-      <c r="G135" s="24"/>
-      <c r="H135" s="24"/>
-      <c r="I135" s="24"/>
-      <c r="J135" s="25"/>
+      <c r="E135" s="25"/>
+      <c r="F135" s="25"/>
+      <c r="G135" s="25"/>
+      <c r="H135" s="25"/>
+      <c r="I135" s="25"/>
+      <c r="J135" s="24"/>
     </row>
     <row r="136" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B136" s="4">
@@ -3927,12 +3927,12 @@
       <c r="D143" s="23" t="s">
         <v>65</v>
       </c>
-      <c r="E143" s="24"/>
-      <c r="F143" s="24"/>
-      <c r="G143" s="24"/>
-      <c r="H143" s="24"/>
-      <c r="I143" s="24"/>
-      <c r="J143" s="25"/>
+      <c r="E143" s="25"/>
+      <c r="F143" s="25"/>
+      <c r="G143" s="25"/>
+      <c r="H143" s="25"/>
+      <c r="I143" s="25"/>
+      <c r="J143" s="24"/>
     </row>
     <row r="144" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B144" s="4">
@@ -4011,9 +4011,9 @@
       <c r="G146" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="H146" s="24"/>
-      <c r="I146" s="24"/>
-      <c r="J146" s="25"/>
+      <c r="H146" s="25"/>
+      <c r="I146" s="25"/>
+      <c r="J146" s="24"/>
     </row>
     <row r="147" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B147" s="4">
@@ -4080,15 +4080,15 @@
       <c r="C149" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D149" s="26" t="s">
+      <c r="D149" s="34" t="s">
         <v>20</v>
       </c>
-      <c r="E149" s="27"/>
-      <c r="F149" s="27"/>
-      <c r="G149" s="27"/>
-      <c r="H149" s="27"/>
-      <c r="I149" s="27"/>
-      <c r="J149" s="30"/>
+      <c r="E149" s="35"/>
+      <c r="F149" s="35"/>
+      <c r="G149" s="35"/>
+      <c r="H149" s="35"/>
+      <c r="I149" s="35"/>
+      <c r="J149" s="36"/>
     </row>
     <row r="150" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B150" s="4">
@@ -4097,13 +4097,13 @@
       <c r="C150" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D150" s="28"/>
-      <c r="E150" s="29"/>
-      <c r="F150" s="29"/>
-      <c r="G150" s="29"/>
-      <c r="H150" s="29"/>
-      <c r="I150" s="29"/>
-      <c r="J150" s="31"/>
+      <c r="D150" s="37"/>
+      <c r="E150" s="38"/>
+      <c r="F150" s="38"/>
+      <c r="G150" s="38"/>
+      <c r="H150" s="38"/>
+      <c r="I150" s="38"/>
+      <c r="J150" s="39"/>
     </row>
     <row r="151" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B151" s="4">
@@ -4153,8 +4153,8 @@
       <c r="G152" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="H152" s="24"/>
-      <c r="I152" s="25"/>
+      <c r="H152" s="25"/>
+      <c r="I152" s="24"/>
       <c r="J152" s="1" t="s">
         <v>69</v>
       </c>
@@ -4285,12 +4285,12 @@
       <c r="D157" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E157" s="24"/>
-      <c r="F157" s="24"/>
-      <c r="G157" s="24"/>
-      <c r="H157" s="24"/>
-      <c r="I157" s="24"/>
-      <c r="J157" s="25"/>
+      <c r="E157" s="25"/>
+      <c r="F157" s="25"/>
+      <c r="G157" s="25"/>
+      <c r="H157" s="25"/>
+      <c r="I157" s="25"/>
+      <c r="J157" s="24"/>
     </row>
     <row r="158" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B158" s="4">
@@ -4474,12 +4474,12 @@
       <c r="D164" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E164" s="24"/>
-      <c r="F164" s="24"/>
-      <c r="G164" s="24"/>
-      <c r="H164" s="24"/>
-      <c r="I164" s="24"/>
-      <c r="J164" s="25"/>
+      <c r="E164" s="25"/>
+      <c r="F164" s="25"/>
+      <c r="G164" s="25"/>
+      <c r="H164" s="25"/>
+      <c r="I164" s="25"/>
+      <c r="J164" s="24"/>
     </row>
     <row r="165" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B165" s="4">
@@ -4680,12 +4680,12 @@
       <c r="D172" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E172" s="24"/>
-      <c r="F172" s="24"/>
-      <c r="G172" s="24"/>
-      <c r="H172" s="24"/>
-      <c r="I172" s="24"/>
-      <c r="J172" s="25"/>
+      <c r="E172" s="25"/>
+      <c r="F172" s="25"/>
+      <c r="G172" s="25"/>
+      <c r="H172" s="25"/>
+      <c r="I172" s="25"/>
+      <c r="J172" s="24"/>
     </row>
     <row r="173" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B173" s="4">
@@ -4749,29 +4749,29 @@
       <c r="B175" s="4">
         <v>45903</v>
       </c>
-      <c r="C175" s="26" t="s">
+      <c r="C175" s="34" t="s">
         <v>39</v>
       </c>
-      <c r="D175" s="27"/>
-      <c r="E175" s="27"/>
-      <c r="F175" s="27"/>
-      <c r="G175" s="27"/>
-      <c r="H175" s="27"/>
-      <c r="I175" s="27"/>
-      <c r="J175" s="27"/>
+      <c r="D175" s="35"/>
+      <c r="E175" s="35"/>
+      <c r="F175" s="35"/>
+      <c r="G175" s="35"/>
+      <c r="H175" s="35"/>
+      <c r="I175" s="35"/>
+      <c r="J175" s="35"/>
     </row>
     <row r="176" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B176" s="4">
         <v>45904</v>
       </c>
-      <c r="C176" s="28"/>
-      <c r="D176" s="29"/>
-      <c r="E176" s="29"/>
-      <c r="F176" s="29"/>
-      <c r="G176" s="29"/>
-      <c r="H176" s="29"/>
-      <c r="I176" s="29"/>
-      <c r="J176" s="29"/>
+      <c r="C176" s="37"/>
+      <c r="D176" s="38"/>
+      <c r="E176" s="38"/>
+      <c r="F176" s="38"/>
+      <c r="G176" s="38"/>
+      <c r="H176" s="38"/>
+      <c r="I176" s="38"/>
+      <c r="J176" s="38"/>
     </row>
     <row r="177" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B177" s="4">
@@ -4780,13 +4780,13 @@
       <c r="C177" s="23" t="s">
         <v>39</v>
       </c>
-      <c r="D177" s="24"/>
-      <c r="E177" s="24"/>
-      <c r="F177" s="24"/>
-      <c r="G177" s="24"/>
-      <c r="H177" s="24"/>
-      <c r="I177" s="24"/>
-      <c r="J177" s="25"/>
+      <c r="D177" s="25"/>
+      <c r="E177" s="25"/>
+      <c r="F177" s="25"/>
+      <c r="G177" s="25"/>
+      <c r="H177" s="25"/>
+      <c r="I177" s="25"/>
+      <c r="J177" s="24"/>
     </row>
     <row r="178" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B178" s="4">
@@ -4985,12 +4985,12 @@
       <c r="D185" s="23" t="s">
         <v>74</v>
       </c>
-      <c r="E185" s="24"/>
-      <c r="F185" s="24"/>
-      <c r="G185" s="24"/>
-      <c r="H185" s="24"/>
-      <c r="I185" s="24"/>
-      <c r="J185" s="25"/>
+      <c r="E185" s="25"/>
+      <c r="F185" s="25"/>
+      <c r="G185" s="25"/>
+      <c r="H185" s="25"/>
+      <c r="I185" s="25"/>
+      <c r="J185" s="24"/>
     </row>
     <row r="186" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B186" s="4">
@@ -5021,12 +5021,12 @@
       <c r="D187" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="E187" s="24"/>
-      <c r="F187" s="24"/>
-      <c r="G187" s="24"/>
-      <c r="H187" s="24"/>
-      <c r="I187" s="24"/>
-      <c r="J187" s="25"/>
+      <c r="E187" s="25"/>
+      <c r="F187" s="25"/>
+      <c r="G187" s="25"/>
+      <c r="H187" s="25"/>
+      <c r="I187" s="25"/>
+      <c r="J187" s="24"/>
     </row>
     <row r="188" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B188" s="3"/>
@@ -7549,6 +7549,79 @@
     </row>
   </sheetData>
   <mergeCells count="89">
+    <mergeCell ref="D187:J187"/>
+    <mergeCell ref="D185:J185"/>
+    <mergeCell ref="C175:J176"/>
+    <mergeCell ref="D164:J164"/>
+    <mergeCell ref="D157:J157"/>
+    <mergeCell ref="D120:H120"/>
+    <mergeCell ref="G123:J123"/>
+    <mergeCell ref="D121:J121"/>
+    <mergeCell ref="D143:J143"/>
+    <mergeCell ref="C177:J177"/>
+    <mergeCell ref="D135:J135"/>
+    <mergeCell ref="D172:J172"/>
+    <mergeCell ref="G146:J146"/>
+    <mergeCell ref="G152:I152"/>
+    <mergeCell ref="D149:J150"/>
+    <mergeCell ref="D31:I31"/>
+    <mergeCell ref="G35:H35"/>
+    <mergeCell ref="D40:I40"/>
+    <mergeCell ref="D33:I33"/>
+    <mergeCell ref="D46:I46"/>
+    <mergeCell ref="D43:I43"/>
+    <mergeCell ref="D78:I78"/>
+    <mergeCell ref="G71:H71"/>
+    <mergeCell ref="D76:I76"/>
+    <mergeCell ref="D66:H66"/>
+    <mergeCell ref="D77:I77"/>
+    <mergeCell ref="D73:I73"/>
+    <mergeCell ref="D70:E70"/>
+    <mergeCell ref="D74:F74"/>
+    <mergeCell ref="D84:I84"/>
+    <mergeCell ref="D69:I69"/>
+    <mergeCell ref="D8:I8"/>
+    <mergeCell ref="D9:I9"/>
+    <mergeCell ref="D10:I10"/>
+    <mergeCell ref="D11:I11"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="D14:I14"/>
+    <mergeCell ref="G27:H27"/>
+    <mergeCell ref="D25:I25"/>
+    <mergeCell ref="G20:H20"/>
+    <mergeCell ref="D19:I19"/>
+    <mergeCell ref="D18:I18"/>
+    <mergeCell ref="D30:I30"/>
+    <mergeCell ref="G80:H80"/>
+    <mergeCell ref="G42:H42"/>
+    <mergeCell ref="D60:I60"/>
+    <mergeCell ref="D62:I62"/>
+    <mergeCell ref="D61:I61"/>
+    <mergeCell ref="G49:H49"/>
+    <mergeCell ref="D47:I47"/>
+    <mergeCell ref="D55:I55"/>
+    <mergeCell ref="G57:H57"/>
+    <mergeCell ref="G64:H64"/>
+    <mergeCell ref="D96:I96"/>
+    <mergeCell ref="D95:F95"/>
+    <mergeCell ref="G95:H95"/>
+    <mergeCell ref="D92:I92"/>
+    <mergeCell ref="D93:I93"/>
+    <mergeCell ref="D90:E90"/>
+    <mergeCell ref="D91:H91"/>
+    <mergeCell ref="E86:G86"/>
+    <mergeCell ref="D88:I88"/>
+    <mergeCell ref="H67:I67"/>
+    <mergeCell ref="G81:H81"/>
+    <mergeCell ref="D67:F67"/>
+    <mergeCell ref="F68:I68"/>
+    <mergeCell ref="D87:E87"/>
+    <mergeCell ref="G87:I87"/>
+    <mergeCell ref="D98:I98"/>
+    <mergeCell ref="D94:I94"/>
+    <mergeCell ref="H89:I89"/>
+    <mergeCell ref="D89:F89"/>
+    <mergeCell ref="D97:I97"/>
     <mergeCell ref="D106:E106"/>
     <mergeCell ref="D99:G99"/>
     <mergeCell ref="G126:I126"/>
@@ -7565,79 +7638,6 @@
     <mergeCell ref="D108:E108"/>
     <mergeCell ref="B112:J113"/>
     <mergeCell ref="G124:J124"/>
-    <mergeCell ref="D98:I98"/>
-    <mergeCell ref="D94:I94"/>
-    <mergeCell ref="H89:I89"/>
-    <mergeCell ref="D89:F89"/>
-    <mergeCell ref="D97:I97"/>
-    <mergeCell ref="G64:H64"/>
-    <mergeCell ref="D96:I96"/>
-    <mergeCell ref="D95:F95"/>
-    <mergeCell ref="G95:H95"/>
-    <mergeCell ref="D92:I92"/>
-    <mergeCell ref="D93:I93"/>
-    <mergeCell ref="D90:E90"/>
-    <mergeCell ref="D91:H91"/>
-    <mergeCell ref="E86:G86"/>
-    <mergeCell ref="D88:I88"/>
-    <mergeCell ref="H67:I67"/>
-    <mergeCell ref="G81:H81"/>
-    <mergeCell ref="D67:F67"/>
-    <mergeCell ref="F68:I68"/>
-    <mergeCell ref="D87:E87"/>
-    <mergeCell ref="G87:I87"/>
-    <mergeCell ref="D60:I60"/>
-    <mergeCell ref="D62:I62"/>
-    <mergeCell ref="D61:I61"/>
-    <mergeCell ref="G49:H49"/>
-    <mergeCell ref="D47:I47"/>
-    <mergeCell ref="D55:I55"/>
-    <mergeCell ref="G57:H57"/>
-    <mergeCell ref="D84:I84"/>
-    <mergeCell ref="D69:I69"/>
-    <mergeCell ref="D8:I8"/>
-    <mergeCell ref="D9:I9"/>
-    <mergeCell ref="D10:I10"/>
-    <mergeCell ref="D11:I11"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="D14:I14"/>
-    <mergeCell ref="G27:H27"/>
-    <mergeCell ref="D25:I25"/>
-    <mergeCell ref="G20:H20"/>
-    <mergeCell ref="D19:I19"/>
-    <mergeCell ref="D18:I18"/>
-    <mergeCell ref="D30:I30"/>
-    <mergeCell ref="G80:H80"/>
-    <mergeCell ref="G42:H42"/>
-    <mergeCell ref="D78:I78"/>
-    <mergeCell ref="G71:H71"/>
-    <mergeCell ref="D76:I76"/>
-    <mergeCell ref="D66:H66"/>
-    <mergeCell ref="D77:I77"/>
-    <mergeCell ref="D73:I73"/>
-    <mergeCell ref="D70:E70"/>
-    <mergeCell ref="D74:F74"/>
-    <mergeCell ref="D31:I31"/>
-    <mergeCell ref="G35:H35"/>
-    <mergeCell ref="D40:I40"/>
-    <mergeCell ref="D33:I33"/>
-    <mergeCell ref="D46:I46"/>
-    <mergeCell ref="D43:I43"/>
-    <mergeCell ref="D120:H120"/>
-    <mergeCell ref="G123:J123"/>
-    <mergeCell ref="D121:J121"/>
-    <mergeCell ref="D143:J143"/>
-    <mergeCell ref="C177:J177"/>
-    <mergeCell ref="D135:J135"/>
-    <mergeCell ref="D172:J172"/>
-    <mergeCell ref="G146:J146"/>
-    <mergeCell ref="G152:I152"/>
-    <mergeCell ref="D149:J150"/>
-    <mergeCell ref="D187:J187"/>
-    <mergeCell ref="D185:J185"/>
-    <mergeCell ref="C175:J176"/>
-    <mergeCell ref="D164:J164"/>
-    <mergeCell ref="D157:J157"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/attendance_sheet.xlsx
+++ b/attendance_sheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\repositary\3rd_Year_5th_Semester\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23405FE1-719C-4CF6-A7E4-F732CF516206}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C412C976-7AE6-44E6-9E07-A3074958DDF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{EB654061-A886-47D1-BF86-9B1A84FCE7FB}"/>
   </bookViews>
@@ -544,11 +544,35 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -566,30 +590,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -993,14 +993,14 @@
       <c r="C8" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D8" s="32" t="s">
+      <c r="D8" s="33" t="s">
         <v>20</v>
       </c>
-      <c r="E8" s="32"/>
-      <c r="F8" s="32"/>
-      <c r="G8" s="32"/>
-      <c r="H8" s="32"/>
-      <c r="I8" s="32"/>
+      <c r="E8" s="33"/>
+      <c r="F8" s="33"/>
+      <c r="G8" s="33"/>
+      <c r="H8" s="33"/>
+      <c r="I8" s="33"/>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B9" s="4">
@@ -1009,14 +1009,14 @@
       <c r="C9" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D9" s="32" t="s">
+      <c r="D9" s="33" t="s">
         <v>20</v>
       </c>
-      <c r="E9" s="32"/>
-      <c r="F9" s="32"/>
-      <c r="G9" s="32"/>
-      <c r="H9" s="32"/>
-      <c r="I9" s="32"/>
+      <c r="E9" s="33"/>
+      <c r="F9" s="33"/>
+      <c r="G9" s="33"/>
+      <c r="H9" s="33"/>
+      <c r="I9" s="33"/>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B10" s="4">
@@ -1025,14 +1025,14 @@
       <c r="C10" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D10" s="32" t="s">
+      <c r="D10" s="33" t="s">
         <v>20</v>
       </c>
-      <c r="E10" s="32"/>
-      <c r="F10" s="32"/>
-      <c r="G10" s="32"/>
-      <c r="H10" s="32"/>
-      <c r="I10" s="32"/>
+      <c r="E10" s="33"/>
+      <c r="F10" s="33"/>
+      <c r="G10" s="33"/>
+      <c r="H10" s="33"/>
+      <c r="I10" s="33"/>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B11" s="4">
@@ -1041,14 +1041,14 @@
       <c r="C11" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D11" s="32" t="s">
+      <c r="D11" s="33" t="s">
         <v>20</v>
       </c>
-      <c r="E11" s="32"/>
-      <c r="F11" s="32"/>
-      <c r="G11" s="32"/>
-      <c r="H11" s="32"/>
-      <c r="I11" s="32"/>
+      <c r="E11" s="33"/>
+      <c r="F11" s="33"/>
+      <c r="G11" s="33"/>
+      <c r="H11" s="33"/>
+      <c r="I11" s="33"/>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B12" s="4">
@@ -1092,10 +1092,10 @@
       <c r="F13" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="G13" s="32" t="s">
+      <c r="G13" s="33" t="s">
         <v>18</v>
       </c>
-      <c r="H13" s="32"/>
+      <c r="H13" s="33"/>
       <c r="I13" s="1" t="s">
         <v>14</v>
       </c>
@@ -1107,14 +1107,14 @@
       <c r="C14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D14" s="32" t="s">
+      <c r="D14" s="33" t="s">
         <v>19</v>
       </c>
-      <c r="E14" s="32"/>
-      <c r="F14" s="32"/>
-      <c r="G14" s="32"/>
-      <c r="H14" s="32"/>
-      <c r="I14" s="32"/>
+      <c r="E14" s="33"/>
+      <c r="F14" s="33"/>
+      <c r="G14" s="33"/>
+      <c r="H14" s="33"/>
+      <c r="I14" s="33"/>
     </row>
     <row r="15" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B15" s="4">
@@ -1201,14 +1201,14 @@
       <c r="C18" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D18" s="32" t="s">
+      <c r="D18" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="E18" s="32"/>
-      <c r="F18" s="32"/>
-      <c r="G18" s="32"/>
-      <c r="H18" s="32"/>
-      <c r="I18" s="32"/>
+      <c r="E18" s="33"/>
+      <c r="F18" s="33"/>
+      <c r="G18" s="33"/>
+      <c r="H18" s="33"/>
+      <c r="I18" s="33"/>
     </row>
     <row r="19" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B19" s="4">
@@ -1217,14 +1217,14 @@
       <c r="C19" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D19" s="32" t="s">
+      <c r="D19" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="E19" s="32"/>
-      <c r="F19" s="32"/>
-      <c r="G19" s="32"/>
-      <c r="H19" s="32"/>
-      <c r="I19" s="32"/>
+      <c r="E19" s="33"/>
+      <c r="F19" s="33"/>
+      <c r="G19" s="33"/>
+      <c r="H19" s="33"/>
+      <c r="I19" s="33"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B20" s="4">
@@ -1242,10 +1242,10 @@
       <c r="F20" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G20" s="32" t="s">
+      <c r="G20" s="33" t="s">
         <v>15</v>
       </c>
-      <c r="H20" s="32"/>
+      <c r="H20" s="33"/>
       <c r="I20" s="1" t="s">
         <v>14</v>
       </c>
@@ -1361,14 +1361,14 @@
       <c r="C25" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D25" s="32" t="s">
+      <c r="D25" s="33" t="s">
         <v>26</v>
       </c>
-      <c r="E25" s="32"/>
-      <c r="F25" s="32"/>
-      <c r="G25" s="32"/>
-      <c r="H25" s="32"/>
-      <c r="I25" s="32"/>
+      <c r="E25" s="33"/>
+      <c r="F25" s="33"/>
+      <c r="G25" s="33"/>
+      <c r="H25" s="33"/>
+      <c r="I25" s="33"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B26" s="4">
@@ -1412,10 +1412,10 @@
       <c r="F27" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G27" s="32" t="s">
+      <c r="G27" s="33" t="s">
         <v>18</v>
       </c>
-      <c r="H27" s="32"/>
+      <c r="H27" s="33"/>
       <c r="I27" s="1" t="s">
         <v>14</v>
       </c>
@@ -1479,14 +1479,14 @@
       <c r="C30" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D30" s="33" t="s">
+      <c r="D30" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="E30" s="33"/>
-      <c r="F30" s="33"/>
-      <c r="G30" s="33"/>
-      <c r="H30" s="33"/>
-      <c r="I30" s="33"/>
+      <c r="E30" s="32"/>
+      <c r="F30" s="32"/>
+      <c r="G30" s="32"/>
+      <c r="H30" s="32"/>
+      <c r="I30" s="32"/>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B31" s="4">
@@ -1495,14 +1495,14 @@
       <c r="C31" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D31" s="33" t="s">
+      <c r="D31" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="E31" s="33"/>
-      <c r="F31" s="33"/>
-      <c r="G31" s="33"/>
-      <c r="H31" s="33"/>
-      <c r="I31" s="33"/>
+      <c r="E31" s="32"/>
+      <c r="F31" s="32"/>
+      <c r="G31" s="32"/>
+      <c r="H31" s="32"/>
+      <c r="I31" s="32"/>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B32" s="4">
@@ -1537,14 +1537,14 @@
       <c r="C33" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D33" s="33" t="s">
+      <c r="D33" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="E33" s="33"/>
-      <c r="F33" s="33"/>
-      <c r="G33" s="33"/>
-      <c r="H33" s="33"/>
-      <c r="I33" s="33"/>
+      <c r="E33" s="32"/>
+      <c r="F33" s="32"/>
+      <c r="G33" s="32"/>
+      <c r="H33" s="32"/>
+      <c r="I33" s="32"/>
     </row>
     <row r="34" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B34" s="4">
@@ -1588,10 +1588,10 @@
       <c r="F35" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G35" s="33" t="s">
+      <c r="G35" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="H35" s="33"/>
+      <c r="H35" s="32"/>
       <c r="I35" s="1" t="s">
         <v>14</v>
       </c>
@@ -1707,14 +1707,14 @@
       <c r="C40" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D40" s="33" t="s">
+      <c r="D40" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="E40" s="33"/>
-      <c r="F40" s="33"/>
-      <c r="G40" s="33"/>
-      <c r="H40" s="33"/>
-      <c r="I40" s="33"/>
+      <c r="E40" s="32"/>
+      <c r="F40" s="32"/>
+      <c r="G40" s="32"/>
+      <c r="H40" s="32"/>
+      <c r="I40" s="32"/>
     </row>
     <row r="41" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B41" s="4">
@@ -1758,10 +1758,10 @@
       <c r="F42" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G42" s="33" t="s">
+      <c r="G42" s="32" t="s">
         <v>28</v>
       </c>
-      <c r="H42" s="33"/>
+      <c r="H42" s="32"/>
       <c r="I42" s="1" t="s">
         <v>15</v>
       </c>
@@ -1773,14 +1773,14 @@
       <c r="C43" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D43" s="33" t="s">
+      <c r="D43" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="E43" s="33"/>
-      <c r="F43" s="33"/>
-      <c r="G43" s="33"/>
-      <c r="H43" s="33"/>
-      <c r="I43" s="33"/>
+      <c r="E43" s="32"/>
+      <c r="F43" s="32"/>
+      <c r="G43" s="32"/>
+      <c r="H43" s="32"/>
+      <c r="I43" s="32"/>
     </row>
     <row r="44" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B44" s="4">
@@ -1844,14 +1844,14 @@
       <c r="C46" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D46" s="33" t="s">
+      <c r="D46" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="E46" s="33"/>
-      <c r="F46" s="33"/>
-      <c r="G46" s="33"/>
-      <c r="H46" s="33"/>
-      <c r="I46" s="33"/>
+      <c r="E46" s="32"/>
+      <c r="F46" s="32"/>
+      <c r="G46" s="32"/>
+      <c r="H46" s="32"/>
+      <c r="I46" s="32"/>
     </row>
     <row r="47" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B47" s="4">
@@ -1863,11 +1863,11 @@
       <c r="D47" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E47" s="25"/>
-      <c r="F47" s="25"/>
-      <c r="G47" s="25"/>
-      <c r="H47" s="25"/>
-      <c r="I47" s="24"/>
+      <c r="E47" s="24"/>
+      <c r="F47" s="24"/>
+      <c r="G47" s="24"/>
+      <c r="H47" s="24"/>
+      <c r="I47" s="25"/>
     </row>
     <row r="48" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B48" s="4">
@@ -1914,7 +1914,7 @@
       <c r="G49" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="H49" s="24"/>
+      <c r="H49" s="25"/>
       <c r="I49" s="1" t="s">
         <v>30</v>
       </c>
@@ -2056,14 +2056,14 @@
       <c r="C55" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="D55" s="25" t="s">
+      <c r="D55" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="E55" s="25"/>
-      <c r="F55" s="25"/>
-      <c r="G55" s="25"/>
-      <c r="H55" s="25"/>
-      <c r="I55" s="25"/>
+      <c r="E55" s="24"/>
+      <c r="F55" s="24"/>
+      <c r="G55" s="24"/>
+      <c r="H55" s="24"/>
+      <c r="I55" s="24"/>
     </row>
     <row r="56" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B56" s="4">
@@ -2110,7 +2110,7 @@
       <c r="G57" s="23" t="s">
         <v>37</v>
       </c>
-      <c r="H57" s="24"/>
+      <c r="H57" s="25"/>
       <c r="I57" s="1" t="s">
         <v>36</v>
       </c>
@@ -2177,11 +2177,11 @@
       <c r="D60" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E60" s="25"/>
-      <c r="F60" s="25"/>
-      <c r="G60" s="25"/>
-      <c r="H60" s="25"/>
-      <c r="I60" s="24"/>
+      <c r="E60" s="24"/>
+      <c r="F60" s="24"/>
+      <c r="G60" s="24"/>
+      <c r="H60" s="24"/>
+      <c r="I60" s="25"/>
     </row>
     <row r="61" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B61" s="4">
@@ -2193,11 +2193,11 @@
       <c r="D61" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E61" s="25"/>
-      <c r="F61" s="25"/>
-      <c r="G61" s="25"/>
-      <c r="H61" s="25"/>
-      <c r="I61" s="24"/>
+      <c r="E61" s="24"/>
+      <c r="F61" s="24"/>
+      <c r="G61" s="24"/>
+      <c r="H61" s="24"/>
+      <c r="I61" s="25"/>
     </row>
     <row r="62" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B62" s="4">
@@ -2209,11 +2209,11 @@
       <c r="D62" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E62" s="25"/>
-      <c r="F62" s="25"/>
-      <c r="G62" s="25"/>
-      <c r="H62" s="25"/>
-      <c r="I62" s="24"/>
+      <c r="E62" s="24"/>
+      <c r="F62" s="24"/>
+      <c r="G62" s="24"/>
+      <c r="H62" s="24"/>
+      <c r="I62" s="25"/>
     </row>
     <row r="63" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B63" s="4">
@@ -2260,7 +2260,7 @@
       <c r="G64" s="23" t="s">
         <v>37</v>
       </c>
-      <c r="H64" s="24"/>
+      <c r="H64" s="25"/>
       <c r="I64" s="1" t="s">
         <v>14</v>
       </c>
@@ -2301,10 +2301,10 @@
       <c r="D66" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="E66" s="25"/>
-      <c r="F66" s="25"/>
-      <c r="G66" s="25"/>
-      <c r="H66" s="24"/>
+      <c r="E66" s="24"/>
+      <c r="F66" s="24"/>
+      <c r="G66" s="24"/>
+      <c r="H66" s="25"/>
       <c r="I66" s="1" t="s">
         <v>16</v>
       </c>
@@ -2319,15 +2319,15 @@
       <c r="D67" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="E67" s="25"/>
-      <c r="F67" s="24"/>
+      <c r="E67" s="24"/>
+      <c r="F67" s="25"/>
       <c r="G67" s="3" t="s">
         <v>16</v>
       </c>
       <c r="H67" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="I67" s="24"/>
+      <c r="I67" s="25"/>
     </row>
     <row r="68" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B68" s="4">
@@ -2345,9 +2345,9 @@
       <c r="F68" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="G68" s="25"/>
-      <c r="H68" s="25"/>
-      <c r="I68" s="24"/>
+      <c r="G68" s="24"/>
+      <c r="H68" s="24"/>
+      <c r="I68" s="25"/>
     </row>
     <row r="69" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B69" s="4">
@@ -2359,11 +2359,11 @@
       <c r="D69" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E69" s="25"/>
-      <c r="F69" s="25"/>
-      <c r="G69" s="25"/>
-      <c r="H69" s="25"/>
-      <c r="I69" s="24"/>
+      <c r="E69" s="24"/>
+      <c r="F69" s="24"/>
+      <c r="G69" s="24"/>
+      <c r="H69" s="24"/>
+      <c r="I69" s="25"/>
     </row>
     <row r="70" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B70" s="4">
@@ -2375,7 +2375,7 @@
       <c r="D70" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="E70" s="24"/>
+      <c r="E70" s="25"/>
       <c r="F70" s="3" t="s">
         <v>15</v>
       </c>
@@ -2408,7 +2408,7 @@
       <c r="G71" s="23" t="s">
         <v>37</v>
       </c>
-      <c r="H71" s="24"/>
+      <c r="H71" s="25"/>
       <c r="I71" s="1" t="s">
         <v>14</v>
       </c>
@@ -2449,11 +2449,11 @@
       <c r="D73" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E73" s="25"/>
-      <c r="F73" s="25"/>
-      <c r="G73" s="25"/>
-      <c r="H73" s="25"/>
-      <c r="I73" s="24"/>
+      <c r="E73" s="24"/>
+      <c r="F73" s="24"/>
+      <c r="G73" s="24"/>
+      <c r="H73" s="24"/>
+      <c r="I73" s="25"/>
     </row>
     <row r="74" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B74" s="4">
@@ -2465,8 +2465,8 @@
       <c r="D74" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="E74" s="25"/>
-      <c r="F74" s="24"/>
+      <c r="E74" s="24"/>
+      <c r="F74" s="25"/>
       <c r="G74" s="3" t="s">
         <v>16</v>
       </c>
@@ -2505,11 +2505,11 @@
       <c r="D76" s="23" t="s">
         <v>39</v>
       </c>
-      <c r="E76" s="25"/>
-      <c r="F76" s="25"/>
-      <c r="G76" s="25"/>
-      <c r="H76" s="25"/>
-      <c r="I76" s="24"/>
+      <c r="E76" s="24"/>
+      <c r="F76" s="24"/>
+      <c r="G76" s="24"/>
+      <c r="H76" s="24"/>
+      <c r="I76" s="25"/>
     </row>
     <row r="77" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B77" s="4">
@@ -2521,11 +2521,11 @@
       <c r="D77" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E77" s="25"/>
-      <c r="F77" s="25"/>
-      <c r="G77" s="25"/>
-      <c r="H77" s="25"/>
-      <c r="I77" s="24"/>
+      <c r="E77" s="24"/>
+      <c r="F77" s="24"/>
+      <c r="G77" s="24"/>
+      <c r="H77" s="24"/>
+      <c r="I77" s="25"/>
     </row>
     <row r="78" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B78" s="4">
@@ -2537,11 +2537,11 @@
       <c r="D78" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E78" s="25"/>
-      <c r="F78" s="25"/>
-      <c r="G78" s="25"/>
-      <c r="H78" s="25"/>
-      <c r="I78" s="24"/>
+      <c r="E78" s="24"/>
+      <c r="F78" s="24"/>
+      <c r="G78" s="24"/>
+      <c r="H78" s="24"/>
+      <c r="I78" s="25"/>
     </row>
     <row r="79" spans="2:9" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B79" s="16" t="s">
@@ -2588,7 +2588,7 @@
       <c r="G80" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="H80" s="24"/>
+      <c r="H80" s="25"/>
       <c r="I80" s="1" t="s">
         <v>14</v>
       </c>
@@ -2612,7 +2612,7 @@
       <c r="G81" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="H81" s="24"/>
+      <c r="H81" s="25"/>
       <c r="I81" s="1" t="s">
         <v>16</v>
       </c>
@@ -2679,11 +2679,11 @@
       <c r="D84" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E84" s="25"/>
-      <c r="F84" s="25"/>
-      <c r="G84" s="25"/>
-      <c r="H84" s="25"/>
-      <c r="I84" s="24"/>
+      <c r="E84" s="24"/>
+      <c r="F84" s="24"/>
+      <c r="G84" s="24"/>
+      <c r="H84" s="24"/>
+      <c r="I84" s="25"/>
     </row>
     <row r="85" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B85" s="4">
@@ -2724,8 +2724,8 @@
       <c r="E86" s="23" t="s">
         <v>43</v>
       </c>
-      <c r="F86" s="25"/>
-      <c r="G86" s="24"/>
+      <c r="F86" s="24"/>
+      <c r="G86" s="25"/>
       <c r="H86" s="3" t="s">
         <v>14</v>
       </c>
@@ -2743,15 +2743,15 @@
       <c r="D87" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="E87" s="24"/>
+      <c r="E87" s="25"/>
       <c r="F87" s="3" t="s">
         <v>16</v>
       </c>
       <c r="G87" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="H87" s="25"/>
-      <c r="I87" s="24"/>
+      <c r="H87" s="24"/>
+      <c r="I87" s="25"/>
     </row>
     <row r="88" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B88" s="4">
@@ -2763,11 +2763,11 @@
       <c r="D88" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E88" s="25"/>
-      <c r="F88" s="25"/>
-      <c r="G88" s="25"/>
-      <c r="H88" s="25"/>
-      <c r="I88" s="24"/>
+      <c r="E88" s="24"/>
+      <c r="F88" s="24"/>
+      <c r="G88" s="24"/>
+      <c r="H88" s="24"/>
+      <c r="I88" s="25"/>
     </row>
     <row r="89" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B89" s="4">
@@ -2779,15 +2779,15 @@
       <c r="D89" s="23" t="s">
         <v>44</v>
       </c>
-      <c r="E89" s="25"/>
-      <c r="F89" s="24"/>
+      <c r="E89" s="24"/>
+      <c r="F89" s="25"/>
       <c r="G89" s="3" t="s">
         <v>16</v>
       </c>
       <c r="H89" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="I89" s="24"/>
+      <c r="I89" s="25"/>
     </row>
     <row r="90" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B90" s="4">
@@ -2799,7 +2799,7 @@
       <c r="D90" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="E90" s="24"/>
+      <c r="E90" s="25"/>
       <c r="F90" s="3" t="s">
         <v>16</v>
       </c>
@@ -2824,10 +2824,10 @@
       <c r="D91" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E91" s="25"/>
-      <c r="F91" s="25"/>
-      <c r="G91" s="25"/>
-      <c r="H91" s="24"/>
+      <c r="E91" s="24"/>
+      <c r="F91" s="24"/>
+      <c r="G91" s="24"/>
+      <c r="H91" s="25"/>
       <c r="I91" s="18" t="s">
         <v>45</v>
       </c>
@@ -2842,11 +2842,11 @@
       <c r="D92" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E92" s="25"/>
-      <c r="F92" s="25"/>
-      <c r="G92" s="25"/>
-      <c r="H92" s="25"/>
-      <c r="I92" s="24"/>
+      <c r="E92" s="24"/>
+      <c r="F92" s="24"/>
+      <c r="G92" s="24"/>
+      <c r="H92" s="24"/>
+      <c r="I92" s="25"/>
     </row>
     <row r="93" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B93" s="4">
@@ -2858,11 +2858,11 @@
       <c r="D93" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="E93" s="25"/>
-      <c r="F93" s="25"/>
-      <c r="G93" s="25"/>
-      <c r="H93" s="25"/>
-      <c r="I93" s="24"/>
+      <c r="E93" s="24"/>
+      <c r="F93" s="24"/>
+      <c r="G93" s="24"/>
+      <c r="H93" s="24"/>
+      <c r="I93" s="25"/>
     </row>
     <row r="94" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B94" s="4">
@@ -2874,11 +2874,11 @@
       <c r="D94" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="E94" s="25"/>
-      <c r="F94" s="25"/>
-      <c r="G94" s="25"/>
-      <c r="H94" s="25"/>
-      <c r="I94" s="24"/>
+      <c r="E94" s="24"/>
+      <c r="F94" s="24"/>
+      <c r="G94" s="24"/>
+      <c r="H94" s="24"/>
+      <c r="I94" s="25"/>
     </row>
     <row r="95" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B95" s="4">
@@ -2890,12 +2890,12 @@
       <c r="D95" s="23" t="s">
         <v>47</v>
       </c>
-      <c r="E95" s="25"/>
-      <c r="F95" s="24"/>
+      <c r="E95" s="24"/>
+      <c r="F95" s="25"/>
       <c r="G95" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="H95" s="24"/>
+      <c r="H95" s="25"/>
       <c r="I95" s="1" t="s">
         <v>14</v>
       </c>
@@ -2910,11 +2910,11 @@
       <c r="D96" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E96" s="25"/>
-      <c r="F96" s="25"/>
-      <c r="G96" s="25"/>
-      <c r="H96" s="25"/>
-      <c r="I96" s="24"/>
+      <c r="E96" s="24"/>
+      <c r="F96" s="24"/>
+      <c r="G96" s="24"/>
+      <c r="H96" s="24"/>
+      <c r="I96" s="25"/>
     </row>
     <row r="97" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B97" s="4">
@@ -2926,11 +2926,11 @@
       <c r="D97" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="E97" s="25"/>
-      <c r="F97" s="25"/>
-      <c r="G97" s="25"/>
-      <c r="H97" s="25"/>
-      <c r="I97" s="24"/>
+      <c r="E97" s="24"/>
+      <c r="F97" s="24"/>
+      <c r="G97" s="24"/>
+      <c r="H97" s="24"/>
+      <c r="I97" s="25"/>
     </row>
     <row r="98" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B98" s="4">
@@ -2942,11 +2942,11 @@
       <c r="D98" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E98" s="25"/>
-      <c r="F98" s="25"/>
-      <c r="G98" s="25"/>
-      <c r="H98" s="25"/>
-      <c r="I98" s="24"/>
+      <c r="E98" s="24"/>
+      <c r="F98" s="24"/>
+      <c r="G98" s="24"/>
+      <c r="H98" s="24"/>
+      <c r="I98" s="25"/>
     </row>
     <row r="99" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B99" s="4">
@@ -2958,9 +2958,9 @@
       <c r="D99" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="E99" s="25"/>
-      <c r="F99" s="25"/>
-      <c r="G99" s="24"/>
+      <c r="E99" s="24"/>
+      <c r="F99" s="24"/>
+      <c r="G99" s="25"/>
       <c r="H99" s="3" t="s">
         <v>49</v>
       </c>
@@ -2987,18 +2987,18 @@
       <c r="G100" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="H100" s="25"/>
-      <c r="I100" s="24"/>
+      <c r="H100" s="24"/>
+      <c r="I100" s="25"/>
     </row>
     <row r="101" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B101" s="23"/>
-      <c r="C101" s="25"/>
-      <c r="D101" s="25"/>
-      <c r="E101" s="25"/>
-      <c r="F101" s="25"/>
-      <c r="G101" s="25"/>
-      <c r="H101" s="25"/>
-      <c r="I101" s="24"/>
+      <c r="C101" s="24"/>
+      <c r="D101" s="24"/>
+      <c r="E101" s="24"/>
+      <c r="F101" s="24"/>
+      <c r="G101" s="24"/>
+      <c r="H101" s="24"/>
+      <c r="I101" s="25"/>
     </row>
     <row r="102" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B102" s="3"/>
@@ -3020,7 +3020,7 @@
       <c r="D103" s="23" t="s">
         <v>51</v>
       </c>
-      <c r="E103" s="24"/>
+      <c r="E103" s="25"/>
       <c r="F103" s="3"/>
       <c r="G103" s="3"/>
       <c r="H103" s="3"/>
@@ -3036,7 +3036,7 @@
       <c r="D104" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="E104" s="24"/>
+      <c r="E104" s="25"/>
       <c r="F104" s="3"/>
       <c r="G104" s="3"/>
       <c r="H104" s="3"/>
@@ -3052,7 +3052,7 @@
       <c r="D105" s="23" t="s">
         <v>53</v>
       </c>
-      <c r="E105" s="24"/>
+      <c r="E105" s="25"/>
       <c r="F105" s="3"/>
       <c r="G105" s="3"/>
       <c r="H105" s="3"/>
@@ -3068,7 +3068,7 @@
       <c r="D106" s="23" t="s">
         <v>54</v>
       </c>
-      <c r="E106" s="24"/>
+      <c r="E106" s="25"/>
       <c r="F106" s="3"/>
       <c r="G106" s="3"/>
       <c r="H106" s="3"/>
@@ -3084,7 +3084,7 @@
       <c r="D107" s="23" t="s">
         <v>55</v>
       </c>
-      <c r="E107" s="24"/>
+      <c r="E107" s="25"/>
       <c r="F107" s="3"/>
       <c r="G107" s="3"/>
       <c r="H107" s="3"/>
@@ -3100,7 +3100,7 @@
       <c r="D108" s="23" t="s">
         <v>56</v>
       </c>
-      <c r="E108" s="24"/>
+      <c r="E108" s="25"/>
       <c r="F108" s="3"/>
       <c r="G108" s="3"/>
       <c r="H108" s="3"/>
@@ -3137,28 +3137,28 @@
       <c r="I111" s="20"/>
     </row>
     <row r="112" spans="2:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B112" s="26" t="s">
+      <c r="B112" s="34" t="s">
         <v>57</v>
       </c>
-      <c r="C112" s="27"/>
-      <c r="D112" s="27"/>
-      <c r="E112" s="27"/>
-      <c r="F112" s="27"/>
-      <c r="G112" s="27"/>
-      <c r="H112" s="27"/>
-      <c r="I112" s="27"/>
-      <c r="J112" s="28"/>
+      <c r="C112" s="35"/>
+      <c r="D112" s="35"/>
+      <c r="E112" s="35"/>
+      <c r="F112" s="35"/>
+      <c r="G112" s="35"/>
+      <c r="H112" s="35"/>
+      <c r="I112" s="35"/>
+      <c r="J112" s="36"/>
     </row>
     <row r="113" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B113" s="29"/>
-      <c r="C113" s="30"/>
-      <c r="D113" s="30"/>
-      <c r="E113" s="30"/>
-      <c r="F113" s="30"/>
-      <c r="G113" s="30"/>
-      <c r="H113" s="30"/>
-      <c r="I113" s="30"/>
-      <c r="J113" s="31"/>
+      <c r="B113" s="37"/>
+      <c r="C113" s="38"/>
+      <c r="D113" s="38"/>
+      <c r="E113" s="38"/>
+      <c r="F113" s="38"/>
+      <c r="G113" s="38"/>
+      <c r="H113" s="38"/>
+      <c r="I113" s="38"/>
+      <c r="J113" s="39"/>
     </row>
     <row r="114" spans="2:10" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B114" s="8" t="s">
@@ -3292,10 +3292,10 @@
       <c r="F118" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="G118" s="25"/>
-      <c r="H118" s="25"/>
-      <c r="I118" s="25"/>
-      <c r="J118" s="24"/>
+      <c r="G118" s="24"/>
+      <c r="H118" s="24"/>
+      <c r="I118" s="24"/>
+      <c r="J118" s="25"/>
     </row>
     <row r="119" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B119" s="4">
@@ -3336,10 +3336,10 @@
       <c r="D120" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="E120" s="25"/>
-      <c r="F120" s="25"/>
-      <c r="G120" s="25"/>
-      <c r="H120" s="24"/>
+      <c r="E120" s="24"/>
+      <c r="F120" s="24"/>
+      <c r="G120" s="24"/>
+      <c r="H120" s="25"/>
       <c r="I120" s="1" t="s">
         <v>16</v>
       </c>
@@ -3357,12 +3357,12 @@
       <c r="D121" s="23" t="s">
         <v>65</v>
       </c>
-      <c r="E121" s="25"/>
-      <c r="F121" s="25"/>
-      <c r="G121" s="25"/>
-      <c r="H121" s="25"/>
-      <c r="I121" s="25"/>
-      <c r="J121" s="24"/>
+      <c r="E121" s="24"/>
+      <c r="F121" s="24"/>
+      <c r="G121" s="24"/>
+      <c r="H121" s="24"/>
+      <c r="I121" s="24"/>
+      <c r="J121" s="25"/>
     </row>
     <row r="122" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B122" s="4">
@@ -3412,9 +3412,9 @@
       <c r="G123" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="H123" s="25"/>
-      <c r="I123" s="25"/>
-      <c r="J123" s="24"/>
+      <c r="H123" s="24"/>
+      <c r="I123" s="24"/>
+      <c r="J123" s="25"/>
     </row>
     <row r="124" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B124" s="4">
@@ -3435,9 +3435,9 @@
       <c r="G124" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="H124" s="25"/>
-      <c r="I124" s="25"/>
-      <c r="J124" s="24"/>
+      <c r="H124" s="24"/>
+      <c r="I124" s="24"/>
+      <c r="J124" s="25"/>
     </row>
     <row r="125" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B125" s="4">
@@ -3455,10 +3455,10 @@
       <c r="F125" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="G125" s="25"/>
-      <c r="H125" s="25"/>
-      <c r="I125" s="25"/>
-      <c r="J125" s="24"/>
+      <c r="G125" s="24"/>
+      <c r="H125" s="24"/>
+      <c r="I125" s="24"/>
+      <c r="J125" s="25"/>
     </row>
     <row r="126" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B126" s="4">
@@ -3479,8 +3479,8 @@
       <c r="G126" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="H126" s="25"/>
-      <c r="I126" s="24"/>
+      <c r="H126" s="24"/>
+      <c r="I126" s="25"/>
       <c r="J126" s="1" t="s">
         <v>16</v>
       </c>
@@ -3501,10 +3501,10 @@
       <c r="F127" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="G127" s="25"/>
-      <c r="H127" s="25"/>
-      <c r="I127" s="25"/>
-      <c r="J127" s="24"/>
+      <c r="G127" s="24"/>
+      <c r="H127" s="24"/>
+      <c r="I127" s="24"/>
+      <c r="J127" s="25"/>
     </row>
     <row r="128" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B128" s="4">
@@ -3516,12 +3516,12 @@
       <c r="D128" s="23" t="s">
         <v>65</v>
       </c>
-      <c r="E128" s="25"/>
-      <c r="F128" s="25"/>
-      <c r="G128" s="25"/>
-      <c r="H128" s="25"/>
-      <c r="I128" s="25"/>
-      <c r="J128" s="24"/>
+      <c r="E128" s="24"/>
+      <c r="F128" s="24"/>
+      <c r="G128" s="24"/>
+      <c r="H128" s="24"/>
+      <c r="I128" s="24"/>
+      <c r="J128" s="25"/>
     </row>
     <row r="129" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B129" s="4">
@@ -3707,12 +3707,12 @@
       <c r="D135" s="23" t="s">
         <v>65</v>
       </c>
-      <c r="E135" s="25"/>
-      <c r="F135" s="25"/>
-      <c r="G135" s="25"/>
-      <c r="H135" s="25"/>
-      <c r="I135" s="25"/>
-      <c r="J135" s="24"/>
+      <c r="E135" s="24"/>
+      <c r="F135" s="24"/>
+      <c r="G135" s="24"/>
+      <c r="H135" s="24"/>
+      <c r="I135" s="24"/>
+      <c r="J135" s="25"/>
     </row>
     <row r="136" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B136" s="4">
@@ -3927,12 +3927,12 @@
       <c r="D143" s="23" t="s">
         <v>65</v>
       </c>
-      <c r="E143" s="25"/>
-      <c r="F143" s="25"/>
-      <c r="G143" s="25"/>
-      <c r="H143" s="25"/>
-      <c r="I143" s="25"/>
-      <c r="J143" s="24"/>
+      <c r="E143" s="24"/>
+      <c r="F143" s="24"/>
+      <c r="G143" s="24"/>
+      <c r="H143" s="24"/>
+      <c r="I143" s="24"/>
+      <c r="J143" s="25"/>
     </row>
     <row r="144" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B144" s="4">
@@ -4011,9 +4011,9 @@
       <c r="G146" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="H146" s="25"/>
-      <c r="I146" s="25"/>
-      <c r="J146" s="24"/>
+      <c r="H146" s="24"/>
+      <c r="I146" s="24"/>
+      <c r="J146" s="25"/>
     </row>
     <row r="147" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B147" s="4">
@@ -4080,15 +4080,15 @@
       <c r="C149" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D149" s="34" t="s">
+      <c r="D149" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="E149" s="35"/>
-      <c r="F149" s="35"/>
-      <c r="G149" s="35"/>
-      <c r="H149" s="35"/>
-      <c r="I149" s="35"/>
-      <c r="J149" s="36"/>
+      <c r="E149" s="27"/>
+      <c r="F149" s="27"/>
+      <c r="G149" s="27"/>
+      <c r="H149" s="27"/>
+      <c r="I149" s="27"/>
+      <c r="J149" s="30"/>
     </row>
     <row r="150" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B150" s="4">
@@ -4097,13 +4097,13 @@
       <c r="C150" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D150" s="37"/>
-      <c r="E150" s="38"/>
-      <c r="F150" s="38"/>
-      <c r="G150" s="38"/>
-      <c r="H150" s="38"/>
-      <c r="I150" s="38"/>
-      <c r="J150" s="39"/>
+      <c r="D150" s="28"/>
+      <c r="E150" s="29"/>
+      <c r="F150" s="29"/>
+      <c r="G150" s="29"/>
+      <c r="H150" s="29"/>
+      <c r="I150" s="29"/>
+      <c r="J150" s="31"/>
     </row>
     <row r="151" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B151" s="4">
@@ -4153,8 +4153,8 @@
       <c r="G152" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="H152" s="25"/>
-      <c r="I152" s="24"/>
+      <c r="H152" s="24"/>
+      <c r="I152" s="25"/>
       <c r="J152" s="1" t="s">
         <v>69</v>
       </c>
@@ -4285,12 +4285,12 @@
       <c r="D157" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E157" s="25"/>
-      <c r="F157" s="25"/>
-      <c r="G157" s="25"/>
-      <c r="H157" s="25"/>
-      <c r="I157" s="25"/>
-      <c r="J157" s="24"/>
+      <c r="E157" s="24"/>
+      <c r="F157" s="24"/>
+      <c r="G157" s="24"/>
+      <c r="H157" s="24"/>
+      <c r="I157" s="24"/>
+      <c r="J157" s="25"/>
     </row>
     <row r="158" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B158" s="4">
@@ -4474,12 +4474,12 @@
       <c r="D164" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E164" s="25"/>
-      <c r="F164" s="25"/>
-      <c r="G164" s="25"/>
-      <c r="H164" s="25"/>
-      <c r="I164" s="25"/>
-      <c r="J164" s="24"/>
+      <c r="E164" s="24"/>
+      <c r="F164" s="24"/>
+      <c r="G164" s="24"/>
+      <c r="H164" s="24"/>
+      <c r="I164" s="24"/>
+      <c r="J164" s="25"/>
     </row>
     <row r="165" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B165" s="4">
@@ -4680,12 +4680,12 @@
       <c r="D172" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E172" s="25"/>
-      <c r="F172" s="25"/>
-      <c r="G172" s="25"/>
-      <c r="H172" s="25"/>
-      <c r="I172" s="25"/>
-      <c r="J172" s="24"/>
+      <c r="E172" s="24"/>
+      <c r="F172" s="24"/>
+      <c r="G172" s="24"/>
+      <c r="H172" s="24"/>
+      <c r="I172" s="24"/>
+      <c r="J172" s="25"/>
     </row>
     <row r="173" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B173" s="4">
@@ -4749,29 +4749,29 @@
       <c r="B175" s="4">
         <v>45903</v>
       </c>
-      <c r="C175" s="34" t="s">
+      <c r="C175" s="26" t="s">
         <v>39</v>
       </c>
-      <c r="D175" s="35"/>
-      <c r="E175" s="35"/>
-      <c r="F175" s="35"/>
-      <c r="G175" s="35"/>
-      <c r="H175" s="35"/>
-      <c r="I175" s="35"/>
-      <c r="J175" s="35"/>
+      <c r="D175" s="27"/>
+      <c r="E175" s="27"/>
+      <c r="F175" s="27"/>
+      <c r="G175" s="27"/>
+      <c r="H175" s="27"/>
+      <c r="I175" s="27"/>
+      <c r="J175" s="27"/>
     </row>
     <row r="176" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B176" s="4">
         <v>45904</v>
       </c>
-      <c r="C176" s="37"/>
-      <c r="D176" s="38"/>
-      <c r="E176" s="38"/>
-      <c r="F176" s="38"/>
-      <c r="G176" s="38"/>
-      <c r="H176" s="38"/>
-      <c r="I176" s="38"/>
-      <c r="J176" s="38"/>
+      <c r="C176" s="28"/>
+      <c r="D176" s="29"/>
+      <c r="E176" s="29"/>
+      <c r="F176" s="29"/>
+      <c r="G176" s="29"/>
+      <c r="H176" s="29"/>
+      <c r="I176" s="29"/>
+      <c r="J176" s="29"/>
     </row>
     <row r="177" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B177" s="4">
@@ -4780,13 +4780,13 @@
       <c r="C177" s="23" t="s">
         <v>39</v>
       </c>
-      <c r="D177" s="25"/>
-      <c r="E177" s="25"/>
-      <c r="F177" s="25"/>
-      <c r="G177" s="25"/>
-      <c r="H177" s="25"/>
-      <c r="I177" s="25"/>
-      <c r="J177" s="24"/>
+      <c r="D177" s="24"/>
+      <c r="E177" s="24"/>
+      <c r="F177" s="24"/>
+      <c r="G177" s="24"/>
+      <c r="H177" s="24"/>
+      <c r="I177" s="24"/>
+      <c r="J177" s="25"/>
     </row>
     <row r="178" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B178" s="4">
@@ -4985,12 +4985,12 @@
       <c r="D185" s="23" t="s">
         <v>74</v>
       </c>
-      <c r="E185" s="25"/>
-      <c r="F185" s="25"/>
-      <c r="G185" s="25"/>
-      <c r="H185" s="25"/>
-      <c r="I185" s="25"/>
-      <c r="J185" s="24"/>
+      <c r="E185" s="24"/>
+      <c r="F185" s="24"/>
+      <c r="G185" s="24"/>
+      <c r="H185" s="24"/>
+      <c r="I185" s="24"/>
+      <c r="J185" s="25"/>
     </row>
     <row r="186" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B186" s="4">
@@ -5021,12 +5021,12 @@
       <c r="D187" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="E187" s="25"/>
-      <c r="F187" s="25"/>
-      <c r="G187" s="25"/>
-      <c r="H187" s="25"/>
-      <c r="I187" s="25"/>
-      <c r="J187" s="24"/>
+      <c r="E187" s="24"/>
+      <c r="F187" s="24"/>
+      <c r="G187" s="24"/>
+      <c r="H187" s="24"/>
+      <c r="I187" s="24"/>
+      <c r="J187" s="25"/>
     </row>
     <row r="188" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B188" s="3"/>
@@ -7549,35 +7549,50 @@
     </row>
   </sheetData>
   <mergeCells count="89">
-    <mergeCell ref="D187:J187"/>
-    <mergeCell ref="D185:J185"/>
-    <mergeCell ref="C175:J176"/>
-    <mergeCell ref="D164:J164"/>
-    <mergeCell ref="D157:J157"/>
-    <mergeCell ref="D120:H120"/>
-    <mergeCell ref="G123:J123"/>
-    <mergeCell ref="D121:J121"/>
-    <mergeCell ref="D143:J143"/>
-    <mergeCell ref="C177:J177"/>
-    <mergeCell ref="D135:J135"/>
-    <mergeCell ref="D172:J172"/>
-    <mergeCell ref="G146:J146"/>
-    <mergeCell ref="G152:I152"/>
-    <mergeCell ref="D149:J150"/>
-    <mergeCell ref="D31:I31"/>
-    <mergeCell ref="G35:H35"/>
-    <mergeCell ref="D40:I40"/>
-    <mergeCell ref="D33:I33"/>
-    <mergeCell ref="D46:I46"/>
-    <mergeCell ref="D43:I43"/>
-    <mergeCell ref="D78:I78"/>
-    <mergeCell ref="G71:H71"/>
-    <mergeCell ref="D76:I76"/>
-    <mergeCell ref="D66:H66"/>
-    <mergeCell ref="D77:I77"/>
-    <mergeCell ref="D73:I73"/>
-    <mergeCell ref="D70:E70"/>
-    <mergeCell ref="D74:F74"/>
+    <mergeCell ref="D106:E106"/>
+    <mergeCell ref="D99:G99"/>
+    <mergeCell ref="G126:I126"/>
+    <mergeCell ref="F125:J125"/>
+    <mergeCell ref="D128:J128"/>
+    <mergeCell ref="D103:E103"/>
+    <mergeCell ref="D104:E104"/>
+    <mergeCell ref="D105:E105"/>
+    <mergeCell ref="G100:I100"/>
+    <mergeCell ref="B101:I101"/>
+    <mergeCell ref="F127:J127"/>
+    <mergeCell ref="D107:E107"/>
+    <mergeCell ref="F118:J118"/>
+    <mergeCell ref="D108:E108"/>
+    <mergeCell ref="B112:J113"/>
+    <mergeCell ref="G124:J124"/>
+    <mergeCell ref="D98:I98"/>
+    <mergeCell ref="D94:I94"/>
+    <mergeCell ref="H89:I89"/>
+    <mergeCell ref="D89:F89"/>
+    <mergeCell ref="D97:I97"/>
+    <mergeCell ref="G64:H64"/>
+    <mergeCell ref="D96:I96"/>
+    <mergeCell ref="D95:F95"/>
+    <mergeCell ref="G95:H95"/>
+    <mergeCell ref="D92:I92"/>
+    <mergeCell ref="D93:I93"/>
+    <mergeCell ref="D90:E90"/>
+    <mergeCell ref="D91:H91"/>
+    <mergeCell ref="E86:G86"/>
+    <mergeCell ref="D88:I88"/>
+    <mergeCell ref="H67:I67"/>
+    <mergeCell ref="G81:H81"/>
+    <mergeCell ref="D67:F67"/>
+    <mergeCell ref="F68:I68"/>
+    <mergeCell ref="D87:E87"/>
+    <mergeCell ref="G87:I87"/>
+    <mergeCell ref="D60:I60"/>
+    <mergeCell ref="D62:I62"/>
+    <mergeCell ref="D61:I61"/>
+    <mergeCell ref="G49:H49"/>
+    <mergeCell ref="D47:I47"/>
+    <mergeCell ref="D55:I55"/>
+    <mergeCell ref="G57:H57"/>
     <mergeCell ref="D84:I84"/>
     <mergeCell ref="D69:I69"/>
     <mergeCell ref="D8:I8"/>
@@ -7594,50 +7609,35 @@
     <mergeCell ref="D30:I30"/>
     <mergeCell ref="G80:H80"/>
     <mergeCell ref="G42:H42"/>
-    <mergeCell ref="D60:I60"/>
-    <mergeCell ref="D62:I62"/>
-    <mergeCell ref="D61:I61"/>
-    <mergeCell ref="G49:H49"/>
-    <mergeCell ref="D47:I47"/>
-    <mergeCell ref="D55:I55"/>
-    <mergeCell ref="G57:H57"/>
-    <mergeCell ref="G64:H64"/>
-    <mergeCell ref="D96:I96"/>
-    <mergeCell ref="D95:F95"/>
-    <mergeCell ref="G95:H95"/>
-    <mergeCell ref="D92:I92"/>
-    <mergeCell ref="D93:I93"/>
-    <mergeCell ref="D90:E90"/>
-    <mergeCell ref="D91:H91"/>
-    <mergeCell ref="E86:G86"/>
-    <mergeCell ref="D88:I88"/>
-    <mergeCell ref="H67:I67"/>
-    <mergeCell ref="G81:H81"/>
-    <mergeCell ref="D67:F67"/>
-    <mergeCell ref="F68:I68"/>
-    <mergeCell ref="D87:E87"/>
-    <mergeCell ref="G87:I87"/>
-    <mergeCell ref="D98:I98"/>
-    <mergeCell ref="D94:I94"/>
-    <mergeCell ref="H89:I89"/>
-    <mergeCell ref="D89:F89"/>
-    <mergeCell ref="D97:I97"/>
-    <mergeCell ref="D106:E106"/>
-    <mergeCell ref="D99:G99"/>
-    <mergeCell ref="G126:I126"/>
-    <mergeCell ref="F125:J125"/>
-    <mergeCell ref="D128:J128"/>
-    <mergeCell ref="D103:E103"/>
-    <mergeCell ref="D104:E104"/>
-    <mergeCell ref="D105:E105"/>
-    <mergeCell ref="G100:I100"/>
-    <mergeCell ref="B101:I101"/>
-    <mergeCell ref="F127:J127"/>
-    <mergeCell ref="D107:E107"/>
-    <mergeCell ref="F118:J118"/>
-    <mergeCell ref="D108:E108"/>
-    <mergeCell ref="B112:J113"/>
-    <mergeCell ref="G124:J124"/>
+    <mergeCell ref="D78:I78"/>
+    <mergeCell ref="G71:H71"/>
+    <mergeCell ref="D76:I76"/>
+    <mergeCell ref="D66:H66"/>
+    <mergeCell ref="D77:I77"/>
+    <mergeCell ref="D73:I73"/>
+    <mergeCell ref="D70:E70"/>
+    <mergeCell ref="D74:F74"/>
+    <mergeCell ref="D31:I31"/>
+    <mergeCell ref="G35:H35"/>
+    <mergeCell ref="D40:I40"/>
+    <mergeCell ref="D33:I33"/>
+    <mergeCell ref="D46:I46"/>
+    <mergeCell ref="D43:I43"/>
+    <mergeCell ref="D120:H120"/>
+    <mergeCell ref="G123:J123"/>
+    <mergeCell ref="D121:J121"/>
+    <mergeCell ref="D143:J143"/>
+    <mergeCell ref="C177:J177"/>
+    <mergeCell ref="D135:J135"/>
+    <mergeCell ref="D172:J172"/>
+    <mergeCell ref="G146:J146"/>
+    <mergeCell ref="G152:I152"/>
+    <mergeCell ref="D149:J150"/>
+    <mergeCell ref="D187:J187"/>
+    <mergeCell ref="D185:J185"/>
+    <mergeCell ref="C175:J176"/>
+    <mergeCell ref="D164:J164"/>
+    <mergeCell ref="D157:J157"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/attendance_sheet.xlsx
+++ b/attendance_sheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\repositary\3rd_Year_5th_Semester\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C412C976-7AE6-44E6-9E07-A3074958DDF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBF564DB-B697-470C-9A45-3A2E87751EE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{EB654061-A886-47D1-BF86-9B1A84FCE7FB}"/>
+    <workbookView xWindow="2304" yWindow="2304" windowWidth="15000" windowHeight="7632" xr2:uid="{EB654061-A886-47D1-BF86-9B1A84FCE7FB}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -544,35 +544,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -590,6 +566,30 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -993,14 +993,14 @@
       <c r="C8" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D8" s="33" t="s">
+      <c r="D8" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="E8" s="33"/>
-      <c r="F8" s="33"/>
-      <c r="G8" s="33"/>
-      <c r="H8" s="33"/>
-      <c r="I8" s="33"/>
+      <c r="E8" s="32"/>
+      <c r="F8" s="32"/>
+      <c r="G8" s="32"/>
+      <c r="H8" s="32"/>
+      <c r="I8" s="32"/>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B9" s="4">
@@ -1009,14 +1009,14 @@
       <c r="C9" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D9" s="33" t="s">
+      <c r="D9" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="E9" s="33"/>
-      <c r="F9" s="33"/>
-      <c r="G9" s="33"/>
-      <c r="H9" s="33"/>
-      <c r="I9" s="33"/>
+      <c r="E9" s="32"/>
+      <c r="F9" s="32"/>
+      <c r="G9" s="32"/>
+      <c r="H9" s="32"/>
+      <c r="I9" s="32"/>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B10" s="4">
@@ -1025,14 +1025,14 @@
       <c r="C10" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D10" s="33" t="s">
+      <c r="D10" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="E10" s="33"/>
-      <c r="F10" s="33"/>
-      <c r="G10" s="33"/>
-      <c r="H10" s="33"/>
-      <c r="I10" s="33"/>
+      <c r="E10" s="32"/>
+      <c r="F10" s="32"/>
+      <c r="G10" s="32"/>
+      <c r="H10" s="32"/>
+      <c r="I10" s="32"/>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B11" s="4">
@@ -1041,14 +1041,14 @@
       <c r="C11" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D11" s="33" t="s">
+      <c r="D11" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="E11" s="33"/>
-      <c r="F11" s="33"/>
-      <c r="G11" s="33"/>
-      <c r="H11" s="33"/>
-      <c r="I11" s="33"/>
+      <c r="E11" s="32"/>
+      <c r="F11" s="32"/>
+      <c r="G11" s="32"/>
+      <c r="H11" s="32"/>
+      <c r="I11" s="32"/>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B12" s="4">
@@ -1092,10 +1092,10 @@
       <c r="F13" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="G13" s="33" t="s">
+      <c r="G13" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="H13" s="33"/>
+      <c r="H13" s="32"/>
       <c r="I13" s="1" t="s">
         <v>14</v>
       </c>
@@ -1107,14 +1107,14 @@
       <c r="C14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D14" s="33" t="s">
+      <c r="D14" s="32" t="s">
         <v>19</v>
       </c>
-      <c r="E14" s="33"/>
-      <c r="F14" s="33"/>
-      <c r="G14" s="33"/>
-      <c r="H14" s="33"/>
-      <c r="I14" s="33"/>
+      <c r="E14" s="32"/>
+      <c r="F14" s="32"/>
+      <c r="G14" s="32"/>
+      <c r="H14" s="32"/>
+      <c r="I14" s="32"/>
     </row>
     <row r="15" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B15" s="4">
@@ -1201,14 +1201,14 @@
       <c r="C18" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D18" s="33" t="s">
+      <c r="D18" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="E18" s="33"/>
-      <c r="F18" s="33"/>
-      <c r="G18" s="33"/>
-      <c r="H18" s="33"/>
-      <c r="I18" s="33"/>
+      <c r="E18" s="32"/>
+      <c r="F18" s="32"/>
+      <c r="G18" s="32"/>
+      <c r="H18" s="32"/>
+      <c r="I18" s="32"/>
     </row>
     <row r="19" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B19" s="4">
@@ -1217,14 +1217,14 @@
       <c r="C19" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D19" s="33" t="s">
+      <c r="D19" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="E19" s="33"/>
-      <c r="F19" s="33"/>
-      <c r="G19" s="33"/>
-      <c r="H19" s="33"/>
-      <c r="I19" s="33"/>
+      <c r="E19" s="32"/>
+      <c r="F19" s="32"/>
+      <c r="G19" s="32"/>
+      <c r="H19" s="32"/>
+      <c r="I19" s="32"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B20" s="4">
@@ -1242,10 +1242,10 @@
       <c r="F20" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G20" s="33" t="s">
+      <c r="G20" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="H20" s="33"/>
+      <c r="H20" s="32"/>
       <c r="I20" s="1" t="s">
         <v>14</v>
       </c>
@@ -1361,14 +1361,14 @@
       <c r="C25" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D25" s="33" t="s">
+      <c r="D25" s="32" t="s">
         <v>26</v>
       </c>
-      <c r="E25" s="33"/>
-      <c r="F25" s="33"/>
-      <c r="G25" s="33"/>
-      <c r="H25" s="33"/>
-      <c r="I25" s="33"/>
+      <c r="E25" s="32"/>
+      <c r="F25" s="32"/>
+      <c r="G25" s="32"/>
+      <c r="H25" s="32"/>
+      <c r="I25" s="32"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B26" s="4">
@@ -1412,10 +1412,10 @@
       <c r="F27" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G27" s="33" t="s">
+      <c r="G27" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="H27" s="33"/>
+      <c r="H27" s="32"/>
       <c r="I27" s="1" t="s">
         <v>14</v>
       </c>
@@ -1479,14 +1479,14 @@
       <c r="C30" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D30" s="32" t="s">
+      <c r="D30" s="33" t="s">
         <v>20</v>
       </c>
-      <c r="E30" s="32"/>
-      <c r="F30" s="32"/>
-      <c r="G30" s="32"/>
-      <c r="H30" s="32"/>
-      <c r="I30" s="32"/>
+      <c r="E30" s="33"/>
+      <c r="F30" s="33"/>
+      <c r="G30" s="33"/>
+      <c r="H30" s="33"/>
+      <c r="I30" s="33"/>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B31" s="4">
@@ -1495,14 +1495,14 @@
       <c r="C31" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D31" s="32" t="s">
+      <c r="D31" s="33" t="s">
         <v>20</v>
       </c>
-      <c r="E31" s="32"/>
-      <c r="F31" s="32"/>
-      <c r="G31" s="32"/>
-      <c r="H31" s="32"/>
-      <c r="I31" s="32"/>
+      <c r="E31" s="33"/>
+      <c r="F31" s="33"/>
+      <c r="G31" s="33"/>
+      <c r="H31" s="33"/>
+      <c r="I31" s="33"/>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B32" s="4">
@@ -1537,14 +1537,14 @@
       <c r="C33" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D33" s="32" t="s">
+      <c r="D33" s="33" t="s">
         <v>20</v>
       </c>
-      <c r="E33" s="32"/>
-      <c r="F33" s="32"/>
-      <c r="G33" s="32"/>
-      <c r="H33" s="32"/>
-      <c r="I33" s="32"/>
+      <c r="E33" s="33"/>
+      <c r="F33" s="33"/>
+      <c r="G33" s="33"/>
+      <c r="H33" s="33"/>
+      <c r="I33" s="33"/>
     </row>
     <row r="34" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B34" s="4">
@@ -1588,10 +1588,10 @@
       <c r="F35" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G35" s="32" t="s">
+      <c r="G35" s="33" t="s">
         <v>18</v>
       </c>
-      <c r="H35" s="32"/>
+      <c r="H35" s="33"/>
       <c r="I35" s="1" t="s">
         <v>14</v>
       </c>
@@ -1707,14 +1707,14 @@
       <c r="C40" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D40" s="32" t="s">
+      <c r="D40" s="33" t="s">
         <v>20</v>
       </c>
-      <c r="E40" s="32"/>
-      <c r="F40" s="32"/>
-      <c r="G40" s="32"/>
-      <c r="H40" s="32"/>
-      <c r="I40" s="32"/>
+      <c r="E40" s="33"/>
+      <c r="F40" s="33"/>
+      <c r="G40" s="33"/>
+      <c r="H40" s="33"/>
+      <c r="I40" s="33"/>
     </row>
     <row r="41" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B41" s="4">
@@ -1758,10 +1758,10 @@
       <c r="F42" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G42" s="32" t="s">
+      <c r="G42" s="33" t="s">
         <v>28</v>
       </c>
-      <c r="H42" s="32"/>
+      <c r="H42" s="33"/>
       <c r="I42" s="1" t="s">
         <v>15</v>
       </c>
@@ -1773,14 +1773,14 @@
       <c r="C43" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D43" s="32" t="s">
+      <c r="D43" s="33" t="s">
         <v>20</v>
       </c>
-      <c r="E43" s="32"/>
-      <c r="F43" s="32"/>
-      <c r="G43" s="32"/>
-      <c r="H43" s="32"/>
-      <c r="I43" s="32"/>
+      <c r="E43" s="33"/>
+      <c r="F43" s="33"/>
+      <c r="G43" s="33"/>
+      <c r="H43" s="33"/>
+      <c r="I43" s="33"/>
     </row>
     <row r="44" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B44" s="4">
@@ -1844,14 +1844,14 @@
       <c r="C46" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D46" s="32" t="s">
+      <c r="D46" s="33" t="s">
         <v>20</v>
       </c>
-      <c r="E46" s="32"/>
-      <c r="F46" s="32"/>
-      <c r="G46" s="32"/>
-      <c r="H46" s="32"/>
-      <c r="I46" s="32"/>
+      <c r="E46" s="33"/>
+      <c r="F46" s="33"/>
+      <c r="G46" s="33"/>
+      <c r="H46" s="33"/>
+      <c r="I46" s="33"/>
     </row>
     <row r="47" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B47" s="4">
@@ -1863,11 +1863,11 @@
       <c r="D47" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E47" s="24"/>
-      <c r="F47" s="24"/>
-      <c r="G47" s="24"/>
-      <c r="H47" s="24"/>
-      <c r="I47" s="25"/>
+      <c r="E47" s="25"/>
+      <c r="F47" s="25"/>
+      <c r="G47" s="25"/>
+      <c r="H47" s="25"/>
+      <c r="I47" s="24"/>
     </row>
     <row r="48" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B48" s="4">
@@ -1914,7 +1914,7 @@
       <c r="G49" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="H49" s="25"/>
+      <c r="H49" s="24"/>
       <c r="I49" s="1" t="s">
         <v>30</v>
       </c>
@@ -2056,14 +2056,14 @@
       <c r="C55" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="D55" s="24" t="s">
+      <c r="D55" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="E55" s="24"/>
-      <c r="F55" s="24"/>
-      <c r="G55" s="24"/>
-      <c r="H55" s="24"/>
-      <c r="I55" s="24"/>
+      <c r="E55" s="25"/>
+      <c r="F55" s="25"/>
+      <c r="G55" s="25"/>
+      <c r="H55" s="25"/>
+      <c r="I55" s="25"/>
     </row>
     <row r="56" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B56" s="4">
@@ -2110,7 +2110,7 @@
       <c r="G57" s="23" t="s">
         <v>37</v>
       </c>
-      <c r="H57" s="25"/>
+      <c r="H57" s="24"/>
       <c r="I57" s="1" t="s">
         <v>36</v>
       </c>
@@ -2177,11 +2177,11 @@
       <c r="D60" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E60" s="24"/>
-      <c r="F60" s="24"/>
-      <c r="G60" s="24"/>
-      <c r="H60" s="24"/>
-      <c r="I60" s="25"/>
+      <c r="E60" s="25"/>
+      <c r="F60" s="25"/>
+      <c r="G60" s="25"/>
+      <c r="H60" s="25"/>
+      <c r="I60" s="24"/>
     </row>
     <row r="61" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B61" s="4">
@@ -2193,11 +2193,11 @@
       <c r="D61" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E61" s="24"/>
-      <c r="F61" s="24"/>
-      <c r="G61" s="24"/>
-      <c r="H61" s="24"/>
-      <c r="I61" s="25"/>
+      <c r="E61" s="25"/>
+      <c r="F61" s="25"/>
+      <c r="G61" s="25"/>
+      <c r="H61" s="25"/>
+      <c r="I61" s="24"/>
     </row>
     <row r="62" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B62" s="4">
@@ -2209,11 +2209,11 @@
       <c r="D62" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E62" s="24"/>
-      <c r="F62" s="24"/>
-      <c r="G62" s="24"/>
-      <c r="H62" s="24"/>
-      <c r="I62" s="25"/>
+      <c r="E62" s="25"/>
+      <c r="F62" s="25"/>
+      <c r="G62" s="25"/>
+      <c r="H62" s="25"/>
+      <c r="I62" s="24"/>
     </row>
     <row r="63" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B63" s="4">
@@ -2260,7 +2260,7 @@
       <c r="G64" s="23" t="s">
         <v>37</v>
       </c>
-      <c r="H64" s="25"/>
+      <c r="H64" s="24"/>
       <c r="I64" s="1" t="s">
         <v>14</v>
       </c>
@@ -2301,10 +2301,10 @@
       <c r="D66" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="E66" s="24"/>
-      <c r="F66" s="24"/>
-      <c r="G66" s="24"/>
-      <c r="H66" s="25"/>
+      <c r="E66" s="25"/>
+      <c r="F66" s="25"/>
+      <c r="G66" s="25"/>
+      <c r="H66" s="24"/>
       <c r="I66" s="1" t="s">
         <v>16</v>
       </c>
@@ -2319,15 +2319,15 @@
       <c r="D67" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="E67" s="24"/>
-      <c r="F67" s="25"/>
+      <c r="E67" s="25"/>
+      <c r="F67" s="24"/>
       <c r="G67" s="3" t="s">
         <v>16</v>
       </c>
       <c r="H67" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="I67" s="25"/>
+      <c r="I67" s="24"/>
     </row>
     <row r="68" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B68" s="4">
@@ -2345,9 +2345,9 @@
       <c r="F68" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="G68" s="24"/>
-      <c r="H68" s="24"/>
-      <c r="I68" s="25"/>
+      <c r="G68" s="25"/>
+      <c r="H68" s="25"/>
+      <c r="I68" s="24"/>
     </row>
     <row r="69" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B69" s="4">
@@ -2359,11 +2359,11 @@
       <c r="D69" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E69" s="24"/>
-      <c r="F69" s="24"/>
-      <c r="G69" s="24"/>
-      <c r="H69" s="24"/>
-      <c r="I69" s="25"/>
+      <c r="E69" s="25"/>
+      <c r="F69" s="25"/>
+      <c r="G69" s="25"/>
+      <c r="H69" s="25"/>
+      <c r="I69" s="24"/>
     </row>
     <row r="70" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B70" s="4">
@@ -2375,7 +2375,7 @@
       <c r="D70" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="E70" s="25"/>
+      <c r="E70" s="24"/>
       <c r="F70" s="3" t="s">
         <v>15</v>
       </c>
@@ -2408,7 +2408,7 @@
       <c r="G71" s="23" t="s">
         <v>37</v>
       </c>
-      <c r="H71" s="25"/>
+      <c r="H71" s="24"/>
       <c r="I71" s="1" t="s">
         <v>14</v>
       </c>
@@ -2449,11 +2449,11 @@
       <c r="D73" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E73" s="24"/>
-      <c r="F73" s="24"/>
-      <c r="G73" s="24"/>
-      <c r="H73" s="24"/>
-      <c r="I73" s="25"/>
+      <c r="E73" s="25"/>
+      <c r="F73" s="25"/>
+      <c r="G73" s="25"/>
+      <c r="H73" s="25"/>
+      <c r="I73" s="24"/>
     </row>
     <row r="74" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B74" s="4">
@@ -2465,8 +2465,8 @@
       <c r="D74" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="E74" s="24"/>
-      <c r="F74" s="25"/>
+      <c r="E74" s="25"/>
+      <c r="F74" s="24"/>
       <c r="G74" s="3" t="s">
         <v>16</v>
       </c>
@@ -2505,11 +2505,11 @@
       <c r="D76" s="23" t="s">
         <v>39</v>
       </c>
-      <c r="E76" s="24"/>
-      <c r="F76" s="24"/>
-      <c r="G76" s="24"/>
-      <c r="H76" s="24"/>
-      <c r="I76" s="25"/>
+      <c r="E76" s="25"/>
+      <c r="F76" s="25"/>
+      <c r="G76" s="25"/>
+      <c r="H76" s="25"/>
+      <c r="I76" s="24"/>
     </row>
     <row r="77" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B77" s="4">
@@ -2521,11 +2521,11 @@
       <c r="D77" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E77" s="24"/>
-      <c r="F77" s="24"/>
-      <c r="G77" s="24"/>
-      <c r="H77" s="24"/>
-      <c r="I77" s="25"/>
+      <c r="E77" s="25"/>
+      <c r="F77" s="25"/>
+      <c r="G77" s="25"/>
+      <c r="H77" s="25"/>
+      <c r="I77" s="24"/>
     </row>
     <row r="78" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B78" s="4">
@@ -2537,11 +2537,11 @@
       <c r="D78" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E78" s="24"/>
-      <c r="F78" s="24"/>
-      <c r="G78" s="24"/>
-      <c r="H78" s="24"/>
-      <c r="I78" s="25"/>
+      <c r="E78" s="25"/>
+      <c r="F78" s="25"/>
+      <c r="G78" s="25"/>
+      <c r="H78" s="25"/>
+      <c r="I78" s="24"/>
     </row>
     <row r="79" spans="2:9" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B79" s="16" t="s">
@@ -2588,7 +2588,7 @@
       <c r="G80" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="H80" s="25"/>
+      <c r="H80" s="24"/>
       <c r="I80" s="1" t="s">
         <v>14</v>
       </c>
@@ -2612,7 +2612,7 @@
       <c r="G81" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="H81" s="25"/>
+      <c r="H81" s="24"/>
       <c r="I81" s="1" t="s">
         <v>16</v>
       </c>
@@ -2679,11 +2679,11 @@
       <c r="D84" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E84" s="24"/>
-      <c r="F84" s="24"/>
-      <c r="G84" s="24"/>
-      <c r="H84" s="24"/>
-      <c r="I84" s="25"/>
+      <c r="E84" s="25"/>
+      <c r="F84" s="25"/>
+      <c r="G84" s="25"/>
+      <c r="H84" s="25"/>
+      <c r="I84" s="24"/>
     </row>
     <row r="85" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B85" s="4">
@@ -2724,8 +2724,8 @@
       <c r="E86" s="23" t="s">
         <v>43</v>
       </c>
-      <c r="F86" s="24"/>
-      <c r="G86" s="25"/>
+      <c r="F86" s="25"/>
+      <c r="G86" s="24"/>
       <c r="H86" s="3" t="s">
         <v>14</v>
       </c>
@@ -2743,15 +2743,15 @@
       <c r="D87" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="E87" s="25"/>
+      <c r="E87" s="24"/>
       <c r="F87" s="3" t="s">
         <v>16</v>
       </c>
       <c r="G87" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="H87" s="24"/>
-      <c r="I87" s="25"/>
+      <c r="H87" s="25"/>
+      <c r="I87" s="24"/>
     </row>
     <row r="88" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B88" s="4">
@@ -2763,11 +2763,11 @@
       <c r="D88" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E88" s="24"/>
-      <c r="F88" s="24"/>
-      <c r="G88" s="24"/>
-      <c r="H88" s="24"/>
-      <c r="I88" s="25"/>
+      <c r="E88" s="25"/>
+      <c r="F88" s="25"/>
+      <c r="G88" s="25"/>
+      <c r="H88" s="25"/>
+      <c r="I88" s="24"/>
     </row>
     <row r="89" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B89" s="4">
@@ -2779,15 +2779,15 @@
       <c r="D89" s="23" t="s">
         <v>44</v>
       </c>
-      <c r="E89" s="24"/>
-      <c r="F89" s="25"/>
+      <c r="E89" s="25"/>
+      <c r="F89" s="24"/>
       <c r="G89" s="3" t="s">
         <v>16</v>
       </c>
       <c r="H89" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="I89" s="25"/>
+      <c r="I89" s="24"/>
     </row>
     <row r="90" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B90" s="4">
@@ -2799,7 +2799,7 @@
       <c r="D90" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="E90" s="25"/>
+      <c r="E90" s="24"/>
       <c r="F90" s="3" t="s">
         <v>16</v>
       </c>
@@ -2824,10 +2824,10 @@
       <c r="D91" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E91" s="24"/>
-      <c r="F91" s="24"/>
-      <c r="G91" s="24"/>
-      <c r="H91" s="25"/>
+      <c r="E91" s="25"/>
+      <c r="F91" s="25"/>
+      <c r="G91" s="25"/>
+      <c r="H91" s="24"/>
       <c r="I91" s="18" t="s">
         <v>45</v>
       </c>
@@ -2842,11 +2842,11 @@
       <c r="D92" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E92" s="24"/>
-      <c r="F92" s="24"/>
-      <c r="G92" s="24"/>
-      <c r="H92" s="24"/>
-      <c r="I92" s="25"/>
+      <c r="E92" s="25"/>
+      <c r="F92" s="25"/>
+      <c r="G92" s="25"/>
+      <c r="H92" s="25"/>
+      <c r="I92" s="24"/>
     </row>
     <row r="93" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B93" s="4">
@@ -2858,11 +2858,11 @@
       <c r="D93" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="E93" s="24"/>
-      <c r="F93" s="24"/>
-      <c r="G93" s="24"/>
-      <c r="H93" s="24"/>
-      <c r="I93" s="25"/>
+      <c r="E93" s="25"/>
+      <c r="F93" s="25"/>
+      <c r="G93" s="25"/>
+      <c r="H93" s="25"/>
+      <c r="I93" s="24"/>
     </row>
     <row r="94" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B94" s="4">
@@ -2874,11 +2874,11 @@
       <c r="D94" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="E94" s="24"/>
-      <c r="F94" s="24"/>
-      <c r="G94" s="24"/>
-      <c r="H94" s="24"/>
-      <c r="I94" s="25"/>
+      <c r="E94" s="25"/>
+      <c r="F94" s="25"/>
+      <c r="G94" s="25"/>
+      <c r="H94" s="25"/>
+      <c r="I94" s="24"/>
     </row>
     <row r="95" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B95" s="4">
@@ -2890,12 +2890,12 @@
       <c r="D95" s="23" t="s">
         <v>47</v>
       </c>
-      <c r="E95" s="24"/>
-      <c r="F95" s="25"/>
+      <c r="E95" s="25"/>
+      <c r="F95" s="24"/>
       <c r="G95" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="H95" s="25"/>
+      <c r="H95" s="24"/>
       <c r="I95" s="1" t="s">
         <v>14</v>
       </c>
@@ -2910,11 +2910,11 @@
       <c r="D96" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E96" s="24"/>
-      <c r="F96" s="24"/>
-      <c r="G96" s="24"/>
-      <c r="H96" s="24"/>
-      <c r="I96" s="25"/>
+      <c r="E96" s="25"/>
+      <c r="F96" s="25"/>
+      <c r="G96" s="25"/>
+      <c r="H96" s="25"/>
+      <c r="I96" s="24"/>
     </row>
     <row r="97" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B97" s="4">
@@ -2926,11 +2926,11 @@
       <c r="D97" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="E97" s="24"/>
-      <c r="F97" s="24"/>
-      <c r="G97" s="24"/>
-      <c r="H97" s="24"/>
-      <c r="I97" s="25"/>
+      <c r="E97" s="25"/>
+      <c r="F97" s="25"/>
+      <c r="G97" s="25"/>
+      <c r="H97" s="25"/>
+      <c r="I97" s="24"/>
     </row>
     <row r="98" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B98" s="4">
@@ -2942,11 +2942,11 @@
       <c r="D98" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E98" s="24"/>
-      <c r="F98" s="24"/>
-      <c r="G98" s="24"/>
-      <c r="H98" s="24"/>
-      <c r="I98" s="25"/>
+      <c r="E98" s="25"/>
+      <c r="F98" s="25"/>
+      <c r="G98" s="25"/>
+      <c r="H98" s="25"/>
+      <c r="I98" s="24"/>
     </row>
     <row r="99" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B99" s="4">
@@ -2958,9 +2958,9 @@
       <c r="D99" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="E99" s="24"/>
-      <c r="F99" s="24"/>
-      <c r="G99" s="25"/>
+      <c r="E99" s="25"/>
+      <c r="F99" s="25"/>
+      <c r="G99" s="24"/>
       <c r="H99" s="3" t="s">
         <v>49</v>
       </c>
@@ -2987,18 +2987,18 @@
       <c r="G100" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="H100" s="24"/>
-      <c r="I100" s="25"/>
+      <c r="H100" s="25"/>
+      <c r="I100" s="24"/>
     </row>
     <row r="101" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B101" s="23"/>
-      <c r="C101" s="24"/>
-      <c r="D101" s="24"/>
-      <c r="E101" s="24"/>
-      <c r="F101" s="24"/>
-      <c r="G101" s="24"/>
-      <c r="H101" s="24"/>
-      <c r="I101" s="25"/>
+      <c r="C101" s="25"/>
+      <c r="D101" s="25"/>
+      <c r="E101" s="25"/>
+      <c r="F101" s="25"/>
+      <c r="G101" s="25"/>
+      <c r="H101" s="25"/>
+      <c r="I101" s="24"/>
     </row>
     <row r="102" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B102" s="3"/>
@@ -3020,7 +3020,7 @@
       <c r="D103" s="23" t="s">
         <v>51</v>
       </c>
-      <c r="E103" s="25"/>
+      <c r="E103" s="24"/>
       <c r="F103" s="3"/>
       <c r="G103" s="3"/>
       <c r="H103" s="3"/>
@@ -3036,7 +3036,7 @@
       <c r="D104" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="E104" s="25"/>
+      <c r="E104" s="24"/>
       <c r="F104" s="3"/>
       <c r="G104" s="3"/>
       <c r="H104" s="3"/>
@@ -3052,7 +3052,7 @@
       <c r="D105" s="23" t="s">
         <v>53</v>
       </c>
-      <c r="E105" s="25"/>
+      <c r="E105" s="24"/>
       <c r="F105" s="3"/>
       <c r="G105" s="3"/>
       <c r="H105" s="3"/>
@@ -3068,7 +3068,7 @@
       <c r="D106" s="23" t="s">
         <v>54</v>
       </c>
-      <c r="E106" s="25"/>
+      <c r="E106" s="24"/>
       <c r="F106" s="3"/>
       <c r="G106" s="3"/>
       <c r="H106" s="3"/>
@@ -3084,7 +3084,7 @@
       <c r="D107" s="23" t="s">
         <v>55</v>
       </c>
-      <c r="E107" s="25"/>
+      <c r="E107" s="24"/>
       <c r="F107" s="3"/>
       <c r="G107" s="3"/>
       <c r="H107" s="3"/>
@@ -3100,7 +3100,7 @@
       <c r="D108" s="23" t="s">
         <v>56</v>
       </c>
-      <c r="E108" s="25"/>
+      <c r="E108" s="24"/>
       <c r="F108" s="3"/>
       <c r="G108" s="3"/>
       <c r="H108" s="3"/>
@@ -3137,28 +3137,28 @@
       <c r="I111" s="20"/>
     </row>
     <row r="112" spans="2:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B112" s="34" t="s">
+      <c r="B112" s="26" t="s">
         <v>57</v>
       </c>
-      <c r="C112" s="35"/>
-      <c r="D112" s="35"/>
-      <c r="E112" s="35"/>
-      <c r="F112" s="35"/>
-      <c r="G112" s="35"/>
-      <c r="H112" s="35"/>
-      <c r="I112" s="35"/>
-      <c r="J112" s="36"/>
+      <c r="C112" s="27"/>
+      <c r="D112" s="27"/>
+      <c r="E112" s="27"/>
+      <c r="F112" s="27"/>
+      <c r="G112" s="27"/>
+      <c r="H112" s="27"/>
+      <c r="I112" s="27"/>
+      <c r="J112" s="28"/>
     </row>
     <row r="113" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B113" s="37"/>
-      <c r="C113" s="38"/>
-      <c r="D113" s="38"/>
-      <c r="E113" s="38"/>
-      <c r="F113" s="38"/>
-      <c r="G113" s="38"/>
-      <c r="H113" s="38"/>
-      <c r="I113" s="38"/>
-      <c r="J113" s="39"/>
+      <c r="B113" s="29"/>
+      <c r="C113" s="30"/>
+      <c r="D113" s="30"/>
+      <c r="E113" s="30"/>
+      <c r="F113" s="30"/>
+      <c r="G113" s="30"/>
+      <c r="H113" s="30"/>
+      <c r="I113" s="30"/>
+      <c r="J113" s="31"/>
     </row>
     <row r="114" spans="2:10" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B114" s="8" t="s">
@@ -3292,10 +3292,10 @@
       <c r="F118" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="G118" s="24"/>
-      <c r="H118" s="24"/>
-      <c r="I118" s="24"/>
-      <c r="J118" s="25"/>
+      <c r="G118" s="25"/>
+      <c r="H118" s="25"/>
+      <c r="I118" s="25"/>
+      <c r="J118" s="24"/>
     </row>
     <row r="119" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B119" s="4">
@@ -3336,10 +3336,10 @@
       <c r="D120" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="E120" s="24"/>
-      <c r="F120" s="24"/>
-      <c r="G120" s="24"/>
-      <c r="H120" s="25"/>
+      <c r="E120" s="25"/>
+      <c r="F120" s="25"/>
+      <c r="G120" s="25"/>
+      <c r="H120" s="24"/>
       <c r="I120" s="1" t="s">
         <v>16</v>
       </c>
@@ -3357,12 +3357,12 @@
       <c r="D121" s="23" t="s">
         <v>65</v>
       </c>
-      <c r="E121" s="24"/>
-      <c r="F121" s="24"/>
-      <c r="G121" s="24"/>
-      <c r="H121" s="24"/>
-      <c r="I121" s="24"/>
-      <c r="J121" s="25"/>
+      <c r="E121" s="25"/>
+      <c r="F121" s="25"/>
+      <c r="G121" s="25"/>
+      <c r="H121" s="25"/>
+      <c r="I121" s="25"/>
+      <c r="J121" s="24"/>
     </row>
     <row r="122" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B122" s="4">
@@ -3412,9 +3412,9 @@
       <c r="G123" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="H123" s="24"/>
-      <c r="I123" s="24"/>
-      <c r="J123" s="25"/>
+      <c r="H123" s="25"/>
+      <c r="I123" s="25"/>
+      <c r="J123" s="24"/>
     </row>
     <row r="124" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B124" s="4">
@@ -3435,9 +3435,9 @@
       <c r="G124" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="H124" s="24"/>
-      <c r="I124" s="24"/>
-      <c r="J124" s="25"/>
+      <c r="H124" s="25"/>
+      <c r="I124" s="25"/>
+      <c r="J124" s="24"/>
     </row>
     <row r="125" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B125" s="4">
@@ -3455,10 +3455,10 @@
       <c r="F125" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="G125" s="24"/>
-      <c r="H125" s="24"/>
-      <c r="I125" s="24"/>
-      <c r="J125" s="25"/>
+      <c r="G125" s="25"/>
+      <c r="H125" s="25"/>
+      <c r="I125" s="25"/>
+      <c r="J125" s="24"/>
     </row>
     <row r="126" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B126" s="4">
@@ -3479,8 +3479,8 @@
       <c r="G126" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="H126" s="24"/>
-      <c r="I126" s="25"/>
+      <c r="H126" s="25"/>
+      <c r="I126" s="24"/>
       <c r="J126" s="1" t="s">
         <v>16</v>
       </c>
@@ -3501,10 +3501,10 @@
       <c r="F127" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="G127" s="24"/>
-      <c r="H127" s="24"/>
-      <c r="I127" s="24"/>
-      <c r="J127" s="25"/>
+      <c r="G127" s="25"/>
+      <c r="H127" s="25"/>
+      <c r="I127" s="25"/>
+      <c r="J127" s="24"/>
     </row>
     <row r="128" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B128" s="4">
@@ -3516,12 +3516,12 @@
       <c r="D128" s="23" t="s">
         <v>65</v>
       </c>
-      <c r="E128" s="24"/>
-      <c r="F128" s="24"/>
-      <c r="G128" s="24"/>
-      <c r="H128" s="24"/>
-      <c r="I128" s="24"/>
-      <c r="J128" s="25"/>
+      <c r="E128" s="25"/>
+      <c r="F128" s="25"/>
+      <c r="G128" s="25"/>
+      <c r="H128" s="25"/>
+      <c r="I128" s="25"/>
+      <c r="J128" s="24"/>
     </row>
     <row r="129" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B129" s="4">
@@ -3707,12 +3707,12 @@
       <c r="D135" s="23" t="s">
         <v>65</v>
       </c>
-      <c r="E135" s="24"/>
-      <c r="F135" s="24"/>
-      <c r="G135" s="24"/>
-      <c r="H135" s="24"/>
-      <c r="I135" s="24"/>
-      <c r="J135" s="25"/>
+      <c r="E135" s="25"/>
+      <c r="F135" s="25"/>
+      <c r="G135" s="25"/>
+      <c r="H135" s="25"/>
+      <c r="I135" s="25"/>
+      <c r="J135" s="24"/>
     </row>
     <row r="136" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B136" s="4">
@@ -3927,12 +3927,12 @@
       <c r="D143" s="23" t="s">
         <v>65</v>
       </c>
-      <c r="E143" s="24"/>
-      <c r="F143" s="24"/>
-      <c r="G143" s="24"/>
-      <c r="H143" s="24"/>
-      <c r="I143" s="24"/>
-      <c r="J143" s="25"/>
+      <c r="E143" s="25"/>
+      <c r="F143" s="25"/>
+      <c r="G143" s="25"/>
+      <c r="H143" s="25"/>
+      <c r="I143" s="25"/>
+      <c r="J143" s="24"/>
     </row>
     <row r="144" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B144" s="4">
@@ -4011,9 +4011,9 @@
       <c r="G146" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="H146" s="24"/>
-      <c r="I146" s="24"/>
-      <c r="J146" s="25"/>
+      <c r="H146" s="25"/>
+      <c r="I146" s="25"/>
+      <c r="J146" s="24"/>
     </row>
     <row r="147" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B147" s="4">
@@ -4080,15 +4080,15 @@
       <c r="C149" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D149" s="26" t="s">
+      <c r="D149" s="34" t="s">
         <v>20</v>
       </c>
-      <c r="E149" s="27"/>
-      <c r="F149" s="27"/>
-      <c r="G149" s="27"/>
-      <c r="H149" s="27"/>
-      <c r="I149" s="27"/>
-      <c r="J149" s="30"/>
+      <c r="E149" s="35"/>
+      <c r="F149" s="35"/>
+      <c r="G149" s="35"/>
+      <c r="H149" s="35"/>
+      <c r="I149" s="35"/>
+      <c r="J149" s="36"/>
     </row>
     <row r="150" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B150" s="4">
@@ -4097,13 +4097,13 @@
       <c r="C150" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D150" s="28"/>
-      <c r="E150" s="29"/>
-      <c r="F150" s="29"/>
-      <c r="G150" s="29"/>
-      <c r="H150" s="29"/>
-      <c r="I150" s="29"/>
-      <c r="J150" s="31"/>
+      <c r="D150" s="37"/>
+      <c r="E150" s="38"/>
+      <c r="F150" s="38"/>
+      <c r="G150" s="38"/>
+      <c r="H150" s="38"/>
+      <c r="I150" s="38"/>
+      <c r="J150" s="39"/>
     </row>
     <row r="151" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B151" s="4">
@@ -4153,8 +4153,8 @@
       <c r="G152" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="H152" s="24"/>
-      <c r="I152" s="25"/>
+      <c r="H152" s="25"/>
+      <c r="I152" s="24"/>
       <c r="J152" s="1" t="s">
         <v>69</v>
       </c>
@@ -4285,12 +4285,12 @@
       <c r="D157" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E157" s="24"/>
-      <c r="F157" s="24"/>
-      <c r="G157" s="24"/>
-      <c r="H157" s="24"/>
-      <c r="I157" s="24"/>
-      <c r="J157" s="25"/>
+      <c r="E157" s="25"/>
+      <c r="F157" s="25"/>
+      <c r="G157" s="25"/>
+      <c r="H157" s="25"/>
+      <c r="I157" s="25"/>
+      <c r="J157" s="24"/>
     </row>
     <row r="158" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B158" s="4">
@@ -4474,12 +4474,12 @@
       <c r="D164" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E164" s="24"/>
-      <c r="F164" s="24"/>
-      <c r="G164" s="24"/>
-      <c r="H164" s="24"/>
-      <c r="I164" s="24"/>
-      <c r="J164" s="25"/>
+      <c r="E164" s="25"/>
+      <c r="F164" s="25"/>
+      <c r="G164" s="25"/>
+      <c r="H164" s="25"/>
+      <c r="I164" s="25"/>
+      <c r="J164" s="24"/>
     </row>
     <row r="165" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B165" s="4">
@@ -4680,12 +4680,12 @@
       <c r="D172" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E172" s="24"/>
-      <c r="F172" s="24"/>
-      <c r="G172" s="24"/>
-      <c r="H172" s="24"/>
-      <c r="I172" s="24"/>
-      <c r="J172" s="25"/>
+      <c r="E172" s="25"/>
+      <c r="F172" s="25"/>
+      <c r="G172" s="25"/>
+      <c r="H172" s="25"/>
+      <c r="I172" s="25"/>
+      <c r="J172" s="24"/>
     </row>
     <row r="173" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B173" s="4">
@@ -4749,29 +4749,29 @@
       <c r="B175" s="4">
         <v>45903</v>
       </c>
-      <c r="C175" s="26" t="s">
+      <c r="C175" s="34" t="s">
         <v>39</v>
       </c>
-      <c r="D175" s="27"/>
-      <c r="E175" s="27"/>
-      <c r="F175" s="27"/>
-      <c r="G175" s="27"/>
-      <c r="H175" s="27"/>
-      <c r="I175" s="27"/>
-      <c r="J175" s="27"/>
+      <c r="D175" s="35"/>
+      <c r="E175" s="35"/>
+      <c r="F175" s="35"/>
+      <c r="G175" s="35"/>
+      <c r="H175" s="35"/>
+      <c r="I175" s="35"/>
+      <c r="J175" s="35"/>
     </row>
     <row r="176" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B176" s="4">
         <v>45904</v>
       </c>
-      <c r="C176" s="28"/>
-      <c r="D176" s="29"/>
-      <c r="E176" s="29"/>
-      <c r="F176" s="29"/>
-      <c r="G176" s="29"/>
-      <c r="H176" s="29"/>
-      <c r="I176" s="29"/>
-      <c r="J176" s="29"/>
+      <c r="C176" s="37"/>
+      <c r="D176" s="38"/>
+      <c r="E176" s="38"/>
+      <c r="F176" s="38"/>
+      <c r="G176" s="38"/>
+      <c r="H176" s="38"/>
+      <c r="I176" s="38"/>
+      <c r="J176" s="38"/>
     </row>
     <row r="177" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B177" s="4">
@@ -4780,13 +4780,13 @@
       <c r="C177" s="23" t="s">
         <v>39</v>
       </c>
-      <c r="D177" s="24"/>
-      <c r="E177" s="24"/>
-      <c r="F177" s="24"/>
-      <c r="G177" s="24"/>
-      <c r="H177" s="24"/>
-      <c r="I177" s="24"/>
-      <c r="J177" s="25"/>
+      <c r="D177" s="25"/>
+      <c r="E177" s="25"/>
+      <c r="F177" s="25"/>
+      <c r="G177" s="25"/>
+      <c r="H177" s="25"/>
+      <c r="I177" s="25"/>
+      <c r="J177" s="24"/>
     </row>
     <row r="178" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B178" s="4">
@@ -4985,12 +4985,12 @@
       <c r="D185" s="23" t="s">
         <v>74</v>
       </c>
-      <c r="E185" s="24"/>
-      <c r="F185" s="24"/>
-      <c r="G185" s="24"/>
-      <c r="H185" s="24"/>
-      <c r="I185" s="24"/>
-      <c r="J185" s="25"/>
+      <c r="E185" s="25"/>
+      <c r="F185" s="25"/>
+      <c r="G185" s="25"/>
+      <c r="H185" s="25"/>
+      <c r="I185" s="25"/>
+      <c r="J185" s="24"/>
     </row>
     <row r="186" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B186" s="4">
@@ -5021,12 +5021,12 @@
       <c r="D187" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="E187" s="24"/>
-      <c r="F187" s="24"/>
-      <c r="G187" s="24"/>
-      <c r="H187" s="24"/>
-      <c r="I187" s="24"/>
-      <c r="J187" s="25"/>
+      <c r="E187" s="25"/>
+      <c r="F187" s="25"/>
+      <c r="G187" s="25"/>
+      <c r="H187" s="25"/>
+      <c r="I187" s="25"/>
+      <c r="J187" s="24"/>
     </row>
     <row r="188" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B188" s="3"/>
@@ -7549,6 +7549,79 @@
     </row>
   </sheetData>
   <mergeCells count="89">
+    <mergeCell ref="D187:J187"/>
+    <mergeCell ref="D185:J185"/>
+    <mergeCell ref="C175:J176"/>
+    <mergeCell ref="D164:J164"/>
+    <mergeCell ref="D157:J157"/>
+    <mergeCell ref="D120:H120"/>
+    <mergeCell ref="G123:J123"/>
+    <mergeCell ref="D121:J121"/>
+    <mergeCell ref="D143:J143"/>
+    <mergeCell ref="C177:J177"/>
+    <mergeCell ref="D135:J135"/>
+    <mergeCell ref="D172:J172"/>
+    <mergeCell ref="G146:J146"/>
+    <mergeCell ref="G152:I152"/>
+    <mergeCell ref="D149:J150"/>
+    <mergeCell ref="D31:I31"/>
+    <mergeCell ref="G35:H35"/>
+    <mergeCell ref="D40:I40"/>
+    <mergeCell ref="D33:I33"/>
+    <mergeCell ref="D46:I46"/>
+    <mergeCell ref="D43:I43"/>
+    <mergeCell ref="D78:I78"/>
+    <mergeCell ref="G71:H71"/>
+    <mergeCell ref="D76:I76"/>
+    <mergeCell ref="D66:H66"/>
+    <mergeCell ref="D77:I77"/>
+    <mergeCell ref="D73:I73"/>
+    <mergeCell ref="D70:E70"/>
+    <mergeCell ref="D74:F74"/>
+    <mergeCell ref="D84:I84"/>
+    <mergeCell ref="D69:I69"/>
+    <mergeCell ref="D8:I8"/>
+    <mergeCell ref="D9:I9"/>
+    <mergeCell ref="D10:I10"/>
+    <mergeCell ref="D11:I11"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="D14:I14"/>
+    <mergeCell ref="G27:H27"/>
+    <mergeCell ref="D25:I25"/>
+    <mergeCell ref="G20:H20"/>
+    <mergeCell ref="D19:I19"/>
+    <mergeCell ref="D18:I18"/>
+    <mergeCell ref="D30:I30"/>
+    <mergeCell ref="G80:H80"/>
+    <mergeCell ref="G42:H42"/>
+    <mergeCell ref="D60:I60"/>
+    <mergeCell ref="D62:I62"/>
+    <mergeCell ref="D61:I61"/>
+    <mergeCell ref="G49:H49"/>
+    <mergeCell ref="D47:I47"/>
+    <mergeCell ref="D55:I55"/>
+    <mergeCell ref="G57:H57"/>
+    <mergeCell ref="G64:H64"/>
+    <mergeCell ref="D96:I96"/>
+    <mergeCell ref="D95:F95"/>
+    <mergeCell ref="G95:H95"/>
+    <mergeCell ref="D92:I92"/>
+    <mergeCell ref="D93:I93"/>
+    <mergeCell ref="D90:E90"/>
+    <mergeCell ref="D91:H91"/>
+    <mergeCell ref="E86:G86"/>
+    <mergeCell ref="D88:I88"/>
+    <mergeCell ref="H67:I67"/>
+    <mergeCell ref="G81:H81"/>
+    <mergeCell ref="D67:F67"/>
+    <mergeCell ref="F68:I68"/>
+    <mergeCell ref="D87:E87"/>
+    <mergeCell ref="G87:I87"/>
+    <mergeCell ref="D98:I98"/>
+    <mergeCell ref="D94:I94"/>
+    <mergeCell ref="H89:I89"/>
+    <mergeCell ref="D89:F89"/>
+    <mergeCell ref="D97:I97"/>
     <mergeCell ref="D106:E106"/>
     <mergeCell ref="D99:G99"/>
     <mergeCell ref="G126:I126"/>
@@ -7565,79 +7638,6 @@
     <mergeCell ref="D108:E108"/>
     <mergeCell ref="B112:J113"/>
     <mergeCell ref="G124:J124"/>
-    <mergeCell ref="D98:I98"/>
-    <mergeCell ref="D94:I94"/>
-    <mergeCell ref="H89:I89"/>
-    <mergeCell ref="D89:F89"/>
-    <mergeCell ref="D97:I97"/>
-    <mergeCell ref="G64:H64"/>
-    <mergeCell ref="D96:I96"/>
-    <mergeCell ref="D95:F95"/>
-    <mergeCell ref="G95:H95"/>
-    <mergeCell ref="D92:I92"/>
-    <mergeCell ref="D93:I93"/>
-    <mergeCell ref="D90:E90"/>
-    <mergeCell ref="D91:H91"/>
-    <mergeCell ref="E86:G86"/>
-    <mergeCell ref="D88:I88"/>
-    <mergeCell ref="H67:I67"/>
-    <mergeCell ref="G81:H81"/>
-    <mergeCell ref="D67:F67"/>
-    <mergeCell ref="F68:I68"/>
-    <mergeCell ref="D87:E87"/>
-    <mergeCell ref="G87:I87"/>
-    <mergeCell ref="D60:I60"/>
-    <mergeCell ref="D62:I62"/>
-    <mergeCell ref="D61:I61"/>
-    <mergeCell ref="G49:H49"/>
-    <mergeCell ref="D47:I47"/>
-    <mergeCell ref="D55:I55"/>
-    <mergeCell ref="G57:H57"/>
-    <mergeCell ref="D84:I84"/>
-    <mergeCell ref="D69:I69"/>
-    <mergeCell ref="D8:I8"/>
-    <mergeCell ref="D9:I9"/>
-    <mergeCell ref="D10:I10"/>
-    <mergeCell ref="D11:I11"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="D14:I14"/>
-    <mergeCell ref="G27:H27"/>
-    <mergeCell ref="D25:I25"/>
-    <mergeCell ref="G20:H20"/>
-    <mergeCell ref="D19:I19"/>
-    <mergeCell ref="D18:I18"/>
-    <mergeCell ref="D30:I30"/>
-    <mergeCell ref="G80:H80"/>
-    <mergeCell ref="G42:H42"/>
-    <mergeCell ref="D78:I78"/>
-    <mergeCell ref="G71:H71"/>
-    <mergeCell ref="D76:I76"/>
-    <mergeCell ref="D66:H66"/>
-    <mergeCell ref="D77:I77"/>
-    <mergeCell ref="D73:I73"/>
-    <mergeCell ref="D70:E70"/>
-    <mergeCell ref="D74:F74"/>
-    <mergeCell ref="D31:I31"/>
-    <mergeCell ref="G35:H35"/>
-    <mergeCell ref="D40:I40"/>
-    <mergeCell ref="D33:I33"/>
-    <mergeCell ref="D46:I46"/>
-    <mergeCell ref="D43:I43"/>
-    <mergeCell ref="D120:H120"/>
-    <mergeCell ref="G123:J123"/>
-    <mergeCell ref="D121:J121"/>
-    <mergeCell ref="D143:J143"/>
-    <mergeCell ref="C177:J177"/>
-    <mergeCell ref="D135:J135"/>
-    <mergeCell ref="D172:J172"/>
-    <mergeCell ref="G146:J146"/>
-    <mergeCell ref="G152:I152"/>
-    <mergeCell ref="D149:J150"/>
-    <mergeCell ref="D187:J187"/>
-    <mergeCell ref="D185:J185"/>
-    <mergeCell ref="C175:J176"/>
-    <mergeCell ref="D164:J164"/>
-    <mergeCell ref="D157:J157"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
